--- a/anciens_eleves.xlsx
+++ b/anciens_eleves.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bruno\Nextcloud2\Boulot 2026\Site orientation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bruno\Nextcloud4\Boulot 2026\Site orientation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FA5455E-D69E-4FDF-8EC2-1371C1877342}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0CBF58B-7B1B-4282-A958-67FC39C73BAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Elèves_BCPST" sheetId="1" r:id="rId1"/>
@@ -22,11 +22,22 @@
     <sheet name="Stats" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2471" uniqueCount="1016">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2473" uniqueCount="1017">
   <si>
     <t>Statistiques 2025</t>
   </si>
@@ -3081,6 +3092,9 @@
   </si>
   <si>
     <t>https://youtu.be/mUE_eBgYsfk</t>
+  </si>
+  <si>
+    <t>https://youtu.be/nZCwqNyJkJg</t>
   </si>
 </sst>
 </file>
@@ -3700,11 +3714,11 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="24" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -4055,17 +4069,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I110"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" customWidth="1"/>
-    <col min="2" max="2" width="14.28515625" customWidth="1"/>
+    <col min="1" max="1" width="27.44140625" customWidth="1"/>
+    <col min="2" max="2" width="14.33203125" customWidth="1"/>
     <col min="3" max="3" width="17" customWidth="1"/>
-    <col min="4" max="4" width="8.5703125" customWidth="1"/>
+    <col min="4" max="4" width="8.5546875" customWidth="1"/>
     <col min="5" max="5" width="9" customWidth="1"/>
-    <col min="6" max="6" width="44.85546875" customWidth="1"/>
+    <col min="6" max="6" width="44.88671875" customWidth="1"/>
     <col min="7" max="7" width="18" customWidth="1"/>
     <col min="8" max="8" width="28" customWidth="1"/>
-    <col min="9" max="9" width="21.42578125" customWidth="1"/>
+    <col min="9" max="9" width="21.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -6402,13 +6416,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:N127"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" customWidth="1"/>
-    <col min="2" max="2" width="16.5703125" customWidth="1"/>
-    <col min="6" max="6" width="42.28515625" customWidth="1"/>
-    <col min="8" max="8" width="32.28515625" customWidth="1"/>
-    <col min="9" max="9" width="96.7109375" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" customWidth="1"/>
+    <col min="2" max="2" width="16.5546875" customWidth="1"/>
+    <col min="6" max="6" width="42.33203125" customWidth="1"/>
+    <col min="8" max="8" width="32.33203125" customWidth="1"/>
+    <col min="9" max="9" width="96.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
@@ -8810,7 +8824,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="113" spans="1:6">
+    <row r="113" spans="1:8">
       <c r="A113" s="9" t="s">
         <v>464</v>
       </c>
@@ -8831,7 +8845,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="114" spans="1:6">
+    <row r="114" spans="1:8">
       <c r="A114" s="9" t="s">
         <v>465</v>
       </c>
@@ -8852,7 +8866,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="115" spans="1:6">
+    <row r="115" spans="1:8">
       <c r="A115" s="9" t="s">
         <v>467</v>
       </c>
@@ -8873,7 +8887,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="116" spans="1:6">
+    <row r="116" spans="1:8">
       <c r="A116" s="9" t="s">
         <v>469</v>
       </c>
@@ -8893,8 +8907,11 @@
       <c r="F116" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="117" spans="1:6">
+      <c r="H116" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8">
       <c r="A117" s="9" t="s">
         <v>471</v>
       </c>
@@ -8914,8 +8931,11 @@
       <c r="F117" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="118" spans="1:6">
+      <c r="H117" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8">
       <c r="A118" s="9" t="s">
         <v>473</v>
       </c>
@@ -8936,7 +8956,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="119" spans="1:6">
+    <row r="119" spans="1:8">
       <c r="A119" s="9" t="s">
         <v>475</v>
       </c>
@@ -8957,7 +8977,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="120" spans="1:6">
+    <row r="120" spans="1:8">
       <c r="A120" s="9" t="s">
         <v>476</v>
       </c>
@@ -8978,7 +8998,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="121" spans="1:6">
+    <row r="121" spans="1:8">
       <c r="A121" s="9" t="s">
         <v>478</v>
       </c>
@@ -8999,7 +9019,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="122" spans="1:6">
+    <row r="122" spans="1:8">
       <c r="A122" s="9" t="s">
         <v>480</v>
       </c>
@@ -9020,7 +9040,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="123" spans="1:6">
+    <row r="123" spans="1:8">
       <c r="A123" s="9" t="s">
         <v>482</v>
       </c>
@@ -9041,7 +9061,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="124" spans="1:6">
+    <row r="124" spans="1:8">
       <c r="A124" s="9" t="s">
         <v>483</v>
       </c>
@@ -9062,7 +9082,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="125" spans="1:6">
+    <row r="125" spans="1:8">
       <c r="A125" t="s">
         <v>484</v>
       </c>
@@ -9083,7 +9103,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="126" spans="1:6">
+    <row r="126" spans="1:8">
       <c r="A126" s="9" t="s">
         <v>485</v>
       </c>
@@ -9104,7 +9124,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="127" spans="1:6">
+    <row r="127" spans="1:8">
       <c r="B127" s="1" t="str">
         <f t="shared" si="13"/>
         <v/>
@@ -9149,20 +9169,20 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:M73"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="22.28515625" style="3" customWidth="1"/>
-    <col min="2" max="6" width="11.42578125" style="3" customWidth="1"/>
-    <col min="7" max="7" width="69.140625" style="3" customWidth="1"/>
-    <col min="8" max="8" width="11.42578125" style="3" customWidth="1"/>
-    <col min="9" max="9" width="21.42578125" style="3" customWidth="1"/>
-    <col min="10" max="10" width="42.42578125" style="3" customWidth="1"/>
-    <col min="11" max="11" width="72.28515625" style="3" customWidth="1"/>
-    <col min="12" max="12" width="11.42578125" style="3" customWidth="1"/>
-    <col min="13" max="16384" width="11.42578125" style="3"/>
+    <col min="1" max="1" width="22.33203125" style="3" customWidth="1"/>
+    <col min="2" max="6" width="11.44140625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="69.109375" style="3" customWidth="1"/>
+    <col min="8" max="8" width="11.44140625" style="3" customWidth="1"/>
+    <col min="9" max="9" width="21.44140625" style="3" customWidth="1"/>
+    <col min="10" max="10" width="42.44140625" style="3" customWidth="1"/>
+    <col min="11" max="11" width="72.33203125" style="3" customWidth="1"/>
+    <col min="12" max="12" width="11.44140625" style="3" customWidth="1"/>
+    <col min="13" max="16384" width="11.44140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="39.950000000000003" customHeight="1">
+    <row r="1" spans="1:12" ht="39.9" customHeight="1">
       <c r="A1" s="3" t="s">
         <v>74</v>
       </c>
@@ -9200,7 +9220,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="39.950000000000003" customHeight="1">
+    <row r="2" spans="1:12" ht="39.9" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>126</v>
       </c>
@@ -9235,7 +9255,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="39.950000000000003" customHeight="1">
+    <row r="3" spans="1:12" ht="39.9" customHeight="1">
       <c r="A3" s="3" t="s">
         <v>115</v>
       </c>
@@ -9273,7 +9293,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="39.950000000000003" customHeight="1">
+    <row r="4" spans="1:12" ht="39.9" customHeight="1">
       <c r="A4" s="3" t="s">
         <v>37</v>
       </c>
@@ -9308,7 +9328,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="39.950000000000003" customHeight="1">
+    <row r="5" spans="1:12" ht="39.9" customHeight="1">
       <c r="A5" s="3" t="s">
         <v>122</v>
       </c>
@@ -9346,7 +9366,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="39.950000000000003" customHeight="1">
+    <row r="6" spans="1:12" ht="39.9" customHeight="1">
       <c r="A6" s="3" t="s">
         <v>104</v>
       </c>
@@ -9384,7 +9404,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="39.950000000000003" customHeight="1">
+    <row r="7" spans="1:12" ht="39.9" customHeight="1">
       <c r="A7" s="3" t="s">
         <v>283</v>
       </c>
@@ -9419,7 +9439,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="39.950000000000003" customHeight="1">
+    <row r="8" spans="1:12" ht="39.9" customHeight="1">
       <c r="A8" s="3" t="s">
         <v>112</v>
       </c>
@@ -9457,7 +9477,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="39.950000000000003" customHeight="1">
+    <row r="9" spans="1:12" ht="39.9" customHeight="1">
       <c r="A9" s="3" t="s">
         <v>136</v>
       </c>
@@ -9495,7 +9515,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="39.950000000000003" customHeight="1">
+    <row r="10" spans="1:12" ht="39.9" customHeight="1">
       <c r="A10" s="3" t="s">
         <v>99</v>
       </c>
@@ -9530,7 +9550,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="39.950000000000003" customHeight="1">
+    <row r="11" spans="1:12" ht="39.9" customHeight="1">
       <c r="A11" s="3" t="s">
         <v>345</v>
       </c>
@@ -9565,7 +9585,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="39.950000000000003" customHeight="1">
+    <row r="12" spans="1:12" ht="39.9" customHeight="1">
       <c r="A12" s="3" t="s">
         <v>370</v>
       </c>
@@ -9600,7 +9620,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="39.950000000000003" customHeight="1">
+    <row r="13" spans="1:12" ht="39.9" customHeight="1">
       <c r="A13" s="3" t="s">
         <v>142</v>
       </c>
@@ -9635,7 +9655,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="39.950000000000003" customHeight="1">
+    <row r="14" spans="1:12" ht="39.9" customHeight="1">
       <c r="A14" s="3" t="s">
         <v>258</v>
       </c>
@@ -9670,7 +9690,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="39.950000000000003" customHeight="1">
+    <row r="15" spans="1:12" ht="39.9" customHeight="1">
       <c r="A15" s="3" t="s">
         <v>232</v>
       </c>
@@ -9702,7 +9722,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="39.950000000000003" customHeight="1">
+    <row r="16" spans="1:12" ht="39.9" customHeight="1">
       <c r="A16" s="3" t="s">
         <v>88</v>
       </c>
@@ -9731,7 +9751,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="39.950000000000003" customHeight="1">
+    <row r="17" spans="1:12" ht="39.9" customHeight="1">
       <c r="A17" s="3" t="s">
         <v>169</v>
       </c>
@@ -9766,7 +9786,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="39.950000000000003" customHeight="1">
+    <row r="18" spans="1:12" ht="39.9" customHeight="1">
       <c r="A18" s="3" t="s">
         <v>91</v>
       </c>
@@ -9801,7 +9821,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="39.950000000000003" customHeight="1">
+    <row r="19" spans="1:12" ht="39.9" customHeight="1">
       <c r="A19" s="3" t="s">
         <v>194</v>
       </c>
@@ -9839,7 +9859,7 @@
         <v>988</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="39.950000000000003" customHeight="1">
+    <row r="20" spans="1:12" ht="39.9" customHeight="1">
       <c r="A20" s="3" t="s">
         <v>145</v>
       </c>
@@ -9874,7 +9894,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="39.950000000000003" customHeight="1">
+    <row r="21" spans="1:12" ht="39.9" customHeight="1">
       <c r="A21" s="3" t="s">
         <v>85</v>
       </c>
@@ -9909,7 +9929,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="39.950000000000003" customHeight="1">
+    <row r="22" spans="1:12" ht="39.9" customHeight="1">
       <c r="A22" s="3" t="s">
         <v>119</v>
       </c>
@@ -9944,7 +9964,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="39.950000000000003" customHeight="1">
+    <row r="23" spans="1:12" ht="39.9" customHeight="1">
       <c r="A23" s="3" t="s">
         <v>595</v>
       </c>
@@ -9979,7 +9999,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="39.950000000000003" customHeight="1">
+    <row r="24" spans="1:12" ht="39.9" customHeight="1">
       <c r="A24" s="3" t="s">
         <v>334</v>
       </c>
@@ -10014,7 +10034,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="39.950000000000003" customHeight="1">
+    <row r="25" spans="1:12" ht="39.9" customHeight="1">
       <c r="A25" s="3" t="s">
         <v>605</v>
       </c>
@@ -10049,7 +10069,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="39.950000000000003" customHeight="1">
+    <row r="26" spans="1:12" ht="39.9" customHeight="1">
       <c r="A26" s="3" t="s">
         <v>107</v>
       </c>
@@ -10084,7 +10104,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="39.950000000000003" customHeight="1">
+    <row r="27" spans="1:12" ht="39.9" customHeight="1">
       <c r="A27" s="3" t="s">
         <v>94</v>
       </c>
@@ -10119,7 +10139,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="39.950000000000003" customHeight="1">
+    <row r="28" spans="1:12" ht="39.9" customHeight="1">
       <c r="A28" s="3" t="s">
         <v>129</v>
       </c>
@@ -10154,7 +10174,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="39.950000000000003" customHeight="1">
+    <row r="29" spans="1:12" ht="39.9" customHeight="1">
       <c r="A29" s="3" t="s">
         <v>322</v>
       </c>
@@ -10189,7 +10209,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="39.950000000000003" customHeight="1">
+    <row r="30" spans="1:12" ht="39.9" customHeight="1">
       <c r="A30" s="3" t="s">
         <v>324</v>
       </c>
@@ -10224,7 +10244,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="39.950000000000003" customHeight="1">
+    <row r="31" spans="1:12" ht="39.9" customHeight="1">
       <c r="A31" s="6" t="s">
         <v>340</v>
       </c>
@@ -10259,7 +10279,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="39.950000000000003" customHeight="1">
+    <row r="32" spans="1:12" ht="39.9" customHeight="1">
       <c r="A32" s="6" t="s">
         <v>267</v>
       </c>
@@ -10297,7 +10317,7 @@
         <v>996</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="39.950000000000003" customHeight="1">
+    <row r="33" spans="1:12" ht="39.9" customHeight="1">
       <c r="A33" s="6" t="s">
         <v>353</v>
       </c>
@@ -10332,7 +10352,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="39.950000000000003" customHeight="1">
+    <row r="34" spans="1:12" ht="39.9" customHeight="1">
       <c r="A34" s="3" t="s">
         <v>212</v>
       </c>
@@ -10367,7 +10387,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="39.950000000000003" customHeight="1">
+    <row r="35" spans="1:12" ht="39.9" customHeight="1">
       <c r="A35" s="3" t="s">
         <v>407</v>
       </c>
@@ -11142,7 +11162,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="86.45" customHeight="1">
+    <row r="58" spans="1:11" ht="86.4" customHeight="1">
       <c r="A58" s="13" t="s">
         <v>766</v>
       </c>
@@ -11547,7 +11567,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="71" spans="1:13" ht="105">
+    <row r="71" spans="1:13" ht="100.8">
       <c r="A71" s="3" t="s">
         <v>952</v>
       </c>
@@ -11585,7 +11605,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="72" spans="1:13" ht="150">
+    <row r="72" spans="1:13" ht="129.6">
       <c r="A72" s="3" t="s">
         <v>961</v>
       </c>
@@ -11623,7 +11643,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="73" spans="1:13" ht="75">
+    <row r="73" spans="1:13" ht="72">
       <c r="A73" s="3" t="s">
         <v>1008</v>
       </c>
@@ -11700,10 +11720,10 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G18"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
-    <col min="5" max="5" width="23.7109375" customWidth="1"/>
-    <col min="6" max="6" width="24.85546875" customWidth="1"/>
+    <col min="5" max="5" width="23.6640625" customWidth="1"/>
+    <col min="6" max="6" width="24.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -11881,7 +11901,7 @@
       <c r="F13" s="20"/>
       <c r="G13" s="1"/>
     </row>
-    <row r="14" spans="1:7" ht="28.9" customHeight="1">
+    <row r="14" spans="1:7" ht="28.95" customHeight="1">
       <c r="A14" s="27" t="s">
         <v>695</v>
       </c>
@@ -11937,7 +11957,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:Q172"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="40"/>
@@ -12061,7 +12081,7 @@
       </c>
     </row>
     <row r="28" spans="1:17">
-      <c r="A28" s="88" t="s">
+      <c r="A28" s="87" t="s">
         <v>843</v>
       </c>
       <c r="B28" s="86"/>
@@ -12100,8 +12120,8 @@
       <c r="P29" s="86"/>
       <c r="Q29" s="86"/>
     </row>
-    <row r="30" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A30" s="87" t="s">
+    <row r="30" spans="1:17" ht="14.4" customHeight="1">
+      <c r="A30" s="88" t="s">
         <v>20</v>
       </c>
       <c r="B30" s="85" t="s">
@@ -12180,7 +12200,7 @@
       <c r="P31" s="86"/>
       <c r="Q31" s="86"/>
     </row>
-    <row r="32" spans="1:17" ht="43.15" customHeight="1">
+    <row r="32" spans="1:17" ht="43.2" customHeight="1">
       <c r="A32" s="43" t="s">
         <v>844</v>
       </c>
@@ -12232,7 +12252,7 @@
       </c>
     </row>
     <row r="33" spans="1:17">
-      <c r="A33" s="88" t="s">
+      <c r="A33" s="87" t="s">
         <v>644</v>
       </c>
       <c r="B33" s="86"/>
@@ -12271,8 +12291,8 @@
       <c r="P34" s="86"/>
       <c r="Q34" s="86"/>
     </row>
-    <row r="35" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A35" s="87" t="s">
+    <row r="35" spans="1:17" ht="14.4" customHeight="1">
+      <c r="A35" s="88" t="s">
         <v>20</v>
       </c>
       <c r="B35" s="85" t="s">
@@ -12402,7 +12422,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="38" spans="1:17" ht="30">
+    <row r="38" spans="1:17">
       <c r="A38" s="43" t="s">
         <v>845</v>
       </c>
@@ -12453,7 +12473,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="28.9" customHeight="1">
+    <row r="39" spans="1:17" ht="28.95" customHeight="1">
       <c r="A39" s="43" t="s">
         <v>68</v>
       </c>
@@ -12570,7 +12590,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="1:17" ht="43.15" customHeight="1">
+    <row r="42" spans="1:17" ht="43.2" customHeight="1">
       <c r="A42" s="46" t="s">
         <v>848</v>
       </c>
@@ -12613,7 +12633,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:17" ht="30">
+    <row r="43" spans="1:17">
       <c r="A43" s="43" t="s">
         <v>849</v>
       </c>
@@ -12646,7 +12666,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="44" spans="1:17" ht="28.9" customHeight="1">
+    <row r="44" spans="1:17" ht="28.95" customHeight="1">
       <c r="A44" s="43" t="s">
         <v>773</v>
       </c>
@@ -12679,7 +12699,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:17" ht="28.9" customHeight="1">
+    <row r="45" spans="1:17" ht="28.95" customHeight="1">
       <c r="A45" s="43" t="s">
         <v>766</v>
       </c>
@@ -12712,7 +12732,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:17" ht="43.15" customHeight="1">
+    <row r="46" spans="1:17" ht="43.2" customHeight="1">
       <c r="A46" s="43" t="s">
         <v>778</v>
       </c>
@@ -12789,7 +12809,7 @@
       </c>
     </row>
     <row r="48" spans="1:17">
-      <c r="A48" s="88" t="s">
+      <c r="A48" s="87" t="s">
         <v>851</v>
       </c>
       <c r="B48" s="86"/>
@@ -12828,8 +12848,8 @@
       <c r="P49" s="86"/>
       <c r="Q49" s="86"/>
     </row>
-    <row r="50" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A50" s="87" t="s">
+    <row r="50" spans="1:17" ht="14.4" customHeight="1">
+      <c r="A50" s="88" t="s">
         <v>20</v>
       </c>
       <c r="B50" s="85" t="s">
@@ -12960,7 +12980,7 @@
       </c>
     </row>
     <row r="53" spans="1:17">
-      <c r="A53" s="88" t="s">
+      <c r="A53" s="87" t="s">
         <v>853</v>
       </c>
       <c r="B53" s="86"/>
@@ -12999,8 +13019,8 @@
       <c r="P54" s="86"/>
       <c r="Q54" s="86"/>
     </row>
-    <row r="55" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A55" s="87" t="s">
+    <row r="55" spans="1:17" ht="14.4" customHeight="1">
+      <c r="A55" s="88" t="s">
         <v>20</v>
       </c>
       <c r="B55" s="85" t="s">
@@ -13079,7 +13099,7 @@
       <c r="P56" s="86"/>
       <c r="Q56" s="86"/>
     </row>
-    <row r="57" spans="1:17" ht="28.9" customHeight="1">
+    <row r="57" spans="1:17" ht="28.95" customHeight="1">
       <c r="A57" s="43" t="s">
         <v>34</v>
       </c>
@@ -13145,7 +13165,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="43.15" customHeight="1">
+    <row r="59" spans="1:17" ht="43.2" customHeight="1">
       <c r="A59" s="43" t="s">
         <v>37</v>
       </c>
@@ -13178,7 +13198,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="43.15" customHeight="1">
+    <row r="60" spans="1:17" ht="43.2" customHeight="1">
       <c r="A60" s="43" t="s">
         <v>40</v>
       </c>
@@ -13211,7 +13231,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="28.9" customHeight="1">
+    <row r="61" spans="1:17" ht="28.95" customHeight="1">
       <c r="A61" s="43" t="s">
         <v>39</v>
       </c>
@@ -13244,7 +13264,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="100.9" customHeight="1">
+    <row r="62" spans="1:17" ht="100.95" customHeight="1">
       <c r="A62" s="43" t="s">
         <v>36</v>
       </c>
@@ -13310,7 +13330,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="115.15" customHeight="1">
+    <row r="64" spans="1:17" ht="115.2" customHeight="1">
       <c r="A64" s="43" t="s">
         <v>44</v>
       </c>
@@ -13343,7 +13363,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="65" spans="1:17" ht="100.9" customHeight="1">
+    <row r="65" spans="1:17" ht="100.95" customHeight="1">
       <c r="A65" s="43" t="s">
         <v>41</v>
       </c>
@@ -13409,7 +13429,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="67" spans="1:17" ht="115.15" customHeight="1">
+    <row r="67" spans="1:17" ht="115.2" customHeight="1">
       <c r="A67" s="43" t="s">
         <v>31</v>
       </c>
@@ -13541,7 +13561,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="71" spans="1:17" ht="43.15" customHeight="1">
+    <row r="71" spans="1:17" ht="43.2" customHeight="1">
       <c r="A71" s="46" t="s">
         <v>855</v>
       </c>
@@ -13585,7 +13605,7 @@
       </c>
     </row>
     <row r="72" spans="1:17">
-      <c r="A72" s="88" t="s">
+      <c r="A72" s="87" t="s">
         <v>856</v>
       </c>
       <c r="B72" s="86"/>
@@ -13624,8 +13644,8 @@
       <c r="P73" s="86"/>
       <c r="Q73" s="86"/>
     </row>
-    <row r="74" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A74" s="87" t="s">
+    <row r="74" spans="1:17" ht="14.4" customHeight="1">
+      <c r="A74" s="88" t="s">
         <v>20</v>
       </c>
       <c r="B74" s="85" t="s">
@@ -13737,7 +13757,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="43.15" customHeight="1">
+    <row r="77" spans="1:17" ht="43.2" customHeight="1">
       <c r="A77" s="43" t="s">
         <v>51</v>
       </c>
@@ -13836,7 +13856,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="28.9" customHeight="1">
+    <row r="80" spans="1:17" ht="28.95" customHeight="1">
       <c r="A80" s="46" t="s">
         <v>857</v>
       </c>
@@ -13880,7 +13900,7 @@
       </c>
     </row>
     <row r="81" spans="1:17">
-      <c r="A81" s="88" t="s">
+      <c r="A81" s="87" t="s">
         <v>858</v>
       </c>
       <c r="B81" s="86"/>
@@ -13919,8 +13939,8 @@
       <c r="P82" s="86"/>
       <c r="Q82" s="86"/>
     </row>
-    <row r="83" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A83" s="87" t="s">
+    <row r="83" spans="1:17" ht="14.4" customHeight="1">
+      <c r="A83" s="88" t="s">
         <v>20</v>
       </c>
       <c r="B83" s="85" t="s">
@@ -13999,7 +14019,7 @@
       <c r="P84" s="86"/>
       <c r="Q84" s="86"/>
     </row>
-    <row r="85" spans="1:17" ht="100.9" customHeight="1">
+    <row r="85" spans="1:17" ht="100.95" customHeight="1">
       <c r="A85" s="43" t="s">
         <v>859</v>
       </c>
@@ -14032,7 +14052,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="86" spans="1:17" ht="100.9" customHeight="1">
+    <row r="86" spans="1:17" ht="100.95" customHeight="1">
       <c r="A86" s="43" t="s">
         <v>860</v>
       </c>
@@ -14065,7 +14085,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="87" spans="1:17" ht="28.9" customHeight="1">
+    <row r="87" spans="1:17" ht="28.95" customHeight="1">
       <c r="A87" s="43" t="s">
         <v>800</v>
       </c>
@@ -14131,7 +14151,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="89" spans="1:17" ht="28.9" customHeight="1">
+    <row r="89" spans="1:17" ht="28.95" customHeight="1">
       <c r="A89" s="43" t="s">
         <v>810</v>
       </c>
@@ -14197,7 +14217,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="91" spans="1:17" ht="28.9" customHeight="1">
+    <row r="91" spans="1:17" ht="28.95" customHeight="1">
       <c r="A91" s="43" t="s">
         <v>861</v>
       </c>
@@ -14230,7 +14250,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="92" spans="1:17" ht="28.9" customHeight="1">
+    <row r="92" spans="1:17" ht="28.95" customHeight="1">
       <c r="A92" s="46" t="s">
         <v>862</v>
       </c>
@@ -14274,7 +14294,7 @@
       </c>
     </row>
     <row r="93" spans="1:17">
-      <c r="A93" s="88" t="s">
+      <c r="A93" s="87" t="s">
         <v>863</v>
       </c>
       <c r="B93" s="86"/>
@@ -14313,8 +14333,8 @@
       <c r="P94" s="86"/>
       <c r="Q94" s="86"/>
     </row>
-    <row r="95" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A95" s="87" t="s">
+    <row r="95" spans="1:17" ht="14.4" customHeight="1">
+      <c r="A95" s="88" t="s">
         <v>20</v>
       </c>
       <c r="B95" s="85" t="s">
@@ -14492,7 +14512,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="100" spans="1:17" ht="28.9" customHeight="1">
+    <row r="100" spans="1:17" ht="28.95" customHeight="1">
       <c r="A100" s="43" t="s">
         <v>56</v>
       </c>
@@ -14525,7 +14545,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="101" spans="1:17" ht="115.15" customHeight="1">
+    <row r="101" spans="1:17" ht="115.2" customHeight="1">
       <c r="A101" s="43" t="s">
         <v>57</v>
       </c>
@@ -14591,7 +14611,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="28.9" customHeight="1">
+    <row r="103" spans="1:17" ht="28.95" customHeight="1">
       <c r="A103" s="43" t="s">
         <v>866</v>
       </c>
@@ -14624,7 +14644,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="43.15" customHeight="1">
+    <row r="104" spans="1:17" ht="43.2" customHeight="1">
       <c r="A104" s="43" t="s">
         <v>58</v>
       </c>
@@ -14723,7 +14743,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="107" spans="1:17" ht="100.9" customHeight="1">
+    <row r="107" spans="1:17" ht="100.95" customHeight="1">
       <c r="A107" s="43" t="s">
         <v>867</v>
       </c>
@@ -14855,7 +14875,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:17" ht="86.45" customHeight="1">
+    <row r="111" spans="1:17" ht="86.4" customHeight="1">
       <c r="A111" s="43" t="s">
         <v>63</v>
       </c>
@@ -14921,7 +14941,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="113" spans="1:17" ht="86.45" customHeight="1">
+    <row r="113" spans="1:17" ht="86.4" customHeight="1">
       <c r="A113" s="43" t="s">
         <v>869</v>
       </c>
@@ -14987,7 +15007,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="115" spans="1:17" ht="86.45" customHeight="1">
+    <row r="115" spans="1:17" ht="86.4" customHeight="1">
       <c r="A115" s="43" t="s">
         <v>871</v>
       </c>
@@ -15218,7 +15238,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="122" spans="1:17" ht="43.15" customHeight="1">
+    <row r="122" spans="1:17" ht="43.2" customHeight="1">
       <c r="A122" s="43" t="s">
         <v>876</v>
       </c>
@@ -15251,7 +15271,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:17" ht="100.9" customHeight="1">
+    <row r="123" spans="1:17" ht="100.95" customHeight="1">
       <c r="A123" s="43" t="s">
         <v>877</v>
       </c>
@@ -15284,7 +15304,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="124" spans="1:17" ht="100.9" customHeight="1">
+    <row r="124" spans="1:17" ht="100.95" customHeight="1">
       <c r="A124" s="43" t="s">
         <v>878</v>
       </c>
@@ -15317,7 +15337,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="125" spans="1:17" ht="43.15" customHeight="1">
+    <row r="125" spans="1:17" ht="43.2" customHeight="1">
       <c r="A125" s="43" t="s">
         <v>879</v>
       </c>
@@ -15350,7 +15370,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="43.15" customHeight="1">
+    <row r="126" spans="1:17" ht="43.2" customHeight="1">
       <c r="A126" s="46" t="s">
         <v>863</v>
       </c>
@@ -15394,7 +15414,7 @@
       </c>
     </row>
     <row r="127" spans="1:17">
-      <c r="A127" s="88" t="s">
+      <c r="A127" s="87" t="s">
         <v>557</v>
       </c>
       <c r="B127" s="86"/>
@@ -15433,8 +15453,8 @@
       <c r="P128" s="86"/>
       <c r="Q128" s="86"/>
     </row>
-    <row r="129" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A129" s="87" t="s">
+    <row r="129" spans="1:17" ht="14.4" customHeight="1">
+      <c r="A129" s="88" t="s">
         <v>20</v>
       </c>
       <c r="B129" s="85" t="s">
@@ -15513,7 +15533,7 @@
       <c r="P130" s="86"/>
       <c r="Q130" s="86"/>
     </row>
-    <row r="131" spans="1:17" ht="43.15" customHeight="1">
+    <row r="131" spans="1:17" ht="43.2" customHeight="1">
       <c r="A131" s="43" t="s">
         <v>880</v>
       </c>
@@ -15615,7 +15635,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="133" spans="1:17" ht="115.15" customHeight="1">
+    <row r="133" spans="1:17" ht="115.2" customHeight="1">
       <c r="A133" s="43" t="s">
         <v>882</v>
       </c>
@@ -15765,7 +15785,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="137" spans="1:17" ht="43.15" customHeight="1">
+    <row r="137" spans="1:17" ht="43.2" customHeight="1">
       <c r="A137" s="46" t="s">
         <v>885</v>
       </c>
@@ -15808,7 +15828,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="138" spans="1:17" ht="30">
+    <row r="138" spans="1:17">
       <c r="A138" s="43" t="s">
         <v>886</v>
       </c>
@@ -15892,7 +15912,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="140" spans="1:17" ht="86.45" customHeight="1">
+    <row r="140" spans="1:17" ht="86.4" customHeight="1">
       <c r="A140" s="43" t="s">
         <v>888</v>
       </c>
@@ -16034,7 +16054,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="144" spans="1:17" ht="43.15" customHeight="1">
+    <row r="144" spans="1:17" ht="43.2" customHeight="1">
       <c r="A144" s="46" t="s">
         <v>892</v>
       </c>
@@ -16110,7 +16130,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="146" spans="1:17" ht="100.9" customHeight="1">
+    <row r="146" spans="1:17" ht="100.95" customHeight="1">
       <c r="A146" s="43" t="s">
         <v>894</v>
       </c>
@@ -16143,7 +16163,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="147" spans="1:17" ht="43.15" customHeight="1">
+    <row r="147" spans="1:17" ht="43.2" customHeight="1">
       <c r="A147" s="46" t="s">
         <v>895</v>
       </c>
@@ -16186,7 +16206,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="148" spans="1:17" ht="28.9" customHeight="1">
+    <row r="148" spans="1:17" ht="28.95" customHeight="1">
       <c r="A148" s="43" t="s">
         <v>896</v>
       </c>
@@ -16270,7 +16290,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="150" spans="1:17" ht="28.9" customHeight="1">
+    <row r="150" spans="1:17" ht="28.95" customHeight="1">
       <c r="A150" s="43" t="s">
         <v>898</v>
       </c>
@@ -16303,7 +16323,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="151" spans="1:17" ht="43.15" customHeight="1">
+    <row r="151" spans="1:17" ht="43.2" customHeight="1">
       <c r="A151" s="46" t="s">
         <v>899</v>
       </c>
@@ -16346,7 +16366,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="152" spans="1:17" ht="43.15" customHeight="1">
+    <row r="152" spans="1:17" ht="43.2" customHeight="1">
       <c r="A152" s="43" t="s">
         <v>900</v>
       </c>
@@ -16397,7 +16417,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="153" spans="1:17" ht="28.9" customHeight="1">
+    <row r="153" spans="1:17" ht="28.95" customHeight="1">
       <c r="A153" s="43" t="s">
         <v>750</v>
       </c>
@@ -16448,7 +16468,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="154" spans="1:17" ht="28.9" customHeight="1">
+    <row r="154" spans="1:17" ht="28.95" customHeight="1">
       <c r="A154" s="43" t="s">
         <v>901</v>
       </c>
@@ -16499,7 +16519,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="155" spans="1:17" ht="28.9" customHeight="1">
+    <row r="155" spans="1:17" ht="28.95" customHeight="1">
       <c r="A155" s="43" t="s">
         <v>706</v>
       </c>
@@ -16532,7 +16552,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="156" spans="1:17" ht="28.9" customHeight="1">
+    <row r="156" spans="1:17" ht="28.95" customHeight="1">
       <c r="A156" s="43" t="s">
         <v>712</v>
       </c>
@@ -16565,7 +16585,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="157" spans="1:17" ht="28.9" customHeight="1">
+    <row r="157" spans="1:17" ht="28.95" customHeight="1">
       <c r="A157" s="43" t="s">
         <v>902</v>
       </c>
@@ -16642,7 +16662,7 @@
       </c>
     </row>
     <row r="159" spans="1:17">
-      <c r="A159" s="88" t="s">
+      <c r="A159" s="87" t="s">
         <v>46</v>
       </c>
       <c r="B159" s="86"/>
@@ -16681,8 +16701,8 @@
       <c r="P160" s="86"/>
       <c r="Q160" s="86"/>
     </row>
-    <row r="161" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A161" s="87" t="s">
+    <row r="161" spans="1:17" ht="14.4" customHeight="1">
+      <c r="A161" s="88" t="s">
         <v>20</v>
       </c>
       <c r="B161" s="85" t="s">
@@ -16761,7 +16781,7 @@
       <c r="P162" s="86"/>
       <c r="Q162" s="86"/>
     </row>
-    <row r="163" spans="1:17" ht="28.9" customHeight="1">
+    <row r="163" spans="1:17" ht="28.95" customHeight="1">
       <c r="A163" s="43" t="s">
         <v>46</v>
       </c>
@@ -16813,7 +16833,7 @@
       </c>
     </row>
     <row r="164" spans="1:17">
-      <c r="A164" s="88" t="s">
+      <c r="A164" s="87" t="s">
         <v>69</v>
       </c>
       <c r="B164" s="86"/>
@@ -16852,8 +16872,8 @@
       <c r="P165" s="86"/>
       <c r="Q165" s="86"/>
     </row>
-    <row r="166" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A166" s="87" t="s">
+    <row r="166" spans="1:17" ht="14.4" customHeight="1">
+      <c r="A166" s="88" t="s">
         <v>20</v>
       </c>
       <c r="B166" s="85" t="s">
@@ -17064,7 +17084,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="172" spans="1:17" ht="86.45" customHeight="1">
+    <row r="172" spans="1:17" ht="86.4" customHeight="1">
       <c r="A172" s="46" t="s">
         <v>905</v>
       </c>
@@ -17109,6 +17129,70 @@
     </row>
   </sheetData>
   <mergeCells count="80">
+    <mergeCell ref="K166:O166"/>
+    <mergeCell ref="H74:J74"/>
+    <mergeCell ref="H83:J83"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="Q50:Q51"/>
+    <mergeCell ref="B55:D55"/>
+    <mergeCell ref="B95:D95"/>
+    <mergeCell ref="E50:G50"/>
+    <mergeCell ref="P74:P75"/>
+    <mergeCell ref="E55:G55"/>
+    <mergeCell ref="K129:O129"/>
+    <mergeCell ref="P95:P96"/>
+    <mergeCell ref="A55:A56"/>
+    <mergeCell ref="A81:Q82"/>
+    <mergeCell ref="A95:A96"/>
+    <mergeCell ref="B129:D129"/>
+    <mergeCell ref="Q166:Q167"/>
+    <mergeCell ref="Q35:Q36"/>
+    <mergeCell ref="P161:P162"/>
+    <mergeCell ref="A159:Q160"/>
+    <mergeCell ref="A93:Q94"/>
+    <mergeCell ref="Q161:Q162"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="P83:P84"/>
+    <mergeCell ref="Q129:Q130"/>
+    <mergeCell ref="Q95:Q96"/>
+    <mergeCell ref="H50:J50"/>
+    <mergeCell ref="A161:A162"/>
+    <mergeCell ref="H55:J55"/>
+    <mergeCell ref="A83:A84"/>
+    <mergeCell ref="P55:P56"/>
+    <mergeCell ref="B161:D161"/>
+    <mergeCell ref="P129:P130"/>
+    <mergeCell ref="A166:A167"/>
+    <mergeCell ref="K74:O74"/>
+    <mergeCell ref="K83:O83"/>
+    <mergeCell ref="A74:A75"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="A129:A130"/>
+    <mergeCell ref="B83:D83"/>
+    <mergeCell ref="H166:J166"/>
+    <mergeCell ref="E129:G129"/>
+    <mergeCell ref="H161:J161"/>
+    <mergeCell ref="H129:J129"/>
+    <mergeCell ref="E74:G74"/>
+    <mergeCell ref="E166:G166"/>
+    <mergeCell ref="K95:O95"/>
+    <mergeCell ref="A28:Q29"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="A48:Q49"/>
+    <mergeCell ref="E83:G83"/>
+    <mergeCell ref="E35:G35"/>
+    <mergeCell ref="Q55:Q56"/>
+    <mergeCell ref="P50:P51"/>
+    <mergeCell ref="E30:G30"/>
+    <mergeCell ref="Q74:Q75"/>
+    <mergeCell ref="H35:J35"/>
+    <mergeCell ref="P30:P31"/>
+    <mergeCell ref="Q83:Q84"/>
+    <mergeCell ref="A50:A51"/>
+    <mergeCell ref="K35:O35"/>
+    <mergeCell ref="Q30:Q31"/>
+    <mergeCell ref="K50:O50"/>
     <mergeCell ref="P35:P36"/>
     <mergeCell ref="E161:G161"/>
     <mergeCell ref="K30:O30"/>
@@ -17125,70 +17209,6 @@
     <mergeCell ref="A127:Q128"/>
     <mergeCell ref="K161:O161"/>
     <mergeCell ref="H30:J30"/>
-    <mergeCell ref="A28:Q29"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="A48:Q49"/>
-    <mergeCell ref="E83:G83"/>
-    <mergeCell ref="E35:G35"/>
-    <mergeCell ref="Q55:Q56"/>
-    <mergeCell ref="P50:P51"/>
-    <mergeCell ref="E30:G30"/>
-    <mergeCell ref="Q74:Q75"/>
-    <mergeCell ref="H35:J35"/>
-    <mergeCell ref="P30:P31"/>
-    <mergeCell ref="Q83:Q84"/>
-    <mergeCell ref="A50:A51"/>
-    <mergeCell ref="K35:O35"/>
-    <mergeCell ref="Q30:Q31"/>
-    <mergeCell ref="K50:O50"/>
-    <mergeCell ref="B161:D161"/>
-    <mergeCell ref="P129:P130"/>
-    <mergeCell ref="A166:A167"/>
-    <mergeCell ref="K74:O74"/>
-    <mergeCell ref="K83:O83"/>
-    <mergeCell ref="A74:A75"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="A129:A130"/>
-    <mergeCell ref="B83:D83"/>
-    <mergeCell ref="H166:J166"/>
-    <mergeCell ref="E129:G129"/>
-    <mergeCell ref="H161:J161"/>
-    <mergeCell ref="H129:J129"/>
-    <mergeCell ref="E74:G74"/>
-    <mergeCell ref="E166:G166"/>
-    <mergeCell ref="K95:O95"/>
-    <mergeCell ref="Q166:Q167"/>
-    <mergeCell ref="Q35:Q36"/>
-    <mergeCell ref="P161:P162"/>
-    <mergeCell ref="A159:Q160"/>
-    <mergeCell ref="A93:Q94"/>
-    <mergeCell ref="Q161:Q162"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="P83:P84"/>
-    <mergeCell ref="Q129:Q130"/>
-    <mergeCell ref="Q95:Q96"/>
-    <mergeCell ref="H50:J50"/>
-    <mergeCell ref="A161:A162"/>
-    <mergeCell ref="H55:J55"/>
-    <mergeCell ref="A83:A84"/>
-    <mergeCell ref="P55:P56"/>
-    <mergeCell ref="K166:O166"/>
-    <mergeCell ref="H74:J74"/>
-    <mergeCell ref="H83:J83"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="Q50:Q51"/>
-    <mergeCell ref="B55:D55"/>
-    <mergeCell ref="B95:D95"/>
-    <mergeCell ref="E50:G50"/>
-    <mergeCell ref="P74:P75"/>
-    <mergeCell ref="E55:G55"/>
-    <mergeCell ref="K129:O129"/>
-    <mergeCell ref="P95:P96"/>
-    <mergeCell ref="A55:A56"/>
-    <mergeCell ref="A81:Q82"/>
-    <mergeCell ref="A95:A96"/>
-    <mergeCell ref="B129:D129"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" display="https://www.scei-concours.fr/stat2025/bcpst.html" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
@@ -17220,7 +17240,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:Q87"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="40"/>
@@ -17324,7 +17344,7 @@
       </c>
     </row>
     <row r="24" spans="1:17">
-      <c r="A24" s="88" t="s">
+      <c r="A24" s="87" t="s">
         <v>19</v>
       </c>
       <c r="B24" s="86"/>
@@ -17363,8 +17383,8 @@
       <c r="P25" s="86"/>
       <c r="Q25" s="86"/>
     </row>
-    <row r="26" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A26" s="87" t="s">
+    <row r="26" spans="1:17" ht="14.4" customHeight="1">
+      <c r="A26" s="88" t="s">
         <v>20</v>
       </c>
       <c r="B26" s="85" t="s">
@@ -17443,7 +17463,7 @@
       <c r="P27" s="86"/>
       <c r="Q27" s="86"/>
     </row>
-    <row r="28" spans="1:17" ht="115.15" customHeight="1">
+    <row r="28" spans="1:17" ht="115.2" customHeight="1">
       <c r="A28" s="43" t="s">
         <v>31</v>
       </c>
@@ -17542,7 +17562,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="28.9" customHeight="1">
+    <row r="31" spans="1:17" ht="28.95" customHeight="1">
       <c r="A31" s="43" t="s">
         <v>34</v>
       </c>
@@ -17608,7 +17628,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:17" ht="100.9" customHeight="1">
+    <row r="33" spans="1:17" ht="100.95" customHeight="1">
       <c r="A33" s="43" t="s">
         <v>36</v>
       </c>
@@ -17641,7 +17661,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="43.15" customHeight="1">
+    <row r="34" spans="1:17" ht="43.2" customHeight="1">
       <c r="A34" s="43" t="s">
         <v>37</v>
       </c>
@@ -17707,7 +17727,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="28.9" customHeight="1">
+    <row r="36" spans="1:17" ht="28.95" customHeight="1">
       <c r="A36" s="43" t="s">
         <v>39</v>
       </c>
@@ -17740,7 +17760,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="37" spans="1:17" ht="43.15" customHeight="1">
+    <row r="37" spans="1:17" ht="43.2" customHeight="1">
       <c r="A37" s="43" t="s">
         <v>40</v>
       </c>
@@ -17773,7 +17793,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="1:17" ht="100.9" customHeight="1">
+    <row r="38" spans="1:17" ht="100.95" customHeight="1">
       <c r="A38" s="43" t="s">
         <v>41</v>
       </c>
@@ -17872,7 +17892,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="1:17" ht="115.15" customHeight="1">
+    <row r="41" spans="1:17" ht="115.2" customHeight="1">
       <c r="A41" s="43" t="s">
         <v>44</v>
       </c>
@@ -17905,7 +17925,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:17" ht="28.9" customHeight="1">
+    <row r="42" spans="1:17" ht="28.95" customHeight="1">
       <c r="A42" s="46" t="s">
         <v>45</v>
       </c>
@@ -17949,7 +17969,7 @@
       </c>
     </row>
     <row r="43" spans="1:17">
-      <c r="A43" s="88" t="s">
+      <c r="A43" s="87" t="s">
         <v>46</v>
       </c>
       <c r="B43" s="86"/>
@@ -17988,8 +18008,8 @@
       <c r="P44" s="86"/>
       <c r="Q44" s="86"/>
     </row>
-    <row r="45" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A45" s="87" t="s">
+    <row r="45" spans="1:17" ht="14.4" customHeight="1">
+      <c r="A45" s="88" t="s">
         <v>20</v>
       </c>
       <c r="B45" s="85" t="s">
@@ -18068,7 +18088,7 @@
       <c r="P46" s="86"/>
       <c r="Q46" s="86"/>
     </row>
-    <row r="47" spans="1:17" ht="28.9" customHeight="1">
+    <row r="47" spans="1:17" ht="28.95" customHeight="1">
       <c r="A47" s="43" t="s">
         <v>46</v>
       </c>
@@ -18120,7 +18140,7 @@
       </c>
     </row>
     <row r="48" spans="1:17">
-      <c r="A48" s="88" t="s">
+      <c r="A48" s="87" t="s">
         <v>47</v>
       </c>
       <c r="B48" s="86"/>
@@ -18159,8 +18179,8 @@
       <c r="P49" s="86"/>
       <c r="Q49" s="86"/>
     </row>
-    <row r="50" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A50" s="87" t="s">
+    <row r="50" spans="1:17" ht="14.4" customHeight="1">
+      <c r="A50" s="88" t="s">
         <v>20</v>
       </c>
       <c r="B50" s="85" t="s">
@@ -18338,7 +18358,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="1:17" ht="43.15" customHeight="1">
+    <row r="55" spans="1:17" ht="43.2" customHeight="1">
       <c r="A55" s="43" t="s">
         <v>51</v>
       </c>
@@ -18371,7 +18391,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="28.9" customHeight="1">
+    <row r="56" spans="1:17" ht="28.95" customHeight="1">
       <c r="A56" s="46" t="s">
         <v>52</v>
       </c>
@@ -18415,7 +18435,7 @@
       </c>
     </row>
     <row r="57" spans="1:17">
-      <c r="A57" s="88" t="s">
+      <c r="A57" s="87" t="s">
         <v>53</v>
       </c>
       <c r="B57" s="86"/>
@@ -18454,8 +18474,8 @@
       <c r="P58" s="86"/>
       <c r="Q58" s="86"/>
     </row>
-    <row r="59" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A59" s="87" t="s">
+    <row r="59" spans="1:17" ht="14.4" customHeight="1">
+      <c r="A59" s="88" t="s">
         <v>20</v>
       </c>
       <c r="B59" s="85" t="s">
@@ -18600,7 +18620,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:17" ht="28.9" customHeight="1">
+    <row r="63" spans="1:17" ht="28.95" customHeight="1">
       <c r="A63" s="43" t="s">
         <v>56</v>
       </c>
@@ -18633,7 +18653,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="115.15" customHeight="1">
+    <row r="64" spans="1:17" ht="115.2" customHeight="1">
       <c r="A64" s="43" t="s">
         <v>57</v>
       </c>
@@ -18666,7 +18686,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:17" ht="43.15" customHeight="1">
+    <row r="65" spans="1:17" ht="43.2" customHeight="1">
       <c r="A65" s="43" t="s">
         <v>58</v>
       </c>
@@ -18831,7 +18851,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:17" ht="86.45" customHeight="1">
+    <row r="70" spans="1:17" ht="86.4" customHeight="1">
       <c r="A70" s="43" t="s">
         <v>63</v>
       </c>
@@ -18963,7 +18983,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="43.15" customHeight="1">
+    <row r="74" spans="1:17" ht="43.2" customHeight="1">
       <c r="A74" s="46" t="s">
         <v>53</v>
       </c>
@@ -19007,7 +19027,7 @@
       </c>
     </row>
     <row r="75" spans="1:17">
-      <c r="A75" s="88" t="s">
+      <c r="A75" s="87" t="s">
         <v>67</v>
       </c>
       <c r="B75" s="86"/>
@@ -19046,8 +19066,8 @@
       <c r="P76" s="86"/>
       <c r="Q76" s="86"/>
     </row>
-    <row r="77" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A77" s="87" t="s">
+    <row r="77" spans="1:17" ht="14.4" customHeight="1">
+      <c r="A77" s="88" t="s">
         <v>20</v>
       </c>
       <c r="B77" s="85" t="s">
@@ -19126,7 +19146,7 @@
       <c r="P78" s="86"/>
       <c r="Q78" s="86"/>
     </row>
-    <row r="79" spans="1:17" ht="28.9" customHeight="1">
+    <row r="79" spans="1:17" ht="28.95" customHeight="1">
       <c r="A79" s="43" t="s">
         <v>68</v>
       </c>
@@ -19178,7 +19198,7 @@
       </c>
     </row>
     <row r="80" spans="1:17">
-      <c r="A80" s="88" t="s">
+      <c r="A80" s="87" t="s">
         <v>69</v>
       </c>
       <c r="B80" s="86"/>
@@ -19217,8 +19237,8 @@
       <c r="P81" s="86"/>
       <c r="Q81" s="86"/>
     </row>
-    <row r="82" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A82" s="87" t="s">
+    <row r="82" spans="1:17" ht="14.4" customHeight="1">
+      <c r="A82" s="88" t="s">
         <v>20</v>
       </c>
       <c r="B82" s="85" t="s">
@@ -19441,6 +19461,38 @@
     </row>
   </sheetData>
   <mergeCells count="48">
+    <mergeCell ref="A24:Q25"/>
+    <mergeCell ref="K82:O82"/>
+    <mergeCell ref="H50:J50"/>
+    <mergeCell ref="P26:P27"/>
+    <mergeCell ref="A59:A60"/>
+    <mergeCell ref="Q77:Q78"/>
+    <mergeCell ref="E82:G82"/>
+    <mergeCell ref="A82:A83"/>
+    <mergeCell ref="B77:D77"/>
+    <mergeCell ref="P45:P46"/>
+    <mergeCell ref="A80:Q81"/>
+    <mergeCell ref="A77:A78"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="H82:J82"/>
+    <mergeCell ref="Q45:Q46"/>
+    <mergeCell ref="A48:Q49"/>
+    <mergeCell ref="P82:P83"/>
+    <mergeCell ref="Q59:Q60"/>
+    <mergeCell ref="H77:J77"/>
+    <mergeCell ref="K59:O59"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="Q82:Q83"/>
+    <mergeCell ref="K77:O77"/>
+    <mergeCell ref="P77:P78"/>
+    <mergeCell ref="E77:G77"/>
+    <mergeCell ref="E50:G50"/>
+    <mergeCell ref="H59:J59"/>
+    <mergeCell ref="A75:Q76"/>
+    <mergeCell ref="P59:P60"/>
+    <mergeCell ref="E59:G59"/>
+    <mergeCell ref="A57:Q58"/>
+    <mergeCell ref="B59:D59"/>
     <mergeCell ref="A26:A27"/>
     <mergeCell ref="K50:O50"/>
     <mergeCell ref="E26:G26"/>
@@ -19457,38 +19509,6 @@
     <mergeCell ref="E45:G45"/>
     <mergeCell ref="B45:D45"/>
     <mergeCell ref="B50:D50"/>
-    <mergeCell ref="E50:G50"/>
-    <mergeCell ref="H59:J59"/>
-    <mergeCell ref="A75:Q76"/>
-    <mergeCell ref="P59:P60"/>
-    <mergeCell ref="E59:G59"/>
-    <mergeCell ref="A57:Q58"/>
-    <mergeCell ref="B59:D59"/>
-    <mergeCell ref="P82:P83"/>
-    <mergeCell ref="Q59:Q60"/>
-    <mergeCell ref="H77:J77"/>
-    <mergeCell ref="K59:O59"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="Q82:Q83"/>
-    <mergeCell ref="K77:O77"/>
-    <mergeCell ref="P77:P78"/>
-    <mergeCell ref="E77:G77"/>
-    <mergeCell ref="A24:Q25"/>
-    <mergeCell ref="K82:O82"/>
-    <mergeCell ref="H50:J50"/>
-    <mergeCell ref="P26:P27"/>
-    <mergeCell ref="A59:A60"/>
-    <mergeCell ref="Q77:Q78"/>
-    <mergeCell ref="E82:G82"/>
-    <mergeCell ref="A82:A83"/>
-    <mergeCell ref="B77:D77"/>
-    <mergeCell ref="P45:P46"/>
-    <mergeCell ref="A80:Q81"/>
-    <mergeCell ref="A77:A78"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="H82:J82"/>
-    <mergeCell ref="Q45:Q46"/>
-    <mergeCell ref="A48:Q49"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" display="https://www.scei-concours.fr/stat2025/tb.html" xr:uid="{00000000-0004-0000-0500-000000000000}"/>
@@ -19516,7 +19536,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:G78"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
@@ -19526,7 +19546,7 @@
     <col min="7" max="7" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="22.15" customHeight="1">
+    <row r="1" spans="1:7" ht="22.2" customHeight="1">
       <c r="A1" s="90" t="s">
         <v>906</v>
       </c>
@@ -19537,7 +19557,7 @@
       <c r="F1" s="86"/>
       <c r="G1" s="86"/>
     </row>
-    <row r="2" spans="1:7" ht="37.9" customHeight="1">
+    <row r="2" spans="1:7" ht="37.950000000000003" customHeight="1">
       <c r="A2" s="48" t="s">
         <v>907</v>
       </c>
@@ -19560,7 +19580,7 @@
         <v>913</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="31.9" customHeight="1">
+    <row r="3" spans="1:7" ht="31.95" customHeight="1">
       <c r="A3" s="55" t="s">
         <v>914</v>
       </c>
@@ -19583,7 +19603,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="4" spans="1:7" ht="16.2" customHeight="1">
       <c r="A4" s="49" t="s">
         <v>126</v>
       </c>
@@ -19604,7 +19624,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="5" spans="1:7" ht="16.2" customHeight="1">
       <c r="A5" s="49" t="s">
         <v>37</v>
       </c>
@@ -19625,7 +19645,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="6" spans="1:7" ht="16.2" customHeight="1">
       <c r="A6" s="49" t="s">
         <v>122</v>
       </c>
@@ -19646,7 +19666,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="7" spans="1:7" ht="16.2" customHeight="1">
       <c r="A7" s="49" t="s">
         <v>212</v>
       </c>
@@ -19667,7 +19687,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="8" spans="1:7" ht="16.2" customHeight="1">
       <c r="A8" s="49" t="s">
         <v>700</v>
       </c>
@@ -19688,7 +19708,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="9" spans="1:7" ht="16.2" customHeight="1">
       <c r="A9" s="49" t="s">
         <v>104</v>
       </c>
@@ -19711,7 +19731,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="10" spans="1:7" ht="16.2" customHeight="1">
       <c r="A10" s="49" t="s">
         <v>104</v>
       </c>
@@ -19734,7 +19754,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="11" spans="1:7" ht="16.2" customHeight="1">
       <c r="A11" s="49" t="s">
         <v>104</v>
       </c>
@@ -19757,7 +19777,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="12" spans="1:7" ht="16.2" customHeight="1">
       <c r="A12" s="49" t="s">
         <v>99</v>
       </c>
@@ -19778,7 +19798,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="13" spans="1:7" ht="16.2" customHeight="1">
       <c r="A13" s="49" t="s">
         <v>99</v>
       </c>
@@ -19799,7 +19819,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="14" spans="1:7" ht="16.2" customHeight="1">
       <c r="A14" s="49" t="s">
         <v>283</v>
       </c>
@@ -19820,7 +19840,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="15" spans="1:7" ht="16.2" customHeight="1">
       <c r="A15" s="49" t="s">
         <v>188</v>
       </c>
@@ -19841,7 +19861,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="16" spans="1:7" ht="16.2" customHeight="1">
       <c r="A16" s="49" t="s">
         <v>112</v>
       </c>
@@ -19862,7 +19882,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="17" spans="1:7" ht="16.2" customHeight="1">
       <c r="A17" s="49" t="s">
         <v>115</v>
       </c>
@@ -19883,7 +19903,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="18" spans="1:7" ht="16.2" customHeight="1">
       <c r="A18" s="49" t="s">
         <v>345</v>
       </c>
@@ -19904,7 +19924,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="19" spans="1:7" ht="16.2" customHeight="1">
       <c r="A19" s="49" t="s">
         <v>142</v>
       </c>
@@ -19925,7 +19945,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="20" spans="1:7" ht="16.2" customHeight="1">
       <c r="A20" s="49" t="s">
         <v>258</v>
       </c>
@@ -19946,7 +19966,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="21" spans="1:7" ht="16.2" customHeight="1">
       <c r="A21" s="49" t="s">
         <v>370</v>
       </c>
@@ -19967,7 +19987,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="22" spans="1:7" ht="16.2" customHeight="1">
       <c r="A22" s="49" t="s">
         <v>794</v>
       </c>
@@ -19988,7 +20008,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="23" spans="1:7" ht="16.2" customHeight="1">
       <c r="A23" s="49" t="s">
         <v>805</v>
       </c>
@@ -20009,7 +20029,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="24" spans="1:7" ht="16.2" customHeight="1">
       <c r="A24" s="49" t="s">
         <v>810</v>
       </c>
@@ -20030,7 +20050,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="25" spans="1:7" ht="16.2" customHeight="1">
       <c r="A25" s="49" t="s">
         <v>800</v>
       </c>
@@ -20051,7 +20071,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="26" spans="1:7" ht="16.2" customHeight="1">
       <c r="A26" s="49" t="s">
         <v>815</v>
       </c>
@@ -20072,7 +20092,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="27" spans="1:7" ht="16.2" customHeight="1">
       <c r="A27" s="49" t="s">
         <v>820</v>
       </c>
@@ -20093,7 +20113,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="28" spans="1:7" ht="16.2" customHeight="1">
       <c r="A28" s="51" t="s">
         <v>126</v>
       </c>
@@ -20114,7 +20134,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="29" spans="1:7" ht="16.2" customHeight="1">
       <c r="A29" s="51" t="s">
         <v>283</v>
       </c>
@@ -20135,7 +20155,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="30" spans="1:7" ht="16.2" customHeight="1">
       <c r="A30" s="51" t="s">
         <v>188</v>
       </c>
@@ -20156,7 +20176,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="31" spans="1:7" ht="16.2" customHeight="1">
       <c r="A31" s="51" t="s">
         <v>104</v>
       </c>
@@ -20179,7 +20199,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="32" spans="1:7" ht="16.2" customHeight="1">
       <c r="A32" s="51" t="s">
         <v>104</v>
       </c>
@@ -20200,7 +20220,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="33" spans="1:7" ht="16.2" customHeight="1">
       <c r="A33" s="51" t="s">
         <v>37</v>
       </c>
@@ -20221,7 +20241,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="34" spans="1:7" ht="16.2" customHeight="1">
       <c r="A34" s="51" t="s">
         <v>232</v>
       </c>
@@ -20240,7 +20260,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="35" spans="1:7" ht="16.2" customHeight="1">
       <c r="A35" s="51" t="s">
         <v>122</v>
       </c>
@@ -20261,7 +20281,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="36" spans="1:7" ht="16.2" customHeight="1">
       <c r="A36" s="51" t="s">
         <v>212</v>
       </c>
@@ -20282,7 +20302,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="37" spans="1:7" ht="16.2" customHeight="1">
       <c r="A37" s="51" t="s">
         <v>99</v>
       </c>
@@ -20303,7 +20323,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="38" spans="1:7" ht="16.2" customHeight="1">
       <c r="A38" s="51" t="s">
         <v>99</v>
       </c>
@@ -20324,7 +20344,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="39" spans="1:7" ht="16.2" customHeight="1">
       <c r="A39" s="51" t="s">
         <v>115</v>
       </c>
@@ -20345,7 +20365,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="40" spans="1:7" ht="16.2" customHeight="1">
       <c r="A40" s="51" t="s">
         <v>112</v>
       </c>
@@ -20366,7 +20386,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="41" spans="1:7" ht="16.2" customHeight="1">
       <c r="A41" s="56" t="s">
         <v>345</v>
       </c>
@@ -20387,7 +20407,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="42" spans="1:7" ht="16.2" customHeight="1">
       <c r="A42" s="51" t="s">
         <v>142</v>
       </c>
@@ -20408,7 +20428,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="43" spans="1:7" ht="16.2" customHeight="1">
       <c r="A43" s="51" t="s">
         <v>258</v>
       </c>
@@ -20429,7 +20449,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="44" spans="1:7" ht="16.2" customHeight="1">
       <c r="A44" s="56" t="s">
         <v>370</v>
       </c>
@@ -20450,7 +20470,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="45" spans="1:7" ht="16.2" customHeight="1">
       <c r="A45" s="60" t="s">
         <v>745</v>
       </c>
@@ -20471,7 +20491,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="46" spans="1:7" ht="16.2" customHeight="1">
       <c r="A46" s="53" t="s">
         <v>232</v>
       </c>
@@ -20490,7 +20510,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="47" spans="1:7" ht="16.2" customHeight="1">
       <c r="A47" s="53" t="s">
         <v>88</v>
       </c>
@@ -20509,7 +20529,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="48" spans="1:7" ht="16.2" customHeight="1">
       <c r="A48" s="53" t="s">
         <v>88</v>
       </c>
@@ -20530,7 +20550,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="49" spans="1:7" ht="16.2" customHeight="1">
       <c r="A49" s="53" t="s">
         <v>88</v>
       </c>
@@ -20551,7 +20571,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="50" spans="1:7" ht="16.2" customHeight="1">
       <c r="A50" s="56" t="s">
         <v>740</v>
       </c>
@@ -20572,7 +20592,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="51" spans="1:7" ht="16.2" customHeight="1">
       <c r="A51" s="58" t="s">
         <v>750</v>
       </c>
@@ -20593,7 +20613,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="52" spans="1:7" ht="16.2" customHeight="1">
       <c r="A52" s="53" t="s">
         <v>706</v>
       </c>
@@ -20612,7 +20632,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="53" spans="1:7" ht="16.2" customHeight="1">
       <c r="A53" s="53" t="s">
         <v>712</v>
       </c>
@@ -20631,7 +20651,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="54" spans="1:7" ht="16.2" customHeight="1">
       <c r="A54" s="53" t="s">
         <v>718</v>
       </c>
@@ -20650,7 +20670,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="55" spans="1:7" ht="16.2" customHeight="1">
       <c r="A55" s="56" t="s">
         <v>136</v>
       </c>
@@ -20669,7 +20689,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="56" spans="1:7" ht="16.2" customHeight="1">
       <c r="A56" s="56" t="s">
         <v>136</v>
       </c>
@@ -20688,7 +20708,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="57" spans="1:7" ht="16.2" customHeight="1">
       <c r="A57" s="58" t="s">
         <v>340</v>
       </c>
@@ -20709,7 +20729,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="58" spans="1:7" ht="16.2" customHeight="1">
       <c r="A58" s="58" t="s">
         <v>340</v>
       </c>
@@ -20730,7 +20750,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="59" spans="1:7" ht="16.2" customHeight="1">
       <c r="A59" s="58" t="s">
         <v>169</v>
       </c>
@@ -20751,7 +20771,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="60" spans="1:7" ht="16.2" customHeight="1">
       <c r="A60" s="58" t="s">
         <v>91</v>
       </c>
@@ -20772,7 +20792,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="61" spans="1:7" ht="16.2" customHeight="1">
       <c r="A61" s="58" t="s">
         <v>91</v>
       </c>
@@ -20793,7 +20813,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="62" spans="1:7" ht="16.2" customHeight="1">
       <c r="A62" s="58" t="s">
         <v>194</v>
       </c>
@@ -20814,7 +20834,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="63" spans="1:7" ht="16.2" customHeight="1">
       <c r="A63" s="58" t="s">
         <v>194</v>
       </c>
@@ -20835,7 +20855,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="64" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="64" spans="1:7" ht="16.2" customHeight="1">
       <c r="A64" s="58" t="s">
         <v>145</v>
       </c>
@@ -20856,7 +20876,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="65" spans="1:7" ht="16.2" customHeight="1">
       <c r="A65" s="58" t="s">
         <v>145</v>
       </c>
@@ -20877,7 +20897,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="66" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="66" spans="1:7" ht="16.2" customHeight="1">
       <c r="A66" s="58" t="s">
         <v>85</v>
       </c>
@@ -20898,7 +20918,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="67" spans="1:7" ht="16.2" customHeight="1">
       <c r="A67" s="58" t="s">
         <v>322</v>
       </c>
@@ -20919,7 +20939,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="68" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="68" spans="1:7" ht="16.2" customHeight="1">
       <c r="A68" s="58" t="s">
         <v>322</v>
       </c>
@@ -20940,7 +20960,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="69" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="69" spans="1:7" ht="16.2" customHeight="1">
       <c r="A69" s="58" t="s">
         <v>267</v>
       </c>
@@ -20961,7 +20981,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="70" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="70" spans="1:7" ht="16.2" customHeight="1">
       <c r="A70" s="58" t="s">
         <v>267</v>
       </c>
@@ -20982,7 +21002,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="71" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="71" spans="1:7" ht="16.2" customHeight="1">
       <c r="A71" s="58" t="s">
         <v>429</v>
       </c>
@@ -21003,7 +21023,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="72" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="72" spans="1:7" ht="16.2" customHeight="1">
       <c r="A72" s="58" t="s">
         <v>459</v>
       </c>
@@ -21024,7 +21044,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="73" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="73" spans="1:7" ht="16.2" customHeight="1">
       <c r="A73" s="58" t="s">
         <v>730</v>
       </c>
@@ -21045,7 +21065,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="74" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="74" spans="1:7" ht="16.2" customHeight="1">
       <c r="A74" s="58" t="s">
         <v>735</v>
       </c>
@@ -21066,7 +21086,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="75" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="75" spans="1:7" ht="16.2" customHeight="1">
       <c r="A75" s="58" t="s">
         <v>197</v>
       </c>
@@ -21087,7 +21107,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="76" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="76" spans="1:7" ht="16.2" customHeight="1">
       <c r="A76" s="58" t="s">
         <v>197</v>
       </c>

--- a/anciens_eleves.xlsx
+++ b/anciens_eleves.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bruno\Nextcloud4\Boulot 2026\Site orientation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bruno\Nextcloud2\Boulot 2026\Site orientation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0CBF58B-7B1B-4282-A958-67FC39C73BAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B31EA939-2636-470C-BE09-3F0FFF044F3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Elèves_BCPST" sheetId="1" r:id="rId1"/>
@@ -22,22 +22,11 @@
     <sheet name="Stats" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2473" uniqueCount="1017">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2482" uniqueCount="1023">
   <si>
     <t>Statistiques 2025</t>
   </si>
@@ -3094,14 +3083,32 @@
     <t>https://youtu.be/mUE_eBgYsfk</t>
   </si>
   <si>
+    <t>https://eekez.github.io/chesnoy-orientation/fiches/ficheLaureenM.pdf</t>
+  </si>
+  <si>
+    <t>https://youtu.be/ZHZfCFbO07Q</t>
+  </si>
+  <si>
     <t>https://youtu.be/nZCwqNyJkJg</t>
+  </si>
+  <si>
+    <t>RONCERET--ARTAL</t>
+  </si>
+  <si>
+    <t>Oniris Nantes</t>
+  </si>
+  <si>
+    <t>VIALLARD</t>
+  </si>
+  <si>
+    <t>Flore</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="30">
+  <fonts count="30" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3689,16 +3696,13 @@
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -3723,6 +3727,9 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="24" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -4068,21 +4075,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I110"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <dimension ref="A1:I111"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.44140625" customWidth="1"/>
-    <col min="2" max="2" width="14.33203125" customWidth="1"/>
+    <col min="1" max="1" width="27.42578125" customWidth="1"/>
+    <col min="2" max="2" width="14.28515625" customWidth="1"/>
     <col min="3" max="3" width="17" customWidth="1"/>
-    <col min="4" max="4" width="8.5546875" customWidth="1"/>
+    <col min="4" max="4" width="8.5703125" customWidth="1"/>
     <col min="5" max="5" width="9" customWidth="1"/>
-    <col min="6" max="6" width="44.88671875" customWidth="1"/>
+    <col min="6" max="6" width="44.85546875" customWidth="1"/>
     <col min="7" max="7" width="18" customWidth="1"/>
     <col min="8" max="8" width="28" customWidth="1"/>
-    <col min="9" max="9" width="21.44140625" customWidth="1"/>
+    <col min="9" max="9" width="21.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="70" t="s">
         <v>74</v>
       </c>
@@ -4111,16 +4118,16 @@
         <v>82</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="78" t="s">
-        <v>973</v>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="90" t="s">
+        <v>1019</v>
       </c>
       <c r="B2" s="64" t="str">
         <f t="shared" ref="B2" si="0">LEFT(A2)</f>
-        <v>G</v>
+        <v>R</v>
       </c>
       <c r="C2" s="64" t="s">
-        <v>178</v>
+        <v>220</v>
       </c>
       <c r="D2" s="64">
         <v>2026</v>
@@ -4129,22 +4136,22 @@
         <v>1</v>
       </c>
       <c r="F2" s="64" t="s">
-        <v>429</v>
+        <v>1020</v>
       </c>
       <c r="G2" s="64"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" s="76" t="s">
-        <v>968</v>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="90" t="s">
+        <v>973</v>
       </c>
       <c r="B3" s="64" t="str">
         <f t="shared" ref="B3" si="1">LEFT(A3)</f>
         <v>G</v>
       </c>
       <c r="C3" s="64" t="s">
-        <v>969</v>
+        <v>178</v>
       </c>
       <c r="D3" s="64">
         <v>2026</v>
@@ -4153,22 +4160,22 @@
         <v>1</v>
       </c>
       <c r="F3" s="64" t="s">
-        <v>188</v>
+        <v>429</v>
       </c>
       <c r="G3" s="64"/>
       <c r="H3" s="77"/>
       <c r="I3" s="77"/>
     </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="72" t="s">
-        <v>966</v>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="76" t="s">
+        <v>968</v>
       </c>
       <c r="B4" s="64" t="str">
         <f t="shared" ref="B4" si="2">LEFT(A4)</f>
-        <v>S</v>
+        <v>G</v>
       </c>
       <c r="C4" s="64" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="D4" s="64">
         <v>2026</v>
@@ -4177,24 +4184,22 @@
         <v>1</v>
       </c>
       <c r="F4" s="64" t="s">
-        <v>104</v>
-      </c>
-      <c r="G4" s="65" t="s">
-        <v>182</v>
-      </c>
-      <c r="H4" s="64"/>
-      <c r="I4" s="64"/>
-    </row>
-    <row r="5" spans="1:9">
+        <v>188</v>
+      </c>
+      <c r="G4" s="64"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="77"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="72" t="s">
-        <v>347</v>
+        <v>966</v>
       </c>
       <c r="B5" s="64" t="str">
         <f t="shared" ref="B5" si="3">LEFT(A5)</f>
-        <v>T</v>
+        <v>S</v>
       </c>
       <c r="C5" s="64" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="D5" s="64">
         <v>2026</v>
@@ -4202,23 +4207,25 @@
       <c r="E5" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="F5" s="73" t="s">
-        <v>253</v>
-      </c>
-      <c r="G5" s="64"/>
+      <c r="F5" s="64" t="s">
+        <v>104</v>
+      </c>
+      <c r="G5" s="65" t="s">
+        <v>182</v>
+      </c>
       <c r="H5" s="64"/>
       <c r="I5" s="64"/>
     </row>
-    <row r="6" spans="1:9">
-      <c r="A6" s="68" t="s">
-        <v>958</v>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="72" t="s">
+        <v>347</v>
       </c>
       <c r="B6" s="64" t="str">
         <f t="shared" ref="B6" si="4">LEFT(A6)</f>
-        <v>B</v>
+        <v>T</v>
       </c>
       <c r="C6" s="64" t="s">
-        <v>172</v>
+        <v>965</v>
       </c>
       <c r="D6" s="64">
         <v>2026</v>
@@ -4226,23 +4233,23 @@
       <c r="E6" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="F6" s="64" t="s">
-        <v>112</v>
-      </c>
-      <c r="G6" s="74"/>
-      <c r="H6" s="74"/>
-      <c r="I6" s="74"/>
-    </row>
-    <row r="7" spans="1:9">
+      <c r="F6" s="73" t="s">
+        <v>253</v>
+      </c>
+      <c r="G6" s="64"/>
+      <c r="H6" s="64"/>
+      <c r="I6" s="64"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="68" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
       <c r="B7" s="64" t="str">
         <f t="shared" ref="B7" si="5">LEFT(A7)</f>
         <v>B</v>
       </c>
       <c r="C7" s="64" t="s">
-        <v>957</v>
+        <v>172</v>
       </c>
       <c r="D7" s="64">
         <v>2026</v>
@@ -4251,22 +4258,22 @@
         <v>1</v>
       </c>
       <c r="F7" s="64" t="s">
-        <v>188</v>
-      </c>
-      <c r="G7" s="64"/>
-      <c r="H7" s="64"/>
-      <c r="I7" s="64"/>
-    </row>
-    <row r="8" spans="1:9">
+        <v>112</v>
+      </c>
+      <c r="G7" s="74"/>
+      <c r="H7" s="74"/>
+      <c r="I7" s="74"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="68" t="s">
-        <v>950</v>
+        <v>956</v>
       </c>
       <c r="B8" s="64" t="str">
         <f t="shared" ref="B8" si="6">LEFT(A8)</f>
-        <v>K</v>
+        <v>B</v>
       </c>
       <c r="C8" s="64" t="s">
-        <v>951</v>
+        <v>957</v>
       </c>
       <c r="D8" s="64">
         <v>2026</v>
@@ -4275,22 +4282,22 @@
         <v>1</v>
       </c>
       <c r="F8" s="64" t="s">
-        <v>952</v>
+        <v>188</v>
       </c>
       <c r="G8" s="64"/>
       <c r="H8" s="64"/>
       <c r="I8" s="64"/>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="68" t="s">
-        <v>948</v>
+        <v>950</v>
       </c>
       <c r="B9" s="64" t="str">
         <f t="shared" ref="B9" si="7">LEFT(A9)</f>
-        <v>C</v>
+        <v>K</v>
       </c>
       <c r="C9" s="64" t="s">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="D9" s="64">
         <v>2026</v>
@@ -4299,22 +4306,22 @@
         <v>1</v>
       </c>
       <c r="F9" s="64" t="s">
-        <v>136</v>
+        <v>952</v>
       </c>
       <c r="G9" s="64"/>
       <c r="H9" s="64"/>
       <c r="I9" s="64"/>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="68" t="s">
-        <v>946</v>
+        <v>948</v>
       </c>
       <c r="B10" s="64" t="str">
-        <f t="shared" ref="B10:B74" si="8">LEFT(A10)</f>
-        <v>V</v>
+        <f t="shared" ref="B10" si="8">LEFT(A10)</f>
+        <v>C</v>
       </c>
       <c r="C10" s="64" t="s">
-        <v>947</v>
+        <v>949</v>
       </c>
       <c r="D10" s="64">
         <v>2026</v>
@@ -4323,24 +4330,22 @@
         <v>1</v>
       </c>
       <c r="F10" s="64" t="s">
-        <v>104</v>
-      </c>
-      <c r="G10" s="65" t="s">
-        <v>182</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="G10" s="64"/>
       <c r="H10" s="64"/>
       <c r="I10" s="64"/>
     </row>
-    <row r="11" spans="1:9">
-      <c r="A11" s="69" t="s">
-        <v>944</v>
-      </c>
-      <c r="B11" s="66" t="str">
-        <f t="shared" si="8"/>
-        <v>H</v>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="68" t="s">
+        <v>946</v>
+      </c>
+      <c r="B11" s="64" t="str">
+        <f t="shared" ref="B11:B75" si="9">LEFT(A11)</f>
+        <v>V</v>
       </c>
       <c r="C11" s="64" t="s">
-        <v>945</v>
+        <v>947</v>
       </c>
       <c r="D11" s="64">
         <v>2026</v>
@@ -4349,69 +4354,72 @@
         <v>1</v>
       </c>
       <c r="F11" s="64" t="s">
-        <v>459</v>
-      </c>
-      <c r="G11" s="64"/>
+        <v>104</v>
+      </c>
+      <c r="G11" s="65" t="s">
+        <v>182</v>
+      </c>
       <c r="H11" s="64"/>
       <c r="I11" s="64"/>
     </row>
-    <row r="12" spans="1:9">
-      <c r="A12" s="66" t="s">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="69" t="s">
+        <v>944</v>
+      </c>
+      <c r="B12" s="66" t="str">
+        <f t="shared" si="9"/>
+        <v>H</v>
+      </c>
+      <c r="C12" s="64" t="s">
+        <v>945</v>
+      </c>
+      <c r="D12" s="64">
+        <v>2026</v>
+      </c>
+      <c r="E12" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="F12" s="64" t="s">
+        <v>459</v>
+      </c>
+      <c r="G12" s="64"/>
+      <c r="H12" s="64"/>
+      <c r="I12" s="64"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="66" t="s">
         <v>83</v>
       </c>
-      <c r="B12" s="66" t="str">
-        <f t="shared" si="8"/>
+      <c r="B13" s="66" t="str">
+        <f t="shared" si="9"/>
         <v>A</v>
       </c>
-      <c r="C12" s="66" t="s">
+      <c r="C13" s="66" t="s">
         <v>84</v>
       </c>
-      <c r="D12" s="66">
+      <c r="D13" s="66">
         <v>2025</v>
       </c>
-      <c r="E12" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="F12" s="66" t="s">
+      <c r="E13" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="F13" s="66" t="s">
         <v>85</v>
       </c>
-      <c r="G12" s="66"/>
-      <c r="H12" s="67"/>
-      <c r="I12" s="67"/>
-    </row>
-    <row r="13" spans="1:9">
-      <c r="A13" s="1" t="s">
+      <c r="G13" s="66"/>
+      <c r="H13" s="67"/>
+      <c r="I13" s="67"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="B13" s="1" t="str">
-        <f t="shared" si="8"/>
+      <c r="B14" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>A</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C14" s="1" t="s">
         <v>87</v>
-      </c>
-      <c r="D13" s="1">
-        <v>2025</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="G13" s="1"/>
-      <c r="H13" s="75"/>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="A14" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="B14" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>B</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>90</v>
       </c>
       <c r="D14" s="1">
         <v>2025</v>
@@ -4420,20 +4428,21 @@
         <v>1</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G14" s="1"/>
-    </row>
-    <row r="15" spans="1:9">
+      <c r="H14" s="75"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B15" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>C</v>
+        <f t="shared" si="9"/>
+        <v>B</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D15" s="1">
         <v>2025</v>
@@ -4442,20 +4451,20 @@
         <v>1</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="G15" s="1"/>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B16" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>D</v>
+        <f t="shared" si="9"/>
+        <v>C</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D16" s="1">
         <v>2025</v>
@@ -4464,20 +4473,20 @@
         <v>1</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>37</v>
+        <v>94</v>
       </c>
       <c r="G16" s="1"/>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B17" s="1" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>D</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D17" s="1">
         <v>2025</v>
@@ -4486,20 +4495,20 @@
         <v>1</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>99</v>
+        <v>37</v>
       </c>
       <c r="G17" s="1"/>
     </row>
-    <row r="18" spans="1:8">
-      <c r="A18" s="36" t="s">
-        <v>100</v>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>97</v>
       </c>
       <c r="B18" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>F</v>
+        <f t="shared" si="9"/>
+        <v>D</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D18" s="1">
         <v>2025</v>
@@ -4508,20 +4517,20 @@
         <v>1</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="G18" s="1"/>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="36" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B19" s="1" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>F</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D19" s="1">
         <v>2025</v>
@@ -4530,20 +4539,20 @@
         <v>1</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="G19" s="1"/>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="36" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B20" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>G</v>
+        <f t="shared" si="9"/>
+        <v>F</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D20" s="1">
         <v>2025</v>
@@ -4552,20 +4561,20 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="G20" s="1"/>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="36" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B21" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>H</v>
+        <f t="shared" si="9"/>
+        <v>G</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D21" s="1">
         <v>2025</v>
@@ -4574,20 +4583,20 @@
         <v>1</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="G21" s="1"/>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="36" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B22" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>J</v>
+        <f t="shared" si="9"/>
+        <v>H</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D22" s="1">
         <v>2025</v>
@@ -4596,20 +4605,20 @@
         <v>1</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="G22" s="1"/>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="36" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B23" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>L</v>
+        <f t="shared" si="9"/>
+        <v>J</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D23" s="1">
         <v>2025</v>
@@ -4618,23 +4627,20 @@
         <v>1</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="G23" s="1"/>
-      <c r="H23" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8">
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="36" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B24" s="1" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>L</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D24" s="1">
         <v>2025</v>
@@ -4643,20 +4649,23 @@
         <v>1</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="G24" s="1"/>
-    </row>
-    <row r="25" spans="1:8">
+      <c r="H24" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="36" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B25" s="1" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>L</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D25" s="1">
         <v>2025</v>
@@ -4665,20 +4674,20 @@
         <v>1</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="G25" s="1"/>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="36" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B26" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>M</v>
+        <f t="shared" si="9"/>
+        <v>L</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D26" s="1">
         <v>2025</v>
@@ -4687,20 +4696,20 @@
         <v>1</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G26" s="1"/>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="36" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B27" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>P</v>
+        <f t="shared" si="9"/>
+        <v>M</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D27" s="1">
         <v>2025</v>
@@ -4709,20 +4718,20 @@
         <v>1</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="G27" s="1"/>
     </row>
-    <row r="28" spans="1:8">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="36" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B28" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>S</v>
+        <f t="shared" si="9"/>
+        <v>P</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D28" s="1">
         <v>2025</v>
@@ -4731,20 +4740,20 @@
         <v>1</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="G28" s="1"/>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="36" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B29" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>V</v>
+        <f t="shared" si="9"/>
+        <v>S</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D29" s="1">
         <v>2025</v>
@@ -4753,20 +4762,20 @@
         <v>1</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="G29" s="1"/>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="36" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B30" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>W</v>
+        <f t="shared" si="9"/>
+        <v>V</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D30" s="1">
         <v>2025</v>
@@ -4775,42 +4784,42 @@
         <v>1</v>
       </c>
       <c r="F30" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="G30" s="1"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="36" t="s">
+        <v>134</v>
+      </c>
+      <c r="B31" s="1" t="str">
+        <f t="shared" si="9"/>
+        <v>W</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="D31" s="1">
+        <v>2025</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F31" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="G30" s="1"/>
-    </row>
-    <row r="31" spans="1:8">
-      <c r="A31" s="38" t="s">
+      <c r="G31" s="1"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="38" t="s">
         <v>137</v>
       </c>
-      <c r="B31" s="1" t="str">
-        <f t="shared" si="8"/>
+      <c r="B32" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>B</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C32" s="1" t="s">
         <v>138</v>
-      </c>
-      <c r="D31" s="1">
-        <v>2024</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="G31" s="1"/>
-    </row>
-    <row r="32" spans="1:8">
-      <c r="A32" s="38" t="s">
-        <v>140</v>
-      </c>
-      <c r="B32" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>B</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>141</v>
       </c>
       <c r="D32" s="1">
         <v>2024</v>
@@ -4819,20 +4828,20 @@
         <v>1</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="G32" s="1"/>
     </row>
-    <row r="33" spans="1:8">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="38" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B33" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>C</v>
+        <f t="shared" si="9"/>
+        <v>B</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D33" s="1">
         <v>2024</v>
@@ -4841,20 +4850,20 @@
         <v>1</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="G33" s="1"/>
     </row>
-    <row r="34" spans="1:8">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="38" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B34" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>D</v>
+        <f t="shared" si="9"/>
+        <v>C</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D34" s="1">
         <v>2024</v>
@@ -4863,20 +4872,20 @@
         <v>1</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>104</v>
+        <v>145</v>
       </c>
       <c r="G34" s="1"/>
     </row>
-    <row r="35" spans="1:8">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="38" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B35" s="1" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>D</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D35" s="1">
         <v>2024</v>
@@ -4885,20 +4894,20 @@
         <v>1</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="G35" s="1"/>
     </row>
-    <row r="36" spans="1:8">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="38" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B36" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>F</v>
+        <f t="shared" si="9"/>
+        <v>D</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>101</v>
+        <v>149</v>
       </c>
       <c r="D36" s="1">
         <v>2024</v>
@@ -4907,20 +4916,20 @@
         <v>1</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="G36" s="1"/>
     </row>
-    <row r="37" spans="1:8">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="38" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B37" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>H</v>
+        <f t="shared" si="9"/>
+        <v>F</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>152</v>
+        <v>101</v>
       </c>
       <c r="D37" s="1">
         <v>2024</v>
@@ -4929,20 +4938,20 @@
         <v>1</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>139</v>
+        <v>104</v>
       </c>
       <c r="G37" s="1"/>
     </row>
-    <row r="38" spans="1:8">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="38" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B38" s="1" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>H</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D38" s="1">
         <v>2024</v>
@@ -4951,18 +4960,20 @@
         <v>1</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="G38" s="1"/>
     </row>
-    <row r="39" spans="1:8">
-      <c r="A39" s="1"/>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" s="38" t="s">
+        <v>153</v>
+      </c>
       <c r="B39" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v/>
+        <f t="shared" si="9"/>
+        <v>H</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D39" s="1">
         <v>2024</v>
@@ -4970,19 +4981,19 @@
       <c r="E39" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F39" s="1"/>
+      <c r="F39" s="1" t="s">
+        <v>136</v>
+      </c>
       <c r="G39" s="1"/>
     </row>
-    <row r="40" spans="1:8">
-      <c r="A40" s="38" t="s">
-        <v>156</v>
-      </c>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" s="1"/>
       <c r="B40" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>J</v>
+        <f t="shared" si="9"/>
+        <v/>
       </c>
       <c r="C40" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D40" s="1">
         <v>2024</v>
@@ -4990,21 +5001,19 @@
       <c r="E40" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F40" s="1" t="s">
-        <v>94</v>
-      </c>
+      <c r="F40" s="1"/>
       <c r="G40" s="1"/>
     </row>
-    <row r="41" spans="1:8">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="38" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B41" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>L</v>
+        <f t="shared" si="9"/>
+        <v>J</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D41" s="1">
         <v>2024</v>
@@ -5013,20 +5022,20 @@
         <v>1</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>139</v>
+        <v>94</v>
       </c>
       <c r="G41" s="1"/>
     </row>
-    <row r="42" spans="1:8">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="38" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B42" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>N</v>
+        <f t="shared" si="9"/>
+        <v>L</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D42" s="1">
         <v>2024</v>
@@ -5035,23 +5044,20 @@
         <v>1</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>115</v>
+        <v>139</v>
       </c>
       <c r="G42" s="1"/>
-      <c r="H42" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8">
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="38" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B43" s="1" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>N</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D43" s="1">
         <v>2024</v>
@@ -5063,15 +5069,20 @@
         <v>115</v>
       </c>
       <c r="G43" s="1"/>
-    </row>
-    <row r="44" spans="1:8">
-      <c r="A44" s="1"/>
+      <c r="H43" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" s="38" t="s">
+        <v>163</v>
+      </c>
       <c r="B44" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v/>
+        <f t="shared" si="9"/>
+        <v>N</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D44" s="1">
         <v>2024</v>
@@ -5080,20 +5091,18 @@
         <v>1</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>85</v>
+        <v>115</v>
       </c>
       <c r="G44" s="1"/>
     </row>
-    <row r="45" spans="1:8">
-      <c r="A45" s="38" t="s">
-        <v>166</v>
-      </c>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" s="1"/>
       <c r="B45" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>P</v>
+        <f t="shared" si="9"/>
+        <v/>
       </c>
       <c r="C45" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D45" s="1">
         <v>2024</v>
@@ -5106,16 +5115,16 @@
       </c>
       <c r="G45" s="1"/>
     </row>
-    <row r="46" spans="1:8">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="38" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B46" s="1" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>P</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D46" s="1">
         <v>2024</v>
@@ -5124,20 +5133,20 @@
         <v>1</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>169</v>
+        <v>85</v>
       </c>
       <c r="G46" s="1"/>
     </row>
-    <row r="47" spans="1:8">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="38" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B47" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>R</v>
+        <f t="shared" si="9"/>
+        <v>P</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="D47" s="1">
         <v>2024</v>
@@ -5146,20 +5155,20 @@
         <v>1</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>37</v>
+        <v>169</v>
       </c>
       <c r="G47" s="1"/>
     </row>
-    <row r="48" spans="1:8">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="38" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B48" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>S</v>
+        <f t="shared" si="9"/>
+        <v>R</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="D48" s="1">
         <v>2024</v>
@@ -5168,20 +5177,20 @@
         <v>1</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>115</v>
+        <v>37</v>
       </c>
       <c r="G48" s="1"/>
     </row>
-    <row r="49" spans="1:7">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="38" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B49" s="1" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>S</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D49" s="1">
         <v>2024</v>
@@ -5194,16 +5203,16 @@
       </c>
       <c r="G49" s="1"/>
     </row>
-    <row r="50" spans="1:7">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="38" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B50" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>T</v>
+        <f t="shared" si="9"/>
+        <v>S</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D50" s="1">
         <v>2024</v>
@@ -5212,42 +5221,42 @@
         <v>1</v>
       </c>
       <c r="F50" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G50" s="1"/>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51" s="38" t="s">
+        <v>175</v>
+      </c>
+      <c r="B51" s="1" t="str">
+        <f t="shared" si="9"/>
+        <v>T</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="D51" s="1">
+        <v>2024</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F51" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="G50" s="1"/>
-    </row>
-    <row r="51" spans="1:7">
-      <c r="A51" s="38" t="s">
+      <c r="G51" s="1"/>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A52" s="38" t="s">
         <v>177</v>
       </c>
-      <c r="B51" s="1" t="str">
-        <f t="shared" si="8"/>
+      <c r="B52" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>B</v>
       </c>
-      <c r="C51" s="34" t="s">
+      <c r="C52" s="34" t="s">
         <v>178</v>
-      </c>
-      <c r="D51" s="29">
-        <v>2023</v>
-      </c>
-      <c r="E51" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="F51" s="35" t="s">
-        <v>139</v>
-      </c>
-      <c r="G51" s="35"/>
-    </row>
-    <row r="52" spans="1:7">
-      <c r="A52" s="38" t="s">
-        <v>179</v>
-      </c>
-      <c r="B52" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>B</v>
-      </c>
-      <c r="C52" s="34" t="s">
-        <v>128</v>
       </c>
       <c r="D52" s="29">
         <v>2023</v>
@@ -5256,20 +5265,20 @@
         <v>1</v>
       </c>
       <c r="F52" s="35" t="s">
-        <v>112</v>
+        <v>139</v>
       </c>
       <c r="G52" s="35"/>
     </row>
-    <row r="53" spans="1:7">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="38" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B53" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>C</v>
+        <f t="shared" si="9"/>
+        <v>B</v>
       </c>
       <c r="C53" s="34" t="s">
-        <v>181</v>
+        <v>128</v>
       </c>
       <c r="D53" s="29">
         <v>2023</v>
@@ -5277,21 +5286,21 @@
       <c r="E53" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="F53" s="30" t="s">
-        <v>104</v>
-      </c>
-      <c r="G53" s="35" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7">
-      <c r="A54" s="1"/>
+      <c r="F53" s="35" t="s">
+        <v>112</v>
+      </c>
+      <c r="G53" s="35"/>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A54" s="38" t="s">
+        <v>180</v>
+      </c>
       <c r="B54" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v/>
+        <f t="shared" si="9"/>
+        <v>C</v>
       </c>
       <c r="C54" s="34" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D54" s="29">
         <v>2023</v>
@@ -5306,14 +5315,14 @@
         <v>182</v>
       </c>
     </row>
-    <row r="55" spans="1:7">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="1"/>
       <c r="B55" s="1" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="C55" s="34" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D55" s="29">
         <v>2023</v>
@@ -5328,14 +5337,14 @@
         <v>182</v>
       </c>
     </row>
-    <row r="56" spans="1:7">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="1"/>
       <c r="B56" s="1" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="C56" s="34" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D56" s="29">
         <v>2023</v>
@@ -5343,21 +5352,21 @@
       <c r="E56" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="F56" s="35" t="s">
-        <v>139</v>
-      </c>
-      <c r="G56" s="35"/>
-    </row>
-    <row r="57" spans="1:7">
-      <c r="A57" s="38" t="s">
-        <v>186</v>
-      </c>
+      <c r="F56" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="G56" s="35" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A57" s="1"/>
       <c r="B57" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>H</v>
+        <f t="shared" si="9"/>
+        <v/>
       </c>
       <c r="C57" s="34" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D57" s="29">
         <v>2023</v>
@@ -5366,20 +5375,20 @@
         <v>1</v>
       </c>
       <c r="F57" s="35" t="s">
-        <v>188</v>
+        <v>139</v>
       </c>
       <c r="G57" s="35"/>
     </row>
-    <row r="58" spans="1:7">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="38" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="B58" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>J</v>
+        <f t="shared" si="9"/>
+        <v>H</v>
       </c>
       <c r="C58" s="34" t="s">
-        <v>84</v>
+        <v>187</v>
       </c>
       <c r="D58" s="29">
         <v>2023</v>
@@ -5388,20 +5397,20 @@
         <v>1</v>
       </c>
       <c r="F58" s="35" t="s">
-        <v>112</v>
+        <v>188</v>
       </c>
       <c r="G58" s="35"/>
     </row>
-    <row r="59" spans="1:7">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="38" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B59" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>K</v>
+        <f t="shared" si="9"/>
+        <v>J</v>
       </c>
       <c r="C59" s="34" t="s">
-        <v>191</v>
+        <v>84</v>
       </c>
       <c r="D59" s="29">
         <v>2023</v>
@@ -5414,16 +5423,16 @@
       </c>
       <c r="G59" s="35"/>
     </row>
-    <row r="60" spans="1:7">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="38" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B60" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>L</v>
+        <f t="shared" si="9"/>
+        <v>K</v>
       </c>
       <c r="C60" s="34" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D60" s="29">
         <v>2023</v>
@@ -5432,20 +5441,20 @@
         <v>1</v>
       </c>
       <c r="F60" s="35" t="s">
-        <v>194</v>
+        <v>112</v>
       </c>
       <c r="G60" s="35"/>
     </row>
-    <row r="61" spans="1:7">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="38" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B61" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>M</v>
+        <f t="shared" si="9"/>
+        <v>L</v>
       </c>
       <c r="C61" s="34" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D61" s="29">
         <v>2023</v>
@@ -5454,20 +5463,20 @@
         <v>1</v>
       </c>
       <c r="F61" s="35" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="G61" s="35"/>
     </row>
-    <row r="62" spans="1:7">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="38" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B62" s="1" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>M</v>
       </c>
       <c r="C62" s="34" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="D62" s="29">
         <v>2023</v>
@@ -5475,21 +5484,21 @@
       <c r="E62" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="F62" s="30" t="s">
-        <v>104</v>
+      <c r="F62" s="35" t="s">
+        <v>197</v>
       </c>
       <c r="G62" s="35"/>
     </row>
-    <row r="63" spans="1:7">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="38" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B63" s="1" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>M</v>
       </c>
       <c r="C63" s="34" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D63" s="29">
         <v>2023</v>
@@ -5497,21 +5506,21 @@
       <c r="E63" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="F63" s="35" t="s">
-        <v>112</v>
+      <c r="F63" s="30" t="s">
+        <v>104</v>
       </c>
       <c r="G63" s="35"/>
     </row>
-    <row r="64" spans="1:7">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="38" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B64" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>P</v>
+        <f t="shared" si="9"/>
+        <v>M</v>
       </c>
       <c r="C64" s="34" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D64" s="29">
         <v>2023</v>
@@ -5519,21 +5528,21 @@
       <c r="E64" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="F64" s="30" t="s">
-        <v>104</v>
+      <c r="F64" s="35" t="s">
+        <v>112</v>
       </c>
       <c r="G64" s="35"/>
     </row>
-    <row r="65" spans="1:7">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="38" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B65" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>T</v>
+        <f t="shared" si="9"/>
+        <v>P</v>
       </c>
       <c r="C65" s="34" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D65" s="29">
         <v>2023</v>
@@ -5541,21 +5550,21 @@
       <c r="E65" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="F65" s="35" t="s">
-        <v>169</v>
+      <c r="F65" s="30" t="s">
+        <v>104</v>
       </c>
       <c r="G65" s="35"/>
     </row>
-    <row r="66" spans="1:7">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="38" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B66" s="1" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>T</v>
       </c>
       <c r="C66" s="34" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D66" s="29">
         <v>2023</v>
@@ -5564,20 +5573,20 @@
         <v>1</v>
       </c>
       <c r="F66" s="35" t="s">
-        <v>85</v>
+        <v>169</v>
       </c>
       <c r="G66" s="35"/>
     </row>
-    <row r="67" spans="1:7">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="38" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B67" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>V</v>
+        <f t="shared" si="9"/>
+        <v>T</v>
       </c>
       <c r="C67" s="34" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D67" s="29">
         <v>2023</v>
@@ -5585,43 +5594,43 @@
       <c r="E67" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="F67" s="30" t="s">
+      <c r="F67" s="35" t="s">
+        <v>85</v>
+      </c>
+      <c r="G67" s="35"/>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A68" s="38" t="s">
+        <v>208</v>
+      </c>
+      <c r="B68" s="1" t="str">
+        <f t="shared" si="9"/>
+        <v>V</v>
+      </c>
+      <c r="C68" s="34" t="s">
+        <v>209</v>
+      </c>
+      <c r="D68" s="29">
+        <v>2023</v>
+      </c>
+      <c r="E68" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="F68" s="30" t="s">
         <v>104</v>
       </c>
-      <c r="G67" s="35"/>
-    </row>
-    <row r="68" spans="1:7">
-      <c r="A68" s="38" t="s">
+      <c r="G68" s="35"/>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A69" s="38" t="s">
         <v>210</v>
       </c>
-      <c r="B68" s="1" t="str">
-        <f t="shared" si="8"/>
+      <c r="B69" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>A</v>
       </c>
-      <c r="C68" s="35" t="s">
+      <c r="C69" s="35" t="s">
         <v>211</v>
-      </c>
-      <c r="D68" s="29">
-        <v>2022</v>
-      </c>
-      <c r="E68" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="F68" s="35" t="s">
-        <v>212</v>
-      </c>
-      <c r="G68" s="35"/>
-    </row>
-    <row r="69" spans="1:7">
-      <c r="A69" s="38" t="s">
-        <v>213</v>
-      </c>
-      <c r="B69" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>A</v>
-      </c>
-      <c r="C69" s="35" t="s">
-        <v>214</v>
       </c>
       <c r="D69" s="29">
         <v>2022</v>
@@ -5630,20 +5639,20 @@
         <v>1</v>
       </c>
       <c r="F69" s="35" t="s">
-        <v>188</v>
+        <v>212</v>
       </c>
       <c r="G69" s="35"/>
     </row>
-    <row r="70" spans="1:7">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="38" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B70" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>B</v>
+        <f t="shared" si="9"/>
+        <v>A</v>
       </c>
       <c r="C70" s="35" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D70" s="29">
         <v>2022</v>
@@ -5652,20 +5661,20 @@
         <v>1</v>
       </c>
       <c r="F70" s="35" t="s">
-        <v>37</v>
+        <v>188</v>
       </c>
       <c r="G70" s="35"/>
     </row>
-    <row r="71" spans="1:7">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="38" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B71" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>C</v>
+        <f t="shared" si="9"/>
+        <v>B</v>
       </c>
       <c r="C71" s="35" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D71" s="29">
         <v>2022</v>
@@ -5674,20 +5683,20 @@
         <v>1</v>
       </c>
       <c r="F71" s="35" t="s">
-        <v>112</v>
+        <v>37</v>
       </c>
       <c r="G71" s="35"/>
     </row>
-    <row r="72" spans="1:7">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="38" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B72" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>D</v>
+        <f t="shared" si="9"/>
+        <v>C</v>
       </c>
       <c r="C72" s="35" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D72" s="29">
         <v>2022</v>
@@ -5696,20 +5705,20 @@
         <v>1</v>
       </c>
       <c r="F72" s="35" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="G72" s="35"/>
     </row>
-    <row r="73" spans="1:7">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="38" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B73" s="1" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>D</v>
       </c>
       <c r="C73" s="35" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D73" s="29">
         <v>2022</v>
@@ -5722,16 +5731,16 @@
       </c>
       <c r="G73" s="35"/>
     </row>
-    <row r="74" spans="1:7">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="38" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B74" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>G</v>
+        <f t="shared" si="9"/>
+        <v>D</v>
       </c>
       <c r="C74" s="35" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D74" s="29">
         <v>2022</v>
@@ -5740,22 +5749,20 @@
         <v>1</v>
       </c>
       <c r="F74" s="35" t="s">
-        <v>104</v>
-      </c>
-      <c r="G74" s="35" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7">
+        <v>122</v>
+      </c>
+      <c r="G74" s="35"/>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="38" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B75" s="1" t="str">
-        <f t="shared" ref="B75:B93" si="9">LEFT(A75)</f>
+        <f t="shared" si="9"/>
         <v>G</v>
       </c>
       <c r="C75" s="35" t="s">
-        <v>128</v>
+        <v>224</v>
       </c>
       <c r="D75" s="29">
         <v>2022</v>
@@ -5764,20 +5771,22 @@
         <v>1</v>
       </c>
       <c r="F75" s="35" t="s">
-        <v>37</v>
-      </c>
-      <c r="G75" s="29"/>
-    </row>
-    <row r="76" spans="1:7">
+        <v>104</v>
+      </c>
+      <c r="G75" s="35" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="38" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B76" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>M</v>
+        <f t="shared" ref="B76:B94" si="10">LEFT(A76)</f>
+        <v>G</v>
       </c>
       <c r="C76" s="35" t="s">
-        <v>227</v>
+        <v>128</v>
       </c>
       <c r="D76" s="29">
         <v>2022</v>
@@ -5786,22 +5795,20 @@
         <v>1</v>
       </c>
       <c r="F76" s="35" t="s">
-        <v>104</v>
-      </c>
-      <c r="G76" s="35" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7">
+        <v>37</v>
+      </c>
+      <c r="G76" s="29"/>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="38" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B77" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>R</v>
+        <f t="shared" si="10"/>
+        <v>M</v>
       </c>
       <c r="C77" s="35" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D77" s="29">
         <v>2022</v>
@@ -5810,20 +5817,22 @@
         <v>1</v>
       </c>
       <c r="F77" s="35" t="s">
-        <v>122</v>
-      </c>
-      <c r="G77" s="35"/>
-    </row>
-    <row r="78" spans="1:7">
+        <v>104</v>
+      </c>
+      <c r="G77" s="35" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="38" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B78" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>R</v>
       </c>
       <c r="C78" s="35" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D78" s="29">
         <v>2022</v>
@@ -5832,20 +5841,20 @@
         <v>1</v>
       </c>
       <c r="F78" s="35" t="s">
-        <v>232</v>
+        <v>122</v>
       </c>
       <c r="G78" s="35"/>
     </row>
-    <row r="79" spans="1:7">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="38" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B79" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>V</v>
+        <f t="shared" si="10"/>
+        <v>R</v>
       </c>
       <c r="C79" s="35" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="D79" s="29">
         <v>2022</v>
@@ -5854,42 +5863,42 @@
         <v>1</v>
       </c>
       <c r="F79" s="35" t="s">
+        <v>232</v>
+      </c>
+      <c r="G79" s="35"/>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A80" s="38" t="s">
+        <v>233</v>
+      </c>
+      <c r="B80" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>V</v>
+      </c>
+      <c r="C80" s="35" t="s">
+        <v>234</v>
+      </c>
+      <c r="D80" s="29">
+        <v>2022</v>
+      </c>
+      <c r="E80" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="F80" s="35" t="s">
         <v>139</v>
       </c>
-      <c r="G79" s="35"/>
-    </row>
-    <row r="80" spans="1:7">
-      <c r="A80" s="35" t="s">
+      <c r="G80" s="35"/>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A81" s="35" t="s">
         <v>235</v>
       </c>
-      <c r="B80" s="1" t="str">
-        <f t="shared" si="9"/>
+      <c r="B81" s="1" t="str">
+        <f t="shared" si="10"/>
         <v>A</v>
       </c>
-      <c r="C80" s="35" t="s">
+      <c r="C81" s="35" t="s">
         <v>236</v>
-      </c>
-      <c r="D80" s="29">
-        <v>2021</v>
-      </c>
-      <c r="E80" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="F80" s="35" t="s">
-        <v>126</v>
-      </c>
-      <c r="G80" s="1"/>
-    </row>
-    <row r="81" spans="1:7">
-      <c r="A81" s="35" t="s">
-        <v>237</v>
-      </c>
-      <c r="B81" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>B</v>
-      </c>
-      <c r="C81" s="35" t="s">
-        <v>238</v>
       </c>
       <c r="D81" s="29">
         <v>2021</v>
@@ -5898,20 +5907,20 @@
         <v>1</v>
       </c>
       <c r="F81" s="35" t="s">
-        <v>188</v>
+        <v>126</v>
       </c>
       <c r="G81" s="1"/>
     </row>
-    <row r="82" spans="1:7">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="35" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B82" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>B</v>
       </c>
       <c r="C82" s="35" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D82" s="29">
         <v>2021</v>
@@ -5920,20 +5929,20 @@
         <v>1</v>
       </c>
       <c r="F82" s="35" t="s">
-        <v>241</v>
+        <v>188</v>
       </c>
       <c r="G82" s="1"/>
     </row>
-    <row r="83" spans="1:7">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="35" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B83" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>C</v>
+        <f t="shared" si="10"/>
+        <v>B</v>
       </c>
       <c r="C83" s="35" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="D83" s="29">
         <v>2021</v>
@@ -5942,20 +5951,20 @@
         <v>1</v>
       </c>
       <c r="F83" s="35" t="s">
-        <v>122</v>
+        <v>241</v>
       </c>
       <c r="G83" s="1"/>
     </row>
-    <row r="84" spans="1:7">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="35" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B84" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>C</v>
       </c>
       <c r="C84" s="35" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="D84" s="29">
         <v>2021</v>
@@ -5964,20 +5973,20 @@
         <v>1</v>
       </c>
       <c r="F84" s="35" t="s">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="G84" s="1"/>
     </row>
-    <row r="85" spans="1:7">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="35" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B85" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>C</v>
       </c>
       <c r="C85" s="35" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="D85" s="29">
         <v>2021</v>
@@ -5986,20 +5995,20 @@
         <v>1</v>
       </c>
       <c r="F85" s="35" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="G85" s="1"/>
     </row>
-    <row r="86" spans="1:7">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="35" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B86" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>C</v>
       </c>
       <c r="C86" s="35" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="D86" s="29">
         <v>2021</v>
@@ -6008,20 +6017,20 @@
         <v>1</v>
       </c>
       <c r="F86" s="35" t="s">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="G86" s="1"/>
     </row>
-    <row r="87" spans="1:7">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="35" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B87" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>E</v>
+        <f t="shared" si="10"/>
+        <v>C</v>
       </c>
       <c r="C87" s="35" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D87" s="29">
         <v>2021</v>
@@ -6030,20 +6039,20 @@
         <v>1</v>
       </c>
       <c r="F87" s="35" t="s">
-        <v>37</v>
+        <v>139</v>
       </c>
       <c r="G87" s="1"/>
     </row>
-    <row r="88" spans="1:7">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="35" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B88" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>G</v>
+        <f t="shared" si="10"/>
+        <v>E</v>
       </c>
       <c r="C88" s="35" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D88" s="29">
         <v>2021</v>
@@ -6052,20 +6061,20 @@
         <v>1</v>
       </c>
       <c r="F88" s="35" t="s">
-        <v>253</v>
+        <v>37</v>
       </c>
       <c r="G88" s="1"/>
     </row>
-    <row r="89" spans="1:7">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="35" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B89" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>J</v>
+        <f t="shared" si="10"/>
+        <v>G</v>
       </c>
       <c r="C89" s="35" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D89" s="29">
         <v>2021</v>
@@ -6074,20 +6083,20 @@
         <v>1</v>
       </c>
       <c r="F89" s="35" t="s">
-        <v>104</v>
+        <v>253</v>
       </c>
       <c r="G89" s="1"/>
     </row>
-    <row r="90" spans="1:7">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="35" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B90" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>L</v>
+        <f t="shared" si="10"/>
+        <v>J</v>
       </c>
       <c r="C90" s="35" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D90" s="29">
         <v>2021</v>
@@ -6096,20 +6105,20 @@
         <v>1</v>
       </c>
       <c r="F90" s="35" t="s">
-        <v>258</v>
+        <v>104</v>
       </c>
       <c r="G90" s="1"/>
     </row>
-    <row r="91" spans="1:7">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="35" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B91" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>M</v>
+        <f t="shared" si="10"/>
+        <v>L</v>
       </c>
       <c r="C91" s="35" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="D91" s="29">
         <v>2021</v>
@@ -6118,20 +6127,20 @@
         <v>1</v>
       </c>
       <c r="F91" s="35" t="s">
-        <v>112</v>
+        <v>258</v>
       </c>
       <c r="G91" s="1"/>
     </row>
-    <row r="92" spans="1:7">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="35" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B92" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>M</v>
       </c>
       <c r="C92" s="35" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D92" s="29">
         <v>2021</v>
@@ -6139,21 +6148,21 @@
       <c r="E92" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="F92" s="29" t="s">
-        <v>126</v>
+      <c r="F92" s="35" t="s">
+        <v>112</v>
       </c>
       <c r="G92" s="1"/>
     </row>
-    <row r="93" spans="1:7">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="35" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B93" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>N</v>
+        <f t="shared" si="10"/>
+        <v>M</v>
       </c>
       <c r="C93" s="35" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D93" s="29">
         <v>2021</v>
@@ -6161,21 +6170,21 @@
       <c r="E93" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="F93" s="35" t="s">
-        <v>122</v>
+      <c r="F93" s="29" t="s">
+        <v>126</v>
       </c>
       <c r="G93" s="1"/>
     </row>
-    <row r="94" spans="1:7">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="35" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B94" s="1" t="str">
-        <f t="shared" ref="B94:B110" si="10">LEFT(A94)</f>
-        <v>P</v>
+        <f t="shared" si="10"/>
+        <v>N</v>
       </c>
       <c r="C94" s="35" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D94" s="29">
         <v>2021</v>
@@ -6184,20 +6193,20 @@
         <v>1</v>
       </c>
       <c r="F94" s="35" t="s">
-        <v>267</v>
+        <v>122</v>
       </c>
       <c r="G94" s="1"/>
     </row>
-    <row r="95" spans="1:7">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="35" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="B95" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>R</v>
+        <f t="shared" ref="B95:B111" si="11">LEFT(A95)</f>
+        <v>P</v>
       </c>
       <c r="C95" s="35" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="D95" s="29">
         <v>2021</v>
@@ -6206,20 +6215,20 @@
         <v>1</v>
       </c>
       <c r="F95" s="35" t="s">
-        <v>212</v>
+        <v>267</v>
       </c>
       <c r="G95" s="1"/>
     </row>
-    <row r="96" spans="1:7">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="35" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B96" s="1" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>R</v>
       </c>
       <c r="C96" s="35" t="s">
-        <v>236</v>
+        <v>269</v>
       </c>
       <c r="D96" s="29">
         <v>2021</v>
@@ -6228,41 +6237,42 @@
         <v>1</v>
       </c>
       <c r="F96" s="35" t="s">
+        <v>212</v>
+      </c>
+      <c r="G96" s="1"/>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A97" s="35" t="s">
+        <v>270</v>
+      </c>
+      <c r="B97" s="1" t="str">
+        <f t="shared" si="11"/>
+        <v>R</v>
+      </c>
+      <c r="C97" s="35" t="s">
+        <v>236</v>
+      </c>
+      <c r="D97" s="29">
+        <v>2021</v>
+      </c>
+      <c r="E97" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="F97" s="35" t="s">
         <v>122</v>
       </c>
-      <c r="G96" s="1"/>
-    </row>
-    <row r="97" spans="1:6">
-      <c r="A97" s="35" t="s">
+      <c r="G97" s="1"/>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A98" s="35" t="s">
         <v>271</v>
       </c>
-      <c r="B97" s="1" t="str">
-        <f t="shared" si="10"/>
+      <c r="B98" s="1" t="str">
+        <f t="shared" si="11"/>
         <v>B</v>
       </c>
-      <c r="C97" s="35" t="s">
+      <c r="C98" s="35" t="s">
         <v>272</v>
-      </c>
-      <c r="D97" s="29">
-        <v>2020</v>
-      </c>
-      <c r="E97" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="F97" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6">
-      <c r="A98" s="35" t="s">
-        <v>273</v>
-      </c>
-      <c r="B98" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>A</v>
-      </c>
-      <c r="C98" s="35" t="s">
-        <v>274</v>
       </c>
       <c r="D98" s="29">
         <v>2020</v>
@@ -6271,121 +6281,153 @@
         <v>1</v>
       </c>
       <c r="F98" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A99" s="35" t="s">
+        <v>273</v>
+      </c>
+      <c r="B99" s="1" t="str">
+        <f t="shared" si="11"/>
+        <v>A</v>
+      </c>
+      <c r="C99" s="35" t="s">
+        <v>274</v>
+      </c>
+      <c r="D99" s="29">
+        <v>2020</v>
+      </c>
+      <c r="E99" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="F99" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="99" spans="1:6">
-      <c r="A99" s="35"/>
-      <c r="B99" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="E99" s="29" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6">
-      <c r="A100" s="35"/>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A100" s="35" t="s">
+        <v>1021</v>
+      </c>
       <c r="B100" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v/>
+        <f t="shared" si="11"/>
+        <v>V</v>
+      </c>
+      <c r="C100" s="35" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D100" s="29">
+        <v>2018</v>
       </c>
       <c r="E100" s="29" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="101" spans="1:6">
+      <c r="F100" s="35" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" s="35"/>
       <c r="B101" s="1" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="E101" s="29" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:6">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="35"/>
       <c r="B102" s="1" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="E102" s="29" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:6">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="35"/>
       <c r="B103" s="1" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="E103" s="29" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:6">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="35"/>
       <c r="B104" s="1" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="E104" s="29" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:6">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="35"/>
       <c r="B105" s="1" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="E105" s="29" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:6">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="35"/>
       <c r="B106" s="1" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="E106" s="29" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:6">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" s="35"/>
       <c r="B107" s="1" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="E107" s="29" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:6">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" s="35"/>
       <c r="B108" s="1" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="E108" s="29" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:6">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A109" s="35"/>
       <c r="B109" s="1" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="E109" s="29" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:6">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B110" s="1" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="E110" s="29" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B111" s="1" t="str">
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -6399,13 +6441,13 @@
           <x14:formula1>
             <xm:f>Ecoles!$A$2:$A$70</xm:f>
           </x14:formula1>
-          <xm:sqref>F110</xm:sqref>
+          <xm:sqref>F111</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{4FACBFD7-136B-4815-BD4C-3FC873C7A761}">
           <x14:formula1>
             <xm:f>Ecoles!$A$2:$A$71</xm:f>
           </x14:formula1>
-          <xm:sqref>F2:F109</xm:sqref>
+          <xm:sqref>F2:F110</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -6416,16 +6458,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:N127"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.33203125" customWidth="1"/>
-    <col min="2" max="2" width="16.5546875" customWidth="1"/>
-    <col min="6" max="6" width="42.33203125" customWidth="1"/>
-    <col min="8" max="8" width="32.33203125" customWidth="1"/>
-    <col min="9" max="9" width="96.6640625" customWidth="1"/>
+    <col min="1" max="1" width="19.28515625" customWidth="1"/>
+    <col min="2" max="2" width="16.5703125" customWidth="1"/>
+    <col min="6" max="6" width="42.28515625" customWidth="1"/>
+    <col min="8" max="8" width="32.28515625" customWidth="1"/>
+    <col min="9" max="9" width="96.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>275</v>
       </c>
@@ -6451,7 +6493,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1007</v>
       </c>
@@ -6471,10 +6513,10 @@
       <c r="F2" s="1" t="s">
         <v>1008</v>
       </c>
-      <c r="H2" s="84"/>
-      <c r="I2" s="84"/>
-    </row>
-    <row r="3" spans="1:14">
+      <c r="H2" s="83"/>
+      <c r="I2" s="83"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1005</v>
       </c>
@@ -6494,10 +6536,10 @@
       <c r="F3" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="H3" s="84"/>
-      <c r="I3" s="84"/>
-    </row>
-    <row r="4" spans="1:14">
+      <c r="H3" s="83"/>
+      <c r="I3" s="83"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>1003</v>
       </c>
@@ -6517,10 +6559,10 @@
       <c r="F4" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="H4" s="84"/>
-      <c r="I4" s="84"/>
-    </row>
-    <row r="5" spans="1:14">
+      <c r="H4" s="83"/>
+      <c r="I4" s="83"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>1002</v>
       </c>
@@ -6540,10 +6582,10 @@
       <c r="F5" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="H5" s="84"/>
-      <c r="I5" s="84"/>
-    </row>
-    <row r="6" spans="1:14">
+      <c r="H5" s="83"/>
+      <c r="I5" s="83"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>1001</v>
       </c>
@@ -6563,10 +6605,10 @@
       <c r="F6" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="H6" s="84"/>
-      <c r="I6" s="84"/>
-    </row>
-    <row r="7" spans="1:14">
+      <c r="H6" s="83"/>
+      <c r="I6" s="83"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>974</v>
       </c>
@@ -6586,10 +6628,10 @@
       <c r="F7" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="H7" s="84"/>
-      <c r="I7" s="84"/>
-    </row>
-    <row r="8" spans="1:14">
+      <c r="H7" s="83"/>
+      <c r="I7" s="83"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>971</v>
       </c>
@@ -6609,10 +6651,10 @@
       <c r="F8" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="H8" s="84"/>
-      <c r="I8" s="84"/>
-    </row>
-    <row r="9" spans="1:14">
+      <c r="H8" s="83"/>
+      <c r="I8" s="83"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>970</v>
       </c>
@@ -6632,10 +6674,10 @@
       <c r="F9" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="H9" s="84"/>
-      <c r="I9" s="84"/>
-    </row>
-    <row r="10" spans="1:14">
+      <c r="H9" s="83"/>
+      <c r="I9" s="83"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>959</v>
       </c>
@@ -6658,7 +6700,7 @@
       <c r="H10" s="74"/>
       <c r="I10" s="74"/>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>276</v>
       </c>
@@ -6681,7 +6723,7 @@
       <c r="H11" s="64"/>
       <c r="I11" s="64"/>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>278</v>
       </c>
@@ -6704,7 +6746,7 @@
       <c r="H12" s="64"/>
       <c r="I12" s="64"/>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>280</v>
       </c>
@@ -6725,7 +6767,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>281</v>
       </c>
@@ -6746,7 +6788,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>284</v>
       </c>
@@ -6773,7 +6815,7 @@
       <c r="M15" s="64"/>
       <c r="N15" s="1"/>
     </row>
-    <row r="16" spans="1:14">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>286</v>
       </c>
@@ -6794,7 +6836,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>288</v>
       </c>
@@ -6815,7 +6857,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>290</v>
       </c>
@@ -6836,7 +6878,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>292</v>
       </c>
@@ -6857,7 +6899,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>294</v>
       </c>
@@ -6878,7 +6920,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>105</v>
       </c>
@@ -6899,7 +6941,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>297</v>
       </c>
@@ -6920,7 +6962,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>299</v>
       </c>
@@ -6941,7 +6983,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>301</v>
       </c>
@@ -6962,7 +7004,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>303</v>
       </c>
@@ -6983,7 +7025,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>305</v>
       </c>
@@ -7004,7 +7046,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>307</v>
       </c>
@@ -7025,7 +7067,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>309</v>
       </c>
@@ -7046,7 +7088,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>311</v>
       </c>
@@ -7067,7 +7109,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>313</v>
       </c>
@@ -7088,7 +7130,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
         <v>315</v>
       </c>
@@ -7109,7 +7151,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="32" spans="1:6">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>316</v>
       </c>
@@ -7130,7 +7172,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="33" spans="1:8">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>318</v>
       </c>
@@ -7151,7 +7193,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="34" spans="1:8">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>320</v>
       </c>
@@ -7172,7 +7214,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="35" spans="1:8">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>321</v>
       </c>
@@ -7193,7 +7235,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="36" spans="1:8">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>323</v>
       </c>
@@ -7214,7 +7256,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="37" spans="1:8">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
         <v>325</v>
       </c>
@@ -7238,7 +7280,7 @@
         <v>1015</v>
       </c>
     </row>
-    <row r="38" spans="1:8">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
         <v>327</v>
       </c>
@@ -7259,7 +7301,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="39" spans="1:8">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
         <v>329</v>
       </c>
@@ -7280,7 +7322,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="40" spans="1:8">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
         <v>331</v>
       </c>
@@ -7301,7 +7343,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="41" spans="1:8">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
         <v>332</v>
       </c>
@@ -7322,7 +7364,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="42" spans="1:8">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
         <v>335</v>
       </c>
@@ -7343,7 +7385,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="43" spans="1:8">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
         <v>337</v>
       </c>
@@ -7364,7 +7406,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="44" spans="1:8">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="7" t="s">
         <v>339</v>
       </c>
@@ -7385,7 +7427,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="45" spans="1:8">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
         <v>341</v>
       </c>
@@ -7406,7 +7448,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="46" spans="1:8">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
         <v>343</v>
       </c>
@@ -7427,7 +7469,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="47" spans="1:8">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
         <v>346</v>
       </c>
@@ -7448,7 +7490,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="48" spans="1:8">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
         <v>348</v>
       </c>
@@ -7469,7 +7511,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="49" spans="1:9">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
         <v>350</v>
       </c>
@@ -7490,7 +7532,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="50" spans="1:9">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>351</v>
       </c>
@@ -7511,7 +7553,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="51" spans="1:9">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
         <v>354</v>
       </c>
@@ -7532,7 +7574,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="52" spans="1:9">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="7" t="s">
         <v>356</v>
       </c>
@@ -7553,7 +7595,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="53" spans="1:9">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
         <v>357</v>
       </c>
@@ -7574,7 +7616,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="54" spans="1:9">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
         <v>359</v>
       </c>
@@ -7598,7 +7640,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="55" spans="1:9">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
         <v>360</v>
       </c>
@@ -7619,7 +7661,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="56" spans="1:9">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="7" t="s">
         <v>362</v>
       </c>
@@ -7646,7 +7688,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="57" spans="1:9">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
         <v>365</v>
       </c>
@@ -7667,7 +7709,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="58" spans="1:9">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="7" t="s">
         <v>288</v>
       </c>
@@ -7688,7 +7730,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="59" spans="1:9">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
         <v>367</v>
       </c>
@@ -7709,7 +7751,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="60" spans="1:9">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="7" t="s">
         <v>368</v>
       </c>
@@ -7730,7 +7772,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="61" spans="1:9">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
         <v>371</v>
       </c>
@@ -7751,7 +7793,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="62" spans="1:9">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="7" t="s">
         <v>373</v>
       </c>
@@ -7772,7 +7814,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="63" spans="1:9">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
         <v>375</v>
       </c>
@@ -7796,7 +7838,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="64" spans="1:9">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="7" t="s">
         <v>377</v>
       </c>
@@ -7817,7 +7859,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="65" spans="1:6">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>378</v>
       </c>
@@ -7838,7 +7880,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="66" spans="1:6">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="7" t="s">
         <v>380</v>
       </c>
@@ -7859,7 +7901,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="67" spans="1:6">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
         <v>382</v>
       </c>
@@ -7880,7 +7922,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="68" spans="1:6">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="7" t="s">
         <v>383</v>
       </c>
@@ -7900,8 +7942,14 @@
       <c r="F68" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="69" spans="1:6">
+      <c r="H68" s="39" t="s">
+        <v>1017</v>
+      </c>
+      <c r="I68" s="39" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>385</v>
       </c>
@@ -7922,7 +7970,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="70" spans="1:6">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>387</v>
       </c>
@@ -7943,7 +7991,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="71" spans="1:6">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>389</v>
       </c>
@@ -7964,7 +8012,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="72" spans="1:6">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>391</v>
       </c>
@@ -7985,7 +8033,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="73" spans="1:6">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>393</v>
       </c>
@@ -8006,7 +8054,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="74" spans="1:6">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>394</v>
       </c>
@@ -8027,7 +8075,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="75" spans="1:6">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>396</v>
       </c>
@@ -8048,7 +8096,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="76" spans="1:6">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>397</v>
       </c>
@@ -8069,7 +8117,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="77" spans="1:6">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>399</v>
       </c>
@@ -8090,7 +8138,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="78" spans="1:6">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>400</v>
       </c>
@@ -8111,7 +8159,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="79" spans="1:6">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>402</v>
       </c>
@@ -8132,7 +8180,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="80" spans="1:6">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>403</v>
       </c>
@@ -8153,7 +8201,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="81" spans="1:6">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>405</v>
       </c>
@@ -8174,7 +8222,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="82" spans="1:6">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>408</v>
       </c>
@@ -8195,7 +8243,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="83" spans="1:6">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>409</v>
       </c>
@@ -8216,7 +8264,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="84" spans="1:6">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>410</v>
       </c>
@@ -8237,7 +8285,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="85" spans="1:6">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>412</v>
       </c>
@@ -8258,7 +8306,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="86" spans="1:6">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>414</v>
       </c>
@@ -8279,7 +8327,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="87" spans="1:6">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>415</v>
       </c>
@@ -8300,7 +8348,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="88" spans="1:6">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>417</v>
       </c>
@@ -8321,7 +8369,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="89" spans="1:6">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>418</v>
       </c>
@@ -8342,7 +8390,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="90" spans="1:6">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>420</v>
       </c>
@@ -8363,7 +8411,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="91" spans="1:6">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>422</v>
       </c>
@@ -8384,7 +8432,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="92" spans="1:6">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>424</v>
       </c>
@@ -8405,7 +8453,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="93" spans="1:6">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>425</v>
       </c>
@@ -8426,7 +8474,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="94" spans="1:6">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>427</v>
       </c>
@@ -8447,7 +8495,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="95" spans="1:6">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>430</v>
       </c>
@@ -8468,7 +8516,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="96" spans="1:6">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>432</v>
       </c>
@@ -8489,7 +8537,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="97" spans="1:6">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>433</v>
       </c>
@@ -8510,7 +8558,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="98" spans="1:6">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>435</v>
       </c>
@@ -8531,7 +8579,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="99" spans="1:6">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>436</v>
       </c>
@@ -8552,7 +8600,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="100" spans="1:6">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>437</v>
       </c>
@@ -8573,7 +8621,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="101" spans="1:6">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>438</v>
       </c>
@@ -8594,7 +8642,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="102" spans="1:6">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>440</v>
       </c>
@@ -8615,7 +8663,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="103" spans="1:6">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>441</v>
       </c>
@@ -8636,7 +8684,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="104" spans="1:6">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>443</v>
       </c>
@@ -8657,7 +8705,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="105" spans="1:6">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>446</v>
       </c>
@@ -8678,7 +8726,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="106" spans="1:6">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>449</v>
       </c>
@@ -8699,7 +8747,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="107" spans="1:6">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>451</v>
       </c>
@@ -8720,7 +8768,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="108" spans="1:6">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="9" t="s">
         <v>453</v>
       </c>
@@ -8740,7 +8788,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="109" spans="1:6">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="9" t="s">
         <v>456</v>
       </c>
@@ -8761,7 +8809,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="110" spans="1:6">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="9" t="s">
         <v>457</v>
       </c>
@@ -8782,7 +8830,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="111" spans="1:6">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="9" t="s">
         <v>460</v>
       </c>
@@ -8803,7 +8851,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="112" spans="1:6">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="9" t="s">
         <v>462</v>
       </c>
@@ -8824,7 +8872,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="113" spans="1:8">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" s="9" t="s">
         <v>464</v>
       </c>
@@ -8845,7 +8893,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="114" spans="1:8">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" s="9" t="s">
         <v>465</v>
       </c>
@@ -8866,7 +8914,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="115" spans="1:8">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" s="9" t="s">
         <v>467</v>
       </c>
@@ -8887,7 +8935,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="116" spans="1:8">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" s="9" t="s">
         <v>469</v>
       </c>
@@ -8908,10 +8956,10 @@
         <v>142</v>
       </c>
       <c r="H116" t="s">
-        <v>1016</v>
-      </c>
-    </row>
-    <row r="117" spans="1:8">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" s="9" t="s">
         <v>471</v>
       </c>
@@ -8932,10 +8980,10 @@
         <v>142</v>
       </c>
       <c r="H117" t="s">
-        <v>1016</v>
-      </c>
-    </row>
-    <row r="118" spans="1:8">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" s="9" t="s">
         <v>473</v>
       </c>
@@ -8956,7 +9004,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="119" spans="1:8">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" s="9" t="s">
         <v>475</v>
       </c>
@@ -8977,7 +9025,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="120" spans="1:8">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" s="9" t="s">
         <v>476</v>
       </c>
@@ -8998,7 +9046,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="121" spans="1:8">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" s="9" t="s">
         <v>478</v>
       </c>
@@ -9019,7 +9067,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="122" spans="1:8">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" s="9" t="s">
         <v>480</v>
       </c>
@@ -9040,7 +9088,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="123" spans="1:8">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" s="9" t="s">
         <v>482</v>
       </c>
@@ -9061,7 +9109,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="124" spans="1:8">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" s="9" t="s">
         <v>483</v>
       </c>
@@ -9082,7 +9130,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="125" spans="1:8">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>484</v>
       </c>
@@ -9103,7 +9151,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="126" spans="1:8">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" s="9" t="s">
         <v>485</v>
       </c>
@@ -9124,7 +9172,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="127" spans="1:8">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B127" s="1" t="str">
         <f t="shared" si="13"/>
         <v/>
@@ -9137,6 +9185,8 @@
     <hyperlink ref="I54" r:id="rId3" xr:uid="{B53F0185-E12A-4B2F-B690-A355769CD3F8}"/>
     <hyperlink ref="I63" r:id="rId4" xr:uid="{65BCD137-8AB5-49F1-9E6E-D630706BF1D1}"/>
     <hyperlink ref="H37" r:id="rId5" xr:uid="{E6008756-EABF-4007-B406-8FDB469A944B}"/>
+    <hyperlink ref="I68" r:id="rId6" xr:uid="{FDC3B03E-2B43-4B00-A129-6DEA0C75C40E}"/>
+    <hyperlink ref="H68" r:id="rId7" xr:uid="{ED0FBD64-C52F-4310-BEB1-D76BDFE4CE1B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
@@ -9169,20 +9219,20 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:M73"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.33203125" style="3" customWidth="1"/>
-    <col min="2" max="6" width="11.44140625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="69.109375" style="3" customWidth="1"/>
-    <col min="8" max="8" width="11.44140625" style="3" customWidth="1"/>
-    <col min="9" max="9" width="21.44140625" style="3" customWidth="1"/>
-    <col min="10" max="10" width="42.44140625" style="3" customWidth="1"/>
-    <col min="11" max="11" width="72.33203125" style="3" customWidth="1"/>
-    <col min="12" max="12" width="11.44140625" style="3" customWidth="1"/>
-    <col min="13" max="16384" width="11.44140625" style="3"/>
+    <col min="1" max="1" width="22.28515625" style="3" customWidth="1"/>
+    <col min="2" max="6" width="11.42578125" style="3" customWidth="1"/>
+    <col min="7" max="7" width="69.140625" style="3" customWidth="1"/>
+    <col min="8" max="8" width="11.42578125" style="3" customWidth="1"/>
+    <col min="9" max="9" width="21.42578125" style="3" customWidth="1"/>
+    <col min="10" max="10" width="42.42578125" style="3" customWidth="1"/>
+    <col min="11" max="11" width="72.28515625" style="3" customWidth="1"/>
+    <col min="12" max="12" width="11.42578125" style="3" customWidth="1"/>
+    <col min="13" max="16384" width="11.42578125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="39.9" customHeight="1">
+    <row r="1" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>74</v>
       </c>
@@ -9220,7 +9270,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="39.9" customHeight="1">
+    <row r="2" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>126</v>
       </c>
@@ -9255,7 +9305,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="39.9" customHeight="1">
+    <row r="3" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>115</v>
       </c>
@@ -9289,11 +9339,11 @@
       <c r="K3" s="3" t="s">
         <v>508</v>
       </c>
-      <c r="L3" s="79" t="s">
+      <c r="L3" s="78" t="s">
         <v>977</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="39.9" customHeight="1">
+    <row r="4" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>37</v>
       </c>
@@ -9328,7 +9378,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="39.9" customHeight="1">
+    <row r="5" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>122</v>
       </c>
@@ -9366,7 +9416,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="39.9" customHeight="1">
+    <row r="6" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>104</v>
       </c>
@@ -9404,7 +9454,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="39.9" customHeight="1">
+    <row r="7" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>283</v>
       </c>
@@ -9439,7 +9489,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="39.9" customHeight="1">
+    <row r="8" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>112</v>
       </c>
@@ -9477,7 +9527,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="39.9" customHeight="1">
+    <row r="9" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>136</v>
       </c>
@@ -9515,7 +9565,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="39.9" customHeight="1">
+    <row r="10" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>99</v>
       </c>
@@ -9550,7 +9600,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="39.9" customHeight="1">
+    <row r="11" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>345</v>
       </c>
@@ -9585,7 +9635,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="39.9" customHeight="1">
+    <row r="12" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>370</v>
       </c>
@@ -9620,7 +9670,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="39.9" customHeight="1">
+    <row r="13" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>142</v>
       </c>
@@ -9655,7 +9705,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="39.9" customHeight="1">
+    <row r="14" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>258</v>
       </c>
@@ -9690,7 +9740,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="39.9" customHeight="1">
+    <row r="15" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>232</v>
       </c>
@@ -9722,7 +9772,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="39.9" customHeight="1">
+    <row r="16" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>88</v>
       </c>
@@ -9751,7 +9801,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="39.9" customHeight="1">
+    <row r="17" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>169</v>
       </c>
@@ -9786,7 +9836,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="39.9" customHeight="1">
+    <row r="18" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>91</v>
       </c>
@@ -9821,7 +9871,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="39.9" customHeight="1">
+    <row r="19" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>194</v>
       </c>
@@ -9859,7 +9909,7 @@
         <v>988</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="39.9" customHeight="1">
+    <row r="20" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>145</v>
       </c>
@@ -9894,7 +9944,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="39.9" customHeight="1">
+    <row r="21" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>85</v>
       </c>
@@ -9929,7 +9979,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="39.9" customHeight="1">
+    <row r="22" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>119</v>
       </c>
@@ -9964,7 +10014,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="39.9" customHeight="1">
+    <row r="23" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>595</v>
       </c>
@@ -9999,7 +10049,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="39.9" customHeight="1">
+    <row r="24" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>334</v>
       </c>
@@ -10034,7 +10084,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="39.9" customHeight="1">
+    <row r="25" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>605</v>
       </c>
@@ -10069,7 +10119,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="39.9" customHeight="1">
+    <row r="26" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>107</v>
       </c>
@@ -10104,7 +10154,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="39.9" customHeight="1">
+    <row r="27" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>94</v>
       </c>
@@ -10139,7 +10189,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="39.9" customHeight="1">
+    <row r="28" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>129</v>
       </c>
@@ -10174,7 +10224,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="39.9" customHeight="1">
+    <row r="29" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>322</v>
       </c>
@@ -10209,7 +10259,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="39.9" customHeight="1">
+    <row r="30" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>324</v>
       </c>
@@ -10244,7 +10294,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="39.9" customHeight="1">
+    <row r="31" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
         <v>340</v>
       </c>
@@ -10279,7 +10329,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="39.9" customHeight="1">
+    <row r="32" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
         <v>267</v>
       </c>
@@ -10317,7 +10367,7 @@
         <v>996</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="39.9" customHeight="1">
+    <row r="33" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
         <v>353</v>
       </c>
@@ -10352,7 +10402,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="39.9" customHeight="1">
+    <row r="34" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>212</v>
       </c>
@@ -10387,7 +10437,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="39.9" customHeight="1">
+    <row r="35" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>407</v>
       </c>
@@ -10422,7 +10472,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="44.25" customHeight="1">
+    <row r="36" spans="1:12" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>429</v>
       </c>
@@ -10460,7 +10510,7 @@
         <v>989</v>
       </c>
     </row>
-    <row r="37" spans="1:12" ht="72" customHeight="1">
+    <row r="37" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>445</v>
       </c>
@@ -10495,7 +10545,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="38" spans="1:12" ht="29.25" customHeight="1">
+    <row r="38" spans="1:12" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>448</v>
       </c>
@@ -10530,7 +10580,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="39" spans="1:12" ht="34.5" customHeight="1">
+    <row r="39" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>450</v>
       </c>
@@ -10565,7 +10615,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="40" spans="1:12" ht="47.25" customHeight="1">
+    <row r="40" spans="1:12" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>452</v>
       </c>
@@ -10600,7 +10650,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="41" spans="1:12" ht="49.5" customHeight="1">
+    <row r="41" spans="1:12" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>455</v>
       </c>
@@ -10635,7 +10685,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="42" spans="1:12" ht="72" customHeight="1">
+    <row r="42" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="11" t="s">
         <v>459</v>
       </c>
@@ -10673,7 +10723,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="43" spans="1:12" ht="72" customHeight="1">
+    <row r="43" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="11" t="s">
         <v>477</v>
       </c>
@@ -10708,7 +10758,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="44" spans="1:12" ht="72" customHeight="1">
+    <row r="44" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="11" t="s">
         <v>689</v>
       </c>
@@ -10743,7 +10793,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="45" spans="1:12" ht="72" customHeight="1">
+    <row r="45" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="15" t="s">
         <v>694</v>
       </c>
@@ -10774,7 +10824,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="46" spans="1:12" ht="72" customHeight="1">
+    <row r="46" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="13" t="s">
         <v>700</v>
       </c>
@@ -10809,7 +10859,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="47" spans="1:12" ht="72" customHeight="1">
+    <row r="47" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="13" t="s">
         <v>706</v>
       </c>
@@ -10840,7 +10890,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="48" spans="1:12" ht="72" customHeight="1">
+    <row r="48" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="13" t="s">
         <v>712</v>
       </c>
@@ -10871,7 +10921,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="72" customHeight="1">
+    <row r="49" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="13" t="s">
         <v>718</v>
       </c>
@@ -10902,7 +10952,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="51" customHeight="1">
+    <row r="50" spans="1:11" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="13" t="s">
         <v>724</v>
       </c>
@@ -10937,7 +10987,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="72" customHeight="1">
+    <row r="51" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="13" t="s">
         <v>730</v>
       </c>
@@ -10972,7 +11022,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="72" customHeight="1">
+    <row r="52" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="13" t="s">
         <v>735</v>
       </c>
@@ -11007,7 +11057,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="57.6" customHeight="1">
+    <row r="53" spans="1:11" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="13" t="s">
         <v>740</v>
       </c>
@@ -11038,7 +11088,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="57.6" customHeight="1">
+    <row r="54" spans="1:11" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="13" t="s">
         <v>745</v>
       </c>
@@ -11069,7 +11119,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="55" spans="1:11" ht="72" customHeight="1">
+    <row r="55" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="13" t="s">
         <v>750</v>
       </c>
@@ -11100,7 +11150,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="72" customHeight="1">
+    <row r="56" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="13" t="s">
         <v>253</v>
       </c>
@@ -11131,11 +11181,11 @@
         <v>758</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="72" customHeight="1">
+    <row r="57" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="13" t="s">
         <v>759</v>
       </c>
-      <c r="B57" s="80" t="s">
+      <c r="B57" s="79" t="s">
         <v>760</v>
       </c>
       <c r="C57" s="26"/>
@@ -11162,7 +11212,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="86.4" customHeight="1">
+    <row r="58" spans="1:11" ht="86.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="13" t="s">
         <v>766</v>
       </c>
@@ -11193,7 +11243,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="72" customHeight="1">
+    <row r="59" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="13" t="s">
         <v>773</v>
       </c>
@@ -11224,7 +11274,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="72" customHeight="1">
+    <row r="60" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="13" t="s">
         <v>778</v>
       </c>
@@ -11255,7 +11305,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="72" customHeight="1">
+    <row r="61" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
         <v>783</v>
       </c>
@@ -11286,7 +11336,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="72" customHeight="1">
+    <row r="62" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="11" t="s">
         <v>789</v>
       </c>
@@ -11317,7 +11367,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="63" spans="1:11" ht="48" customHeight="1">
+    <row r="63" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="18" t="s">
         <v>794</v>
       </c>
@@ -11346,7 +11396,7 @@
         <v>799</v>
       </c>
     </row>
-    <row r="64" spans="1:11" ht="42" customHeight="1">
+    <row r="64" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="19" t="s">
         <v>800</v>
       </c>
@@ -11375,7 +11425,7 @@
         <v>804</v>
       </c>
     </row>
-    <row r="65" spans="1:13" ht="45" customHeight="1">
+    <row r="65" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="19" t="s">
         <v>805</v>
       </c>
@@ -11404,7 +11454,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="66" spans="1:13" ht="72" customHeight="1">
+    <row r="66" spans="1:13" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="19" t="s">
         <v>810</v>
       </c>
@@ -11433,7 +11483,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="67" spans="1:13" ht="72" customHeight="1">
+    <row r="67" spans="1:13" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="19" t="s">
         <v>815</v>
       </c>
@@ -11462,7 +11512,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="68" spans="1:13" ht="72" customHeight="1">
+    <row r="68" spans="1:13" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="19" t="s">
         <v>820</v>
       </c>
@@ -11491,7 +11541,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="69" spans="1:13" ht="409.6" customHeight="1">
+    <row r="69" spans="1:13" ht="409.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="31" t="s">
         <v>197</v>
       </c>
@@ -11526,7 +11576,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="70" spans="1:13" ht="409.6" customHeight="1">
+    <row r="70" spans="1:13" ht="409.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="31" t="s">
         <v>188</v>
       </c>
@@ -11567,7 +11617,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="71" spans="1:13" ht="100.8">
+    <row r="71" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
         <v>952</v>
       </c>
@@ -11605,7 +11655,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="72" spans="1:13" ht="129.6">
+    <row r="72" spans="1:13" ht="150" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
         <v>961</v>
       </c>
@@ -11624,7 +11674,7 @@
       <c r="F72" s="3" t="s">
         <v>498</v>
       </c>
-      <c r="G72" s="81" t="s">
+      <c r="G72" s="80" t="s">
         <v>991</v>
       </c>
       <c r="H72" s="63" t="s">
@@ -11643,7 +11693,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="73" spans="1:13" ht="72">
+    <row r="73" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
         <v>1008</v>
       </c>
@@ -11653,19 +11703,19 @@
       <c r="G73" s="43" t="s">
         <v>1009</v>
       </c>
-      <c r="H73" s="82" t="s">
+      <c r="H73" s="81" t="s">
         <v>1010</v>
       </c>
-      <c r="I73" s="82" t="s">
+      <c r="I73" s="81" t="s">
         <v>1011</v>
       </c>
-      <c r="J73" s="82" t="s">
+      <c r="J73" s="81" t="s">
         <v>1012</v>
       </c>
       <c r="K73" s="3" t="s">
         <v>1014</v>
       </c>
-      <c r="L73" s="83" t="s">
+      <c r="L73" s="82" t="s">
         <v>1013</v>
       </c>
     </row>
@@ -11720,13 +11770,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G18"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="5" max="5" width="23.6640625" customWidth="1"/>
-    <col min="6" max="6" width="24.88671875" customWidth="1"/>
+    <col min="5" max="5" width="23.7109375" customWidth="1"/>
+    <col min="6" max="6" width="24.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>831</v>
       </c>
@@ -11743,7 +11793,7 @@
       </c>
       <c r="G1" s="1"/>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="20" t="s">
         <v>496</v>
       </c>
@@ -11760,7 +11810,7 @@
       </c>
       <c r="G2" s="1"/>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="20" t="s">
         <v>557</v>
       </c>
@@ -11777,7 +11827,7 @@
       </c>
       <c r="G3" s="1"/>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="20" t="s">
         <v>567</v>
       </c>
@@ -11794,7 +11844,7 @@
       </c>
       <c r="G4" s="1"/>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="20" t="s">
         <v>590</v>
       </c>
@@ -11809,7 +11859,7 @@
       </c>
       <c r="G5" s="1"/>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="20" t="s">
         <v>615</v>
       </c>
@@ -11824,7 +11874,7 @@
       </c>
       <c r="G6" s="1"/>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="20" t="s">
         <v>540</v>
       </c>
@@ -11835,7 +11885,7 @@
       <c r="F7" s="20"/>
       <c r="G7" s="1"/>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="21" t="s">
         <v>644</v>
       </c>
@@ -11846,7 +11896,7 @@
       <c r="F8" s="20"/>
       <c r="G8" s="1"/>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="22" t="s">
         <v>767</v>
       </c>
@@ -11857,7 +11907,7 @@
       <c r="F9" s="20"/>
       <c r="G9" s="1"/>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="20" t="s">
         <v>784</v>
       </c>
@@ -11868,7 +11918,7 @@
       <c r="F10" s="20"/>
       <c r="G10" s="1"/>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="22" t="s">
         <v>795</v>
       </c>
@@ -11879,7 +11929,7 @@
       <c r="F11" s="20"/>
       <c r="G11" s="1"/>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="20" t="s">
         <v>760</v>
       </c>
@@ -11890,7 +11940,7 @@
       <c r="F12" s="20"/>
       <c r="G12" s="1"/>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="20" t="s">
         <v>530</v>
       </c>
@@ -11901,7 +11951,7 @@
       <c r="F13" s="20"/>
       <c r="G13" s="1"/>
     </row>
-    <row r="14" spans="1:7" ht="28.95" customHeight="1">
+    <row r="14" spans="1:7" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="27" t="s">
         <v>695</v>
       </c>
@@ -11912,7 +11962,7 @@
       <c r="F14" s="20"/>
       <c r="G14" s="1"/>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="20"/>
       <c r="B15" s="20"/>
       <c r="C15" s="20"/>
@@ -11921,7 +11971,7 @@
       <c r="F15" s="20"/>
       <c r="G15" s="1"/>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="20"/>
       <c r="B16" s="20"/>
       <c r="C16" s="20"/>
@@ -11930,7 +11980,7 @@
       <c r="F16" s="20"/>
       <c r="G16" s="1"/>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="20"/>
       <c r="B17" s="20"/>
       <c r="C17" s="20"/>
@@ -11939,7 +11989,7 @@
       <c r="F17" s="20"/>
       <c r="G17" s="1"/>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -11957,204 +12007,204 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:Q172"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="40"/>
     </row>
-    <row r="2" spans="1:1">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="41" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="41" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:1">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="41" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="41" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="41" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="41" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:1">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="41" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:1">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="41" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:1">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="41" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:1">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="41" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:1" ht="15.6" customHeight="1">
+    <row r="13" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="42" t="s">
         <v>834</v>
       </c>
     </row>
-    <row r="14" spans="1:1">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="40"/>
     </row>
-    <row r="15" spans="1:1">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="41" t="s">
         <v>835</v>
       </c>
     </row>
-    <row r="16" spans="1:1">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="41" t="s">
         <v>836</v>
       </c>
     </row>
-    <row r="17" spans="1:17">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="41" t="s">
         <v>837</v>
       </c>
     </row>
-    <row r="18" spans="1:17">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="41" t="s">
         <v>838</v>
       </c>
     </row>
-    <row r="19" spans="1:17">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="41" t="s">
         <v>839</v>
       </c>
     </row>
-    <row r="20" spans="1:17">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="41" t="s">
         <v>840</v>
       </c>
     </row>
-    <row r="21" spans="1:17">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="41" t="s">
         <v>841</v>
       </c>
     </row>
-    <row r="22" spans="1:17">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" s="41" t="s">
         <v>842</v>
       </c>
     </row>
-    <row r="23" spans="1:17">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" s="41" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="1:17">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" s="41" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="26" spans="1:17">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="27" spans="1:17">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="28" spans="1:17">
-      <c r="A28" s="87" t="s">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A28" s="86" t="s">
         <v>843</v>
       </c>
-      <c r="B28" s="86"/>
-      <c r="C28" s="86"/>
-      <c r="D28" s="86"/>
-      <c r="E28" s="86"/>
-      <c r="F28" s="86"/>
-      <c r="G28" s="86"/>
-      <c r="H28" s="86"/>
-      <c r="I28" s="86"/>
-      <c r="J28" s="86"/>
-      <c r="K28" s="86"/>
-      <c r="L28" s="86"/>
-      <c r="M28" s="86"/>
-      <c r="N28" s="86"/>
-      <c r="O28" s="86"/>
-      <c r="P28" s="86"/>
-      <c r="Q28" s="86"/>
-    </row>
-    <row r="29" spans="1:17">
-      <c r="A29" s="86"/>
-      <c r="B29" s="86"/>
-      <c r="C29" s="86"/>
-      <c r="D29" s="86"/>
-      <c r="E29" s="86"/>
-      <c r="F29" s="86"/>
-      <c r="G29" s="86"/>
-      <c r="H29" s="86"/>
-      <c r="I29" s="86"/>
-      <c r="J29" s="86"/>
-      <c r="K29" s="86"/>
-      <c r="L29" s="86"/>
-      <c r="M29" s="86"/>
-      <c r="N29" s="86"/>
-      <c r="O29" s="86"/>
-      <c r="P29" s="86"/>
-      <c r="Q29" s="86"/>
-    </row>
-    <row r="30" spans="1:17" ht="14.4" customHeight="1">
-      <c r="A30" s="88" t="s">
+      <c r="B28" s="85"/>
+      <c r="C28" s="85"/>
+      <c r="D28" s="85"/>
+      <c r="E28" s="85"/>
+      <c r="F28" s="85"/>
+      <c r="G28" s="85"/>
+      <c r="H28" s="85"/>
+      <c r="I28" s="85"/>
+      <c r="J28" s="85"/>
+      <c r="K28" s="85"/>
+      <c r="L28" s="85"/>
+      <c r="M28" s="85"/>
+      <c r="N28" s="85"/>
+      <c r="O28" s="85"/>
+      <c r="P28" s="85"/>
+      <c r="Q28" s="85"/>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A29" s="85"/>
+      <c r="B29" s="85"/>
+      <c r="C29" s="85"/>
+      <c r="D29" s="85"/>
+      <c r="E29" s="85"/>
+      <c r="F29" s="85"/>
+      <c r="G29" s="85"/>
+      <c r="H29" s="85"/>
+      <c r="I29" s="85"/>
+      <c r="J29" s="85"/>
+      <c r="K29" s="85"/>
+      <c r="L29" s="85"/>
+      <c r="M29" s="85"/>
+      <c r="N29" s="85"/>
+      <c r="O29" s="85"/>
+      <c r="P29" s="85"/>
+      <c r="Q29" s="85"/>
+    </row>
+    <row r="30" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="B30" s="85" t="s">
+      <c r="B30" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="C30" s="86"/>
-      <c r="D30" s="86"/>
-      <c r="E30" s="85" t="s">
+      <c r="C30" s="85"/>
+      <c r="D30" s="85"/>
+      <c r="E30" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="F30" s="86"/>
-      <c r="G30" s="86"/>
-      <c r="H30" s="85" t="s">
+      <c r="F30" s="85"/>
+      <c r="G30" s="85"/>
+      <c r="H30" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="I30" s="86"/>
-      <c r="J30" s="86"/>
-      <c r="K30" s="85" t="s">
+      <c r="I30" s="85"/>
+      <c r="J30" s="85"/>
+      <c r="K30" s="84" t="s">
         <v>24</v>
       </c>
-      <c r="L30" s="86"/>
-      <c r="M30" s="86"/>
-      <c r="N30" s="86"/>
-      <c r="O30" s="86"/>
-      <c r="P30" s="85" t="s">
+      <c r="L30" s="85"/>
+      <c r="M30" s="85"/>
+      <c r="N30" s="85"/>
+      <c r="O30" s="85"/>
+      <c r="P30" s="84" t="s">
         <v>25</v>
       </c>
-      <c r="Q30" s="85" t="s">
+      <c r="Q30" s="84" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="31" spans="1:17">
-      <c r="A31" s="86"/>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A31" s="85"/>
       <c r="B31" s="43" t="s">
         <v>27</v>
       </c>
@@ -12197,10 +12247,10 @@
       <c r="O31" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P31" s="86"/>
-      <c r="Q31" s="86"/>
-    </row>
-    <row r="32" spans="1:17" ht="43.2" customHeight="1">
+      <c r="P31" s="85"/>
+      <c r="Q31" s="85"/>
+    </row>
+    <row r="32" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="43" t="s">
         <v>844</v>
       </c>
@@ -12251,81 +12301,81 @@
         <v>13</v>
       </c>
     </row>
-    <row r="33" spans="1:17">
-      <c r="A33" s="87" t="s">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A33" s="86" t="s">
         <v>644</v>
       </c>
-      <c r="B33" s="86"/>
-      <c r="C33" s="86"/>
-      <c r="D33" s="86"/>
-      <c r="E33" s="86"/>
-      <c r="F33" s="86"/>
-      <c r="G33" s="86"/>
-      <c r="H33" s="86"/>
-      <c r="I33" s="86"/>
-      <c r="J33" s="86"/>
-      <c r="K33" s="86"/>
-      <c r="L33" s="86"/>
-      <c r="M33" s="86"/>
-      <c r="N33" s="86"/>
-      <c r="O33" s="86"/>
-      <c r="P33" s="86"/>
-      <c r="Q33" s="86"/>
-    </row>
-    <row r="34" spans="1:17">
-      <c r="A34" s="86"/>
-      <c r="B34" s="86"/>
-      <c r="C34" s="86"/>
-      <c r="D34" s="86"/>
-      <c r="E34" s="86"/>
-      <c r="F34" s="86"/>
-      <c r="G34" s="86"/>
-      <c r="H34" s="86"/>
-      <c r="I34" s="86"/>
-      <c r="J34" s="86"/>
-      <c r="K34" s="86"/>
-      <c r="L34" s="86"/>
-      <c r="M34" s="86"/>
-      <c r="N34" s="86"/>
-      <c r="O34" s="86"/>
-      <c r="P34" s="86"/>
-      <c r="Q34" s="86"/>
-    </row>
-    <row r="35" spans="1:17" ht="14.4" customHeight="1">
-      <c r="A35" s="88" t="s">
+      <c r="B33" s="85"/>
+      <c r="C33" s="85"/>
+      <c r="D33" s="85"/>
+      <c r="E33" s="85"/>
+      <c r="F33" s="85"/>
+      <c r="G33" s="85"/>
+      <c r="H33" s="85"/>
+      <c r="I33" s="85"/>
+      <c r="J33" s="85"/>
+      <c r="K33" s="85"/>
+      <c r="L33" s="85"/>
+      <c r="M33" s="85"/>
+      <c r="N33" s="85"/>
+      <c r="O33" s="85"/>
+      <c r="P33" s="85"/>
+      <c r="Q33" s="85"/>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A34" s="85"/>
+      <c r="B34" s="85"/>
+      <c r="C34" s="85"/>
+      <c r="D34" s="85"/>
+      <c r="E34" s="85"/>
+      <c r="F34" s="85"/>
+      <c r="G34" s="85"/>
+      <c r="H34" s="85"/>
+      <c r="I34" s="85"/>
+      <c r="J34" s="85"/>
+      <c r="K34" s="85"/>
+      <c r="L34" s="85"/>
+      <c r="M34" s="85"/>
+      <c r="N34" s="85"/>
+      <c r="O34" s="85"/>
+      <c r="P34" s="85"/>
+      <c r="Q34" s="85"/>
+    </row>
+    <row r="35" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="B35" s="85" t="s">
+      <c r="B35" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="C35" s="86"/>
-      <c r="D35" s="86"/>
-      <c r="E35" s="85" t="s">
+      <c r="C35" s="85"/>
+      <c r="D35" s="85"/>
+      <c r="E35" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="F35" s="86"/>
-      <c r="G35" s="86"/>
-      <c r="H35" s="85" t="s">
+      <c r="F35" s="85"/>
+      <c r="G35" s="85"/>
+      <c r="H35" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="I35" s="86"/>
-      <c r="J35" s="86"/>
-      <c r="K35" s="85" t="s">
+      <c r="I35" s="85"/>
+      <c r="J35" s="85"/>
+      <c r="K35" s="84" t="s">
         <v>24</v>
       </c>
-      <c r="L35" s="86"/>
-      <c r="M35" s="86"/>
-      <c r="N35" s="86"/>
-      <c r="O35" s="86"/>
-      <c r="P35" s="85" t="s">
+      <c r="L35" s="85"/>
+      <c r="M35" s="85"/>
+      <c r="N35" s="85"/>
+      <c r="O35" s="85"/>
+      <c r="P35" s="84" t="s">
         <v>25</v>
       </c>
-      <c r="Q35" s="85" t="s">
+      <c r="Q35" s="84" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="36" spans="1:17">
-      <c r="A36" s="86"/>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A36" s="85"/>
       <c r="B36" s="43" t="s">
         <v>27</v>
       </c>
@@ -12368,10 +12418,10 @@
       <c r="O36" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P36" s="86"/>
-      <c r="Q36" s="86"/>
-    </row>
-    <row r="37" spans="1:17">
+      <c r="P36" s="85"/>
+      <c r="Q36" s="85"/>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="43" t="s">
         <v>689</v>
       </c>
@@ -12422,7 +12472,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="38" spans="1:17">
+    <row r="38" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="43" t="s">
         <v>845</v>
       </c>
@@ -12473,7 +12523,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="28.95" customHeight="1">
+    <row r="39" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="43" t="s">
         <v>68</v>
       </c>
@@ -12524,7 +12574,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="40" spans="1:17" ht="57.6" customHeight="1">
+    <row r="40" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="43" t="s">
         <v>846</v>
       </c>
@@ -12557,7 +12607,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="41" spans="1:17">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="43" t="s">
         <v>847</v>
       </c>
@@ -12590,7 +12640,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="1:17" ht="43.2" customHeight="1">
+    <row r="42" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="46" t="s">
         <v>848</v>
       </c>
@@ -12633,7 +12683,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:17">
+    <row r="43" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A43" s="43" t="s">
         <v>849</v>
       </c>
@@ -12666,7 +12716,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="44" spans="1:17" ht="28.95" customHeight="1">
+    <row r="44" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="43" t="s">
         <v>773</v>
       </c>
@@ -12699,7 +12749,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:17" ht="28.95" customHeight="1">
+    <row r="45" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="43" t="s">
         <v>766</v>
       </c>
@@ -12732,7 +12782,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:17" ht="43.2" customHeight="1">
+    <row r="46" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="43" t="s">
         <v>778</v>
       </c>
@@ -12765,7 +12815,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:17" ht="57.6" customHeight="1">
+    <row r="47" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="46" t="s">
         <v>850</v>
       </c>
@@ -12808,81 +12858,81 @@
         <v>20</v>
       </c>
     </row>
-    <row r="48" spans="1:17">
-      <c r="A48" s="87" t="s">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A48" s="86" t="s">
         <v>851</v>
       </c>
-      <c r="B48" s="86"/>
-      <c r="C48" s="86"/>
-      <c r="D48" s="86"/>
-      <c r="E48" s="86"/>
-      <c r="F48" s="86"/>
-      <c r="G48" s="86"/>
-      <c r="H48" s="86"/>
-      <c r="I48" s="86"/>
-      <c r="J48" s="86"/>
-      <c r="K48" s="86"/>
-      <c r="L48" s="86"/>
-      <c r="M48" s="86"/>
-      <c r="N48" s="86"/>
-      <c r="O48" s="86"/>
-      <c r="P48" s="86"/>
-      <c r="Q48" s="86"/>
-    </row>
-    <row r="49" spans="1:17">
-      <c r="A49" s="86"/>
-      <c r="B49" s="86"/>
-      <c r="C49" s="86"/>
-      <c r="D49" s="86"/>
-      <c r="E49" s="86"/>
-      <c r="F49" s="86"/>
-      <c r="G49" s="86"/>
-      <c r="H49" s="86"/>
-      <c r="I49" s="86"/>
-      <c r="J49" s="86"/>
-      <c r="K49" s="86"/>
-      <c r="L49" s="86"/>
-      <c r="M49" s="86"/>
-      <c r="N49" s="86"/>
-      <c r="O49" s="86"/>
-      <c r="P49" s="86"/>
-      <c r="Q49" s="86"/>
-    </row>
-    <row r="50" spans="1:17" ht="14.4" customHeight="1">
-      <c r="A50" s="88" t="s">
+      <c r="B48" s="85"/>
+      <c r="C48" s="85"/>
+      <c r="D48" s="85"/>
+      <c r="E48" s="85"/>
+      <c r="F48" s="85"/>
+      <c r="G48" s="85"/>
+      <c r="H48" s="85"/>
+      <c r="I48" s="85"/>
+      <c r="J48" s="85"/>
+      <c r="K48" s="85"/>
+      <c r="L48" s="85"/>
+      <c r="M48" s="85"/>
+      <c r="N48" s="85"/>
+      <c r="O48" s="85"/>
+      <c r="P48" s="85"/>
+      <c r="Q48" s="85"/>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A49" s="85"/>
+      <c r="B49" s="85"/>
+      <c r="C49" s="85"/>
+      <c r="D49" s="85"/>
+      <c r="E49" s="85"/>
+      <c r="F49" s="85"/>
+      <c r="G49" s="85"/>
+      <c r="H49" s="85"/>
+      <c r="I49" s="85"/>
+      <c r="J49" s="85"/>
+      <c r="K49" s="85"/>
+      <c r="L49" s="85"/>
+      <c r="M49" s="85"/>
+      <c r="N49" s="85"/>
+      <c r="O49" s="85"/>
+      <c r="P49" s="85"/>
+      <c r="Q49" s="85"/>
+    </row>
+    <row r="50" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="B50" s="85" t="s">
+      <c r="B50" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="C50" s="86"/>
-      <c r="D50" s="86"/>
-      <c r="E50" s="85" t="s">
+      <c r="C50" s="85"/>
+      <c r="D50" s="85"/>
+      <c r="E50" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="F50" s="86"/>
-      <c r="G50" s="86"/>
-      <c r="H50" s="85" t="s">
+      <c r="F50" s="85"/>
+      <c r="G50" s="85"/>
+      <c r="H50" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="I50" s="86"/>
-      <c r="J50" s="86"/>
-      <c r="K50" s="85" t="s">
+      <c r="I50" s="85"/>
+      <c r="J50" s="85"/>
+      <c r="K50" s="84" t="s">
         <v>24</v>
       </c>
-      <c r="L50" s="86"/>
-      <c r="M50" s="86"/>
-      <c r="N50" s="86"/>
-      <c r="O50" s="86"/>
-      <c r="P50" s="85" t="s">
+      <c r="L50" s="85"/>
+      <c r="M50" s="85"/>
+      <c r="N50" s="85"/>
+      <c r="O50" s="85"/>
+      <c r="P50" s="84" t="s">
         <v>25</v>
       </c>
-      <c r="Q50" s="85" t="s">
+      <c r="Q50" s="84" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="51" spans="1:17">
-      <c r="A51" s="86"/>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A51" s="85"/>
       <c r="B51" s="43" t="s">
         <v>27</v>
       </c>
@@ -12925,10 +12975,10 @@
       <c r="O51" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P51" s="86"/>
-      <c r="Q51" s="86"/>
-    </row>
-    <row r="52" spans="1:17" ht="57.6" customHeight="1">
+      <c r="P51" s="85"/>
+      <c r="Q51" s="85"/>
+    </row>
+    <row r="52" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="43" t="s">
         <v>852</v>
       </c>
@@ -12979,81 +13029,81 @@
         <v>15</v>
       </c>
     </row>
-    <row r="53" spans="1:17">
-      <c r="A53" s="87" t="s">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A53" s="86" t="s">
         <v>853</v>
       </c>
-      <c r="B53" s="86"/>
-      <c r="C53" s="86"/>
-      <c r="D53" s="86"/>
-      <c r="E53" s="86"/>
-      <c r="F53" s="86"/>
-      <c r="G53" s="86"/>
-      <c r="H53" s="86"/>
-      <c r="I53" s="86"/>
-      <c r="J53" s="86"/>
-      <c r="K53" s="86"/>
-      <c r="L53" s="86"/>
-      <c r="M53" s="86"/>
-      <c r="N53" s="86"/>
-      <c r="O53" s="86"/>
-      <c r="P53" s="86"/>
-      <c r="Q53" s="86"/>
-    </row>
-    <row r="54" spans="1:17">
-      <c r="A54" s="86"/>
-      <c r="B54" s="86"/>
-      <c r="C54" s="86"/>
-      <c r="D54" s="86"/>
-      <c r="E54" s="86"/>
-      <c r="F54" s="86"/>
-      <c r="G54" s="86"/>
-      <c r="H54" s="86"/>
-      <c r="I54" s="86"/>
-      <c r="J54" s="86"/>
-      <c r="K54" s="86"/>
-      <c r="L54" s="86"/>
-      <c r="M54" s="86"/>
-      <c r="N54" s="86"/>
-      <c r="O54" s="86"/>
-      <c r="P54" s="86"/>
-      <c r="Q54" s="86"/>
-    </row>
-    <row r="55" spans="1:17" ht="14.4" customHeight="1">
-      <c r="A55" s="88" t="s">
+      <c r="B53" s="85"/>
+      <c r="C53" s="85"/>
+      <c r="D53" s="85"/>
+      <c r="E53" s="85"/>
+      <c r="F53" s="85"/>
+      <c r="G53" s="85"/>
+      <c r="H53" s="85"/>
+      <c r="I53" s="85"/>
+      <c r="J53" s="85"/>
+      <c r="K53" s="85"/>
+      <c r="L53" s="85"/>
+      <c r="M53" s="85"/>
+      <c r="N53" s="85"/>
+      <c r="O53" s="85"/>
+      <c r="P53" s="85"/>
+      <c r="Q53" s="85"/>
+    </row>
+    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A54" s="85"/>
+      <c r="B54" s="85"/>
+      <c r="C54" s="85"/>
+      <c r="D54" s="85"/>
+      <c r="E54" s="85"/>
+      <c r="F54" s="85"/>
+      <c r="G54" s="85"/>
+      <c r="H54" s="85"/>
+      <c r="I54" s="85"/>
+      <c r="J54" s="85"/>
+      <c r="K54" s="85"/>
+      <c r="L54" s="85"/>
+      <c r="M54" s="85"/>
+      <c r="N54" s="85"/>
+      <c r="O54" s="85"/>
+      <c r="P54" s="85"/>
+      <c r="Q54" s="85"/>
+    </row>
+    <row r="55" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="B55" s="85" t="s">
+      <c r="B55" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="C55" s="86"/>
-      <c r="D55" s="86"/>
-      <c r="E55" s="85" t="s">
+      <c r="C55" s="85"/>
+      <c r="D55" s="85"/>
+      <c r="E55" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="F55" s="86"/>
-      <c r="G55" s="86"/>
-      <c r="H55" s="85" t="s">
+      <c r="F55" s="85"/>
+      <c r="G55" s="85"/>
+      <c r="H55" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="I55" s="86"/>
-      <c r="J55" s="86"/>
-      <c r="K55" s="85" t="s">
+      <c r="I55" s="85"/>
+      <c r="J55" s="85"/>
+      <c r="K55" s="84" t="s">
         <v>24</v>
       </c>
-      <c r="L55" s="86"/>
-      <c r="M55" s="86"/>
-      <c r="N55" s="86"/>
-      <c r="O55" s="86"/>
-      <c r="P55" s="85" t="s">
+      <c r="L55" s="85"/>
+      <c r="M55" s="85"/>
+      <c r="N55" s="85"/>
+      <c r="O55" s="85"/>
+      <c r="P55" s="84" t="s">
         <v>25</v>
       </c>
-      <c r="Q55" s="85" t="s">
+      <c r="Q55" s="84" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="56" spans="1:17">
-      <c r="A56" s="86"/>
+    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A56" s="85"/>
       <c r="B56" s="43" t="s">
         <v>27</v>
       </c>
@@ -13096,10 +13146,10 @@
       <c r="O56" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P56" s="86"/>
-      <c r="Q56" s="86"/>
-    </row>
-    <row r="57" spans="1:17" ht="28.95" customHeight="1">
+      <c r="P56" s="85"/>
+      <c r="Q56" s="85"/>
+    </row>
+    <row r="57" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="43" t="s">
         <v>34</v>
       </c>
@@ -13132,7 +13182,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="58" spans="1:17" ht="57.6" customHeight="1">
+    <row r="58" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="43" t="s">
         <v>854</v>
       </c>
@@ -13165,7 +13215,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="43.2" customHeight="1">
+    <row r="59" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="43" t="s">
         <v>37</v>
       </c>
@@ -13198,7 +13248,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="43.2" customHeight="1">
+    <row r="60" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="43" t="s">
         <v>40</v>
       </c>
@@ -13231,7 +13281,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="28.95" customHeight="1">
+    <row r="61" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="43" t="s">
         <v>39</v>
       </c>
@@ -13264,7 +13314,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="100.95" customHeight="1">
+    <row r="62" spans="1:17" ht="100.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="43" t="s">
         <v>36</v>
       </c>
@@ -13297,7 +13347,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="63" spans="1:17" ht="144" customHeight="1">
+    <row r="63" spans="1:17" ht="144" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="43" t="s">
         <v>35</v>
       </c>
@@ -13330,7 +13380,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="115.2" customHeight="1">
+    <row r="64" spans="1:17" ht="115.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="43" t="s">
         <v>44</v>
       </c>
@@ -13363,7 +13413,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="65" spans="1:17" ht="100.95" customHeight="1">
+    <row r="65" spans="1:17" ht="100.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="43" t="s">
         <v>41</v>
       </c>
@@ -13396,7 +13446,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="66" spans="1:17" ht="144" customHeight="1">
+    <row r="66" spans="1:17" ht="144" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="43" t="s">
         <v>32</v>
       </c>
@@ -13429,7 +13479,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="67" spans="1:17" ht="115.2" customHeight="1">
+    <row r="67" spans="1:17" ht="115.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="43" t="s">
         <v>31</v>
       </c>
@@ -13462,7 +13512,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="68" spans="1:17" ht="129.6" customHeight="1">
+    <row r="68" spans="1:17" ht="129.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="43" t="s">
         <v>33</v>
       </c>
@@ -13495,7 +13545,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="69" spans="1:17" ht="72" customHeight="1">
+    <row r="69" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="43" t="s">
         <v>42</v>
       </c>
@@ -13528,7 +13578,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="70" spans="1:17" ht="72" customHeight="1">
+    <row r="70" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="43" t="s">
         <v>43</v>
       </c>
@@ -13561,7 +13611,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="71" spans="1:17" ht="43.2" customHeight="1">
+    <row r="71" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="46" t="s">
         <v>855</v>
       </c>
@@ -13604,81 +13654,81 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="72" spans="1:17">
-      <c r="A72" s="87" t="s">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A72" s="86" t="s">
         <v>856</v>
       </c>
-      <c r="B72" s="86"/>
-      <c r="C72" s="86"/>
-      <c r="D72" s="86"/>
-      <c r="E72" s="86"/>
-      <c r="F72" s="86"/>
-      <c r="G72" s="86"/>
-      <c r="H72" s="86"/>
-      <c r="I72" s="86"/>
-      <c r="J72" s="86"/>
-      <c r="K72" s="86"/>
-      <c r="L72" s="86"/>
-      <c r="M72" s="86"/>
-      <c r="N72" s="86"/>
-      <c r="O72" s="86"/>
-      <c r="P72" s="86"/>
-      <c r="Q72" s="86"/>
-    </row>
-    <row r="73" spans="1:17">
-      <c r="A73" s="86"/>
-      <c r="B73" s="86"/>
-      <c r="C73" s="86"/>
-      <c r="D73" s="86"/>
-      <c r="E73" s="86"/>
-      <c r="F73" s="86"/>
-      <c r="G73" s="86"/>
-      <c r="H73" s="86"/>
-      <c r="I73" s="86"/>
-      <c r="J73" s="86"/>
-      <c r="K73" s="86"/>
-      <c r="L73" s="86"/>
-      <c r="M73" s="86"/>
-      <c r="N73" s="86"/>
-      <c r="O73" s="86"/>
-      <c r="P73" s="86"/>
-      <c r="Q73" s="86"/>
-    </row>
-    <row r="74" spans="1:17" ht="14.4" customHeight="1">
-      <c r="A74" s="88" t="s">
+      <c r="B72" s="85"/>
+      <c r="C72" s="85"/>
+      <c r="D72" s="85"/>
+      <c r="E72" s="85"/>
+      <c r="F72" s="85"/>
+      <c r="G72" s="85"/>
+      <c r="H72" s="85"/>
+      <c r="I72" s="85"/>
+      <c r="J72" s="85"/>
+      <c r="K72" s="85"/>
+      <c r="L72" s="85"/>
+      <c r="M72" s="85"/>
+      <c r="N72" s="85"/>
+      <c r="O72" s="85"/>
+      <c r="P72" s="85"/>
+      <c r="Q72" s="85"/>
+    </row>
+    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A73" s="85"/>
+      <c r="B73" s="85"/>
+      <c r="C73" s="85"/>
+      <c r="D73" s="85"/>
+      <c r="E73" s="85"/>
+      <c r="F73" s="85"/>
+      <c r="G73" s="85"/>
+      <c r="H73" s="85"/>
+      <c r="I73" s="85"/>
+      <c r="J73" s="85"/>
+      <c r="K73" s="85"/>
+      <c r="L73" s="85"/>
+      <c r="M73" s="85"/>
+      <c r="N73" s="85"/>
+      <c r="O73" s="85"/>
+      <c r="P73" s="85"/>
+      <c r="Q73" s="85"/>
+    </row>
+    <row r="74" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="B74" s="85" t="s">
+      <c r="B74" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="C74" s="86"/>
-      <c r="D74" s="86"/>
-      <c r="E74" s="85" t="s">
+      <c r="C74" s="85"/>
+      <c r="D74" s="85"/>
+      <c r="E74" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="F74" s="86"/>
-      <c r="G74" s="86"/>
-      <c r="H74" s="85" t="s">
+      <c r="F74" s="85"/>
+      <c r="G74" s="85"/>
+      <c r="H74" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="I74" s="86"/>
-      <c r="J74" s="86"/>
-      <c r="K74" s="85" t="s">
+      <c r="I74" s="85"/>
+      <c r="J74" s="85"/>
+      <c r="K74" s="84" t="s">
         <v>24</v>
       </c>
-      <c r="L74" s="86"/>
-      <c r="M74" s="86"/>
-      <c r="N74" s="86"/>
-      <c r="O74" s="86"/>
-      <c r="P74" s="85" t="s">
+      <c r="L74" s="85"/>
+      <c r="M74" s="85"/>
+      <c r="N74" s="85"/>
+      <c r="O74" s="85"/>
+      <c r="P74" s="84" t="s">
         <v>25</v>
       </c>
-      <c r="Q74" s="85" t="s">
+      <c r="Q74" s="84" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="75" spans="1:17">
-      <c r="A75" s="86"/>
+    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A75" s="85"/>
       <c r="B75" s="43" t="s">
         <v>27</v>
       </c>
@@ -13721,10 +13771,10 @@
       <c r="O75" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P75" s="86"/>
-      <c r="Q75" s="86"/>
-    </row>
-    <row r="76" spans="1:17" ht="57.6" customHeight="1">
+      <c r="P75" s="85"/>
+      <c r="Q75" s="85"/>
+    </row>
+    <row r="76" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="43" t="s">
         <v>48</v>
       </c>
@@ -13757,7 +13807,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="43.2" customHeight="1">
+    <row r="77" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="43" t="s">
         <v>51</v>
       </c>
@@ -13790,7 +13840,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="72" customHeight="1">
+    <row r="78" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="43" t="s">
         <v>50</v>
       </c>
@@ -13823,7 +13873,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="57.6" customHeight="1">
+    <row r="79" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="43" t="s">
         <v>49</v>
       </c>
@@ -13856,7 +13906,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="28.95" customHeight="1">
+    <row r="80" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="46" t="s">
         <v>857</v>
       </c>
@@ -13899,81 +13949,81 @@
         <v>272</v>
       </c>
     </row>
-    <row r="81" spans="1:17">
-      <c r="A81" s="87" t="s">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A81" s="86" t="s">
         <v>858</v>
       </c>
-      <c r="B81" s="86"/>
-      <c r="C81" s="86"/>
-      <c r="D81" s="86"/>
-      <c r="E81" s="86"/>
-      <c r="F81" s="86"/>
-      <c r="G81" s="86"/>
-      <c r="H81" s="86"/>
-      <c r="I81" s="86"/>
-      <c r="J81" s="86"/>
-      <c r="K81" s="86"/>
-      <c r="L81" s="86"/>
-      <c r="M81" s="86"/>
-      <c r="N81" s="86"/>
-      <c r="O81" s="86"/>
-      <c r="P81" s="86"/>
-      <c r="Q81" s="86"/>
-    </row>
-    <row r="82" spans="1:17">
-      <c r="A82" s="86"/>
-      <c r="B82" s="86"/>
-      <c r="C82" s="86"/>
-      <c r="D82" s="86"/>
-      <c r="E82" s="86"/>
-      <c r="F82" s="86"/>
-      <c r="G82" s="86"/>
-      <c r="H82" s="86"/>
-      <c r="I82" s="86"/>
-      <c r="J82" s="86"/>
-      <c r="K82" s="86"/>
-      <c r="L82" s="86"/>
-      <c r="M82" s="86"/>
-      <c r="N82" s="86"/>
-      <c r="O82" s="86"/>
-      <c r="P82" s="86"/>
-      <c r="Q82" s="86"/>
-    </row>
-    <row r="83" spans="1:17" ht="14.4" customHeight="1">
-      <c r="A83" s="88" t="s">
+      <c r="B81" s="85"/>
+      <c r="C81" s="85"/>
+      <c r="D81" s="85"/>
+      <c r="E81" s="85"/>
+      <c r="F81" s="85"/>
+      <c r="G81" s="85"/>
+      <c r="H81" s="85"/>
+      <c r="I81" s="85"/>
+      <c r="J81" s="85"/>
+      <c r="K81" s="85"/>
+      <c r="L81" s="85"/>
+      <c r="M81" s="85"/>
+      <c r="N81" s="85"/>
+      <c r="O81" s="85"/>
+      <c r="P81" s="85"/>
+      <c r="Q81" s="85"/>
+    </row>
+    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A82" s="85"/>
+      <c r="B82" s="85"/>
+      <c r="C82" s="85"/>
+      <c r="D82" s="85"/>
+      <c r="E82" s="85"/>
+      <c r="F82" s="85"/>
+      <c r="G82" s="85"/>
+      <c r="H82" s="85"/>
+      <c r="I82" s="85"/>
+      <c r="J82" s="85"/>
+      <c r="K82" s="85"/>
+      <c r="L82" s="85"/>
+      <c r="M82" s="85"/>
+      <c r="N82" s="85"/>
+      <c r="O82" s="85"/>
+      <c r="P82" s="85"/>
+      <c r="Q82" s="85"/>
+    </row>
+    <row r="83" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="B83" s="85" t="s">
+      <c r="B83" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="C83" s="86"/>
-      <c r="D83" s="86"/>
-      <c r="E83" s="85" t="s">
+      <c r="C83" s="85"/>
+      <c r="D83" s="85"/>
+      <c r="E83" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="F83" s="86"/>
-      <c r="G83" s="86"/>
-      <c r="H83" s="85" t="s">
+      <c r="F83" s="85"/>
+      <c r="G83" s="85"/>
+      <c r="H83" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="I83" s="86"/>
-      <c r="J83" s="86"/>
-      <c r="K83" s="85" t="s">
+      <c r="I83" s="85"/>
+      <c r="J83" s="85"/>
+      <c r="K83" s="84" t="s">
         <v>24</v>
       </c>
-      <c r="L83" s="86"/>
-      <c r="M83" s="86"/>
-      <c r="N83" s="86"/>
-      <c r="O83" s="86"/>
-      <c r="P83" s="85" t="s">
+      <c r="L83" s="85"/>
+      <c r="M83" s="85"/>
+      <c r="N83" s="85"/>
+      <c r="O83" s="85"/>
+      <c r="P83" s="84" t="s">
         <v>25</v>
       </c>
-      <c r="Q83" s="85" t="s">
+      <c r="Q83" s="84" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="84" spans="1:17">
-      <c r="A84" s="86"/>
+    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A84" s="85"/>
       <c r="B84" s="43" t="s">
         <v>27</v>
       </c>
@@ -14016,10 +14066,10 @@
       <c r="O84" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P84" s="86"/>
-      <c r="Q84" s="86"/>
-    </row>
-    <row r="85" spans="1:17" ht="100.95" customHeight="1">
+      <c r="P84" s="85"/>
+      <c r="Q84" s="85"/>
+    </row>
+    <row r="85" spans="1:17" ht="100.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="43" t="s">
         <v>859</v>
       </c>
@@ -14052,7 +14102,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="86" spans="1:17" ht="100.95" customHeight="1">
+    <row r="86" spans="1:17" ht="100.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="43" t="s">
         <v>860</v>
       </c>
@@ -14085,7 +14135,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="87" spans="1:17" ht="28.95" customHeight="1">
+    <row r="87" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="43" t="s">
         <v>800</v>
       </c>
@@ -14118,7 +14168,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="88" spans="1:17">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88" s="43" t="s">
         <v>805</v>
       </c>
@@ -14151,7 +14201,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="89" spans="1:17" ht="28.95" customHeight="1">
+    <row r="89" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="43" t="s">
         <v>810</v>
       </c>
@@ -14184,7 +14234,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="90" spans="1:17">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90" s="43" t="s">
         <v>815</v>
       </c>
@@ -14217,7 +14267,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="91" spans="1:17" ht="28.95" customHeight="1">
+    <row r="91" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="43" t="s">
         <v>861</v>
       </c>
@@ -14250,7 +14300,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="92" spans="1:17" ht="28.95" customHeight="1">
+    <row r="92" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="46" t="s">
         <v>862</v>
       </c>
@@ -14293,81 +14343,81 @@
         <v>30</v>
       </c>
     </row>
-    <row r="93" spans="1:17">
-      <c r="A93" s="87" t="s">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A93" s="86" t="s">
         <v>863</v>
       </c>
-      <c r="B93" s="86"/>
-      <c r="C93" s="86"/>
-      <c r="D93" s="86"/>
-      <c r="E93" s="86"/>
-      <c r="F93" s="86"/>
-      <c r="G93" s="86"/>
-      <c r="H93" s="86"/>
-      <c r="I93" s="86"/>
-      <c r="J93" s="86"/>
-      <c r="K93" s="86"/>
-      <c r="L93" s="86"/>
-      <c r="M93" s="86"/>
-      <c r="N93" s="86"/>
-      <c r="O93" s="86"/>
-      <c r="P93" s="86"/>
-      <c r="Q93" s="86"/>
-    </row>
-    <row r="94" spans="1:17">
-      <c r="A94" s="86"/>
-      <c r="B94" s="86"/>
-      <c r="C94" s="86"/>
-      <c r="D94" s="86"/>
-      <c r="E94" s="86"/>
-      <c r="F94" s="86"/>
-      <c r="G94" s="86"/>
-      <c r="H94" s="86"/>
-      <c r="I94" s="86"/>
-      <c r="J94" s="86"/>
-      <c r="K94" s="86"/>
-      <c r="L94" s="86"/>
-      <c r="M94" s="86"/>
-      <c r="N94" s="86"/>
-      <c r="O94" s="86"/>
-      <c r="P94" s="86"/>
-      <c r="Q94" s="86"/>
-    </row>
-    <row r="95" spans="1:17" ht="14.4" customHeight="1">
-      <c r="A95" s="88" t="s">
+      <c r="B93" s="85"/>
+      <c r="C93" s="85"/>
+      <c r="D93" s="85"/>
+      <c r="E93" s="85"/>
+      <c r="F93" s="85"/>
+      <c r="G93" s="85"/>
+      <c r="H93" s="85"/>
+      <c r="I93" s="85"/>
+      <c r="J93" s="85"/>
+      <c r="K93" s="85"/>
+      <c r="L93" s="85"/>
+      <c r="M93" s="85"/>
+      <c r="N93" s="85"/>
+      <c r="O93" s="85"/>
+      <c r="P93" s="85"/>
+      <c r="Q93" s="85"/>
+    </row>
+    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A94" s="85"/>
+      <c r="B94" s="85"/>
+      <c r="C94" s="85"/>
+      <c r="D94" s="85"/>
+      <c r="E94" s="85"/>
+      <c r="F94" s="85"/>
+      <c r="G94" s="85"/>
+      <c r="H94" s="85"/>
+      <c r="I94" s="85"/>
+      <c r="J94" s="85"/>
+      <c r="K94" s="85"/>
+      <c r="L94" s="85"/>
+      <c r="M94" s="85"/>
+      <c r="N94" s="85"/>
+      <c r="O94" s="85"/>
+      <c r="P94" s="85"/>
+      <c r="Q94" s="85"/>
+    </row>
+    <row r="95" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="B95" s="85" t="s">
+      <c r="B95" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="C95" s="86"/>
-      <c r="D95" s="86"/>
-      <c r="E95" s="85" t="s">
+      <c r="C95" s="85"/>
+      <c r="D95" s="85"/>
+      <c r="E95" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="F95" s="86"/>
-      <c r="G95" s="86"/>
-      <c r="H95" s="85" t="s">
+      <c r="F95" s="85"/>
+      <c r="G95" s="85"/>
+      <c r="H95" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="I95" s="86"/>
-      <c r="J95" s="86"/>
-      <c r="K95" s="85" t="s">
+      <c r="I95" s="85"/>
+      <c r="J95" s="85"/>
+      <c r="K95" s="84" t="s">
         <v>24</v>
       </c>
-      <c r="L95" s="86"/>
-      <c r="M95" s="86"/>
-      <c r="N95" s="86"/>
-      <c r="O95" s="86"/>
-      <c r="P95" s="85" t="s">
+      <c r="L95" s="85"/>
+      <c r="M95" s="85"/>
+      <c r="N95" s="85"/>
+      <c r="O95" s="85"/>
+      <c r="P95" s="84" t="s">
         <v>25</v>
       </c>
-      <c r="Q95" s="85" t="s">
+      <c r="Q95" s="84" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="96" spans="1:17">
-      <c r="A96" s="86"/>
+    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A96" s="85"/>
       <c r="B96" s="43" t="s">
         <v>27</v>
       </c>
@@ -14410,10 +14460,10 @@
       <c r="O96" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P96" s="86"/>
-      <c r="Q96" s="86"/>
-    </row>
-    <row r="97" spans="1:17" ht="57.6" customHeight="1">
+      <c r="P96" s="85"/>
+      <c r="Q96" s="85"/>
+    </row>
+    <row r="97" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="43" t="s">
         <v>864</v>
       </c>
@@ -14446,7 +14496,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="98" spans="1:17" ht="57.6" customHeight="1">
+    <row r="98" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="43" t="s">
         <v>54</v>
       </c>
@@ -14479,7 +14529,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="99" spans="1:17" ht="72" customHeight="1">
+    <row r="99" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="43" t="s">
         <v>55</v>
       </c>
@@ -14512,7 +14562,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="100" spans="1:17" ht="28.95" customHeight="1">
+    <row r="100" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="43" t="s">
         <v>56</v>
       </c>
@@ -14545,7 +14595,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="101" spans="1:17" ht="115.2" customHeight="1">
+    <row r="101" spans="1:17" ht="115.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="43" t="s">
         <v>57</v>
       </c>
@@ -14578,7 +14628,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="72" customHeight="1">
+    <row r="102" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="43" t="s">
         <v>865</v>
       </c>
@@ -14611,7 +14661,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="28.95" customHeight="1">
+    <row r="103" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="43" t="s">
         <v>866</v>
       </c>
@@ -14644,7 +14694,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="43.2" customHeight="1">
+    <row r="104" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="43" t="s">
         <v>58</v>
       </c>
@@ -14677,7 +14727,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="57.6" customHeight="1">
+    <row r="105" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="43" t="s">
         <v>59</v>
       </c>
@@ -14710,7 +14760,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="106" spans="1:17" ht="72" customHeight="1">
+    <row r="106" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="43" t="s">
         <v>60</v>
       </c>
@@ -14743,7 +14793,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="107" spans="1:17" ht="100.95" customHeight="1">
+    <row r="107" spans="1:17" ht="100.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="43" t="s">
         <v>867</v>
       </c>
@@ -14776,7 +14826,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:17" ht="57.6" customHeight="1">
+    <row r="108" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="43" t="s">
         <v>61</v>
       </c>
@@ -14809,7 +14859,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="72" customHeight="1">
+    <row r="109" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="43" t="s">
         <v>868</v>
       </c>
@@ -14842,7 +14892,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="110" spans="1:17" ht="57.6" customHeight="1">
+    <row r="110" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="43" t="s">
         <v>62</v>
       </c>
@@ -14875,7 +14925,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:17" ht="86.4" customHeight="1">
+    <row r="111" spans="1:17" ht="86.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="43" t="s">
         <v>63</v>
       </c>
@@ -14908,7 +14958,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:17" ht="57.6" customHeight="1">
+    <row r="112" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="43" t="s">
         <v>64</v>
       </c>
@@ -14941,7 +14991,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="113" spans="1:17" ht="86.4" customHeight="1">
+    <row r="113" spans="1:17" ht="86.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="43" t="s">
         <v>869</v>
       </c>
@@ -14974,7 +15024,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="114" spans="1:17" ht="57.6" customHeight="1">
+    <row r="114" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="43" t="s">
         <v>870</v>
       </c>
@@ -15007,7 +15057,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="115" spans="1:17" ht="86.4" customHeight="1">
+    <row r="115" spans="1:17" ht="86.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="43" t="s">
         <v>871</v>
       </c>
@@ -15040,7 +15090,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="116" spans="1:17" ht="72" customHeight="1">
+    <row r="116" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="43" t="s">
         <v>872</v>
       </c>
@@ -15073,7 +15123,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="117" spans="1:17" ht="72" customHeight="1">
+    <row r="117" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="43" t="s">
         <v>65</v>
       </c>
@@ -15106,7 +15156,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="57.6" customHeight="1">
+    <row r="118" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="43" t="s">
         <v>66</v>
       </c>
@@ -15139,7 +15189,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="72" customHeight="1">
+    <row r="119" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="43" t="s">
         <v>873</v>
       </c>
@@ -15172,7 +15222,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="57.6" customHeight="1">
+    <row r="120" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="43" t="s">
         <v>874</v>
       </c>
@@ -15205,7 +15255,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:17" ht="57.6" customHeight="1">
+    <row r="121" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="43" t="s">
         <v>875</v>
       </c>
@@ -15238,7 +15288,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="122" spans="1:17" ht="43.2" customHeight="1">
+    <row r="122" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="43" t="s">
         <v>876</v>
       </c>
@@ -15271,7 +15321,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:17" ht="100.95" customHeight="1">
+    <row r="123" spans="1:17" ht="100.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="43" t="s">
         <v>877</v>
       </c>
@@ -15304,7 +15354,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="124" spans="1:17" ht="100.95" customHeight="1">
+    <row r="124" spans="1:17" ht="100.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="43" t="s">
         <v>878</v>
       </c>
@@ -15337,7 +15387,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="125" spans="1:17" ht="43.2" customHeight="1">
+    <row r="125" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="43" t="s">
         <v>879</v>
       </c>
@@ -15370,7 +15420,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="43.2" customHeight="1">
+    <row r="126" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="46" t="s">
         <v>863</v>
       </c>
@@ -15413,81 +15463,81 @@
         <v>128</v>
       </c>
     </row>
-    <row r="127" spans="1:17">
-      <c r="A127" s="87" t="s">
+    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A127" s="86" t="s">
         <v>557</v>
       </c>
-      <c r="B127" s="86"/>
-      <c r="C127" s="86"/>
-      <c r="D127" s="86"/>
-      <c r="E127" s="86"/>
-      <c r="F127" s="86"/>
-      <c r="G127" s="86"/>
-      <c r="H127" s="86"/>
-      <c r="I127" s="86"/>
-      <c r="J127" s="86"/>
-      <c r="K127" s="86"/>
-      <c r="L127" s="86"/>
-      <c r="M127" s="86"/>
-      <c r="N127" s="86"/>
-      <c r="O127" s="86"/>
-      <c r="P127" s="86"/>
-      <c r="Q127" s="86"/>
-    </row>
-    <row r="128" spans="1:17">
-      <c r="A128" s="86"/>
-      <c r="B128" s="86"/>
-      <c r="C128" s="86"/>
-      <c r="D128" s="86"/>
-      <c r="E128" s="86"/>
-      <c r="F128" s="86"/>
-      <c r="G128" s="86"/>
-      <c r="H128" s="86"/>
-      <c r="I128" s="86"/>
-      <c r="J128" s="86"/>
-      <c r="K128" s="86"/>
-      <c r="L128" s="86"/>
-      <c r="M128" s="86"/>
-      <c r="N128" s="86"/>
-      <c r="O128" s="86"/>
-      <c r="P128" s="86"/>
-      <c r="Q128" s="86"/>
-    </row>
-    <row r="129" spans="1:17" ht="14.4" customHeight="1">
-      <c r="A129" s="88" t="s">
+      <c r="B127" s="85"/>
+      <c r="C127" s="85"/>
+      <c r="D127" s="85"/>
+      <c r="E127" s="85"/>
+      <c r="F127" s="85"/>
+      <c r="G127" s="85"/>
+      <c r="H127" s="85"/>
+      <c r="I127" s="85"/>
+      <c r="J127" s="85"/>
+      <c r="K127" s="85"/>
+      <c r="L127" s="85"/>
+      <c r="M127" s="85"/>
+      <c r="N127" s="85"/>
+      <c r="O127" s="85"/>
+      <c r="P127" s="85"/>
+      <c r="Q127" s="85"/>
+    </row>
+    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A128" s="85"/>
+      <c r="B128" s="85"/>
+      <c r="C128" s="85"/>
+      <c r="D128" s="85"/>
+      <c r="E128" s="85"/>
+      <c r="F128" s="85"/>
+      <c r="G128" s="85"/>
+      <c r="H128" s="85"/>
+      <c r="I128" s="85"/>
+      <c r="J128" s="85"/>
+      <c r="K128" s="85"/>
+      <c r="L128" s="85"/>
+      <c r="M128" s="85"/>
+      <c r="N128" s="85"/>
+      <c r="O128" s="85"/>
+      <c r="P128" s="85"/>
+      <c r="Q128" s="85"/>
+    </row>
+    <row r="129" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A129" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="B129" s="85" t="s">
+      <c r="B129" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="C129" s="86"/>
-      <c r="D129" s="86"/>
-      <c r="E129" s="85" t="s">
+      <c r="C129" s="85"/>
+      <c r="D129" s="85"/>
+      <c r="E129" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="F129" s="86"/>
-      <c r="G129" s="86"/>
-      <c r="H129" s="85" t="s">
+      <c r="F129" s="85"/>
+      <c r="G129" s="85"/>
+      <c r="H129" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="I129" s="86"/>
-      <c r="J129" s="86"/>
-      <c r="K129" s="85" t="s">
+      <c r="I129" s="85"/>
+      <c r="J129" s="85"/>
+      <c r="K129" s="84" t="s">
         <v>24</v>
       </c>
-      <c r="L129" s="86"/>
-      <c r="M129" s="86"/>
-      <c r="N129" s="86"/>
-      <c r="O129" s="86"/>
-      <c r="P129" s="85" t="s">
+      <c r="L129" s="85"/>
+      <c r="M129" s="85"/>
+      <c r="N129" s="85"/>
+      <c r="O129" s="85"/>
+      <c r="P129" s="84" t="s">
         <v>25</v>
       </c>
-      <c r="Q129" s="85" t="s">
+      <c r="Q129" s="84" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="130" spans="1:17">
-      <c r="A130" s="86"/>
+    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A130" s="85"/>
       <c r="B130" s="43" t="s">
         <v>27</v>
       </c>
@@ -15530,10 +15580,10 @@
       <c r="O130" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P130" s="86"/>
-      <c r="Q130" s="86"/>
-    </row>
-    <row r="131" spans="1:17" ht="43.2" customHeight="1">
+      <c r="P130" s="85"/>
+      <c r="Q130" s="85"/>
+    </row>
+    <row r="131" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="43" t="s">
         <v>880</v>
       </c>
@@ -15584,7 +15634,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="132" spans="1:17" ht="72" customHeight="1">
+    <row r="132" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="43" t="s">
         <v>881</v>
       </c>
@@ -15635,7 +15685,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="133" spans="1:17" ht="115.2" customHeight="1">
+    <row r="133" spans="1:17" ht="115.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="43" t="s">
         <v>882</v>
       </c>
@@ -15686,7 +15736,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="134" spans="1:17" ht="129.6" customHeight="1">
+    <row r="134" spans="1:17" ht="129.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="43" t="s">
         <v>883</v>
       </c>
@@ -15719,7 +15769,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="135" spans="1:17" ht="129.6" customHeight="1">
+    <row r="135" spans="1:17" ht="129.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="43" t="s">
         <v>38</v>
       </c>
@@ -15752,7 +15802,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="136" spans="1:17" ht="144" customHeight="1">
+    <row r="136" spans="1:17" ht="144" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="43" t="s">
         <v>884</v>
       </c>
@@ -15785,7 +15835,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="137" spans="1:17" ht="43.2" customHeight="1">
+    <row r="137" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="46" t="s">
         <v>885</v>
       </c>
@@ -15828,7 +15878,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="138" spans="1:17">
+    <row r="138" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A138" s="43" t="s">
         <v>886</v>
       </c>
@@ -15879,7 +15929,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="139" spans="1:17" ht="57.6" customHeight="1">
+    <row r="139" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="43" t="s">
         <v>887</v>
       </c>
@@ -15912,7 +15962,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="140" spans="1:17" ht="86.4" customHeight="1">
+    <row r="140" spans="1:17" ht="86.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="43" t="s">
         <v>888</v>
       </c>
@@ -15945,7 +15995,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="141" spans="1:17" ht="57.6" customHeight="1">
+    <row r="141" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="46" t="s">
         <v>889</v>
       </c>
@@ -15988,7 +16038,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="142" spans="1:17" ht="57.6" customHeight="1">
+    <row r="142" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="43" t="s">
         <v>890</v>
       </c>
@@ -16021,7 +16071,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="143" spans="1:17" ht="72" customHeight="1">
+    <row r="143" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="43" t="s">
         <v>891</v>
       </c>
@@ -16054,7 +16104,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="144" spans="1:17" ht="43.2" customHeight="1">
+    <row r="144" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="46" t="s">
         <v>892</v>
       </c>
@@ -16097,7 +16147,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="145" spans="1:17" ht="72" customHeight="1">
+    <row r="145" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="43" t="s">
         <v>893</v>
       </c>
@@ -16130,7 +16180,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="146" spans="1:17" ht="100.95" customHeight="1">
+    <row r="146" spans="1:17" ht="100.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="43" t="s">
         <v>894</v>
       </c>
@@ -16163,7 +16213,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="147" spans="1:17" ht="43.2" customHeight="1">
+    <row r="147" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="46" t="s">
         <v>895</v>
       </c>
@@ -16206,7 +16256,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="148" spans="1:17" ht="28.95" customHeight="1">
+    <row r="148" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="43" t="s">
         <v>896</v>
       </c>
@@ -16257,7 +16307,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="149" spans="1:17" ht="57.6" customHeight="1">
+    <row r="149" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="43" t="s">
         <v>897</v>
       </c>
@@ -16290,7 +16340,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="150" spans="1:17" ht="28.95" customHeight="1">
+    <row r="150" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="43" t="s">
         <v>898</v>
       </c>
@@ -16323,7 +16373,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="151" spans="1:17" ht="43.2" customHeight="1">
+    <row r="151" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="46" t="s">
         <v>899</v>
       </c>
@@ -16366,7 +16416,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="152" spans="1:17" ht="43.2" customHeight="1">
+    <row r="152" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="43" t="s">
         <v>900</v>
       </c>
@@ -16417,7 +16467,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="153" spans="1:17" ht="28.95" customHeight="1">
+    <row r="153" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="43" t="s">
         <v>750</v>
       </c>
@@ -16468,7 +16518,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="154" spans="1:17" ht="28.95" customHeight="1">
+    <row r="154" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="43" t="s">
         <v>901</v>
       </c>
@@ -16519,7 +16569,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="155" spans="1:17" ht="28.95" customHeight="1">
+    <row r="155" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="43" t="s">
         <v>706</v>
       </c>
@@ -16552,7 +16602,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="156" spans="1:17" ht="28.95" customHeight="1">
+    <row r="156" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="43" t="s">
         <v>712</v>
       </c>
@@ -16585,7 +16635,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="157" spans="1:17" ht="28.95" customHeight="1">
+    <row r="157" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="43" t="s">
         <v>902</v>
       </c>
@@ -16618,7 +16668,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="158" spans="1:17" ht="57.6" customHeight="1">
+    <row r="158" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="46" t="s">
         <v>903</v>
       </c>
@@ -16661,81 +16711,81 @@
         <v>17</v>
       </c>
     </row>
-    <row r="159" spans="1:17">
-      <c r="A159" s="87" t="s">
+    <row r="159" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A159" s="86" t="s">
         <v>46</v>
       </c>
-      <c r="B159" s="86"/>
-      <c r="C159" s="86"/>
-      <c r="D159" s="86"/>
-      <c r="E159" s="86"/>
-      <c r="F159" s="86"/>
-      <c r="G159" s="86"/>
-      <c r="H159" s="86"/>
-      <c r="I159" s="86"/>
-      <c r="J159" s="86"/>
-      <c r="K159" s="86"/>
-      <c r="L159" s="86"/>
-      <c r="M159" s="86"/>
-      <c r="N159" s="86"/>
-      <c r="O159" s="86"/>
-      <c r="P159" s="86"/>
-      <c r="Q159" s="86"/>
-    </row>
-    <row r="160" spans="1:17">
-      <c r="A160" s="86"/>
-      <c r="B160" s="86"/>
-      <c r="C160" s="86"/>
-      <c r="D160" s="86"/>
-      <c r="E160" s="86"/>
-      <c r="F160" s="86"/>
-      <c r="G160" s="86"/>
-      <c r="H160" s="86"/>
-      <c r="I160" s="86"/>
-      <c r="J160" s="86"/>
-      <c r="K160" s="86"/>
-      <c r="L160" s="86"/>
-      <c r="M160" s="86"/>
-      <c r="N160" s="86"/>
-      <c r="O160" s="86"/>
-      <c r="P160" s="86"/>
-      <c r="Q160" s="86"/>
-    </row>
-    <row r="161" spans="1:17" ht="14.4" customHeight="1">
-      <c r="A161" s="88" t="s">
+      <c r="B159" s="85"/>
+      <c r="C159" s="85"/>
+      <c r="D159" s="85"/>
+      <c r="E159" s="85"/>
+      <c r="F159" s="85"/>
+      <c r="G159" s="85"/>
+      <c r="H159" s="85"/>
+      <c r="I159" s="85"/>
+      <c r="J159" s="85"/>
+      <c r="K159" s="85"/>
+      <c r="L159" s="85"/>
+      <c r="M159" s="85"/>
+      <c r="N159" s="85"/>
+      <c r="O159" s="85"/>
+      <c r="P159" s="85"/>
+      <c r="Q159" s="85"/>
+    </row>
+    <row r="160" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A160" s="85"/>
+      <c r="B160" s="85"/>
+      <c r="C160" s="85"/>
+      <c r="D160" s="85"/>
+      <c r="E160" s="85"/>
+      <c r="F160" s="85"/>
+      <c r="G160" s="85"/>
+      <c r="H160" s="85"/>
+      <c r="I160" s="85"/>
+      <c r="J160" s="85"/>
+      <c r="K160" s="85"/>
+      <c r="L160" s="85"/>
+      <c r="M160" s="85"/>
+      <c r="N160" s="85"/>
+      <c r="O160" s="85"/>
+      <c r="P160" s="85"/>
+      <c r="Q160" s="85"/>
+    </row>
+    <row r="161" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A161" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="B161" s="85" t="s">
+      <c r="B161" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="C161" s="86"/>
-      <c r="D161" s="86"/>
-      <c r="E161" s="85" t="s">
+      <c r="C161" s="85"/>
+      <c r="D161" s="85"/>
+      <c r="E161" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="F161" s="86"/>
-      <c r="G161" s="86"/>
-      <c r="H161" s="85" t="s">
+      <c r="F161" s="85"/>
+      <c r="G161" s="85"/>
+      <c r="H161" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="I161" s="86"/>
-      <c r="J161" s="86"/>
-      <c r="K161" s="85" t="s">
+      <c r="I161" s="85"/>
+      <c r="J161" s="85"/>
+      <c r="K161" s="84" t="s">
         <v>24</v>
       </c>
-      <c r="L161" s="86"/>
-      <c r="M161" s="86"/>
-      <c r="N161" s="86"/>
-      <c r="O161" s="86"/>
-      <c r="P161" s="85" t="s">
+      <c r="L161" s="85"/>
+      <c r="M161" s="85"/>
+      <c r="N161" s="85"/>
+      <c r="O161" s="85"/>
+      <c r="P161" s="84" t="s">
         <v>25</v>
       </c>
-      <c r="Q161" s="85" t="s">
+      <c r="Q161" s="84" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="162" spans="1:17">
-      <c r="A162" s="86"/>
+    <row r="162" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A162" s="85"/>
       <c r="B162" s="43" t="s">
         <v>27</v>
       </c>
@@ -16778,10 +16828,10 @@
       <c r="O162" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P162" s="86"/>
-      <c r="Q162" s="86"/>
-    </row>
-    <row r="163" spans="1:17" ht="28.95" customHeight="1">
+      <c r="P162" s="85"/>
+      <c r="Q162" s="85"/>
+    </row>
+    <row r="163" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="43" t="s">
         <v>46</v>
       </c>
@@ -16832,81 +16882,81 @@
         <v>13</v>
       </c>
     </row>
-    <row r="164" spans="1:17">
-      <c r="A164" s="87" t="s">
+    <row r="164" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A164" s="86" t="s">
         <v>69</v>
       </c>
-      <c r="B164" s="86"/>
-      <c r="C164" s="86"/>
-      <c r="D164" s="86"/>
-      <c r="E164" s="86"/>
-      <c r="F164" s="86"/>
-      <c r="G164" s="86"/>
-      <c r="H164" s="86"/>
-      <c r="I164" s="86"/>
-      <c r="J164" s="86"/>
-      <c r="K164" s="86"/>
-      <c r="L164" s="86"/>
-      <c r="M164" s="86"/>
-      <c r="N164" s="86"/>
-      <c r="O164" s="86"/>
-      <c r="P164" s="86"/>
-      <c r="Q164" s="86"/>
-    </row>
-    <row r="165" spans="1:17">
-      <c r="A165" s="86"/>
-      <c r="B165" s="86"/>
-      <c r="C165" s="86"/>
-      <c r="D165" s="86"/>
-      <c r="E165" s="86"/>
-      <c r="F165" s="86"/>
-      <c r="G165" s="86"/>
-      <c r="H165" s="86"/>
-      <c r="I165" s="86"/>
-      <c r="J165" s="86"/>
-      <c r="K165" s="86"/>
-      <c r="L165" s="86"/>
-      <c r="M165" s="86"/>
-      <c r="N165" s="86"/>
-      <c r="O165" s="86"/>
-      <c r="P165" s="86"/>
-      <c r="Q165" s="86"/>
-    </row>
-    <row r="166" spans="1:17" ht="14.4" customHeight="1">
-      <c r="A166" s="88" t="s">
+      <c r="B164" s="85"/>
+      <c r="C164" s="85"/>
+      <c r="D164" s="85"/>
+      <c r="E164" s="85"/>
+      <c r="F164" s="85"/>
+      <c r="G164" s="85"/>
+      <c r="H164" s="85"/>
+      <c r="I164" s="85"/>
+      <c r="J164" s="85"/>
+      <c r="K164" s="85"/>
+      <c r="L164" s="85"/>
+      <c r="M164" s="85"/>
+      <c r="N164" s="85"/>
+      <c r="O164" s="85"/>
+      <c r="P164" s="85"/>
+      <c r="Q164" s="85"/>
+    </row>
+    <row r="165" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A165" s="85"/>
+      <c r="B165" s="85"/>
+      <c r="C165" s="85"/>
+      <c r="D165" s="85"/>
+      <c r="E165" s="85"/>
+      <c r="F165" s="85"/>
+      <c r="G165" s="85"/>
+      <c r="H165" s="85"/>
+      <c r="I165" s="85"/>
+      <c r="J165" s="85"/>
+      <c r="K165" s="85"/>
+      <c r="L165" s="85"/>
+      <c r="M165" s="85"/>
+      <c r="N165" s="85"/>
+      <c r="O165" s="85"/>
+      <c r="P165" s="85"/>
+      <c r="Q165" s="85"/>
+    </row>
+    <row r="166" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A166" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="B166" s="85" t="s">
+      <c r="B166" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="C166" s="86"/>
-      <c r="D166" s="86"/>
-      <c r="E166" s="85" t="s">
+      <c r="C166" s="85"/>
+      <c r="D166" s="85"/>
+      <c r="E166" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="F166" s="86"/>
-      <c r="G166" s="86"/>
-      <c r="H166" s="85" t="s">
+      <c r="F166" s="85"/>
+      <c r="G166" s="85"/>
+      <c r="H166" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="I166" s="86"/>
-      <c r="J166" s="86"/>
-      <c r="K166" s="85" t="s">
+      <c r="I166" s="85"/>
+      <c r="J166" s="85"/>
+      <c r="K166" s="84" t="s">
         <v>24</v>
       </c>
-      <c r="L166" s="86"/>
-      <c r="M166" s="86"/>
-      <c r="N166" s="86"/>
-      <c r="O166" s="86"/>
-      <c r="P166" s="85" t="s">
+      <c r="L166" s="85"/>
+      <c r="M166" s="85"/>
+      <c r="N166" s="85"/>
+      <c r="O166" s="85"/>
+      <c r="P166" s="84" t="s">
         <v>25</v>
       </c>
-      <c r="Q166" s="85" t="s">
+      <c r="Q166" s="84" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="167" spans="1:17">
-      <c r="A167" s="86"/>
+    <row r="167" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A167" s="85"/>
       <c r="B167" s="43" t="s">
         <v>27</v>
       </c>
@@ -16949,10 +16999,10 @@
       <c r="O167" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P167" s="86"/>
-      <c r="Q167" s="86"/>
-    </row>
-    <row r="168" spans="1:17" ht="72" customHeight="1">
+      <c r="P167" s="85"/>
+      <c r="Q167" s="85"/>
+    </row>
+    <row r="168" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="43" t="s">
         <v>904</v>
       </c>
@@ -16985,7 +17035,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="169" spans="1:17" ht="57.6" customHeight="1">
+    <row r="169" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="43" t="s">
         <v>70</v>
       </c>
@@ -17018,7 +17068,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="170" spans="1:17" ht="72" customHeight="1">
+    <row r="170" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="43" t="s">
         <v>71</v>
       </c>
@@ -17051,7 +17101,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="171" spans="1:17" ht="57.6" customHeight="1">
+    <row r="171" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="43" t="s">
         <v>72</v>
       </c>
@@ -17084,7 +17134,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="172" spans="1:17" ht="86.4" customHeight="1">
+    <row r="172" spans="1:17" ht="86.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="46" t="s">
         <v>905</v>
       </c>
@@ -17240,184 +17290,184 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:Q87"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="40"/>
     </row>
-    <row r="2" spans="1:1">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="41" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="41" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:1">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="41" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="41" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="41" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="41" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:1">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="41" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:1">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="41" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:1">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="41" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:1">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="41" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:1" ht="15.6" customHeight="1">
+    <row r="13" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="42" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:1">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="40"/>
     </row>
-    <row r="15" spans="1:1">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="41" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:1">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="41" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:17">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="41" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:17">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="41" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:17">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="41" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:17">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="41" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:17">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:17">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:17">
-      <c r="A24" s="87" t="s">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A24" s="86" t="s">
         <v>19</v>
       </c>
-      <c r="B24" s="86"/>
-      <c r="C24" s="86"/>
-      <c r="D24" s="86"/>
-      <c r="E24" s="86"/>
-      <c r="F24" s="86"/>
-      <c r="G24" s="86"/>
-      <c r="H24" s="86"/>
-      <c r="I24" s="86"/>
-      <c r="J24" s="86"/>
-      <c r="K24" s="86"/>
-      <c r="L24" s="86"/>
-      <c r="M24" s="86"/>
-      <c r="N24" s="86"/>
-      <c r="O24" s="86"/>
-      <c r="P24" s="86"/>
-      <c r="Q24" s="86"/>
-    </row>
-    <row r="25" spans="1:17">
-      <c r="A25" s="86"/>
-      <c r="B25" s="86"/>
-      <c r="C25" s="86"/>
-      <c r="D25" s="86"/>
-      <c r="E25" s="86"/>
-      <c r="F25" s="86"/>
-      <c r="G25" s="86"/>
-      <c r="H25" s="86"/>
-      <c r="I25" s="86"/>
-      <c r="J25" s="86"/>
-      <c r="K25" s="86"/>
-      <c r="L25" s="86"/>
-      <c r="M25" s="86"/>
-      <c r="N25" s="86"/>
-      <c r="O25" s="86"/>
-      <c r="P25" s="86"/>
-      <c r="Q25" s="86"/>
-    </row>
-    <row r="26" spans="1:17" ht="14.4" customHeight="1">
-      <c r="A26" s="88" t="s">
+      <c r="B24" s="85"/>
+      <c r="C24" s="85"/>
+      <c r="D24" s="85"/>
+      <c r="E24" s="85"/>
+      <c r="F24" s="85"/>
+      <c r="G24" s="85"/>
+      <c r="H24" s="85"/>
+      <c r="I24" s="85"/>
+      <c r="J24" s="85"/>
+      <c r="K24" s="85"/>
+      <c r="L24" s="85"/>
+      <c r="M24" s="85"/>
+      <c r="N24" s="85"/>
+      <c r="O24" s="85"/>
+      <c r="P24" s="85"/>
+      <c r="Q24" s="85"/>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A25" s="85"/>
+      <c r="B25" s="85"/>
+      <c r="C25" s="85"/>
+      <c r="D25" s="85"/>
+      <c r="E25" s="85"/>
+      <c r="F25" s="85"/>
+      <c r="G25" s="85"/>
+      <c r="H25" s="85"/>
+      <c r="I25" s="85"/>
+      <c r="J25" s="85"/>
+      <c r="K25" s="85"/>
+      <c r="L25" s="85"/>
+      <c r="M25" s="85"/>
+      <c r="N25" s="85"/>
+      <c r="O25" s="85"/>
+      <c r="P25" s="85"/>
+      <c r="Q25" s="85"/>
+    </row>
+    <row r="26" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="B26" s="85" t="s">
+      <c r="B26" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="C26" s="86"/>
-      <c r="D26" s="86"/>
-      <c r="E26" s="85" t="s">
+      <c r="C26" s="85"/>
+      <c r="D26" s="85"/>
+      <c r="E26" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="F26" s="86"/>
-      <c r="G26" s="86"/>
-      <c r="H26" s="85" t="s">
+      <c r="F26" s="85"/>
+      <c r="G26" s="85"/>
+      <c r="H26" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="I26" s="86"/>
-      <c r="J26" s="86"/>
-      <c r="K26" s="85" t="s">
+      <c r="I26" s="85"/>
+      <c r="J26" s="85"/>
+      <c r="K26" s="84" t="s">
         <v>24</v>
       </c>
-      <c r="L26" s="86"/>
-      <c r="M26" s="86"/>
-      <c r="N26" s="86"/>
-      <c r="O26" s="86"/>
-      <c r="P26" s="85" t="s">
+      <c r="L26" s="85"/>
+      <c r="M26" s="85"/>
+      <c r="N26" s="85"/>
+      <c r="O26" s="85"/>
+      <c r="P26" s="84" t="s">
         <v>25</v>
       </c>
-      <c r="Q26" s="85" t="s">
+      <c r="Q26" s="84" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="27" spans="1:17">
-      <c r="A27" s="86"/>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A27" s="85"/>
       <c r="B27" s="43" t="s">
         <v>27</v>
       </c>
@@ -17460,10 +17510,10 @@
       <c r="O27" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P27" s="86"/>
-      <c r="Q27" s="86"/>
-    </row>
-    <row r="28" spans="1:17" ht="115.2" customHeight="1">
+      <c r="P27" s="85"/>
+      <c r="Q27" s="85"/>
+    </row>
+    <row r="28" spans="1:17" ht="115.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="43" t="s">
         <v>31</v>
       </c>
@@ -17496,7 +17546,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="144" customHeight="1">
+    <row r="29" spans="1:17" ht="144" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="43" t="s">
         <v>32</v>
       </c>
@@ -17529,7 +17579,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="129.6" customHeight="1">
+    <row r="30" spans="1:17" ht="129.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="43" t="s">
         <v>33</v>
       </c>
@@ -17562,7 +17612,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="28.95" customHeight="1">
+    <row r="31" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="43" t="s">
         <v>34</v>
       </c>
@@ -17595,7 +17645,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="32" spans="1:17" ht="144" customHeight="1">
+    <row r="32" spans="1:17" ht="144" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="43" t="s">
         <v>35</v>
       </c>
@@ -17628,7 +17678,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:17" ht="100.95" customHeight="1">
+    <row r="33" spans="1:17" ht="100.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="43" t="s">
         <v>36</v>
       </c>
@@ -17661,7 +17711,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="43.2" customHeight="1">
+    <row r="34" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="43" t="s">
         <v>37</v>
       </c>
@@ -17694,7 +17744,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="129.6" customHeight="1">
+    <row r="35" spans="1:17" ht="129.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="43" t="s">
         <v>38</v>
       </c>
@@ -17727,7 +17777,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="28.95" customHeight="1">
+    <row r="36" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="43" t="s">
         <v>39</v>
       </c>
@@ -17760,7 +17810,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="37" spans="1:17" ht="43.2" customHeight="1">
+    <row r="37" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="43" t="s">
         <v>40</v>
       </c>
@@ -17793,7 +17843,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="1:17" ht="100.95" customHeight="1">
+    <row r="38" spans="1:17" ht="100.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="43" t="s">
         <v>41</v>
       </c>
@@ -17826,7 +17876,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="72" customHeight="1">
+    <row r="39" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="43" t="s">
         <v>42</v>
       </c>
@@ -17859,7 +17909,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="40" spans="1:17" ht="72" customHeight="1">
+    <row r="40" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="43" t="s">
         <v>43</v>
       </c>
@@ -17892,7 +17942,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="1:17" ht="115.2" customHeight="1">
+    <row r="41" spans="1:17" ht="115.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="43" t="s">
         <v>44</v>
       </c>
@@ -17925,7 +17975,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:17" ht="28.95" customHeight="1">
+    <row r="42" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="46" t="s">
         <v>45</v>
       </c>
@@ -17968,81 +18018,81 @@
         <v>72</v>
       </c>
     </row>
-    <row r="43" spans="1:17">
-      <c r="A43" s="87" t="s">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A43" s="86" t="s">
         <v>46</v>
       </c>
-      <c r="B43" s="86"/>
-      <c r="C43" s="86"/>
-      <c r="D43" s="86"/>
-      <c r="E43" s="86"/>
-      <c r="F43" s="86"/>
-      <c r="G43" s="86"/>
-      <c r="H43" s="86"/>
-      <c r="I43" s="86"/>
-      <c r="J43" s="86"/>
-      <c r="K43" s="86"/>
-      <c r="L43" s="86"/>
-      <c r="M43" s="86"/>
-      <c r="N43" s="86"/>
-      <c r="O43" s="86"/>
-      <c r="P43" s="86"/>
-      <c r="Q43" s="86"/>
-    </row>
-    <row r="44" spans="1:17">
-      <c r="A44" s="86"/>
-      <c r="B44" s="86"/>
-      <c r="C44" s="86"/>
-      <c r="D44" s="86"/>
-      <c r="E44" s="86"/>
-      <c r="F44" s="86"/>
-      <c r="G44" s="86"/>
-      <c r="H44" s="86"/>
-      <c r="I44" s="86"/>
-      <c r="J44" s="86"/>
-      <c r="K44" s="86"/>
-      <c r="L44" s="86"/>
-      <c r="M44" s="86"/>
-      <c r="N44" s="86"/>
-      <c r="O44" s="86"/>
-      <c r="P44" s="86"/>
-      <c r="Q44" s="86"/>
-    </row>
-    <row r="45" spans="1:17" ht="14.4" customHeight="1">
-      <c r="A45" s="88" t="s">
+      <c r="B43" s="85"/>
+      <c r="C43" s="85"/>
+      <c r="D43" s="85"/>
+      <c r="E43" s="85"/>
+      <c r="F43" s="85"/>
+      <c r="G43" s="85"/>
+      <c r="H43" s="85"/>
+      <c r="I43" s="85"/>
+      <c r="J43" s="85"/>
+      <c r="K43" s="85"/>
+      <c r="L43" s="85"/>
+      <c r="M43" s="85"/>
+      <c r="N43" s="85"/>
+      <c r="O43" s="85"/>
+      <c r="P43" s="85"/>
+      <c r="Q43" s="85"/>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A44" s="85"/>
+      <c r="B44" s="85"/>
+      <c r="C44" s="85"/>
+      <c r="D44" s="85"/>
+      <c r="E44" s="85"/>
+      <c r="F44" s="85"/>
+      <c r="G44" s="85"/>
+      <c r="H44" s="85"/>
+      <c r="I44" s="85"/>
+      <c r="J44" s="85"/>
+      <c r="K44" s="85"/>
+      <c r="L44" s="85"/>
+      <c r="M44" s="85"/>
+      <c r="N44" s="85"/>
+      <c r="O44" s="85"/>
+      <c r="P44" s="85"/>
+      <c r="Q44" s="85"/>
+    </row>
+    <row r="45" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="B45" s="85" t="s">
+      <c r="B45" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="C45" s="86"/>
-      <c r="D45" s="86"/>
-      <c r="E45" s="85" t="s">
+      <c r="C45" s="85"/>
+      <c r="D45" s="85"/>
+      <c r="E45" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="F45" s="86"/>
-      <c r="G45" s="86"/>
-      <c r="H45" s="85" t="s">
+      <c r="F45" s="85"/>
+      <c r="G45" s="85"/>
+      <c r="H45" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="I45" s="86"/>
-      <c r="J45" s="86"/>
-      <c r="K45" s="85" t="s">
+      <c r="I45" s="85"/>
+      <c r="J45" s="85"/>
+      <c r="K45" s="84" t="s">
         <v>24</v>
       </c>
-      <c r="L45" s="86"/>
-      <c r="M45" s="86"/>
-      <c r="N45" s="86"/>
-      <c r="O45" s="86"/>
-      <c r="P45" s="85" t="s">
+      <c r="L45" s="85"/>
+      <c r="M45" s="85"/>
+      <c r="N45" s="85"/>
+      <c r="O45" s="85"/>
+      <c r="P45" s="84" t="s">
         <v>25</v>
       </c>
-      <c r="Q45" s="85" t="s">
+      <c r="Q45" s="84" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="46" spans="1:17">
-      <c r="A46" s="86"/>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A46" s="85"/>
       <c r="B46" s="43" t="s">
         <v>27</v>
       </c>
@@ -18085,10 +18135,10 @@
       <c r="O46" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P46" s="86"/>
-      <c r="Q46" s="86"/>
-    </row>
-    <row r="47" spans="1:17" ht="28.95" customHeight="1">
+      <c r="P46" s="85"/>
+      <c r="Q46" s="85"/>
+    </row>
+    <row r="47" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="43" t="s">
         <v>46</v>
       </c>
@@ -18139,81 +18189,81 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:17">
-      <c r="A48" s="87" t="s">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A48" s="86" t="s">
         <v>47</v>
       </c>
-      <c r="B48" s="86"/>
-      <c r="C48" s="86"/>
-      <c r="D48" s="86"/>
-      <c r="E48" s="86"/>
-      <c r="F48" s="86"/>
-      <c r="G48" s="86"/>
-      <c r="H48" s="86"/>
-      <c r="I48" s="86"/>
-      <c r="J48" s="86"/>
-      <c r="K48" s="86"/>
-      <c r="L48" s="86"/>
-      <c r="M48" s="86"/>
-      <c r="N48" s="86"/>
-      <c r="O48" s="86"/>
-      <c r="P48" s="86"/>
-      <c r="Q48" s="86"/>
-    </row>
-    <row r="49" spans="1:17">
-      <c r="A49" s="86"/>
-      <c r="B49" s="86"/>
-      <c r="C49" s="86"/>
-      <c r="D49" s="86"/>
-      <c r="E49" s="86"/>
-      <c r="F49" s="86"/>
-      <c r="G49" s="86"/>
-      <c r="H49" s="86"/>
-      <c r="I49" s="86"/>
-      <c r="J49" s="86"/>
-      <c r="K49" s="86"/>
-      <c r="L49" s="86"/>
-      <c r="M49" s="86"/>
-      <c r="N49" s="86"/>
-      <c r="O49" s="86"/>
-      <c r="P49" s="86"/>
-      <c r="Q49" s="86"/>
-    </row>
-    <row r="50" spans="1:17" ht="14.4" customHeight="1">
-      <c r="A50" s="88" t="s">
+      <c r="B48" s="85"/>
+      <c r="C48" s="85"/>
+      <c r="D48" s="85"/>
+      <c r="E48" s="85"/>
+      <c r="F48" s="85"/>
+      <c r="G48" s="85"/>
+      <c r="H48" s="85"/>
+      <c r="I48" s="85"/>
+      <c r="J48" s="85"/>
+      <c r="K48" s="85"/>
+      <c r="L48" s="85"/>
+      <c r="M48" s="85"/>
+      <c r="N48" s="85"/>
+      <c r="O48" s="85"/>
+      <c r="P48" s="85"/>
+      <c r="Q48" s="85"/>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A49" s="85"/>
+      <c r="B49" s="85"/>
+      <c r="C49" s="85"/>
+      <c r="D49" s="85"/>
+      <c r="E49" s="85"/>
+      <c r="F49" s="85"/>
+      <c r="G49" s="85"/>
+      <c r="H49" s="85"/>
+      <c r="I49" s="85"/>
+      <c r="J49" s="85"/>
+      <c r="K49" s="85"/>
+      <c r="L49" s="85"/>
+      <c r="M49" s="85"/>
+      <c r="N49" s="85"/>
+      <c r="O49" s="85"/>
+      <c r="P49" s="85"/>
+      <c r="Q49" s="85"/>
+    </row>
+    <row r="50" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="B50" s="85" t="s">
+      <c r="B50" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="C50" s="86"/>
-      <c r="D50" s="86"/>
-      <c r="E50" s="85" t="s">
+      <c r="C50" s="85"/>
+      <c r="D50" s="85"/>
+      <c r="E50" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="F50" s="86"/>
-      <c r="G50" s="86"/>
-      <c r="H50" s="85" t="s">
+      <c r="F50" s="85"/>
+      <c r="G50" s="85"/>
+      <c r="H50" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="I50" s="86"/>
-      <c r="J50" s="86"/>
-      <c r="K50" s="85" t="s">
+      <c r="I50" s="85"/>
+      <c r="J50" s="85"/>
+      <c r="K50" s="84" t="s">
         <v>24</v>
       </c>
-      <c r="L50" s="86"/>
-      <c r="M50" s="86"/>
-      <c r="N50" s="86"/>
-      <c r="O50" s="86"/>
-      <c r="P50" s="85" t="s">
+      <c r="L50" s="85"/>
+      <c r="M50" s="85"/>
+      <c r="N50" s="85"/>
+      <c r="O50" s="85"/>
+      <c r="P50" s="84" t="s">
         <v>25</v>
       </c>
-      <c r="Q50" s="85" t="s">
+      <c r="Q50" s="84" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="51" spans="1:17">
-      <c r="A51" s="86"/>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A51" s="85"/>
       <c r="B51" s="43" t="s">
         <v>27</v>
       </c>
@@ -18256,10 +18306,10 @@
       <c r="O51" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P51" s="86"/>
-      <c r="Q51" s="86"/>
-    </row>
-    <row r="52" spans="1:17" ht="57.6" customHeight="1">
+      <c r="P51" s="85"/>
+      <c r="Q51" s="85"/>
+    </row>
+    <row r="52" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="43" t="s">
         <v>48</v>
       </c>
@@ -18292,7 +18342,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="1:17" ht="57.6" customHeight="1">
+    <row r="53" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="43" t="s">
         <v>49</v>
       </c>
@@ -18325,7 +18375,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="54" spans="1:17" ht="72" customHeight="1">
+    <row r="54" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="43" t="s">
         <v>50</v>
       </c>
@@ -18358,7 +18408,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="1:17" ht="43.2" customHeight="1">
+    <row r="55" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="43" t="s">
         <v>51</v>
       </c>
@@ -18391,7 +18441,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="28.95" customHeight="1">
+    <row r="56" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="46" t="s">
         <v>52</v>
       </c>
@@ -18434,81 +18484,81 @@
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:17">
-      <c r="A57" s="87" t="s">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A57" s="86" t="s">
         <v>53</v>
       </c>
-      <c r="B57" s="86"/>
-      <c r="C57" s="86"/>
-      <c r="D57" s="86"/>
-      <c r="E57" s="86"/>
-      <c r="F57" s="86"/>
-      <c r="G57" s="86"/>
-      <c r="H57" s="86"/>
-      <c r="I57" s="86"/>
-      <c r="J57" s="86"/>
-      <c r="K57" s="86"/>
-      <c r="L57" s="86"/>
-      <c r="M57" s="86"/>
-      <c r="N57" s="86"/>
-      <c r="O57" s="86"/>
-      <c r="P57" s="86"/>
-      <c r="Q57" s="86"/>
-    </row>
-    <row r="58" spans="1:17">
-      <c r="A58" s="86"/>
-      <c r="B58" s="86"/>
-      <c r="C58" s="86"/>
-      <c r="D58" s="86"/>
-      <c r="E58" s="86"/>
-      <c r="F58" s="86"/>
-      <c r="G58" s="86"/>
-      <c r="H58" s="86"/>
-      <c r="I58" s="86"/>
-      <c r="J58" s="86"/>
-      <c r="K58" s="86"/>
-      <c r="L58" s="86"/>
-      <c r="M58" s="86"/>
-      <c r="N58" s="86"/>
-      <c r="O58" s="86"/>
-      <c r="P58" s="86"/>
-      <c r="Q58" s="86"/>
-    </row>
-    <row r="59" spans="1:17" ht="14.4" customHeight="1">
-      <c r="A59" s="88" t="s">
+      <c r="B57" s="85"/>
+      <c r="C57" s="85"/>
+      <c r="D57" s="85"/>
+      <c r="E57" s="85"/>
+      <c r="F57" s="85"/>
+      <c r="G57" s="85"/>
+      <c r="H57" s="85"/>
+      <c r="I57" s="85"/>
+      <c r="J57" s="85"/>
+      <c r="K57" s="85"/>
+      <c r="L57" s="85"/>
+      <c r="M57" s="85"/>
+      <c r="N57" s="85"/>
+      <c r="O57" s="85"/>
+      <c r="P57" s="85"/>
+      <c r="Q57" s="85"/>
+    </row>
+    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A58" s="85"/>
+      <c r="B58" s="85"/>
+      <c r="C58" s="85"/>
+      <c r="D58" s="85"/>
+      <c r="E58" s="85"/>
+      <c r="F58" s="85"/>
+      <c r="G58" s="85"/>
+      <c r="H58" s="85"/>
+      <c r="I58" s="85"/>
+      <c r="J58" s="85"/>
+      <c r="K58" s="85"/>
+      <c r="L58" s="85"/>
+      <c r="M58" s="85"/>
+      <c r="N58" s="85"/>
+      <c r="O58" s="85"/>
+      <c r="P58" s="85"/>
+      <c r="Q58" s="85"/>
+    </row>
+    <row r="59" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="B59" s="85" t="s">
+      <c r="B59" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="C59" s="86"/>
-      <c r="D59" s="86"/>
-      <c r="E59" s="85" t="s">
+      <c r="C59" s="85"/>
+      <c r="D59" s="85"/>
+      <c r="E59" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="F59" s="86"/>
-      <c r="G59" s="86"/>
-      <c r="H59" s="85" t="s">
+      <c r="F59" s="85"/>
+      <c r="G59" s="85"/>
+      <c r="H59" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="I59" s="86"/>
-      <c r="J59" s="86"/>
-      <c r="K59" s="85" t="s">
+      <c r="I59" s="85"/>
+      <c r="J59" s="85"/>
+      <c r="K59" s="84" t="s">
         <v>24</v>
       </c>
-      <c r="L59" s="86"/>
-      <c r="M59" s="86"/>
-      <c r="N59" s="86"/>
-      <c r="O59" s="86"/>
-      <c r="P59" s="85" t="s">
+      <c r="L59" s="85"/>
+      <c r="M59" s="85"/>
+      <c r="N59" s="85"/>
+      <c r="O59" s="85"/>
+      <c r="P59" s="84" t="s">
         <v>25</v>
       </c>
-      <c r="Q59" s="85" t="s">
+      <c r="Q59" s="84" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="60" spans="1:17">
-      <c r="A60" s="86"/>
+    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A60" s="85"/>
       <c r="B60" s="43" t="s">
         <v>27</v>
       </c>
@@ -18551,10 +18601,10 @@
       <c r="O60" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P60" s="86"/>
-      <c r="Q60" s="86"/>
-    </row>
-    <row r="61" spans="1:17" ht="57.6" customHeight="1">
+      <c r="P60" s="85"/>
+      <c r="Q60" s="85"/>
+    </row>
+    <row r="61" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="43" t="s">
         <v>54</v>
       </c>
@@ -18587,7 +18637,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="72" customHeight="1">
+    <row r="62" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="43" t="s">
         <v>55</v>
       </c>
@@ -18620,7 +18670,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:17" ht="28.95" customHeight="1">
+    <row r="63" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="43" t="s">
         <v>56</v>
       </c>
@@ -18653,7 +18703,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="115.2" customHeight="1">
+    <row r="64" spans="1:17" ht="115.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="43" t="s">
         <v>57</v>
       </c>
@@ -18686,7 +18736,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:17" ht="43.2" customHeight="1">
+    <row r="65" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="43" t="s">
         <v>58</v>
       </c>
@@ -18719,7 +18769,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:17" ht="57.6" customHeight="1">
+    <row r="66" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="43" t="s">
         <v>59</v>
       </c>
@@ -18752,7 +18802,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:17" ht="72" customHeight="1">
+    <row r="67" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="43" t="s">
         <v>60</v>
       </c>
@@ -18785,7 +18835,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:17" ht="57.6" customHeight="1">
+    <row r="68" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="43" t="s">
         <v>61</v>
       </c>
@@ -18818,7 +18868,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:17" ht="57.6" customHeight="1">
+    <row r="69" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="43" t="s">
         <v>62</v>
       </c>
@@ -18851,7 +18901,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:17" ht="86.4" customHeight="1">
+    <row r="70" spans="1:17" ht="86.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="43" t="s">
         <v>63</v>
       </c>
@@ -18884,7 +18934,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:17" ht="57.6" customHeight="1">
+    <row r="71" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="43" t="s">
         <v>64</v>
       </c>
@@ -18917,7 +18967,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:17" ht="72" customHeight="1">
+    <row r="72" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="43" t="s">
         <v>65</v>
       </c>
@@ -18950,7 +19000,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:17" ht="57.6" customHeight="1">
+    <row r="73" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="43" t="s">
         <v>66</v>
       </c>
@@ -18983,7 +19033,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="43.2" customHeight="1">
+    <row r="74" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="46" t="s">
         <v>53</v>
       </c>
@@ -19026,81 +19076,81 @@
         <v>13</v>
       </c>
     </row>
-    <row r="75" spans="1:17">
-      <c r="A75" s="87" t="s">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A75" s="86" t="s">
         <v>67</v>
       </c>
-      <c r="B75" s="86"/>
-      <c r="C75" s="86"/>
-      <c r="D75" s="86"/>
-      <c r="E75" s="86"/>
-      <c r="F75" s="86"/>
-      <c r="G75" s="86"/>
-      <c r="H75" s="86"/>
-      <c r="I75" s="86"/>
-      <c r="J75" s="86"/>
-      <c r="K75" s="86"/>
-      <c r="L75" s="86"/>
-      <c r="M75" s="86"/>
-      <c r="N75" s="86"/>
-      <c r="O75" s="86"/>
-      <c r="P75" s="86"/>
-      <c r="Q75" s="86"/>
-    </row>
-    <row r="76" spans="1:17">
-      <c r="A76" s="86"/>
-      <c r="B76" s="86"/>
-      <c r="C76" s="86"/>
-      <c r="D76" s="86"/>
-      <c r="E76" s="86"/>
-      <c r="F76" s="86"/>
-      <c r="G76" s="86"/>
-      <c r="H76" s="86"/>
-      <c r="I76" s="86"/>
-      <c r="J76" s="86"/>
-      <c r="K76" s="86"/>
-      <c r="L76" s="86"/>
-      <c r="M76" s="86"/>
-      <c r="N76" s="86"/>
-      <c r="O76" s="86"/>
-      <c r="P76" s="86"/>
-      <c r="Q76" s="86"/>
-    </row>
-    <row r="77" spans="1:17" ht="14.4" customHeight="1">
-      <c r="A77" s="88" t="s">
+      <c r="B75" s="85"/>
+      <c r="C75" s="85"/>
+      <c r="D75" s="85"/>
+      <c r="E75" s="85"/>
+      <c r="F75" s="85"/>
+      <c r="G75" s="85"/>
+      <c r="H75" s="85"/>
+      <c r="I75" s="85"/>
+      <c r="J75" s="85"/>
+      <c r="K75" s="85"/>
+      <c r="L75" s="85"/>
+      <c r="M75" s="85"/>
+      <c r="N75" s="85"/>
+      <c r="O75" s="85"/>
+      <c r="P75" s="85"/>
+      <c r="Q75" s="85"/>
+    </row>
+    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A76" s="85"/>
+      <c r="B76" s="85"/>
+      <c r="C76" s="85"/>
+      <c r="D76" s="85"/>
+      <c r="E76" s="85"/>
+      <c r="F76" s="85"/>
+      <c r="G76" s="85"/>
+      <c r="H76" s="85"/>
+      <c r="I76" s="85"/>
+      <c r="J76" s="85"/>
+      <c r="K76" s="85"/>
+      <c r="L76" s="85"/>
+      <c r="M76" s="85"/>
+      <c r="N76" s="85"/>
+      <c r="O76" s="85"/>
+      <c r="P76" s="85"/>
+      <c r="Q76" s="85"/>
+    </row>
+    <row r="77" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="B77" s="85" t="s">
+      <c r="B77" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="C77" s="86"/>
-      <c r="D77" s="86"/>
-      <c r="E77" s="85" t="s">
+      <c r="C77" s="85"/>
+      <c r="D77" s="85"/>
+      <c r="E77" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="F77" s="86"/>
-      <c r="G77" s="86"/>
-      <c r="H77" s="85" t="s">
+      <c r="F77" s="85"/>
+      <c r="G77" s="85"/>
+      <c r="H77" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="I77" s="86"/>
-      <c r="J77" s="86"/>
-      <c r="K77" s="85" t="s">
+      <c r="I77" s="85"/>
+      <c r="J77" s="85"/>
+      <c r="K77" s="84" t="s">
         <v>24</v>
       </c>
-      <c r="L77" s="86"/>
-      <c r="M77" s="86"/>
-      <c r="N77" s="86"/>
-      <c r="O77" s="86"/>
-      <c r="P77" s="85" t="s">
+      <c r="L77" s="85"/>
+      <c r="M77" s="85"/>
+      <c r="N77" s="85"/>
+      <c r="O77" s="85"/>
+      <c r="P77" s="84" t="s">
         <v>25</v>
       </c>
-      <c r="Q77" s="85" t="s">
+      <c r="Q77" s="84" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="78" spans="1:17">
-      <c r="A78" s="86"/>
+    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A78" s="85"/>
       <c r="B78" s="43" t="s">
         <v>27</v>
       </c>
@@ -19143,10 +19193,10 @@
       <c r="O78" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P78" s="86"/>
-      <c r="Q78" s="86"/>
-    </row>
-    <row r="79" spans="1:17" ht="28.95" customHeight="1">
+      <c r="P78" s="85"/>
+      <c r="Q78" s="85"/>
+    </row>
+    <row r="79" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="43" t="s">
         <v>68</v>
       </c>
@@ -19197,81 +19247,81 @@
         <v>2</v>
       </c>
     </row>
-    <row r="80" spans="1:17">
-      <c r="A80" s="87" t="s">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A80" s="86" t="s">
         <v>69</v>
       </c>
-      <c r="B80" s="86"/>
-      <c r="C80" s="86"/>
-      <c r="D80" s="86"/>
-      <c r="E80" s="86"/>
-      <c r="F80" s="86"/>
-      <c r="G80" s="86"/>
-      <c r="H80" s="86"/>
-      <c r="I80" s="86"/>
-      <c r="J80" s="86"/>
-      <c r="K80" s="86"/>
-      <c r="L80" s="86"/>
-      <c r="M80" s="86"/>
-      <c r="N80" s="86"/>
-      <c r="O80" s="86"/>
-      <c r="P80" s="86"/>
-      <c r="Q80" s="86"/>
-    </row>
-    <row r="81" spans="1:17">
-      <c r="A81" s="86"/>
-      <c r="B81" s="86"/>
-      <c r="C81" s="86"/>
-      <c r="D81" s="86"/>
-      <c r="E81" s="86"/>
-      <c r="F81" s="86"/>
-      <c r="G81" s="86"/>
-      <c r="H81" s="86"/>
-      <c r="I81" s="86"/>
-      <c r="J81" s="86"/>
-      <c r="K81" s="86"/>
-      <c r="L81" s="86"/>
-      <c r="M81" s="86"/>
-      <c r="N81" s="86"/>
-      <c r="O81" s="86"/>
-      <c r="P81" s="86"/>
-      <c r="Q81" s="86"/>
-    </row>
-    <row r="82" spans="1:17" ht="14.4" customHeight="1">
-      <c r="A82" s="88" t="s">
+      <c r="B80" s="85"/>
+      <c r="C80" s="85"/>
+      <c r="D80" s="85"/>
+      <c r="E80" s="85"/>
+      <c r="F80" s="85"/>
+      <c r="G80" s="85"/>
+      <c r="H80" s="85"/>
+      <c r="I80" s="85"/>
+      <c r="J80" s="85"/>
+      <c r="K80" s="85"/>
+      <c r="L80" s="85"/>
+      <c r="M80" s="85"/>
+      <c r="N80" s="85"/>
+      <c r="O80" s="85"/>
+      <c r="P80" s="85"/>
+      <c r="Q80" s="85"/>
+    </row>
+    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A81" s="85"/>
+      <c r="B81" s="85"/>
+      <c r="C81" s="85"/>
+      <c r="D81" s="85"/>
+      <c r="E81" s="85"/>
+      <c r="F81" s="85"/>
+      <c r="G81" s="85"/>
+      <c r="H81" s="85"/>
+      <c r="I81" s="85"/>
+      <c r="J81" s="85"/>
+      <c r="K81" s="85"/>
+      <c r="L81" s="85"/>
+      <c r="M81" s="85"/>
+      <c r="N81" s="85"/>
+      <c r="O81" s="85"/>
+      <c r="P81" s="85"/>
+      <c r="Q81" s="85"/>
+    </row>
+    <row r="82" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="B82" s="85" t="s">
+      <c r="B82" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="C82" s="86"/>
-      <c r="D82" s="86"/>
-      <c r="E82" s="85" t="s">
+      <c r="C82" s="85"/>
+      <c r="D82" s="85"/>
+      <c r="E82" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="F82" s="86"/>
-      <c r="G82" s="86"/>
-      <c r="H82" s="85" t="s">
+      <c r="F82" s="85"/>
+      <c r="G82" s="85"/>
+      <c r="H82" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="I82" s="86"/>
-      <c r="J82" s="86"/>
-      <c r="K82" s="85" t="s">
+      <c r="I82" s="85"/>
+      <c r="J82" s="85"/>
+      <c r="K82" s="84" t="s">
         <v>24</v>
       </c>
-      <c r="L82" s="86"/>
-      <c r="M82" s="86"/>
-      <c r="N82" s="86"/>
-      <c r="O82" s="86"/>
-      <c r="P82" s="85" t="s">
+      <c r="L82" s="85"/>
+      <c r="M82" s="85"/>
+      <c r="N82" s="85"/>
+      <c r="O82" s="85"/>
+      <c r="P82" s="84" t="s">
         <v>25</v>
       </c>
-      <c r="Q82" s="85" t="s">
+      <c r="Q82" s="84" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="83" spans="1:17">
-      <c r="A83" s="86"/>
+    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A83" s="85"/>
       <c r="B83" s="43" t="s">
         <v>27</v>
       </c>
@@ -19314,10 +19364,10 @@
       <c r="O83" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P83" s="86"/>
-      <c r="Q83" s="86"/>
-    </row>
-    <row r="84" spans="1:17" ht="57.6" customHeight="1">
+      <c r="P83" s="85"/>
+      <c r="Q83" s="85"/>
+    </row>
+    <row r="84" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="43" t="s">
         <v>70</v>
       </c>
@@ -19350,7 +19400,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:17" ht="72" customHeight="1">
+    <row r="85" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="43" t="s">
         <v>71</v>
       </c>
@@ -19383,7 +19433,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:17" ht="57.6" customHeight="1">
+    <row r="86" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="43" t="s">
         <v>72</v>
       </c>
@@ -19416,7 +19466,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:17" ht="72" customHeight="1">
+    <row r="87" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="46" t="s">
         <v>73</v>
       </c>
@@ -19536,7 +19586,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:G78"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
@@ -19546,18 +19596,18 @@
     <col min="7" max="7" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="22.2" customHeight="1">
-      <c r="A1" s="90" t="s">
+    <row r="1" spans="1:7" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="89" t="s">
         <v>906</v>
       </c>
-      <c r="B1" s="86"/>
-      <c r="C1" s="86"/>
-      <c r="D1" s="86"/>
-      <c r="E1" s="86"/>
-      <c r="F1" s="86"/>
-      <c r="G1" s="86"/>
-    </row>
-    <row r="2" spans="1:7" ht="37.950000000000003" customHeight="1">
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="85"/>
+      <c r="G1" s="85"/>
+    </row>
+    <row r="2" spans="1:7" ht="37.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="48" t="s">
         <v>907</v>
       </c>
@@ -19580,7 +19630,7 @@
         <v>913</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="31.95" customHeight="1">
+    <row r="3" spans="1:7" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="55" t="s">
         <v>914</v>
       </c>
@@ -19603,7 +19653,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.2" customHeight="1">
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="49" t="s">
         <v>126</v>
       </c>
@@ -19624,7 +19674,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.2" customHeight="1">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="49" t="s">
         <v>37</v>
       </c>
@@ -19645,7 +19695,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.2" customHeight="1">
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="49" t="s">
         <v>122</v>
       </c>
@@ -19666,7 +19716,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.2" customHeight="1">
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="49" t="s">
         <v>212</v>
       </c>
@@ -19687,7 +19737,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.2" customHeight="1">
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="49" t="s">
         <v>700</v>
       </c>
@@ -19708,7 +19758,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.2" customHeight="1">
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="49" t="s">
         <v>104</v>
       </c>
@@ -19731,7 +19781,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.2" customHeight="1">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="49" t="s">
         <v>104</v>
       </c>
@@ -19754,7 +19804,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.2" customHeight="1">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="49" t="s">
         <v>104</v>
       </c>
@@ -19777,7 +19827,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.2" customHeight="1">
+    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="49" t="s">
         <v>99</v>
       </c>
@@ -19798,7 +19848,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.2" customHeight="1">
+    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="49" t="s">
         <v>99</v>
       </c>
@@ -19819,7 +19869,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.2" customHeight="1">
+    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="49" t="s">
         <v>283</v>
       </c>
@@ -19840,7 +19890,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.2" customHeight="1">
+    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="49" t="s">
         <v>188</v>
       </c>
@@ -19861,7 +19911,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.2" customHeight="1">
+    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="49" t="s">
         <v>112</v>
       </c>
@@ -19882,7 +19932,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.2" customHeight="1">
+    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="49" t="s">
         <v>115</v>
       </c>
@@ -19903,7 +19953,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.2" customHeight="1">
+    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="49" t="s">
         <v>345</v>
       </c>
@@ -19924,7 +19974,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.2" customHeight="1">
+    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="49" t="s">
         <v>142</v>
       </c>
@@ -19945,7 +19995,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.2" customHeight="1">
+    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="49" t="s">
         <v>258</v>
       </c>
@@ -19966,7 +20016,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.2" customHeight="1">
+    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="49" t="s">
         <v>370</v>
       </c>
@@ -19987,7 +20037,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.2" customHeight="1">
+    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="49" t="s">
         <v>794</v>
       </c>
@@ -20008,7 +20058,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.2" customHeight="1">
+    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="49" t="s">
         <v>805</v>
       </c>
@@ -20029,7 +20079,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.2" customHeight="1">
+    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="49" t="s">
         <v>810</v>
       </c>
@@ -20050,7 +20100,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.2" customHeight="1">
+    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="49" t="s">
         <v>800</v>
       </c>
@@ -20071,7 +20121,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.2" customHeight="1">
+    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="49" t="s">
         <v>815</v>
       </c>
@@ -20092,7 +20142,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="16.2" customHeight="1">
+    <row r="27" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="49" t="s">
         <v>820</v>
       </c>
@@ -20113,7 +20163,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="16.2" customHeight="1">
+    <row r="28" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="51" t="s">
         <v>126</v>
       </c>
@@ -20134,7 +20184,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="16.2" customHeight="1">
+    <row r="29" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="51" t="s">
         <v>283</v>
       </c>
@@ -20155,7 +20205,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="16.2" customHeight="1">
+    <row r="30" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="51" t="s">
         <v>188</v>
       </c>
@@ -20176,7 +20226,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="16.2" customHeight="1">
+    <row r="31" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="51" t="s">
         <v>104</v>
       </c>
@@ -20199,7 +20249,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="16.2" customHeight="1">
+    <row r="32" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="51" t="s">
         <v>104</v>
       </c>
@@ -20220,7 +20270,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="16.2" customHeight="1">
+    <row r="33" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="51" t="s">
         <v>37</v>
       </c>
@@ -20241,7 +20291,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="16.2" customHeight="1">
+    <row r="34" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="51" t="s">
         <v>232</v>
       </c>
@@ -20260,7 +20310,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="16.2" customHeight="1">
+    <row r="35" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="51" t="s">
         <v>122</v>
       </c>
@@ -20281,7 +20331,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="16.2" customHeight="1">
+    <row r="36" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="51" t="s">
         <v>212</v>
       </c>
@@ -20302,7 +20352,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="16.2" customHeight="1">
+    <row r="37" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="51" t="s">
         <v>99</v>
       </c>
@@ -20323,7 +20373,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="16.2" customHeight="1">
+    <row r="38" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="51" t="s">
         <v>99</v>
       </c>
@@ -20344,7 +20394,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="16.2" customHeight="1">
+    <row r="39" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="51" t="s">
         <v>115</v>
       </c>
@@ -20365,7 +20415,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="16.2" customHeight="1">
+    <row r="40" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="51" t="s">
         <v>112</v>
       </c>
@@ -20386,7 +20436,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="16.2" customHeight="1">
+    <row r="41" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="56" t="s">
         <v>345</v>
       </c>
@@ -20407,7 +20457,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="16.2" customHeight="1">
+    <row r="42" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="51" t="s">
         <v>142</v>
       </c>
@@ -20428,7 +20478,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="16.2" customHeight="1">
+    <row r="43" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="51" t="s">
         <v>258</v>
       </c>
@@ -20449,7 +20499,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="16.2" customHeight="1">
+    <row r="44" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="56" t="s">
         <v>370</v>
       </c>
@@ -20470,7 +20520,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="16.2" customHeight="1">
+    <row r="45" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="60" t="s">
         <v>745</v>
       </c>
@@ -20491,7 +20541,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="16.2" customHeight="1">
+    <row r="46" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="53" t="s">
         <v>232</v>
       </c>
@@ -20510,7 +20560,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="16.2" customHeight="1">
+    <row r="47" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="53" t="s">
         <v>88</v>
       </c>
@@ -20529,7 +20579,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="16.2" customHeight="1">
+    <row r="48" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="53" t="s">
         <v>88</v>
       </c>
@@ -20550,7 +20600,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="16.2" customHeight="1">
+    <row r="49" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="53" t="s">
         <v>88</v>
       </c>
@@ -20571,7 +20621,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="16.2" customHeight="1">
+    <row r="50" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="56" t="s">
         <v>740</v>
       </c>
@@ -20592,7 +20642,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="16.2" customHeight="1">
+    <row r="51" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="58" t="s">
         <v>750</v>
       </c>
@@ -20613,7 +20663,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="16.2" customHeight="1">
+    <row r="52" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="53" t="s">
         <v>706</v>
       </c>
@@ -20632,7 +20682,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="16.2" customHeight="1">
+    <row r="53" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="53" t="s">
         <v>712</v>
       </c>
@@ -20651,7 +20701,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="16.2" customHeight="1">
+    <row r="54" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="53" t="s">
         <v>718</v>
       </c>
@@ -20670,7 +20720,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="16.2" customHeight="1">
+    <row r="55" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="56" t="s">
         <v>136</v>
       </c>
@@ -20689,7 +20739,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="16.2" customHeight="1">
+    <row r="56" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="56" t="s">
         <v>136</v>
       </c>
@@ -20708,7 +20758,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="16.2" customHeight="1">
+    <row r="57" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="58" t="s">
         <v>340</v>
       </c>
@@ -20729,7 +20779,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="16.2" customHeight="1">
+    <row r="58" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="58" t="s">
         <v>340</v>
       </c>
@@ -20750,7 +20800,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="16.2" customHeight="1">
+    <row r="59" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="58" t="s">
         <v>169</v>
       </c>
@@ -20771,7 +20821,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="16.2" customHeight="1">
+    <row r="60" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="58" t="s">
         <v>91</v>
       </c>
@@ -20792,7 +20842,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="16.2" customHeight="1">
+    <row r="61" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="58" t="s">
         <v>91</v>
       </c>
@@ -20813,7 +20863,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="16.2" customHeight="1">
+    <row r="62" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="58" t="s">
         <v>194</v>
       </c>
@@ -20834,7 +20884,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="16.2" customHeight="1">
+    <row r="63" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="58" t="s">
         <v>194</v>
       </c>
@@ -20855,7 +20905,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="64" spans="1:7" ht="16.2" customHeight="1">
+    <row r="64" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="58" t="s">
         <v>145</v>
       </c>
@@ -20876,7 +20926,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="16.2" customHeight="1">
+    <row r="65" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="58" t="s">
         <v>145</v>
       </c>
@@ -20897,7 +20947,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="66" spans="1:7" ht="16.2" customHeight="1">
+    <row r="66" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="58" t="s">
         <v>85</v>
       </c>
@@ -20918,7 +20968,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="16.2" customHeight="1">
+    <row r="67" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="58" t="s">
         <v>322</v>
       </c>
@@ -20939,7 +20989,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="68" spans="1:7" ht="16.2" customHeight="1">
+    <row r="68" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="58" t="s">
         <v>322</v>
       </c>
@@ -20960,7 +21010,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="69" spans="1:7" ht="16.2" customHeight="1">
+    <row r="69" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="58" t="s">
         <v>267</v>
       </c>
@@ -20981,7 +21031,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="70" spans="1:7" ht="16.2" customHeight="1">
+    <row r="70" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="58" t="s">
         <v>267</v>
       </c>
@@ -21002,7 +21052,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="71" spans="1:7" ht="16.2" customHeight="1">
+    <row r="71" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="58" t="s">
         <v>429</v>
       </c>
@@ -21023,7 +21073,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="72" spans="1:7" ht="16.2" customHeight="1">
+    <row r="72" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="58" t="s">
         <v>459</v>
       </c>
@@ -21044,7 +21094,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="73" spans="1:7" ht="16.2" customHeight="1">
+    <row r="73" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="58" t="s">
         <v>730</v>
       </c>
@@ -21065,7 +21115,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="74" spans="1:7" ht="16.2" customHeight="1">
+    <row r="74" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="58" t="s">
         <v>735</v>
       </c>
@@ -21086,7 +21136,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="75" spans="1:7" ht="16.2" customHeight="1">
+    <row r="75" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="58" t="s">
         <v>197</v>
       </c>
@@ -21107,7 +21157,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="76" spans="1:7" ht="16.2" customHeight="1">
+    <row r="76" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="58" t="s">
         <v>197</v>
       </c>
@@ -21128,16 +21178,16 @@
         <v>928</v>
       </c>
     </row>
-    <row r="78" spans="1:7">
-      <c r="A78" s="89" t="s">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A78" s="88" t="s">
         <v>942</v>
       </c>
-      <c r="B78" s="86"/>
-      <c r="C78" s="86"/>
-      <c r="D78" s="86"/>
-      <c r="E78" s="86"/>
-      <c r="F78" s="86"/>
-      <c r="G78" s="86"/>
+      <c r="B78" s="85"/>
+      <c r="C78" s="85"/>
+      <c r="D78" s="85"/>
+      <c r="E78" s="85"/>
+      <c r="F78" s="85"/>
+      <c r="G78" s="85"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/anciens_eleves.xlsx
+++ b/anciens_eleves.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bruno\Nextcloud2\Boulot 2026\Site orientation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B31EA939-2636-470C-BE09-3F0FFF044F3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCFC08D8-B9CD-41CD-8925-5D8B5A76F089}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2482" uniqueCount="1023">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2482" uniqueCount="1022">
   <si>
     <t>Statistiques 2025</t>
   </si>
@@ -3093,9 +3093,6 @@
   </si>
   <si>
     <t>RONCERET--ARTAL</t>
-  </si>
-  <si>
-    <t>Oniris Nantes</t>
   </si>
   <si>
     <t>VIALLARD</t>
@@ -3108,7 +3105,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="30" x14ac:knownFonts="1">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3714,22 +3711,22 @@
     <xf numFmtId="0" fontId="0" fillId="13" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="24" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -4076,7 +4073,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I111"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="27.42578125" customWidth="1"/>
     <col min="2" max="2" width="14.28515625" customWidth="1"/>
@@ -4089,7 +4086,7 @@
     <col min="9" max="9" width="21.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9">
       <c r="A1" s="70" t="s">
         <v>74</v>
       </c>
@@ -4118,8 +4115,8 @@
         <v>82</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="90" t="s">
+    <row r="2" spans="1:9">
+      <c r="A2" s="84" t="s">
         <v>1019</v>
       </c>
       <c r="B2" s="64" t="str">
@@ -4136,14 +4133,14 @@
         <v>1</v>
       </c>
       <c r="F2" s="64" t="s">
-        <v>1020</v>
+        <v>115</v>
       </c>
       <c r="G2" s="64"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="90" t="s">
+    <row r="3" spans="1:9">
+      <c r="A3" s="84" t="s">
         <v>973</v>
       </c>
       <c r="B3" s="64" t="str">
@@ -4166,7 +4163,7 @@
       <c r="H3" s="77"/>
       <c r="I3" s="77"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9">
       <c r="A4" s="76" t="s">
         <v>968</v>
       </c>
@@ -4190,7 +4187,7 @@
       <c r="H4" s="77"/>
       <c r="I4" s="77"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9">
       <c r="A5" s="72" t="s">
         <v>966</v>
       </c>
@@ -4216,7 +4213,7 @@
       <c r="H5" s="64"/>
       <c r="I5" s="64"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9">
       <c r="A6" s="72" t="s">
         <v>347</v>
       </c>
@@ -4240,7 +4237,7 @@
       <c r="H6" s="64"/>
       <c r="I6" s="64"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9">
       <c r="A7" s="68" t="s">
         <v>958</v>
       </c>
@@ -4264,7 +4261,7 @@
       <c r="H7" s="74"/>
       <c r="I7" s="74"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9">
       <c r="A8" s="68" t="s">
         <v>956</v>
       </c>
@@ -4288,7 +4285,7 @@
       <c r="H8" s="64"/>
       <c r="I8" s="64"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9">
       <c r="A9" s="68" t="s">
         <v>950</v>
       </c>
@@ -4312,7 +4309,7 @@
       <c r="H9" s="64"/>
       <c r="I9" s="64"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9">
       <c r="A10" s="68" t="s">
         <v>948</v>
       </c>
@@ -4336,7 +4333,7 @@
       <c r="H10" s="64"/>
       <c r="I10" s="64"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9">
       <c r="A11" s="68" t="s">
         <v>946</v>
       </c>
@@ -4362,7 +4359,7 @@
       <c r="H11" s="64"/>
       <c r="I11" s="64"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9">
       <c r="A12" s="69" t="s">
         <v>944</v>
       </c>
@@ -4386,7 +4383,7 @@
       <c r="H12" s="64"/>
       <c r="I12" s="64"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9">
       <c r="A13" s="66" t="s">
         <v>83</v>
       </c>
@@ -4410,7 +4407,7 @@
       <c r="H13" s="67"/>
       <c r="I13" s="67"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9">
       <c r="A14" s="1" t="s">
         <v>86</v>
       </c>
@@ -4433,7 +4430,7 @@
       <c r="G14" s="1"/>
       <c r="H14" s="75"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9">
       <c r="A15" s="1" t="s">
         <v>89</v>
       </c>
@@ -4455,7 +4452,7 @@
       </c>
       <c r="G15" s="1"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9">
       <c r="A16" s="1" t="s">
         <v>92</v>
       </c>
@@ -4477,7 +4474,7 @@
       </c>
       <c r="G16" s="1"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8">
       <c r="A17" s="1" t="s">
         <v>95</v>
       </c>
@@ -4499,7 +4496,7 @@
       </c>
       <c r="G17" s="1"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8">
       <c r="A18" s="1" t="s">
         <v>97</v>
       </c>
@@ -4521,7 +4518,7 @@
       </c>
       <c r="G18" s="1"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8">
       <c r="A19" s="36" t="s">
         <v>100</v>
       </c>
@@ -4543,7 +4540,7 @@
       </c>
       <c r="G19" s="1"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8">
       <c r="A20" s="36" t="s">
         <v>102</v>
       </c>
@@ -4565,7 +4562,7 @@
       </c>
       <c r="G20" s="1"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8">
       <c r="A21" s="36" t="s">
         <v>105</v>
       </c>
@@ -4587,7 +4584,7 @@
       </c>
       <c r="G21" s="1"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8">
       <c r="A22" s="36" t="s">
         <v>108</v>
       </c>
@@ -4609,7 +4606,7 @@
       </c>
       <c r="G22" s="1"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8">
       <c r="A23" s="36" t="s">
         <v>110</v>
       </c>
@@ -4631,7 +4628,7 @@
       </c>
       <c r="G23" s="1"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8">
       <c r="A24" s="36" t="s">
         <v>113</v>
       </c>
@@ -4656,7 +4653,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8">
       <c r="A25" s="36" t="s">
         <v>117</v>
       </c>
@@ -4678,7 +4675,7 @@
       </c>
       <c r="G25" s="1"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8">
       <c r="A26" s="36" t="s">
         <v>120</v>
       </c>
@@ -4700,7 +4697,7 @@
       </c>
       <c r="G26" s="1"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8">
       <c r="A27" s="36" t="s">
         <v>123</v>
       </c>
@@ -4722,7 +4719,7 @@
       </c>
       <c r="G27" s="1"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8">
       <c r="A28" s="36" t="s">
         <v>127</v>
       </c>
@@ -4744,7 +4741,7 @@
       </c>
       <c r="G28" s="1"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8">
       <c r="A29" s="36" t="s">
         <v>130</v>
       </c>
@@ -4766,7 +4763,7 @@
       </c>
       <c r="G29" s="1"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8">
       <c r="A30" s="36" t="s">
         <v>132</v>
       </c>
@@ -4788,7 +4785,7 @@
       </c>
       <c r="G30" s="1"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8">
       <c r="A31" s="36" t="s">
         <v>134</v>
       </c>
@@ -4810,7 +4807,7 @@
       </c>
       <c r="G31" s="1"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8">
       <c r="A32" s="38" t="s">
         <v>137</v>
       </c>
@@ -4832,7 +4829,7 @@
       </c>
       <c r="G32" s="1"/>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8">
       <c r="A33" s="38" t="s">
         <v>140</v>
       </c>
@@ -4854,7 +4851,7 @@
       </c>
       <c r="G33" s="1"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8">
       <c r="A34" s="38" t="s">
         <v>143</v>
       </c>
@@ -4876,7 +4873,7 @@
       </c>
       <c r="G34" s="1"/>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8">
       <c r="A35" s="38" t="s">
         <v>146</v>
       </c>
@@ -4898,7 +4895,7 @@
       </c>
       <c r="G35" s="1"/>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8">
       <c r="A36" s="38" t="s">
         <v>148</v>
       </c>
@@ -4920,7 +4917,7 @@
       </c>
       <c r="G36" s="1"/>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8">
       <c r="A37" s="38" t="s">
         <v>150</v>
       </c>
@@ -4942,7 +4939,7 @@
       </c>
       <c r="G37" s="1"/>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8">
       <c r="A38" s="38" t="s">
         <v>151</v>
       </c>
@@ -4964,7 +4961,7 @@
       </c>
       <c r="G38" s="1"/>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8">
       <c r="A39" s="38" t="s">
         <v>153</v>
       </c>
@@ -4986,7 +4983,7 @@
       </c>
       <c r="G39" s="1"/>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8">
       <c r="A40" s="1"/>
       <c r="B40" s="1" t="str">
         <f t="shared" si="9"/>
@@ -5004,7 +5001,7 @@
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8">
       <c r="A41" s="38" t="s">
         <v>156</v>
       </c>
@@ -5026,7 +5023,7 @@
       </c>
       <c r="G41" s="1"/>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8">
       <c r="A42" s="38" t="s">
         <v>158</v>
       </c>
@@ -5048,7 +5045,7 @@
       </c>
       <c r="G42" s="1"/>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8">
       <c r="A43" s="38" t="s">
         <v>160</v>
       </c>
@@ -5073,7 +5070,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8">
       <c r="A44" s="38" t="s">
         <v>163</v>
       </c>
@@ -5095,7 +5092,7 @@
       </c>
       <c r="G44" s="1"/>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8">
       <c r="A45" s="1"/>
       <c r="B45" s="1" t="str">
         <f t="shared" si="9"/>
@@ -5115,7 +5112,7 @@
       </c>
       <c r="G45" s="1"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8">
       <c r="A46" s="38" t="s">
         <v>166</v>
       </c>
@@ -5137,7 +5134,7 @@
       </c>
       <c r="G46" s="1"/>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8">
       <c r="A47" s="38" t="s">
         <v>167</v>
       </c>
@@ -5159,7 +5156,7 @@
       </c>
       <c r="G47" s="1"/>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8">
       <c r="A48" s="38" t="s">
         <v>170</v>
       </c>
@@ -5181,7 +5178,7 @@
       </c>
       <c r="G48" s="1"/>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7">
       <c r="A49" s="38" t="s">
         <v>171</v>
       </c>
@@ -5203,7 +5200,7 @@
       </c>
       <c r="G49" s="1"/>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7">
       <c r="A50" s="38" t="s">
         <v>173</v>
       </c>
@@ -5225,7 +5222,7 @@
       </c>
       <c r="G50" s="1"/>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7">
       <c r="A51" s="38" t="s">
         <v>175</v>
       </c>
@@ -5247,7 +5244,7 @@
       </c>
       <c r="G51" s="1"/>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7">
       <c r="A52" s="38" t="s">
         <v>177</v>
       </c>
@@ -5269,7 +5266,7 @@
       </c>
       <c r="G52" s="35"/>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7">
       <c r="A53" s="38" t="s">
         <v>179</v>
       </c>
@@ -5291,7 +5288,7 @@
       </c>
       <c r="G53" s="35"/>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7">
       <c r="A54" s="38" t="s">
         <v>180</v>
       </c>
@@ -5315,7 +5312,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7">
       <c r="A55" s="1"/>
       <c r="B55" s="1" t="str">
         <f t="shared" si="9"/>
@@ -5337,7 +5334,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7">
       <c r="A56" s="1"/>
       <c r="B56" s="1" t="str">
         <f t="shared" si="9"/>
@@ -5359,7 +5356,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7">
       <c r="A57" s="1"/>
       <c r="B57" s="1" t="str">
         <f t="shared" si="9"/>
@@ -5379,7 +5376,7 @@
       </c>
       <c r="G57" s="35"/>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7">
       <c r="A58" s="38" t="s">
         <v>186</v>
       </c>
@@ -5401,7 +5398,7 @@
       </c>
       <c r="G58" s="35"/>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7">
       <c r="A59" s="38" t="s">
         <v>189</v>
       </c>
@@ -5423,7 +5420,7 @@
       </c>
       <c r="G59" s="35"/>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7">
       <c r="A60" s="38" t="s">
         <v>190</v>
       </c>
@@ -5445,7 +5442,7 @@
       </c>
       <c r="G60" s="35"/>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7">
       <c r="A61" s="38" t="s">
         <v>192</v>
       </c>
@@ -5467,7 +5464,7 @@
       </c>
       <c r="G61" s="35"/>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7">
       <c r="A62" s="38" t="s">
         <v>195</v>
       </c>
@@ -5489,7 +5486,7 @@
       </c>
       <c r="G62" s="35"/>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7">
       <c r="A63" s="38" t="s">
         <v>198</v>
       </c>
@@ -5511,7 +5508,7 @@
       </c>
       <c r="G63" s="35"/>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7">
       <c r="A64" s="38" t="s">
         <v>200</v>
       </c>
@@ -5533,7 +5530,7 @@
       </c>
       <c r="G64" s="35"/>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7">
       <c r="A65" s="38" t="s">
         <v>202</v>
       </c>
@@ -5555,7 +5552,7 @@
       </c>
       <c r="G65" s="35"/>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7">
       <c r="A66" s="38" t="s">
         <v>204</v>
       </c>
@@ -5577,7 +5574,7 @@
       </c>
       <c r="G66" s="35"/>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7">
       <c r="A67" s="38" t="s">
         <v>206</v>
       </c>
@@ -5599,7 +5596,7 @@
       </c>
       <c r="G67" s="35"/>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7">
       <c r="A68" s="38" t="s">
         <v>208</v>
       </c>
@@ -5621,7 +5618,7 @@
       </c>
       <c r="G68" s="35"/>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7">
       <c r="A69" s="38" t="s">
         <v>210</v>
       </c>
@@ -5643,7 +5640,7 @@
       </c>
       <c r="G69" s="35"/>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7">
       <c r="A70" s="38" t="s">
         <v>213</v>
       </c>
@@ -5665,7 +5662,7 @@
       </c>
       <c r="G70" s="35"/>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7">
       <c r="A71" s="38" t="s">
         <v>215</v>
       </c>
@@ -5687,7 +5684,7 @@
       </c>
       <c r="G71" s="35"/>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7">
       <c r="A72" s="38" t="s">
         <v>217</v>
       </c>
@@ -5709,7 +5706,7 @@
       </c>
       <c r="G72" s="35"/>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7">
       <c r="A73" s="38" t="s">
         <v>219</v>
       </c>
@@ -5731,7 +5728,7 @@
       </c>
       <c r="G73" s="35"/>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7">
       <c r="A74" s="38" t="s">
         <v>221</v>
       </c>
@@ -5753,7 +5750,7 @@
       </c>
       <c r="G74" s="35"/>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7">
       <c r="A75" s="38" t="s">
         <v>223</v>
       </c>
@@ -5777,7 +5774,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7">
       <c r="A76" s="38" t="s">
         <v>225</v>
       </c>
@@ -5799,7 +5796,7 @@
       </c>
       <c r="G76" s="29"/>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7">
       <c r="A77" s="38" t="s">
         <v>226</v>
       </c>
@@ -5823,7 +5820,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7">
       <c r="A78" s="38" t="s">
         <v>228</v>
       </c>
@@ -5845,7 +5842,7 @@
       </c>
       <c r="G78" s="35"/>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7">
       <c r="A79" s="38" t="s">
         <v>230</v>
       </c>
@@ -5867,7 +5864,7 @@
       </c>
       <c r="G79" s="35"/>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7">
       <c r="A80" s="38" t="s">
         <v>233</v>
       </c>
@@ -5889,7 +5886,7 @@
       </c>
       <c r="G80" s="35"/>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7">
       <c r="A81" s="35" t="s">
         <v>235</v>
       </c>
@@ -5911,7 +5908,7 @@
       </c>
       <c r="G81" s="1"/>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7">
       <c r="A82" s="35" t="s">
         <v>237</v>
       </c>
@@ -5933,7 +5930,7 @@
       </c>
       <c r="G82" s="1"/>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:7">
       <c r="A83" s="35" t="s">
         <v>239</v>
       </c>
@@ -5955,7 +5952,7 @@
       </c>
       <c r="G83" s="1"/>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7">
       <c r="A84" s="35" t="s">
         <v>242</v>
       </c>
@@ -5977,7 +5974,7 @@
       </c>
       <c r="G84" s="1"/>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7">
       <c r="A85" s="35" t="s">
         <v>244</v>
       </c>
@@ -5999,7 +5996,7 @@
       </c>
       <c r="G85" s="1"/>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:7">
       <c r="A86" s="35" t="s">
         <v>245</v>
       </c>
@@ -6021,7 +6018,7 @@
       </c>
       <c r="G86" s="1"/>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7">
       <c r="A87" s="35" t="s">
         <v>247</v>
       </c>
@@ -6043,7 +6040,7 @@
       </c>
       <c r="G87" s="1"/>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7">
       <c r="A88" s="35" t="s">
         <v>249</v>
       </c>
@@ -6065,7 +6062,7 @@
       </c>
       <c r="G88" s="1"/>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:7">
       <c r="A89" s="35" t="s">
         <v>251</v>
       </c>
@@ -6087,7 +6084,7 @@
       </c>
       <c r="G89" s="1"/>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:7">
       <c r="A90" s="35" t="s">
         <v>254</v>
       </c>
@@ -6109,7 +6106,7 @@
       </c>
       <c r="G90" s="1"/>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7">
       <c r="A91" s="35" t="s">
         <v>256</v>
       </c>
@@ -6131,7 +6128,7 @@
       </c>
       <c r="G91" s="1"/>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:7">
       <c r="A92" s="35" t="s">
         <v>259</v>
       </c>
@@ -6153,7 +6150,7 @@
       </c>
       <c r="G92" s="1"/>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:7">
       <c r="A93" s="35" t="s">
         <v>261</v>
       </c>
@@ -6175,7 +6172,7 @@
       </c>
       <c r="G93" s="1"/>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7">
       <c r="A94" s="35" t="s">
         <v>263</v>
       </c>
@@ -6197,7 +6194,7 @@
       </c>
       <c r="G94" s="1"/>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:7">
       <c r="A95" s="35" t="s">
         <v>265</v>
       </c>
@@ -6219,7 +6216,7 @@
       </c>
       <c r="G95" s="1"/>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:7">
       <c r="A96" s="35" t="s">
         <v>268</v>
       </c>
@@ -6241,7 +6238,7 @@
       </c>
       <c r="G96" s="1"/>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7">
       <c r="A97" s="35" t="s">
         <v>270</v>
       </c>
@@ -6263,7 +6260,7 @@
       </c>
       <c r="G97" s="1"/>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7">
       <c r="A98" s="35" t="s">
         <v>271</v>
       </c>
@@ -6284,7 +6281,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:7">
       <c r="A99" s="35" t="s">
         <v>273</v>
       </c>
@@ -6305,16 +6302,16 @@
         <v>37</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7">
       <c r="A100" s="35" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B100" s="1" t="str">
         <f t="shared" si="11"/>
         <v>V</v>
       </c>
       <c r="C100" s="35" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="D100" s="29">
         <v>2018</v>
@@ -6326,7 +6323,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7">
       <c r="A101" s="35"/>
       <c r="B101" s="1" t="str">
         <f t="shared" si="11"/>
@@ -6336,7 +6333,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7">
       <c r="A102" s="35"/>
       <c r="B102" s="1" t="str">
         <f t="shared" si="11"/>
@@ -6346,7 +6343,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7">
       <c r="A103" s="35"/>
       <c r="B103" s="1" t="str">
         <f t="shared" si="11"/>
@@ -6356,7 +6353,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7">
       <c r="A104" s="35"/>
       <c r="B104" s="1" t="str">
         <f t="shared" si="11"/>
@@ -6366,7 +6363,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7">
       <c r="A105" s="35"/>
       <c r="B105" s="1" t="str">
         <f t="shared" si="11"/>
@@ -6376,7 +6373,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7">
       <c r="A106" s="35"/>
       <c r="B106" s="1" t="str">
         <f t="shared" si="11"/>
@@ -6386,7 +6383,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7">
       <c r="A107" s="35"/>
       <c r="B107" s="1" t="str">
         <f t="shared" si="11"/>
@@ -6396,7 +6393,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7">
       <c r="A108" s="35"/>
       <c r="B108" s="1" t="str">
         <f t="shared" si="11"/>
@@ -6406,7 +6403,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:7">
       <c r="A109" s="35"/>
       <c r="B109" s="1" t="str">
         <f t="shared" si="11"/>
@@ -6416,7 +6413,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7">
       <c r="B110" s="1" t="str">
         <f t="shared" si="11"/>
         <v/>
@@ -6425,7 +6422,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:7">
       <c r="B111" s="1" t="str">
         <f t="shared" si="11"/>
         <v/>
@@ -6458,7 +6455,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:N127"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19.28515625" customWidth="1"/>
     <col min="2" max="2" width="16.5703125" customWidth="1"/>
@@ -6467,7 +6464,7 @@
     <col min="9" max="9" width="96.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>275</v>
       </c>
@@ -6493,7 +6490,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
         <v>1007</v>
       </c>
@@ -6516,7 +6513,7 @@
       <c r="H2" s="83"/>
       <c r="I2" s="83"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14">
       <c r="A3" s="1" t="s">
         <v>1005</v>
       </c>
@@ -6539,7 +6536,7 @@
       <c r="H3" s="83"/>
       <c r="I3" s="83"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14">
       <c r="A4" s="1" t="s">
         <v>1003</v>
       </c>
@@ -6562,7 +6559,7 @@
       <c r="H4" s="83"/>
       <c r="I4" s="83"/>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14">
       <c r="A5" s="1" t="s">
         <v>1002</v>
       </c>
@@ -6585,7 +6582,7 @@
       <c r="H5" s="83"/>
       <c r="I5" s="83"/>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14">
       <c r="A6" s="1" t="s">
         <v>1001</v>
       </c>
@@ -6608,7 +6605,7 @@
       <c r="H6" s="83"/>
       <c r="I6" s="83"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14">
       <c r="A7" s="1" t="s">
         <v>974</v>
       </c>
@@ -6631,7 +6628,7 @@
       <c r="H7" s="83"/>
       <c r="I7" s="83"/>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14">
       <c r="A8" s="1" t="s">
         <v>971</v>
       </c>
@@ -6654,7 +6651,7 @@
       <c r="H8" s="83"/>
       <c r="I8" s="83"/>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14">
       <c r="A9" s="1" t="s">
         <v>970</v>
       </c>
@@ -6677,7 +6674,7 @@
       <c r="H9" s="83"/>
       <c r="I9" s="83"/>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14">
       <c r="A10" s="1" t="s">
         <v>959</v>
       </c>
@@ -6700,7 +6697,7 @@
       <c r="H10" s="74"/>
       <c r="I10" s="74"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14">
       <c r="A11" s="1" t="s">
         <v>276</v>
       </c>
@@ -6723,7 +6720,7 @@
       <c r="H11" s="64"/>
       <c r="I11" s="64"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14">
       <c r="A12" s="1" t="s">
         <v>278</v>
       </c>
@@ -6746,7 +6743,7 @@
       <c r="H12" s="64"/>
       <c r="I12" s="64"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14">
       <c r="A13" s="1" t="s">
         <v>280</v>
       </c>
@@ -6767,7 +6764,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14">
       <c r="A14" s="1" t="s">
         <v>281</v>
       </c>
@@ -6788,7 +6785,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14">
       <c r="A15" s="1" t="s">
         <v>284</v>
       </c>
@@ -6815,7 +6812,7 @@
       <c r="M15" s="64"/>
       <c r="N15" s="1"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14">
       <c r="A16" s="1" t="s">
         <v>286</v>
       </c>
@@ -6836,7 +6833,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6">
       <c r="A17" s="1" t="s">
         <v>288</v>
       </c>
@@ -6857,7 +6854,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6">
       <c r="A18" s="1" t="s">
         <v>290</v>
       </c>
@@ -6878,7 +6875,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6">
       <c r="A19" s="1" t="s">
         <v>292</v>
       </c>
@@ -6899,7 +6896,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6">
       <c r="A20" s="1" t="s">
         <v>294</v>
       </c>
@@ -6920,7 +6917,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6">
       <c r="A21" s="1" t="s">
         <v>105</v>
       </c>
@@ -6941,7 +6938,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6">
       <c r="A22" s="1" t="s">
         <v>297</v>
       </c>
@@ -6962,7 +6959,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6">
       <c r="A23" s="1" t="s">
         <v>299</v>
       </c>
@@ -6983,7 +6980,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6">
       <c r="A24" s="1" t="s">
         <v>301</v>
       </c>
@@ -7004,7 +7001,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6">
       <c r="A25" s="1" t="s">
         <v>303</v>
       </c>
@@ -7025,7 +7022,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6">
       <c r="A26" s="1" t="s">
         <v>305</v>
       </c>
@@ -7046,7 +7043,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6">
       <c r="A27" s="1" t="s">
         <v>307</v>
       </c>
@@ -7067,7 +7064,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6">
       <c r="A28" s="1" t="s">
         <v>309</v>
       </c>
@@ -7088,7 +7085,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6">
       <c r="A29" s="1" t="s">
         <v>311</v>
       </c>
@@ -7109,7 +7106,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6">
       <c r="A30" t="s">
         <v>313</v>
       </c>
@@ -7130,7 +7127,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6">
       <c r="A31" s="7" t="s">
         <v>315</v>
       </c>
@@ -7151,7 +7148,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6">
       <c r="A32" s="1" t="s">
         <v>316</v>
       </c>
@@ -7172,7 +7169,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8">
       <c r="A33" s="1" t="s">
         <v>318</v>
       </c>
@@ -7193,7 +7190,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8">
       <c r="A34" t="s">
         <v>320</v>
       </c>
@@ -7214,7 +7211,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8">
       <c r="A35" s="1" t="s">
         <v>321</v>
       </c>
@@ -7235,7 +7232,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8">
       <c r="A36" t="s">
         <v>323</v>
       </c>
@@ -7256,7 +7253,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8">
       <c r="A37" s="7" t="s">
         <v>325</v>
       </c>
@@ -7280,7 +7277,7 @@
         <v>1015</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8">
       <c r="A38" s="7" t="s">
         <v>327</v>
       </c>
@@ -7301,7 +7298,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8">
       <c r="A39" s="7" t="s">
         <v>329</v>
       </c>
@@ -7322,7 +7319,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8">
       <c r="A40" s="7" t="s">
         <v>331</v>
       </c>
@@ -7343,7 +7340,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8">
       <c r="A41" s="7" t="s">
         <v>332</v>
       </c>
@@ -7364,7 +7361,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8">
       <c r="A42" s="7" t="s">
         <v>335</v>
       </c>
@@ -7385,7 +7382,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8">
       <c r="A43" s="7" t="s">
         <v>337</v>
       </c>
@@ -7406,7 +7403,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8">
       <c r="A44" s="7" t="s">
         <v>339</v>
       </c>
@@ -7427,7 +7424,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8">
       <c r="A45" s="7" t="s">
         <v>341</v>
       </c>
@@ -7448,7 +7445,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8">
       <c r="A46" s="7" t="s">
         <v>343</v>
       </c>
@@ -7469,7 +7466,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8">
       <c r="A47" s="7" t="s">
         <v>346</v>
       </c>
@@ -7490,7 +7487,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8">
       <c r="A48" s="7" t="s">
         <v>348</v>
       </c>
@@ -7511,7 +7508,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9">
       <c r="A49" s="7" t="s">
         <v>350</v>
       </c>
@@ -7532,7 +7529,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9">
       <c r="A50" t="s">
         <v>351</v>
       </c>
@@ -7553,7 +7550,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9">
       <c r="A51" s="7" t="s">
         <v>354</v>
       </c>
@@ -7574,7 +7571,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9">
       <c r="A52" s="7" t="s">
         <v>356</v>
       </c>
@@ -7595,7 +7592,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9">
       <c r="A53" s="7" t="s">
         <v>357</v>
       </c>
@@ -7616,7 +7613,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9">
       <c r="A54" s="7" t="s">
         <v>359</v>
       </c>
@@ -7640,7 +7637,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9">
       <c r="A55" s="7" t="s">
         <v>360</v>
       </c>
@@ -7661,7 +7658,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9">
       <c r="A56" s="7" t="s">
         <v>362</v>
       </c>
@@ -7688,7 +7685,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9">
       <c r="A57" s="7" t="s">
         <v>365</v>
       </c>
@@ -7709,7 +7706,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9">
       <c r="A58" s="7" t="s">
         <v>288</v>
       </c>
@@ -7730,7 +7727,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9">
       <c r="A59" s="7" t="s">
         <v>367</v>
       </c>
@@ -7751,7 +7748,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9">
       <c r="A60" s="7" t="s">
         <v>368</v>
       </c>
@@ -7772,7 +7769,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9">
       <c r="A61" s="7" t="s">
         <v>371</v>
       </c>
@@ -7793,7 +7790,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9">
       <c r="A62" s="7" t="s">
         <v>373</v>
       </c>
@@ -7814,7 +7811,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9">
       <c r="A63" s="7" t="s">
         <v>375</v>
       </c>
@@ -7838,7 +7835,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9">
       <c r="A64" s="7" t="s">
         <v>377</v>
       </c>
@@ -7859,7 +7856,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9">
       <c r="A65" t="s">
         <v>378</v>
       </c>
@@ -7880,7 +7877,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9">
       <c r="A66" s="7" t="s">
         <v>380</v>
       </c>
@@ -7901,7 +7898,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9">
       <c r="A67" s="7" t="s">
         <v>382</v>
       </c>
@@ -7922,7 +7919,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9">
       <c r="A68" s="7" t="s">
         <v>383</v>
       </c>
@@ -7949,7 +7946,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9">
       <c r="A69" t="s">
         <v>385</v>
       </c>
@@ -7970,7 +7967,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9">
       <c r="A70" t="s">
         <v>387</v>
       </c>
@@ -7991,7 +7988,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9">
       <c r="A71" t="s">
         <v>389</v>
       </c>
@@ -8012,7 +8009,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9">
       <c r="A72" t="s">
         <v>391</v>
       </c>
@@ -8033,7 +8030,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9">
       <c r="A73" t="s">
         <v>393</v>
       </c>
@@ -8054,7 +8051,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9">
       <c r="A74" t="s">
         <v>394</v>
       </c>
@@ -8075,7 +8072,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9">
       <c r="A75" t="s">
         <v>396</v>
       </c>
@@ -8096,7 +8093,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9">
       <c r="A76" t="s">
         <v>397</v>
       </c>
@@ -8117,7 +8114,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9">
       <c r="A77" t="s">
         <v>399</v>
       </c>
@@ -8138,7 +8135,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9">
       <c r="A78" t="s">
         <v>400</v>
       </c>
@@ -8159,7 +8156,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9">
       <c r="A79" t="s">
         <v>402</v>
       </c>
@@ -8180,7 +8177,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9">
       <c r="A80" t="s">
         <v>403</v>
       </c>
@@ -8201,7 +8198,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6">
       <c r="A81" t="s">
         <v>405</v>
       </c>
@@ -8222,7 +8219,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6">
       <c r="A82" t="s">
         <v>408</v>
       </c>
@@ -8243,7 +8240,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6">
       <c r="A83" t="s">
         <v>409</v>
       </c>
@@ -8264,7 +8261,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6">
       <c r="A84" t="s">
         <v>410</v>
       </c>
@@ -8285,7 +8282,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6">
       <c r="A85" t="s">
         <v>412</v>
       </c>
@@ -8306,7 +8303,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6">
       <c r="A86" t="s">
         <v>414</v>
       </c>
@@ -8327,7 +8324,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6">
       <c r="A87" t="s">
         <v>415</v>
       </c>
@@ -8348,7 +8345,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6">
       <c r="A88" t="s">
         <v>417</v>
       </c>
@@ -8369,7 +8366,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6">
       <c r="A89" t="s">
         <v>418</v>
       </c>
@@ -8390,7 +8387,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6">
       <c r="A90" t="s">
         <v>420</v>
       </c>
@@ -8411,7 +8408,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6">
       <c r="A91" t="s">
         <v>422</v>
       </c>
@@ -8432,7 +8429,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6">
       <c r="A92" t="s">
         <v>424</v>
       </c>
@@ -8453,7 +8450,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6">
       <c r="A93" t="s">
         <v>425</v>
       </c>
@@ -8474,7 +8471,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6">
       <c r="A94" t="s">
         <v>427</v>
       </c>
@@ -8495,7 +8492,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6">
       <c r="A95" t="s">
         <v>430</v>
       </c>
@@ -8516,7 +8513,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6">
       <c r="A96" t="s">
         <v>432</v>
       </c>
@@ -8537,7 +8534,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6">
       <c r="A97" t="s">
         <v>433</v>
       </c>
@@ -8558,7 +8555,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6">
       <c r="A98" t="s">
         <v>435</v>
       </c>
@@ -8579,7 +8576,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6">
       <c r="A99" t="s">
         <v>436</v>
       </c>
@@ -8600,7 +8597,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6">
       <c r="A100" t="s">
         <v>437</v>
       </c>
@@ -8621,7 +8618,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6">
       <c r="A101" t="s">
         <v>438</v>
       </c>
@@ -8642,7 +8639,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6">
       <c r="A102" t="s">
         <v>440</v>
       </c>
@@ -8663,7 +8660,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6">
       <c r="A103" t="s">
         <v>441</v>
       </c>
@@ -8684,7 +8681,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6">
       <c r="A104" t="s">
         <v>443</v>
       </c>
@@ -8705,7 +8702,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6">
       <c r="A105" t="s">
         <v>446</v>
       </c>
@@ -8726,7 +8723,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6">
       <c r="A106" t="s">
         <v>449</v>
       </c>
@@ -8747,7 +8744,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6">
       <c r="A107" t="s">
         <v>451</v>
       </c>
@@ -8768,7 +8765,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6">
       <c r="A108" s="9" t="s">
         <v>453</v>
       </c>
@@ -8788,7 +8785,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6">
       <c r="A109" s="9" t="s">
         <v>456</v>
       </c>
@@ -8809,7 +8806,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6">
       <c r="A110" s="9" t="s">
         <v>457</v>
       </c>
@@ -8830,7 +8827,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6">
       <c r="A111" s="9" t="s">
         <v>460</v>
       </c>
@@ -8851,7 +8848,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:6">
       <c r="A112" s="9" t="s">
         <v>462</v>
       </c>
@@ -8872,7 +8869,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:8">
       <c r="A113" s="9" t="s">
         <v>464</v>
       </c>
@@ -8893,7 +8890,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:8">
       <c r="A114" s="9" t="s">
         <v>465</v>
       </c>
@@ -8914,7 +8911,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:8">
       <c r="A115" s="9" t="s">
         <v>467</v>
       </c>
@@ -8935,7 +8932,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:8">
       <c r="A116" s="9" t="s">
         <v>469</v>
       </c>
@@ -8959,7 +8956,7 @@
         <v>1018</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:8">
       <c r="A117" s="9" t="s">
         <v>471</v>
       </c>
@@ -8983,7 +8980,7 @@
         <v>1018</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:8">
       <c r="A118" s="9" t="s">
         <v>473</v>
       </c>
@@ -9004,7 +9001,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:8">
       <c r="A119" s="9" t="s">
         <v>475</v>
       </c>
@@ -9025,7 +9022,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:8">
       <c r="A120" s="9" t="s">
         <v>476</v>
       </c>
@@ -9046,7 +9043,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:8">
       <c r="A121" s="9" t="s">
         <v>478</v>
       </c>
@@ -9067,7 +9064,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:8">
       <c r="A122" s="9" t="s">
         <v>480</v>
       </c>
@@ -9088,7 +9085,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:8">
       <c r="A123" s="9" t="s">
         <v>482</v>
       </c>
@@ -9109,7 +9106,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:8">
       <c r="A124" s="9" t="s">
         <v>483</v>
       </c>
@@ -9130,7 +9127,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:8">
       <c r="A125" t="s">
         <v>484</v>
       </c>
@@ -9151,7 +9148,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:8">
       <c r="A126" s="9" t="s">
         <v>485</v>
       </c>
@@ -9172,7 +9169,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:8">
       <c r="B127" s="1" t="str">
         <f t="shared" si="13"/>
         <v/>
@@ -9219,7 +9216,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:M73"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22.28515625" style="3" customWidth="1"/>
     <col min="2" max="6" width="11.42578125" style="3" customWidth="1"/>
@@ -9232,7 +9229,7 @@
     <col min="13" max="16384" width="11.42578125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A1" s="3" t="s">
         <v>74</v>
       </c>
@@ -9270,7 +9267,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>126</v>
       </c>
@@ -9305,7 +9302,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A3" s="3" t="s">
         <v>115</v>
       </c>
@@ -9343,7 +9340,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A4" s="3" t="s">
         <v>37</v>
       </c>
@@ -9378,7 +9375,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A5" s="3" t="s">
         <v>122</v>
       </c>
@@ -9416,7 +9413,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A6" s="3" t="s">
         <v>104</v>
       </c>
@@ -9454,7 +9451,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A7" s="3" t="s">
         <v>283</v>
       </c>
@@ -9489,7 +9486,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A8" s="3" t="s">
         <v>112</v>
       </c>
@@ -9527,7 +9524,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A9" s="3" t="s">
         <v>136</v>
       </c>
@@ -9565,7 +9562,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A10" s="3" t="s">
         <v>99</v>
       </c>
@@ -9600,7 +9597,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A11" s="3" t="s">
         <v>345</v>
       </c>
@@ -9635,7 +9632,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A12" s="3" t="s">
         <v>370</v>
       </c>
@@ -9670,7 +9667,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A13" s="3" t="s">
         <v>142</v>
       </c>
@@ -9705,7 +9702,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A14" s="3" t="s">
         <v>258</v>
       </c>
@@ -9740,7 +9737,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A15" s="3" t="s">
         <v>232</v>
       </c>
@@ -9772,7 +9769,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A16" s="3" t="s">
         <v>88</v>
       </c>
@@ -9801,7 +9798,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A17" s="3" t="s">
         <v>169</v>
       </c>
@@ -9836,7 +9833,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A18" s="3" t="s">
         <v>91</v>
       </c>
@@ -9871,7 +9868,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A19" s="3" t="s">
         <v>194</v>
       </c>
@@ -9909,7 +9906,7 @@
         <v>988</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A20" s="3" t="s">
         <v>145</v>
       </c>
@@ -9944,7 +9941,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A21" s="3" t="s">
         <v>85</v>
       </c>
@@ -9979,7 +9976,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A22" s="3" t="s">
         <v>119</v>
       </c>
@@ -10014,7 +10011,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A23" s="3" t="s">
         <v>595</v>
       </c>
@@ -10049,7 +10046,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A24" s="3" t="s">
         <v>334</v>
       </c>
@@ -10084,7 +10081,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A25" s="3" t="s">
         <v>605</v>
       </c>
@@ -10119,7 +10116,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A26" s="3" t="s">
         <v>107</v>
       </c>
@@ -10154,7 +10151,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A27" s="3" t="s">
         <v>94</v>
       </c>
@@ -10189,7 +10186,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A28" s="3" t="s">
         <v>129</v>
       </c>
@@ -10224,7 +10221,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A29" s="3" t="s">
         <v>322</v>
       </c>
@@ -10259,7 +10256,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A30" s="3" t="s">
         <v>324</v>
       </c>
@@ -10294,7 +10291,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A31" s="6" t="s">
         <v>340</v>
       </c>
@@ -10329,7 +10326,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A32" s="6" t="s">
         <v>267</v>
       </c>
@@ -10367,7 +10364,7 @@
         <v>996</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A33" s="6" t="s">
         <v>353</v>
       </c>
@@ -10402,7 +10399,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A34" s="3" t="s">
         <v>212</v>
       </c>
@@ -10437,7 +10434,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A35" s="3" t="s">
         <v>407</v>
       </c>
@@ -10472,7 +10469,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" ht="44.25" customHeight="1">
       <c r="A36" s="3" t="s">
         <v>429</v>
       </c>
@@ -10510,7 +10507,7 @@
         <v>989</v>
       </c>
     </row>
-    <row r="37" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" ht="72" customHeight="1">
       <c r="A37" s="3" t="s">
         <v>445</v>
       </c>
@@ -10545,7 +10542,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="38" spans="1:12" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" ht="29.25" customHeight="1">
       <c r="A38" s="3" t="s">
         <v>448</v>
       </c>
@@ -10580,7 +10577,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="39" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" ht="34.5" customHeight="1">
       <c r="A39" s="3" t="s">
         <v>450</v>
       </c>
@@ -10615,7 +10612,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="40" spans="1:12" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" ht="47.25" customHeight="1">
       <c r="A40" s="3" t="s">
         <v>452</v>
       </c>
@@ -10650,7 +10647,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="41" spans="1:12" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" ht="49.5" customHeight="1">
       <c r="A41" s="3" t="s">
         <v>455</v>
       </c>
@@ -10685,7 +10682,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="42" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" ht="72" customHeight="1">
       <c r="A42" s="11" t="s">
         <v>459</v>
       </c>
@@ -10723,7 +10720,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="43" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" ht="72" customHeight="1">
       <c r="A43" s="11" t="s">
         <v>477</v>
       </c>
@@ -10758,7 +10755,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="44" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" ht="72" customHeight="1">
       <c r="A44" s="11" t="s">
         <v>689</v>
       </c>
@@ -10793,7 +10790,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="45" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" ht="72" customHeight="1">
       <c r="A45" s="15" t="s">
         <v>694</v>
       </c>
@@ -10824,7 +10821,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="46" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" ht="72" customHeight="1">
       <c r="A46" s="13" t="s">
         <v>700</v>
       </c>
@@ -10859,7 +10856,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="47" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" ht="72" customHeight="1">
       <c r="A47" s="13" t="s">
         <v>706</v>
       </c>
@@ -10890,7 +10887,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="48" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" ht="72" customHeight="1">
       <c r="A48" s="13" t="s">
         <v>712</v>
       </c>
@@ -10921,7 +10918,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11" ht="72" customHeight="1">
       <c r="A49" s="13" t="s">
         <v>718</v>
       </c>
@@ -10952,7 +10949,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11" ht="51" customHeight="1">
       <c r="A50" s="13" t="s">
         <v>724</v>
       </c>
@@ -10987,7 +10984,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11" ht="72" customHeight="1">
       <c r="A51" s="13" t="s">
         <v>730</v>
       </c>
@@ -11022,7 +11019,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:11" ht="72" customHeight="1">
       <c r="A52" s="13" t="s">
         <v>735</v>
       </c>
@@ -11057,7 +11054,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:11" ht="57.6" customHeight="1">
       <c r="A53" s="13" t="s">
         <v>740</v>
       </c>
@@ -11088,7 +11085,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:11" ht="57.6" customHeight="1">
       <c r="A54" s="13" t="s">
         <v>745</v>
       </c>
@@ -11119,7 +11116,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="55" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11" ht="72" customHeight="1">
       <c r="A55" s="13" t="s">
         <v>750</v>
       </c>
@@ -11150,7 +11147,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:11" ht="72" customHeight="1">
       <c r="A56" s="13" t="s">
         <v>253</v>
       </c>
@@ -11181,7 +11178,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" ht="72" customHeight="1">
       <c r="A57" s="13" t="s">
         <v>759</v>
       </c>
@@ -11212,7 +11209,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="86.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:11" ht="86.45" customHeight="1">
       <c r="A58" s="13" t="s">
         <v>766</v>
       </c>
@@ -11243,7 +11240,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:11" ht="72" customHeight="1">
       <c r="A59" s="13" t="s">
         <v>773</v>
       </c>
@@ -11274,7 +11271,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:11" ht="72" customHeight="1">
       <c r="A60" s="13" t="s">
         <v>778</v>
       </c>
@@ -11305,7 +11302,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:11" ht="72" customHeight="1">
       <c r="A61" s="3" t="s">
         <v>783</v>
       </c>
@@ -11336,7 +11333,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:11" ht="72" customHeight="1">
       <c r="A62" s="11" t="s">
         <v>789</v>
       </c>
@@ -11367,7 +11364,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="63" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:11" ht="48" customHeight="1">
       <c r="A63" s="18" t="s">
         <v>794</v>
       </c>
@@ -11396,7 +11393,7 @@
         <v>799</v>
       </c>
     </row>
-    <row r="64" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:11" ht="42" customHeight="1">
       <c r="A64" s="19" t="s">
         <v>800</v>
       </c>
@@ -11425,7 +11422,7 @@
         <v>804</v>
       </c>
     </row>
-    <row r="65" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:13" ht="45" customHeight="1">
       <c r="A65" s="19" t="s">
         <v>805</v>
       </c>
@@ -11454,7 +11451,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="66" spans="1:13" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:13" ht="72" customHeight="1">
       <c r="A66" s="19" t="s">
         <v>810</v>
       </c>
@@ -11483,7 +11480,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="67" spans="1:13" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:13" ht="72" customHeight="1">
       <c r="A67" s="19" t="s">
         <v>815</v>
       </c>
@@ -11512,7 +11509,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="68" spans="1:13" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:13" ht="72" customHeight="1">
       <c r="A68" s="19" t="s">
         <v>820</v>
       </c>
@@ -11541,7 +11538,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="69" spans="1:13" ht="409.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:13" ht="409.6" customHeight="1">
       <c r="A69" s="31" t="s">
         <v>197</v>
       </c>
@@ -11576,7 +11573,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="70" spans="1:13" ht="409.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:13" ht="409.6" customHeight="1">
       <c r="A70" s="31" t="s">
         <v>188</v>
       </c>
@@ -11617,7 +11614,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="71" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:13" ht="105">
       <c r="A71" s="3" t="s">
         <v>952</v>
       </c>
@@ -11655,7 +11652,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="72" spans="1:13" ht="150" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:13" ht="150">
       <c r="A72" s="3" t="s">
         <v>961</v>
       </c>
@@ -11693,7 +11690,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="73" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:13" ht="75">
       <c r="A73" s="3" t="s">
         <v>1008</v>
       </c>
@@ -11770,13 +11767,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G18"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="5" max="5" width="23.7109375" customWidth="1"/>
     <col min="6" max="6" width="24.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7">
       <c r="A1" s="23" t="s">
         <v>831</v>
       </c>
@@ -11793,7 +11790,7 @@
       </c>
       <c r="G1" s="1"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7">
       <c r="A2" s="20" t="s">
         <v>496</v>
       </c>
@@ -11810,7 +11807,7 @@
       </c>
       <c r="G2" s="1"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7">
       <c r="A3" s="20" t="s">
         <v>557</v>
       </c>
@@ -11827,7 +11824,7 @@
       </c>
       <c r="G3" s="1"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7">
       <c r="A4" s="20" t="s">
         <v>567</v>
       </c>
@@ -11844,7 +11841,7 @@
       </c>
       <c r="G4" s="1"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7">
       <c r="A5" s="20" t="s">
         <v>590</v>
       </c>
@@ -11859,7 +11856,7 @@
       </c>
       <c r="G5" s="1"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7">
       <c r="A6" s="20" t="s">
         <v>615</v>
       </c>
@@ -11874,7 +11871,7 @@
       </c>
       <c r="G6" s="1"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7">
       <c r="A7" s="20" t="s">
         <v>540</v>
       </c>
@@ -11885,7 +11882,7 @@
       <c r="F7" s="20"/>
       <c r="G7" s="1"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7">
       <c r="A8" s="21" t="s">
         <v>644</v>
       </c>
@@ -11896,7 +11893,7 @@
       <c r="F8" s="20"/>
       <c r="G8" s="1"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7">
       <c r="A9" s="22" t="s">
         <v>767</v>
       </c>
@@ -11907,7 +11904,7 @@
       <c r="F9" s="20"/>
       <c r="G9" s="1"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7">
       <c r="A10" s="20" t="s">
         <v>784</v>
       </c>
@@ -11918,7 +11915,7 @@
       <c r="F10" s="20"/>
       <c r="G10" s="1"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7">
       <c r="A11" s="22" t="s">
         <v>795</v>
       </c>
@@ -11929,7 +11926,7 @@
       <c r="F11" s="20"/>
       <c r="G11" s="1"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7">
       <c r="A12" s="20" t="s">
         <v>760</v>
       </c>
@@ -11940,7 +11937,7 @@
       <c r="F12" s="20"/>
       <c r="G12" s="1"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7">
       <c r="A13" s="20" t="s">
         <v>530</v>
       </c>
@@ -11951,7 +11948,7 @@
       <c r="F13" s="20"/>
       <c r="G13" s="1"/>
     </row>
-    <row r="14" spans="1:7" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="28.9" customHeight="1">
       <c r="A14" s="27" t="s">
         <v>695</v>
       </c>
@@ -11962,7 +11959,7 @@
       <c r="F14" s="20"/>
       <c r="G14" s="1"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7">
       <c r="A15" s="20"/>
       <c r="B15" s="20"/>
       <c r="C15" s="20"/>
@@ -11971,7 +11968,7 @@
       <c r="F15" s="20"/>
       <c r="G15" s="1"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7">
       <c r="A16" s="20"/>
       <c r="B16" s="20"/>
       <c r="C16" s="20"/>
@@ -11980,7 +11977,7 @@
       <c r="F16" s="20"/>
       <c r="G16" s="1"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7">
       <c r="A17" s="20"/>
       <c r="B17" s="20"/>
       <c r="C17" s="20"/>
@@ -11989,7 +11986,7 @@
       <c r="F17" s="20"/>
       <c r="G17" s="1"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -12007,204 +12004,204 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:Q172"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1">
       <c r="A1" s="40"/>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1">
       <c r="A2" s="41" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1">
       <c r="A3" s="41" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1">
       <c r="A4" s="41" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1">
       <c r="A5" s="41" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1">
       <c r="A6" s="41" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1">
       <c r="A7" s="41" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1">
       <c r="A8" s="41" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1">
       <c r="A9" s="41" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1">
       <c r="A10" s="41" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1">
       <c r="A11" s="41" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" ht="15.6" customHeight="1">
       <c r="A13" s="42" t="s">
         <v>834</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1">
       <c r="A14" s="40"/>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1">
       <c r="A15" s="41" t="s">
         <v>835</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1">
       <c r="A16" s="41" t="s">
         <v>836</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17">
       <c r="A17" s="41" t="s">
         <v>837</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17">
       <c r="A18" s="41" t="s">
         <v>838</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17">
       <c r="A19" s="41" t="s">
         <v>839</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17">
       <c r="A20" s="41" t="s">
         <v>840</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17">
       <c r="A21" s="41" t="s">
         <v>841</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:17">
       <c r="A22" s="41" t="s">
         <v>842</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:17">
       <c r="A23" s="41" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:17">
       <c r="A24" s="41" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17">
       <c r="A26" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:17">
       <c r="A27" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A28" s="86" t="s">
+    <row r="28" spans="1:17">
+      <c r="A28" s="88" t="s">
         <v>843</v>
       </c>
-      <c r="B28" s="85"/>
-      <c r="C28" s="85"/>
-      <c r="D28" s="85"/>
-      <c r="E28" s="85"/>
-      <c r="F28" s="85"/>
-      <c r="G28" s="85"/>
-      <c r="H28" s="85"/>
-      <c r="I28" s="85"/>
-      <c r="J28" s="85"/>
-      <c r="K28" s="85"/>
-      <c r="L28" s="85"/>
-      <c r="M28" s="85"/>
-      <c r="N28" s="85"/>
-      <c r="O28" s="85"/>
-      <c r="P28" s="85"/>
-      <c r="Q28" s="85"/>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A29" s="85"/>
-      <c r="B29" s="85"/>
-      <c r="C29" s="85"/>
-      <c r="D29" s="85"/>
-      <c r="E29" s="85"/>
-      <c r="F29" s="85"/>
-      <c r="G29" s="85"/>
-      <c r="H29" s="85"/>
-      <c r="I29" s="85"/>
-      <c r="J29" s="85"/>
-      <c r="K29" s="85"/>
-      <c r="L29" s="85"/>
-      <c r="M29" s="85"/>
-      <c r="N29" s="85"/>
-      <c r="O29" s="85"/>
-      <c r="P29" s="85"/>
-      <c r="Q29" s="85"/>
-    </row>
-    <row r="30" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="86"/>
+      <c r="C28" s="86"/>
+      <c r="D28" s="86"/>
+      <c r="E28" s="86"/>
+      <c r="F28" s="86"/>
+      <c r="G28" s="86"/>
+      <c r="H28" s="86"/>
+      <c r="I28" s="86"/>
+      <c r="J28" s="86"/>
+      <c r="K28" s="86"/>
+      <c r="L28" s="86"/>
+      <c r="M28" s="86"/>
+      <c r="N28" s="86"/>
+      <c r="O28" s="86"/>
+      <c r="P28" s="86"/>
+      <c r="Q28" s="86"/>
+    </row>
+    <row r="29" spans="1:17">
+      <c r="A29" s="86"/>
+      <c r="B29" s="86"/>
+      <c r="C29" s="86"/>
+      <c r="D29" s="86"/>
+      <c r="E29" s="86"/>
+      <c r="F29" s="86"/>
+      <c r="G29" s="86"/>
+      <c r="H29" s="86"/>
+      <c r="I29" s="86"/>
+      <c r="J29" s="86"/>
+      <c r="K29" s="86"/>
+      <c r="L29" s="86"/>
+      <c r="M29" s="86"/>
+      <c r="N29" s="86"/>
+      <c r="O29" s="86"/>
+      <c r="P29" s="86"/>
+      <c r="Q29" s="86"/>
+    </row>
+    <row r="30" spans="1:17" ht="14.45" customHeight="1">
       <c r="A30" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="B30" s="84" t="s">
+      <c r="B30" s="85" t="s">
         <v>21</v>
       </c>
-      <c r="C30" s="85"/>
-      <c r="D30" s="85"/>
-      <c r="E30" s="84" t="s">
+      <c r="C30" s="86"/>
+      <c r="D30" s="86"/>
+      <c r="E30" s="85" t="s">
         <v>22</v>
       </c>
-      <c r="F30" s="85"/>
-      <c r="G30" s="85"/>
-      <c r="H30" s="84" t="s">
+      <c r="F30" s="86"/>
+      <c r="G30" s="86"/>
+      <c r="H30" s="85" t="s">
         <v>23</v>
       </c>
-      <c r="I30" s="85"/>
-      <c r="J30" s="85"/>
-      <c r="K30" s="84" t="s">
+      <c r="I30" s="86"/>
+      <c r="J30" s="86"/>
+      <c r="K30" s="85" t="s">
         <v>24</v>
       </c>
-      <c r="L30" s="85"/>
-      <c r="M30" s="85"/>
-      <c r="N30" s="85"/>
-      <c r="O30" s="85"/>
-      <c r="P30" s="84" t="s">
+      <c r="L30" s="86"/>
+      <c r="M30" s="86"/>
+      <c r="N30" s="86"/>
+      <c r="O30" s="86"/>
+      <c r="P30" s="85" t="s">
         <v>25</v>
       </c>
-      <c r="Q30" s="84" t="s">
+      <c r="Q30" s="85" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A31" s="85"/>
+    <row r="31" spans="1:17">
+      <c r="A31" s="86"/>
       <c r="B31" s="43" t="s">
         <v>27</v>
       </c>
@@ -12247,10 +12244,10 @@
       <c r="O31" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P31" s="85"/>
-      <c r="Q31" s="85"/>
-    </row>
-    <row r="32" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P31" s="86"/>
+      <c r="Q31" s="86"/>
+    </row>
+    <row r="32" spans="1:17" ht="43.15" customHeight="1">
       <c r="A32" s="43" t="s">
         <v>844</v>
       </c>
@@ -12301,81 +12298,81 @@
         <v>13</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A33" s="86" t="s">
+    <row r="33" spans="1:17">
+      <c r="A33" s="88" t="s">
         <v>644</v>
       </c>
-      <c r="B33" s="85"/>
-      <c r="C33" s="85"/>
-      <c r="D33" s="85"/>
-      <c r="E33" s="85"/>
-      <c r="F33" s="85"/>
-      <c r="G33" s="85"/>
-      <c r="H33" s="85"/>
-      <c r="I33" s="85"/>
-      <c r="J33" s="85"/>
-      <c r="K33" s="85"/>
-      <c r="L33" s="85"/>
-      <c r="M33" s="85"/>
-      <c r="N33" s="85"/>
-      <c r="O33" s="85"/>
-      <c r="P33" s="85"/>
-      <c r="Q33" s="85"/>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A34" s="85"/>
-      <c r="B34" s="85"/>
-      <c r="C34" s="85"/>
-      <c r="D34" s="85"/>
-      <c r="E34" s="85"/>
-      <c r="F34" s="85"/>
-      <c r="G34" s="85"/>
-      <c r="H34" s="85"/>
-      <c r="I34" s="85"/>
-      <c r="J34" s="85"/>
-      <c r="K34" s="85"/>
-      <c r="L34" s="85"/>
-      <c r="M34" s="85"/>
-      <c r="N34" s="85"/>
-      <c r="O34" s="85"/>
-      <c r="P34" s="85"/>
-      <c r="Q34" s="85"/>
-    </row>
-    <row r="35" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="86"/>
+      <c r="C33" s="86"/>
+      <c r="D33" s="86"/>
+      <c r="E33" s="86"/>
+      <c r="F33" s="86"/>
+      <c r="G33" s="86"/>
+      <c r="H33" s="86"/>
+      <c r="I33" s="86"/>
+      <c r="J33" s="86"/>
+      <c r="K33" s="86"/>
+      <c r="L33" s="86"/>
+      <c r="M33" s="86"/>
+      <c r="N33" s="86"/>
+      <c r="O33" s="86"/>
+      <c r="P33" s="86"/>
+      <c r="Q33" s="86"/>
+    </row>
+    <row r="34" spans="1:17">
+      <c r="A34" s="86"/>
+      <c r="B34" s="86"/>
+      <c r="C34" s="86"/>
+      <c r="D34" s="86"/>
+      <c r="E34" s="86"/>
+      <c r="F34" s="86"/>
+      <c r="G34" s="86"/>
+      <c r="H34" s="86"/>
+      <c r="I34" s="86"/>
+      <c r="J34" s="86"/>
+      <c r="K34" s="86"/>
+      <c r="L34" s="86"/>
+      <c r="M34" s="86"/>
+      <c r="N34" s="86"/>
+      <c r="O34" s="86"/>
+      <c r="P34" s="86"/>
+      <c r="Q34" s="86"/>
+    </row>
+    <row r="35" spans="1:17" ht="14.45" customHeight="1">
       <c r="A35" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="B35" s="84" t="s">
+      <c r="B35" s="85" t="s">
         <v>21</v>
       </c>
-      <c r="C35" s="85"/>
-      <c r="D35" s="85"/>
-      <c r="E35" s="84" t="s">
+      <c r="C35" s="86"/>
+      <c r="D35" s="86"/>
+      <c r="E35" s="85" t="s">
         <v>22</v>
       </c>
-      <c r="F35" s="85"/>
-      <c r="G35" s="85"/>
-      <c r="H35" s="84" t="s">
+      <c r="F35" s="86"/>
+      <c r="G35" s="86"/>
+      <c r="H35" s="85" t="s">
         <v>23</v>
       </c>
-      <c r="I35" s="85"/>
-      <c r="J35" s="85"/>
-      <c r="K35" s="84" t="s">
+      <c r="I35" s="86"/>
+      <c r="J35" s="86"/>
+      <c r="K35" s="85" t="s">
         <v>24</v>
       </c>
-      <c r="L35" s="85"/>
-      <c r="M35" s="85"/>
-      <c r="N35" s="85"/>
-      <c r="O35" s="85"/>
-      <c r="P35" s="84" t="s">
+      <c r="L35" s="86"/>
+      <c r="M35" s="86"/>
+      <c r="N35" s="86"/>
+      <c r="O35" s="86"/>
+      <c r="P35" s="85" t="s">
         <v>25</v>
       </c>
-      <c r="Q35" s="84" t="s">
+      <c r="Q35" s="85" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A36" s="85"/>
+    <row r="36" spans="1:17">
+      <c r="A36" s="86"/>
       <c r="B36" s="43" t="s">
         <v>27</v>
       </c>
@@ -12418,10 +12415,10 @@
       <c r="O36" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P36" s="85"/>
-      <c r="Q36" s="85"/>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="P36" s="86"/>
+      <c r="Q36" s="86"/>
+    </row>
+    <row r="37" spans="1:17">
       <c r="A37" s="43" t="s">
         <v>689</v>
       </c>
@@ -12472,7 +12469,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="38" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:17" ht="30">
       <c r="A38" s="43" t="s">
         <v>845</v>
       </c>
@@ -12523,7 +12520,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:17" ht="28.9" customHeight="1">
       <c r="A39" s="43" t="s">
         <v>68</v>
       </c>
@@ -12574,7 +12571,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="40" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:17" ht="57.6" customHeight="1">
       <c r="A40" s="43" t="s">
         <v>846</v>
       </c>
@@ -12607,7 +12604,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:17">
       <c r="A41" s="43" t="s">
         <v>847</v>
       </c>
@@ -12640,7 +12637,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:17" ht="43.15" customHeight="1">
       <c r="A42" s="46" t="s">
         <v>848</v>
       </c>
@@ -12683,7 +12680,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:17" ht="30">
       <c r="A43" s="43" t="s">
         <v>849</v>
       </c>
@@ -12716,7 +12713,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="44" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:17" ht="28.9" customHeight="1">
       <c r="A44" s="43" t="s">
         <v>773</v>
       </c>
@@ -12749,7 +12746,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" ht="28.9" customHeight="1">
       <c r="A45" s="43" t="s">
         <v>766</v>
       </c>
@@ -12782,7 +12779,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:17" ht="43.15" customHeight="1">
       <c r="A46" s="43" t="s">
         <v>778</v>
       </c>
@@ -12815,7 +12812,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:17" ht="57.6" customHeight="1">
       <c r="A47" s="46" t="s">
         <v>850</v>
       </c>
@@ -12858,81 +12855,81 @@
         <v>20</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A48" s="86" t="s">
+    <row r="48" spans="1:17">
+      <c r="A48" s="88" t="s">
         <v>851</v>
       </c>
-      <c r="B48" s="85"/>
-      <c r="C48" s="85"/>
-      <c r="D48" s="85"/>
-      <c r="E48" s="85"/>
-      <c r="F48" s="85"/>
-      <c r="G48" s="85"/>
-      <c r="H48" s="85"/>
-      <c r="I48" s="85"/>
-      <c r="J48" s="85"/>
-      <c r="K48" s="85"/>
-      <c r="L48" s="85"/>
-      <c r="M48" s="85"/>
-      <c r="N48" s="85"/>
-      <c r="O48" s="85"/>
-      <c r="P48" s="85"/>
-      <c r="Q48" s="85"/>
-    </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A49" s="85"/>
-      <c r="B49" s="85"/>
-      <c r="C49" s="85"/>
-      <c r="D49" s="85"/>
-      <c r="E49" s="85"/>
-      <c r="F49" s="85"/>
-      <c r="G49" s="85"/>
-      <c r="H49" s="85"/>
-      <c r="I49" s="85"/>
-      <c r="J49" s="85"/>
-      <c r="K49" s="85"/>
-      <c r="L49" s="85"/>
-      <c r="M49" s="85"/>
-      <c r="N49" s="85"/>
-      <c r="O49" s="85"/>
-      <c r="P49" s="85"/>
-      <c r="Q49" s="85"/>
-    </row>
-    <row r="50" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B48" s="86"/>
+      <c r="C48" s="86"/>
+      <c r="D48" s="86"/>
+      <c r="E48" s="86"/>
+      <c r="F48" s="86"/>
+      <c r="G48" s="86"/>
+      <c r="H48" s="86"/>
+      <c r="I48" s="86"/>
+      <c r="J48" s="86"/>
+      <c r="K48" s="86"/>
+      <c r="L48" s="86"/>
+      <c r="M48" s="86"/>
+      <c r="N48" s="86"/>
+      <c r="O48" s="86"/>
+      <c r="P48" s="86"/>
+      <c r="Q48" s="86"/>
+    </row>
+    <row r="49" spans="1:17">
+      <c r="A49" s="86"/>
+      <c r="B49" s="86"/>
+      <c r="C49" s="86"/>
+      <c r="D49" s="86"/>
+      <c r="E49" s="86"/>
+      <c r="F49" s="86"/>
+      <c r="G49" s="86"/>
+      <c r="H49" s="86"/>
+      <c r="I49" s="86"/>
+      <c r="J49" s="86"/>
+      <c r="K49" s="86"/>
+      <c r="L49" s="86"/>
+      <c r="M49" s="86"/>
+      <c r="N49" s="86"/>
+      <c r="O49" s="86"/>
+      <c r="P49" s="86"/>
+      <c r="Q49" s="86"/>
+    </row>
+    <row r="50" spans="1:17" ht="14.45" customHeight="1">
       <c r="A50" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="B50" s="84" t="s">
+      <c r="B50" s="85" t="s">
         <v>21</v>
       </c>
-      <c r="C50" s="85"/>
-      <c r="D50" s="85"/>
-      <c r="E50" s="84" t="s">
+      <c r="C50" s="86"/>
+      <c r="D50" s="86"/>
+      <c r="E50" s="85" t="s">
         <v>22</v>
       </c>
-      <c r="F50" s="85"/>
-      <c r="G50" s="85"/>
-      <c r="H50" s="84" t="s">
+      <c r="F50" s="86"/>
+      <c r="G50" s="86"/>
+      <c r="H50" s="85" t="s">
         <v>23</v>
       </c>
-      <c r="I50" s="85"/>
-      <c r="J50" s="85"/>
-      <c r="K50" s="84" t="s">
+      <c r="I50" s="86"/>
+      <c r="J50" s="86"/>
+      <c r="K50" s="85" t="s">
         <v>24</v>
       </c>
-      <c r="L50" s="85"/>
-      <c r="M50" s="85"/>
-      <c r="N50" s="85"/>
-      <c r="O50" s="85"/>
-      <c r="P50" s="84" t="s">
+      <c r="L50" s="86"/>
+      <c r="M50" s="86"/>
+      <c r="N50" s="86"/>
+      <c r="O50" s="86"/>
+      <c r="P50" s="85" t="s">
         <v>25</v>
       </c>
-      <c r="Q50" s="84" t="s">
+      <c r="Q50" s="85" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A51" s="85"/>
+    <row r="51" spans="1:17">
+      <c r="A51" s="86"/>
       <c r="B51" s="43" t="s">
         <v>27</v>
       </c>
@@ -12975,10 +12972,10 @@
       <c r="O51" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P51" s="85"/>
-      <c r="Q51" s="85"/>
-    </row>
-    <row r="52" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P51" s="86"/>
+      <c r="Q51" s="86"/>
+    </row>
+    <row r="52" spans="1:17" ht="57.6" customHeight="1">
       <c r="A52" s="43" t="s">
         <v>852</v>
       </c>
@@ -13029,81 +13026,81 @@
         <v>15</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A53" s="86" t="s">
+    <row r="53" spans="1:17">
+      <c r="A53" s="88" t="s">
         <v>853</v>
       </c>
-      <c r="B53" s="85"/>
-      <c r="C53" s="85"/>
-      <c r="D53" s="85"/>
-      <c r="E53" s="85"/>
-      <c r="F53" s="85"/>
-      <c r="G53" s="85"/>
-      <c r="H53" s="85"/>
-      <c r="I53" s="85"/>
-      <c r="J53" s="85"/>
-      <c r="K53" s="85"/>
-      <c r="L53" s="85"/>
-      <c r="M53" s="85"/>
-      <c r="N53" s="85"/>
-      <c r="O53" s="85"/>
-      <c r="P53" s="85"/>
-      <c r="Q53" s="85"/>
-    </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A54" s="85"/>
-      <c r="B54" s="85"/>
-      <c r="C54" s="85"/>
-      <c r="D54" s="85"/>
-      <c r="E54" s="85"/>
-      <c r="F54" s="85"/>
-      <c r="G54" s="85"/>
-      <c r="H54" s="85"/>
-      <c r="I54" s="85"/>
-      <c r="J54" s="85"/>
-      <c r="K54" s="85"/>
-      <c r="L54" s="85"/>
-      <c r="M54" s="85"/>
-      <c r="N54" s="85"/>
-      <c r="O54" s="85"/>
-      <c r="P54" s="85"/>
-      <c r="Q54" s="85"/>
-    </row>
-    <row r="55" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B53" s="86"/>
+      <c r="C53" s="86"/>
+      <c r="D53" s="86"/>
+      <c r="E53" s="86"/>
+      <c r="F53" s="86"/>
+      <c r="G53" s="86"/>
+      <c r="H53" s="86"/>
+      <c r="I53" s="86"/>
+      <c r="J53" s="86"/>
+      <c r="K53" s="86"/>
+      <c r="L53" s="86"/>
+      <c r="M53" s="86"/>
+      <c r="N53" s="86"/>
+      <c r="O53" s="86"/>
+      <c r="P53" s="86"/>
+      <c r="Q53" s="86"/>
+    </row>
+    <row r="54" spans="1:17">
+      <c r="A54" s="86"/>
+      <c r="B54" s="86"/>
+      <c r="C54" s="86"/>
+      <c r="D54" s="86"/>
+      <c r="E54" s="86"/>
+      <c r="F54" s="86"/>
+      <c r="G54" s="86"/>
+      <c r="H54" s="86"/>
+      <c r="I54" s="86"/>
+      <c r="J54" s="86"/>
+      <c r="K54" s="86"/>
+      <c r="L54" s="86"/>
+      <c r="M54" s="86"/>
+      <c r="N54" s="86"/>
+      <c r="O54" s="86"/>
+      <c r="P54" s="86"/>
+      <c r="Q54" s="86"/>
+    </row>
+    <row r="55" spans="1:17" ht="14.45" customHeight="1">
       <c r="A55" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="B55" s="84" t="s">
+      <c r="B55" s="85" t="s">
         <v>21</v>
       </c>
-      <c r="C55" s="85"/>
-      <c r="D55" s="85"/>
-      <c r="E55" s="84" t="s">
+      <c r="C55" s="86"/>
+      <c r="D55" s="86"/>
+      <c r="E55" s="85" t="s">
         <v>22</v>
       </c>
-      <c r="F55" s="85"/>
-      <c r="G55" s="85"/>
-      <c r="H55" s="84" t="s">
+      <c r="F55" s="86"/>
+      <c r="G55" s="86"/>
+      <c r="H55" s="85" t="s">
         <v>23</v>
       </c>
-      <c r="I55" s="85"/>
-      <c r="J55" s="85"/>
-      <c r="K55" s="84" t="s">
+      <c r="I55" s="86"/>
+      <c r="J55" s="86"/>
+      <c r="K55" s="85" t="s">
         <v>24</v>
       </c>
-      <c r="L55" s="85"/>
-      <c r="M55" s="85"/>
-      <c r="N55" s="85"/>
-      <c r="O55" s="85"/>
-      <c r="P55" s="84" t="s">
+      <c r="L55" s="86"/>
+      <c r="M55" s="86"/>
+      <c r="N55" s="86"/>
+      <c r="O55" s="86"/>
+      <c r="P55" s="85" t="s">
         <v>25</v>
       </c>
-      <c r="Q55" s="84" t="s">
+      <c r="Q55" s="85" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A56" s="85"/>
+    <row r="56" spans="1:17">
+      <c r="A56" s="86"/>
       <c r="B56" s="43" t="s">
         <v>27</v>
       </c>
@@ -13146,10 +13143,10 @@
       <c r="O56" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P56" s="85"/>
-      <c r="Q56" s="85"/>
-    </row>
-    <row r="57" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P56" s="86"/>
+      <c r="Q56" s="86"/>
+    </row>
+    <row r="57" spans="1:17" ht="28.9" customHeight="1">
       <c r="A57" s="43" t="s">
         <v>34</v>
       </c>
@@ -13182,7 +13179,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="58" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:17" ht="57.6" customHeight="1">
       <c r="A58" s="43" t="s">
         <v>854</v>
       </c>
@@ -13215,7 +13212,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:17" ht="43.15" customHeight="1">
       <c r="A59" s="43" t="s">
         <v>37</v>
       </c>
@@ -13248,7 +13245,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:17" ht="43.15" customHeight="1">
       <c r="A60" s="43" t="s">
         <v>40</v>
       </c>
@@ -13281,7 +13278,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:17" ht="28.9" customHeight="1">
       <c r="A61" s="43" t="s">
         <v>39</v>
       </c>
@@ -13314,7 +13311,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="100.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:17" ht="100.9" customHeight="1">
       <c r="A62" s="43" t="s">
         <v>36</v>
       </c>
@@ -13347,7 +13344,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="63" spans="1:17" ht="144" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:17" ht="144" customHeight="1">
       <c r="A63" s="43" t="s">
         <v>35</v>
       </c>
@@ -13380,7 +13377,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="115.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:17" ht="115.15" customHeight="1">
       <c r="A64" s="43" t="s">
         <v>44</v>
       </c>
@@ -13413,7 +13410,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="65" spans="1:17" ht="100.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:17" ht="100.9" customHeight="1">
       <c r="A65" s="43" t="s">
         <v>41</v>
       </c>
@@ -13446,7 +13443,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="66" spans="1:17" ht="144" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:17" ht="144" customHeight="1">
       <c r="A66" s="43" t="s">
         <v>32</v>
       </c>
@@ -13479,7 +13476,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="67" spans="1:17" ht="115.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:17" ht="115.15" customHeight="1">
       <c r="A67" s="43" t="s">
         <v>31</v>
       </c>
@@ -13512,7 +13509,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="68" spans="1:17" ht="129.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:17" ht="129.6" customHeight="1">
       <c r="A68" s="43" t="s">
         <v>33</v>
       </c>
@@ -13545,7 +13542,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="69" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:17" ht="72" customHeight="1">
       <c r="A69" s="43" t="s">
         <v>42</v>
       </c>
@@ -13578,7 +13575,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="70" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:17" ht="72" customHeight="1">
       <c r="A70" s="43" t="s">
         <v>43</v>
       </c>
@@ -13611,7 +13608,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="71" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" ht="43.15" customHeight="1">
       <c r="A71" s="46" t="s">
         <v>855</v>
       </c>
@@ -13654,81 +13651,81 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A72" s="86" t="s">
+    <row r="72" spans="1:17">
+      <c r="A72" s="88" t="s">
         <v>856</v>
       </c>
-      <c r="B72" s="85"/>
-      <c r="C72" s="85"/>
-      <c r="D72" s="85"/>
-      <c r="E72" s="85"/>
-      <c r="F72" s="85"/>
-      <c r="G72" s="85"/>
-      <c r="H72" s="85"/>
-      <c r="I72" s="85"/>
-      <c r="J72" s="85"/>
-      <c r="K72" s="85"/>
-      <c r="L72" s="85"/>
-      <c r="M72" s="85"/>
-      <c r="N72" s="85"/>
-      <c r="O72" s="85"/>
-      <c r="P72" s="85"/>
-      <c r="Q72" s="85"/>
-    </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A73" s="85"/>
-      <c r="B73" s="85"/>
-      <c r="C73" s="85"/>
-      <c r="D73" s="85"/>
-      <c r="E73" s="85"/>
-      <c r="F73" s="85"/>
-      <c r="G73" s="85"/>
-      <c r="H73" s="85"/>
-      <c r="I73" s="85"/>
-      <c r="J73" s="85"/>
-      <c r="K73" s="85"/>
-      <c r="L73" s="85"/>
-      <c r="M73" s="85"/>
-      <c r="N73" s="85"/>
-      <c r="O73" s="85"/>
-      <c r="P73" s="85"/>
-      <c r="Q73" s="85"/>
-    </row>
-    <row r="74" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B72" s="86"/>
+      <c r="C72" s="86"/>
+      <c r="D72" s="86"/>
+      <c r="E72" s="86"/>
+      <c r="F72" s="86"/>
+      <c r="G72" s="86"/>
+      <c r="H72" s="86"/>
+      <c r="I72" s="86"/>
+      <c r="J72" s="86"/>
+      <c r="K72" s="86"/>
+      <c r="L72" s="86"/>
+      <c r="M72" s="86"/>
+      <c r="N72" s="86"/>
+      <c r="O72" s="86"/>
+      <c r="P72" s="86"/>
+      <c r="Q72" s="86"/>
+    </row>
+    <row r="73" spans="1:17">
+      <c r="A73" s="86"/>
+      <c r="B73" s="86"/>
+      <c r="C73" s="86"/>
+      <c r="D73" s="86"/>
+      <c r="E73" s="86"/>
+      <c r="F73" s="86"/>
+      <c r="G73" s="86"/>
+      <c r="H73" s="86"/>
+      <c r="I73" s="86"/>
+      <c r="J73" s="86"/>
+      <c r="K73" s="86"/>
+      <c r="L73" s="86"/>
+      <c r="M73" s="86"/>
+      <c r="N73" s="86"/>
+      <c r="O73" s="86"/>
+      <c r="P73" s="86"/>
+      <c r="Q73" s="86"/>
+    </row>
+    <row r="74" spans="1:17" ht="14.45" customHeight="1">
       <c r="A74" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="B74" s="84" t="s">
+      <c r="B74" s="85" t="s">
         <v>21</v>
       </c>
-      <c r="C74" s="85"/>
-      <c r="D74" s="85"/>
-      <c r="E74" s="84" t="s">
+      <c r="C74" s="86"/>
+      <c r="D74" s="86"/>
+      <c r="E74" s="85" t="s">
         <v>22</v>
       </c>
-      <c r="F74" s="85"/>
-      <c r="G74" s="85"/>
-      <c r="H74" s="84" t="s">
+      <c r="F74" s="86"/>
+      <c r="G74" s="86"/>
+      <c r="H74" s="85" t="s">
         <v>23</v>
       </c>
-      <c r="I74" s="85"/>
-      <c r="J74" s="85"/>
-      <c r="K74" s="84" t="s">
+      <c r="I74" s="86"/>
+      <c r="J74" s="86"/>
+      <c r="K74" s="85" t="s">
         <v>24</v>
       </c>
-      <c r="L74" s="85"/>
-      <c r="M74" s="85"/>
-      <c r="N74" s="85"/>
-      <c r="O74" s="85"/>
-      <c r="P74" s="84" t="s">
+      <c r="L74" s="86"/>
+      <c r="M74" s="86"/>
+      <c r="N74" s="86"/>
+      <c r="O74" s="86"/>
+      <c r="P74" s="85" t="s">
         <v>25</v>
       </c>
-      <c r="Q74" s="84" t="s">
+      <c r="Q74" s="85" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A75" s="85"/>
+    <row r="75" spans="1:17">
+      <c r="A75" s="86"/>
       <c r="B75" s="43" t="s">
         <v>27</v>
       </c>
@@ -13771,10 +13768,10 @@
       <c r="O75" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P75" s="85"/>
-      <c r="Q75" s="85"/>
-    </row>
-    <row r="76" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P75" s="86"/>
+      <c r="Q75" s="86"/>
+    </row>
+    <row r="76" spans="1:17" ht="57.6" customHeight="1">
       <c r="A76" s="43" t="s">
         <v>48</v>
       </c>
@@ -13807,7 +13804,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:17" ht="43.15" customHeight="1">
       <c r="A77" s="43" t="s">
         <v>51</v>
       </c>
@@ -13840,7 +13837,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:17" ht="72" customHeight="1">
       <c r="A78" s="43" t="s">
         <v>50</v>
       </c>
@@ -13873,7 +13870,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:17" ht="57.6" customHeight="1">
       <c r="A79" s="43" t="s">
         <v>49</v>
       </c>
@@ -13906,7 +13903,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:17" ht="28.9" customHeight="1">
       <c r="A80" s="46" t="s">
         <v>857</v>
       </c>
@@ -13949,81 +13946,81 @@
         <v>272</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A81" s="86" t="s">
+    <row r="81" spans="1:17">
+      <c r="A81" s="88" t="s">
         <v>858</v>
       </c>
-      <c r="B81" s="85"/>
-      <c r="C81" s="85"/>
-      <c r="D81" s="85"/>
-      <c r="E81" s="85"/>
-      <c r="F81" s="85"/>
-      <c r="G81" s="85"/>
-      <c r="H81" s="85"/>
-      <c r="I81" s="85"/>
-      <c r="J81" s="85"/>
-      <c r="K81" s="85"/>
-      <c r="L81" s="85"/>
-      <c r="M81" s="85"/>
-      <c r="N81" s="85"/>
-      <c r="O81" s="85"/>
-      <c r="P81" s="85"/>
-      <c r="Q81" s="85"/>
-    </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A82" s="85"/>
-      <c r="B82" s="85"/>
-      <c r="C82" s="85"/>
-      <c r="D82" s="85"/>
-      <c r="E82" s="85"/>
-      <c r="F82" s="85"/>
-      <c r="G82" s="85"/>
-      <c r="H82" s="85"/>
-      <c r="I82" s="85"/>
-      <c r="J82" s="85"/>
-      <c r="K82" s="85"/>
-      <c r="L82" s="85"/>
-      <c r="M82" s="85"/>
-      <c r="N82" s="85"/>
-      <c r="O82" s="85"/>
-      <c r="P82" s="85"/>
-      <c r="Q82" s="85"/>
-    </row>
-    <row r="83" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B81" s="86"/>
+      <c r="C81" s="86"/>
+      <c r="D81" s="86"/>
+      <c r="E81" s="86"/>
+      <c r="F81" s="86"/>
+      <c r="G81" s="86"/>
+      <c r="H81" s="86"/>
+      <c r="I81" s="86"/>
+      <c r="J81" s="86"/>
+      <c r="K81" s="86"/>
+      <c r="L81" s="86"/>
+      <c r="M81" s="86"/>
+      <c r="N81" s="86"/>
+      <c r="O81" s="86"/>
+      <c r="P81" s="86"/>
+      <c r="Q81" s="86"/>
+    </row>
+    <row r="82" spans="1:17">
+      <c r="A82" s="86"/>
+      <c r="B82" s="86"/>
+      <c r="C82" s="86"/>
+      <c r="D82" s="86"/>
+      <c r="E82" s="86"/>
+      <c r="F82" s="86"/>
+      <c r="G82" s="86"/>
+      <c r="H82" s="86"/>
+      <c r="I82" s="86"/>
+      <c r="J82" s="86"/>
+      <c r="K82" s="86"/>
+      <c r="L82" s="86"/>
+      <c r="M82" s="86"/>
+      <c r="N82" s="86"/>
+      <c r="O82" s="86"/>
+      <c r="P82" s="86"/>
+      <c r="Q82" s="86"/>
+    </row>
+    <row r="83" spans="1:17" ht="14.45" customHeight="1">
       <c r="A83" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="B83" s="84" t="s">
+      <c r="B83" s="85" t="s">
         <v>21</v>
       </c>
-      <c r="C83" s="85"/>
-      <c r="D83" s="85"/>
-      <c r="E83" s="84" t="s">
+      <c r="C83" s="86"/>
+      <c r="D83" s="86"/>
+      <c r="E83" s="85" t="s">
         <v>22</v>
       </c>
-      <c r="F83" s="85"/>
-      <c r="G83" s="85"/>
-      <c r="H83" s="84" t="s">
+      <c r="F83" s="86"/>
+      <c r="G83" s="86"/>
+      <c r="H83" s="85" t="s">
         <v>23</v>
       </c>
-      <c r="I83" s="85"/>
-      <c r="J83" s="85"/>
-      <c r="K83" s="84" t="s">
+      <c r="I83" s="86"/>
+      <c r="J83" s="86"/>
+      <c r="K83" s="85" t="s">
         <v>24</v>
       </c>
-      <c r="L83" s="85"/>
-      <c r="M83" s="85"/>
-      <c r="N83" s="85"/>
-      <c r="O83" s="85"/>
-      <c r="P83" s="84" t="s">
+      <c r="L83" s="86"/>
+      <c r="M83" s="86"/>
+      <c r="N83" s="86"/>
+      <c r="O83" s="86"/>
+      <c r="P83" s="85" t="s">
         <v>25</v>
       </c>
-      <c r="Q83" s="84" t="s">
+      <c r="Q83" s="85" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A84" s="85"/>
+    <row r="84" spans="1:17">
+      <c r="A84" s="86"/>
       <c r="B84" s="43" t="s">
         <v>27</v>
       </c>
@@ -14066,10 +14063,10 @@
       <c r="O84" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P84" s="85"/>
-      <c r="Q84" s="85"/>
-    </row>
-    <row r="85" spans="1:17" ht="100.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P84" s="86"/>
+      <c r="Q84" s="86"/>
+    </row>
+    <row r="85" spans="1:17" ht="100.9" customHeight="1">
       <c r="A85" s="43" t="s">
         <v>859</v>
       </c>
@@ -14102,7 +14099,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="86" spans="1:17" ht="100.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:17" ht="100.9" customHeight="1">
       <c r="A86" s="43" t="s">
         <v>860</v>
       </c>
@@ -14135,7 +14132,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="87" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:17" ht="28.9" customHeight="1">
       <c r="A87" s="43" t="s">
         <v>800</v>
       </c>
@@ -14168,7 +14165,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:17">
       <c r="A88" s="43" t="s">
         <v>805</v>
       </c>
@@ -14201,7 +14198,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="89" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:17" ht="28.9" customHeight="1">
       <c r="A89" s="43" t="s">
         <v>810</v>
       </c>
@@ -14234,7 +14231,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:17">
       <c r="A90" s="43" t="s">
         <v>815</v>
       </c>
@@ -14267,7 +14264,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="91" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:17" ht="28.9" customHeight="1">
       <c r="A91" s="43" t="s">
         <v>861</v>
       </c>
@@ -14300,7 +14297,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="92" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:17" ht="28.9" customHeight="1">
       <c r="A92" s="46" t="s">
         <v>862</v>
       </c>
@@ -14343,81 +14340,81 @@
         <v>30</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A93" s="86" t="s">
+    <row r="93" spans="1:17">
+      <c r="A93" s="88" t="s">
         <v>863</v>
       </c>
-      <c r="B93" s="85"/>
-      <c r="C93" s="85"/>
-      <c r="D93" s="85"/>
-      <c r="E93" s="85"/>
-      <c r="F93" s="85"/>
-      <c r="G93" s="85"/>
-      <c r="H93" s="85"/>
-      <c r="I93" s="85"/>
-      <c r="J93" s="85"/>
-      <c r="K93" s="85"/>
-      <c r="L93" s="85"/>
-      <c r="M93" s="85"/>
-      <c r="N93" s="85"/>
-      <c r="O93" s="85"/>
-      <c r="P93" s="85"/>
-      <c r="Q93" s="85"/>
-    </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A94" s="85"/>
-      <c r="B94" s="85"/>
-      <c r="C94" s="85"/>
-      <c r="D94" s="85"/>
-      <c r="E94" s="85"/>
-      <c r="F94" s="85"/>
-      <c r="G94" s="85"/>
-      <c r="H94" s="85"/>
-      <c r="I94" s="85"/>
-      <c r="J94" s="85"/>
-      <c r="K94" s="85"/>
-      <c r="L94" s="85"/>
-      <c r="M94" s="85"/>
-      <c r="N94" s="85"/>
-      <c r="O94" s="85"/>
-      <c r="P94" s="85"/>
-      <c r="Q94" s="85"/>
-    </row>
-    <row r="95" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B93" s="86"/>
+      <c r="C93" s="86"/>
+      <c r="D93" s="86"/>
+      <c r="E93" s="86"/>
+      <c r="F93" s="86"/>
+      <c r="G93" s="86"/>
+      <c r="H93" s="86"/>
+      <c r="I93" s="86"/>
+      <c r="J93" s="86"/>
+      <c r="K93" s="86"/>
+      <c r="L93" s="86"/>
+      <c r="M93" s="86"/>
+      <c r="N93" s="86"/>
+      <c r="O93" s="86"/>
+      <c r="P93" s="86"/>
+      <c r="Q93" s="86"/>
+    </row>
+    <row r="94" spans="1:17">
+      <c r="A94" s="86"/>
+      <c r="B94" s="86"/>
+      <c r="C94" s="86"/>
+      <c r="D94" s="86"/>
+      <c r="E94" s="86"/>
+      <c r="F94" s="86"/>
+      <c r="G94" s="86"/>
+      <c r="H94" s="86"/>
+      <c r="I94" s="86"/>
+      <c r="J94" s="86"/>
+      <c r="K94" s="86"/>
+      <c r="L94" s="86"/>
+      <c r="M94" s="86"/>
+      <c r="N94" s="86"/>
+      <c r="O94" s="86"/>
+      <c r="P94" s="86"/>
+      <c r="Q94" s="86"/>
+    </row>
+    <row r="95" spans="1:17" ht="14.45" customHeight="1">
       <c r="A95" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="B95" s="84" t="s">
+      <c r="B95" s="85" t="s">
         <v>21</v>
       </c>
-      <c r="C95" s="85"/>
-      <c r="D95" s="85"/>
-      <c r="E95" s="84" t="s">
+      <c r="C95" s="86"/>
+      <c r="D95" s="86"/>
+      <c r="E95" s="85" t="s">
         <v>22</v>
       </c>
-      <c r="F95" s="85"/>
-      <c r="G95" s="85"/>
-      <c r="H95" s="84" t="s">
+      <c r="F95" s="86"/>
+      <c r="G95" s="86"/>
+      <c r="H95" s="85" t="s">
         <v>23</v>
       </c>
-      <c r="I95" s="85"/>
-      <c r="J95" s="85"/>
-      <c r="K95" s="84" t="s">
+      <c r="I95" s="86"/>
+      <c r="J95" s="86"/>
+      <c r="K95" s="85" t="s">
         <v>24</v>
       </c>
-      <c r="L95" s="85"/>
-      <c r="M95" s="85"/>
-      <c r="N95" s="85"/>
-      <c r="O95" s="85"/>
-      <c r="P95" s="84" t="s">
+      <c r="L95" s="86"/>
+      <c r="M95" s="86"/>
+      <c r="N95" s="86"/>
+      <c r="O95" s="86"/>
+      <c r="P95" s="85" t="s">
         <v>25</v>
       </c>
-      <c r="Q95" s="84" t="s">
+      <c r="Q95" s="85" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A96" s="85"/>
+    <row r="96" spans="1:17">
+      <c r="A96" s="86"/>
       <c r="B96" s="43" t="s">
         <v>27</v>
       </c>
@@ -14460,10 +14457,10 @@
       <c r="O96" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P96" s="85"/>
-      <c r="Q96" s="85"/>
-    </row>
-    <row r="97" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P96" s="86"/>
+      <c r="Q96" s="86"/>
+    </row>
+    <row r="97" spans="1:17" ht="57.6" customHeight="1">
       <c r="A97" s="43" t="s">
         <v>864</v>
       </c>
@@ -14496,7 +14493,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="98" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:17" ht="57.6" customHeight="1">
       <c r="A98" s="43" t="s">
         <v>54</v>
       </c>
@@ -14529,7 +14526,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="99" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:17" ht="72" customHeight="1">
       <c r="A99" s="43" t="s">
         <v>55</v>
       </c>
@@ -14562,7 +14559,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="100" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:17" ht="28.9" customHeight="1">
       <c r="A100" s="43" t="s">
         <v>56</v>
       </c>
@@ -14595,7 +14592,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="101" spans="1:17" ht="115.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:17" ht="115.15" customHeight="1">
       <c r="A101" s="43" t="s">
         <v>57</v>
       </c>
@@ -14628,7 +14625,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:17" ht="72" customHeight="1">
       <c r="A102" s="43" t="s">
         <v>865</v>
       </c>
@@ -14661,7 +14658,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:17" ht="28.9" customHeight="1">
       <c r="A103" s="43" t="s">
         <v>866</v>
       </c>
@@ -14694,7 +14691,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:17" ht="43.15" customHeight="1">
       <c r="A104" s="43" t="s">
         <v>58</v>
       </c>
@@ -14727,7 +14724,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:17" ht="57.6" customHeight="1">
       <c r="A105" s="43" t="s">
         <v>59</v>
       </c>
@@ -14760,7 +14757,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="106" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:17" ht="72" customHeight="1">
       <c r="A106" s="43" t="s">
         <v>60</v>
       </c>
@@ -14793,7 +14790,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="107" spans="1:17" ht="100.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:17" ht="100.9" customHeight="1">
       <c r="A107" s="43" t="s">
         <v>867</v>
       </c>
@@ -14826,7 +14823,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:17" ht="57.6" customHeight="1">
       <c r="A108" s="43" t="s">
         <v>61</v>
       </c>
@@ -14859,7 +14856,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:17" ht="72" customHeight="1">
       <c r="A109" s="43" t="s">
         <v>868</v>
       </c>
@@ -14892,7 +14889,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="110" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:17" ht="57.6" customHeight="1">
       <c r="A110" s="43" t="s">
         <v>62</v>
       </c>
@@ -14925,7 +14922,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:17" ht="86.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:17" ht="86.45" customHeight="1">
       <c r="A111" s="43" t="s">
         <v>63</v>
       </c>
@@ -14958,7 +14955,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:17" ht="57.6" customHeight="1">
       <c r="A112" s="43" t="s">
         <v>64</v>
       </c>
@@ -14991,7 +14988,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="113" spans="1:17" ht="86.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:17" ht="86.45" customHeight="1">
       <c r="A113" s="43" t="s">
         <v>869</v>
       </c>
@@ -15024,7 +15021,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="114" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:17" ht="57.6" customHeight="1">
       <c r="A114" s="43" t="s">
         <v>870</v>
       </c>
@@ -15057,7 +15054,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="115" spans="1:17" ht="86.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:17" ht="86.45" customHeight="1">
       <c r="A115" s="43" t="s">
         <v>871</v>
       </c>
@@ -15090,7 +15087,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="116" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:17" ht="72" customHeight="1">
       <c r="A116" s="43" t="s">
         <v>872</v>
       </c>
@@ -15123,7 +15120,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="117" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:17" ht="72" customHeight="1">
       <c r="A117" s="43" t="s">
         <v>65</v>
       </c>
@@ -15156,7 +15153,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:17" ht="57.6" customHeight="1">
       <c r="A118" s="43" t="s">
         <v>66</v>
       </c>
@@ -15189,7 +15186,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:17" ht="72" customHeight="1">
       <c r="A119" s="43" t="s">
         <v>873</v>
       </c>
@@ -15222,7 +15219,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:17" ht="57.6" customHeight="1">
       <c r="A120" s="43" t="s">
         <v>874</v>
       </c>
@@ -15255,7 +15252,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:17" ht="57.6" customHeight="1">
       <c r="A121" s="43" t="s">
         <v>875</v>
       </c>
@@ -15288,7 +15285,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="122" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:17" ht="43.15" customHeight="1">
       <c r="A122" s="43" t="s">
         <v>876</v>
       </c>
@@ -15321,7 +15318,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:17" ht="100.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:17" ht="100.9" customHeight="1">
       <c r="A123" s="43" t="s">
         <v>877</v>
       </c>
@@ -15354,7 +15351,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="124" spans="1:17" ht="100.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:17" ht="100.9" customHeight="1">
       <c r="A124" s="43" t="s">
         <v>878</v>
       </c>
@@ -15387,7 +15384,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="125" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:17" ht="43.15" customHeight="1">
       <c r="A125" s="43" t="s">
         <v>879</v>
       </c>
@@ -15420,7 +15417,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:17" ht="43.15" customHeight="1">
       <c r="A126" s="46" t="s">
         <v>863</v>
       </c>
@@ -15463,81 +15460,81 @@
         <v>128</v>
       </c>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A127" s="86" t="s">
+    <row r="127" spans="1:17">
+      <c r="A127" s="88" t="s">
         <v>557</v>
       </c>
-      <c r="B127" s="85"/>
-      <c r="C127" s="85"/>
-      <c r="D127" s="85"/>
-      <c r="E127" s="85"/>
-      <c r="F127" s="85"/>
-      <c r="G127" s="85"/>
-      <c r="H127" s="85"/>
-      <c r="I127" s="85"/>
-      <c r="J127" s="85"/>
-      <c r="K127" s="85"/>
-      <c r="L127" s="85"/>
-      <c r="M127" s="85"/>
-      <c r="N127" s="85"/>
-      <c r="O127" s="85"/>
-      <c r="P127" s="85"/>
-      <c r="Q127" s="85"/>
-    </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A128" s="85"/>
-      <c r="B128" s="85"/>
-      <c r="C128" s="85"/>
-      <c r="D128" s="85"/>
-      <c r="E128" s="85"/>
-      <c r="F128" s="85"/>
-      <c r="G128" s="85"/>
-      <c r="H128" s="85"/>
-      <c r="I128" s="85"/>
-      <c r="J128" s="85"/>
-      <c r="K128" s="85"/>
-      <c r="L128" s="85"/>
-      <c r="M128" s="85"/>
-      <c r="N128" s="85"/>
-      <c r="O128" s="85"/>
-      <c r="P128" s="85"/>
-      <c r="Q128" s="85"/>
-    </row>
-    <row r="129" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B127" s="86"/>
+      <c r="C127" s="86"/>
+      <c r="D127" s="86"/>
+      <c r="E127" s="86"/>
+      <c r="F127" s="86"/>
+      <c r="G127" s="86"/>
+      <c r="H127" s="86"/>
+      <c r="I127" s="86"/>
+      <c r="J127" s="86"/>
+      <c r="K127" s="86"/>
+      <c r="L127" s="86"/>
+      <c r="M127" s="86"/>
+      <c r="N127" s="86"/>
+      <c r="O127" s="86"/>
+      <c r="P127" s="86"/>
+      <c r="Q127" s="86"/>
+    </row>
+    <row r="128" spans="1:17">
+      <c r="A128" s="86"/>
+      <c r="B128" s="86"/>
+      <c r="C128" s="86"/>
+      <c r="D128" s="86"/>
+      <c r="E128" s="86"/>
+      <c r="F128" s="86"/>
+      <c r="G128" s="86"/>
+      <c r="H128" s="86"/>
+      <c r="I128" s="86"/>
+      <c r="J128" s="86"/>
+      <c r="K128" s="86"/>
+      <c r="L128" s="86"/>
+      <c r="M128" s="86"/>
+      <c r="N128" s="86"/>
+      <c r="O128" s="86"/>
+      <c r="P128" s="86"/>
+      <c r="Q128" s="86"/>
+    </row>
+    <row r="129" spans="1:17" ht="14.45" customHeight="1">
       <c r="A129" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="B129" s="84" t="s">
+      <c r="B129" s="85" t="s">
         <v>21</v>
       </c>
-      <c r="C129" s="85"/>
-      <c r="D129" s="85"/>
-      <c r="E129" s="84" t="s">
+      <c r="C129" s="86"/>
+      <c r="D129" s="86"/>
+      <c r="E129" s="85" t="s">
         <v>22</v>
       </c>
-      <c r="F129" s="85"/>
-      <c r="G129" s="85"/>
-      <c r="H129" s="84" t="s">
+      <c r="F129" s="86"/>
+      <c r="G129" s="86"/>
+      <c r="H129" s="85" t="s">
         <v>23</v>
       </c>
-      <c r="I129" s="85"/>
-      <c r="J129" s="85"/>
-      <c r="K129" s="84" t="s">
+      <c r="I129" s="86"/>
+      <c r="J129" s="86"/>
+      <c r="K129" s="85" t="s">
         <v>24</v>
       </c>
-      <c r="L129" s="85"/>
-      <c r="M129" s="85"/>
-      <c r="N129" s="85"/>
-      <c r="O129" s="85"/>
-      <c r="P129" s="84" t="s">
+      <c r="L129" s="86"/>
+      <c r="M129" s="86"/>
+      <c r="N129" s="86"/>
+      <c r="O129" s="86"/>
+      <c r="P129" s="85" t="s">
         <v>25</v>
       </c>
-      <c r="Q129" s="84" t="s">
+      <c r="Q129" s="85" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A130" s="85"/>
+    <row r="130" spans="1:17">
+      <c r="A130" s="86"/>
       <c r="B130" s="43" t="s">
         <v>27</v>
       </c>
@@ -15580,10 +15577,10 @@
       <c r="O130" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P130" s="85"/>
-      <c r="Q130" s="85"/>
-    </row>
-    <row r="131" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P130" s="86"/>
+      <c r="Q130" s="86"/>
+    </row>
+    <row r="131" spans="1:17" ht="43.15" customHeight="1">
       <c r="A131" s="43" t="s">
         <v>880</v>
       </c>
@@ -15634,7 +15631,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="132" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:17" ht="72" customHeight="1">
       <c r="A132" s="43" t="s">
         <v>881</v>
       </c>
@@ -15685,7 +15682,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="133" spans="1:17" ht="115.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:17" ht="115.15" customHeight="1">
       <c r="A133" s="43" t="s">
         <v>882</v>
       </c>
@@ -15736,7 +15733,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="134" spans="1:17" ht="129.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:17" ht="129.6" customHeight="1">
       <c r="A134" s="43" t="s">
         <v>883</v>
       </c>
@@ -15769,7 +15766,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="135" spans="1:17" ht="129.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:17" ht="129.6" customHeight="1">
       <c r="A135" s="43" t="s">
         <v>38</v>
       </c>
@@ -15802,7 +15799,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="136" spans="1:17" ht="144" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:17" ht="144" customHeight="1">
       <c r="A136" s="43" t="s">
         <v>884</v>
       </c>
@@ -15835,7 +15832,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="137" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:17" ht="43.15" customHeight="1">
       <c r="A137" s="46" t="s">
         <v>885</v>
       </c>
@@ -15878,7 +15875,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="138" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:17" ht="30">
       <c r="A138" s="43" t="s">
         <v>886</v>
       </c>
@@ -15929,7 +15926,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="139" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:17" ht="57.6" customHeight="1">
       <c r="A139" s="43" t="s">
         <v>887</v>
       </c>
@@ -15962,7 +15959,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="140" spans="1:17" ht="86.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:17" ht="86.45" customHeight="1">
       <c r="A140" s="43" t="s">
         <v>888</v>
       </c>
@@ -15995,7 +15992,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="141" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:17" ht="57.6" customHeight="1">
       <c r="A141" s="46" t="s">
         <v>889</v>
       </c>
@@ -16038,7 +16035,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="142" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:17" ht="57.6" customHeight="1">
       <c r="A142" s="43" t="s">
         <v>890</v>
       </c>
@@ -16071,7 +16068,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="143" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:17" ht="72" customHeight="1">
       <c r="A143" s="43" t="s">
         <v>891</v>
       </c>
@@ -16104,7 +16101,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="144" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:17" ht="43.15" customHeight="1">
       <c r="A144" s="46" t="s">
         <v>892</v>
       </c>
@@ -16147,7 +16144,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="145" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:17" ht="72" customHeight="1">
       <c r="A145" s="43" t="s">
         <v>893</v>
       </c>
@@ -16180,7 +16177,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="146" spans="1:17" ht="100.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:17" ht="100.9" customHeight="1">
       <c r="A146" s="43" t="s">
         <v>894</v>
       </c>
@@ -16213,7 +16210,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="147" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:17" ht="43.15" customHeight="1">
       <c r="A147" s="46" t="s">
         <v>895</v>
       </c>
@@ -16256,7 +16253,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="148" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:17" ht="28.9" customHeight="1">
       <c r="A148" s="43" t="s">
         <v>896</v>
       </c>
@@ -16307,7 +16304,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="149" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:17" ht="57.6" customHeight="1">
       <c r="A149" s="43" t="s">
         <v>897</v>
       </c>
@@ -16340,7 +16337,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="150" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:17" ht="28.9" customHeight="1">
       <c r="A150" s="43" t="s">
         <v>898</v>
       </c>
@@ -16373,7 +16370,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="151" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:17" ht="43.15" customHeight="1">
       <c r="A151" s="46" t="s">
         <v>899</v>
       </c>
@@ -16416,7 +16413,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="152" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:17" ht="43.15" customHeight="1">
       <c r="A152" s="43" t="s">
         <v>900</v>
       </c>
@@ -16467,7 +16464,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="153" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:17" ht="28.9" customHeight="1">
       <c r="A153" s="43" t="s">
         <v>750</v>
       </c>
@@ -16518,7 +16515,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="154" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:17" ht="28.9" customHeight="1">
       <c r="A154" s="43" t="s">
         <v>901</v>
       </c>
@@ -16569,7 +16566,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="155" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:17" ht="28.9" customHeight="1">
       <c r="A155" s="43" t="s">
         <v>706</v>
       </c>
@@ -16602,7 +16599,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="156" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:17" ht="28.9" customHeight="1">
       <c r="A156" s="43" t="s">
         <v>712</v>
       </c>
@@ -16635,7 +16632,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="157" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:17" ht="28.9" customHeight="1">
       <c r="A157" s="43" t="s">
         <v>902</v>
       </c>
@@ -16668,7 +16665,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="158" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:17" ht="57.6" customHeight="1">
       <c r="A158" s="46" t="s">
         <v>903</v>
       </c>
@@ -16711,81 +16708,81 @@
         <v>17</v>
       </c>
     </row>
-    <row r="159" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A159" s="86" t="s">
+    <row r="159" spans="1:17">
+      <c r="A159" s="88" t="s">
         <v>46</v>
       </c>
-      <c r="B159" s="85"/>
-      <c r="C159" s="85"/>
-      <c r="D159" s="85"/>
-      <c r="E159" s="85"/>
-      <c r="F159" s="85"/>
-      <c r="G159" s="85"/>
-      <c r="H159" s="85"/>
-      <c r="I159" s="85"/>
-      <c r="J159" s="85"/>
-      <c r="K159" s="85"/>
-      <c r="L159" s="85"/>
-      <c r="M159" s="85"/>
-      <c r="N159" s="85"/>
-      <c r="O159" s="85"/>
-      <c r="P159" s="85"/>
-      <c r="Q159" s="85"/>
-    </row>
-    <row r="160" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A160" s="85"/>
-      <c r="B160" s="85"/>
-      <c r="C160" s="85"/>
-      <c r="D160" s="85"/>
-      <c r="E160" s="85"/>
-      <c r="F160" s="85"/>
-      <c r="G160" s="85"/>
-      <c r="H160" s="85"/>
-      <c r="I160" s="85"/>
-      <c r="J160" s="85"/>
-      <c r="K160" s="85"/>
-      <c r="L160" s="85"/>
-      <c r="M160" s="85"/>
-      <c r="N160" s="85"/>
-      <c r="O160" s="85"/>
-      <c r="P160" s="85"/>
-      <c r="Q160" s="85"/>
-    </row>
-    <row r="161" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B159" s="86"/>
+      <c r="C159" s="86"/>
+      <c r="D159" s="86"/>
+      <c r="E159" s="86"/>
+      <c r="F159" s="86"/>
+      <c r="G159" s="86"/>
+      <c r="H159" s="86"/>
+      <c r="I159" s="86"/>
+      <c r="J159" s="86"/>
+      <c r="K159" s="86"/>
+      <c r="L159" s="86"/>
+      <c r="M159" s="86"/>
+      <c r="N159" s="86"/>
+      <c r="O159" s="86"/>
+      <c r="P159" s="86"/>
+      <c r="Q159" s="86"/>
+    </row>
+    <row r="160" spans="1:17">
+      <c r="A160" s="86"/>
+      <c r="B160" s="86"/>
+      <c r="C160" s="86"/>
+      <c r="D160" s="86"/>
+      <c r="E160" s="86"/>
+      <c r="F160" s="86"/>
+      <c r="G160" s="86"/>
+      <c r="H160" s="86"/>
+      <c r="I160" s="86"/>
+      <c r="J160" s="86"/>
+      <c r="K160" s="86"/>
+      <c r="L160" s="86"/>
+      <c r="M160" s="86"/>
+      <c r="N160" s="86"/>
+      <c r="O160" s="86"/>
+      <c r="P160" s="86"/>
+      <c r="Q160" s="86"/>
+    </row>
+    <row r="161" spans="1:17" ht="14.45" customHeight="1">
       <c r="A161" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="B161" s="84" t="s">
+      <c r="B161" s="85" t="s">
         <v>21</v>
       </c>
-      <c r="C161" s="85"/>
-      <c r="D161" s="85"/>
-      <c r="E161" s="84" t="s">
+      <c r="C161" s="86"/>
+      <c r="D161" s="86"/>
+      <c r="E161" s="85" t="s">
         <v>22</v>
       </c>
-      <c r="F161" s="85"/>
-      <c r="G161" s="85"/>
-      <c r="H161" s="84" t="s">
+      <c r="F161" s="86"/>
+      <c r="G161" s="86"/>
+      <c r="H161" s="85" t="s">
         <v>23</v>
       </c>
-      <c r="I161" s="85"/>
-      <c r="J161" s="85"/>
-      <c r="K161" s="84" t="s">
+      <c r="I161" s="86"/>
+      <c r="J161" s="86"/>
+      <c r="K161" s="85" t="s">
         <v>24</v>
       </c>
-      <c r="L161" s="85"/>
-      <c r="M161" s="85"/>
-      <c r="N161" s="85"/>
-      <c r="O161" s="85"/>
-      <c r="P161" s="84" t="s">
+      <c r="L161" s="86"/>
+      <c r="M161" s="86"/>
+      <c r="N161" s="86"/>
+      <c r="O161" s="86"/>
+      <c r="P161" s="85" t="s">
         <v>25</v>
       </c>
-      <c r="Q161" s="84" t="s">
+      <c r="Q161" s="85" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="162" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A162" s="85"/>
+    <row r="162" spans="1:17">
+      <c r="A162" s="86"/>
       <c r="B162" s="43" t="s">
         <v>27</v>
       </c>
@@ -16828,10 +16825,10 @@
       <c r="O162" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P162" s="85"/>
-      <c r="Q162" s="85"/>
-    </row>
-    <row r="163" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P162" s="86"/>
+      <c r="Q162" s="86"/>
+    </row>
+    <row r="163" spans="1:17" ht="28.9" customHeight="1">
       <c r="A163" s="43" t="s">
         <v>46</v>
       </c>
@@ -16882,81 +16879,81 @@
         <v>13</v>
       </c>
     </row>
-    <row r="164" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A164" s="86" t="s">
+    <row r="164" spans="1:17">
+      <c r="A164" s="88" t="s">
         <v>69</v>
       </c>
-      <c r="B164" s="85"/>
-      <c r="C164" s="85"/>
-      <c r="D164" s="85"/>
-      <c r="E164" s="85"/>
-      <c r="F164" s="85"/>
-      <c r="G164" s="85"/>
-      <c r="H164" s="85"/>
-      <c r="I164" s="85"/>
-      <c r="J164" s="85"/>
-      <c r="K164" s="85"/>
-      <c r="L164" s="85"/>
-      <c r="M164" s="85"/>
-      <c r="N164" s="85"/>
-      <c r="O164" s="85"/>
-      <c r="P164" s="85"/>
-      <c r="Q164" s="85"/>
-    </row>
-    <row r="165" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A165" s="85"/>
-      <c r="B165" s="85"/>
-      <c r="C165" s="85"/>
-      <c r="D165" s="85"/>
-      <c r="E165" s="85"/>
-      <c r="F165" s="85"/>
-      <c r="G165" s="85"/>
-      <c r="H165" s="85"/>
-      <c r="I165" s="85"/>
-      <c r="J165" s="85"/>
-      <c r="K165" s="85"/>
-      <c r="L165" s="85"/>
-      <c r="M165" s="85"/>
-      <c r="N165" s="85"/>
-      <c r="O165" s="85"/>
-      <c r="P165" s="85"/>
-      <c r="Q165" s="85"/>
-    </row>
-    <row r="166" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B164" s="86"/>
+      <c r="C164" s="86"/>
+      <c r="D164" s="86"/>
+      <c r="E164" s="86"/>
+      <c r="F164" s="86"/>
+      <c r="G164" s="86"/>
+      <c r="H164" s="86"/>
+      <c r="I164" s="86"/>
+      <c r="J164" s="86"/>
+      <c r="K164" s="86"/>
+      <c r="L164" s="86"/>
+      <c r="M164" s="86"/>
+      <c r="N164" s="86"/>
+      <c r="O164" s="86"/>
+      <c r="P164" s="86"/>
+      <c r="Q164" s="86"/>
+    </row>
+    <row r="165" spans="1:17">
+      <c r="A165" s="86"/>
+      <c r="B165" s="86"/>
+      <c r="C165" s="86"/>
+      <c r="D165" s="86"/>
+      <c r="E165" s="86"/>
+      <c r="F165" s="86"/>
+      <c r="G165" s="86"/>
+      <c r="H165" s="86"/>
+      <c r="I165" s="86"/>
+      <c r="J165" s="86"/>
+      <c r="K165" s="86"/>
+      <c r="L165" s="86"/>
+      <c r="M165" s="86"/>
+      <c r="N165" s="86"/>
+      <c r="O165" s="86"/>
+      <c r="P165" s="86"/>
+      <c r="Q165" s="86"/>
+    </row>
+    <row r="166" spans="1:17" ht="14.45" customHeight="1">
       <c r="A166" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="B166" s="84" t="s">
+      <c r="B166" s="85" t="s">
         <v>21</v>
       </c>
-      <c r="C166" s="85"/>
-      <c r="D166" s="85"/>
-      <c r="E166" s="84" t="s">
+      <c r="C166" s="86"/>
+      <c r="D166" s="86"/>
+      <c r="E166" s="85" t="s">
         <v>22</v>
       </c>
-      <c r="F166" s="85"/>
-      <c r="G166" s="85"/>
-      <c r="H166" s="84" t="s">
+      <c r="F166" s="86"/>
+      <c r="G166" s="86"/>
+      <c r="H166" s="85" t="s">
         <v>23</v>
       </c>
-      <c r="I166" s="85"/>
-      <c r="J166" s="85"/>
-      <c r="K166" s="84" t="s">
+      <c r="I166" s="86"/>
+      <c r="J166" s="86"/>
+      <c r="K166" s="85" t="s">
         <v>24</v>
       </c>
-      <c r="L166" s="85"/>
-      <c r="M166" s="85"/>
-      <c r="N166" s="85"/>
-      <c r="O166" s="85"/>
-      <c r="P166" s="84" t="s">
+      <c r="L166" s="86"/>
+      <c r="M166" s="86"/>
+      <c r="N166" s="86"/>
+      <c r="O166" s="86"/>
+      <c r="P166" s="85" t="s">
         <v>25</v>
       </c>
-      <c r="Q166" s="84" t="s">
+      <c r="Q166" s="85" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="167" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A167" s="85"/>
+    <row r="167" spans="1:17">
+      <c r="A167" s="86"/>
       <c r="B167" s="43" t="s">
         <v>27</v>
       </c>
@@ -16999,10 +16996,10 @@
       <c r="O167" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P167" s="85"/>
-      <c r="Q167" s="85"/>
-    </row>
-    <row r="168" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P167" s="86"/>
+      <c r="Q167" s="86"/>
+    </row>
+    <row r="168" spans="1:17" ht="72" customHeight="1">
       <c r="A168" s="43" t="s">
         <v>904</v>
       </c>
@@ -17035,7 +17032,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="169" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:17" ht="57.6" customHeight="1">
       <c r="A169" s="43" t="s">
         <v>70</v>
       </c>
@@ -17068,7 +17065,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="170" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:17" ht="72" customHeight="1">
       <c r="A170" s="43" t="s">
         <v>71</v>
       </c>
@@ -17101,7 +17098,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="171" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:17" ht="57.6" customHeight="1">
       <c r="A171" s="43" t="s">
         <v>72</v>
       </c>
@@ -17134,7 +17131,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="172" spans="1:17" ht="86.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:17" ht="86.45" customHeight="1">
       <c r="A172" s="46" t="s">
         <v>905</v>
       </c>
@@ -17179,6 +17176,70 @@
     </row>
   </sheetData>
   <mergeCells count="80">
+    <mergeCell ref="P35:P36"/>
+    <mergeCell ref="E161:G161"/>
+    <mergeCell ref="K30:O30"/>
+    <mergeCell ref="A164:Q165"/>
+    <mergeCell ref="B166:D166"/>
+    <mergeCell ref="K55:O55"/>
+    <mergeCell ref="E95:G95"/>
+    <mergeCell ref="A33:Q34"/>
+    <mergeCell ref="A72:Q73"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="A53:Q54"/>
+    <mergeCell ref="H95:J95"/>
+    <mergeCell ref="P166:P167"/>
+    <mergeCell ref="A127:Q128"/>
+    <mergeCell ref="K161:O161"/>
+    <mergeCell ref="H30:J30"/>
+    <mergeCell ref="A28:Q29"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="A48:Q49"/>
+    <mergeCell ref="E83:G83"/>
+    <mergeCell ref="E35:G35"/>
+    <mergeCell ref="Q55:Q56"/>
+    <mergeCell ref="P50:P51"/>
+    <mergeCell ref="E30:G30"/>
+    <mergeCell ref="Q74:Q75"/>
+    <mergeCell ref="H35:J35"/>
+    <mergeCell ref="P30:P31"/>
+    <mergeCell ref="Q83:Q84"/>
+    <mergeCell ref="A50:A51"/>
+    <mergeCell ref="K35:O35"/>
+    <mergeCell ref="Q30:Q31"/>
+    <mergeCell ref="K50:O50"/>
+    <mergeCell ref="B161:D161"/>
+    <mergeCell ref="P129:P130"/>
+    <mergeCell ref="A166:A167"/>
+    <mergeCell ref="K74:O74"/>
+    <mergeCell ref="K83:O83"/>
+    <mergeCell ref="A74:A75"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="A129:A130"/>
+    <mergeCell ref="B83:D83"/>
+    <mergeCell ref="H166:J166"/>
+    <mergeCell ref="E129:G129"/>
+    <mergeCell ref="H161:J161"/>
+    <mergeCell ref="H129:J129"/>
+    <mergeCell ref="E74:G74"/>
+    <mergeCell ref="E166:G166"/>
+    <mergeCell ref="K95:O95"/>
+    <mergeCell ref="Q166:Q167"/>
+    <mergeCell ref="Q35:Q36"/>
+    <mergeCell ref="P161:P162"/>
+    <mergeCell ref="A159:Q160"/>
+    <mergeCell ref="A93:Q94"/>
+    <mergeCell ref="Q161:Q162"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="P83:P84"/>
+    <mergeCell ref="Q129:Q130"/>
+    <mergeCell ref="Q95:Q96"/>
+    <mergeCell ref="H50:J50"/>
+    <mergeCell ref="A161:A162"/>
+    <mergeCell ref="H55:J55"/>
+    <mergeCell ref="A83:A84"/>
+    <mergeCell ref="P55:P56"/>
     <mergeCell ref="K166:O166"/>
     <mergeCell ref="H74:J74"/>
     <mergeCell ref="H83:J83"/>
@@ -17195,70 +17256,6 @@
     <mergeCell ref="A81:Q82"/>
     <mergeCell ref="A95:A96"/>
     <mergeCell ref="B129:D129"/>
-    <mergeCell ref="Q166:Q167"/>
-    <mergeCell ref="Q35:Q36"/>
-    <mergeCell ref="P161:P162"/>
-    <mergeCell ref="A159:Q160"/>
-    <mergeCell ref="A93:Q94"/>
-    <mergeCell ref="Q161:Q162"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="P83:P84"/>
-    <mergeCell ref="Q129:Q130"/>
-    <mergeCell ref="Q95:Q96"/>
-    <mergeCell ref="H50:J50"/>
-    <mergeCell ref="A161:A162"/>
-    <mergeCell ref="H55:J55"/>
-    <mergeCell ref="A83:A84"/>
-    <mergeCell ref="P55:P56"/>
-    <mergeCell ref="B161:D161"/>
-    <mergeCell ref="P129:P130"/>
-    <mergeCell ref="A166:A167"/>
-    <mergeCell ref="K74:O74"/>
-    <mergeCell ref="K83:O83"/>
-    <mergeCell ref="A74:A75"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="A129:A130"/>
-    <mergeCell ref="B83:D83"/>
-    <mergeCell ref="H166:J166"/>
-    <mergeCell ref="E129:G129"/>
-    <mergeCell ref="H161:J161"/>
-    <mergeCell ref="H129:J129"/>
-    <mergeCell ref="E74:G74"/>
-    <mergeCell ref="E166:G166"/>
-    <mergeCell ref="K95:O95"/>
-    <mergeCell ref="A28:Q29"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="A48:Q49"/>
-    <mergeCell ref="E83:G83"/>
-    <mergeCell ref="E35:G35"/>
-    <mergeCell ref="Q55:Q56"/>
-    <mergeCell ref="P50:P51"/>
-    <mergeCell ref="E30:G30"/>
-    <mergeCell ref="Q74:Q75"/>
-    <mergeCell ref="H35:J35"/>
-    <mergeCell ref="P30:P31"/>
-    <mergeCell ref="Q83:Q84"/>
-    <mergeCell ref="A50:A51"/>
-    <mergeCell ref="K35:O35"/>
-    <mergeCell ref="Q30:Q31"/>
-    <mergeCell ref="K50:O50"/>
-    <mergeCell ref="P35:P36"/>
-    <mergeCell ref="E161:G161"/>
-    <mergeCell ref="K30:O30"/>
-    <mergeCell ref="A164:Q165"/>
-    <mergeCell ref="B166:D166"/>
-    <mergeCell ref="K55:O55"/>
-    <mergeCell ref="E95:G95"/>
-    <mergeCell ref="A33:Q34"/>
-    <mergeCell ref="A72:Q73"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="A53:Q54"/>
-    <mergeCell ref="H95:J95"/>
-    <mergeCell ref="P166:P167"/>
-    <mergeCell ref="A127:Q128"/>
-    <mergeCell ref="K161:O161"/>
-    <mergeCell ref="H30:J30"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" display="https://www.scei-concours.fr/stat2025/bcpst.html" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
@@ -17290,184 +17287,184 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:Q87"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1">
       <c r="A1" s="40"/>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1">
       <c r="A2" s="41" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1">
       <c r="A3" s="41" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1">
       <c r="A4" s="41" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1">
       <c r="A5" s="41" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1">
       <c r="A6" s="41" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1">
       <c r="A7" s="41" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1">
       <c r="A8" s="41" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1">
       <c r="A9" s="41" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1">
       <c r="A10" s="41" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1">
       <c r="A11" s="41" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" ht="15.6" customHeight="1">
       <c r="A13" s="42" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1">
       <c r="A14" s="40"/>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1">
       <c r="A15" s="41" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1">
       <c r="A16" s="41" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17">
       <c r="A17" s="41" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17">
       <c r="A18" s="41" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17">
       <c r="A19" s="41" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17">
       <c r="A20" s="41" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:17">
       <c r="A22" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:17">
       <c r="A23" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A24" s="86" t="s">
+    <row r="24" spans="1:17">
+      <c r="A24" s="88" t="s">
         <v>19</v>
       </c>
-      <c r="B24" s="85"/>
-      <c r="C24" s="85"/>
-      <c r="D24" s="85"/>
-      <c r="E24" s="85"/>
-      <c r="F24" s="85"/>
-      <c r="G24" s="85"/>
-      <c r="H24" s="85"/>
-      <c r="I24" s="85"/>
-      <c r="J24" s="85"/>
-      <c r="K24" s="85"/>
-      <c r="L24" s="85"/>
-      <c r="M24" s="85"/>
-      <c r="N24" s="85"/>
-      <c r="O24" s="85"/>
-      <c r="P24" s="85"/>
-      <c r="Q24" s="85"/>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A25" s="85"/>
-      <c r="B25" s="85"/>
-      <c r="C25" s="85"/>
-      <c r="D25" s="85"/>
-      <c r="E25" s="85"/>
-      <c r="F25" s="85"/>
-      <c r="G25" s="85"/>
-      <c r="H25" s="85"/>
-      <c r="I25" s="85"/>
-      <c r="J25" s="85"/>
-      <c r="K25" s="85"/>
-      <c r="L25" s="85"/>
-      <c r="M25" s="85"/>
-      <c r="N25" s="85"/>
-      <c r="O25" s="85"/>
-      <c r="P25" s="85"/>
-      <c r="Q25" s="85"/>
-    </row>
-    <row r="26" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="86"/>
+      <c r="C24" s="86"/>
+      <c r="D24" s="86"/>
+      <c r="E24" s="86"/>
+      <c r="F24" s="86"/>
+      <c r="G24" s="86"/>
+      <c r="H24" s="86"/>
+      <c r="I24" s="86"/>
+      <c r="J24" s="86"/>
+      <c r="K24" s="86"/>
+      <c r="L24" s="86"/>
+      <c r="M24" s="86"/>
+      <c r="N24" s="86"/>
+      <c r="O24" s="86"/>
+      <c r="P24" s="86"/>
+      <c r="Q24" s="86"/>
+    </row>
+    <row r="25" spans="1:17">
+      <c r="A25" s="86"/>
+      <c r="B25" s="86"/>
+      <c r="C25" s="86"/>
+      <c r="D25" s="86"/>
+      <c r="E25" s="86"/>
+      <c r="F25" s="86"/>
+      <c r="G25" s="86"/>
+      <c r="H25" s="86"/>
+      <c r="I25" s="86"/>
+      <c r="J25" s="86"/>
+      <c r="K25" s="86"/>
+      <c r="L25" s="86"/>
+      <c r="M25" s="86"/>
+      <c r="N25" s="86"/>
+      <c r="O25" s="86"/>
+      <c r="P25" s="86"/>
+      <c r="Q25" s="86"/>
+    </row>
+    <row r="26" spans="1:17" ht="14.45" customHeight="1">
       <c r="A26" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="B26" s="84" t="s">
+      <c r="B26" s="85" t="s">
         <v>21</v>
       </c>
-      <c r="C26" s="85"/>
-      <c r="D26" s="85"/>
-      <c r="E26" s="84" t="s">
+      <c r="C26" s="86"/>
+      <c r="D26" s="86"/>
+      <c r="E26" s="85" t="s">
         <v>22</v>
       </c>
-      <c r="F26" s="85"/>
-      <c r="G26" s="85"/>
-      <c r="H26" s="84" t="s">
+      <c r="F26" s="86"/>
+      <c r="G26" s="86"/>
+      <c r="H26" s="85" t="s">
         <v>23</v>
       </c>
-      <c r="I26" s="85"/>
-      <c r="J26" s="85"/>
-      <c r="K26" s="84" t="s">
+      <c r="I26" s="86"/>
+      <c r="J26" s="86"/>
+      <c r="K26" s="85" t="s">
         <v>24</v>
       </c>
-      <c r="L26" s="85"/>
-      <c r="M26" s="85"/>
-      <c r="N26" s="85"/>
-      <c r="O26" s="85"/>
-      <c r="P26" s="84" t="s">
+      <c r="L26" s="86"/>
+      <c r="M26" s="86"/>
+      <c r="N26" s="86"/>
+      <c r="O26" s="86"/>
+      <c r="P26" s="85" t="s">
         <v>25</v>
       </c>
-      <c r="Q26" s="84" t="s">
+      <c r="Q26" s="85" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A27" s="85"/>
+    <row r="27" spans="1:17">
+      <c r="A27" s="86"/>
       <c r="B27" s="43" t="s">
         <v>27</v>
       </c>
@@ -17510,10 +17507,10 @@
       <c r="O27" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P27" s="85"/>
-      <c r="Q27" s="85"/>
-    </row>
-    <row r="28" spans="1:17" ht="115.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P27" s="86"/>
+      <c r="Q27" s="86"/>
+    </row>
+    <row r="28" spans="1:17" ht="115.15" customHeight="1">
       <c r="A28" s="43" t="s">
         <v>31</v>
       </c>
@@ -17546,7 +17543,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="144" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:17" ht="144" customHeight="1">
       <c r="A29" s="43" t="s">
         <v>32</v>
       </c>
@@ -17579,7 +17576,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="129.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:17" ht="129.6" customHeight="1">
       <c r="A30" s="43" t="s">
         <v>33</v>
       </c>
@@ -17612,7 +17609,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:17" ht="28.9" customHeight="1">
       <c r="A31" s="43" t="s">
         <v>34</v>
       </c>
@@ -17645,7 +17642,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="32" spans="1:17" ht="144" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:17" ht="144" customHeight="1">
       <c r="A32" s="43" t="s">
         <v>35</v>
       </c>
@@ -17678,7 +17675,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:17" ht="100.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:17" ht="100.9" customHeight="1">
       <c r="A33" s="43" t="s">
         <v>36</v>
       </c>
@@ -17711,7 +17708,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:17" ht="43.15" customHeight="1">
       <c r="A34" s="43" t="s">
         <v>37</v>
       </c>
@@ -17744,7 +17741,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="129.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:17" ht="129.6" customHeight="1">
       <c r="A35" s="43" t="s">
         <v>38</v>
       </c>
@@ -17777,7 +17774,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:17" ht="28.9" customHeight="1">
       <c r="A36" s="43" t="s">
         <v>39</v>
       </c>
@@ -17810,7 +17807,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="37" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:17" ht="43.15" customHeight="1">
       <c r="A37" s="43" t="s">
         <v>40</v>
       </c>
@@ -17843,7 +17840,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="1:17" ht="100.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:17" ht="100.9" customHeight="1">
       <c r="A38" s="43" t="s">
         <v>41</v>
       </c>
@@ -17876,7 +17873,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:17" ht="72" customHeight="1">
       <c r="A39" s="43" t="s">
         <v>42</v>
       </c>
@@ -17909,7 +17906,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="40" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:17" ht="72" customHeight="1">
       <c r="A40" s="43" t="s">
         <v>43</v>
       </c>
@@ -17942,7 +17939,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="1:17" ht="115.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:17" ht="115.15" customHeight="1">
       <c r="A41" s="43" t="s">
         <v>44</v>
       </c>
@@ -17975,7 +17972,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:17" ht="28.9" customHeight="1">
       <c r="A42" s="46" t="s">
         <v>45</v>
       </c>
@@ -18018,81 +18015,81 @@
         <v>72</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A43" s="86" t="s">
+    <row r="43" spans="1:17">
+      <c r="A43" s="88" t="s">
         <v>46</v>
       </c>
-      <c r="B43" s="85"/>
-      <c r="C43" s="85"/>
-      <c r="D43" s="85"/>
-      <c r="E43" s="85"/>
-      <c r="F43" s="85"/>
-      <c r="G43" s="85"/>
-      <c r="H43" s="85"/>
-      <c r="I43" s="85"/>
-      <c r="J43" s="85"/>
-      <c r="K43" s="85"/>
-      <c r="L43" s="85"/>
-      <c r="M43" s="85"/>
-      <c r="N43" s="85"/>
-      <c r="O43" s="85"/>
-      <c r="P43" s="85"/>
-      <c r="Q43" s="85"/>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A44" s="85"/>
-      <c r="B44" s="85"/>
-      <c r="C44" s="85"/>
-      <c r="D44" s="85"/>
-      <c r="E44" s="85"/>
-      <c r="F44" s="85"/>
-      <c r="G44" s="85"/>
-      <c r="H44" s="85"/>
-      <c r="I44" s="85"/>
-      <c r="J44" s="85"/>
-      <c r="K44" s="85"/>
-      <c r="L44" s="85"/>
-      <c r="M44" s="85"/>
-      <c r="N44" s="85"/>
-      <c r="O44" s="85"/>
-      <c r="P44" s="85"/>
-      <c r="Q44" s="85"/>
-    </row>
-    <row r="45" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="86"/>
+      <c r="C43" s="86"/>
+      <c r="D43" s="86"/>
+      <c r="E43" s="86"/>
+      <c r="F43" s="86"/>
+      <c r="G43" s="86"/>
+      <c r="H43" s="86"/>
+      <c r="I43" s="86"/>
+      <c r="J43" s="86"/>
+      <c r="K43" s="86"/>
+      <c r="L43" s="86"/>
+      <c r="M43" s="86"/>
+      <c r="N43" s="86"/>
+      <c r="O43" s="86"/>
+      <c r="P43" s="86"/>
+      <c r="Q43" s="86"/>
+    </row>
+    <row r="44" spans="1:17">
+      <c r="A44" s="86"/>
+      <c r="B44" s="86"/>
+      <c r="C44" s="86"/>
+      <c r="D44" s="86"/>
+      <c r="E44" s="86"/>
+      <c r="F44" s="86"/>
+      <c r="G44" s="86"/>
+      <c r="H44" s="86"/>
+      <c r="I44" s="86"/>
+      <c r="J44" s="86"/>
+      <c r="K44" s="86"/>
+      <c r="L44" s="86"/>
+      <c r="M44" s="86"/>
+      <c r="N44" s="86"/>
+      <c r="O44" s="86"/>
+      <c r="P44" s="86"/>
+      <c r="Q44" s="86"/>
+    </row>
+    <row r="45" spans="1:17" ht="14.45" customHeight="1">
       <c r="A45" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="B45" s="84" t="s">
+      <c r="B45" s="85" t="s">
         <v>21</v>
       </c>
-      <c r="C45" s="85"/>
-      <c r="D45" s="85"/>
-      <c r="E45" s="84" t="s">
+      <c r="C45" s="86"/>
+      <c r="D45" s="86"/>
+      <c r="E45" s="85" t="s">
         <v>22</v>
       </c>
-      <c r="F45" s="85"/>
-      <c r="G45" s="85"/>
-      <c r="H45" s="84" t="s">
+      <c r="F45" s="86"/>
+      <c r="G45" s="86"/>
+      <c r="H45" s="85" t="s">
         <v>23</v>
       </c>
-      <c r="I45" s="85"/>
-      <c r="J45" s="85"/>
-      <c r="K45" s="84" t="s">
+      <c r="I45" s="86"/>
+      <c r="J45" s="86"/>
+      <c r="K45" s="85" t="s">
         <v>24</v>
       </c>
-      <c r="L45" s="85"/>
-      <c r="M45" s="85"/>
-      <c r="N45" s="85"/>
-      <c r="O45" s="85"/>
-      <c r="P45" s="84" t="s">
+      <c r="L45" s="86"/>
+      <c r="M45" s="86"/>
+      <c r="N45" s="86"/>
+      <c r="O45" s="86"/>
+      <c r="P45" s="85" t="s">
         <v>25</v>
       </c>
-      <c r="Q45" s="84" t="s">
+      <c r="Q45" s="85" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A46" s="85"/>
+    <row r="46" spans="1:17">
+      <c r="A46" s="86"/>
       <c r="B46" s="43" t="s">
         <v>27</v>
       </c>
@@ -18135,10 +18132,10 @@
       <c r="O46" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P46" s="85"/>
-      <c r="Q46" s="85"/>
-    </row>
-    <row r="47" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P46" s="86"/>
+      <c r="Q46" s="86"/>
+    </row>
+    <row r="47" spans="1:17" ht="28.9" customHeight="1">
       <c r="A47" s="43" t="s">
         <v>46</v>
       </c>
@@ -18189,81 +18186,81 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A48" s="86" t="s">
+    <row r="48" spans="1:17">
+      <c r="A48" s="88" t="s">
         <v>47</v>
       </c>
-      <c r="B48" s="85"/>
-      <c r="C48" s="85"/>
-      <c r="D48" s="85"/>
-      <c r="E48" s="85"/>
-      <c r="F48" s="85"/>
-      <c r="G48" s="85"/>
-      <c r="H48" s="85"/>
-      <c r="I48" s="85"/>
-      <c r="J48" s="85"/>
-      <c r="K48" s="85"/>
-      <c r="L48" s="85"/>
-      <c r="M48" s="85"/>
-      <c r="N48" s="85"/>
-      <c r="O48" s="85"/>
-      <c r="P48" s="85"/>
-      <c r="Q48" s="85"/>
-    </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A49" s="85"/>
-      <c r="B49" s="85"/>
-      <c r="C49" s="85"/>
-      <c r="D49" s="85"/>
-      <c r="E49" s="85"/>
-      <c r="F49" s="85"/>
-      <c r="G49" s="85"/>
-      <c r="H49" s="85"/>
-      <c r="I49" s="85"/>
-      <c r="J49" s="85"/>
-      <c r="K49" s="85"/>
-      <c r="L49" s="85"/>
-      <c r="M49" s="85"/>
-      <c r="N49" s="85"/>
-      <c r="O49" s="85"/>
-      <c r="P49" s="85"/>
-      <c r="Q49" s="85"/>
-    </row>
-    <row r="50" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B48" s="86"/>
+      <c r="C48" s="86"/>
+      <c r="D48" s="86"/>
+      <c r="E48" s="86"/>
+      <c r="F48" s="86"/>
+      <c r="G48" s="86"/>
+      <c r="H48" s="86"/>
+      <c r="I48" s="86"/>
+      <c r="J48" s="86"/>
+      <c r="K48" s="86"/>
+      <c r="L48" s="86"/>
+      <c r="M48" s="86"/>
+      <c r="N48" s="86"/>
+      <c r="O48" s="86"/>
+      <c r="P48" s="86"/>
+      <c r="Q48" s="86"/>
+    </row>
+    <row r="49" spans="1:17">
+      <c r="A49" s="86"/>
+      <c r="B49" s="86"/>
+      <c r="C49" s="86"/>
+      <c r="D49" s="86"/>
+      <c r="E49" s="86"/>
+      <c r="F49" s="86"/>
+      <c r="G49" s="86"/>
+      <c r="H49" s="86"/>
+      <c r="I49" s="86"/>
+      <c r="J49" s="86"/>
+      <c r="K49" s="86"/>
+      <c r="L49" s="86"/>
+      <c r="M49" s="86"/>
+      <c r="N49" s="86"/>
+      <c r="O49" s="86"/>
+      <c r="P49" s="86"/>
+      <c r="Q49" s="86"/>
+    </row>
+    <row r="50" spans="1:17" ht="14.45" customHeight="1">
       <c r="A50" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="B50" s="84" t="s">
+      <c r="B50" s="85" t="s">
         <v>21</v>
       </c>
-      <c r="C50" s="85"/>
-      <c r="D50" s="85"/>
-      <c r="E50" s="84" t="s">
+      <c r="C50" s="86"/>
+      <c r="D50" s="86"/>
+      <c r="E50" s="85" t="s">
         <v>22</v>
       </c>
-      <c r="F50" s="85"/>
-      <c r="G50" s="85"/>
-      <c r="H50" s="84" t="s">
+      <c r="F50" s="86"/>
+      <c r="G50" s="86"/>
+      <c r="H50" s="85" t="s">
         <v>23</v>
       </c>
-      <c r="I50" s="85"/>
-      <c r="J50" s="85"/>
-      <c r="K50" s="84" t="s">
+      <c r="I50" s="86"/>
+      <c r="J50" s="86"/>
+      <c r="K50" s="85" t="s">
         <v>24</v>
       </c>
-      <c r="L50" s="85"/>
-      <c r="M50" s="85"/>
-      <c r="N50" s="85"/>
-      <c r="O50" s="85"/>
-      <c r="P50" s="84" t="s">
+      <c r="L50" s="86"/>
+      <c r="M50" s="86"/>
+      <c r="N50" s="86"/>
+      <c r="O50" s="86"/>
+      <c r="P50" s="85" t="s">
         <v>25</v>
       </c>
-      <c r="Q50" s="84" t="s">
+      <c r="Q50" s="85" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A51" s="85"/>
+    <row r="51" spans="1:17">
+      <c r="A51" s="86"/>
       <c r="B51" s="43" t="s">
         <v>27</v>
       </c>
@@ -18306,10 +18303,10 @@
       <c r="O51" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P51" s="85"/>
-      <c r="Q51" s="85"/>
-    </row>
-    <row r="52" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P51" s="86"/>
+      <c r="Q51" s="86"/>
+    </row>
+    <row r="52" spans="1:17" ht="57.6" customHeight="1">
       <c r="A52" s="43" t="s">
         <v>48</v>
       </c>
@@ -18342,7 +18339,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:17" ht="57.6" customHeight="1">
       <c r="A53" s="43" t="s">
         <v>49</v>
       </c>
@@ -18375,7 +18372,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="54" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:17" ht="72" customHeight="1">
       <c r="A54" s="43" t="s">
         <v>50</v>
       </c>
@@ -18408,7 +18405,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:17" ht="43.15" customHeight="1">
       <c r="A55" s="43" t="s">
         <v>51</v>
       </c>
@@ -18441,7 +18438,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:17" ht="28.9" customHeight="1">
       <c r="A56" s="46" t="s">
         <v>52</v>
       </c>
@@ -18484,81 +18481,81 @@
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A57" s="86" t="s">
+    <row r="57" spans="1:17">
+      <c r="A57" s="88" t="s">
         <v>53</v>
       </c>
-      <c r="B57" s="85"/>
-      <c r="C57" s="85"/>
-      <c r="D57" s="85"/>
-      <c r="E57" s="85"/>
-      <c r="F57" s="85"/>
-      <c r="G57" s="85"/>
-      <c r="H57" s="85"/>
-      <c r="I57" s="85"/>
-      <c r="J57" s="85"/>
-      <c r="K57" s="85"/>
-      <c r="L57" s="85"/>
-      <c r="M57" s="85"/>
-      <c r="N57" s="85"/>
-      <c r="O57" s="85"/>
-      <c r="P57" s="85"/>
-      <c r="Q57" s="85"/>
-    </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A58" s="85"/>
-      <c r="B58" s="85"/>
-      <c r="C58" s="85"/>
-      <c r="D58" s="85"/>
-      <c r="E58" s="85"/>
-      <c r="F58" s="85"/>
-      <c r="G58" s="85"/>
-      <c r="H58" s="85"/>
-      <c r="I58" s="85"/>
-      <c r="J58" s="85"/>
-      <c r="K58" s="85"/>
-      <c r="L58" s="85"/>
-      <c r="M58" s="85"/>
-      <c r="N58" s="85"/>
-      <c r="O58" s="85"/>
-      <c r="P58" s="85"/>
-      <c r="Q58" s="85"/>
-    </row>
-    <row r="59" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B57" s="86"/>
+      <c r="C57" s="86"/>
+      <c r="D57" s="86"/>
+      <c r="E57" s="86"/>
+      <c r="F57" s="86"/>
+      <c r="G57" s="86"/>
+      <c r="H57" s="86"/>
+      <c r="I57" s="86"/>
+      <c r="J57" s="86"/>
+      <c r="K57" s="86"/>
+      <c r="L57" s="86"/>
+      <c r="M57" s="86"/>
+      <c r="N57" s="86"/>
+      <c r="O57" s="86"/>
+      <c r="P57" s="86"/>
+      <c r="Q57" s="86"/>
+    </row>
+    <row r="58" spans="1:17">
+      <c r="A58" s="86"/>
+      <c r="B58" s="86"/>
+      <c r="C58" s="86"/>
+      <c r="D58" s="86"/>
+      <c r="E58" s="86"/>
+      <c r="F58" s="86"/>
+      <c r="G58" s="86"/>
+      <c r="H58" s="86"/>
+      <c r="I58" s="86"/>
+      <c r="J58" s="86"/>
+      <c r="K58" s="86"/>
+      <c r="L58" s="86"/>
+      <c r="M58" s="86"/>
+      <c r="N58" s="86"/>
+      <c r="O58" s="86"/>
+      <c r="P58" s="86"/>
+      <c r="Q58" s="86"/>
+    </row>
+    <row r="59" spans="1:17" ht="14.45" customHeight="1">
       <c r="A59" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="B59" s="84" t="s">
+      <c r="B59" s="85" t="s">
         <v>21</v>
       </c>
-      <c r="C59" s="85"/>
-      <c r="D59" s="85"/>
-      <c r="E59" s="84" t="s">
+      <c r="C59" s="86"/>
+      <c r="D59" s="86"/>
+      <c r="E59" s="85" t="s">
         <v>22</v>
       </c>
-      <c r="F59" s="85"/>
-      <c r="G59" s="85"/>
-      <c r="H59" s="84" t="s">
+      <c r="F59" s="86"/>
+      <c r="G59" s="86"/>
+      <c r="H59" s="85" t="s">
         <v>23</v>
       </c>
-      <c r="I59" s="85"/>
-      <c r="J59" s="85"/>
-      <c r="K59" s="84" t="s">
+      <c r="I59" s="86"/>
+      <c r="J59" s="86"/>
+      <c r="K59" s="85" t="s">
         <v>24</v>
       </c>
-      <c r="L59" s="85"/>
-      <c r="M59" s="85"/>
-      <c r="N59" s="85"/>
-      <c r="O59" s="85"/>
-      <c r="P59" s="84" t="s">
+      <c r="L59" s="86"/>
+      <c r="M59" s="86"/>
+      <c r="N59" s="86"/>
+      <c r="O59" s="86"/>
+      <c r="P59" s="85" t="s">
         <v>25</v>
       </c>
-      <c r="Q59" s="84" t="s">
+      <c r="Q59" s="85" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A60" s="85"/>
+    <row r="60" spans="1:17">
+      <c r="A60" s="86"/>
       <c r="B60" s="43" t="s">
         <v>27</v>
       </c>
@@ -18601,10 +18598,10 @@
       <c r="O60" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P60" s="85"/>
-      <c r="Q60" s="85"/>
-    </row>
-    <row r="61" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P60" s="86"/>
+      <c r="Q60" s="86"/>
+    </row>
+    <row r="61" spans="1:17" ht="57.6" customHeight="1">
       <c r="A61" s="43" t="s">
         <v>54</v>
       </c>
@@ -18637,7 +18634,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:17" ht="72" customHeight="1">
       <c r="A62" s="43" t="s">
         <v>55</v>
       </c>
@@ -18670,7 +18667,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:17" ht="28.9" customHeight="1">
       <c r="A63" s="43" t="s">
         <v>56</v>
       </c>
@@ -18703,7 +18700,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="115.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:17" ht="115.15" customHeight="1">
       <c r="A64" s="43" t="s">
         <v>57</v>
       </c>
@@ -18736,7 +18733,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:17" ht="43.15" customHeight="1">
       <c r="A65" s="43" t="s">
         <v>58</v>
       </c>
@@ -18769,7 +18766,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:17" ht="57.6" customHeight="1">
       <c r="A66" s="43" t="s">
         <v>59</v>
       </c>
@@ -18802,7 +18799,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:17" ht="72" customHeight="1">
       <c r="A67" s="43" t="s">
         <v>60</v>
       </c>
@@ -18835,7 +18832,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:17" ht="57.6" customHeight="1">
       <c r="A68" s="43" t="s">
         <v>61</v>
       </c>
@@ -18868,7 +18865,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:17" ht="57.6" customHeight="1">
       <c r="A69" s="43" t="s">
         <v>62</v>
       </c>
@@ -18901,7 +18898,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:17" ht="86.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:17" ht="86.45" customHeight="1">
       <c r="A70" s="43" t="s">
         <v>63</v>
       </c>
@@ -18934,7 +18931,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" ht="57.6" customHeight="1">
       <c r="A71" s="43" t="s">
         <v>64</v>
       </c>
@@ -18967,7 +18964,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:17" ht="72" customHeight="1">
       <c r="A72" s="43" t="s">
         <v>65</v>
       </c>
@@ -19000,7 +18997,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:17" ht="57.6" customHeight="1">
       <c r="A73" s="43" t="s">
         <v>66</v>
       </c>
@@ -19033,7 +19030,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:17" ht="43.15" customHeight="1">
       <c r="A74" s="46" t="s">
         <v>53</v>
       </c>
@@ -19076,81 +19073,81 @@
         <v>13</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A75" s="86" t="s">
+    <row r="75" spans="1:17">
+      <c r="A75" s="88" t="s">
         <v>67</v>
       </c>
-      <c r="B75" s="85"/>
-      <c r="C75" s="85"/>
-      <c r="D75" s="85"/>
-      <c r="E75" s="85"/>
-      <c r="F75" s="85"/>
-      <c r="G75" s="85"/>
-      <c r="H75" s="85"/>
-      <c r="I75" s="85"/>
-      <c r="J75" s="85"/>
-      <c r="K75" s="85"/>
-      <c r="L75" s="85"/>
-      <c r="M75" s="85"/>
-      <c r="N75" s="85"/>
-      <c r="O75" s="85"/>
-      <c r="P75" s="85"/>
-      <c r="Q75" s="85"/>
-    </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A76" s="85"/>
-      <c r="B76" s="85"/>
-      <c r="C76" s="85"/>
-      <c r="D76" s="85"/>
-      <c r="E76" s="85"/>
-      <c r="F76" s="85"/>
-      <c r="G76" s="85"/>
-      <c r="H76" s="85"/>
-      <c r="I76" s="85"/>
-      <c r="J76" s="85"/>
-      <c r="K76" s="85"/>
-      <c r="L76" s="85"/>
-      <c r="M76" s="85"/>
-      <c r="N76" s="85"/>
-      <c r="O76" s="85"/>
-      <c r="P76" s="85"/>
-      <c r="Q76" s="85"/>
-    </row>
-    <row r="77" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B75" s="86"/>
+      <c r="C75" s="86"/>
+      <c r="D75" s="86"/>
+      <c r="E75" s="86"/>
+      <c r="F75" s="86"/>
+      <c r="G75" s="86"/>
+      <c r="H75" s="86"/>
+      <c r="I75" s="86"/>
+      <c r="J75" s="86"/>
+      <c r="K75" s="86"/>
+      <c r="L75" s="86"/>
+      <c r="M75" s="86"/>
+      <c r="N75" s="86"/>
+      <c r="O75" s="86"/>
+      <c r="P75" s="86"/>
+      <c r="Q75" s="86"/>
+    </row>
+    <row r="76" spans="1:17">
+      <c r="A76" s="86"/>
+      <c r="B76" s="86"/>
+      <c r="C76" s="86"/>
+      <c r="D76" s="86"/>
+      <c r="E76" s="86"/>
+      <c r="F76" s="86"/>
+      <c r="G76" s="86"/>
+      <c r="H76" s="86"/>
+      <c r="I76" s="86"/>
+      <c r="J76" s="86"/>
+      <c r="K76" s="86"/>
+      <c r="L76" s="86"/>
+      <c r="M76" s="86"/>
+      <c r="N76" s="86"/>
+      <c r="O76" s="86"/>
+      <c r="P76" s="86"/>
+      <c r="Q76" s="86"/>
+    </row>
+    <row r="77" spans="1:17" ht="14.45" customHeight="1">
       <c r="A77" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="B77" s="84" t="s">
+      <c r="B77" s="85" t="s">
         <v>21</v>
       </c>
-      <c r="C77" s="85"/>
-      <c r="D77" s="85"/>
-      <c r="E77" s="84" t="s">
+      <c r="C77" s="86"/>
+      <c r="D77" s="86"/>
+      <c r="E77" s="85" t="s">
         <v>22</v>
       </c>
-      <c r="F77" s="85"/>
-      <c r="G77" s="85"/>
-      <c r="H77" s="84" t="s">
+      <c r="F77" s="86"/>
+      <c r="G77" s="86"/>
+      <c r="H77" s="85" t="s">
         <v>23</v>
       </c>
-      <c r="I77" s="85"/>
-      <c r="J77" s="85"/>
-      <c r="K77" s="84" t="s">
+      <c r="I77" s="86"/>
+      <c r="J77" s="86"/>
+      <c r="K77" s="85" t="s">
         <v>24</v>
       </c>
-      <c r="L77" s="85"/>
-      <c r="M77" s="85"/>
-      <c r="N77" s="85"/>
-      <c r="O77" s="85"/>
-      <c r="P77" s="84" t="s">
+      <c r="L77" s="86"/>
+      <c r="M77" s="86"/>
+      <c r="N77" s="86"/>
+      <c r="O77" s="86"/>
+      <c r="P77" s="85" t="s">
         <v>25</v>
       </c>
-      <c r="Q77" s="84" t="s">
+      <c r="Q77" s="85" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A78" s="85"/>
+    <row r="78" spans="1:17">
+      <c r="A78" s="86"/>
       <c r="B78" s="43" t="s">
         <v>27</v>
       </c>
@@ -19193,10 +19190,10 @@
       <c r="O78" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P78" s="85"/>
-      <c r="Q78" s="85"/>
-    </row>
-    <row r="79" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P78" s="86"/>
+      <c r="Q78" s="86"/>
+    </row>
+    <row r="79" spans="1:17" ht="28.9" customHeight="1">
       <c r="A79" s="43" t="s">
         <v>68</v>
       </c>
@@ -19247,81 +19244,81 @@
         <v>2</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A80" s="86" t="s">
+    <row r="80" spans="1:17">
+      <c r="A80" s="88" t="s">
         <v>69</v>
       </c>
-      <c r="B80" s="85"/>
-      <c r="C80" s="85"/>
-      <c r="D80" s="85"/>
-      <c r="E80" s="85"/>
-      <c r="F80" s="85"/>
-      <c r="G80" s="85"/>
-      <c r="H80" s="85"/>
-      <c r="I80" s="85"/>
-      <c r="J80" s="85"/>
-      <c r="K80" s="85"/>
-      <c r="L80" s="85"/>
-      <c r="M80" s="85"/>
-      <c r="N80" s="85"/>
-      <c r="O80" s="85"/>
-      <c r="P80" s="85"/>
-      <c r="Q80" s="85"/>
-    </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A81" s="85"/>
-      <c r="B81" s="85"/>
-      <c r="C81" s="85"/>
-      <c r="D81" s="85"/>
-      <c r="E81" s="85"/>
-      <c r="F81" s="85"/>
-      <c r="G81" s="85"/>
-      <c r="H81" s="85"/>
-      <c r="I81" s="85"/>
-      <c r="J81" s="85"/>
-      <c r="K81" s="85"/>
-      <c r="L81" s="85"/>
-      <c r="M81" s="85"/>
-      <c r="N81" s="85"/>
-      <c r="O81" s="85"/>
-      <c r="P81" s="85"/>
-      <c r="Q81" s="85"/>
-    </row>
-    <row r="82" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B80" s="86"/>
+      <c r="C80" s="86"/>
+      <c r="D80" s="86"/>
+      <c r="E80" s="86"/>
+      <c r="F80" s="86"/>
+      <c r="G80" s="86"/>
+      <c r="H80" s="86"/>
+      <c r="I80" s="86"/>
+      <c r="J80" s="86"/>
+      <c r="K80" s="86"/>
+      <c r="L80" s="86"/>
+      <c r="M80" s="86"/>
+      <c r="N80" s="86"/>
+      <c r="O80" s="86"/>
+      <c r="P80" s="86"/>
+      <c r="Q80" s="86"/>
+    </row>
+    <row r="81" spans="1:17">
+      <c r="A81" s="86"/>
+      <c r="B81" s="86"/>
+      <c r="C81" s="86"/>
+      <c r="D81" s="86"/>
+      <c r="E81" s="86"/>
+      <c r="F81" s="86"/>
+      <c r="G81" s="86"/>
+      <c r="H81" s="86"/>
+      <c r="I81" s="86"/>
+      <c r="J81" s="86"/>
+      <c r="K81" s="86"/>
+      <c r="L81" s="86"/>
+      <c r="M81" s="86"/>
+      <c r="N81" s="86"/>
+      <c r="O81" s="86"/>
+      <c r="P81" s="86"/>
+      <c r="Q81" s="86"/>
+    </row>
+    <row r="82" spans="1:17" ht="14.45" customHeight="1">
       <c r="A82" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="B82" s="84" t="s">
+      <c r="B82" s="85" t="s">
         <v>21</v>
       </c>
-      <c r="C82" s="85"/>
-      <c r="D82" s="85"/>
-      <c r="E82" s="84" t="s">
+      <c r="C82" s="86"/>
+      <c r="D82" s="86"/>
+      <c r="E82" s="85" t="s">
         <v>22</v>
       </c>
-      <c r="F82" s="85"/>
-      <c r="G82" s="85"/>
-      <c r="H82" s="84" t="s">
+      <c r="F82" s="86"/>
+      <c r="G82" s="86"/>
+      <c r="H82" s="85" t="s">
         <v>23</v>
       </c>
-      <c r="I82" s="85"/>
-      <c r="J82" s="85"/>
-      <c r="K82" s="84" t="s">
+      <c r="I82" s="86"/>
+      <c r="J82" s="86"/>
+      <c r="K82" s="85" t="s">
         <v>24</v>
       </c>
-      <c r="L82" s="85"/>
-      <c r="M82" s="85"/>
-      <c r="N82" s="85"/>
-      <c r="O82" s="85"/>
-      <c r="P82" s="84" t="s">
+      <c r="L82" s="86"/>
+      <c r="M82" s="86"/>
+      <c r="N82" s="86"/>
+      <c r="O82" s="86"/>
+      <c r="P82" s="85" t="s">
         <v>25</v>
       </c>
-      <c r="Q82" s="84" t="s">
+      <c r="Q82" s="85" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A83" s="85"/>
+    <row r="83" spans="1:17">
+      <c r="A83" s="86"/>
       <c r="B83" s="43" t="s">
         <v>27</v>
       </c>
@@ -19364,10 +19361,10 @@
       <c r="O83" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P83" s="85"/>
-      <c r="Q83" s="85"/>
-    </row>
-    <row r="84" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P83" s="86"/>
+      <c r="Q83" s="86"/>
+    </row>
+    <row r="84" spans="1:17" ht="57.6" customHeight="1">
       <c r="A84" s="43" t="s">
         <v>70</v>
       </c>
@@ -19400,7 +19397,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:17" ht="72" customHeight="1">
       <c r="A85" s="43" t="s">
         <v>71</v>
       </c>
@@ -19433,7 +19430,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:17" ht="57.6" customHeight="1">
       <c r="A86" s="43" t="s">
         <v>72</v>
       </c>
@@ -19466,7 +19463,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:17" ht="72" customHeight="1">
       <c r="A87" s="46" t="s">
         <v>73</v>
       </c>
@@ -19511,6 +19508,38 @@
     </row>
   </sheetData>
   <mergeCells count="48">
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="K50:O50"/>
+    <mergeCell ref="E26:G26"/>
+    <mergeCell ref="Q50:Q51"/>
+    <mergeCell ref="A43:Q44"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="Q26:Q27"/>
+    <mergeCell ref="A45:A46"/>
+    <mergeCell ref="A50:A51"/>
+    <mergeCell ref="P50:P51"/>
+    <mergeCell ref="K45:O45"/>
+    <mergeCell ref="H45:J45"/>
+    <mergeCell ref="K26:O26"/>
+    <mergeCell ref="E45:G45"/>
+    <mergeCell ref="B45:D45"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="E50:G50"/>
+    <mergeCell ref="H59:J59"/>
+    <mergeCell ref="A75:Q76"/>
+    <mergeCell ref="P59:P60"/>
+    <mergeCell ref="E59:G59"/>
+    <mergeCell ref="A57:Q58"/>
+    <mergeCell ref="B59:D59"/>
+    <mergeCell ref="P82:P83"/>
+    <mergeCell ref="Q59:Q60"/>
+    <mergeCell ref="H77:J77"/>
+    <mergeCell ref="K59:O59"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="Q82:Q83"/>
+    <mergeCell ref="K77:O77"/>
+    <mergeCell ref="P77:P78"/>
+    <mergeCell ref="E77:G77"/>
     <mergeCell ref="A24:Q25"/>
     <mergeCell ref="K82:O82"/>
     <mergeCell ref="H50:J50"/>
@@ -19527,38 +19556,6 @@
     <mergeCell ref="H82:J82"/>
     <mergeCell ref="Q45:Q46"/>
     <mergeCell ref="A48:Q49"/>
-    <mergeCell ref="P82:P83"/>
-    <mergeCell ref="Q59:Q60"/>
-    <mergeCell ref="H77:J77"/>
-    <mergeCell ref="K59:O59"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="Q82:Q83"/>
-    <mergeCell ref="K77:O77"/>
-    <mergeCell ref="P77:P78"/>
-    <mergeCell ref="E77:G77"/>
-    <mergeCell ref="E50:G50"/>
-    <mergeCell ref="H59:J59"/>
-    <mergeCell ref="A75:Q76"/>
-    <mergeCell ref="P59:P60"/>
-    <mergeCell ref="E59:G59"/>
-    <mergeCell ref="A57:Q58"/>
-    <mergeCell ref="B59:D59"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="K50:O50"/>
-    <mergeCell ref="E26:G26"/>
-    <mergeCell ref="Q50:Q51"/>
-    <mergeCell ref="A43:Q44"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="Q26:Q27"/>
-    <mergeCell ref="A45:A46"/>
-    <mergeCell ref="A50:A51"/>
-    <mergeCell ref="P50:P51"/>
-    <mergeCell ref="K45:O45"/>
-    <mergeCell ref="H45:J45"/>
-    <mergeCell ref="K26:O26"/>
-    <mergeCell ref="E45:G45"/>
-    <mergeCell ref="B45:D45"/>
-    <mergeCell ref="B50:D50"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" display="https://www.scei-concours.fr/stat2025/tb.html" xr:uid="{00000000-0004-0000-0500-000000000000}"/>
@@ -19586,7 +19583,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:G78"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
@@ -19596,18 +19593,18 @@
     <col min="7" max="7" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="89" t="s">
+    <row r="1" spans="1:7" ht="22.15" customHeight="1">
+      <c r="A1" s="90" t="s">
         <v>906</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="85"/>
-      <c r="D1" s="85"/>
-      <c r="E1" s="85"/>
-      <c r="F1" s="85"/>
-      <c r="G1" s="85"/>
-    </row>
-    <row r="2" spans="1:7" ht="37.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="86"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="86"/>
+      <c r="F1" s="86"/>
+      <c r="G1" s="86"/>
+    </row>
+    <row r="2" spans="1:7" ht="37.9" customHeight="1">
       <c r="A2" s="48" t="s">
         <v>907</v>
       </c>
@@ -19630,7 +19627,7 @@
         <v>913</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="31.9" customHeight="1">
       <c r="A3" s="55" t="s">
         <v>914</v>
       </c>
@@ -19653,7 +19650,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A4" s="49" t="s">
         <v>126</v>
       </c>
@@ -19674,7 +19671,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A5" s="49" t="s">
         <v>37</v>
       </c>
@@ -19695,7 +19692,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A6" s="49" t="s">
         <v>122</v>
       </c>
@@ -19716,7 +19713,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A7" s="49" t="s">
         <v>212</v>
       </c>
@@ -19737,7 +19734,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A8" s="49" t="s">
         <v>700</v>
       </c>
@@ -19758,7 +19755,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A9" s="49" t="s">
         <v>104</v>
       </c>
@@ -19781,7 +19778,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A10" s="49" t="s">
         <v>104</v>
       </c>
@@ -19804,7 +19801,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A11" s="49" t="s">
         <v>104</v>
       </c>
@@ -19827,7 +19824,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A12" s="49" t="s">
         <v>99</v>
       </c>
@@ -19848,7 +19845,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A13" s="49" t="s">
         <v>99</v>
       </c>
@@ -19869,7 +19866,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A14" s="49" t="s">
         <v>283</v>
       </c>
@@ -19890,7 +19887,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A15" s="49" t="s">
         <v>188</v>
       </c>
@@ -19911,7 +19908,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A16" s="49" t="s">
         <v>112</v>
       </c>
@@ -19932,7 +19929,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A17" s="49" t="s">
         <v>115</v>
       </c>
@@ -19953,7 +19950,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A18" s="49" t="s">
         <v>345</v>
       </c>
@@ -19974,7 +19971,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A19" s="49" t="s">
         <v>142</v>
       </c>
@@ -19995,7 +19992,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A20" s="49" t="s">
         <v>258</v>
       </c>
@@ -20016,7 +20013,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A21" s="49" t="s">
         <v>370</v>
       </c>
@@ -20037,7 +20034,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A22" s="49" t="s">
         <v>794</v>
       </c>
@@ -20058,7 +20055,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A23" s="49" t="s">
         <v>805</v>
       </c>
@@ -20079,7 +20076,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A24" s="49" t="s">
         <v>810</v>
       </c>
@@ -20100,7 +20097,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A25" s="49" t="s">
         <v>800</v>
       </c>
@@ -20121,7 +20118,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A26" s="49" t="s">
         <v>815</v>
       </c>
@@ -20142,7 +20139,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A27" s="49" t="s">
         <v>820</v>
       </c>
@@ -20163,7 +20160,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A28" s="51" t="s">
         <v>126</v>
       </c>
@@ -20184,7 +20181,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A29" s="51" t="s">
         <v>283</v>
       </c>
@@ -20205,7 +20202,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A30" s="51" t="s">
         <v>188</v>
       </c>
@@ -20226,7 +20223,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A31" s="51" t="s">
         <v>104</v>
       </c>
@@ -20249,7 +20246,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A32" s="51" t="s">
         <v>104</v>
       </c>
@@ -20270,7 +20267,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A33" s="51" t="s">
         <v>37</v>
       </c>
@@ -20291,7 +20288,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A34" s="51" t="s">
         <v>232</v>
       </c>
@@ -20310,7 +20307,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A35" s="51" t="s">
         <v>122</v>
       </c>
@@ -20331,7 +20328,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A36" s="51" t="s">
         <v>212</v>
       </c>
@@ -20352,7 +20349,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A37" s="51" t="s">
         <v>99</v>
       </c>
@@ -20373,7 +20370,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A38" s="51" t="s">
         <v>99</v>
       </c>
@@ -20394,7 +20391,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A39" s="51" t="s">
         <v>115</v>
       </c>
@@ -20415,7 +20412,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A40" s="51" t="s">
         <v>112</v>
       </c>
@@ -20436,7 +20433,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A41" s="56" t="s">
         <v>345</v>
       </c>
@@ -20457,7 +20454,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A42" s="51" t="s">
         <v>142</v>
       </c>
@@ -20478,7 +20475,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A43" s="51" t="s">
         <v>258</v>
       </c>
@@ -20499,7 +20496,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A44" s="56" t="s">
         <v>370</v>
       </c>
@@ -20520,7 +20517,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A45" s="60" t="s">
         <v>745</v>
       </c>
@@ -20541,7 +20538,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A46" s="53" t="s">
         <v>232</v>
       </c>
@@ -20560,7 +20557,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A47" s="53" t="s">
         <v>88</v>
       </c>
@@ -20579,7 +20576,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A48" s="53" t="s">
         <v>88</v>
       </c>
@@ -20600,7 +20597,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A49" s="53" t="s">
         <v>88</v>
       </c>
@@ -20621,7 +20618,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A50" s="56" t="s">
         <v>740</v>
       </c>
@@ -20642,7 +20639,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A51" s="58" t="s">
         <v>750</v>
       </c>
@@ -20663,7 +20660,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A52" s="53" t="s">
         <v>706</v>
       </c>
@@ -20682,7 +20679,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A53" s="53" t="s">
         <v>712</v>
       </c>
@@ -20701,7 +20698,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A54" s="53" t="s">
         <v>718</v>
       </c>
@@ -20720,7 +20717,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A55" s="56" t="s">
         <v>136</v>
       </c>
@@ -20739,7 +20736,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A56" s="56" t="s">
         <v>136</v>
       </c>
@@ -20758,7 +20755,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A57" s="58" t="s">
         <v>340</v>
       </c>
@@ -20779,7 +20776,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A58" s="58" t="s">
         <v>340</v>
       </c>
@@ -20800,7 +20797,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A59" s="58" t="s">
         <v>169</v>
       </c>
@@ -20821,7 +20818,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A60" s="58" t="s">
         <v>91</v>
       </c>
@@ -20842,7 +20839,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A61" s="58" t="s">
         <v>91</v>
       </c>
@@ -20863,7 +20860,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A62" s="58" t="s">
         <v>194</v>
       </c>
@@ -20884,7 +20881,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A63" s="58" t="s">
         <v>194</v>
       </c>
@@ -20905,7 +20902,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="64" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A64" s="58" t="s">
         <v>145</v>
       </c>
@@ -20926,7 +20923,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A65" s="58" t="s">
         <v>145</v>
       </c>
@@ -20947,7 +20944,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="66" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A66" s="58" t="s">
         <v>85</v>
       </c>
@@ -20968,7 +20965,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A67" s="58" t="s">
         <v>322</v>
       </c>
@@ -20989,7 +20986,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="68" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A68" s="58" t="s">
         <v>322</v>
       </c>
@@ -21010,7 +21007,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="69" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A69" s="58" t="s">
         <v>267</v>
       </c>
@@ -21031,7 +21028,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="70" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A70" s="58" t="s">
         <v>267</v>
       </c>
@@ -21052,7 +21049,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="71" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A71" s="58" t="s">
         <v>429</v>
       </c>
@@ -21073,7 +21070,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="72" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A72" s="58" t="s">
         <v>459</v>
       </c>
@@ -21094,7 +21091,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="73" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A73" s="58" t="s">
         <v>730</v>
       </c>
@@ -21115,7 +21112,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="74" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A74" s="58" t="s">
         <v>735</v>
       </c>
@@ -21136,7 +21133,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="75" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A75" s="58" t="s">
         <v>197</v>
       </c>
@@ -21157,7 +21154,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="76" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A76" s="58" t="s">
         <v>197</v>
       </c>
@@ -21178,16 +21175,16 @@
         <v>928</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" s="88" t="s">
+    <row r="78" spans="1:7">
+      <c r="A78" s="89" t="s">
         <v>942</v>
       </c>
-      <c r="B78" s="85"/>
-      <c r="C78" s="85"/>
-      <c r="D78" s="85"/>
-      <c r="E78" s="85"/>
-      <c r="F78" s="85"/>
-      <c r="G78" s="85"/>
+      <c r="B78" s="86"/>
+      <c r="C78" s="86"/>
+      <c r="D78" s="86"/>
+      <c r="E78" s="86"/>
+      <c r="F78" s="86"/>
+      <c r="G78" s="86"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/anciens_eleves.xlsx
+++ b/anciens_eleves.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bruno\Nextcloud2\Boulot 2026\Site orientation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCFC08D8-B9CD-41CD-8925-5D8B5A76F089}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30652FE4-A0BD-4531-999C-7253530897D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2482" uniqueCount="1022">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2487" uniqueCount="1024">
   <si>
     <t>Statistiques 2025</t>
   </si>
@@ -3099,17 +3099,30 @@
   </si>
   <si>
     <t>Flore</t>
+  </si>
+  <si>
+    <t>THOMAS</t>
+  </si>
+  <si>
+    <t>Titouan</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="30">
+  <fonts count="31">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -3483,10 +3496,10 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3500,64 +3513,64 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -3566,44 +3579,44 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -3615,69 +3628,69 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3687,7 +3700,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -3696,37 +3709,40 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -4072,7 +4088,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I111"/>
+  <dimension ref="A1:I112"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="27.42578125" customWidth="1"/>
@@ -4116,15 +4132,15 @@
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="84" t="s">
-        <v>1019</v>
+      <c r="A2" s="91" t="s">
+        <v>1022</v>
       </c>
       <c r="B2" s="64" t="str">
         <f t="shared" ref="B2" si="0">LEFT(A2)</f>
-        <v>R</v>
+        <v>T</v>
       </c>
       <c r="C2" s="64" t="s">
-        <v>220</v>
+        <v>1023</v>
       </c>
       <c r="D2" s="64">
         <v>2026</v>
@@ -4133,22 +4149,24 @@
         <v>1</v>
       </c>
       <c r="F2" s="64" t="s">
-        <v>115</v>
-      </c>
-      <c r="G2" s="64"/>
+        <v>104</v>
+      </c>
+      <c r="G2" s="65" t="s">
+        <v>182</v>
+      </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="84" t="s">
-        <v>973</v>
+        <v>1019</v>
       </c>
       <c r="B3" s="64" t="str">
         <f t="shared" ref="B3" si="1">LEFT(A3)</f>
-        <v>G</v>
+        <v>R</v>
       </c>
       <c r="C3" s="64" t="s">
-        <v>178</v>
+        <v>220</v>
       </c>
       <c r="D3" s="64">
         <v>2026</v>
@@ -4157,22 +4175,22 @@
         <v>1</v>
       </c>
       <c r="F3" s="64" t="s">
-        <v>429</v>
+        <v>115</v>
       </c>
       <c r="G3" s="64"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="76" t="s">
-        <v>968</v>
+      <c r="A4" s="84" t="s">
+        <v>973</v>
       </c>
       <c r="B4" s="64" t="str">
         <f t="shared" ref="B4" si="2">LEFT(A4)</f>
         <v>G</v>
       </c>
       <c r="C4" s="64" t="s">
-        <v>969</v>
+        <v>178</v>
       </c>
       <c r="D4" s="64">
         <v>2026</v>
@@ -4181,22 +4199,22 @@
         <v>1</v>
       </c>
       <c r="F4" s="64" t="s">
-        <v>188</v>
+        <v>429</v>
       </c>
       <c r="G4" s="64"/>
       <c r="H4" s="77"/>
       <c r="I4" s="77"/>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="72" t="s">
-        <v>966</v>
+      <c r="A5" s="76" t="s">
+        <v>968</v>
       </c>
       <c r="B5" s="64" t="str">
         <f t="shared" ref="B5" si="3">LEFT(A5)</f>
-        <v>S</v>
+        <v>G</v>
       </c>
       <c r="C5" s="64" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="D5" s="64">
         <v>2026</v>
@@ -4205,24 +4223,22 @@
         <v>1</v>
       </c>
       <c r="F5" s="64" t="s">
-        <v>104</v>
-      </c>
-      <c r="G5" s="65" t="s">
-        <v>182</v>
-      </c>
-      <c r="H5" s="64"/>
-      <c r="I5" s="64"/>
+        <v>188</v>
+      </c>
+      <c r="G5" s="64"/>
+      <c r="H5" s="77"/>
+      <c r="I5" s="77"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="72" t="s">
-        <v>347</v>
+        <v>966</v>
       </c>
       <c r="B6" s="64" t="str">
         <f t="shared" ref="B6" si="4">LEFT(A6)</f>
-        <v>T</v>
+        <v>S</v>
       </c>
       <c r="C6" s="64" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="D6" s="64">
         <v>2026</v>
@@ -4230,23 +4246,25 @@
       <c r="E6" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="F6" s="73" t="s">
-        <v>253</v>
-      </c>
-      <c r="G6" s="64"/>
+      <c r="F6" s="64" t="s">
+        <v>104</v>
+      </c>
+      <c r="G6" s="65" t="s">
+        <v>182</v>
+      </c>
       <c r="H6" s="64"/>
       <c r="I6" s="64"/>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="68" t="s">
-        <v>958</v>
+      <c r="A7" s="72" t="s">
+        <v>347</v>
       </c>
       <c r="B7" s="64" t="str">
         <f t="shared" ref="B7" si="5">LEFT(A7)</f>
-        <v>B</v>
+        <v>T</v>
       </c>
       <c r="C7" s="64" t="s">
-        <v>172</v>
+        <v>965</v>
       </c>
       <c r="D7" s="64">
         <v>2026</v>
@@ -4254,23 +4272,23 @@
       <c r="E7" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="F7" s="64" t="s">
-        <v>112</v>
-      </c>
-      <c r="G7" s="74"/>
-      <c r="H7" s="74"/>
-      <c r="I7" s="74"/>
+      <c r="F7" s="73" t="s">
+        <v>253</v>
+      </c>
+      <c r="G7" s="64"/>
+      <c r="H7" s="64"/>
+      <c r="I7" s="64"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="68" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
       <c r="B8" s="64" t="str">
         <f t="shared" ref="B8" si="6">LEFT(A8)</f>
         <v>B</v>
       </c>
       <c r="C8" s="64" t="s">
-        <v>957</v>
+        <v>172</v>
       </c>
       <c r="D8" s="64">
         <v>2026</v>
@@ -4279,22 +4297,22 @@
         <v>1</v>
       </c>
       <c r="F8" s="64" t="s">
-        <v>188</v>
-      </c>
-      <c r="G8" s="64"/>
-      <c r="H8" s="64"/>
-      <c r="I8" s="64"/>
+        <v>112</v>
+      </c>
+      <c r="G8" s="74"/>
+      <c r="H8" s="74"/>
+      <c r="I8" s="74"/>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="68" t="s">
-        <v>950</v>
+        <v>956</v>
       </c>
       <c r="B9" s="64" t="str">
         <f t="shared" ref="B9" si="7">LEFT(A9)</f>
-        <v>K</v>
+        <v>B</v>
       </c>
       <c r="C9" s="64" t="s">
-        <v>951</v>
+        <v>957</v>
       </c>
       <c r="D9" s="64">
         <v>2026</v>
@@ -4303,7 +4321,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="64" t="s">
-        <v>952</v>
+        <v>188</v>
       </c>
       <c r="G9" s="64"/>
       <c r="H9" s="64"/>
@@ -4311,14 +4329,14 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="68" t="s">
-        <v>948</v>
+        <v>950</v>
       </c>
       <c r="B10" s="64" t="str">
         <f t="shared" ref="B10" si="8">LEFT(A10)</f>
-        <v>C</v>
+        <v>K</v>
       </c>
       <c r="C10" s="64" t="s">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="D10" s="64">
         <v>2026</v>
@@ -4327,7 +4345,7 @@
         <v>1</v>
       </c>
       <c r="F10" s="64" t="s">
-        <v>136</v>
+        <v>952</v>
       </c>
       <c r="G10" s="64"/>
       <c r="H10" s="64"/>
@@ -4335,14 +4353,14 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="68" t="s">
-        <v>946</v>
+        <v>948</v>
       </c>
       <c r="B11" s="64" t="str">
-        <f t="shared" ref="B11:B75" si="9">LEFT(A11)</f>
-        <v>V</v>
+        <f t="shared" ref="B11" si="9">LEFT(A11)</f>
+        <v>C</v>
       </c>
       <c r="C11" s="64" t="s">
-        <v>947</v>
+        <v>949</v>
       </c>
       <c r="D11" s="64">
         <v>2026</v>
@@ -4351,24 +4369,22 @@
         <v>1</v>
       </c>
       <c r="F11" s="64" t="s">
-        <v>104</v>
-      </c>
-      <c r="G11" s="65" t="s">
-        <v>182</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="G11" s="64"/>
       <c r="H11" s="64"/>
       <c r="I11" s="64"/>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" s="69" t="s">
-        <v>944</v>
-      </c>
-      <c r="B12" s="66" t="str">
-        <f t="shared" si="9"/>
-        <v>H</v>
+      <c r="A12" s="68" t="s">
+        <v>946</v>
+      </c>
+      <c r="B12" s="64" t="str">
+        <f t="shared" ref="B12:B76" si="10">LEFT(A12)</f>
+        <v>V</v>
       </c>
       <c r="C12" s="64" t="s">
-        <v>945</v>
+        <v>947</v>
       </c>
       <c r="D12" s="64">
         <v>2026</v>
@@ -4377,69 +4393,72 @@
         <v>1</v>
       </c>
       <c r="F12" s="64" t="s">
-        <v>459</v>
-      </c>
-      <c r="G12" s="64"/>
+        <v>104</v>
+      </c>
+      <c r="G12" s="65" t="s">
+        <v>182</v>
+      </c>
       <c r="H12" s="64"/>
       <c r="I12" s="64"/>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" s="66" t="s">
+      <c r="A13" s="69" t="s">
+        <v>944</v>
+      </c>
+      <c r="B13" s="66" t="str">
+        <f t="shared" si="10"/>
+        <v>H</v>
+      </c>
+      <c r="C13" s="64" t="s">
+        <v>945</v>
+      </c>
+      <c r="D13" s="64">
+        <v>2026</v>
+      </c>
+      <c r="E13" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="F13" s="64" t="s">
+        <v>459</v>
+      </c>
+      <c r="G13" s="64"/>
+      <c r="H13" s="64"/>
+      <c r="I13" s="64"/>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="66" t="s">
         <v>83</v>
       </c>
-      <c r="B13" s="66" t="str">
-        <f t="shared" si="9"/>
+      <c r="B14" s="66" t="str">
+        <f t="shared" si="10"/>
         <v>A</v>
       </c>
-      <c r="C13" s="66" t="s">
+      <c r="C14" s="66" t="s">
         <v>84</v>
       </c>
-      <c r="D13" s="66">
+      <c r="D14" s="66">
         <v>2025</v>
       </c>
-      <c r="E13" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="F13" s="66" t="s">
+      <c r="E14" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="F14" s="66" t="s">
         <v>85</v>
       </c>
-      <c r="G13" s="66"/>
-      <c r="H13" s="67"/>
-      <c r="I13" s="67"/>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="A14" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="B14" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>A</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="D14" s="1">
-        <v>2025</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="G14" s="1"/>
-      <c r="H14" s="75"/>
+      <c r="G14" s="66"/>
+      <c r="H14" s="67"/>
+      <c r="I14" s="67"/>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B15" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>B</v>
+        <f t="shared" si="10"/>
+        <v>A</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D15" s="1">
         <v>2025</v>
@@ -4448,20 +4467,21 @@
         <v>1</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G15" s="1"/>
+      <c r="H15" s="75"/>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B16" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>C</v>
+        <f t="shared" si="10"/>
+        <v>B</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D16" s="1">
         <v>2025</v>
@@ -4470,20 +4490,20 @@
         <v>1</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="G16" s="1"/>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B17" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>D</v>
+        <f t="shared" si="10"/>
+        <v>C</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D17" s="1">
         <v>2025</v>
@@ -4492,20 +4512,20 @@
         <v>1</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>37</v>
+        <v>94</v>
       </c>
       <c r="G17" s="1"/>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B18" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>D</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D18" s="1">
         <v>2025</v>
@@ -4514,20 +4534,20 @@
         <v>1</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>99</v>
+        <v>37</v>
       </c>
       <c r="G18" s="1"/>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="36" t="s">
-        <v>100</v>
+      <c r="A19" s="1" t="s">
+        <v>97</v>
       </c>
       <c r="B19" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>F</v>
+        <f t="shared" si="10"/>
+        <v>D</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D19" s="1">
         <v>2025</v>
@@ -4536,20 +4556,20 @@
         <v>1</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="G19" s="1"/>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="36" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B20" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>F</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D20" s="1">
         <v>2025</v>
@@ -4558,20 +4578,20 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="G20" s="1"/>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="36" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B21" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>G</v>
+        <f t="shared" si="10"/>
+        <v>F</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D21" s="1">
         <v>2025</v>
@@ -4580,20 +4600,20 @@
         <v>1</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="G21" s="1"/>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="36" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B22" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>H</v>
+        <f t="shared" si="10"/>
+        <v>G</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D22" s="1">
         <v>2025</v>
@@ -4602,20 +4622,20 @@
         <v>1</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="G22" s="1"/>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="36" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B23" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>J</v>
+        <f t="shared" si="10"/>
+        <v>H</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D23" s="1">
         <v>2025</v>
@@ -4624,20 +4644,20 @@
         <v>1</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="G23" s="1"/>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="36" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B24" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>L</v>
+        <f t="shared" si="10"/>
+        <v>J</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D24" s="1">
         <v>2025</v>
@@ -4646,23 +4666,20 @@
         <v>1</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="G24" s="1"/>
-      <c r="H24" t="s">
-        <v>116</v>
-      </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="36" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B25" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>L</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D25" s="1">
         <v>2025</v>
@@ -4671,20 +4688,23 @@
         <v>1</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="G25" s="1"/>
+      <c r="H25" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="36" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B26" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>L</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D26" s="1">
         <v>2025</v>
@@ -4693,20 +4713,20 @@
         <v>1</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="G26" s="1"/>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="36" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B27" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>M</v>
+        <f t="shared" si="10"/>
+        <v>L</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D27" s="1">
         <v>2025</v>
@@ -4715,20 +4735,20 @@
         <v>1</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G27" s="1"/>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="36" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B28" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>P</v>
+        <f t="shared" si="10"/>
+        <v>M</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D28" s="1">
         <v>2025</v>
@@ -4737,20 +4757,20 @@
         <v>1</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="G28" s="1"/>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="36" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B29" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>S</v>
+        <f t="shared" si="10"/>
+        <v>P</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D29" s="1">
         <v>2025</v>
@@ -4759,20 +4779,20 @@
         <v>1</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="G29" s="1"/>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="36" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B30" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>V</v>
+        <f t="shared" si="10"/>
+        <v>S</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D30" s="1">
         <v>2025</v>
@@ -4781,20 +4801,20 @@
         <v>1</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="G30" s="1"/>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="36" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B31" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>W</v>
+        <f t="shared" si="10"/>
+        <v>V</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D31" s="1">
         <v>2025</v>
@@ -4803,42 +4823,42 @@
         <v>1</v>
       </c>
       <c r="F31" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="G31" s="1"/>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" s="36" t="s">
+        <v>134</v>
+      </c>
+      <c r="B32" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>W</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="D32" s="1">
+        <v>2025</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F32" s="1" t="s">
         <v>136</v>
-      </c>
-      <c r="G31" s="1"/>
-    </row>
-    <row r="32" spans="1:8">
-      <c r="A32" s="38" t="s">
-        <v>137</v>
-      </c>
-      <c r="B32" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>B</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="D32" s="1">
-        <v>2024</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>139</v>
       </c>
       <c r="G32" s="1"/>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="38" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B33" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>B</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D33" s="1">
         <v>2024</v>
@@ -4847,20 +4867,20 @@
         <v>1</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="G33" s="1"/>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="38" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B34" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>C</v>
+        <f t="shared" si="10"/>
+        <v>B</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D34" s="1">
         <v>2024</v>
@@ -4869,20 +4889,20 @@
         <v>1</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="G34" s="1"/>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="38" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B35" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>D</v>
+        <f t="shared" si="10"/>
+        <v>C</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D35" s="1">
         <v>2024</v>
@@ -4891,20 +4911,20 @@
         <v>1</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>104</v>
+        <v>145</v>
       </c>
       <c r="G35" s="1"/>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="38" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B36" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>D</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D36" s="1">
         <v>2024</v>
@@ -4913,20 +4933,20 @@
         <v>1</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="G36" s="1"/>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="38" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B37" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>F</v>
+        <f t="shared" si="10"/>
+        <v>D</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>101</v>
+        <v>149</v>
       </c>
       <c r="D37" s="1">
         <v>2024</v>
@@ -4935,20 +4955,20 @@
         <v>1</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="G37" s="1"/>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="38" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B38" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>H</v>
+        <f t="shared" si="10"/>
+        <v>F</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>152</v>
+        <v>101</v>
       </c>
       <c r="D38" s="1">
         <v>2024</v>
@@ -4957,20 +4977,20 @@
         <v>1</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>139</v>
+        <v>104</v>
       </c>
       <c r="G38" s="1"/>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="38" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B39" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>H</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D39" s="1">
         <v>2024</v>
@@ -4979,18 +4999,20 @@
         <v>1</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="G39" s="1"/>
     </row>
     <row r="40" spans="1:8">
-      <c r="A40" s="1"/>
+      <c r="A40" s="38" t="s">
+        <v>153</v>
+      </c>
       <c r="B40" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v/>
+        <f t="shared" si="10"/>
+        <v>H</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D40" s="1">
         <v>2024</v>
@@ -4998,19 +5020,19 @@
       <c r="E40" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F40" s="1"/>
+      <c r="F40" s="1" t="s">
+        <v>136</v>
+      </c>
       <c r="G40" s="1"/>
     </row>
     <row r="41" spans="1:8">
-      <c r="A41" s="38" t="s">
-        <v>156</v>
-      </c>
+      <c r="A41" s="1"/>
       <c r="B41" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>J</v>
+        <f t="shared" si="10"/>
+        <v/>
       </c>
       <c r="C41" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D41" s="1">
         <v>2024</v>
@@ -5018,21 +5040,19 @@
       <c r="E41" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F41" s="1" t="s">
-        <v>94</v>
-      </c>
+      <c r="F41" s="1"/>
       <c r="G41" s="1"/>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="38" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B42" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>L</v>
+        <f t="shared" si="10"/>
+        <v>J</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D42" s="1">
         <v>2024</v>
@@ -5041,20 +5061,20 @@
         <v>1</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>139</v>
+        <v>94</v>
       </c>
       <c r="G42" s="1"/>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="38" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B43" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>N</v>
+        <f t="shared" si="10"/>
+        <v>L</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D43" s="1">
         <v>2024</v>
@@ -5063,23 +5083,20 @@
         <v>1</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>115</v>
+        <v>139</v>
       </c>
       <c r="G43" s="1"/>
-      <c r="H43" t="s">
-        <v>162</v>
-      </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="38" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B44" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>N</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D44" s="1">
         <v>2024</v>
@@ -5091,15 +5108,20 @@
         <v>115</v>
       </c>
       <c r="G44" s="1"/>
+      <c r="H44" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="45" spans="1:8">
-      <c r="A45" s="1"/>
+      <c r="A45" s="38" t="s">
+        <v>163</v>
+      </c>
       <c r="B45" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v/>
+        <f t="shared" si="10"/>
+        <v>N</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D45" s="1">
         <v>2024</v>
@@ -5108,20 +5130,18 @@
         <v>1</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>85</v>
+        <v>115</v>
       </c>
       <c r="G45" s="1"/>
     </row>
     <row r="46" spans="1:8">
-      <c r="A46" s="38" t="s">
-        <v>166</v>
-      </c>
+      <c r="A46" s="1"/>
       <c r="B46" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>P</v>
+        <f t="shared" si="10"/>
+        <v/>
       </c>
       <c r="C46" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D46" s="1">
         <v>2024</v>
@@ -5136,14 +5156,14 @@
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="38" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B47" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>P</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D47" s="1">
         <v>2024</v>
@@ -5152,20 +5172,20 @@
         <v>1</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>169</v>
+        <v>85</v>
       </c>
       <c r="G47" s="1"/>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="38" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B48" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>R</v>
+        <f t="shared" si="10"/>
+        <v>P</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="D48" s="1">
         <v>2024</v>
@@ -5174,20 +5194,20 @@
         <v>1</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>37</v>
+        <v>169</v>
       </c>
       <c r="G48" s="1"/>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="38" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B49" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>S</v>
+        <f t="shared" si="10"/>
+        <v>R</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="D49" s="1">
         <v>2024</v>
@@ -5196,20 +5216,20 @@
         <v>1</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>115</v>
+        <v>37</v>
       </c>
       <c r="G49" s="1"/>
     </row>
     <row r="50" spans="1:7">
       <c r="A50" s="38" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B50" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>S</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D50" s="1">
         <v>2024</v>
@@ -5224,14 +5244,14 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51" s="38" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B51" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>T</v>
+        <f t="shared" si="10"/>
+        <v>S</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D51" s="1">
         <v>2024</v>
@@ -5240,42 +5260,42 @@
         <v>1</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="G51" s="1"/>
     </row>
     <row r="52" spans="1:7">
       <c r="A52" s="38" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B52" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>B</v>
-      </c>
-      <c r="C52" s="34" t="s">
-        <v>178</v>
-      </c>
-      <c r="D52" s="29">
-        <v>2023</v>
-      </c>
-      <c r="E52" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="F52" s="35" t="s">
-        <v>139</v>
-      </c>
-      <c r="G52" s="35"/>
+        <f t="shared" si="10"/>
+        <v>T</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="D52" s="1">
+        <v>2024</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="G52" s="1"/>
     </row>
     <row r="53" spans="1:7">
       <c r="A53" s="38" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B53" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>B</v>
       </c>
       <c r="C53" s="34" t="s">
-        <v>128</v>
+        <v>178</v>
       </c>
       <c r="D53" s="29">
         <v>2023</v>
@@ -5284,20 +5304,20 @@
         <v>1</v>
       </c>
       <c r="F53" s="35" t="s">
-        <v>112</v>
+        <v>139</v>
       </c>
       <c r="G53" s="35"/>
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="38" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B54" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>C</v>
+        <f t="shared" si="10"/>
+        <v>B</v>
       </c>
       <c r="C54" s="34" t="s">
-        <v>181</v>
+        <v>128</v>
       </c>
       <c r="D54" s="29">
         <v>2023</v>
@@ -5305,21 +5325,21 @@
       <c r="E54" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="F54" s="30" t="s">
-        <v>104</v>
-      </c>
-      <c r="G54" s="35" t="s">
-        <v>182</v>
-      </c>
+      <c r="F54" s="35" t="s">
+        <v>112</v>
+      </c>
+      <c r="G54" s="35"/>
     </row>
     <row r="55" spans="1:7">
-      <c r="A55" s="1"/>
+      <c r="A55" s="38" t="s">
+        <v>180</v>
+      </c>
       <c r="B55" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v/>
+        <f t="shared" si="10"/>
+        <v>C</v>
       </c>
       <c r="C55" s="34" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D55" s="29">
         <v>2023</v>
@@ -5337,11 +5357,11 @@
     <row r="56" spans="1:7">
       <c r="A56" s="1"/>
       <c r="B56" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="C56" s="34" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D56" s="29">
         <v>2023</v>
@@ -5359,11 +5379,11 @@
     <row r="57" spans="1:7">
       <c r="A57" s="1"/>
       <c r="B57" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="C57" s="34" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D57" s="29">
         <v>2023</v>
@@ -5371,21 +5391,21 @@
       <c r="E57" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="F57" s="35" t="s">
-        <v>139</v>
-      </c>
-      <c r="G57" s="35"/>
+      <c r="F57" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="G57" s="35" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="58" spans="1:7">
-      <c r="A58" s="38" t="s">
-        <v>186</v>
-      </c>
+      <c r="A58" s="1"/>
       <c r="B58" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>H</v>
+        <f t="shared" si="10"/>
+        <v/>
       </c>
       <c r="C58" s="34" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D58" s="29">
         <v>2023</v>
@@ -5394,20 +5414,20 @@
         <v>1</v>
       </c>
       <c r="F58" s="35" t="s">
-        <v>188</v>
+        <v>139</v>
       </c>
       <c r="G58" s="35"/>
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="38" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="B59" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>J</v>
+        <f t="shared" si="10"/>
+        <v>H</v>
       </c>
       <c r="C59" s="34" t="s">
-        <v>84</v>
+        <v>187</v>
       </c>
       <c r="D59" s="29">
         <v>2023</v>
@@ -5416,20 +5436,20 @@
         <v>1</v>
       </c>
       <c r="F59" s="35" t="s">
-        <v>112</v>
+        <v>188</v>
       </c>
       <c r="G59" s="35"/>
     </row>
     <row r="60" spans="1:7">
       <c r="A60" s="38" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B60" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>K</v>
+        <f t="shared" si="10"/>
+        <v>J</v>
       </c>
       <c r="C60" s="34" t="s">
-        <v>191</v>
+        <v>84</v>
       </c>
       <c r="D60" s="29">
         <v>2023</v>
@@ -5444,14 +5464,14 @@
     </row>
     <row r="61" spans="1:7">
       <c r="A61" s="38" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B61" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>L</v>
+        <f t="shared" si="10"/>
+        <v>K</v>
       </c>
       <c r="C61" s="34" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D61" s="29">
         <v>2023</v>
@@ -5460,20 +5480,20 @@
         <v>1</v>
       </c>
       <c r="F61" s="35" t="s">
-        <v>194</v>
+        <v>112</v>
       </c>
       <c r="G61" s="35"/>
     </row>
     <row r="62" spans="1:7">
       <c r="A62" s="38" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B62" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>M</v>
+        <f t="shared" si="10"/>
+        <v>L</v>
       </c>
       <c r="C62" s="34" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D62" s="29">
         <v>2023</v>
@@ -5482,20 +5502,20 @@
         <v>1</v>
       </c>
       <c r="F62" s="35" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="G62" s="35"/>
     </row>
     <row r="63" spans="1:7">
       <c r="A63" s="38" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B63" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>M</v>
       </c>
       <c r="C63" s="34" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="D63" s="29">
         <v>2023</v>
@@ -5503,21 +5523,21 @@
       <c r="E63" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="F63" s="30" t="s">
-        <v>104</v>
+      <c r="F63" s="35" t="s">
+        <v>197</v>
       </c>
       <c r="G63" s="35"/>
     </row>
     <row r="64" spans="1:7">
       <c r="A64" s="38" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B64" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>M</v>
       </c>
       <c r="C64" s="34" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D64" s="29">
         <v>2023</v>
@@ -5525,21 +5545,21 @@
       <c r="E64" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="F64" s="35" t="s">
-        <v>112</v>
+      <c r="F64" s="30" t="s">
+        <v>104</v>
       </c>
       <c r="G64" s="35"/>
     </row>
     <row r="65" spans="1:7">
       <c r="A65" s="38" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B65" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>P</v>
+        <f t="shared" si="10"/>
+        <v>M</v>
       </c>
       <c r="C65" s="34" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D65" s="29">
         <v>2023</v>
@@ -5547,21 +5567,21 @@
       <c r="E65" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="F65" s="30" t="s">
-        <v>104</v>
+      <c r="F65" s="35" t="s">
+        <v>112</v>
       </c>
       <c r="G65" s="35"/>
     </row>
     <row r="66" spans="1:7">
       <c r="A66" s="38" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B66" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>T</v>
+        <f t="shared" si="10"/>
+        <v>P</v>
       </c>
       <c r="C66" s="34" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D66" s="29">
         <v>2023</v>
@@ -5569,21 +5589,21 @@
       <c r="E66" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="F66" s="35" t="s">
-        <v>169</v>
+      <c r="F66" s="30" t="s">
+        <v>104</v>
       </c>
       <c r="G66" s="35"/>
     </row>
     <row r="67" spans="1:7">
       <c r="A67" s="38" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B67" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>T</v>
       </c>
       <c r="C67" s="34" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D67" s="29">
         <v>2023</v>
@@ -5592,20 +5612,20 @@
         <v>1</v>
       </c>
       <c r="F67" s="35" t="s">
-        <v>85</v>
+        <v>169</v>
       </c>
       <c r="G67" s="35"/>
     </row>
     <row r="68" spans="1:7">
       <c r="A68" s="38" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B68" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>V</v>
+        <f t="shared" si="10"/>
+        <v>T</v>
       </c>
       <c r="C68" s="34" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D68" s="29">
         <v>2023</v>
@@ -5613,43 +5633,43 @@
       <c r="E68" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="F68" s="30" t="s">
-        <v>104</v>
+      <c r="F68" s="35" t="s">
+        <v>85</v>
       </c>
       <c r="G68" s="35"/>
     </row>
     <row r="69" spans="1:7">
       <c r="A69" s="38" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B69" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>A</v>
-      </c>
-      <c r="C69" s="35" t="s">
-        <v>211</v>
+        <f t="shared" si="10"/>
+        <v>V</v>
+      </c>
+      <c r="C69" s="34" t="s">
+        <v>209</v>
       </c>
       <c r="D69" s="29">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E69" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="F69" s="35" t="s">
-        <v>212</v>
+      <c r="F69" s="30" t="s">
+        <v>104</v>
       </c>
       <c r="G69" s="35"/>
     </row>
     <row r="70" spans="1:7">
       <c r="A70" s="38" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B70" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>A</v>
       </c>
       <c r="C70" s="35" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D70" s="29">
         <v>2022</v>
@@ -5658,20 +5678,20 @@
         <v>1</v>
       </c>
       <c r="F70" s="35" t="s">
-        <v>188</v>
+        <v>212</v>
       </c>
       <c r="G70" s="35"/>
     </row>
     <row r="71" spans="1:7">
       <c r="A71" s="38" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B71" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>B</v>
+        <f t="shared" si="10"/>
+        <v>A</v>
       </c>
       <c r="C71" s="35" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D71" s="29">
         <v>2022</v>
@@ -5680,20 +5700,20 @@
         <v>1</v>
       </c>
       <c r="F71" s="35" t="s">
-        <v>37</v>
+        <v>188</v>
       </c>
       <c r="G71" s="35"/>
     </row>
     <row r="72" spans="1:7">
       <c r="A72" s="38" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B72" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>C</v>
+        <f t="shared" si="10"/>
+        <v>B</v>
       </c>
       <c r="C72" s="35" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D72" s="29">
         <v>2022</v>
@@ -5702,20 +5722,20 @@
         <v>1</v>
       </c>
       <c r="F72" s="35" t="s">
-        <v>112</v>
+        <v>37</v>
       </c>
       <c r="G72" s="35"/>
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="38" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B73" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>D</v>
+        <f t="shared" si="10"/>
+        <v>C</v>
       </c>
       <c r="C73" s="35" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D73" s="29">
         <v>2022</v>
@@ -5724,20 +5744,20 @@
         <v>1</v>
       </c>
       <c r="F73" s="35" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="G73" s="35"/>
     </row>
     <row r="74" spans="1:7">
       <c r="A74" s="38" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B74" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>D</v>
       </c>
       <c r="C74" s="35" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D74" s="29">
         <v>2022</v>
@@ -5752,14 +5772,14 @@
     </row>
     <row r="75" spans="1:7">
       <c r="A75" s="38" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B75" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>G</v>
+        <f t="shared" si="10"/>
+        <v>D</v>
       </c>
       <c r="C75" s="35" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D75" s="29">
         <v>2022</v>
@@ -5768,22 +5788,20 @@
         <v>1</v>
       </c>
       <c r="F75" s="35" t="s">
-        <v>104</v>
-      </c>
-      <c r="G75" s="35" t="s">
-        <v>182</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="G75" s="35"/>
     </row>
     <row r="76" spans="1:7">
       <c r="A76" s="38" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B76" s="1" t="str">
-        <f t="shared" ref="B76:B94" si="10">LEFT(A76)</f>
+        <f t="shared" si="10"/>
         <v>G</v>
       </c>
       <c r="C76" s="35" t="s">
-        <v>128</v>
+        <v>224</v>
       </c>
       <c r="D76" s="29">
         <v>2022</v>
@@ -5792,20 +5810,22 @@
         <v>1</v>
       </c>
       <c r="F76" s="35" t="s">
-        <v>37</v>
-      </c>
-      <c r="G76" s="29"/>
+        <v>104</v>
+      </c>
+      <c r="G76" s="35" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="77" spans="1:7">
       <c r="A77" s="38" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B77" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>M</v>
+        <f t="shared" ref="B77:B95" si="11">LEFT(A77)</f>
+        <v>G</v>
       </c>
       <c r="C77" s="35" t="s">
-        <v>227</v>
+        <v>128</v>
       </c>
       <c r="D77" s="29">
         <v>2022</v>
@@ -5814,22 +5834,20 @@
         <v>1</v>
       </c>
       <c r="F77" s="35" t="s">
-        <v>104</v>
-      </c>
-      <c r="G77" s="35" t="s">
-        <v>182</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="G77" s="29"/>
     </row>
     <row r="78" spans="1:7">
       <c r="A78" s="38" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B78" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>R</v>
+        <f t="shared" si="11"/>
+        <v>M</v>
       </c>
       <c r="C78" s="35" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D78" s="29">
         <v>2022</v>
@@ -5838,20 +5856,22 @@
         <v>1</v>
       </c>
       <c r="F78" s="35" t="s">
-        <v>122</v>
-      </c>
-      <c r="G78" s="35"/>
+        <v>104</v>
+      </c>
+      <c r="G78" s="35" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="79" spans="1:7">
       <c r="A79" s="38" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B79" s="1" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>R</v>
       </c>
       <c r="C79" s="35" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D79" s="29">
         <v>2022</v>
@@ -5860,20 +5880,20 @@
         <v>1</v>
       </c>
       <c r="F79" s="35" t="s">
-        <v>232</v>
+        <v>122</v>
       </c>
       <c r="G79" s="35"/>
     </row>
     <row r="80" spans="1:7">
       <c r="A80" s="38" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B80" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>V</v>
+        <f t="shared" si="11"/>
+        <v>R</v>
       </c>
       <c r="C80" s="35" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="D80" s="29">
         <v>2022</v>
@@ -5882,42 +5902,42 @@
         <v>1</v>
       </c>
       <c r="F80" s="35" t="s">
+        <v>232</v>
+      </c>
+      <c r="G80" s="35"/>
+    </row>
+    <row r="81" spans="1:7">
+      <c r="A81" s="38" t="s">
+        <v>233</v>
+      </c>
+      <c r="B81" s="1" t="str">
+        <f t="shared" si="11"/>
+        <v>V</v>
+      </c>
+      <c r="C81" s="35" t="s">
+        <v>234</v>
+      </c>
+      <c r="D81" s="29">
+        <v>2022</v>
+      </c>
+      <c r="E81" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="F81" s="35" t="s">
         <v>139</v>
       </c>
-      <c r="G80" s="35"/>
-    </row>
-    <row r="81" spans="1:7">
-      <c r="A81" s="35" t="s">
-        <v>235</v>
-      </c>
-      <c r="B81" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>A</v>
-      </c>
-      <c r="C81" s="35" t="s">
-        <v>236</v>
-      </c>
-      <c r="D81" s="29">
-        <v>2021</v>
-      </c>
-      <c r="E81" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="F81" s="35" t="s">
-        <v>126</v>
-      </c>
-      <c r="G81" s="1"/>
+      <c r="G81" s="35"/>
     </row>
     <row r="82" spans="1:7">
       <c r="A82" s="35" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B82" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>B</v>
+        <f t="shared" si="11"/>
+        <v>A</v>
       </c>
       <c r="C82" s="35" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D82" s="29">
         <v>2021</v>
@@ -5926,20 +5946,20 @@
         <v>1</v>
       </c>
       <c r="F82" s="35" t="s">
-        <v>188</v>
+        <v>126</v>
       </c>
       <c r="G82" s="1"/>
     </row>
     <row r="83" spans="1:7">
       <c r="A83" s="35" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B83" s="1" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>B</v>
       </c>
       <c r="C83" s="35" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D83" s="29">
         <v>2021</v>
@@ -5948,20 +5968,20 @@
         <v>1</v>
       </c>
       <c r="F83" s="35" t="s">
-        <v>241</v>
+        <v>188</v>
       </c>
       <c r="G83" s="1"/>
     </row>
     <row r="84" spans="1:7">
       <c r="A84" s="35" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B84" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>C</v>
+        <f t="shared" si="11"/>
+        <v>B</v>
       </c>
       <c r="C84" s="35" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="D84" s="29">
         <v>2021</v>
@@ -5970,20 +5990,20 @@
         <v>1</v>
       </c>
       <c r="F84" s="35" t="s">
-        <v>122</v>
+        <v>241</v>
       </c>
       <c r="G84" s="1"/>
     </row>
     <row r="85" spans="1:7">
       <c r="A85" s="35" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B85" s="1" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>C</v>
       </c>
       <c r="C85" s="35" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="D85" s="29">
         <v>2021</v>
@@ -5992,20 +6012,20 @@
         <v>1</v>
       </c>
       <c r="F85" s="35" t="s">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="G85" s="1"/>
     </row>
     <row r="86" spans="1:7">
       <c r="A86" s="35" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B86" s="1" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>C</v>
       </c>
       <c r="C86" s="35" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="D86" s="29">
         <v>2021</v>
@@ -6014,20 +6034,20 @@
         <v>1</v>
       </c>
       <c r="F86" s="35" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="G86" s="1"/>
     </row>
     <row r="87" spans="1:7">
       <c r="A87" s="35" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B87" s="1" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>C</v>
       </c>
       <c r="C87" s="35" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="D87" s="29">
         <v>2021</v>
@@ -6036,20 +6056,20 @@
         <v>1</v>
       </c>
       <c r="F87" s="35" t="s">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="G87" s="1"/>
     </row>
     <row r="88" spans="1:7">
       <c r="A88" s="35" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B88" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>E</v>
+        <f t="shared" si="11"/>
+        <v>C</v>
       </c>
       <c r="C88" s="35" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D88" s="29">
         <v>2021</v>
@@ -6058,20 +6078,20 @@
         <v>1</v>
       </c>
       <c r="F88" s="35" t="s">
-        <v>37</v>
+        <v>139</v>
       </c>
       <c r="G88" s="1"/>
     </row>
     <row r="89" spans="1:7">
       <c r="A89" s="35" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B89" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>G</v>
+        <f t="shared" si="11"/>
+        <v>E</v>
       </c>
       <c r="C89" s="35" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D89" s="29">
         <v>2021</v>
@@ -6080,20 +6100,20 @@
         <v>1</v>
       </c>
       <c r="F89" s="35" t="s">
-        <v>253</v>
+        <v>37</v>
       </c>
       <c r="G89" s="1"/>
     </row>
     <row r="90" spans="1:7">
       <c r="A90" s="35" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B90" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>J</v>
+        <f t="shared" si="11"/>
+        <v>G</v>
       </c>
       <c r="C90" s="35" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D90" s="29">
         <v>2021</v>
@@ -6102,20 +6122,20 @@
         <v>1</v>
       </c>
       <c r="F90" s="35" t="s">
-        <v>104</v>
+        <v>253</v>
       </c>
       <c r="G90" s="1"/>
     </row>
     <row r="91" spans="1:7">
       <c r="A91" s="35" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B91" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>L</v>
+        <f t="shared" si="11"/>
+        <v>J</v>
       </c>
       <c r="C91" s="35" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D91" s="29">
         <v>2021</v>
@@ -6124,20 +6144,20 @@
         <v>1</v>
       </c>
       <c r="F91" s="35" t="s">
-        <v>258</v>
+        <v>104</v>
       </c>
       <c r="G91" s="1"/>
     </row>
     <row r="92" spans="1:7">
       <c r="A92" s="35" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B92" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>M</v>
+        <f t="shared" si="11"/>
+        <v>L</v>
       </c>
       <c r="C92" s="35" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="D92" s="29">
         <v>2021</v>
@@ -6146,20 +6166,20 @@
         <v>1</v>
       </c>
       <c r="F92" s="35" t="s">
-        <v>112</v>
+        <v>258</v>
       </c>
       <c r="G92" s="1"/>
     </row>
     <row r="93" spans="1:7">
       <c r="A93" s="35" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B93" s="1" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>M</v>
       </c>
       <c r="C93" s="35" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D93" s="29">
         <v>2021</v>
@@ -6167,21 +6187,21 @@
       <c r="E93" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="F93" s="29" t="s">
-        <v>126</v>
+      <c r="F93" s="35" t="s">
+        <v>112</v>
       </c>
       <c r="G93" s="1"/>
     </row>
     <row r="94" spans="1:7">
       <c r="A94" s="35" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B94" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>N</v>
+        <f t="shared" si="11"/>
+        <v>M</v>
       </c>
       <c r="C94" s="35" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D94" s="29">
         <v>2021</v>
@@ -6189,21 +6209,21 @@
       <c r="E94" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="F94" s="35" t="s">
-        <v>122</v>
+      <c r="F94" s="29" t="s">
+        <v>126</v>
       </c>
       <c r="G94" s="1"/>
     </row>
     <row r="95" spans="1:7">
       <c r="A95" s="35" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B95" s="1" t="str">
-        <f t="shared" ref="B95:B111" si="11">LEFT(A95)</f>
-        <v>P</v>
+        <f t="shared" si="11"/>
+        <v>N</v>
       </c>
       <c r="C95" s="35" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D95" s="29">
         <v>2021</v>
@@ -6212,20 +6232,20 @@
         <v>1</v>
       </c>
       <c r="F95" s="35" t="s">
-        <v>267</v>
+        <v>122</v>
       </c>
       <c r="G95" s="1"/>
     </row>
     <row r="96" spans="1:7">
       <c r="A96" s="35" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="B96" s="1" t="str">
-        <f t="shared" si="11"/>
-        <v>R</v>
+        <f t="shared" ref="B96:B112" si="12">LEFT(A96)</f>
+        <v>P</v>
       </c>
       <c r="C96" s="35" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="D96" s="29">
         <v>2021</v>
@@ -6234,20 +6254,20 @@
         <v>1</v>
       </c>
       <c r="F96" s="35" t="s">
-        <v>212</v>
+        <v>267</v>
       </c>
       <c r="G96" s="1"/>
     </row>
     <row r="97" spans="1:7">
       <c r="A97" s="35" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B97" s="1" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>R</v>
       </c>
       <c r="C97" s="35" t="s">
-        <v>236</v>
+        <v>269</v>
       </c>
       <c r="D97" s="29">
         <v>2021</v>
@@ -6256,41 +6276,42 @@
         <v>1</v>
       </c>
       <c r="F97" s="35" t="s">
-        <v>122</v>
+        <v>212</v>
       </c>
       <c r="G97" s="1"/>
     </row>
     <row r="98" spans="1:7">
       <c r="A98" s="35" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B98" s="1" t="str">
-        <f t="shared" si="11"/>
-        <v>B</v>
+        <f t="shared" si="12"/>
+        <v>R</v>
       </c>
       <c r="C98" s="35" t="s">
-        <v>272</v>
+        <v>236</v>
       </c>
       <c r="D98" s="29">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E98" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="F98" t="s">
-        <v>188</v>
-      </c>
+      <c r="F98" s="35" t="s">
+        <v>122</v>
+      </c>
+      <c r="G98" s="1"/>
     </row>
     <row r="99" spans="1:7">
       <c r="A99" s="35" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B99" s="1" t="str">
-        <f t="shared" si="11"/>
-        <v>A</v>
+        <f t="shared" si="12"/>
+        <v>B</v>
       </c>
       <c r="C99" s="35" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D99" s="29">
         <v>2020</v>
@@ -6299,44 +6320,55 @@
         <v>1</v>
       </c>
       <c r="F99" t="s">
-        <v>37</v>
+        <v>188</v>
       </c>
     </row>
     <row r="100" spans="1:7">
       <c r="A100" s="35" t="s">
+        <v>273</v>
+      </c>
+      <c r="B100" s="1" t="str">
+        <f t="shared" si="12"/>
+        <v>A</v>
+      </c>
+      <c r="C100" s="35" t="s">
+        <v>274</v>
+      </c>
+      <c r="D100" s="29">
+        <v>2020</v>
+      </c>
+      <c r="E100" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="F100" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7">
+      <c r="A101" s="35" t="s">
         <v>1020</v>
       </c>
-      <c r="B100" s="1" t="str">
-        <f t="shared" si="11"/>
+      <c r="B101" s="1" t="str">
+        <f t="shared" si="12"/>
         <v>V</v>
       </c>
-      <c r="C100" s="35" t="s">
+      <c r="C101" s="35" t="s">
         <v>1021</v>
       </c>
-      <c r="D100" s="29">
+      <c r="D101" s="29">
         <v>2018</v>
       </c>
-      <c r="E100" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="F100" s="35" t="s">
+      <c r="E101" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="F101" s="35" t="s">
         <v>112</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7">
-      <c r="A101" s="35"/>
-      <c r="B101" s="1" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="E101" s="29" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="102" spans="1:7">
       <c r="A102" s="35"/>
       <c r="B102" s="1" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="E102" s="29" t="s">
@@ -6346,7 +6378,7 @@
     <row r="103" spans="1:7">
       <c r="A103" s="35"/>
       <c r="B103" s="1" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="E103" s="29" t="s">
@@ -6356,7 +6388,7 @@
     <row r="104" spans="1:7">
       <c r="A104" s="35"/>
       <c r="B104" s="1" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="E104" s="29" t="s">
@@ -6366,7 +6398,7 @@
     <row r="105" spans="1:7">
       <c r="A105" s="35"/>
       <c r="B105" s="1" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="E105" s="29" t="s">
@@ -6376,7 +6408,7 @@
     <row r="106" spans="1:7">
       <c r="A106" s="35"/>
       <c r="B106" s="1" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="E106" s="29" t="s">
@@ -6386,7 +6418,7 @@
     <row r="107" spans="1:7">
       <c r="A107" s="35"/>
       <c r="B107" s="1" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="E107" s="29" t="s">
@@ -6396,7 +6428,7 @@
     <row r="108" spans="1:7">
       <c r="A108" s="35"/>
       <c r="B108" s="1" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="E108" s="29" t="s">
@@ -6406,7 +6438,7 @@
     <row r="109" spans="1:7">
       <c r="A109" s="35"/>
       <c r="B109" s="1" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="E109" s="29" t="s">
@@ -6414,8 +6446,9 @@
       </c>
     </row>
     <row r="110" spans="1:7">
+      <c r="A110" s="35"/>
       <c r="B110" s="1" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="E110" s="29" t="s">
@@ -6424,7 +6457,16 @@
     </row>
     <row r="111" spans="1:7">
       <c r="B111" s="1" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="E111" s="29" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7">
+      <c r="B112" s="1" t="str">
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -6438,13 +6480,13 @@
           <x14:formula1>
             <xm:f>Ecoles!$A$2:$A$70</xm:f>
           </x14:formula1>
-          <xm:sqref>F111</xm:sqref>
+          <xm:sqref>F112</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{4FACBFD7-136B-4815-BD4C-3FC873C7A761}">
           <x14:formula1>
             <xm:f>Ecoles!$A$2:$A$71</xm:f>
           </x14:formula1>
-          <xm:sqref>F2:F110</xm:sqref>
+          <xm:sqref>F2:F111</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -12128,7 +12170,7 @@
       </c>
     </row>
     <row r="28" spans="1:17">
-      <c r="A28" s="88" t="s">
+      <c r="A28" s="87" t="s">
         <v>843</v>
       </c>
       <c r="B28" s="86"/>
@@ -12168,7 +12210,7 @@
       <c r="Q29" s="86"/>
     </row>
     <row r="30" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A30" s="87" t="s">
+      <c r="A30" s="88" t="s">
         <v>20</v>
       </c>
       <c r="B30" s="85" t="s">
@@ -12299,7 +12341,7 @@
       </c>
     </row>
     <row r="33" spans="1:17">
-      <c r="A33" s="88" t="s">
+      <c r="A33" s="87" t="s">
         <v>644</v>
       </c>
       <c r="B33" s="86"/>
@@ -12339,7 +12381,7 @@
       <c r="Q34" s="86"/>
     </row>
     <row r="35" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A35" s="87" t="s">
+      <c r="A35" s="88" t="s">
         <v>20</v>
       </c>
       <c r="B35" s="85" t="s">
@@ -12856,7 +12898,7 @@
       </c>
     </row>
     <row r="48" spans="1:17">
-      <c r="A48" s="88" t="s">
+      <c r="A48" s="87" t="s">
         <v>851</v>
       </c>
       <c r="B48" s="86"/>
@@ -12896,7 +12938,7 @@
       <c r="Q49" s="86"/>
     </row>
     <row r="50" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A50" s="87" t="s">
+      <c r="A50" s="88" t="s">
         <v>20</v>
       </c>
       <c r="B50" s="85" t="s">
@@ -13027,7 +13069,7 @@
       </c>
     </row>
     <row r="53" spans="1:17">
-      <c r="A53" s="88" t="s">
+      <c r="A53" s="87" t="s">
         <v>853</v>
       </c>
       <c r="B53" s="86"/>
@@ -13067,7 +13109,7 @@
       <c r="Q54" s="86"/>
     </row>
     <row r="55" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A55" s="87" t="s">
+      <c r="A55" s="88" t="s">
         <v>20</v>
       </c>
       <c r="B55" s="85" t="s">
@@ -13652,7 +13694,7 @@
       </c>
     </row>
     <row r="72" spans="1:17">
-      <c r="A72" s="88" t="s">
+      <c r="A72" s="87" t="s">
         <v>856</v>
       </c>
       <c r="B72" s="86"/>
@@ -13692,7 +13734,7 @@
       <c r="Q73" s="86"/>
     </row>
     <row r="74" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A74" s="87" t="s">
+      <c r="A74" s="88" t="s">
         <v>20</v>
       </c>
       <c r="B74" s="85" t="s">
@@ -13947,7 +13989,7 @@
       </c>
     </row>
     <row r="81" spans="1:17">
-      <c r="A81" s="88" t="s">
+      <c r="A81" s="87" t="s">
         <v>858</v>
       </c>
       <c r="B81" s="86"/>
@@ -13987,7 +14029,7 @@
       <c r="Q82" s="86"/>
     </row>
     <row r="83" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A83" s="87" t="s">
+      <c r="A83" s="88" t="s">
         <v>20</v>
       </c>
       <c r="B83" s="85" t="s">
@@ -14341,7 +14383,7 @@
       </c>
     </row>
     <row r="93" spans="1:17">
-      <c r="A93" s="88" t="s">
+      <c r="A93" s="87" t="s">
         <v>863</v>
       </c>
       <c r="B93" s="86"/>
@@ -14381,7 +14423,7 @@
       <c r="Q94" s="86"/>
     </row>
     <row r="95" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A95" s="87" t="s">
+      <c r="A95" s="88" t="s">
         <v>20</v>
       </c>
       <c r="B95" s="85" t="s">
@@ -15461,7 +15503,7 @@
       </c>
     </row>
     <row r="127" spans="1:17">
-      <c r="A127" s="88" t="s">
+      <c r="A127" s="87" t="s">
         <v>557</v>
       </c>
       <c r="B127" s="86"/>
@@ -15501,7 +15543,7 @@
       <c r="Q128" s="86"/>
     </row>
     <row r="129" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A129" s="87" t="s">
+      <c r="A129" s="88" t="s">
         <v>20</v>
       </c>
       <c r="B129" s="85" t="s">
@@ -16709,7 +16751,7 @@
       </c>
     </row>
     <row r="159" spans="1:17">
-      <c r="A159" s="88" t="s">
+      <c r="A159" s="87" t="s">
         <v>46</v>
       </c>
       <c r="B159" s="86"/>
@@ -16749,7 +16791,7 @@
       <c r="Q160" s="86"/>
     </row>
     <row r="161" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A161" s="87" t="s">
+      <c r="A161" s="88" t="s">
         <v>20</v>
       </c>
       <c r="B161" s="85" t="s">
@@ -16880,7 +16922,7 @@
       </c>
     </row>
     <row r="164" spans="1:17">
-      <c r="A164" s="88" t="s">
+      <c r="A164" s="87" t="s">
         <v>69</v>
       </c>
       <c r="B164" s="86"/>
@@ -16920,7 +16962,7 @@
       <c r="Q165" s="86"/>
     </row>
     <row r="166" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A166" s="87" t="s">
+      <c r="A166" s="88" t="s">
         <v>20</v>
       </c>
       <c r="B166" s="85" t="s">
@@ -17176,6 +17218,70 @@
     </row>
   </sheetData>
   <mergeCells count="80">
+    <mergeCell ref="K166:O166"/>
+    <mergeCell ref="H74:J74"/>
+    <mergeCell ref="H83:J83"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="Q50:Q51"/>
+    <mergeCell ref="B55:D55"/>
+    <mergeCell ref="B95:D95"/>
+    <mergeCell ref="E50:G50"/>
+    <mergeCell ref="P74:P75"/>
+    <mergeCell ref="E55:G55"/>
+    <mergeCell ref="K129:O129"/>
+    <mergeCell ref="P95:P96"/>
+    <mergeCell ref="A55:A56"/>
+    <mergeCell ref="A81:Q82"/>
+    <mergeCell ref="A95:A96"/>
+    <mergeCell ref="B129:D129"/>
+    <mergeCell ref="Q166:Q167"/>
+    <mergeCell ref="Q35:Q36"/>
+    <mergeCell ref="P161:P162"/>
+    <mergeCell ref="A159:Q160"/>
+    <mergeCell ref="A93:Q94"/>
+    <mergeCell ref="Q161:Q162"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="P83:P84"/>
+    <mergeCell ref="Q129:Q130"/>
+    <mergeCell ref="Q95:Q96"/>
+    <mergeCell ref="H50:J50"/>
+    <mergeCell ref="A161:A162"/>
+    <mergeCell ref="H55:J55"/>
+    <mergeCell ref="A83:A84"/>
+    <mergeCell ref="P55:P56"/>
+    <mergeCell ref="B161:D161"/>
+    <mergeCell ref="P129:P130"/>
+    <mergeCell ref="A166:A167"/>
+    <mergeCell ref="K74:O74"/>
+    <mergeCell ref="K83:O83"/>
+    <mergeCell ref="A74:A75"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="A129:A130"/>
+    <mergeCell ref="B83:D83"/>
+    <mergeCell ref="H166:J166"/>
+    <mergeCell ref="E129:G129"/>
+    <mergeCell ref="H161:J161"/>
+    <mergeCell ref="H129:J129"/>
+    <mergeCell ref="E74:G74"/>
+    <mergeCell ref="E166:G166"/>
+    <mergeCell ref="K95:O95"/>
+    <mergeCell ref="A28:Q29"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="A48:Q49"/>
+    <mergeCell ref="E83:G83"/>
+    <mergeCell ref="E35:G35"/>
+    <mergeCell ref="Q55:Q56"/>
+    <mergeCell ref="P50:P51"/>
+    <mergeCell ref="E30:G30"/>
+    <mergeCell ref="Q74:Q75"/>
+    <mergeCell ref="H35:J35"/>
+    <mergeCell ref="P30:P31"/>
+    <mergeCell ref="Q83:Q84"/>
+    <mergeCell ref="A50:A51"/>
+    <mergeCell ref="K35:O35"/>
+    <mergeCell ref="Q30:Q31"/>
+    <mergeCell ref="K50:O50"/>
     <mergeCell ref="P35:P36"/>
     <mergeCell ref="E161:G161"/>
     <mergeCell ref="K30:O30"/>
@@ -17192,70 +17298,6 @@
     <mergeCell ref="A127:Q128"/>
     <mergeCell ref="K161:O161"/>
     <mergeCell ref="H30:J30"/>
-    <mergeCell ref="A28:Q29"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="A48:Q49"/>
-    <mergeCell ref="E83:G83"/>
-    <mergeCell ref="E35:G35"/>
-    <mergeCell ref="Q55:Q56"/>
-    <mergeCell ref="P50:P51"/>
-    <mergeCell ref="E30:G30"/>
-    <mergeCell ref="Q74:Q75"/>
-    <mergeCell ref="H35:J35"/>
-    <mergeCell ref="P30:P31"/>
-    <mergeCell ref="Q83:Q84"/>
-    <mergeCell ref="A50:A51"/>
-    <mergeCell ref="K35:O35"/>
-    <mergeCell ref="Q30:Q31"/>
-    <mergeCell ref="K50:O50"/>
-    <mergeCell ref="B161:D161"/>
-    <mergeCell ref="P129:P130"/>
-    <mergeCell ref="A166:A167"/>
-    <mergeCell ref="K74:O74"/>
-    <mergeCell ref="K83:O83"/>
-    <mergeCell ref="A74:A75"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="A129:A130"/>
-    <mergeCell ref="B83:D83"/>
-    <mergeCell ref="H166:J166"/>
-    <mergeCell ref="E129:G129"/>
-    <mergeCell ref="H161:J161"/>
-    <mergeCell ref="H129:J129"/>
-    <mergeCell ref="E74:G74"/>
-    <mergeCell ref="E166:G166"/>
-    <mergeCell ref="K95:O95"/>
-    <mergeCell ref="Q166:Q167"/>
-    <mergeCell ref="Q35:Q36"/>
-    <mergeCell ref="P161:P162"/>
-    <mergeCell ref="A159:Q160"/>
-    <mergeCell ref="A93:Q94"/>
-    <mergeCell ref="Q161:Q162"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="P83:P84"/>
-    <mergeCell ref="Q129:Q130"/>
-    <mergeCell ref="Q95:Q96"/>
-    <mergeCell ref="H50:J50"/>
-    <mergeCell ref="A161:A162"/>
-    <mergeCell ref="H55:J55"/>
-    <mergeCell ref="A83:A84"/>
-    <mergeCell ref="P55:P56"/>
-    <mergeCell ref="K166:O166"/>
-    <mergeCell ref="H74:J74"/>
-    <mergeCell ref="H83:J83"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="Q50:Q51"/>
-    <mergeCell ref="B55:D55"/>
-    <mergeCell ref="B95:D95"/>
-    <mergeCell ref="E50:G50"/>
-    <mergeCell ref="P74:P75"/>
-    <mergeCell ref="E55:G55"/>
-    <mergeCell ref="K129:O129"/>
-    <mergeCell ref="P95:P96"/>
-    <mergeCell ref="A55:A56"/>
-    <mergeCell ref="A81:Q82"/>
-    <mergeCell ref="A95:A96"/>
-    <mergeCell ref="B129:D129"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" display="https://www.scei-concours.fr/stat2025/bcpst.html" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
@@ -17391,7 +17433,7 @@
       </c>
     </row>
     <row r="24" spans="1:17">
-      <c r="A24" s="88" t="s">
+      <c r="A24" s="87" t="s">
         <v>19</v>
       </c>
       <c r="B24" s="86"/>
@@ -17431,7 +17473,7 @@
       <c r="Q25" s="86"/>
     </row>
     <row r="26" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A26" s="87" t="s">
+      <c r="A26" s="88" t="s">
         <v>20</v>
       </c>
       <c r="B26" s="85" t="s">
@@ -18016,7 +18058,7 @@
       </c>
     </row>
     <row r="43" spans="1:17">
-      <c r="A43" s="88" t="s">
+      <c r="A43" s="87" t="s">
         <v>46</v>
       </c>
       <c r="B43" s="86"/>
@@ -18056,7 +18098,7 @@
       <c r="Q44" s="86"/>
     </row>
     <row r="45" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A45" s="87" t="s">
+      <c r="A45" s="88" t="s">
         <v>20</v>
       </c>
       <c r="B45" s="85" t="s">
@@ -18187,7 +18229,7 @@
       </c>
     </row>
     <row r="48" spans="1:17">
-      <c r="A48" s="88" t="s">
+      <c r="A48" s="87" t="s">
         <v>47</v>
       </c>
       <c r="B48" s="86"/>
@@ -18227,7 +18269,7 @@
       <c r="Q49" s="86"/>
     </row>
     <row r="50" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A50" s="87" t="s">
+      <c r="A50" s="88" t="s">
         <v>20</v>
       </c>
       <c r="B50" s="85" t="s">
@@ -18482,7 +18524,7 @@
       </c>
     </row>
     <row r="57" spans="1:17">
-      <c r="A57" s="88" t="s">
+      <c r="A57" s="87" t="s">
         <v>53</v>
       </c>
       <c r="B57" s="86"/>
@@ -18522,7 +18564,7 @@
       <c r="Q58" s="86"/>
     </row>
     <row r="59" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A59" s="87" t="s">
+      <c r="A59" s="88" t="s">
         <v>20</v>
       </c>
       <c r="B59" s="85" t="s">
@@ -19074,7 +19116,7 @@
       </c>
     </row>
     <row r="75" spans="1:17">
-      <c r="A75" s="88" t="s">
+      <c r="A75" s="87" t="s">
         <v>67</v>
       </c>
       <c r="B75" s="86"/>
@@ -19114,7 +19156,7 @@
       <c r="Q76" s="86"/>
     </row>
     <row r="77" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A77" s="87" t="s">
+      <c r="A77" s="88" t="s">
         <v>20</v>
       </c>
       <c r="B77" s="85" t="s">
@@ -19245,7 +19287,7 @@
       </c>
     </row>
     <row r="80" spans="1:17">
-      <c r="A80" s="88" t="s">
+      <c r="A80" s="87" t="s">
         <v>69</v>
       </c>
       <c r="B80" s="86"/>
@@ -19285,7 +19327,7 @@
       <c r="Q81" s="86"/>
     </row>
     <row r="82" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A82" s="87" t="s">
+      <c r="A82" s="88" t="s">
         <v>20</v>
       </c>
       <c r="B82" s="85" t="s">
@@ -19508,6 +19550,38 @@
     </row>
   </sheetData>
   <mergeCells count="48">
+    <mergeCell ref="A24:Q25"/>
+    <mergeCell ref="K82:O82"/>
+    <mergeCell ref="H50:J50"/>
+    <mergeCell ref="P26:P27"/>
+    <mergeCell ref="A59:A60"/>
+    <mergeCell ref="Q77:Q78"/>
+    <mergeCell ref="E82:G82"/>
+    <mergeCell ref="A82:A83"/>
+    <mergeCell ref="B77:D77"/>
+    <mergeCell ref="P45:P46"/>
+    <mergeCell ref="A80:Q81"/>
+    <mergeCell ref="A77:A78"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="H82:J82"/>
+    <mergeCell ref="Q45:Q46"/>
+    <mergeCell ref="A48:Q49"/>
+    <mergeCell ref="P82:P83"/>
+    <mergeCell ref="Q59:Q60"/>
+    <mergeCell ref="H77:J77"/>
+    <mergeCell ref="K59:O59"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="Q82:Q83"/>
+    <mergeCell ref="K77:O77"/>
+    <mergeCell ref="P77:P78"/>
+    <mergeCell ref="E77:G77"/>
+    <mergeCell ref="E50:G50"/>
+    <mergeCell ref="H59:J59"/>
+    <mergeCell ref="A75:Q76"/>
+    <mergeCell ref="P59:P60"/>
+    <mergeCell ref="E59:G59"/>
+    <mergeCell ref="A57:Q58"/>
+    <mergeCell ref="B59:D59"/>
     <mergeCell ref="A26:A27"/>
     <mergeCell ref="K50:O50"/>
     <mergeCell ref="E26:G26"/>
@@ -19524,38 +19598,6 @@
     <mergeCell ref="E45:G45"/>
     <mergeCell ref="B45:D45"/>
     <mergeCell ref="B50:D50"/>
-    <mergeCell ref="E50:G50"/>
-    <mergeCell ref="H59:J59"/>
-    <mergeCell ref="A75:Q76"/>
-    <mergeCell ref="P59:P60"/>
-    <mergeCell ref="E59:G59"/>
-    <mergeCell ref="A57:Q58"/>
-    <mergeCell ref="B59:D59"/>
-    <mergeCell ref="P82:P83"/>
-    <mergeCell ref="Q59:Q60"/>
-    <mergeCell ref="H77:J77"/>
-    <mergeCell ref="K59:O59"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="Q82:Q83"/>
-    <mergeCell ref="K77:O77"/>
-    <mergeCell ref="P77:P78"/>
-    <mergeCell ref="E77:G77"/>
-    <mergeCell ref="A24:Q25"/>
-    <mergeCell ref="K82:O82"/>
-    <mergeCell ref="H50:J50"/>
-    <mergeCell ref="P26:P27"/>
-    <mergeCell ref="A59:A60"/>
-    <mergeCell ref="Q77:Q78"/>
-    <mergeCell ref="E82:G82"/>
-    <mergeCell ref="A82:A83"/>
-    <mergeCell ref="B77:D77"/>
-    <mergeCell ref="P45:P46"/>
-    <mergeCell ref="A80:Q81"/>
-    <mergeCell ref="A77:A78"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="H82:J82"/>
-    <mergeCell ref="Q45:Q46"/>
-    <mergeCell ref="A48:Q49"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" display="https://www.scei-concours.fr/stat2025/tb.html" xr:uid="{00000000-0004-0000-0500-000000000000}"/>

--- a/anciens_eleves.xlsx
+++ b/anciens_eleves.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bruno\Nextcloud2\Boulot 2026\Site orientation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C40A196F-6735-4C2D-8B32-75B12B1BD869}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05224369-8457-4A06-82CA-CC1F7B35B8AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Elèves_BCPST" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2944" uniqueCount="1208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2953" uniqueCount="1216">
   <si>
     <t>Statistiques 2025</t>
   </si>
@@ -3657,17 +3657,48 @@
   </si>
   <si>
     <t>GUILLERAULT</t>
+  </si>
+  <si>
+    <t>Après l'école</t>
+  </si>
+  <si>
+    <t>paysagiste conceptrice en cabinet</t>
+  </si>
+  <si>
+    <t>consultante R et D en biotechnologies</t>
+  </si>
+  <si>
+    <t>gestion des milieux naturels</t>
+  </si>
+  <si>
+    <t>ingé biologiste cutanée</t>
+  </si>
+  <si>
+    <t>conseillere dans une COOP de noix</t>
+  </si>
+  <si>
+    <t>thèsarde en pologne</t>
+  </si>
+  <si>
+    <t>stages bien-être animal – thèse sur transition dans l’élevage</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="36" x14ac:knownFonts="1">
+  <fonts count="38">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -3912,6 +3943,11 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFC9211E"/>
+      <name val="Liberation Sans1"/>
+    </font>
   </fonts>
   <fills count="14">
     <fill>
@@ -4092,10 +4128,10 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="106">
+  <cellXfs count="108">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4109,64 +4145,64 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -4175,44 +4211,44 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -4224,69 +4260,69 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="32" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="33" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="32" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="33" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="32" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="33" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="32" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="33" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="32" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="33" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="32" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="33" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4296,7 +4332,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -4305,76 +4341,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="29" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="30" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -4720,8 +4760,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I193"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J193"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="27.42578125" customWidth="1"/>
     <col min="2" max="2" width="14.28515625" customWidth="1"/>
@@ -4732,9 +4772,10 @@
     <col min="7" max="7" width="18" customWidth="1"/>
     <col min="8" max="8" width="28" customWidth="1"/>
     <col min="9" max="9" width="21.42578125" customWidth="1"/>
+    <col min="10" max="10" width="33" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10">
       <c r="A1" s="70" t="s">
         <v>74</v>
       </c>
@@ -4762,8 +4803,11 @@
       <c r="I1" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J1" s="2" t="s">
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" s="98" t="s">
         <v>1197</v>
       </c>
@@ -4787,7 +4831,7 @@
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10">
       <c r="A3" s="98" t="s">
         <v>1195</v>
       </c>
@@ -4811,7 +4855,7 @@
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10">
       <c r="A4" s="85" t="s">
         <v>1020</v>
       </c>
@@ -4837,7 +4881,7 @@
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10">
       <c r="A5" s="84" t="s">
         <v>1017</v>
       </c>
@@ -4861,7 +4905,7 @@
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10">
       <c r="A6" s="84" t="s">
         <v>971</v>
       </c>
@@ -4885,7 +4929,7 @@
       <c r="H6" s="77"/>
       <c r="I6" s="77"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10">
       <c r="A7" s="76" t="s">
         <v>966</v>
       </c>
@@ -4909,7 +4953,7 @@
       <c r="H7" s="77"/>
       <c r="I7" s="77"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10">
       <c r="A8" s="72" t="s">
         <v>964</v>
       </c>
@@ -4935,7 +4979,7 @@
       <c r="H8" s="64"/>
       <c r="I8" s="64"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10">
       <c r="A9" s="72" t="s">
         <v>346</v>
       </c>
@@ -4959,7 +5003,7 @@
       <c r="H9" s="64"/>
       <c r="I9" s="64"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10">
       <c r="A10" s="68" t="s">
         <v>956</v>
       </c>
@@ -4983,7 +5027,7 @@
       <c r="H10" s="74"/>
       <c r="I10" s="74"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10">
       <c r="A11" s="68" t="s">
         <v>954</v>
       </c>
@@ -5007,7 +5051,7 @@
       <c r="H11" s="64"/>
       <c r="I11" s="64"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10">
       <c r="A12" s="68" t="s">
         <v>949</v>
       </c>
@@ -5031,7 +5075,7 @@
       <c r="H12" s="64"/>
       <c r="I12" s="64"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10">
       <c r="A13" s="68" t="s">
         <v>947</v>
       </c>
@@ -5055,7 +5099,7 @@
       <c r="H13" s="64"/>
       <c r="I13" s="64"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10">
       <c r="A14" s="68" t="s">
         <v>945</v>
       </c>
@@ -5081,7 +5125,7 @@
       <c r="H14" s="64"/>
       <c r="I14" s="64"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10">
       <c r="A15" s="69" t="s">
         <v>943</v>
       </c>
@@ -5105,7 +5149,7 @@
       <c r="H15" s="64"/>
       <c r="I15" s="64"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10">
       <c r="A16" s="66" t="s">
         <v>83</v>
       </c>
@@ -5129,7 +5173,7 @@
       <c r="H16" s="67"/>
       <c r="I16" s="67"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8">
       <c r="A17" s="1" t="s">
         <v>86</v>
       </c>
@@ -5152,7 +5196,7 @@
       <c r="G17" s="1"/>
       <c r="H17" s="75"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8">
       <c r="A18" s="1" t="s">
         <v>89</v>
       </c>
@@ -5174,7 +5218,7 @@
       </c>
       <c r="G18" s="1"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8">
       <c r="A19" s="1" t="s">
         <v>92</v>
       </c>
@@ -5196,7 +5240,7 @@
       </c>
       <c r="G19" s="1"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8">
       <c r="A20" s="1" t="s">
         <v>95</v>
       </c>
@@ -5218,7 +5262,7 @@
       </c>
       <c r="G20" s="1"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8">
       <c r="A21" s="1" t="s">
         <v>97</v>
       </c>
@@ -5240,7 +5284,7 @@
       </c>
       <c r="G21" s="1"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8">
       <c r="A22" s="36" t="s">
         <v>100</v>
       </c>
@@ -5262,7 +5306,7 @@
       </c>
       <c r="G22" s="1"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8">
       <c r="A23" s="36" t="s">
         <v>102</v>
       </c>
@@ -5284,7 +5328,7 @@
       </c>
       <c r="G23" s="1"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8">
       <c r="A24" s="36" t="s">
         <v>105</v>
       </c>
@@ -5306,7 +5350,7 @@
       </c>
       <c r="G24" s="1"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8">
       <c r="A25" s="36" t="s">
         <v>108</v>
       </c>
@@ -5328,7 +5372,7 @@
       </c>
       <c r="G25" s="1"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8">
       <c r="A26" s="36" t="s">
         <v>110</v>
       </c>
@@ -5350,7 +5394,7 @@
       </c>
       <c r="G26" s="1"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8">
       <c r="A27" s="36" t="s">
         <v>113</v>
       </c>
@@ -5375,7 +5419,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8">
       <c r="A28" s="36" t="s">
         <v>117</v>
       </c>
@@ -5397,7 +5441,7 @@
       </c>
       <c r="G28" s="1"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8">
       <c r="A29" s="36" t="s">
         <v>120</v>
       </c>
@@ -5419,7 +5463,7 @@
       </c>
       <c r="G29" s="1"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8">
       <c r="A30" s="36" t="s">
         <v>123</v>
       </c>
@@ -5441,7 +5485,7 @@
       </c>
       <c r="G30" s="1"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8">
       <c r="A31" s="36" t="s">
         <v>127</v>
       </c>
@@ -5463,7 +5507,7 @@
       </c>
       <c r="G31" s="1"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8">
       <c r="A32" s="36" t="s">
         <v>130</v>
       </c>
@@ -5485,7 +5529,7 @@
       </c>
       <c r="G32" s="1"/>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8">
       <c r="A33" s="36" t="s">
         <v>132</v>
       </c>
@@ -5507,7 +5551,7 @@
       </c>
       <c r="G33" s="1"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8">
       <c r="A34" s="36" t="s">
         <v>134</v>
       </c>
@@ -5529,7 +5573,7 @@
       </c>
       <c r="G34" s="1"/>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8">
       <c r="A35" s="38" t="s">
         <v>137</v>
       </c>
@@ -5551,7 +5595,7 @@
       </c>
       <c r="G35" s="1"/>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8">
       <c r="A36" s="38" t="s">
         <v>139</v>
       </c>
@@ -5573,7 +5617,7 @@
       </c>
       <c r="G36" s="1"/>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8">
       <c r="A37" s="38" t="s">
         <v>142</v>
       </c>
@@ -5595,7 +5639,7 @@
       </c>
       <c r="G37" s="1"/>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8">
       <c r="A38" s="38" t="s">
         <v>145</v>
       </c>
@@ -5617,7 +5661,7 @@
       </c>
       <c r="G38" s="1"/>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8">
       <c r="A39" s="38" t="s">
         <v>147</v>
       </c>
@@ -5639,7 +5683,7 @@
       </c>
       <c r="G39" s="1"/>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8">
       <c r="A40" s="38" t="s">
         <v>149</v>
       </c>
@@ -5661,7 +5705,7 @@
       </c>
       <c r="G40" s="1"/>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8">
       <c r="A41" s="38" t="s">
         <v>150</v>
       </c>
@@ -5683,7 +5727,7 @@
       </c>
       <c r="G41" s="1"/>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8">
       <c r="A42" s="38" t="s">
         <v>152</v>
       </c>
@@ -5705,7 +5749,7 @@
       </c>
       <c r="G42" s="1"/>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8">
       <c r="A43" s="1"/>
       <c r="B43" s="1" t="str">
         <f t="shared" si="12"/>
@@ -5723,7 +5767,7 @@
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8">
       <c r="A44" s="38" t="s">
         <v>155</v>
       </c>
@@ -5745,7 +5789,7 @@
       </c>
       <c r="G44" s="1"/>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8">
       <c r="A45" s="38" t="s">
         <v>157</v>
       </c>
@@ -5767,7 +5811,7 @@
       </c>
       <c r="G45" s="1"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8">
       <c r="A46" s="38" t="s">
         <v>159</v>
       </c>
@@ -5792,7 +5836,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8">
       <c r="A47" s="38" t="s">
         <v>162</v>
       </c>
@@ -5814,7 +5858,7 @@
       </c>
       <c r="G47" s="1"/>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8">
       <c r="A48" s="1"/>
       <c r="B48" s="1" t="str">
         <f t="shared" si="12"/>
@@ -5834,7 +5878,7 @@
       </c>
       <c r="G48" s="1"/>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7">
       <c r="A49" s="38" t="s">
         <v>165</v>
       </c>
@@ -5856,7 +5900,7 @@
       </c>
       <c r="G49" s="1"/>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7">
       <c r="A50" s="38" t="s">
         <v>166</v>
       </c>
@@ -5878,7 +5922,7 @@
       </c>
       <c r="G50" s="1"/>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7">
       <c r="A51" s="38" t="s">
         <v>169</v>
       </c>
@@ -5900,7 +5944,7 @@
       </c>
       <c r="G51" s="1"/>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7">
       <c r="A52" s="38" t="s">
         <v>170</v>
       </c>
@@ -5922,7 +5966,7 @@
       </c>
       <c r="G52" s="1"/>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7">
       <c r="A53" s="38" t="s">
         <v>172</v>
       </c>
@@ -5944,7 +5988,7 @@
       </c>
       <c r="G53" s="1"/>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7">
       <c r="A54" s="38" t="s">
         <v>174</v>
       </c>
@@ -5966,7 +6010,7 @@
       </c>
       <c r="G54" s="1"/>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7">
       <c r="A55" s="38" t="s">
         <v>176</v>
       </c>
@@ -5988,7 +6032,7 @@
       </c>
       <c r="G55" s="35"/>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7">
       <c r="A56" s="38" t="s">
         <v>178</v>
       </c>
@@ -6010,7 +6054,7 @@
       </c>
       <c r="G56" s="35"/>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7">
       <c r="A57" s="38" t="s">
         <v>179</v>
       </c>
@@ -6034,8 +6078,8 @@
         <v>181</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" s="105" t="s">
+    <row r="58" spans="1:7">
+      <c r="A58" s="99" t="s">
         <v>1205</v>
       </c>
       <c r="B58" s="1" t="str">
@@ -6058,8 +6102,8 @@
         <v>181</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="105" t="s">
+    <row r="59" spans="1:7">
+      <c r="A59" s="99" t="s">
         <v>1207</v>
       </c>
       <c r="B59" s="1" t="str">
@@ -6082,8 +6126,8 @@
         <v>181</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="105" t="s">
+    <row r="60" spans="1:7">
+      <c r="A60" s="100" t="s">
         <v>1206</v>
       </c>
       <c r="B60" s="1" t="str">
@@ -6104,7 +6148,7 @@
       </c>
       <c r="G60" s="35"/>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7">
       <c r="A61" s="38" t="s">
         <v>185</v>
       </c>
@@ -6126,7 +6170,7 @@
       </c>
       <c r="G61" s="35"/>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7">
       <c r="A62" s="38" t="s">
         <v>188</v>
       </c>
@@ -6148,7 +6192,7 @@
       </c>
       <c r="G62" s="35"/>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7">
       <c r="A63" s="38" t="s">
         <v>189</v>
       </c>
@@ -6170,7 +6214,7 @@
       </c>
       <c r="G63" s="35"/>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7">
       <c r="A64" s="38" t="s">
         <v>191</v>
       </c>
@@ -6192,7 +6236,7 @@
       </c>
       <c r="G64" s="35"/>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7">
       <c r="A65" s="38" t="s">
         <v>194</v>
       </c>
@@ -6214,7 +6258,7 @@
       </c>
       <c r="G65" s="35"/>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7">
       <c r="A66" s="38" t="s">
         <v>197</v>
       </c>
@@ -6236,7 +6280,7 @@
       </c>
       <c r="G66" s="35"/>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7">
       <c r="A67" s="38" t="s">
         <v>199</v>
       </c>
@@ -6258,7 +6302,7 @@
       </c>
       <c r="G67" s="35"/>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7">
       <c r="A68" s="38" t="s">
         <v>201</v>
       </c>
@@ -6280,7 +6324,7 @@
       </c>
       <c r="G68" s="35"/>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7">
       <c r="A69" s="38" t="s">
         <v>203</v>
       </c>
@@ -6302,7 +6346,7 @@
       </c>
       <c r="G69" s="35"/>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7">
       <c r="A70" s="38" t="s">
         <v>205</v>
       </c>
@@ -6324,7 +6368,7 @@
       </c>
       <c r="G70" s="35"/>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7">
       <c r="A71" s="38" t="s">
         <v>207</v>
       </c>
@@ -6346,7 +6390,7 @@
       </c>
       <c r="G71" s="35"/>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7">
       <c r="A72" s="38" t="s">
         <v>209</v>
       </c>
@@ -6368,7 +6412,7 @@
       </c>
       <c r="G72" s="35"/>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7">
       <c r="A73" s="38" t="s">
         <v>212</v>
       </c>
@@ -6390,7 +6434,7 @@
       </c>
       <c r="G73" s="35"/>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7">
       <c r="A74" s="38" t="s">
         <v>214</v>
       </c>
@@ -6412,7 +6456,7 @@
       </c>
       <c r="G74" s="35"/>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7">
       <c r="A75" s="38" t="s">
         <v>216</v>
       </c>
@@ -6434,7 +6478,7 @@
       </c>
       <c r="G75" s="35"/>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7">
       <c r="A76" s="38" t="s">
         <v>218</v>
       </c>
@@ -6456,7 +6500,7 @@
       </c>
       <c r="G76" s="35"/>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7">
       <c r="A77" s="38" t="s">
         <v>220</v>
       </c>
@@ -6478,7 +6522,7 @@
       </c>
       <c r="G77" s="35"/>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7">
       <c r="A78" s="38" t="s">
         <v>222</v>
       </c>
@@ -6502,7 +6546,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7">
       <c r="A79" s="38" t="s">
         <v>224</v>
       </c>
@@ -6524,7 +6568,7 @@
       </c>
       <c r="G79" s="29"/>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7">
       <c r="A80" s="38" t="s">
         <v>225</v>
       </c>
@@ -6548,7 +6592,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:10">
       <c r="A81" s="38" t="s">
         <v>227</v>
       </c>
@@ -6570,7 +6614,7 @@
       </c>
       <c r="G81" s="35"/>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:10">
       <c r="A82" s="38" t="s">
         <v>229</v>
       </c>
@@ -6592,7 +6636,7 @@
       </c>
       <c r="G82" s="35"/>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:10">
       <c r="A83" s="38" t="s">
         <v>232</v>
       </c>
@@ -6614,7 +6658,7 @@
       </c>
       <c r="G83" s="35"/>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:10">
       <c r="A84" s="35" t="s">
         <v>234</v>
       </c>
@@ -6636,7 +6680,7 @@
       </c>
       <c r="G84" s="1"/>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:10">
       <c r="A85" s="35" t="s">
         <v>236</v>
       </c>
@@ -6657,8 +6701,11 @@
         <v>187</v>
       </c>
       <c r="G85" s="1"/>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="J85" s="101" t="s">
+        <v>1209</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10">
       <c r="A86" s="35" t="s">
         <v>238</v>
       </c>
@@ -6680,7 +6727,7 @@
       </c>
       <c r="G86" s="1"/>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:10">
       <c r="A87" s="35" t="s">
         <v>241</v>
       </c>
@@ -6702,7 +6749,7 @@
       </c>
       <c r="G87" s="1"/>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:10">
       <c r="A88" s="35" t="s">
         <v>243</v>
       </c>
@@ -6724,7 +6771,7 @@
       </c>
       <c r="G88" s="1"/>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:10">
       <c r="A89" s="35" t="s">
         <v>244</v>
       </c>
@@ -6745,8 +6792,11 @@
         <v>122</v>
       </c>
       <c r="G89" s="1"/>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="J89" s="101" t="s">
+        <v>1210</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10">
       <c r="A90" s="35" t="s">
         <v>246</v>
       </c>
@@ -6768,7 +6818,7 @@
       </c>
       <c r="G90" s="1"/>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:10">
       <c r="A91" s="35" t="s">
         <v>248</v>
       </c>
@@ -6790,7 +6840,7 @@
       </c>
       <c r="G91" s="1"/>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:10">
       <c r="A92" s="35" t="s">
         <v>250</v>
       </c>
@@ -6812,7 +6862,7 @@
       </c>
       <c r="G92" s="1"/>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:10">
       <c r="A93" s="35" t="s">
         <v>253</v>
       </c>
@@ -6833,8 +6883,11 @@
         <v>104</v>
       </c>
       <c r="G93" s="1"/>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="J93" s="101" t="s">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10">
       <c r="A94" s="35" t="s">
         <v>255</v>
       </c>
@@ -6856,7 +6909,7 @@
       </c>
       <c r="G94" s="1"/>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:10">
       <c r="A95" s="35" t="s">
         <v>258</v>
       </c>
@@ -6877,8 +6930,11 @@
         <v>112</v>
       </c>
       <c r="G95" s="1"/>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="J95" s="101" t="s">
+        <v>1212</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10">
       <c r="A96" s="35" t="s">
         <v>260</v>
       </c>
@@ -6900,7 +6956,7 @@
       </c>
       <c r="G96" s="1"/>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:10">
       <c r="A97" s="35" t="s">
         <v>262</v>
       </c>
@@ -6922,7 +6978,7 @@
       </c>
       <c r="G97" s="1"/>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:10">
       <c r="A98" s="35" t="s">
         <v>264</v>
       </c>
@@ -6944,7 +7000,7 @@
       </c>
       <c r="G98" s="1"/>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:10">
       <c r="A99" s="35" t="s">
         <v>267</v>
       </c>
@@ -6966,7 +7022,7 @@
       </c>
       <c r="G99" s="1"/>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:10">
       <c r="A100" s="35" t="s">
         <v>269</v>
       </c>
@@ -6988,7 +7044,7 @@
       </c>
       <c r="G100" s="1"/>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:10">
       <c r="A101" s="35" t="s">
         <v>270</v>
       </c>
@@ -7008,8 +7064,11 @@
       <c r="F101" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="J101" s="101" t="s">
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10">
       <c r="A102" s="35" t="s">
         <v>272</v>
       </c>
@@ -7030,7 +7089,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:10">
       <c r="A103" s="35" t="s">
         <v>1018</v>
       </c>
@@ -7051,7 +7110,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:10">
       <c r="A104" s="35" t="s">
         <v>1022</v>
       </c>
@@ -7072,7 +7131,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:10">
       <c r="A105" s="35" t="s">
         <v>1023</v>
       </c>
@@ -7093,7 +7152,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:10">
       <c r="A106" s="35" t="s">
         <v>1024</v>
       </c>
@@ -7113,8 +7172,11 @@
       <c r="F106" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="J106" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10">
       <c r="A107" s="35" t="s">
         <v>1026</v>
       </c>
@@ -7135,7 +7197,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:10">
       <c r="A108" s="35" t="s">
         <v>1027</v>
       </c>
@@ -7156,7 +7218,7 @@
         <v>1029</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:10">
       <c r="A109" s="35" t="s">
         <v>1035</v>
       </c>
@@ -7177,7 +7239,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:10">
       <c r="A110" s="35" t="s">
         <v>1037</v>
       </c>
@@ -7198,7 +7260,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:10">
       <c r="A111" s="35" t="s">
         <v>1045</v>
       </c>
@@ -7219,7 +7281,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:10">
       <c r="A112" s="35" t="s">
         <v>1051</v>
       </c>
@@ -7239,8 +7301,11 @@
       <c r="F112" s="30" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="J112" t="s">
+        <v>1215</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7">
       <c r="A113" s="35" t="s">
         <v>1052</v>
       </c>
@@ -7261,7 +7326,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:7">
       <c r="A114" s="35" t="s">
         <v>1053</v>
       </c>
@@ -7282,7 +7347,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:7">
       <c r="A115" s="35" t="s">
         <v>1054</v>
       </c>
@@ -7303,7 +7368,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:7">
       <c r="A116" s="35" t="s">
         <v>1055</v>
       </c>
@@ -7324,7 +7389,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:7">
       <c r="A117" s="35" t="s">
         <v>1057</v>
       </c>
@@ -7345,7 +7410,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:7">
       <c r="A118" s="35" t="s">
         <v>1059</v>
       </c>
@@ -7366,7 +7431,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:7">
       <c r="A119" s="35" t="s">
         <v>1068</v>
       </c>
@@ -7387,7 +7452,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7">
       <c r="A120" s="35" t="s">
         <v>1076</v>
       </c>
@@ -7408,7 +7473,7 @@
         <v>1029</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:7">
       <c r="A121" s="35" t="s">
         <v>1078</v>
       </c>
@@ -7429,7 +7494,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:7">
       <c r="A122" s="35" t="s">
         <v>1080</v>
       </c>
@@ -7450,7 +7515,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:7">
       <c r="A123" s="35" t="s">
         <v>1081</v>
       </c>
@@ -7471,7 +7536,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:7">
       <c r="A124" s="35" t="s">
         <v>1083</v>
       </c>
@@ -7495,7 +7560,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:7">
       <c r="A125" s="35" t="s">
         <v>1085</v>
       </c>
@@ -7516,7 +7581,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:7">
       <c r="A126" s="35" t="s">
         <v>1086</v>
       </c>
@@ -7537,7 +7602,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:7">
       <c r="A127" s="35" t="s">
         <v>1088</v>
       </c>
@@ -7558,7 +7623,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:7">
       <c r="A128" s="35" t="s">
         <v>1090</v>
       </c>
@@ -7579,7 +7644,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:7">
       <c r="A129" s="35" t="s">
         <v>1091</v>
       </c>
@@ -7600,7 +7665,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:7">
       <c r="A130" s="35" t="s">
         <v>1092</v>
       </c>
@@ -7621,7 +7686,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:7">
       <c r="A131" s="35" t="s">
         <v>1093</v>
       </c>
@@ -7642,7 +7707,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:7">
       <c r="A132" s="35" t="s">
         <v>1094</v>
       </c>
@@ -7663,7 +7728,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:7">
       <c r="A133" s="35" t="s">
         <v>1096</v>
       </c>
@@ -7684,7 +7749,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:7">
       <c r="A134" s="35" t="s">
         <v>1097</v>
       </c>
@@ -7708,7 +7773,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:7">
       <c r="A135" s="35" t="s">
         <v>1098</v>
       </c>
@@ -7729,7 +7794,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:7">
       <c r="A136" s="35" t="s">
         <v>1100</v>
       </c>
@@ -7750,7 +7815,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:7">
       <c r="A137" s="35" t="s">
         <v>1101</v>
       </c>
@@ -7771,7 +7836,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:7">
       <c r="A138" s="35" t="s">
         <v>1102</v>
       </c>
@@ -7792,7 +7857,7 @@
         <v>1029</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:7">
       <c r="A139" s="35" t="s">
         <v>1104</v>
       </c>
@@ -7813,7 +7878,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:7">
       <c r="A140" s="35" t="s">
         <v>1105</v>
       </c>
@@ -7834,7 +7899,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:7">
       <c r="A141" s="35" t="s">
         <v>1106</v>
       </c>
@@ -7855,7 +7920,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:7">
       <c r="A142" s="35" t="s">
         <v>1107</v>
       </c>
@@ -7876,7 +7941,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:7">
       <c r="A143" s="35" t="s">
         <v>1109</v>
       </c>
@@ -7897,7 +7962,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:7">
       <c r="A144" s="35" t="s">
         <v>1110</v>
       </c>
@@ -7918,7 +7983,7 @@
         <v>1112</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:7">
       <c r="A145" s="35" t="s">
         <v>1118</v>
       </c>
@@ -7939,7 +8004,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:7">
       <c r="A146" s="35" t="s">
         <v>1119</v>
       </c>
@@ -7960,7 +8025,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:7">
       <c r="A147" s="35" t="s">
         <v>1120</v>
       </c>
@@ -7981,7 +8046,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:7">
       <c r="A148" s="35" t="s">
         <v>1094</v>
       </c>
@@ -8002,7 +8067,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:7">
       <c r="A149" s="35" t="s">
         <v>1121</v>
       </c>
@@ -8023,7 +8088,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:7">
       <c r="A150" s="35" t="s">
         <v>1122</v>
       </c>
@@ -8047,7 +8112,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:7">
       <c r="A151" s="35" t="s">
         <v>1124</v>
       </c>
@@ -8068,7 +8133,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:7">
       <c r="A152" s="35" t="s">
         <v>1125</v>
       </c>
@@ -8089,7 +8154,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:7">
       <c r="A153" s="35" t="s">
         <v>1127</v>
       </c>
@@ -8110,7 +8175,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:7">
       <c r="A154" s="35" t="s">
         <v>1088</v>
       </c>
@@ -8131,7 +8196,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:7">
       <c r="A155" s="35" t="s">
         <v>1130</v>
       </c>
@@ -8152,7 +8217,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:7">
       <c r="A156" s="35" t="s">
         <v>1131</v>
       </c>
@@ -8173,7 +8238,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:7">
       <c r="A157" s="35" t="s">
         <v>1132</v>
       </c>
@@ -8194,7 +8259,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:7">
       <c r="A158" s="35" t="s">
         <v>1134</v>
       </c>
@@ -8215,7 +8280,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:7">
       <c r="A159" s="35" t="s">
         <v>1136</v>
       </c>
@@ -8236,7 +8301,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:7">
       <c r="A160" s="35" t="s">
         <v>1137</v>
       </c>
@@ -8257,7 +8322,7 @@
         <v>959</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:6">
       <c r="A161" s="35" t="s">
         <v>1139</v>
       </c>
@@ -8278,7 +8343,7 @@
         <v>1140</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:6">
       <c r="A162" s="35" t="s">
         <v>1146</v>
       </c>
@@ -8299,7 +8364,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:6">
       <c r="A163" s="35" t="s">
         <v>1148</v>
       </c>
@@ -8320,7 +8385,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:6">
       <c r="A164" s="35" t="s">
         <v>1149</v>
       </c>
@@ -8341,7 +8406,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:6">
       <c r="A165" s="35" t="s">
         <v>1151</v>
       </c>
@@ -8362,7 +8427,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:6">
       <c r="A166" s="35" t="s">
         <v>1153</v>
       </c>
@@ -8377,7 +8442,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:6">
       <c r="A167" s="35" t="s">
         <v>1154</v>
       </c>
@@ -8398,7 +8463,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:6">
       <c r="A168" s="35" t="s">
         <v>1156</v>
       </c>
@@ -8419,7 +8484,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:6">
       <c r="A169" s="35" t="s">
         <v>1157</v>
       </c>
@@ -8440,7 +8505,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:6">
       <c r="A170" s="35" t="s">
         <v>1159</v>
       </c>
@@ -8461,7 +8526,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:6">
       <c r="A171" s="35" t="s">
         <v>1160</v>
       </c>
@@ -8482,7 +8547,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:6">
       <c r="A172" s="35" t="s">
         <v>1162</v>
       </c>
@@ -8503,7 +8568,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:6">
       <c r="A173" s="35" t="s">
         <v>1164</v>
       </c>
@@ -8524,7 +8589,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:6">
       <c r="A174" s="35" t="s">
         <v>1165</v>
       </c>
@@ -8545,7 +8610,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:6">
       <c r="A175" s="35" t="s">
         <v>1167</v>
       </c>
@@ -8566,7 +8631,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:6">
       <c r="A176" s="35" t="s">
         <v>1169</v>
       </c>
@@ -8587,7 +8652,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:6">
       <c r="A177" s="35" t="s">
         <v>1170</v>
       </c>
@@ -8608,7 +8673,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:6">
       <c r="A178" s="35" t="s">
         <v>1172</v>
       </c>
@@ -8629,7 +8694,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:6">
       <c r="A179" s="35" t="s">
         <v>1174</v>
       </c>
@@ -8650,7 +8715,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:6">
       <c r="A180" s="35" t="s">
         <v>1175</v>
       </c>
@@ -8671,7 +8736,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:6">
       <c r="A181" s="35" t="s">
         <v>1176</v>
       </c>
@@ -8692,7 +8757,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:6">
       <c r="A182" s="35" t="s">
         <v>1178</v>
       </c>
@@ -8713,7 +8778,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:6">
       <c r="A183" s="35" t="s">
         <v>1180</v>
       </c>
@@ -8734,7 +8799,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:6">
       <c r="A184" s="35" t="s">
         <v>1181</v>
       </c>
@@ -8755,7 +8820,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:6">
       <c r="A185" s="35" t="s">
         <v>1182</v>
       </c>
@@ -8776,7 +8841,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:6">
       <c r="A186" s="35" t="s">
         <v>1183</v>
       </c>
@@ -8797,7 +8862,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:6">
       <c r="A187" s="35" t="s">
         <v>1185</v>
       </c>
@@ -8818,7 +8883,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:6">
       <c r="A188" s="35" t="s">
         <v>1186</v>
       </c>
@@ -8839,7 +8904,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:6">
       <c r="A189" s="35" t="s">
         <v>1188</v>
       </c>
@@ -8860,7 +8925,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:6">
       <c r="A190" s="35" t="s">
         <v>1190</v>
       </c>
@@ -8881,7 +8946,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:6">
       <c r="A191" s="35" t="s">
         <v>1146</v>
       </c>
@@ -8902,7 +8967,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:6">
       <c r="A192" s="35" t="s">
         <v>1193</v>
       </c>
@@ -8923,7 +8988,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:6">
       <c r="A193" s="35" t="s">
         <v>1194</v>
       </c>
@@ -8971,7 +9036,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:N127"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19.28515625" customWidth="1"/>
     <col min="2" max="2" width="16.5703125" customWidth="1"/>
@@ -8980,7 +9045,7 @@
     <col min="9" max="9" width="96.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>274</v>
       </c>
@@ -9005,8 +9070,11 @@
       <c r="I1" s="37" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J1" s="2" t="s">
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
         <v>1005</v>
       </c>
@@ -9029,7 +9097,7 @@
       <c r="H2" s="83"/>
       <c r="I2" s="83"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14">
       <c r="A3" s="1" t="s">
         <v>1003</v>
       </c>
@@ -9052,7 +9120,7 @@
       <c r="H3" s="83"/>
       <c r="I3" s="83"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14">
       <c r="A4" s="1" t="s">
         <v>1001</v>
       </c>
@@ -9075,7 +9143,7 @@
       <c r="H4" s="83"/>
       <c r="I4" s="83"/>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14">
       <c r="A5" s="1" t="s">
         <v>1000</v>
       </c>
@@ -9098,7 +9166,7 @@
       <c r="H5" s="83"/>
       <c r="I5" s="83"/>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14">
       <c r="A6" s="1" t="s">
         <v>999</v>
       </c>
@@ -9121,7 +9189,7 @@
       <c r="H6" s="83"/>
       <c r="I6" s="83"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14">
       <c r="A7" s="1" t="s">
         <v>972</v>
       </c>
@@ -9144,7 +9212,7 @@
       <c r="H7" s="83"/>
       <c r="I7" s="83"/>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14">
       <c r="A8" s="1" t="s">
         <v>969</v>
       </c>
@@ -9167,7 +9235,7 @@
       <c r="H8" s="83"/>
       <c r="I8" s="83"/>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14">
       <c r="A9" s="1" t="s">
         <v>968</v>
       </c>
@@ -9190,7 +9258,7 @@
       <c r="H9" s="83"/>
       <c r="I9" s="83"/>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14">
       <c r="A10" s="1" t="s">
         <v>957</v>
       </c>
@@ -9213,7 +9281,7 @@
       <c r="H10" s="74"/>
       <c r="I10" s="74"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14">
       <c r="A11" s="1" t="s">
         <v>275</v>
       </c>
@@ -9236,7 +9304,7 @@
       <c r="H11" s="64"/>
       <c r="I11" s="64"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14">
       <c r="A12" s="1" t="s">
         <v>277</v>
       </c>
@@ -9259,7 +9327,7 @@
       <c r="H12" s="64"/>
       <c r="I12" s="64"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14">
       <c r="A13" s="1" t="s">
         <v>279</v>
       </c>
@@ -9280,7 +9348,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14">
       <c r="A14" s="1" t="s">
         <v>280</v>
       </c>
@@ -9301,7 +9369,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14">
       <c r="A15" s="1" t="s">
         <v>283</v>
       </c>
@@ -9328,7 +9396,7 @@
       <c r="M15" s="64"/>
       <c r="N15" s="1"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14">
       <c r="A16" s="1" t="s">
         <v>285</v>
       </c>
@@ -9349,7 +9417,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6">
       <c r="A17" s="1" t="s">
         <v>287</v>
       </c>
@@ -9370,7 +9438,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6">
       <c r="A18" s="1" t="s">
         <v>289</v>
       </c>
@@ -9391,7 +9459,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6">
       <c r="A19" s="1" t="s">
         <v>291</v>
       </c>
@@ -9412,7 +9480,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6">
       <c r="A20" s="1" t="s">
         <v>293</v>
       </c>
@@ -9433,7 +9501,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6">
       <c r="A21" s="1" t="s">
         <v>105</v>
       </c>
@@ -9454,7 +9522,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6">
       <c r="A22" s="1" t="s">
         <v>296</v>
       </c>
@@ -9475,7 +9543,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6">
       <c r="A23" s="1" t="s">
         <v>298</v>
       </c>
@@ -9496,7 +9564,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6">
       <c r="A24" s="1" t="s">
         <v>300</v>
       </c>
@@ -9517,7 +9585,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6">
       <c r="A25" s="1" t="s">
         <v>302</v>
       </c>
@@ -9538,7 +9606,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6">
       <c r="A26" s="1" t="s">
         <v>304</v>
       </c>
@@ -9559,7 +9627,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6">
       <c r="A27" s="1" t="s">
         <v>306</v>
       </c>
@@ -9580,7 +9648,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6">
       <c r="A28" s="1" t="s">
         <v>308</v>
       </c>
@@ -9601,7 +9669,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6">
       <c r="A29" s="1" t="s">
         <v>310</v>
       </c>
@@ -9622,7 +9690,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6">
       <c r="A30" t="s">
         <v>312</v>
       </c>
@@ -9643,7 +9711,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6">
       <c r="A31" s="7" t="s">
         <v>314</v>
       </c>
@@ -9664,7 +9732,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6">
       <c r="A32" s="1" t="s">
         <v>315</v>
       </c>
@@ -9685,7 +9753,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8">
       <c r="A33" s="1" t="s">
         <v>317</v>
       </c>
@@ -9706,7 +9774,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8">
       <c r="A34" t="s">
         <v>319</v>
       </c>
@@ -9727,7 +9795,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8">
       <c r="A35" s="1" t="s">
         <v>320</v>
       </c>
@@ -9748,7 +9816,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8">
       <c r="A36" t="s">
         <v>322</v>
       </c>
@@ -9769,7 +9837,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8">
       <c r="A37" s="7" t="s">
         <v>324</v>
       </c>
@@ -9793,7 +9861,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8">
       <c r="A38" s="7" t="s">
         <v>326</v>
       </c>
@@ -9814,7 +9882,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8">
       <c r="A39" s="7" t="s">
         <v>328</v>
       </c>
@@ -9835,7 +9903,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8">
       <c r="A40" s="7" t="s">
         <v>330</v>
       </c>
@@ -9856,7 +9924,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8">
       <c r="A41" s="7" t="s">
         <v>331</v>
       </c>
@@ -9877,7 +9945,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8">
       <c r="A42" s="7" t="s">
         <v>334</v>
       </c>
@@ -9898,7 +9966,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8">
       <c r="A43" s="7" t="s">
         <v>336</v>
       </c>
@@ -9919,7 +9987,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8">
       <c r="A44" s="7" t="s">
         <v>338</v>
       </c>
@@ -9940,7 +10008,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8">
       <c r="A45" s="7" t="s">
         <v>340</v>
       </c>
@@ -9961,7 +10029,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8">
       <c r="A46" s="7" t="s">
         <v>342</v>
       </c>
@@ -9982,7 +10050,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8">
       <c r="A47" s="7" t="s">
         <v>345</v>
       </c>
@@ -10003,7 +10071,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8">
       <c r="A48" s="7" t="s">
         <v>347</v>
       </c>
@@ -10024,7 +10092,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9">
       <c r="A49" s="7" t="s">
         <v>349</v>
       </c>
@@ -10045,7 +10113,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9">
       <c r="A50" t="s">
         <v>350</v>
       </c>
@@ -10066,7 +10134,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9">
       <c r="A51" s="7" t="s">
         <v>353</v>
       </c>
@@ -10087,7 +10155,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9">
       <c r="A52" s="7" t="s">
         <v>355</v>
       </c>
@@ -10108,7 +10176,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9">
       <c r="A53" s="7" t="s">
         <v>356</v>
       </c>
@@ -10129,7 +10197,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9">
       <c r="A54" s="7" t="s">
         <v>358</v>
       </c>
@@ -10153,7 +10221,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9">
       <c r="A55" s="7" t="s">
         <v>359</v>
       </c>
@@ -10174,7 +10242,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9">
       <c r="A56" s="7" t="s">
         <v>361</v>
       </c>
@@ -10201,7 +10269,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9">
       <c r="A57" s="7" t="s">
         <v>364</v>
       </c>
@@ -10222,7 +10290,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9">
       <c r="A58" s="7" t="s">
         <v>287</v>
       </c>
@@ -10243,7 +10311,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9">
       <c r="A59" s="7" t="s">
         <v>366</v>
       </c>
@@ -10264,7 +10332,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9">
       <c r="A60" s="7" t="s">
         <v>367</v>
       </c>
@@ -10285,7 +10353,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9">
       <c r="A61" s="7" t="s">
         <v>370</v>
       </c>
@@ -10306,7 +10374,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9">
       <c r="A62" s="7" t="s">
         <v>372</v>
       </c>
@@ -10327,7 +10395,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9">
       <c r="A63" s="7" t="s">
         <v>374</v>
       </c>
@@ -10351,7 +10419,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9">
       <c r="A64" s="7" t="s">
         <v>376</v>
       </c>
@@ -10372,7 +10440,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9">
       <c r="A65" t="s">
         <v>377</v>
       </c>
@@ -10393,7 +10461,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9">
       <c r="A66" s="7" t="s">
         <v>379</v>
       </c>
@@ -10414,7 +10482,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9">
       <c r="A67" s="7" t="s">
         <v>381</v>
       </c>
@@ -10435,7 +10503,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9">
       <c r="A68" s="7" t="s">
         <v>382</v>
       </c>
@@ -10462,7 +10530,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9">
       <c r="A69" t="s">
         <v>384</v>
       </c>
@@ -10483,7 +10551,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9">
       <c r="A70" t="s">
         <v>386</v>
       </c>
@@ -10504,7 +10572,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9">
       <c r="A71" t="s">
         <v>388</v>
       </c>
@@ -10525,7 +10593,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9">
       <c r="A72" t="s">
         <v>390</v>
       </c>
@@ -10546,7 +10614,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9">
       <c r="A73" t="s">
         <v>392</v>
       </c>
@@ -10567,7 +10635,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9">
       <c r="A74" t="s">
         <v>393</v>
       </c>
@@ -10588,7 +10656,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9">
       <c r="A75" t="s">
         <v>395</v>
       </c>
@@ -10609,7 +10677,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9">
       <c r="A76" t="s">
         <v>396</v>
       </c>
@@ -10630,7 +10698,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9">
       <c r="A77" t="s">
         <v>398</v>
       </c>
@@ -10651,7 +10719,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9">
       <c r="A78" t="s">
         <v>399</v>
       </c>
@@ -10672,7 +10740,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9">
       <c r="A79" t="s">
         <v>401</v>
       </c>
@@ -10693,7 +10761,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9">
       <c r="A80" t="s">
         <v>402</v>
       </c>
@@ -10714,7 +10782,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6">
       <c r="A81" t="s">
         <v>404</v>
       </c>
@@ -10735,7 +10803,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6">
       <c r="A82" t="s">
         <v>407</v>
       </c>
@@ -10756,7 +10824,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6">
       <c r="A83" t="s">
         <v>408</v>
       </c>
@@ -10777,7 +10845,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6">
       <c r="A84" t="s">
         <v>409</v>
       </c>
@@ -10798,7 +10866,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6">
       <c r="A85" t="s">
         <v>411</v>
       </c>
@@ -10819,7 +10887,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6">
       <c r="A86" t="s">
         <v>413</v>
       </c>
@@ -10840,7 +10908,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6">
       <c r="A87" t="s">
         <v>414</v>
       </c>
@@ -10861,7 +10929,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6">
       <c r="A88" t="s">
         <v>416</v>
       </c>
@@ -10882,7 +10950,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6">
       <c r="A89" t="s">
         <v>417</v>
       </c>
@@ -10903,7 +10971,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6">
       <c r="A90" t="s">
         <v>419</v>
       </c>
@@ -10924,7 +10992,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6">
       <c r="A91" t="s">
         <v>421</v>
       </c>
@@ -10945,7 +11013,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6">
       <c r="A92" t="s">
         <v>423</v>
       </c>
@@ -10966,7 +11034,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6">
       <c r="A93" t="s">
         <v>424</v>
       </c>
@@ -10987,7 +11055,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6">
       <c r="A94" t="s">
         <v>426</v>
       </c>
@@ -11008,7 +11076,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6">
       <c r="A95" t="s">
         <v>429</v>
       </c>
@@ -11029,7 +11097,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6">
       <c r="A96" t="s">
         <v>431</v>
       </c>
@@ -11050,7 +11118,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6">
       <c r="A97" t="s">
         <v>432</v>
       </c>
@@ -11071,7 +11139,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6">
       <c r="A98" t="s">
         <v>434</v>
       </c>
@@ -11092,7 +11160,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6">
       <c r="A99" t="s">
         <v>435</v>
       </c>
@@ -11113,7 +11181,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6">
       <c r="A100" t="s">
         <v>436</v>
       </c>
@@ -11134,7 +11202,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6">
       <c r="A101" t="s">
         <v>437</v>
       </c>
@@ -11155,7 +11223,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6">
       <c r="A102" t="s">
         <v>439</v>
       </c>
@@ -11176,7 +11244,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6">
       <c r="A103" t="s">
         <v>440</v>
       </c>
@@ -11197,7 +11265,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6">
       <c r="A104" t="s">
         <v>442</v>
       </c>
@@ -11218,7 +11286,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6">
       <c r="A105" t="s">
         <v>445</v>
       </c>
@@ -11239,7 +11307,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6">
       <c r="A106" t="s">
         <v>448</v>
       </c>
@@ -11260,7 +11328,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6">
       <c r="A107" t="s">
         <v>450</v>
       </c>
@@ -11281,7 +11349,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6">
       <c r="A108" s="9" t="s">
         <v>452</v>
       </c>
@@ -11301,7 +11369,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6">
       <c r="A109" s="9" t="s">
         <v>455</v>
       </c>
@@ -11322,7 +11390,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6">
       <c r="A110" s="9" t="s">
         <v>456</v>
       </c>
@@ -11343,7 +11411,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6">
       <c r="A111" s="9" t="s">
         <v>459</v>
       </c>
@@ -11364,7 +11432,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:6">
       <c r="A112" s="9" t="s">
         <v>461</v>
       </c>
@@ -11385,7 +11453,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:8">
       <c r="A113" s="9" t="s">
         <v>463</v>
       </c>
@@ -11406,7 +11474,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:8">
       <c r="A114" s="9" t="s">
         <v>464</v>
       </c>
@@ -11427,7 +11495,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:8">
       <c r="A115" s="9" t="s">
         <v>466</v>
       </c>
@@ -11448,7 +11516,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:8">
       <c r="A116" s="9" t="s">
         <v>468</v>
       </c>
@@ -11472,7 +11540,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:8">
       <c r="A117" s="9" t="s">
         <v>470</v>
       </c>
@@ -11496,7 +11564,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:8">
       <c r="A118" s="9" t="s">
         <v>472</v>
       </c>
@@ -11517,7 +11585,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:8">
       <c r="A119" s="9" t="s">
         <v>474</v>
       </c>
@@ -11538,7 +11606,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:8">
       <c r="A120" s="9" t="s">
         <v>475</v>
       </c>
@@ -11559,7 +11627,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:8">
       <c r="A121" s="9" t="s">
         <v>477</v>
       </c>
@@ -11580,7 +11648,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:8">
       <c r="A122" s="9" t="s">
         <v>479</v>
       </c>
@@ -11601,7 +11669,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:8">
       <c r="A123" s="9" t="s">
         <v>481</v>
       </c>
@@ -11622,7 +11690,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:8">
       <c r="A124" s="9" t="s">
         <v>482</v>
       </c>
@@ -11643,7 +11711,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:8">
       <c r="A125" t="s">
         <v>483</v>
       </c>
@@ -11664,7 +11732,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:8">
       <c r="A126" s="9" t="s">
         <v>484</v>
       </c>
@@ -11685,7 +11753,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:8">
       <c r="B127" s="1" t="str">
         <f t="shared" si="13"/>
         <v/>
@@ -11732,7 +11800,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:M81"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22.28515625" style="3" customWidth="1"/>
     <col min="2" max="6" width="11.42578125" style="3" customWidth="1"/>
@@ -11745,7 +11813,7 @@
     <col min="13" max="16384" width="11.42578125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A1" s="3" t="s">
         <v>74</v>
       </c>
@@ -11783,7 +11851,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>126</v>
       </c>
@@ -11818,7 +11886,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A3" s="3" t="s">
         <v>115</v>
       </c>
@@ -11856,7 +11924,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A4" s="3" t="s">
         <v>37</v>
       </c>
@@ -11891,7 +11959,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A5" s="3" t="s">
         <v>122</v>
       </c>
@@ -11929,7 +11997,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A6" s="3" t="s">
         <v>104</v>
       </c>
@@ -11967,7 +12035,7 @@
         <v>980</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A7" s="3" t="s">
         <v>282</v>
       </c>
@@ -12002,7 +12070,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A8" s="3" t="s">
         <v>112</v>
       </c>
@@ -12040,7 +12108,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A9" s="3" t="s">
         <v>136</v>
       </c>
@@ -12078,7 +12146,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A10" s="3" t="s">
         <v>99</v>
       </c>
@@ -12113,7 +12181,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A11" s="3" t="s">
         <v>344</v>
       </c>
@@ -12148,7 +12216,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A12" s="3" t="s">
         <v>369</v>
       </c>
@@ -12183,7 +12251,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A13" s="3" t="s">
         <v>141</v>
       </c>
@@ -12218,7 +12286,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A14" s="3" t="s">
         <v>257</v>
       </c>
@@ -12253,7 +12321,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A15" s="3" t="s">
         <v>231</v>
       </c>
@@ -12285,7 +12353,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A16" s="3" t="s">
         <v>88</v>
       </c>
@@ -12314,7 +12382,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A17" s="3" t="s">
         <v>168</v>
       </c>
@@ -12349,7 +12417,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A18" s="3" t="s">
         <v>91</v>
       </c>
@@ -12384,7 +12452,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A19" s="3" t="s">
         <v>193</v>
       </c>
@@ -12422,7 +12490,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A20" s="3" t="s">
         <v>144</v>
       </c>
@@ -12457,7 +12525,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A21" s="3" t="s">
         <v>85</v>
       </c>
@@ -12492,7 +12560,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A22" s="3" t="s">
         <v>119</v>
       </c>
@@ -12527,7 +12595,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A23" s="3" t="s">
         <v>594</v>
       </c>
@@ -12562,7 +12630,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A24" s="3" t="s">
         <v>333</v>
       </c>
@@ -12597,7 +12665,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A25" s="3" t="s">
         <v>604</v>
       </c>
@@ -12632,7 +12700,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A26" s="3" t="s">
         <v>107</v>
       </c>
@@ -12667,7 +12735,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A27" s="3" t="s">
         <v>94</v>
       </c>
@@ -12702,7 +12770,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A28" s="3" t="s">
         <v>129</v>
       </c>
@@ -12737,7 +12805,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A29" s="3" t="s">
         <v>321</v>
       </c>
@@ -12772,7 +12840,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A30" s="3" t="s">
         <v>323</v>
       </c>
@@ -12807,7 +12875,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A31" s="6" t="s">
         <v>339</v>
       </c>
@@ -12842,7 +12910,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A32" s="6" t="s">
         <v>266</v>
       </c>
@@ -12880,7 +12948,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A33" s="6" t="s">
         <v>352</v>
       </c>
@@ -12915,7 +12983,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A34" s="3" t="s">
         <v>211</v>
       </c>
@@ -12950,7 +13018,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" ht="39.950000000000003" customHeight="1">
       <c r="A35" s="3" t="s">
         <v>406</v>
       </c>
@@ -12985,7 +13053,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" ht="44.25" customHeight="1">
       <c r="A36" s="3" t="s">
         <v>428</v>
       </c>
@@ -13023,7 +13091,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="37" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" ht="72" customHeight="1">
       <c r="A37" s="3" t="s">
         <v>444</v>
       </c>
@@ -13058,7 +13126,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="38" spans="1:12" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" ht="29.25" customHeight="1">
       <c r="A38" s="3" t="s">
         <v>447</v>
       </c>
@@ -13093,7 +13161,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="39" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" ht="34.5" customHeight="1">
       <c r="A39" s="3" t="s">
         <v>449</v>
       </c>
@@ -13128,7 +13196,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="40" spans="1:12" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" ht="47.25" customHeight="1">
       <c r="A40" s="3" t="s">
         <v>451</v>
       </c>
@@ -13163,7 +13231,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="41" spans="1:12" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" ht="49.5" customHeight="1">
       <c r="A41" s="3" t="s">
         <v>454</v>
       </c>
@@ -13198,7 +13266,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="42" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" ht="72" customHeight="1">
       <c r="A42" s="11" t="s">
         <v>458</v>
       </c>
@@ -13236,7 +13304,7 @@
         <v>988</v>
       </c>
     </row>
-    <row r="43" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" ht="72" customHeight="1">
       <c r="A43" s="11" t="s">
         <v>476</v>
       </c>
@@ -13271,7 +13339,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="44" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" ht="72" customHeight="1">
       <c r="A44" s="11" t="s">
         <v>688</v>
       </c>
@@ -13306,7 +13374,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="45" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" ht="72" customHeight="1">
       <c r="A45" s="15" t="s">
         <v>693</v>
       </c>
@@ -13337,7 +13405,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="46" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" ht="72" customHeight="1">
       <c r="A46" s="13" t="s">
         <v>699</v>
       </c>
@@ -13372,7 +13440,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="47" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" ht="72" customHeight="1">
       <c r="A47" s="13" t="s">
         <v>705</v>
       </c>
@@ -13403,7 +13471,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="48" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" ht="72" customHeight="1">
       <c r="A48" s="13" t="s">
         <v>711</v>
       </c>
@@ -13434,7 +13502,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11" ht="72" customHeight="1">
       <c r="A49" s="13" t="s">
         <v>717</v>
       </c>
@@ -13465,7 +13533,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11" ht="51" customHeight="1">
       <c r="A50" s="13" t="s">
         <v>723</v>
       </c>
@@ -13500,7 +13568,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11" ht="72" customHeight="1">
       <c r="A51" s="13" t="s">
         <v>729</v>
       </c>
@@ -13535,7 +13603,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:11" ht="72" customHeight="1">
       <c r="A52" s="13" t="s">
         <v>734</v>
       </c>
@@ -13570,7 +13638,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:11" ht="57.6" customHeight="1">
       <c r="A53" s="13" t="s">
         <v>739</v>
       </c>
@@ -13601,7 +13669,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:11" ht="57.6" customHeight="1">
       <c r="A54" s="13" t="s">
         <v>744</v>
       </c>
@@ -13632,7 +13700,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="55" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11" ht="72" customHeight="1">
       <c r="A55" s="13" t="s">
         <v>749</v>
       </c>
@@ -13663,7 +13731,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:11" ht="72" customHeight="1">
       <c r="A56" s="13" t="s">
         <v>252</v>
       </c>
@@ -13694,7 +13762,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" ht="72" customHeight="1">
       <c r="A57" s="13" t="s">
         <v>758</v>
       </c>
@@ -13725,7 +13793,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="86.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:11" ht="86.45" customHeight="1">
       <c r="A58" s="13" t="s">
         <v>765</v>
       </c>
@@ -13756,7 +13824,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:11" ht="72" customHeight="1">
       <c r="A59" s="13" t="s">
         <v>772</v>
       </c>
@@ -13787,7 +13855,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:11" ht="72" customHeight="1">
       <c r="A60" s="13" t="s">
         <v>777</v>
       </c>
@@ -13818,7 +13886,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:11" ht="72" customHeight="1">
       <c r="A61" s="3" t="s">
         <v>782</v>
       </c>
@@ -13849,7 +13917,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:11" ht="72" customHeight="1">
       <c r="A62" s="11" t="s">
         <v>788</v>
       </c>
@@ -13880,7 +13948,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="63" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:11" ht="48" customHeight="1">
       <c r="A63" s="18" t="s">
         <v>793</v>
       </c>
@@ -13909,7 +13977,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="64" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:11" ht="42" customHeight="1">
       <c r="A64" s="19" t="s">
         <v>799</v>
       </c>
@@ -13938,7 +14006,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="65" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:13" ht="45" customHeight="1">
       <c r="A65" s="19" t="s">
         <v>804</v>
       </c>
@@ -13967,7 +14035,7 @@
         <v>808</v>
       </c>
     </row>
-    <row r="66" spans="1:13" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:13" ht="72" customHeight="1">
       <c r="A66" s="19" t="s">
         <v>809</v>
       </c>
@@ -13996,7 +14064,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="67" spans="1:13" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:13" ht="72" customHeight="1">
       <c r="A67" s="19" t="s">
         <v>814</v>
       </c>
@@ -14025,7 +14093,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="68" spans="1:13" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:13" ht="72" customHeight="1">
       <c r="A68" s="19" t="s">
         <v>819</v>
       </c>
@@ -14054,7 +14122,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="69" spans="1:13" ht="409.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:13" ht="409.6" customHeight="1">
       <c r="A69" s="31" t="s">
         <v>196</v>
       </c>
@@ -14089,7 +14157,7 @@
         <v>827</v>
       </c>
     </row>
-    <row r="70" spans="1:13" ht="409.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:13" ht="409.6" customHeight="1">
       <c r="A70" s="31" t="s">
         <v>187</v>
       </c>
@@ -14130,7 +14198,7 @@
         <v>973</v>
       </c>
     </row>
-    <row r="71" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:13" ht="105">
       <c r="A71" s="3" t="s">
         <v>951</v>
       </c>
@@ -14168,7 +14236,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="72" spans="1:13" ht="150" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:13" ht="150">
       <c r="A72" s="3" t="s">
         <v>959</v>
       </c>
@@ -14206,7 +14274,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="73" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:13" ht="75">
       <c r="A73" s="3" t="s">
         <v>1006</v>
       </c>
@@ -14238,7 +14306,7 @@
         <v>1011</v>
       </c>
     </row>
-    <row r="74" spans="1:13" ht="120" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:13" ht="120">
       <c r="A74" s="86" t="s">
         <v>1029</v>
       </c>
@@ -14270,7 +14338,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="75" spans="1:13" ht="135" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:13" ht="135">
       <c r="A75" s="89" t="s">
         <v>1039</v>
       </c>
@@ -14308,7 +14376,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="76" spans="1:13" ht="150" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:13" ht="150">
       <c r="A76" s="91" t="s">
         <v>1046</v>
       </c>
@@ -14346,7 +14414,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="77" spans="1:13" ht="360" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:13" ht="360">
       <c r="A77" s="94" t="s">
         <v>1061</v>
       </c>
@@ -14384,7 +14452,7 @@
         <v>1066</v>
       </c>
     </row>
-    <row r="78" spans="1:13" ht="135" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:13" ht="135">
       <c r="A78" s="94" t="s">
         <v>1069</v>
       </c>
@@ -14422,7 +14490,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="79" spans="1:13" ht="120" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:13" ht="120">
       <c r="A79" s="93" t="s">
         <v>1112</v>
       </c>
@@ -14460,7 +14528,7 @@
         <v>1116</v>
       </c>
     </row>
-    <row r="80" spans="1:13" ht="120" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:13" ht="120">
       <c r="A80" s="94" t="s">
         <v>1140</v>
       </c>
@@ -14492,7 +14560,7 @@
         <v>1144</v>
       </c>
     </row>
-    <row r="81" spans="1:12" ht="150" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:12" ht="150">
       <c r="A81" s="94" t="s">
         <v>1198</v>
       </c>
@@ -14588,13 +14656,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G18"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="5" max="5" width="23.7109375" customWidth="1"/>
     <col min="6" max="6" width="24.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7">
       <c r="A1" s="23" t="s">
         <v>830</v>
       </c>
@@ -14611,7 +14679,7 @@
       </c>
       <c r="G1" s="1"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7">
       <c r="A2" s="20" t="s">
         <v>495</v>
       </c>
@@ -14628,7 +14696,7 @@
       </c>
       <c r="G2" s="1"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7">
       <c r="A3" s="20" t="s">
         <v>556</v>
       </c>
@@ -14645,7 +14713,7 @@
       </c>
       <c r="G3" s="1"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7">
       <c r="A4" s="20" t="s">
         <v>566</v>
       </c>
@@ -14662,7 +14730,7 @@
       </c>
       <c r="G4" s="1"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7">
       <c r="A5" s="20" t="s">
         <v>589</v>
       </c>
@@ -14677,7 +14745,7 @@
       </c>
       <c r="G5" s="1"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7">
       <c r="A6" s="20" t="s">
         <v>614</v>
       </c>
@@ -14692,7 +14760,7 @@
       </c>
       <c r="G6" s="1"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7">
       <c r="A7" s="20" t="s">
         <v>539</v>
       </c>
@@ -14703,7 +14771,7 @@
       <c r="F7" s="20"/>
       <c r="G7" s="1"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7">
       <c r="A8" s="21" t="s">
         <v>643</v>
       </c>
@@ -14714,7 +14782,7 @@
       <c r="F8" s="20"/>
       <c r="G8" s="1"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7">
       <c r="A9" s="22" t="s">
         <v>766</v>
       </c>
@@ -14725,7 +14793,7 @@
       <c r="F9" s="20"/>
       <c r="G9" s="1"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7">
       <c r="A10" s="20" t="s">
         <v>783</v>
       </c>
@@ -14736,7 +14804,7 @@
       <c r="F10" s="20"/>
       <c r="G10" s="1"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7">
       <c r="A11" s="22" t="s">
         <v>794</v>
       </c>
@@ -14747,7 +14815,7 @@
       <c r="F11" s="20"/>
       <c r="G11" s="1"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7">
       <c r="A12" s="20" t="s">
         <v>759</v>
       </c>
@@ -14758,7 +14826,7 @@
       <c r="F12" s="20"/>
       <c r="G12" s="1"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7">
       <c r="A13" s="20" t="s">
         <v>529</v>
       </c>
@@ -14769,7 +14837,7 @@
       <c r="F13" s="20"/>
       <c r="G13" s="1"/>
     </row>
-    <row r="14" spans="1:7" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="28.9" customHeight="1">
       <c r="A14" s="27" t="s">
         <v>694</v>
       </c>
@@ -14780,7 +14848,7 @@
       <c r="F14" s="20"/>
       <c r="G14" s="1"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7">
       <c r="A15" s="20"/>
       <c r="B15" s="20"/>
       <c r="C15" s="20"/>
@@ -14789,7 +14857,7 @@
       <c r="F15" s="20"/>
       <c r="G15" s="1"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7">
       <c r="A16" s="20"/>
       <c r="B16" s="20"/>
       <c r="C16" s="20"/>
@@ -14798,7 +14866,7 @@
       <c r="F16" s="20"/>
       <c r="G16" s="1"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7">
       <c r="A17" s="20"/>
       <c r="B17" s="20"/>
       <c r="C17" s="20"/>
@@ -14807,7 +14875,7 @@
       <c r="F17" s="20"/>
       <c r="G17" s="1"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -14825,204 +14893,204 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:Q172"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1">
       <c r="A1" s="40"/>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1">
       <c r="A2" s="41" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1">
       <c r="A3" s="41" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1">
       <c r="A4" s="41" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1">
       <c r="A5" s="41" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1">
       <c r="A6" s="41" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1">
       <c r="A7" s="41" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1">
       <c r="A8" s="41" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1">
       <c r="A9" s="41" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1">
       <c r="A10" s="41" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1">
       <c r="A11" s="41" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" ht="15.6" customHeight="1">
       <c r="A13" s="42" t="s">
         <v>833</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1">
       <c r="A14" s="40"/>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1">
       <c r="A15" s="41" t="s">
         <v>834</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1">
       <c r="A16" s="41" t="s">
         <v>835</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17">
       <c r="A17" s="41" t="s">
         <v>836</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17">
       <c r="A18" s="41" t="s">
         <v>837</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17">
       <c r="A19" s="41" t="s">
         <v>838</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17">
       <c r="A20" s="41" t="s">
         <v>839</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17">
       <c r="A21" s="41" t="s">
         <v>840</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:17">
       <c r="A22" s="41" t="s">
         <v>841</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:17">
       <c r="A23" s="41" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:17">
       <c r="A24" s="41" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17">
       <c r="A26" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:17">
       <c r="A27" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A28" s="102" t="s">
+    <row r="28" spans="1:17">
+      <c r="A28" s="104" t="s">
         <v>842</v>
       </c>
-      <c r="B28" s="100"/>
-      <c r="C28" s="100"/>
-      <c r="D28" s="100"/>
-      <c r="E28" s="100"/>
-      <c r="F28" s="100"/>
-      <c r="G28" s="100"/>
-      <c r="H28" s="100"/>
-      <c r="I28" s="100"/>
-      <c r="J28" s="100"/>
-      <c r="K28" s="100"/>
-      <c r="L28" s="100"/>
-      <c r="M28" s="100"/>
-      <c r="N28" s="100"/>
-      <c r="O28" s="100"/>
-      <c r="P28" s="100"/>
-      <c r="Q28" s="100"/>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A29" s="100"/>
-      <c r="B29" s="100"/>
-      <c r="C29" s="100"/>
-      <c r="D29" s="100"/>
-      <c r="E29" s="100"/>
-      <c r="F29" s="100"/>
-      <c r="G29" s="100"/>
-      <c r="H29" s="100"/>
-      <c r="I29" s="100"/>
-      <c r="J29" s="100"/>
-      <c r="K29" s="100"/>
-      <c r="L29" s="100"/>
-      <c r="M29" s="100"/>
-      <c r="N29" s="100"/>
-      <c r="O29" s="100"/>
-      <c r="P29" s="100"/>
-      <c r="Q29" s="100"/>
-    </row>
-    <row r="30" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="101" t="s">
+      <c r="B28" s="103"/>
+      <c r="C28" s="103"/>
+      <c r="D28" s="103"/>
+      <c r="E28" s="103"/>
+      <c r="F28" s="103"/>
+      <c r="G28" s="103"/>
+      <c r="H28" s="103"/>
+      <c r="I28" s="103"/>
+      <c r="J28" s="103"/>
+      <c r="K28" s="103"/>
+      <c r="L28" s="103"/>
+      <c r="M28" s="103"/>
+      <c r="N28" s="103"/>
+      <c r="O28" s="103"/>
+      <c r="P28" s="103"/>
+      <c r="Q28" s="103"/>
+    </row>
+    <row r="29" spans="1:17">
+      <c r="A29" s="103"/>
+      <c r="B29" s="103"/>
+      <c r="C29" s="103"/>
+      <c r="D29" s="103"/>
+      <c r="E29" s="103"/>
+      <c r="F29" s="103"/>
+      <c r="G29" s="103"/>
+      <c r="H29" s="103"/>
+      <c r="I29" s="103"/>
+      <c r="J29" s="103"/>
+      <c r="K29" s="103"/>
+      <c r="L29" s="103"/>
+      <c r="M29" s="103"/>
+      <c r="N29" s="103"/>
+      <c r="O29" s="103"/>
+      <c r="P29" s="103"/>
+      <c r="Q29" s="103"/>
+    </row>
+    <row r="30" spans="1:17" ht="14.45" customHeight="1">
+      <c r="A30" s="105" t="s">
         <v>20</v>
       </c>
-      <c r="B30" s="99" t="s">
+      <c r="B30" s="102" t="s">
         <v>21</v>
       </c>
-      <c r="C30" s="100"/>
-      <c r="D30" s="100"/>
-      <c r="E30" s="99" t="s">
+      <c r="C30" s="103"/>
+      <c r="D30" s="103"/>
+      <c r="E30" s="102" t="s">
         <v>22</v>
       </c>
-      <c r="F30" s="100"/>
-      <c r="G30" s="100"/>
-      <c r="H30" s="99" t="s">
+      <c r="F30" s="103"/>
+      <c r="G30" s="103"/>
+      <c r="H30" s="102" t="s">
         <v>23</v>
       </c>
-      <c r="I30" s="100"/>
-      <c r="J30" s="100"/>
-      <c r="K30" s="99" t="s">
+      <c r="I30" s="103"/>
+      <c r="J30" s="103"/>
+      <c r="K30" s="102" t="s">
         <v>24</v>
       </c>
-      <c r="L30" s="100"/>
-      <c r="M30" s="100"/>
-      <c r="N30" s="100"/>
-      <c r="O30" s="100"/>
-      <c r="P30" s="99" t="s">
+      <c r="L30" s="103"/>
+      <c r="M30" s="103"/>
+      <c r="N30" s="103"/>
+      <c r="O30" s="103"/>
+      <c r="P30" s="102" t="s">
         <v>25</v>
       </c>
-      <c r="Q30" s="99" t="s">
+      <c r="Q30" s="102" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A31" s="100"/>
+    <row r="31" spans="1:17">
+      <c r="A31" s="103"/>
       <c r="B31" s="43" t="s">
         <v>27</v>
       </c>
@@ -15065,10 +15133,10 @@
       <c r="O31" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P31" s="100"/>
-      <c r="Q31" s="100"/>
-    </row>
-    <row r="32" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P31" s="103"/>
+      <c r="Q31" s="103"/>
+    </row>
+    <row r="32" spans="1:17" ht="43.15" customHeight="1">
       <c r="A32" s="43" t="s">
         <v>843</v>
       </c>
@@ -15119,81 +15187,81 @@
         <v>13</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A33" s="102" t="s">
+    <row r="33" spans="1:17">
+      <c r="A33" s="104" t="s">
         <v>643</v>
       </c>
-      <c r="B33" s="100"/>
-      <c r="C33" s="100"/>
-      <c r="D33" s="100"/>
-      <c r="E33" s="100"/>
-      <c r="F33" s="100"/>
-      <c r="G33" s="100"/>
-      <c r="H33" s="100"/>
-      <c r="I33" s="100"/>
-      <c r="J33" s="100"/>
-      <c r="K33" s="100"/>
-      <c r="L33" s="100"/>
-      <c r="M33" s="100"/>
-      <c r="N33" s="100"/>
-      <c r="O33" s="100"/>
-      <c r="P33" s="100"/>
-      <c r="Q33" s="100"/>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A34" s="100"/>
-      <c r="B34" s="100"/>
-      <c r="C34" s="100"/>
-      <c r="D34" s="100"/>
-      <c r="E34" s="100"/>
-      <c r="F34" s="100"/>
-      <c r="G34" s="100"/>
-      <c r="H34" s="100"/>
-      <c r="I34" s="100"/>
-      <c r="J34" s="100"/>
-      <c r="K34" s="100"/>
-      <c r="L34" s="100"/>
-      <c r="M34" s="100"/>
-      <c r="N34" s="100"/>
-      <c r="O34" s="100"/>
-      <c r="P34" s="100"/>
-      <c r="Q34" s="100"/>
-    </row>
-    <row r="35" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="101" t="s">
+      <c r="B33" s="103"/>
+      <c r="C33" s="103"/>
+      <c r="D33" s="103"/>
+      <c r="E33" s="103"/>
+      <c r="F33" s="103"/>
+      <c r="G33" s="103"/>
+      <c r="H33" s="103"/>
+      <c r="I33" s="103"/>
+      <c r="J33" s="103"/>
+      <c r="K33" s="103"/>
+      <c r="L33" s="103"/>
+      <c r="M33" s="103"/>
+      <c r="N33" s="103"/>
+      <c r="O33" s="103"/>
+      <c r="P33" s="103"/>
+      <c r="Q33" s="103"/>
+    </row>
+    <row r="34" spans="1:17">
+      <c r="A34" s="103"/>
+      <c r="B34" s="103"/>
+      <c r="C34" s="103"/>
+      <c r="D34" s="103"/>
+      <c r="E34" s="103"/>
+      <c r="F34" s="103"/>
+      <c r="G34" s="103"/>
+      <c r="H34" s="103"/>
+      <c r="I34" s="103"/>
+      <c r="J34" s="103"/>
+      <c r="K34" s="103"/>
+      <c r="L34" s="103"/>
+      <c r="M34" s="103"/>
+      <c r="N34" s="103"/>
+      <c r="O34" s="103"/>
+      <c r="P34" s="103"/>
+      <c r="Q34" s="103"/>
+    </row>
+    <row r="35" spans="1:17" ht="14.45" customHeight="1">
+      <c r="A35" s="105" t="s">
         <v>20</v>
       </c>
-      <c r="B35" s="99" t="s">
+      <c r="B35" s="102" t="s">
         <v>21</v>
       </c>
-      <c r="C35" s="100"/>
-      <c r="D35" s="100"/>
-      <c r="E35" s="99" t="s">
+      <c r="C35" s="103"/>
+      <c r="D35" s="103"/>
+      <c r="E35" s="102" t="s">
         <v>22</v>
       </c>
-      <c r="F35" s="100"/>
-      <c r="G35" s="100"/>
-      <c r="H35" s="99" t="s">
+      <c r="F35" s="103"/>
+      <c r="G35" s="103"/>
+      <c r="H35" s="102" t="s">
         <v>23</v>
       </c>
-      <c r="I35" s="100"/>
-      <c r="J35" s="100"/>
-      <c r="K35" s="99" t="s">
+      <c r="I35" s="103"/>
+      <c r="J35" s="103"/>
+      <c r="K35" s="102" t="s">
         <v>24</v>
       </c>
-      <c r="L35" s="100"/>
-      <c r="M35" s="100"/>
-      <c r="N35" s="100"/>
-      <c r="O35" s="100"/>
-      <c r="P35" s="99" t="s">
+      <c r="L35" s="103"/>
+      <c r="M35" s="103"/>
+      <c r="N35" s="103"/>
+      <c r="O35" s="103"/>
+      <c r="P35" s="102" t="s">
         <v>25</v>
       </c>
-      <c r="Q35" s="99" t="s">
+      <c r="Q35" s="102" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A36" s="100"/>
+    <row r="36" spans="1:17">
+      <c r="A36" s="103"/>
       <c r="B36" s="43" t="s">
         <v>27</v>
       </c>
@@ -15236,10 +15304,10 @@
       <c r="O36" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P36" s="100"/>
-      <c r="Q36" s="100"/>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="P36" s="103"/>
+      <c r="Q36" s="103"/>
+    </row>
+    <row r="37" spans="1:17">
       <c r="A37" s="43" t="s">
         <v>688</v>
       </c>
@@ -15290,7 +15358,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="38" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:17" ht="30">
       <c r="A38" s="43" t="s">
         <v>844</v>
       </c>
@@ -15341,7 +15409,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:17" ht="28.9" customHeight="1">
       <c r="A39" s="43" t="s">
         <v>68</v>
       </c>
@@ -15392,7 +15460,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="40" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:17" ht="57.6" customHeight="1">
       <c r="A40" s="43" t="s">
         <v>845</v>
       </c>
@@ -15425,7 +15493,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:17">
       <c r="A41" s="43" t="s">
         <v>846</v>
       </c>
@@ -15458,7 +15526,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:17" ht="43.15" customHeight="1">
       <c r="A42" s="46" t="s">
         <v>847</v>
       </c>
@@ -15501,7 +15569,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:17" ht="30">
       <c r="A43" s="43" t="s">
         <v>848</v>
       </c>
@@ -15534,7 +15602,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="44" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:17" ht="28.9" customHeight="1">
       <c r="A44" s="43" t="s">
         <v>772</v>
       </c>
@@ -15567,7 +15635,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" ht="28.9" customHeight="1">
       <c r="A45" s="43" t="s">
         <v>765</v>
       </c>
@@ -15600,7 +15668,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:17" ht="43.15" customHeight="1">
       <c r="A46" s="43" t="s">
         <v>777</v>
       </c>
@@ -15633,7 +15701,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:17" ht="57.6" customHeight="1">
       <c r="A47" s="46" t="s">
         <v>849</v>
       </c>
@@ -15676,81 +15744,81 @@
         <v>20</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A48" s="102" t="s">
+    <row r="48" spans="1:17">
+      <c r="A48" s="104" t="s">
         <v>850</v>
       </c>
-      <c r="B48" s="100"/>
-      <c r="C48" s="100"/>
-      <c r="D48" s="100"/>
-      <c r="E48" s="100"/>
-      <c r="F48" s="100"/>
-      <c r="G48" s="100"/>
-      <c r="H48" s="100"/>
-      <c r="I48" s="100"/>
-      <c r="J48" s="100"/>
-      <c r="K48" s="100"/>
-      <c r="L48" s="100"/>
-      <c r="M48" s="100"/>
-      <c r="N48" s="100"/>
-      <c r="O48" s="100"/>
-      <c r="P48" s="100"/>
-      <c r="Q48" s="100"/>
-    </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A49" s="100"/>
-      <c r="B49" s="100"/>
-      <c r="C49" s="100"/>
-      <c r="D49" s="100"/>
-      <c r="E49" s="100"/>
-      <c r="F49" s="100"/>
-      <c r="G49" s="100"/>
-      <c r="H49" s="100"/>
-      <c r="I49" s="100"/>
-      <c r="J49" s="100"/>
-      <c r="K49" s="100"/>
-      <c r="L49" s="100"/>
-      <c r="M49" s="100"/>
-      <c r="N49" s="100"/>
-      <c r="O49" s="100"/>
-      <c r="P49" s="100"/>
-      <c r="Q49" s="100"/>
-    </row>
-    <row r="50" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="101" t="s">
+      <c r="B48" s="103"/>
+      <c r="C48" s="103"/>
+      <c r="D48" s="103"/>
+      <c r="E48" s="103"/>
+      <c r="F48" s="103"/>
+      <c r="G48" s="103"/>
+      <c r="H48" s="103"/>
+      <c r="I48" s="103"/>
+      <c r="J48" s="103"/>
+      <c r="K48" s="103"/>
+      <c r="L48" s="103"/>
+      <c r="M48" s="103"/>
+      <c r="N48" s="103"/>
+      <c r="O48" s="103"/>
+      <c r="P48" s="103"/>
+      <c r="Q48" s="103"/>
+    </row>
+    <row r="49" spans="1:17">
+      <c r="A49" s="103"/>
+      <c r="B49" s="103"/>
+      <c r="C49" s="103"/>
+      <c r="D49" s="103"/>
+      <c r="E49" s="103"/>
+      <c r="F49" s="103"/>
+      <c r="G49" s="103"/>
+      <c r="H49" s="103"/>
+      <c r="I49" s="103"/>
+      <c r="J49" s="103"/>
+      <c r="K49" s="103"/>
+      <c r="L49" s="103"/>
+      <c r="M49" s="103"/>
+      <c r="N49" s="103"/>
+      <c r="O49" s="103"/>
+      <c r="P49" s="103"/>
+      <c r="Q49" s="103"/>
+    </row>
+    <row r="50" spans="1:17" ht="14.45" customHeight="1">
+      <c r="A50" s="105" t="s">
         <v>20</v>
       </c>
-      <c r="B50" s="99" t="s">
+      <c r="B50" s="102" t="s">
         <v>21</v>
       </c>
-      <c r="C50" s="100"/>
-      <c r="D50" s="100"/>
-      <c r="E50" s="99" t="s">
+      <c r="C50" s="103"/>
+      <c r="D50" s="103"/>
+      <c r="E50" s="102" t="s">
         <v>22</v>
       </c>
-      <c r="F50" s="100"/>
-      <c r="G50" s="100"/>
-      <c r="H50" s="99" t="s">
+      <c r="F50" s="103"/>
+      <c r="G50" s="103"/>
+      <c r="H50" s="102" t="s">
         <v>23</v>
       </c>
-      <c r="I50" s="100"/>
-      <c r="J50" s="100"/>
-      <c r="K50" s="99" t="s">
+      <c r="I50" s="103"/>
+      <c r="J50" s="103"/>
+      <c r="K50" s="102" t="s">
         <v>24</v>
       </c>
-      <c r="L50" s="100"/>
-      <c r="M50" s="100"/>
-      <c r="N50" s="100"/>
-      <c r="O50" s="100"/>
-      <c r="P50" s="99" t="s">
+      <c r="L50" s="103"/>
+      <c r="M50" s="103"/>
+      <c r="N50" s="103"/>
+      <c r="O50" s="103"/>
+      <c r="P50" s="102" t="s">
         <v>25</v>
       </c>
-      <c r="Q50" s="99" t="s">
+      <c r="Q50" s="102" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A51" s="100"/>
+    <row r="51" spans="1:17">
+      <c r="A51" s="103"/>
       <c r="B51" s="43" t="s">
         <v>27</v>
       </c>
@@ -15793,10 +15861,10 @@
       <c r="O51" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P51" s="100"/>
-      <c r="Q51" s="100"/>
-    </row>
-    <row r="52" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P51" s="103"/>
+      <c r="Q51" s="103"/>
+    </row>
+    <row r="52" spans="1:17" ht="57.6" customHeight="1">
       <c r="A52" s="43" t="s">
         <v>851</v>
       </c>
@@ -15847,81 +15915,81 @@
         <v>15</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A53" s="102" t="s">
+    <row r="53" spans="1:17">
+      <c r="A53" s="104" t="s">
         <v>852</v>
       </c>
-      <c r="B53" s="100"/>
-      <c r="C53" s="100"/>
-      <c r="D53" s="100"/>
-      <c r="E53" s="100"/>
-      <c r="F53" s="100"/>
-      <c r="G53" s="100"/>
-      <c r="H53" s="100"/>
-      <c r="I53" s="100"/>
-      <c r="J53" s="100"/>
-      <c r="K53" s="100"/>
-      <c r="L53" s="100"/>
-      <c r="M53" s="100"/>
-      <c r="N53" s="100"/>
-      <c r="O53" s="100"/>
-      <c r="P53" s="100"/>
-      <c r="Q53" s="100"/>
-    </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A54" s="100"/>
-      <c r="B54" s="100"/>
-      <c r="C54" s="100"/>
-      <c r="D54" s="100"/>
-      <c r="E54" s="100"/>
-      <c r="F54" s="100"/>
-      <c r="G54" s="100"/>
-      <c r="H54" s="100"/>
-      <c r="I54" s="100"/>
-      <c r="J54" s="100"/>
-      <c r="K54" s="100"/>
-      <c r="L54" s="100"/>
-      <c r="M54" s="100"/>
-      <c r="N54" s="100"/>
-      <c r="O54" s="100"/>
-      <c r="P54" s="100"/>
-      <c r="Q54" s="100"/>
-    </row>
-    <row r="55" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="101" t="s">
+      <c r="B53" s="103"/>
+      <c r="C53" s="103"/>
+      <c r="D53" s="103"/>
+      <c r="E53" s="103"/>
+      <c r="F53" s="103"/>
+      <c r="G53" s="103"/>
+      <c r="H53" s="103"/>
+      <c r="I53" s="103"/>
+      <c r="J53" s="103"/>
+      <c r="K53" s="103"/>
+      <c r="L53" s="103"/>
+      <c r="M53" s="103"/>
+      <c r="N53" s="103"/>
+      <c r="O53" s="103"/>
+      <c r="P53" s="103"/>
+      <c r="Q53" s="103"/>
+    </row>
+    <row r="54" spans="1:17">
+      <c r="A54" s="103"/>
+      <c r="B54" s="103"/>
+      <c r="C54" s="103"/>
+      <c r="D54" s="103"/>
+      <c r="E54" s="103"/>
+      <c r="F54" s="103"/>
+      <c r="G54" s="103"/>
+      <c r="H54" s="103"/>
+      <c r="I54" s="103"/>
+      <c r="J54" s="103"/>
+      <c r="K54" s="103"/>
+      <c r="L54" s="103"/>
+      <c r="M54" s="103"/>
+      <c r="N54" s="103"/>
+      <c r="O54" s="103"/>
+      <c r="P54" s="103"/>
+      <c r="Q54" s="103"/>
+    </row>
+    <row r="55" spans="1:17" ht="14.45" customHeight="1">
+      <c r="A55" s="105" t="s">
         <v>20</v>
       </c>
-      <c r="B55" s="99" t="s">
+      <c r="B55" s="102" t="s">
         <v>21</v>
       </c>
-      <c r="C55" s="100"/>
-      <c r="D55" s="100"/>
-      <c r="E55" s="99" t="s">
+      <c r="C55" s="103"/>
+      <c r="D55" s="103"/>
+      <c r="E55" s="102" t="s">
         <v>22</v>
       </c>
-      <c r="F55" s="100"/>
-      <c r="G55" s="100"/>
-      <c r="H55" s="99" t="s">
+      <c r="F55" s="103"/>
+      <c r="G55" s="103"/>
+      <c r="H55" s="102" t="s">
         <v>23</v>
       </c>
-      <c r="I55" s="100"/>
-      <c r="J55" s="100"/>
-      <c r="K55" s="99" t="s">
+      <c r="I55" s="103"/>
+      <c r="J55" s="103"/>
+      <c r="K55" s="102" t="s">
         <v>24</v>
       </c>
-      <c r="L55" s="100"/>
-      <c r="M55" s="100"/>
-      <c r="N55" s="100"/>
-      <c r="O55" s="100"/>
-      <c r="P55" s="99" t="s">
+      <c r="L55" s="103"/>
+      <c r="M55" s="103"/>
+      <c r="N55" s="103"/>
+      <c r="O55" s="103"/>
+      <c r="P55" s="102" t="s">
         <v>25</v>
       </c>
-      <c r="Q55" s="99" t="s">
+      <c r="Q55" s="102" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A56" s="100"/>
+    <row r="56" spans="1:17">
+      <c r="A56" s="103"/>
       <c r="B56" s="43" t="s">
         <v>27</v>
       </c>
@@ -15964,10 +16032,10 @@
       <c r="O56" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P56" s="100"/>
-      <c r="Q56" s="100"/>
-    </row>
-    <row r="57" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P56" s="103"/>
+      <c r="Q56" s="103"/>
+    </row>
+    <row r="57" spans="1:17" ht="28.9" customHeight="1">
       <c r="A57" s="43" t="s">
         <v>34</v>
       </c>
@@ -16000,7 +16068,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="58" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:17" ht="57.6" customHeight="1">
       <c r="A58" s="43" t="s">
         <v>853</v>
       </c>
@@ -16033,7 +16101,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:17" ht="43.15" customHeight="1">
       <c r="A59" s="43" t="s">
         <v>37</v>
       </c>
@@ -16066,7 +16134,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:17" ht="43.15" customHeight="1">
       <c r="A60" s="43" t="s">
         <v>40</v>
       </c>
@@ -16099,7 +16167,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:17" ht="28.9" customHeight="1">
       <c r="A61" s="43" t="s">
         <v>39</v>
       </c>
@@ -16132,7 +16200,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="100.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:17" ht="100.9" customHeight="1">
       <c r="A62" s="43" t="s">
         <v>36</v>
       </c>
@@ -16165,7 +16233,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="63" spans="1:17" ht="144" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:17" ht="144" customHeight="1">
       <c r="A63" s="43" t="s">
         <v>35</v>
       </c>
@@ -16198,7 +16266,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="115.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:17" ht="115.15" customHeight="1">
       <c r="A64" s="43" t="s">
         <v>44</v>
       </c>
@@ -16231,7 +16299,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="65" spans="1:17" ht="100.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:17" ht="100.9" customHeight="1">
       <c r="A65" s="43" t="s">
         <v>41</v>
       </c>
@@ -16264,7 +16332,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="66" spans="1:17" ht="144" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:17" ht="144" customHeight="1">
       <c r="A66" s="43" t="s">
         <v>32</v>
       </c>
@@ -16297,7 +16365,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="67" spans="1:17" ht="115.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:17" ht="115.15" customHeight="1">
       <c r="A67" s="43" t="s">
         <v>31</v>
       </c>
@@ -16330,7 +16398,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="68" spans="1:17" ht="129.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:17" ht="129.6" customHeight="1">
       <c r="A68" s="43" t="s">
         <v>33</v>
       </c>
@@ -16363,7 +16431,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="69" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:17" ht="72" customHeight="1">
       <c r="A69" s="43" t="s">
         <v>42</v>
       </c>
@@ -16396,7 +16464,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="70" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:17" ht="72" customHeight="1">
       <c r="A70" s="43" t="s">
         <v>43</v>
       </c>
@@ -16429,7 +16497,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="71" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" ht="43.15" customHeight="1">
       <c r="A71" s="46" t="s">
         <v>854</v>
       </c>
@@ -16472,81 +16540,81 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A72" s="102" t="s">
+    <row r="72" spans="1:17">
+      <c r="A72" s="104" t="s">
         <v>855</v>
       </c>
-      <c r="B72" s="100"/>
-      <c r="C72" s="100"/>
-      <c r="D72" s="100"/>
-      <c r="E72" s="100"/>
-      <c r="F72" s="100"/>
-      <c r="G72" s="100"/>
-      <c r="H72" s="100"/>
-      <c r="I72" s="100"/>
-      <c r="J72" s="100"/>
-      <c r="K72" s="100"/>
-      <c r="L72" s="100"/>
-      <c r="M72" s="100"/>
-      <c r="N72" s="100"/>
-      <c r="O72" s="100"/>
-      <c r="P72" s="100"/>
-      <c r="Q72" s="100"/>
-    </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A73" s="100"/>
-      <c r="B73" s="100"/>
-      <c r="C73" s="100"/>
-      <c r="D73" s="100"/>
-      <c r="E73" s="100"/>
-      <c r="F73" s="100"/>
-      <c r="G73" s="100"/>
-      <c r="H73" s="100"/>
-      <c r="I73" s="100"/>
-      <c r="J73" s="100"/>
-      <c r="K73" s="100"/>
-      <c r="L73" s="100"/>
-      <c r="M73" s="100"/>
-      <c r="N73" s="100"/>
-      <c r="O73" s="100"/>
-      <c r="P73" s="100"/>
-      <c r="Q73" s="100"/>
-    </row>
-    <row r="74" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="101" t="s">
+      <c r="B72" s="103"/>
+      <c r="C72" s="103"/>
+      <c r="D72" s="103"/>
+      <c r="E72" s="103"/>
+      <c r="F72" s="103"/>
+      <c r="G72" s="103"/>
+      <c r="H72" s="103"/>
+      <c r="I72" s="103"/>
+      <c r="J72" s="103"/>
+      <c r="K72" s="103"/>
+      <c r="L72" s="103"/>
+      <c r="M72" s="103"/>
+      <c r="N72" s="103"/>
+      <c r="O72" s="103"/>
+      <c r="P72" s="103"/>
+      <c r="Q72" s="103"/>
+    </row>
+    <row r="73" spans="1:17">
+      <c r="A73" s="103"/>
+      <c r="B73" s="103"/>
+      <c r="C73" s="103"/>
+      <c r="D73" s="103"/>
+      <c r="E73" s="103"/>
+      <c r="F73" s="103"/>
+      <c r="G73" s="103"/>
+      <c r="H73" s="103"/>
+      <c r="I73" s="103"/>
+      <c r="J73" s="103"/>
+      <c r="K73" s="103"/>
+      <c r="L73" s="103"/>
+      <c r="M73" s="103"/>
+      <c r="N73" s="103"/>
+      <c r="O73" s="103"/>
+      <c r="P73" s="103"/>
+      <c r="Q73" s="103"/>
+    </row>
+    <row r="74" spans="1:17" ht="14.45" customHeight="1">
+      <c r="A74" s="105" t="s">
         <v>20</v>
       </c>
-      <c r="B74" s="99" t="s">
+      <c r="B74" s="102" t="s">
         <v>21</v>
       </c>
-      <c r="C74" s="100"/>
-      <c r="D74" s="100"/>
-      <c r="E74" s="99" t="s">
+      <c r="C74" s="103"/>
+      <c r="D74" s="103"/>
+      <c r="E74" s="102" t="s">
         <v>22</v>
       </c>
-      <c r="F74" s="100"/>
-      <c r="G74" s="100"/>
-      <c r="H74" s="99" t="s">
+      <c r="F74" s="103"/>
+      <c r="G74" s="103"/>
+      <c r="H74" s="102" t="s">
         <v>23</v>
       </c>
-      <c r="I74" s="100"/>
-      <c r="J74" s="100"/>
-      <c r="K74" s="99" t="s">
+      <c r="I74" s="103"/>
+      <c r="J74" s="103"/>
+      <c r="K74" s="102" t="s">
         <v>24</v>
       </c>
-      <c r="L74" s="100"/>
-      <c r="M74" s="100"/>
-      <c r="N74" s="100"/>
-      <c r="O74" s="100"/>
-      <c r="P74" s="99" t="s">
+      <c r="L74" s="103"/>
+      <c r="M74" s="103"/>
+      <c r="N74" s="103"/>
+      <c r="O74" s="103"/>
+      <c r="P74" s="102" t="s">
         <v>25</v>
       </c>
-      <c r="Q74" s="99" t="s">
+      <c r="Q74" s="102" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A75" s="100"/>
+    <row r="75" spans="1:17">
+      <c r="A75" s="103"/>
       <c r="B75" s="43" t="s">
         <v>27</v>
       </c>
@@ -16589,10 +16657,10 @@
       <c r="O75" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P75" s="100"/>
-      <c r="Q75" s="100"/>
-    </row>
-    <row r="76" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P75" s="103"/>
+      <c r="Q75" s="103"/>
+    </row>
+    <row r="76" spans="1:17" ht="57.6" customHeight="1">
       <c r="A76" s="43" t="s">
         <v>48</v>
       </c>
@@ -16625,7 +16693,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:17" ht="43.15" customHeight="1">
       <c r="A77" s="43" t="s">
         <v>51</v>
       </c>
@@ -16658,7 +16726,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:17" ht="72" customHeight="1">
       <c r="A78" s="43" t="s">
         <v>50</v>
       </c>
@@ -16691,7 +16759,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:17" ht="57.6" customHeight="1">
       <c r="A79" s="43" t="s">
         <v>49</v>
       </c>
@@ -16724,7 +16792,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:17" ht="28.9" customHeight="1">
       <c r="A80" s="46" t="s">
         <v>856</v>
       </c>
@@ -16767,81 +16835,81 @@
         <v>272</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A81" s="102" t="s">
+    <row r="81" spans="1:17">
+      <c r="A81" s="104" t="s">
         <v>857</v>
       </c>
-      <c r="B81" s="100"/>
-      <c r="C81" s="100"/>
-      <c r="D81" s="100"/>
-      <c r="E81" s="100"/>
-      <c r="F81" s="100"/>
-      <c r="G81" s="100"/>
-      <c r="H81" s="100"/>
-      <c r="I81" s="100"/>
-      <c r="J81" s="100"/>
-      <c r="K81" s="100"/>
-      <c r="L81" s="100"/>
-      <c r="M81" s="100"/>
-      <c r="N81" s="100"/>
-      <c r="O81" s="100"/>
-      <c r="P81" s="100"/>
-      <c r="Q81" s="100"/>
-    </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A82" s="100"/>
-      <c r="B82" s="100"/>
-      <c r="C82" s="100"/>
-      <c r="D82" s="100"/>
-      <c r="E82" s="100"/>
-      <c r="F82" s="100"/>
-      <c r="G82" s="100"/>
-      <c r="H82" s="100"/>
-      <c r="I82" s="100"/>
-      <c r="J82" s="100"/>
-      <c r="K82" s="100"/>
-      <c r="L82" s="100"/>
-      <c r="M82" s="100"/>
-      <c r="N82" s="100"/>
-      <c r="O82" s="100"/>
-      <c r="P82" s="100"/>
-      <c r="Q82" s="100"/>
-    </row>
-    <row r="83" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="101" t="s">
+      <c r="B81" s="103"/>
+      <c r="C81" s="103"/>
+      <c r="D81" s="103"/>
+      <c r="E81" s="103"/>
+      <c r="F81" s="103"/>
+      <c r="G81" s="103"/>
+      <c r="H81" s="103"/>
+      <c r="I81" s="103"/>
+      <c r="J81" s="103"/>
+      <c r="K81" s="103"/>
+      <c r="L81" s="103"/>
+      <c r="M81" s="103"/>
+      <c r="N81" s="103"/>
+      <c r="O81" s="103"/>
+      <c r="P81" s="103"/>
+      <c r="Q81" s="103"/>
+    </row>
+    <row r="82" spans="1:17">
+      <c r="A82" s="103"/>
+      <c r="B82" s="103"/>
+      <c r="C82" s="103"/>
+      <c r="D82" s="103"/>
+      <c r="E82" s="103"/>
+      <c r="F82" s="103"/>
+      <c r="G82" s="103"/>
+      <c r="H82" s="103"/>
+      <c r="I82" s="103"/>
+      <c r="J82" s="103"/>
+      <c r="K82" s="103"/>
+      <c r="L82" s="103"/>
+      <c r="M82" s="103"/>
+      <c r="N82" s="103"/>
+      <c r="O82" s="103"/>
+      <c r="P82" s="103"/>
+      <c r="Q82" s="103"/>
+    </row>
+    <row r="83" spans="1:17" ht="14.45" customHeight="1">
+      <c r="A83" s="105" t="s">
         <v>20</v>
       </c>
-      <c r="B83" s="99" t="s">
+      <c r="B83" s="102" t="s">
         <v>21</v>
       </c>
-      <c r="C83" s="100"/>
-      <c r="D83" s="100"/>
-      <c r="E83" s="99" t="s">
+      <c r="C83" s="103"/>
+      <c r="D83" s="103"/>
+      <c r="E83" s="102" t="s">
         <v>22</v>
       </c>
-      <c r="F83" s="100"/>
-      <c r="G83" s="100"/>
-      <c r="H83" s="99" t="s">
+      <c r="F83" s="103"/>
+      <c r="G83" s="103"/>
+      <c r="H83" s="102" t="s">
         <v>23</v>
       </c>
-      <c r="I83" s="100"/>
-      <c r="J83" s="100"/>
-      <c r="K83" s="99" t="s">
+      <c r="I83" s="103"/>
+      <c r="J83" s="103"/>
+      <c r="K83" s="102" t="s">
         <v>24</v>
       </c>
-      <c r="L83" s="100"/>
-      <c r="M83" s="100"/>
-      <c r="N83" s="100"/>
-      <c r="O83" s="100"/>
-      <c r="P83" s="99" t="s">
+      <c r="L83" s="103"/>
+      <c r="M83" s="103"/>
+      <c r="N83" s="103"/>
+      <c r="O83" s="103"/>
+      <c r="P83" s="102" t="s">
         <v>25</v>
       </c>
-      <c r="Q83" s="99" t="s">
+      <c r="Q83" s="102" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A84" s="100"/>
+    <row r="84" spans="1:17">
+      <c r="A84" s="103"/>
       <c r="B84" s="43" t="s">
         <v>27</v>
       </c>
@@ -16884,10 +16952,10 @@
       <c r="O84" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P84" s="100"/>
-      <c r="Q84" s="100"/>
-    </row>
-    <row r="85" spans="1:17" ht="100.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P84" s="103"/>
+      <c r="Q84" s="103"/>
+    </row>
+    <row r="85" spans="1:17" ht="100.9" customHeight="1">
       <c r="A85" s="43" t="s">
         <v>858</v>
       </c>
@@ -16920,7 +16988,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="86" spans="1:17" ht="100.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:17" ht="100.9" customHeight="1">
       <c r="A86" s="43" t="s">
         <v>859</v>
       </c>
@@ -16953,7 +17021,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="87" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:17" ht="28.9" customHeight="1">
       <c r="A87" s="43" t="s">
         <v>799</v>
       </c>
@@ -16986,7 +17054,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:17">
       <c r="A88" s="43" t="s">
         <v>804</v>
       </c>
@@ -17019,7 +17087,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="89" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:17" ht="28.9" customHeight="1">
       <c r="A89" s="43" t="s">
         <v>809</v>
       </c>
@@ -17052,7 +17120,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:17">
       <c r="A90" s="43" t="s">
         <v>814</v>
       </c>
@@ -17085,7 +17153,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="91" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:17" ht="28.9" customHeight="1">
       <c r="A91" s="43" t="s">
         <v>860</v>
       </c>
@@ -17118,7 +17186,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="92" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:17" ht="28.9" customHeight="1">
       <c r="A92" s="46" t="s">
         <v>861</v>
       </c>
@@ -17161,81 +17229,81 @@
         <v>30</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A93" s="102" t="s">
+    <row r="93" spans="1:17">
+      <c r="A93" s="104" t="s">
         <v>862</v>
       </c>
-      <c r="B93" s="100"/>
-      <c r="C93" s="100"/>
-      <c r="D93" s="100"/>
-      <c r="E93" s="100"/>
-      <c r="F93" s="100"/>
-      <c r="G93" s="100"/>
-      <c r="H93" s="100"/>
-      <c r="I93" s="100"/>
-      <c r="J93" s="100"/>
-      <c r="K93" s="100"/>
-      <c r="L93" s="100"/>
-      <c r="M93" s="100"/>
-      <c r="N93" s="100"/>
-      <c r="O93" s="100"/>
-      <c r="P93" s="100"/>
-      <c r="Q93" s="100"/>
-    </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A94" s="100"/>
-      <c r="B94" s="100"/>
-      <c r="C94" s="100"/>
-      <c r="D94" s="100"/>
-      <c r="E94" s="100"/>
-      <c r="F94" s="100"/>
-      <c r="G94" s="100"/>
-      <c r="H94" s="100"/>
-      <c r="I94" s="100"/>
-      <c r="J94" s="100"/>
-      <c r="K94" s="100"/>
-      <c r="L94" s="100"/>
-      <c r="M94" s="100"/>
-      <c r="N94" s="100"/>
-      <c r="O94" s="100"/>
-      <c r="P94" s="100"/>
-      <c r="Q94" s="100"/>
-    </row>
-    <row r="95" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="101" t="s">
+      <c r="B93" s="103"/>
+      <c r="C93" s="103"/>
+      <c r="D93" s="103"/>
+      <c r="E93" s="103"/>
+      <c r="F93" s="103"/>
+      <c r="G93" s="103"/>
+      <c r="H93" s="103"/>
+      <c r="I93" s="103"/>
+      <c r="J93" s="103"/>
+      <c r="K93" s="103"/>
+      <c r="L93" s="103"/>
+      <c r="M93" s="103"/>
+      <c r="N93" s="103"/>
+      <c r="O93" s="103"/>
+      <c r="P93" s="103"/>
+      <c r="Q93" s="103"/>
+    </row>
+    <row r="94" spans="1:17">
+      <c r="A94" s="103"/>
+      <c r="B94" s="103"/>
+      <c r="C94" s="103"/>
+      <c r="D94" s="103"/>
+      <c r="E94" s="103"/>
+      <c r="F94" s="103"/>
+      <c r="G94" s="103"/>
+      <c r="H94" s="103"/>
+      <c r="I94" s="103"/>
+      <c r="J94" s="103"/>
+      <c r="K94" s="103"/>
+      <c r="L94" s="103"/>
+      <c r="M94" s="103"/>
+      <c r="N94" s="103"/>
+      <c r="O94" s="103"/>
+      <c r="P94" s="103"/>
+      <c r="Q94" s="103"/>
+    </row>
+    <row r="95" spans="1:17" ht="14.45" customHeight="1">
+      <c r="A95" s="105" t="s">
         <v>20</v>
       </c>
-      <c r="B95" s="99" t="s">
+      <c r="B95" s="102" t="s">
         <v>21</v>
       </c>
-      <c r="C95" s="100"/>
-      <c r="D95" s="100"/>
-      <c r="E95" s="99" t="s">
+      <c r="C95" s="103"/>
+      <c r="D95" s="103"/>
+      <c r="E95" s="102" t="s">
         <v>22</v>
       </c>
-      <c r="F95" s="100"/>
-      <c r="G95" s="100"/>
-      <c r="H95" s="99" t="s">
+      <c r="F95" s="103"/>
+      <c r="G95" s="103"/>
+      <c r="H95" s="102" t="s">
         <v>23</v>
       </c>
-      <c r="I95" s="100"/>
-      <c r="J95" s="100"/>
-      <c r="K95" s="99" t="s">
+      <c r="I95" s="103"/>
+      <c r="J95" s="103"/>
+      <c r="K95" s="102" t="s">
         <v>24</v>
       </c>
-      <c r="L95" s="100"/>
-      <c r="M95" s="100"/>
-      <c r="N95" s="100"/>
-      <c r="O95" s="100"/>
-      <c r="P95" s="99" t="s">
+      <c r="L95" s="103"/>
+      <c r="M95" s="103"/>
+      <c r="N95" s="103"/>
+      <c r="O95" s="103"/>
+      <c r="P95" s="102" t="s">
         <v>25</v>
       </c>
-      <c r="Q95" s="99" t="s">
+      <c r="Q95" s="102" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A96" s="100"/>
+    <row r="96" spans="1:17">
+      <c r="A96" s="103"/>
       <c r="B96" s="43" t="s">
         <v>27</v>
       </c>
@@ -17278,10 +17346,10 @@
       <c r="O96" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P96" s="100"/>
-      <c r="Q96" s="100"/>
-    </row>
-    <row r="97" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P96" s="103"/>
+      <c r="Q96" s="103"/>
+    </row>
+    <row r="97" spans="1:17" ht="57.6" customHeight="1">
       <c r="A97" s="43" t="s">
         <v>863</v>
       </c>
@@ -17314,7 +17382,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="98" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:17" ht="57.6" customHeight="1">
       <c r="A98" s="43" t="s">
         <v>54</v>
       </c>
@@ -17347,7 +17415,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="99" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:17" ht="72" customHeight="1">
       <c r="A99" s="43" t="s">
         <v>55</v>
       </c>
@@ -17380,7 +17448,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="100" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:17" ht="28.9" customHeight="1">
       <c r="A100" s="43" t="s">
         <v>56</v>
       </c>
@@ -17413,7 +17481,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="101" spans="1:17" ht="115.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:17" ht="115.15" customHeight="1">
       <c r="A101" s="43" t="s">
         <v>57</v>
       </c>
@@ -17446,7 +17514,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:17" ht="72" customHeight="1">
       <c r="A102" s="43" t="s">
         <v>864</v>
       </c>
@@ -17479,7 +17547,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:17" ht="28.9" customHeight="1">
       <c r="A103" s="43" t="s">
         <v>865</v>
       </c>
@@ -17512,7 +17580,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:17" ht="43.15" customHeight="1">
       <c r="A104" s="43" t="s">
         <v>58</v>
       </c>
@@ -17545,7 +17613,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:17" ht="57.6" customHeight="1">
       <c r="A105" s="43" t="s">
         <v>59</v>
       </c>
@@ -17578,7 +17646,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="106" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:17" ht="72" customHeight="1">
       <c r="A106" s="43" t="s">
         <v>60</v>
       </c>
@@ -17611,7 +17679,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="107" spans="1:17" ht="100.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:17" ht="100.9" customHeight="1">
       <c r="A107" s="43" t="s">
         <v>866</v>
       </c>
@@ -17644,7 +17712,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:17" ht="57.6" customHeight="1">
       <c r="A108" s="43" t="s">
         <v>61</v>
       </c>
@@ -17677,7 +17745,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:17" ht="72" customHeight="1">
       <c r="A109" s="43" t="s">
         <v>867</v>
       </c>
@@ -17710,7 +17778,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="110" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:17" ht="57.6" customHeight="1">
       <c r="A110" s="43" t="s">
         <v>62</v>
       </c>
@@ -17743,7 +17811,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:17" ht="86.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:17" ht="86.45" customHeight="1">
       <c r="A111" s="43" t="s">
         <v>63</v>
       </c>
@@ -17776,7 +17844,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:17" ht="57.6" customHeight="1">
       <c r="A112" s="43" t="s">
         <v>64</v>
       </c>
@@ -17809,7 +17877,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="113" spans="1:17" ht="86.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:17" ht="86.45" customHeight="1">
       <c r="A113" s="43" t="s">
         <v>868</v>
       </c>
@@ -17842,7 +17910,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="114" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:17" ht="57.6" customHeight="1">
       <c r="A114" s="43" t="s">
         <v>869</v>
       </c>
@@ -17875,7 +17943,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="115" spans="1:17" ht="86.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:17" ht="86.45" customHeight="1">
       <c r="A115" s="43" t="s">
         <v>870</v>
       </c>
@@ -17908,7 +17976,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="116" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:17" ht="72" customHeight="1">
       <c r="A116" s="43" t="s">
         <v>871</v>
       </c>
@@ -17941,7 +18009,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="117" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:17" ht="72" customHeight="1">
       <c r="A117" s="43" t="s">
         <v>65</v>
       </c>
@@ -17974,7 +18042,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:17" ht="57.6" customHeight="1">
       <c r="A118" s="43" t="s">
         <v>66</v>
       </c>
@@ -18007,7 +18075,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:17" ht="72" customHeight="1">
       <c r="A119" s="43" t="s">
         <v>872</v>
       </c>
@@ -18040,7 +18108,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:17" ht="57.6" customHeight="1">
       <c r="A120" s="43" t="s">
         <v>873</v>
       </c>
@@ -18073,7 +18141,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:17" ht="57.6" customHeight="1">
       <c r="A121" s="43" t="s">
         <v>874</v>
       </c>
@@ -18106,7 +18174,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="122" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:17" ht="43.15" customHeight="1">
       <c r="A122" s="43" t="s">
         <v>875</v>
       </c>
@@ -18139,7 +18207,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:17" ht="100.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:17" ht="100.9" customHeight="1">
       <c r="A123" s="43" t="s">
         <v>876</v>
       </c>
@@ -18172,7 +18240,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="124" spans="1:17" ht="100.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:17" ht="100.9" customHeight="1">
       <c r="A124" s="43" t="s">
         <v>877</v>
       </c>
@@ -18205,7 +18273,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="125" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:17" ht="43.15" customHeight="1">
       <c r="A125" s="43" t="s">
         <v>878</v>
       </c>
@@ -18238,7 +18306,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:17" ht="43.15" customHeight="1">
       <c r="A126" s="46" t="s">
         <v>862</v>
       </c>
@@ -18281,81 +18349,81 @@
         <v>128</v>
       </c>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A127" s="102" t="s">
+    <row r="127" spans="1:17">
+      <c r="A127" s="104" t="s">
         <v>556</v>
       </c>
-      <c r="B127" s="100"/>
-      <c r="C127" s="100"/>
-      <c r="D127" s="100"/>
-      <c r="E127" s="100"/>
-      <c r="F127" s="100"/>
-      <c r="G127" s="100"/>
-      <c r="H127" s="100"/>
-      <c r="I127" s="100"/>
-      <c r="J127" s="100"/>
-      <c r="K127" s="100"/>
-      <c r="L127" s="100"/>
-      <c r="M127" s="100"/>
-      <c r="N127" s="100"/>
-      <c r="O127" s="100"/>
-      <c r="P127" s="100"/>
-      <c r="Q127" s="100"/>
-    </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A128" s="100"/>
-      <c r="B128" s="100"/>
-      <c r="C128" s="100"/>
-      <c r="D128" s="100"/>
-      <c r="E128" s="100"/>
-      <c r="F128" s="100"/>
-      <c r="G128" s="100"/>
-      <c r="H128" s="100"/>
-      <c r="I128" s="100"/>
-      <c r="J128" s="100"/>
-      <c r="K128" s="100"/>
-      <c r="L128" s="100"/>
-      <c r="M128" s="100"/>
-      <c r="N128" s="100"/>
-      <c r="O128" s="100"/>
-      <c r="P128" s="100"/>
-      <c r="Q128" s="100"/>
-    </row>
-    <row r="129" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="101" t="s">
+      <c r="B127" s="103"/>
+      <c r="C127" s="103"/>
+      <c r="D127" s="103"/>
+      <c r="E127" s="103"/>
+      <c r="F127" s="103"/>
+      <c r="G127" s="103"/>
+      <c r="H127" s="103"/>
+      <c r="I127" s="103"/>
+      <c r="J127" s="103"/>
+      <c r="K127" s="103"/>
+      <c r="L127" s="103"/>
+      <c r="M127" s="103"/>
+      <c r="N127" s="103"/>
+      <c r="O127" s="103"/>
+      <c r="P127" s="103"/>
+      <c r="Q127" s="103"/>
+    </row>
+    <row r="128" spans="1:17">
+      <c r="A128" s="103"/>
+      <c r="B128" s="103"/>
+      <c r="C128" s="103"/>
+      <c r="D128" s="103"/>
+      <c r="E128" s="103"/>
+      <c r="F128" s="103"/>
+      <c r="G128" s="103"/>
+      <c r="H128" s="103"/>
+      <c r="I128" s="103"/>
+      <c r="J128" s="103"/>
+      <c r="K128" s="103"/>
+      <c r="L128" s="103"/>
+      <c r="M128" s="103"/>
+      <c r="N128" s="103"/>
+      <c r="O128" s="103"/>
+      <c r="P128" s="103"/>
+      <c r="Q128" s="103"/>
+    </row>
+    <row r="129" spans="1:17" ht="14.45" customHeight="1">
+      <c r="A129" s="105" t="s">
         <v>20</v>
       </c>
-      <c r="B129" s="99" t="s">
+      <c r="B129" s="102" t="s">
         <v>21</v>
       </c>
-      <c r="C129" s="100"/>
-      <c r="D129" s="100"/>
-      <c r="E129" s="99" t="s">
+      <c r="C129" s="103"/>
+      <c r="D129" s="103"/>
+      <c r="E129" s="102" t="s">
         <v>22</v>
       </c>
-      <c r="F129" s="100"/>
-      <c r="G129" s="100"/>
-      <c r="H129" s="99" t="s">
+      <c r="F129" s="103"/>
+      <c r="G129" s="103"/>
+      <c r="H129" s="102" t="s">
         <v>23</v>
       </c>
-      <c r="I129" s="100"/>
-      <c r="J129" s="100"/>
-      <c r="K129" s="99" t="s">
+      <c r="I129" s="103"/>
+      <c r="J129" s="103"/>
+      <c r="K129" s="102" t="s">
         <v>24</v>
       </c>
-      <c r="L129" s="100"/>
-      <c r="M129" s="100"/>
-      <c r="N129" s="100"/>
-      <c r="O129" s="100"/>
-      <c r="P129" s="99" t="s">
+      <c r="L129" s="103"/>
+      <c r="M129" s="103"/>
+      <c r="N129" s="103"/>
+      <c r="O129" s="103"/>
+      <c r="P129" s="102" t="s">
         <v>25</v>
       </c>
-      <c r="Q129" s="99" t="s">
+      <c r="Q129" s="102" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A130" s="100"/>
+    <row r="130" spans="1:17">
+      <c r="A130" s="103"/>
       <c r="B130" s="43" t="s">
         <v>27</v>
       </c>
@@ -18398,10 +18466,10 @@
       <c r="O130" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P130" s="100"/>
-      <c r="Q130" s="100"/>
-    </row>
-    <row r="131" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P130" s="103"/>
+      <c r="Q130" s="103"/>
+    </row>
+    <row r="131" spans="1:17" ht="43.15" customHeight="1">
       <c r="A131" s="43" t="s">
         <v>879</v>
       </c>
@@ -18452,7 +18520,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="132" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:17" ht="72" customHeight="1">
       <c r="A132" s="43" t="s">
         <v>880</v>
       </c>
@@ -18503,7 +18571,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="133" spans="1:17" ht="115.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:17" ht="115.15" customHeight="1">
       <c r="A133" s="43" t="s">
         <v>881</v>
       </c>
@@ -18554,7 +18622,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="134" spans="1:17" ht="129.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:17" ht="129.6" customHeight="1">
       <c r="A134" s="43" t="s">
         <v>882</v>
       </c>
@@ -18587,7 +18655,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="135" spans="1:17" ht="129.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:17" ht="129.6" customHeight="1">
       <c r="A135" s="43" t="s">
         <v>38</v>
       </c>
@@ -18620,7 +18688,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="136" spans="1:17" ht="144" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:17" ht="144" customHeight="1">
       <c r="A136" s="43" t="s">
         <v>883</v>
       </c>
@@ -18653,7 +18721,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="137" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:17" ht="43.15" customHeight="1">
       <c r="A137" s="46" t="s">
         <v>884</v>
       </c>
@@ -18696,7 +18764,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="138" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:17" ht="30">
       <c r="A138" s="43" t="s">
         <v>885</v>
       </c>
@@ -18747,7 +18815,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="139" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:17" ht="57.6" customHeight="1">
       <c r="A139" s="43" t="s">
         <v>886</v>
       </c>
@@ -18780,7 +18848,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="140" spans="1:17" ht="86.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:17" ht="86.45" customHeight="1">
       <c r="A140" s="43" t="s">
         <v>887</v>
       </c>
@@ -18813,7 +18881,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="141" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:17" ht="57.6" customHeight="1">
       <c r="A141" s="46" t="s">
         <v>888</v>
       </c>
@@ -18856,7 +18924,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="142" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:17" ht="57.6" customHeight="1">
       <c r="A142" s="43" t="s">
         <v>889</v>
       </c>
@@ -18889,7 +18957,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="143" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:17" ht="72" customHeight="1">
       <c r="A143" s="43" t="s">
         <v>890</v>
       </c>
@@ -18922,7 +18990,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="144" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:17" ht="43.15" customHeight="1">
       <c r="A144" s="46" t="s">
         <v>891</v>
       </c>
@@ -18965,7 +19033,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="145" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:17" ht="72" customHeight="1">
       <c r="A145" s="43" t="s">
         <v>892</v>
       </c>
@@ -18998,7 +19066,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="146" spans="1:17" ht="100.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:17" ht="100.9" customHeight="1">
       <c r="A146" s="43" t="s">
         <v>893</v>
       </c>
@@ -19031,7 +19099,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="147" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:17" ht="43.15" customHeight="1">
       <c r="A147" s="46" t="s">
         <v>894</v>
       </c>
@@ -19074,7 +19142,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="148" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:17" ht="28.9" customHeight="1">
       <c r="A148" s="43" t="s">
         <v>895</v>
       </c>
@@ -19125,7 +19193,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="149" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:17" ht="57.6" customHeight="1">
       <c r="A149" s="43" t="s">
         <v>896</v>
       </c>
@@ -19158,7 +19226,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="150" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:17" ht="28.9" customHeight="1">
       <c r="A150" s="43" t="s">
         <v>897</v>
       </c>
@@ -19191,7 +19259,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="151" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:17" ht="43.15" customHeight="1">
       <c r="A151" s="46" t="s">
         <v>898</v>
       </c>
@@ -19234,7 +19302,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="152" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:17" ht="43.15" customHeight="1">
       <c r="A152" s="43" t="s">
         <v>899</v>
       </c>
@@ -19285,7 +19353,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="153" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:17" ht="28.9" customHeight="1">
       <c r="A153" s="43" t="s">
         <v>749</v>
       </c>
@@ -19336,7 +19404,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="154" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:17" ht="28.9" customHeight="1">
       <c r="A154" s="43" t="s">
         <v>900</v>
       </c>
@@ -19387,7 +19455,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="155" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:17" ht="28.9" customHeight="1">
       <c r="A155" s="43" t="s">
         <v>705</v>
       </c>
@@ -19420,7 +19488,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="156" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:17" ht="28.9" customHeight="1">
       <c r="A156" s="43" t="s">
         <v>711</v>
       </c>
@@ -19453,7 +19521,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="157" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:17" ht="28.9" customHeight="1">
       <c r="A157" s="43" t="s">
         <v>901</v>
       </c>
@@ -19486,7 +19554,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="158" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:17" ht="57.6" customHeight="1">
       <c r="A158" s="46" t="s">
         <v>902</v>
       </c>
@@ -19529,81 +19597,81 @@
         <v>17</v>
       </c>
     </row>
-    <row r="159" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A159" s="102" t="s">
+    <row r="159" spans="1:17">
+      <c r="A159" s="104" t="s">
         <v>46</v>
       </c>
-      <c r="B159" s="100"/>
-      <c r="C159" s="100"/>
-      <c r="D159" s="100"/>
-      <c r="E159" s="100"/>
-      <c r="F159" s="100"/>
-      <c r="G159" s="100"/>
-      <c r="H159" s="100"/>
-      <c r="I159" s="100"/>
-      <c r="J159" s="100"/>
-      <c r="K159" s="100"/>
-      <c r="L159" s="100"/>
-      <c r="M159" s="100"/>
-      <c r="N159" s="100"/>
-      <c r="O159" s="100"/>
-      <c r="P159" s="100"/>
-      <c r="Q159" s="100"/>
-    </row>
-    <row r="160" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A160" s="100"/>
-      <c r="B160" s="100"/>
-      <c r="C160" s="100"/>
-      <c r="D160" s="100"/>
-      <c r="E160" s="100"/>
-      <c r="F160" s="100"/>
-      <c r="G160" s="100"/>
-      <c r="H160" s="100"/>
-      <c r="I160" s="100"/>
-      <c r="J160" s="100"/>
-      <c r="K160" s="100"/>
-      <c r="L160" s="100"/>
-      <c r="M160" s="100"/>
-      <c r="N160" s="100"/>
-      <c r="O160" s="100"/>
-      <c r="P160" s="100"/>
-      <c r="Q160" s="100"/>
-    </row>
-    <row r="161" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A161" s="101" t="s">
+      <c r="B159" s="103"/>
+      <c r="C159" s="103"/>
+      <c r="D159" s="103"/>
+      <c r="E159" s="103"/>
+      <c r="F159" s="103"/>
+      <c r="G159" s="103"/>
+      <c r="H159" s="103"/>
+      <c r="I159" s="103"/>
+      <c r="J159" s="103"/>
+      <c r="K159" s="103"/>
+      <c r="L159" s="103"/>
+      <c r="M159" s="103"/>
+      <c r="N159" s="103"/>
+      <c r="O159" s="103"/>
+      <c r="P159" s="103"/>
+      <c r="Q159" s="103"/>
+    </row>
+    <row r="160" spans="1:17">
+      <c r="A160" s="103"/>
+      <c r="B160" s="103"/>
+      <c r="C160" s="103"/>
+      <c r="D160" s="103"/>
+      <c r="E160" s="103"/>
+      <c r="F160" s="103"/>
+      <c r="G160" s="103"/>
+      <c r="H160" s="103"/>
+      <c r="I160" s="103"/>
+      <c r="J160" s="103"/>
+      <c r="K160" s="103"/>
+      <c r="L160" s="103"/>
+      <c r="M160" s="103"/>
+      <c r="N160" s="103"/>
+      <c r="O160" s="103"/>
+      <c r="P160" s="103"/>
+      <c r="Q160" s="103"/>
+    </row>
+    <row r="161" spans="1:17" ht="14.45" customHeight="1">
+      <c r="A161" s="105" t="s">
         <v>20</v>
       </c>
-      <c r="B161" s="99" t="s">
+      <c r="B161" s="102" t="s">
         <v>21</v>
       </c>
-      <c r="C161" s="100"/>
-      <c r="D161" s="100"/>
-      <c r="E161" s="99" t="s">
+      <c r="C161" s="103"/>
+      <c r="D161" s="103"/>
+      <c r="E161" s="102" t="s">
         <v>22</v>
       </c>
-      <c r="F161" s="100"/>
-      <c r="G161" s="100"/>
-      <c r="H161" s="99" t="s">
+      <c r="F161" s="103"/>
+      <c r="G161" s="103"/>
+      <c r="H161" s="102" t="s">
         <v>23</v>
       </c>
-      <c r="I161" s="100"/>
-      <c r="J161" s="100"/>
-      <c r="K161" s="99" t="s">
+      <c r="I161" s="103"/>
+      <c r="J161" s="103"/>
+      <c r="K161" s="102" t="s">
         <v>24</v>
       </c>
-      <c r="L161" s="100"/>
-      <c r="M161" s="100"/>
-      <c r="N161" s="100"/>
-      <c r="O161" s="100"/>
-      <c r="P161" s="99" t="s">
+      <c r="L161" s="103"/>
+      <c r="M161" s="103"/>
+      <c r="N161" s="103"/>
+      <c r="O161" s="103"/>
+      <c r="P161" s="102" t="s">
         <v>25</v>
       </c>
-      <c r="Q161" s="99" t="s">
+      <c r="Q161" s="102" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="162" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A162" s="100"/>
+    <row r="162" spans="1:17">
+      <c r="A162" s="103"/>
       <c r="B162" s="43" t="s">
         <v>27</v>
       </c>
@@ -19646,10 +19714,10 @@
       <c r="O162" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P162" s="100"/>
-      <c r="Q162" s="100"/>
-    </row>
-    <row r="163" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P162" s="103"/>
+      <c r="Q162" s="103"/>
+    </row>
+    <row r="163" spans="1:17" ht="28.9" customHeight="1">
       <c r="A163" s="43" t="s">
         <v>46</v>
       </c>
@@ -19700,81 +19768,81 @@
         <v>13</v>
       </c>
     </row>
-    <row r="164" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A164" s="102" t="s">
+    <row r="164" spans="1:17">
+      <c r="A164" s="104" t="s">
         <v>69</v>
       </c>
-      <c r="B164" s="100"/>
-      <c r="C164" s="100"/>
-      <c r="D164" s="100"/>
-      <c r="E164" s="100"/>
-      <c r="F164" s="100"/>
-      <c r="G164" s="100"/>
-      <c r="H164" s="100"/>
-      <c r="I164" s="100"/>
-      <c r="J164" s="100"/>
-      <c r="K164" s="100"/>
-      <c r="L164" s="100"/>
-      <c r="M164" s="100"/>
-      <c r="N164" s="100"/>
-      <c r="O164" s="100"/>
-      <c r="P164" s="100"/>
-      <c r="Q164" s="100"/>
-    </row>
-    <row r="165" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A165" s="100"/>
-      <c r="B165" s="100"/>
-      <c r="C165" s="100"/>
-      <c r="D165" s="100"/>
-      <c r="E165" s="100"/>
-      <c r="F165" s="100"/>
-      <c r="G165" s="100"/>
-      <c r="H165" s="100"/>
-      <c r="I165" s="100"/>
-      <c r="J165" s="100"/>
-      <c r="K165" s="100"/>
-      <c r="L165" s="100"/>
-      <c r="M165" s="100"/>
-      <c r="N165" s="100"/>
-      <c r="O165" s="100"/>
-      <c r="P165" s="100"/>
-      <c r="Q165" s="100"/>
-    </row>
-    <row r="166" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A166" s="101" t="s">
+      <c r="B164" s="103"/>
+      <c r="C164" s="103"/>
+      <c r="D164" s="103"/>
+      <c r="E164" s="103"/>
+      <c r="F164" s="103"/>
+      <c r="G164" s="103"/>
+      <c r="H164" s="103"/>
+      <c r="I164" s="103"/>
+      <c r="J164" s="103"/>
+      <c r="K164" s="103"/>
+      <c r="L164" s="103"/>
+      <c r="M164" s="103"/>
+      <c r="N164" s="103"/>
+      <c r="O164" s="103"/>
+      <c r="P164" s="103"/>
+      <c r="Q164" s="103"/>
+    </row>
+    <row r="165" spans="1:17">
+      <c r="A165" s="103"/>
+      <c r="B165" s="103"/>
+      <c r="C165" s="103"/>
+      <c r="D165" s="103"/>
+      <c r="E165" s="103"/>
+      <c r="F165" s="103"/>
+      <c r="G165" s="103"/>
+      <c r="H165" s="103"/>
+      <c r="I165" s="103"/>
+      <c r="J165" s="103"/>
+      <c r="K165" s="103"/>
+      <c r="L165" s="103"/>
+      <c r="M165" s="103"/>
+      <c r="N165" s="103"/>
+      <c r="O165" s="103"/>
+      <c r="P165" s="103"/>
+      <c r="Q165" s="103"/>
+    </row>
+    <row r="166" spans="1:17" ht="14.45" customHeight="1">
+      <c r="A166" s="105" t="s">
         <v>20</v>
       </c>
-      <c r="B166" s="99" t="s">
+      <c r="B166" s="102" t="s">
         <v>21</v>
       </c>
-      <c r="C166" s="100"/>
-      <c r="D166" s="100"/>
-      <c r="E166" s="99" t="s">
+      <c r="C166" s="103"/>
+      <c r="D166" s="103"/>
+      <c r="E166" s="102" t="s">
         <v>22</v>
       </c>
-      <c r="F166" s="100"/>
-      <c r="G166" s="100"/>
-      <c r="H166" s="99" t="s">
+      <c r="F166" s="103"/>
+      <c r="G166" s="103"/>
+      <c r="H166" s="102" t="s">
         <v>23</v>
       </c>
-      <c r="I166" s="100"/>
-      <c r="J166" s="100"/>
-      <c r="K166" s="99" t="s">
+      <c r="I166" s="103"/>
+      <c r="J166" s="103"/>
+      <c r="K166" s="102" t="s">
         <v>24</v>
       </c>
-      <c r="L166" s="100"/>
-      <c r="M166" s="100"/>
-      <c r="N166" s="100"/>
-      <c r="O166" s="100"/>
-      <c r="P166" s="99" t="s">
+      <c r="L166" s="103"/>
+      <c r="M166" s="103"/>
+      <c r="N166" s="103"/>
+      <c r="O166" s="103"/>
+      <c r="P166" s="102" t="s">
         <v>25</v>
       </c>
-      <c r="Q166" s="99" t="s">
+      <c r="Q166" s="102" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="167" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A167" s="100"/>
+    <row r="167" spans="1:17">
+      <c r="A167" s="103"/>
       <c r="B167" s="43" t="s">
         <v>27</v>
       </c>
@@ -19817,10 +19885,10 @@
       <c r="O167" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P167" s="100"/>
-      <c r="Q167" s="100"/>
-    </row>
-    <row r="168" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P167" s="103"/>
+      <c r="Q167" s="103"/>
+    </row>
+    <row r="168" spans="1:17" ht="72" customHeight="1">
       <c r="A168" s="43" t="s">
         <v>903</v>
       </c>
@@ -19853,7 +19921,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="169" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:17" ht="57.6" customHeight="1">
       <c r="A169" s="43" t="s">
         <v>70</v>
       </c>
@@ -19886,7 +19954,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="170" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:17" ht="72" customHeight="1">
       <c r="A170" s="43" t="s">
         <v>71</v>
       </c>
@@ -19919,7 +19987,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="171" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:17" ht="57.6" customHeight="1">
       <c r="A171" s="43" t="s">
         <v>72</v>
       </c>
@@ -19952,7 +20020,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="172" spans="1:17" ht="86.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:17" ht="86.45" customHeight="1">
       <c r="A172" s="46" t="s">
         <v>904</v>
       </c>
@@ -19997,6 +20065,70 @@
     </row>
   </sheetData>
   <mergeCells count="80">
+    <mergeCell ref="K166:O166"/>
+    <mergeCell ref="H74:J74"/>
+    <mergeCell ref="H83:J83"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="Q50:Q51"/>
+    <mergeCell ref="B55:D55"/>
+    <mergeCell ref="B95:D95"/>
+    <mergeCell ref="E50:G50"/>
+    <mergeCell ref="P74:P75"/>
+    <mergeCell ref="E55:G55"/>
+    <mergeCell ref="K129:O129"/>
+    <mergeCell ref="P95:P96"/>
+    <mergeCell ref="A55:A56"/>
+    <mergeCell ref="A81:Q82"/>
+    <mergeCell ref="A95:A96"/>
+    <mergeCell ref="B129:D129"/>
+    <mergeCell ref="Q166:Q167"/>
+    <mergeCell ref="Q35:Q36"/>
+    <mergeCell ref="P161:P162"/>
+    <mergeCell ref="A159:Q160"/>
+    <mergeCell ref="A93:Q94"/>
+    <mergeCell ref="Q161:Q162"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="P83:P84"/>
+    <mergeCell ref="Q129:Q130"/>
+    <mergeCell ref="Q95:Q96"/>
+    <mergeCell ref="H50:J50"/>
+    <mergeCell ref="A161:A162"/>
+    <mergeCell ref="H55:J55"/>
+    <mergeCell ref="A83:A84"/>
+    <mergeCell ref="P55:P56"/>
+    <mergeCell ref="B161:D161"/>
+    <mergeCell ref="P129:P130"/>
+    <mergeCell ref="A166:A167"/>
+    <mergeCell ref="K74:O74"/>
+    <mergeCell ref="K83:O83"/>
+    <mergeCell ref="A74:A75"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="A129:A130"/>
+    <mergeCell ref="B83:D83"/>
+    <mergeCell ref="H166:J166"/>
+    <mergeCell ref="E129:G129"/>
+    <mergeCell ref="H161:J161"/>
+    <mergeCell ref="H129:J129"/>
+    <mergeCell ref="E74:G74"/>
+    <mergeCell ref="E166:G166"/>
+    <mergeCell ref="K95:O95"/>
+    <mergeCell ref="A28:Q29"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="A48:Q49"/>
+    <mergeCell ref="E83:G83"/>
+    <mergeCell ref="E35:G35"/>
+    <mergeCell ref="Q55:Q56"/>
+    <mergeCell ref="P50:P51"/>
+    <mergeCell ref="E30:G30"/>
+    <mergeCell ref="Q74:Q75"/>
+    <mergeCell ref="H35:J35"/>
+    <mergeCell ref="P30:P31"/>
+    <mergeCell ref="Q83:Q84"/>
+    <mergeCell ref="A50:A51"/>
+    <mergeCell ref="K35:O35"/>
+    <mergeCell ref="Q30:Q31"/>
+    <mergeCell ref="K50:O50"/>
     <mergeCell ref="P35:P36"/>
     <mergeCell ref="E161:G161"/>
     <mergeCell ref="K30:O30"/>
@@ -20013,70 +20145,6 @@
     <mergeCell ref="A127:Q128"/>
     <mergeCell ref="K161:O161"/>
     <mergeCell ref="H30:J30"/>
-    <mergeCell ref="A28:Q29"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="A48:Q49"/>
-    <mergeCell ref="E83:G83"/>
-    <mergeCell ref="E35:G35"/>
-    <mergeCell ref="Q55:Q56"/>
-    <mergeCell ref="P50:P51"/>
-    <mergeCell ref="E30:G30"/>
-    <mergeCell ref="Q74:Q75"/>
-    <mergeCell ref="H35:J35"/>
-    <mergeCell ref="P30:P31"/>
-    <mergeCell ref="Q83:Q84"/>
-    <mergeCell ref="A50:A51"/>
-    <mergeCell ref="K35:O35"/>
-    <mergeCell ref="Q30:Q31"/>
-    <mergeCell ref="K50:O50"/>
-    <mergeCell ref="B161:D161"/>
-    <mergeCell ref="P129:P130"/>
-    <mergeCell ref="A166:A167"/>
-    <mergeCell ref="K74:O74"/>
-    <mergeCell ref="K83:O83"/>
-    <mergeCell ref="A74:A75"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="A129:A130"/>
-    <mergeCell ref="B83:D83"/>
-    <mergeCell ref="H166:J166"/>
-    <mergeCell ref="E129:G129"/>
-    <mergeCell ref="H161:J161"/>
-    <mergeCell ref="H129:J129"/>
-    <mergeCell ref="E74:G74"/>
-    <mergeCell ref="E166:G166"/>
-    <mergeCell ref="K95:O95"/>
-    <mergeCell ref="Q166:Q167"/>
-    <mergeCell ref="Q35:Q36"/>
-    <mergeCell ref="P161:P162"/>
-    <mergeCell ref="A159:Q160"/>
-    <mergeCell ref="A93:Q94"/>
-    <mergeCell ref="Q161:Q162"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="P83:P84"/>
-    <mergeCell ref="Q129:Q130"/>
-    <mergeCell ref="Q95:Q96"/>
-    <mergeCell ref="H50:J50"/>
-    <mergeCell ref="A161:A162"/>
-    <mergeCell ref="H55:J55"/>
-    <mergeCell ref="A83:A84"/>
-    <mergeCell ref="P55:P56"/>
-    <mergeCell ref="K166:O166"/>
-    <mergeCell ref="H74:J74"/>
-    <mergeCell ref="H83:J83"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="Q50:Q51"/>
-    <mergeCell ref="B55:D55"/>
-    <mergeCell ref="B95:D95"/>
-    <mergeCell ref="E50:G50"/>
-    <mergeCell ref="P74:P75"/>
-    <mergeCell ref="E55:G55"/>
-    <mergeCell ref="K129:O129"/>
-    <mergeCell ref="P95:P96"/>
-    <mergeCell ref="A55:A56"/>
-    <mergeCell ref="A81:Q82"/>
-    <mergeCell ref="A95:A96"/>
-    <mergeCell ref="B129:D129"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" display="https://www.scei-concours.fr/stat2025/bcpst.html" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
@@ -20108,184 +20176,184 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:Q87"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1">
       <c r="A1" s="40"/>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1">
       <c r="A2" s="41" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1">
       <c r="A3" s="41" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1">
       <c r="A4" s="41" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1">
       <c r="A5" s="41" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1">
       <c r="A6" s="41" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1">
       <c r="A7" s="41" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1">
       <c r="A8" s="41" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1">
       <c r="A9" s="41" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1">
       <c r="A10" s="41" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1">
       <c r="A11" s="41" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" ht="15.6" customHeight="1">
       <c r="A13" s="42" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1">
       <c r="A14" s="40"/>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1">
       <c r="A15" s="41" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1">
       <c r="A16" s="41" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17">
       <c r="A17" s="41" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17">
       <c r="A18" s="41" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17">
       <c r="A19" s="41" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17">
       <c r="A20" s="41" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:17">
       <c r="A22" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:17">
       <c r="A23" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A24" s="102" t="s">
+    <row r="24" spans="1:17">
+      <c r="A24" s="104" t="s">
         <v>19</v>
       </c>
-      <c r="B24" s="100"/>
-      <c r="C24" s="100"/>
-      <c r="D24" s="100"/>
-      <c r="E24" s="100"/>
-      <c r="F24" s="100"/>
-      <c r="G24" s="100"/>
-      <c r="H24" s="100"/>
-      <c r="I24" s="100"/>
-      <c r="J24" s="100"/>
-      <c r="K24" s="100"/>
-      <c r="L24" s="100"/>
-      <c r="M24" s="100"/>
-      <c r="N24" s="100"/>
-      <c r="O24" s="100"/>
-      <c r="P24" s="100"/>
-      <c r="Q24" s="100"/>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A25" s="100"/>
-      <c r="B25" s="100"/>
-      <c r="C25" s="100"/>
-      <c r="D25" s="100"/>
-      <c r="E25" s="100"/>
-      <c r="F25" s="100"/>
-      <c r="G25" s="100"/>
-      <c r="H25" s="100"/>
-      <c r="I25" s="100"/>
-      <c r="J25" s="100"/>
-      <c r="K25" s="100"/>
-      <c r="L25" s="100"/>
-      <c r="M25" s="100"/>
-      <c r="N25" s="100"/>
-      <c r="O25" s="100"/>
-      <c r="P25" s="100"/>
-      <c r="Q25" s="100"/>
-    </row>
-    <row r="26" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="101" t="s">
+      <c r="B24" s="103"/>
+      <c r="C24" s="103"/>
+      <c r="D24" s="103"/>
+      <c r="E24" s="103"/>
+      <c r="F24" s="103"/>
+      <c r="G24" s="103"/>
+      <c r="H24" s="103"/>
+      <c r="I24" s="103"/>
+      <c r="J24" s="103"/>
+      <c r="K24" s="103"/>
+      <c r="L24" s="103"/>
+      <c r="M24" s="103"/>
+      <c r="N24" s="103"/>
+      <c r="O24" s="103"/>
+      <c r="P24" s="103"/>
+      <c r="Q24" s="103"/>
+    </row>
+    <row r="25" spans="1:17">
+      <c r="A25" s="103"/>
+      <c r="B25" s="103"/>
+      <c r="C25" s="103"/>
+      <c r="D25" s="103"/>
+      <c r="E25" s="103"/>
+      <c r="F25" s="103"/>
+      <c r="G25" s="103"/>
+      <c r="H25" s="103"/>
+      <c r="I25" s="103"/>
+      <c r="J25" s="103"/>
+      <c r="K25" s="103"/>
+      <c r="L25" s="103"/>
+      <c r="M25" s="103"/>
+      <c r="N25" s="103"/>
+      <c r="O25" s="103"/>
+      <c r="P25" s="103"/>
+      <c r="Q25" s="103"/>
+    </row>
+    <row r="26" spans="1:17" ht="14.45" customHeight="1">
+      <c r="A26" s="105" t="s">
         <v>20</v>
       </c>
-      <c r="B26" s="99" t="s">
+      <c r="B26" s="102" t="s">
         <v>21</v>
       </c>
-      <c r="C26" s="100"/>
-      <c r="D26" s="100"/>
-      <c r="E26" s="99" t="s">
+      <c r="C26" s="103"/>
+      <c r="D26" s="103"/>
+      <c r="E26" s="102" t="s">
         <v>22</v>
       </c>
-      <c r="F26" s="100"/>
-      <c r="G26" s="100"/>
-      <c r="H26" s="99" t="s">
+      <c r="F26" s="103"/>
+      <c r="G26" s="103"/>
+      <c r="H26" s="102" t="s">
         <v>23</v>
       </c>
-      <c r="I26" s="100"/>
-      <c r="J26" s="100"/>
-      <c r="K26" s="99" t="s">
+      <c r="I26" s="103"/>
+      <c r="J26" s="103"/>
+      <c r="K26" s="102" t="s">
         <v>24</v>
       </c>
-      <c r="L26" s="100"/>
-      <c r="M26" s="100"/>
-      <c r="N26" s="100"/>
-      <c r="O26" s="100"/>
-      <c r="P26" s="99" t="s">
+      <c r="L26" s="103"/>
+      <c r="M26" s="103"/>
+      <c r="N26" s="103"/>
+      <c r="O26" s="103"/>
+      <c r="P26" s="102" t="s">
         <v>25</v>
       </c>
-      <c r="Q26" s="99" t="s">
+      <c r="Q26" s="102" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A27" s="100"/>
+    <row r="27" spans="1:17">
+      <c r="A27" s="103"/>
       <c r="B27" s="43" t="s">
         <v>27</v>
       </c>
@@ -20328,10 +20396,10 @@
       <c r="O27" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P27" s="100"/>
-      <c r="Q27" s="100"/>
-    </row>
-    <row r="28" spans="1:17" ht="115.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P27" s="103"/>
+      <c r="Q27" s="103"/>
+    </row>
+    <row r="28" spans="1:17" ht="115.15" customHeight="1">
       <c r="A28" s="43" t="s">
         <v>31</v>
       </c>
@@ -20364,7 +20432,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="144" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:17" ht="144" customHeight="1">
       <c r="A29" s="43" t="s">
         <v>32</v>
       </c>
@@ -20397,7 +20465,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="129.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:17" ht="129.6" customHeight="1">
       <c r="A30" s="43" t="s">
         <v>33</v>
       </c>
@@ -20430,7 +20498,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:17" ht="28.9" customHeight="1">
       <c r="A31" s="43" t="s">
         <v>34</v>
       </c>
@@ -20463,7 +20531,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="32" spans="1:17" ht="144" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:17" ht="144" customHeight="1">
       <c r="A32" s="43" t="s">
         <v>35</v>
       </c>
@@ -20496,7 +20564,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:17" ht="100.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:17" ht="100.9" customHeight="1">
       <c r="A33" s="43" t="s">
         <v>36</v>
       </c>
@@ -20529,7 +20597,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:17" ht="43.15" customHeight="1">
       <c r="A34" s="43" t="s">
         <v>37</v>
       </c>
@@ -20562,7 +20630,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="129.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:17" ht="129.6" customHeight="1">
       <c r="A35" s="43" t="s">
         <v>38</v>
       </c>
@@ -20595,7 +20663,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:17" ht="28.9" customHeight="1">
       <c r="A36" s="43" t="s">
         <v>39</v>
       </c>
@@ -20628,7 +20696,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="37" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:17" ht="43.15" customHeight="1">
       <c r="A37" s="43" t="s">
         <v>40</v>
       </c>
@@ -20661,7 +20729,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="1:17" ht="100.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:17" ht="100.9" customHeight="1">
       <c r="A38" s="43" t="s">
         <v>41</v>
       </c>
@@ -20694,7 +20762,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:17" ht="72" customHeight="1">
       <c r="A39" s="43" t="s">
         <v>42</v>
       </c>
@@ -20727,7 +20795,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="40" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:17" ht="72" customHeight="1">
       <c r="A40" s="43" t="s">
         <v>43</v>
       </c>
@@ -20760,7 +20828,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="1:17" ht="115.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:17" ht="115.15" customHeight="1">
       <c r="A41" s="43" t="s">
         <v>44</v>
       </c>
@@ -20793,7 +20861,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:17" ht="28.9" customHeight="1">
       <c r="A42" s="46" t="s">
         <v>45</v>
       </c>
@@ -20836,81 +20904,81 @@
         <v>72</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A43" s="102" t="s">
+    <row r="43" spans="1:17">
+      <c r="A43" s="104" t="s">
         <v>46</v>
       </c>
-      <c r="B43" s="100"/>
-      <c r="C43" s="100"/>
-      <c r="D43" s="100"/>
-      <c r="E43" s="100"/>
-      <c r="F43" s="100"/>
-      <c r="G43" s="100"/>
-      <c r="H43" s="100"/>
-      <c r="I43" s="100"/>
-      <c r="J43" s="100"/>
-      <c r="K43" s="100"/>
-      <c r="L43" s="100"/>
-      <c r="M43" s="100"/>
-      <c r="N43" s="100"/>
-      <c r="O43" s="100"/>
-      <c r="P43" s="100"/>
-      <c r="Q43" s="100"/>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A44" s="100"/>
-      <c r="B44" s="100"/>
-      <c r="C44" s="100"/>
-      <c r="D44" s="100"/>
-      <c r="E44" s="100"/>
-      <c r="F44" s="100"/>
-      <c r="G44" s="100"/>
-      <c r="H44" s="100"/>
-      <c r="I44" s="100"/>
-      <c r="J44" s="100"/>
-      <c r="K44" s="100"/>
-      <c r="L44" s="100"/>
-      <c r="M44" s="100"/>
-      <c r="N44" s="100"/>
-      <c r="O44" s="100"/>
-      <c r="P44" s="100"/>
-      <c r="Q44" s="100"/>
-    </row>
-    <row r="45" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="101" t="s">
+      <c r="B43" s="103"/>
+      <c r="C43" s="103"/>
+      <c r="D43" s="103"/>
+      <c r="E43" s="103"/>
+      <c r="F43" s="103"/>
+      <c r="G43" s="103"/>
+      <c r="H43" s="103"/>
+      <c r="I43" s="103"/>
+      <c r="J43" s="103"/>
+      <c r="K43" s="103"/>
+      <c r="L43" s="103"/>
+      <c r="M43" s="103"/>
+      <c r="N43" s="103"/>
+      <c r="O43" s="103"/>
+      <c r="P43" s="103"/>
+      <c r="Q43" s="103"/>
+    </row>
+    <row r="44" spans="1:17">
+      <c r="A44" s="103"/>
+      <c r="B44" s="103"/>
+      <c r="C44" s="103"/>
+      <c r="D44" s="103"/>
+      <c r="E44" s="103"/>
+      <c r="F44" s="103"/>
+      <c r="G44" s="103"/>
+      <c r="H44" s="103"/>
+      <c r="I44" s="103"/>
+      <c r="J44" s="103"/>
+      <c r="K44" s="103"/>
+      <c r="L44" s="103"/>
+      <c r="M44" s="103"/>
+      <c r="N44" s="103"/>
+      <c r="O44" s="103"/>
+      <c r="P44" s="103"/>
+      <c r="Q44" s="103"/>
+    </row>
+    <row r="45" spans="1:17" ht="14.45" customHeight="1">
+      <c r="A45" s="105" t="s">
         <v>20</v>
       </c>
-      <c r="B45" s="99" t="s">
+      <c r="B45" s="102" t="s">
         <v>21</v>
       </c>
-      <c r="C45" s="100"/>
-      <c r="D45" s="100"/>
-      <c r="E45" s="99" t="s">
+      <c r="C45" s="103"/>
+      <c r="D45" s="103"/>
+      <c r="E45" s="102" t="s">
         <v>22</v>
       </c>
-      <c r="F45" s="100"/>
-      <c r="G45" s="100"/>
-      <c r="H45" s="99" t="s">
+      <c r="F45" s="103"/>
+      <c r="G45" s="103"/>
+      <c r="H45" s="102" t="s">
         <v>23</v>
       </c>
-      <c r="I45" s="100"/>
-      <c r="J45" s="100"/>
-      <c r="K45" s="99" t="s">
+      <c r="I45" s="103"/>
+      <c r="J45" s="103"/>
+      <c r="K45" s="102" t="s">
         <v>24</v>
       </c>
-      <c r="L45" s="100"/>
-      <c r="M45" s="100"/>
-      <c r="N45" s="100"/>
-      <c r="O45" s="100"/>
-      <c r="P45" s="99" t="s">
+      <c r="L45" s="103"/>
+      <c r="M45" s="103"/>
+      <c r="N45" s="103"/>
+      <c r="O45" s="103"/>
+      <c r="P45" s="102" t="s">
         <v>25</v>
       </c>
-      <c r="Q45" s="99" t="s">
+      <c r="Q45" s="102" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A46" s="100"/>
+    <row r="46" spans="1:17">
+      <c r="A46" s="103"/>
       <c r="B46" s="43" t="s">
         <v>27</v>
       </c>
@@ -20953,10 +21021,10 @@
       <c r="O46" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P46" s="100"/>
-      <c r="Q46" s="100"/>
-    </row>
-    <row r="47" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P46" s="103"/>
+      <c r="Q46" s="103"/>
+    </row>
+    <row r="47" spans="1:17" ht="28.9" customHeight="1">
       <c r="A47" s="43" t="s">
         <v>46</v>
       </c>
@@ -21007,81 +21075,81 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A48" s="102" t="s">
+    <row r="48" spans="1:17">
+      <c r="A48" s="104" t="s">
         <v>47</v>
       </c>
-      <c r="B48" s="100"/>
-      <c r="C48" s="100"/>
-      <c r="D48" s="100"/>
-      <c r="E48" s="100"/>
-      <c r="F48" s="100"/>
-      <c r="G48" s="100"/>
-      <c r="H48" s="100"/>
-      <c r="I48" s="100"/>
-      <c r="J48" s="100"/>
-      <c r="K48" s="100"/>
-      <c r="L48" s="100"/>
-      <c r="M48" s="100"/>
-      <c r="N48" s="100"/>
-      <c r="O48" s="100"/>
-      <c r="P48" s="100"/>
-      <c r="Q48" s="100"/>
-    </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A49" s="100"/>
-      <c r="B49" s="100"/>
-      <c r="C49" s="100"/>
-      <c r="D49" s="100"/>
-      <c r="E49" s="100"/>
-      <c r="F49" s="100"/>
-      <c r="G49" s="100"/>
-      <c r="H49" s="100"/>
-      <c r="I49" s="100"/>
-      <c r="J49" s="100"/>
-      <c r="K49" s="100"/>
-      <c r="L49" s="100"/>
-      <c r="M49" s="100"/>
-      <c r="N49" s="100"/>
-      <c r="O49" s="100"/>
-      <c r="P49" s="100"/>
-      <c r="Q49" s="100"/>
-    </row>
-    <row r="50" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="101" t="s">
+      <c r="B48" s="103"/>
+      <c r="C48" s="103"/>
+      <c r="D48" s="103"/>
+      <c r="E48" s="103"/>
+      <c r="F48" s="103"/>
+      <c r="G48" s="103"/>
+      <c r="H48" s="103"/>
+      <c r="I48" s="103"/>
+      <c r="J48" s="103"/>
+      <c r="K48" s="103"/>
+      <c r="L48" s="103"/>
+      <c r="M48" s="103"/>
+      <c r="N48" s="103"/>
+      <c r="O48" s="103"/>
+      <c r="P48" s="103"/>
+      <c r="Q48" s="103"/>
+    </row>
+    <row r="49" spans="1:17">
+      <c r="A49" s="103"/>
+      <c r="B49" s="103"/>
+      <c r="C49" s="103"/>
+      <c r="D49" s="103"/>
+      <c r="E49" s="103"/>
+      <c r="F49" s="103"/>
+      <c r="G49" s="103"/>
+      <c r="H49" s="103"/>
+      <c r="I49" s="103"/>
+      <c r="J49" s="103"/>
+      <c r="K49" s="103"/>
+      <c r="L49" s="103"/>
+      <c r="M49" s="103"/>
+      <c r="N49" s="103"/>
+      <c r="O49" s="103"/>
+      <c r="P49" s="103"/>
+      <c r="Q49" s="103"/>
+    </row>
+    <row r="50" spans="1:17" ht="14.45" customHeight="1">
+      <c r="A50" s="105" t="s">
         <v>20</v>
       </c>
-      <c r="B50" s="99" t="s">
+      <c r="B50" s="102" t="s">
         <v>21</v>
       </c>
-      <c r="C50" s="100"/>
-      <c r="D50" s="100"/>
-      <c r="E50" s="99" t="s">
+      <c r="C50" s="103"/>
+      <c r="D50" s="103"/>
+      <c r="E50" s="102" t="s">
         <v>22</v>
       </c>
-      <c r="F50" s="100"/>
-      <c r="G50" s="100"/>
-      <c r="H50" s="99" t="s">
+      <c r="F50" s="103"/>
+      <c r="G50" s="103"/>
+      <c r="H50" s="102" t="s">
         <v>23</v>
       </c>
-      <c r="I50" s="100"/>
-      <c r="J50" s="100"/>
-      <c r="K50" s="99" t="s">
+      <c r="I50" s="103"/>
+      <c r="J50" s="103"/>
+      <c r="K50" s="102" t="s">
         <v>24</v>
       </c>
-      <c r="L50" s="100"/>
-      <c r="M50" s="100"/>
-      <c r="N50" s="100"/>
-      <c r="O50" s="100"/>
-      <c r="P50" s="99" t="s">
+      <c r="L50" s="103"/>
+      <c r="M50" s="103"/>
+      <c r="N50" s="103"/>
+      <c r="O50" s="103"/>
+      <c r="P50" s="102" t="s">
         <v>25</v>
       </c>
-      <c r="Q50" s="99" t="s">
+      <c r="Q50" s="102" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A51" s="100"/>
+    <row r="51" spans="1:17">
+      <c r="A51" s="103"/>
       <c r="B51" s="43" t="s">
         <v>27</v>
       </c>
@@ -21124,10 +21192,10 @@
       <c r="O51" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P51" s="100"/>
-      <c r="Q51" s="100"/>
-    </row>
-    <row r="52" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P51" s="103"/>
+      <c r="Q51" s="103"/>
+    </row>
+    <row r="52" spans="1:17" ht="57.6" customHeight="1">
       <c r="A52" s="43" t="s">
         <v>48</v>
       </c>
@@ -21160,7 +21228,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:17" ht="57.6" customHeight="1">
       <c r="A53" s="43" t="s">
         <v>49</v>
       </c>
@@ -21193,7 +21261,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="54" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:17" ht="72" customHeight="1">
       <c r="A54" s="43" t="s">
         <v>50</v>
       </c>
@@ -21226,7 +21294,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:17" ht="43.15" customHeight="1">
       <c r="A55" s="43" t="s">
         <v>51</v>
       </c>
@@ -21259,7 +21327,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:17" ht="28.9" customHeight="1">
       <c r="A56" s="46" t="s">
         <v>52</v>
       </c>
@@ -21302,81 +21370,81 @@
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A57" s="102" t="s">
+    <row r="57" spans="1:17">
+      <c r="A57" s="104" t="s">
         <v>53</v>
       </c>
-      <c r="B57" s="100"/>
-      <c r="C57" s="100"/>
-      <c r="D57" s="100"/>
-      <c r="E57" s="100"/>
-      <c r="F57" s="100"/>
-      <c r="G57" s="100"/>
-      <c r="H57" s="100"/>
-      <c r="I57" s="100"/>
-      <c r="J57" s="100"/>
-      <c r="K57" s="100"/>
-      <c r="L57" s="100"/>
-      <c r="M57" s="100"/>
-      <c r="N57" s="100"/>
-      <c r="O57" s="100"/>
-      <c r="P57" s="100"/>
-      <c r="Q57" s="100"/>
-    </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A58" s="100"/>
-      <c r="B58" s="100"/>
-      <c r="C58" s="100"/>
-      <c r="D58" s="100"/>
-      <c r="E58" s="100"/>
-      <c r="F58" s="100"/>
-      <c r="G58" s="100"/>
-      <c r="H58" s="100"/>
-      <c r="I58" s="100"/>
-      <c r="J58" s="100"/>
-      <c r="K58" s="100"/>
-      <c r="L58" s="100"/>
-      <c r="M58" s="100"/>
-      <c r="N58" s="100"/>
-      <c r="O58" s="100"/>
-      <c r="P58" s="100"/>
-      <c r="Q58" s="100"/>
-    </row>
-    <row r="59" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="101" t="s">
+      <c r="B57" s="103"/>
+      <c r="C57" s="103"/>
+      <c r="D57" s="103"/>
+      <c r="E57" s="103"/>
+      <c r="F57" s="103"/>
+      <c r="G57" s="103"/>
+      <c r="H57" s="103"/>
+      <c r="I57" s="103"/>
+      <c r="J57" s="103"/>
+      <c r="K57" s="103"/>
+      <c r="L57" s="103"/>
+      <c r="M57" s="103"/>
+      <c r="N57" s="103"/>
+      <c r="O57" s="103"/>
+      <c r="P57" s="103"/>
+      <c r="Q57" s="103"/>
+    </row>
+    <row r="58" spans="1:17">
+      <c r="A58" s="103"/>
+      <c r="B58" s="103"/>
+      <c r="C58" s="103"/>
+      <c r="D58" s="103"/>
+      <c r="E58" s="103"/>
+      <c r="F58" s="103"/>
+      <c r="G58" s="103"/>
+      <c r="H58" s="103"/>
+      <c r="I58" s="103"/>
+      <c r="J58" s="103"/>
+      <c r="K58" s="103"/>
+      <c r="L58" s="103"/>
+      <c r="M58" s="103"/>
+      <c r="N58" s="103"/>
+      <c r="O58" s="103"/>
+      <c r="P58" s="103"/>
+      <c r="Q58" s="103"/>
+    </row>
+    <row r="59" spans="1:17" ht="14.45" customHeight="1">
+      <c r="A59" s="105" t="s">
         <v>20</v>
       </c>
-      <c r="B59" s="99" t="s">
+      <c r="B59" s="102" t="s">
         <v>21</v>
       </c>
-      <c r="C59" s="100"/>
-      <c r="D59" s="100"/>
-      <c r="E59" s="99" t="s">
+      <c r="C59" s="103"/>
+      <c r="D59" s="103"/>
+      <c r="E59" s="102" t="s">
         <v>22</v>
       </c>
-      <c r="F59" s="100"/>
-      <c r="G59" s="100"/>
-      <c r="H59" s="99" t="s">
+      <c r="F59" s="103"/>
+      <c r="G59" s="103"/>
+      <c r="H59" s="102" t="s">
         <v>23</v>
       </c>
-      <c r="I59" s="100"/>
-      <c r="J59" s="100"/>
-      <c r="K59" s="99" t="s">
+      <c r="I59" s="103"/>
+      <c r="J59" s="103"/>
+      <c r="K59" s="102" t="s">
         <v>24</v>
       </c>
-      <c r="L59" s="100"/>
-      <c r="M59" s="100"/>
-      <c r="N59" s="100"/>
-      <c r="O59" s="100"/>
-      <c r="P59" s="99" t="s">
+      <c r="L59" s="103"/>
+      <c r="M59" s="103"/>
+      <c r="N59" s="103"/>
+      <c r="O59" s="103"/>
+      <c r="P59" s="102" t="s">
         <v>25</v>
       </c>
-      <c r="Q59" s="99" t="s">
+      <c r="Q59" s="102" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A60" s="100"/>
+    <row r="60" spans="1:17">
+      <c r="A60" s="103"/>
       <c r="B60" s="43" t="s">
         <v>27</v>
       </c>
@@ -21419,10 +21487,10 @@
       <c r="O60" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P60" s="100"/>
-      <c r="Q60" s="100"/>
-    </row>
-    <row r="61" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P60" s="103"/>
+      <c r="Q60" s="103"/>
+    </row>
+    <row r="61" spans="1:17" ht="57.6" customHeight="1">
       <c r="A61" s="43" t="s">
         <v>54</v>
       </c>
@@ -21455,7 +21523,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:17" ht="72" customHeight="1">
       <c r="A62" s="43" t="s">
         <v>55</v>
       </c>
@@ -21488,7 +21556,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:17" ht="28.9" customHeight="1">
       <c r="A63" s="43" t="s">
         <v>56</v>
       </c>
@@ -21521,7 +21589,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="115.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:17" ht="115.15" customHeight="1">
       <c r="A64" s="43" t="s">
         <v>57</v>
       </c>
@@ -21554,7 +21622,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:17" ht="43.15" customHeight="1">
       <c r="A65" s="43" t="s">
         <v>58</v>
       </c>
@@ -21587,7 +21655,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:17" ht="57.6" customHeight="1">
       <c r="A66" s="43" t="s">
         <v>59</v>
       </c>
@@ -21620,7 +21688,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:17" ht="72" customHeight="1">
       <c r="A67" s="43" t="s">
         <v>60</v>
       </c>
@@ -21653,7 +21721,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:17" ht="57.6" customHeight="1">
       <c r="A68" s="43" t="s">
         <v>61</v>
       </c>
@@ -21686,7 +21754,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:17" ht="57.6" customHeight="1">
       <c r="A69" s="43" t="s">
         <v>62</v>
       </c>
@@ -21719,7 +21787,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:17" ht="86.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:17" ht="86.45" customHeight="1">
       <c r="A70" s="43" t="s">
         <v>63</v>
       </c>
@@ -21752,7 +21820,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" ht="57.6" customHeight="1">
       <c r="A71" s="43" t="s">
         <v>64</v>
       </c>
@@ -21785,7 +21853,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:17" ht="72" customHeight="1">
       <c r="A72" s="43" t="s">
         <v>65</v>
       </c>
@@ -21818,7 +21886,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:17" ht="57.6" customHeight="1">
       <c r="A73" s="43" t="s">
         <v>66</v>
       </c>
@@ -21851,7 +21919,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:17" ht="43.15" customHeight="1">
       <c r="A74" s="46" t="s">
         <v>53</v>
       </c>
@@ -21894,81 +21962,81 @@
         <v>13</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A75" s="102" t="s">
+    <row r="75" spans="1:17">
+      <c r="A75" s="104" t="s">
         <v>67</v>
       </c>
-      <c r="B75" s="100"/>
-      <c r="C75" s="100"/>
-      <c r="D75" s="100"/>
-      <c r="E75" s="100"/>
-      <c r="F75" s="100"/>
-      <c r="G75" s="100"/>
-      <c r="H75" s="100"/>
-      <c r="I75" s="100"/>
-      <c r="J75" s="100"/>
-      <c r="K75" s="100"/>
-      <c r="L75" s="100"/>
-      <c r="M75" s="100"/>
-      <c r="N75" s="100"/>
-      <c r="O75" s="100"/>
-      <c r="P75" s="100"/>
-      <c r="Q75" s="100"/>
-    </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A76" s="100"/>
-      <c r="B76" s="100"/>
-      <c r="C76" s="100"/>
-      <c r="D76" s="100"/>
-      <c r="E76" s="100"/>
-      <c r="F76" s="100"/>
-      <c r="G76" s="100"/>
-      <c r="H76" s="100"/>
-      <c r="I76" s="100"/>
-      <c r="J76" s="100"/>
-      <c r="K76" s="100"/>
-      <c r="L76" s="100"/>
-      <c r="M76" s="100"/>
-      <c r="N76" s="100"/>
-      <c r="O76" s="100"/>
-      <c r="P76" s="100"/>
-      <c r="Q76" s="100"/>
-    </row>
-    <row r="77" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="101" t="s">
+      <c r="B75" s="103"/>
+      <c r="C75" s="103"/>
+      <c r="D75" s="103"/>
+      <c r="E75" s="103"/>
+      <c r="F75" s="103"/>
+      <c r="G75" s="103"/>
+      <c r="H75" s="103"/>
+      <c r="I75" s="103"/>
+      <c r="J75" s="103"/>
+      <c r="K75" s="103"/>
+      <c r="L75" s="103"/>
+      <c r="M75" s="103"/>
+      <c r="N75" s="103"/>
+      <c r="O75" s="103"/>
+      <c r="P75" s="103"/>
+      <c r="Q75" s="103"/>
+    </row>
+    <row r="76" spans="1:17">
+      <c r="A76" s="103"/>
+      <c r="B76" s="103"/>
+      <c r="C76" s="103"/>
+      <c r="D76" s="103"/>
+      <c r="E76" s="103"/>
+      <c r="F76" s="103"/>
+      <c r="G76" s="103"/>
+      <c r="H76" s="103"/>
+      <c r="I76" s="103"/>
+      <c r="J76" s="103"/>
+      <c r="K76" s="103"/>
+      <c r="L76" s="103"/>
+      <c r="M76" s="103"/>
+      <c r="N76" s="103"/>
+      <c r="O76" s="103"/>
+      <c r="P76" s="103"/>
+      <c r="Q76" s="103"/>
+    </row>
+    <row r="77" spans="1:17" ht="14.45" customHeight="1">
+      <c r="A77" s="105" t="s">
         <v>20</v>
       </c>
-      <c r="B77" s="99" t="s">
+      <c r="B77" s="102" t="s">
         <v>21</v>
       </c>
-      <c r="C77" s="100"/>
-      <c r="D77" s="100"/>
-      <c r="E77" s="99" t="s">
+      <c r="C77" s="103"/>
+      <c r="D77" s="103"/>
+      <c r="E77" s="102" t="s">
         <v>22</v>
       </c>
-      <c r="F77" s="100"/>
-      <c r="G77" s="100"/>
-      <c r="H77" s="99" t="s">
+      <c r="F77" s="103"/>
+      <c r="G77" s="103"/>
+      <c r="H77" s="102" t="s">
         <v>23</v>
       </c>
-      <c r="I77" s="100"/>
-      <c r="J77" s="100"/>
-      <c r="K77" s="99" t="s">
+      <c r="I77" s="103"/>
+      <c r="J77" s="103"/>
+      <c r="K77" s="102" t="s">
         <v>24</v>
       </c>
-      <c r="L77" s="100"/>
-      <c r="M77" s="100"/>
-      <c r="N77" s="100"/>
-      <c r="O77" s="100"/>
-      <c r="P77" s="99" t="s">
+      <c r="L77" s="103"/>
+      <c r="M77" s="103"/>
+      <c r="N77" s="103"/>
+      <c r="O77" s="103"/>
+      <c r="P77" s="102" t="s">
         <v>25</v>
       </c>
-      <c r="Q77" s="99" t="s">
+      <c r="Q77" s="102" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A78" s="100"/>
+    <row r="78" spans="1:17">
+      <c r="A78" s="103"/>
       <c r="B78" s="43" t="s">
         <v>27</v>
       </c>
@@ -22011,10 +22079,10 @@
       <c r="O78" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P78" s="100"/>
-      <c r="Q78" s="100"/>
-    </row>
-    <row r="79" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P78" s="103"/>
+      <c r="Q78" s="103"/>
+    </row>
+    <row r="79" spans="1:17" ht="28.9" customHeight="1">
       <c r="A79" s="43" t="s">
         <v>68</v>
       </c>
@@ -22065,81 +22133,81 @@
         <v>2</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A80" s="102" t="s">
+    <row r="80" spans="1:17">
+      <c r="A80" s="104" t="s">
         <v>69</v>
       </c>
-      <c r="B80" s="100"/>
-      <c r="C80" s="100"/>
-      <c r="D80" s="100"/>
-      <c r="E80" s="100"/>
-      <c r="F80" s="100"/>
-      <c r="G80" s="100"/>
-      <c r="H80" s="100"/>
-      <c r="I80" s="100"/>
-      <c r="J80" s="100"/>
-      <c r="K80" s="100"/>
-      <c r="L80" s="100"/>
-      <c r="M80" s="100"/>
-      <c r="N80" s="100"/>
-      <c r="O80" s="100"/>
-      <c r="P80" s="100"/>
-      <c r="Q80" s="100"/>
-    </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A81" s="100"/>
-      <c r="B81" s="100"/>
-      <c r="C81" s="100"/>
-      <c r="D81" s="100"/>
-      <c r="E81" s="100"/>
-      <c r="F81" s="100"/>
-      <c r="G81" s="100"/>
-      <c r="H81" s="100"/>
-      <c r="I81" s="100"/>
-      <c r="J81" s="100"/>
-      <c r="K81" s="100"/>
-      <c r="L81" s="100"/>
-      <c r="M81" s="100"/>
-      <c r="N81" s="100"/>
-      <c r="O81" s="100"/>
-      <c r="P81" s="100"/>
-      <c r="Q81" s="100"/>
-    </row>
-    <row r="82" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="101" t="s">
+      <c r="B80" s="103"/>
+      <c r="C80" s="103"/>
+      <c r="D80" s="103"/>
+      <c r="E80" s="103"/>
+      <c r="F80" s="103"/>
+      <c r="G80" s="103"/>
+      <c r="H80" s="103"/>
+      <c r="I80" s="103"/>
+      <c r="J80" s="103"/>
+      <c r="K80" s="103"/>
+      <c r="L80" s="103"/>
+      <c r="M80" s="103"/>
+      <c r="N80" s="103"/>
+      <c r="O80" s="103"/>
+      <c r="P80" s="103"/>
+      <c r="Q80" s="103"/>
+    </row>
+    <row r="81" spans="1:17">
+      <c r="A81" s="103"/>
+      <c r="B81" s="103"/>
+      <c r="C81" s="103"/>
+      <c r="D81" s="103"/>
+      <c r="E81" s="103"/>
+      <c r="F81" s="103"/>
+      <c r="G81" s="103"/>
+      <c r="H81" s="103"/>
+      <c r="I81" s="103"/>
+      <c r="J81" s="103"/>
+      <c r="K81" s="103"/>
+      <c r="L81" s="103"/>
+      <c r="M81" s="103"/>
+      <c r="N81" s="103"/>
+      <c r="O81" s="103"/>
+      <c r="P81" s="103"/>
+      <c r="Q81" s="103"/>
+    </row>
+    <row r="82" spans="1:17" ht="14.45" customHeight="1">
+      <c r="A82" s="105" t="s">
         <v>20</v>
       </c>
-      <c r="B82" s="99" t="s">
+      <c r="B82" s="102" t="s">
         <v>21</v>
       </c>
-      <c r="C82" s="100"/>
-      <c r="D82" s="100"/>
-      <c r="E82" s="99" t="s">
+      <c r="C82" s="103"/>
+      <c r="D82" s="103"/>
+      <c r="E82" s="102" t="s">
         <v>22</v>
       </c>
-      <c r="F82" s="100"/>
-      <c r="G82" s="100"/>
-      <c r="H82" s="99" t="s">
+      <c r="F82" s="103"/>
+      <c r="G82" s="103"/>
+      <c r="H82" s="102" t="s">
         <v>23</v>
       </c>
-      <c r="I82" s="100"/>
-      <c r="J82" s="100"/>
-      <c r="K82" s="99" t="s">
+      <c r="I82" s="103"/>
+      <c r="J82" s="103"/>
+      <c r="K82" s="102" t="s">
         <v>24</v>
       </c>
-      <c r="L82" s="100"/>
-      <c r="M82" s="100"/>
-      <c r="N82" s="100"/>
-      <c r="O82" s="100"/>
-      <c r="P82" s="99" t="s">
+      <c r="L82" s="103"/>
+      <c r="M82" s="103"/>
+      <c r="N82" s="103"/>
+      <c r="O82" s="103"/>
+      <c r="P82" s="102" t="s">
         <v>25</v>
       </c>
-      <c r="Q82" s="99" t="s">
+      <c r="Q82" s="102" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A83" s="100"/>
+    <row r="83" spans="1:17">
+      <c r="A83" s="103"/>
       <c r="B83" s="43" t="s">
         <v>27</v>
       </c>
@@ -22182,10 +22250,10 @@
       <c r="O83" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="P83" s="100"/>
-      <c r="Q83" s="100"/>
-    </row>
-    <row r="84" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P83" s="103"/>
+      <c r="Q83" s="103"/>
+    </row>
+    <row r="84" spans="1:17" ht="57.6" customHeight="1">
       <c r="A84" s="43" t="s">
         <v>70</v>
       </c>
@@ -22218,7 +22286,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:17" ht="72" customHeight="1">
       <c r="A85" s="43" t="s">
         <v>71</v>
       </c>
@@ -22251,7 +22319,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:17" ht="57.6" customHeight="1">
       <c r="A86" s="43" t="s">
         <v>72</v>
       </c>
@@ -22284,7 +22352,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:17" ht="72" customHeight="1">
       <c r="A87" s="46" t="s">
         <v>73</v>
       </c>
@@ -22329,6 +22397,38 @@
     </row>
   </sheetData>
   <mergeCells count="48">
+    <mergeCell ref="A24:Q25"/>
+    <mergeCell ref="K82:O82"/>
+    <mergeCell ref="H50:J50"/>
+    <mergeCell ref="P26:P27"/>
+    <mergeCell ref="A59:A60"/>
+    <mergeCell ref="Q77:Q78"/>
+    <mergeCell ref="E82:G82"/>
+    <mergeCell ref="A82:A83"/>
+    <mergeCell ref="B77:D77"/>
+    <mergeCell ref="P45:P46"/>
+    <mergeCell ref="A80:Q81"/>
+    <mergeCell ref="A77:A78"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="H82:J82"/>
+    <mergeCell ref="Q45:Q46"/>
+    <mergeCell ref="A48:Q49"/>
+    <mergeCell ref="P82:P83"/>
+    <mergeCell ref="Q59:Q60"/>
+    <mergeCell ref="H77:J77"/>
+    <mergeCell ref="K59:O59"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="Q82:Q83"/>
+    <mergeCell ref="K77:O77"/>
+    <mergeCell ref="P77:P78"/>
+    <mergeCell ref="E77:G77"/>
+    <mergeCell ref="E50:G50"/>
+    <mergeCell ref="H59:J59"/>
+    <mergeCell ref="A75:Q76"/>
+    <mergeCell ref="P59:P60"/>
+    <mergeCell ref="E59:G59"/>
+    <mergeCell ref="A57:Q58"/>
+    <mergeCell ref="B59:D59"/>
     <mergeCell ref="A26:A27"/>
     <mergeCell ref="K50:O50"/>
     <mergeCell ref="E26:G26"/>
@@ -22345,38 +22445,6 @@
     <mergeCell ref="E45:G45"/>
     <mergeCell ref="B45:D45"/>
     <mergeCell ref="B50:D50"/>
-    <mergeCell ref="E50:G50"/>
-    <mergeCell ref="H59:J59"/>
-    <mergeCell ref="A75:Q76"/>
-    <mergeCell ref="P59:P60"/>
-    <mergeCell ref="E59:G59"/>
-    <mergeCell ref="A57:Q58"/>
-    <mergeCell ref="B59:D59"/>
-    <mergeCell ref="P82:P83"/>
-    <mergeCell ref="Q59:Q60"/>
-    <mergeCell ref="H77:J77"/>
-    <mergeCell ref="K59:O59"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="Q82:Q83"/>
-    <mergeCell ref="K77:O77"/>
-    <mergeCell ref="P77:P78"/>
-    <mergeCell ref="E77:G77"/>
-    <mergeCell ref="A24:Q25"/>
-    <mergeCell ref="K82:O82"/>
-    <mergeCell ref="H50:J50"/>
-    <mergeCell ref="P26:P27"/>
-    <mergeCell ref="A59:A60"/>
-    <mergeCell ref="Q77:Q78"/>
-    <mergeCell ref="E82:G82"/>
-    <mergeCell ref="A82:A83"/>
-    <mergeCell ref="B77:D77"/>
-    <mergeCell ref="P45:P46"/>
-    <mergeCell ref="A80:Q81"/>
-    <mergeCell ref="A77:A78"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="H82:J82"/>
-    <mergeCell ref="Q45:Q46"/>
-    <mergeCell ref="A48:Q49"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" display="https://www.scei-concours.fr/stat2025/tb.html" xr:uid="{00000000-0004-0000-0500-000000000000}"/>
@@ -22404,7 +22472,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:G78"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
@@ -22414,18 +22482,18 @@
     <col min="7" max="7" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="104" t="s">
+    <row r="1" spans="1:7" ht="22.15" customHeight="1">
+      <c r="A1" s="107" t="s">
         <v>905</v>
       </c>
-      <c r="B1" s="100"/>
-      <c r="C1" s="100"/>
-      <c r="D1" s="100"/>
-      <c r="E1" s="100"/>
-      <c r="F1" s="100"/>
-      <c r="G1" s="100"/>
-    </row>
-    <row r="2" spans="1:7" ht="37.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="103"/>
+      <c r="C1" s="103"/>
+      <c r="D1" s="103"/>
+      <c r="E1" s="103"/>
+      <c r="F1" s="103"/>
+      <c r="G1" s="103"/>
+    </row>
+    <row r="2" spans="1:7" ht="37.9" customHeight="1">
       <c r="A2" s="48" t="s">
         <v>906</v>
       </c>
@@ -22448,7 +22516,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="31.9" customHeight="1">
       <c r="A3" s="55" t="s">
         <v>913</v>
       </c>
@@ -22471,7 +22539,7 @@
         <v>919</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A4" s="49" t="s">
         <v>126</v>
       </c>
@@ -22492,7 +22560,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A5" s="49" t="s">
         <v>37</v>
       </c>
@@ -22513,7 +22581,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A6" s="49" t="s">
         <v>122</v>
       </c>
@@ -22534,7 +22602,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A7" s="49" t="s">
         <v>211</v>
       </c>
@@ -22555,7 +22623,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A8" s="49" t="s">
         <v>699</v>
       </c>
@@ -22576,7 +22644,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A9" s="49" t="s">
         <v>104</v>
       </c>
@@ -22599,7 +22667,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A10" s="49" t="s">
         <v>104</v>
       </c>
@@ -22622,7 +22690,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A11" s="49" t="s">
         <v>104</v>
       </c>
@@ -22645,7 +22713,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A12" s="49" t="s">
         <v>99</v>
       </c>
@@ -22666,7 +22734,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A13" s="49" t="s">
         <v>99</v>
       </c>
@@ -22687,7 +22755,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A14" s="49" t="s">
         <v>282</v>
       </c>
@@ -22708,7 +22776,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A15" s="49" t="s">
         <v>187</v>
       </c>
@@ -22729,7 +22797,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A16" s="49" t="s">
         <v>112</v>
       </c>
@@ -22750,7 +22818,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A17" s="49" t="s">
         <v>115</v>
       </c>
@@ -22771,7 +22839,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A18" s="49" t="s">
         <v>344</v>
       </c>
@@ -22792,7 +22860,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A19" s="49" t="s">
         <v>141</v>
       </c>
@@ -22813,7 +22881,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A20" s="49" t="s">
         <v>257</v>
       </c>
@@ -22834,7 +22902,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A21" s="49" t="s">
         <v>369</v>
       </c>
@@ -22855,7 +22923,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A22" s="49" t="s">
         <v>793</v>
       </c>
@@ -22876,7 +22944,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A23" s="49" t="s">
         <v>804</v>
       </c>
@@ -22897,7 +22965,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A24" s="49" t="s">
         <v>809</v>
       </c>
@@ -22918,7 +22986,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A25" s="49" t="s">
         <v>799</v>
       </c>
@@ -22939,7 +23007,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A26" s="49" t="s">
         <v>814</v>
       </c>
@@ -22960,7 +23028,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A27" s="49" t="s">
         <v>819</v>
       </c>
@@ -22981,7 +23049,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A28" s="51" t="s">
         <v>126</v>
       </c>
@@ -23002,7 +23070,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A29" s="51" t="s">
         <v>282</v>
       </c>
@@ -23023,7 +23091,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A30" s="51" t="s">
         <v>187</v>
       </c>
@@ -23044,7 +23112,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A31" s="51" t="s">
         <v>104</v>
       </c>
@@ -23067,7 +23135,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A32" s="51" t="s">
         <v>104</v>
       </c>
@@ -23088,7 +23156,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A33" s="51" t="s">
         <v>37</v>
       </c>
@@ -23109,7 +23177,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A34" s="51" t="s">
         <v>231</v>
       </c>
@@ -23128,7 +23196,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A35" s="51" t="s">
         <v>122</v>
       </c>
@@ -23149,7 +23217,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A36" s="51" t="s">
         <v>211</v>
       </c>
@@ -23170,7 +23238,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A37" s="51" t="s">
         <v>99</v>
       </c>
@@ -23191,7 +23259,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A38" s="51" t="s">
         <v>99</v>
       </c>
@@ -23212,7 +23280,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A39" s="51" t="s">
         <v>115</v>
       </c>
@@ -23233,7 +23301,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A40" s="51" t="s">
         <v>112</v>
       </c>
@@ -23254,7 +23322,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A41" s="56" t="s">
         <v>344</v>
       </c>
@@ -23275,7 +23343,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A42" s="51" t="s">
         <v>141</v>
       </c>
@@ -23296,7 +23364,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A43" s="51" t="s">
         <v>257</v>
       </c>
@@ -23317,7 +23385,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A44" s="56" t="s">
         <v>369</v>
       </c>
@@ -23338,7 +23406,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A45" s="60" t="s">
         <v>744</v>
       </c>
@@ -23359,7 +23427,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A46" s="53" t="s">
         <v>231</v>
       </c>
@@ -23378,7 +23446,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A47" s="53" t="s">
         <v>88</v>
       </c>
@@ -23397,7 +23465,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A48" s="53" t="s">
         <v>88</v>
       </c>
@@ -23418,7 +23486,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A49" s="53" t="s">
         <v>88</v>
       </c>
@@ -23439,7 +23507,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A50" s="56" t="s">
         <v>739</v>
       </c>
@@ -23460,7 +23528,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A51" s="58" t="s">
         <v>749</v>
       </c>
@@ -23481,7 +23549,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A52" s="53" t="s">
         <v>705</v>
       </c>
@@ -23500,7 +23568,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A53" s="53" t="s">
         <v>711</v>
       </c>
@@ -23519,7 +23587,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A54" s="53" t="s">
         <v>717</v>
       </c>
@@ -23538,7 +23606,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A55" s="56" t="s">
         <v>136</v>
       </c>
@@ -23557,7 +23625,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A56" s="56" t="s">
         <v>136</v>
       </c>
@@ -23576,7 +23644,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A57" s="58" t="s">
         <v>339</v>
       </c>
@@ -23597,7 +23665,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A58" s="58" t="s">
         <v>339</v>
       </c>
@@ -23618,7 +23686,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A59" s="58" t="s">
         <v>168</v>
       </c>
@@ -23639,7 +23707,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A60" s="58" t="s">
         <v>91</v>
       </c>
@@ -23660,7 +23728,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A61" s="58" t="s">
         <v>91</v>
       </c>
@@ -23681,7 +23749,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A62" s="58" t="s">
         <v>193</v>
       </c>
@@ -23702,7 +23770,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A63" s="58" t="s">
         <v>193</v>
       </c>
@@ -23723,7 +23791,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="64" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A64" s="58" t="s">
         <v>144</v>
       </c>
@@ -23744,7 +23812,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A65" s="58" t="s">
         <v>144</v>
       </c>
@@ -23765,7 +23833,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="66" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A66" s="58" t="s">
         <v>85</v>
       </c>
@@ -23786,7 +23854,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A67" s="58" t="s">
         <v>321</v>
       </c>
@@ -23807,7 +23875,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="68" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A68" s="58" t="s">
         <v>321</v>
       </c>
@@ -23828,7 +23896,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="69" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A69" s="58" t="s">
         <v>266</v>
       </c>
@@ -23849,7 +23917,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="70" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A70" s="58" t="s">
         <v>266</v>
       </c>
@@ -23870,7 +23938,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="71" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A71" s="58" t="s">
         <v>428</v>
       </c>
@@ -23891,7 +23959,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="72" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A72" s="58" t="s">
         <v>458</v>
       </c>
@@ -23912,7 +23980,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="73" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A73" s="58" t="s">
         <v>729</v>
       </c>
@@ -23933,7 +24001,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="74" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A74" s="58" t="s">
         <v>734</v>
       </c>
@@ -23954,7 +24022,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="75" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A75" s="58" t="s">
         <v>196</v>
       </c>
@@ -23975,7 +24043,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="76" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" ht="16.149999999999999" customHeight="1">
       <c r="A76" s="58" t="s">
         <v>196</v>
       </c>
@@ -23996,16 +24064,16 @@
         <v>927</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" s="103" t="s">
+    <row r="78" spans="1:7">
+      <c r="A78" s="106" t="s">
         <v>941</v>
       </c>
-      <c r="B78" s="100"/>
-      <c r="C78" s="100"/>
-      <c r="D78" s="100"/>
-      <c r="E78" s="100"/>
-      <c r="F78" s="100"/>
-      <c r="G78" s="100"/>
+      <c r="B78" s="103"/>
+      <c r="C78" s="103"/>
+      <c r="D78" s="103"/>
+      <c r="E78" s="103"/>
+      <c r="F78" s="103"/>
+      <c r="G78" s="103"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/anciens_eleves.xlsx
+++ b/anciens_eleves.xlsx
@@ -12684,7 +12684,7 @@
         <v>925</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="39.950000000000003" customHeight="1">
+    <row r="2" spans="1:12" ht="99" customHeight="99">
       <c r="A2" s="3" t="s">
         <v>126</v>
       </c>
@@ -12703,8 +12703,10 @@
       <c r="F2" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>1177</v>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AgroParisTech est une grande école d’ingénieurs agronomes, membre de l’Université Paris-Saclay. Le cursus ingénieur dure 3 ans (statut étudiant, apprentissage possible, élèves fonctionnaires) et associe sciences du vivant, sciences de l’ingénieur et sciences humaines, économiques et sociales, avec des dominantes d’approfondissement.</t>
+        </is>
       </c>
       <c r="H2" s="3" t="s">
         <v>495</v>
@@ -12718,8 +12720,10 @@
       <c r="K2" s="3" t="s">
         <v>498</v>
       </c>
-      <c r="L2" s="3" t="s">
-        <v>1236</v>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Agronomie ; Sciences du vivant ; Sciences de l’ingénieur ; Sciences humaines, économiques et sociales ; Alimentation ; Environnement ; Dominantes d’approfondissement ; Apprentissage ; Élèves fonctionnaires ; Paris-Saclay</t>
+        </is>
       </c>
     </row>
     <row r="3" spans="1:12" ht="39.950000000000003" customHeight="1">
@@ -12760,7 +12764,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="39.950000000000003" customHeight="1">
+    <row r="4" spans="1:12" ht="99" customHeight="99">
       <c r="A4" s="3" t="s">
         <v>37</v>
       </c>
@@ -12779,8 +12783,10 @@
       <c r="F4" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>1178</v>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bordeaux Sciences Agro est une école publique d’ingénieurs agronomes, située à Gradignan près de Bordeaux. Le cursus ingénieur dure 3 ans (apprentissage possible) et s’appuie sur le vignoble voisin pour proposer des formations reconnues autour de la vigne et du vin, en plus de l’agronomie, de l’agroalimentaire et de l’agroécologie.</t>
+        </is>
       </c>
       <c r="H4" s="3" t="s">
         <v>503</v>
@@ -12794,8 +12800,10 @@
       <c r="K4" s="3" t="s">
         <v>506</v>
       </c>
-      <c r="L4" s="3" t="s">
-        <v>1237</v>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Agronomie ; Vigne et vin ; Agroalimentaire ; Agroécologie ; Agreenium ; Apprentissage ; Gradignan</t>
+        </is>
       </c>
     </row>
     <row r="5" spans="1:12" ht="39.950000000000003" customHeight="1">
@@ -12874,7 +12882,7 @@
         <v>921</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="39.950000000000003" customHeight="1">
+    <row r="7" spans="1:12" ht="114" customHeight="114">
       <c r="A7" s="3" t="s">
         <v>280</v>
       </c>
@@ -12893,8 +12901,10 @@
       <c r="F7" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>1179</v>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Le campus de Rennes de l’Institut Agro Rennes-Angers (ex-Agrocampus Ouest) propose les cursus d’ingénieur agronome et d’ingénieur agroalimentaire, avec des spécialisations comme l’agroécologie, l’agroéconomie et les politiques publiques ou le management des entreprises de l’alimentation. L’halieutique (sciences de la mer et du littoral) fait aussi partie de l’offre de formation.</t>
+        </is>
       </c>
       <c r="H7" s="3" t="s">
         <v>514</v>
@@ -12908,8 +12918,10 @@
       <c r="K7" s="3" t="s">
         <v>517</v>
       </c>
-      <c r="L7" s="3" t="s">
-        <v>1239</v>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Agronomie ; Agroalimentaire ; Halieutique ; Mer et littoral ; Agroécologie ; Agroéconomie ; Politiques publiques ; Management des entreprises ; Spécialisations</t>
+        </is>
       </c>
     </row>
     <row r="8" spans="1:12" ht="39.950000000000003" customHeight="1">
@@ -12988,7 +13000,7 @@
         <v>918</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="39.950000000000003" customHeight="1">
+    <row r="10" spans="1:12" ht="114" customHeight="114">
       <c r="A10" s="3" t="s">
         <v>99</v>
       </c>
@@ -13007,8 +13019,10 @@
       <c r="F10" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>1180</v>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L’Institut Agro Montpellier (ex-Montpellier SupAgro) forme des ingénieurs en agronomie, avec un cursus orienté vers l’agronomie et l’agroalimentaire durables, notamment pour les agricultures du Sud (méditerranéennes et tropicales). Il propose de nombreuses options en 3e année, un pôle fort sur la vigne et le vin, ainsi que des doubles diplômes avec des établissements partenaires.</t>
+        </is>
       </c>
       <c r="H10" s="3" t="s">
         <v>527</v>
@@ -13022,11 +13036,13 @@
       <c r="K10" s="3" t="s">
         <v>530</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>1240</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="39.950000000000003" customHeight="1">
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Agronomie ; Agroalimentaire ; Agricultures du Sud ; Méditerranée et tropiques ; Vigne et vin ; Systèmes agricoles durables ; Options de 3e année ; Double diplôme</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="99" customHeight="99">
       <c r="A11" s="3" t="s">
         <v>342</v>
       </c>
@@ -13045,8 +13061,10 @@
       <c r="F11" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="G11" s="3" t="s">
-        <v>1181</v>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L’École nationale vétérinaire d’Alfort, à Maisons-Alfort près de Paris, est l’une des quatre écoles vétérinaires publiques françaises. Elle forme des docteurs vétérinaires en 6 ans et dispose d’un centre hospitalier universitaire vétérinaire, ainsi que d’un site dédié aux équidés en Normandie (Goustranville).</t>
+        </is>
       </c>
       <c r="H11" s="3" t="s">
         <v>532</v>
@@ -13060,11 +13078,13 @@
       <c r="K11" s="3" t="s">
         <v>535</v>
       </c>
-      <c r="L11" s="3" t="s">
-        <v>1241</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="39.950000000000003" customHeight="1">
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Médecine vétérinaire ; Docteur vétérinaire ; Santé animale ; Centre hospitalier universitaire vétérinaire ; Équidés ; Animaux de compagnie ; Maisons-Alfort ; Campus équin Normandie</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="114" customHeight="114">
       <c r="A12" s="3" t="s">
         <v>367</v>
       </c>
@@ -13083,8 +13103,10 @@
       <c r="F12" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>1182</v>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L’École nationale vétérinaire de Toulouse, membre de l’Université de Toulouse, est l’une des quatre écoles vétérinaires publiques françaises. Elle forme des docteurs vétérinaires en 6 ans, avec un centre hospitalier universitaire vétérinaire (animaux de compagnie, équidés, animaux de production), des formations de spécialisation, un volet santé publique vétérinaire et un stage à l’étranger obligatoire.</t>
+        </is>
       </c>
       <c r="H12" s="3" t="s">
         <v>536</v>
@@ -13098,11 +13120,13 @@
       <c r="K12" s="3" t="s">
         <v>539</v>
       </c>
-      <c r="L12" s="3" t="s">
-        <v>1242</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" ht="39.950000000000003" customHeight="1">
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Médecine vétérinaire ; Docteur vétérinaire ; Centre hospitalier universitaire vétérinaire ; Animaux de compagnie ; Équidés ; Animaux de production ; Santé publique vétérinaire ; Spécialisation ; Stage à l’étranger</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="114" customHeight="114">
       <c r="A13" s="3" t="s">
         <v>141</v>
       </c>
@@ -13121,8 +13145,10 @@
       <c r="F13" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="G13" s="3" t="s">
-        <v>1183</v>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Le campus vétérinaire de VetAgro Sup se situe à Marcy-l’Étoile, près de Lyon. Il forme des docteurs vétérinaires et s’appuie sur trois centres hospitaliers universitaires vétérinaires (animaux de compagnie, équidés, animaux de production). VetAgro Sup est la seule structure française à former à la fois des vétérinaires, des ingénieurs agronomes et des inspecteurs de santé publique vétérinaire.</t>
+        </is>
       </c>
       <c r="H13" s="3" t="s">
         <v>540</v>
@@ -13136,11 +13162,13 @@
       <c r="K13" s="3" t="s">
         <v>542</v>
       </c>
-      <c r="L13" s="3" t="s">
-        <v>1243</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" ht="39.950000000000003" customHeight="1">
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Médecine vétérinaire ; Docteur vétérinaire ; Animaux de compagnie ; Équidés ; Animaux de production ; Centre hospitalier universitaire vétérinaire ; Inspecteur de santé publique vétérinaire ; Marcy-l’Étoile</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="99" customHeight="99">
       <c r="A14" s="3" t="s">
         <v>255</v>
       </c>
@@ -13159,8 +13187,10 @@
       <c r="F14" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>1184</v>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Le site vétérinaire d’Oniris VetAgroBio, à Nantes, forme des docteurs vétérinaires au sein de l’une des quatre écoles vétérinaires publiques françaises, avec une approche « One Health » qui relie santé animale, santé humaine et environnement. L’école propose aussi un cursus d’ingénieur dans le domaine de l’alimentation (voir ONIRIS Nantes).</t>
+        </is>
       </c>
       <c r="H14" s="3" t="s">
         <v>499</v>
@@ -13174,11 +13204,13 @@
       <c r="K14" s="3" t="s">
         <v>544</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>1244</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" ht="39.950000000000003" customHeight="1">
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Médecine vétérinaire ; Docteur vétérinaire ; One Health ; Santé animale ; Santé publique ; Alimentation ; Nantes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="114" customHeight="114">
       <c r="A15" s="3" t="s">
         <v>229</v>
       </c>
@@ -13194,8 +13226,10 @@
       <c r="F15" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="G15" s="3" t="s">
-        <v>1185</v>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L’ENGEES (École nationale du génie de l’eau et de l’environnement de Strasbourg) forme en 3 ans des ingénieurs (statut étudiant, apprenti ou fonctionnaire) aux métiers de l’eau et de l’environnement : eau potable, assainissement, ingénierie des cours d’eau et renaturation, gestion des déchets. Les diplômés travaillent notamment en bureaux d’études, en collectivités et dans les entreprises de l’eau.</t>
+        </is>
       </c>
       <c r="H15" s="3" t="s">
         <v>546</v>
@@ -13209,11 +13243,13 @@
       <c r="K15" s="3" t="s">
         <v>549</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>1245</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" ht="39.950000000000003" customHeight="1">
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eau potable ; Assainissement ; Cours d’eau ; Renaturation ; Gestion des déchets ; Environnement ; Bureaux d’études ; Collectivités ; Apprentissage ; Élèves fonctionnaires ; Strasbourg</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="130" customHeight="130">
       <c r="A16" s="3" t="s">
         <v>88</v>
       </c>
@@ -13226,8 +13262,10 @@
       <c r="F16" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="G16" s="3" t="s">
-        <v>1186</v>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Géodata Paris (ex ENSG-Géomatique) est une école d’ingénieurs spécialisée en géomatique et en sciences de l’information géographique, située à Champs-sur-Marne. Elle recrute les élèves de BCPST via le concours G2E, avec un statut civil ou fonctionnaire. Les enseignements portent sur les données géographiques, la cartographie, la télédétection et leurs applications (environnement, aménagement, agriculture…).</t>
+        </is>
       </c>
       <c r="H16" s="3" t="s">
         <v>495</v>
@@ -13241,11 +13279,13 @@
       <c r="K16" s="3" t="s">
         <v>552</v>
       </c>
-      <c r="L16" s="3" t="s">
-        <v>1246</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" ht="39.950000000000003" customHeight="1">
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Géomatique ; Information géographique ; Systèmes d’information géographique ; Télédétection ; Cartographie ; Données spatiales ; Environnement ; Aménagement du territoire ; Concours G2E ; Élèves fonctionnaires</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="114" customHeight="114">
       <c r="A17" s="3" t="s">
         <v>167</v>
       </c>
@@ -13264,8 +13304,10 @@
       <c r="F17" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="G17" s="3" t="s">
-        <v>1187</v>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L’ESIR (École supérieure d’ingénieurs de Rennes, Université de Rennes) propose les spécialités informatique, matériaux, systèmes numériques et réseaux (en apprentissage) et technologies de l’information pour la santé. Les élèves de BCPST peuvent y accéder via le concours Polytech BCPST, notamment pour les technologies de l’information pour la santé et les matériaux.</t>
+        </is>
       </c>
       <c r="H17" s="3" t="s">
         <v>514</v>
@@ -13279,11 +13321,13 @@
       <c r="K17" s="3" t="s">
         <v>556</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>1247</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" ht="39.950000000000003" customHeight="1">
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Informatique ; Matériaux ; Systèmes numériques et réseaux ; Technologies de l’information pour la santé ; Santé numérique ; Apprentissage ; Concours Polytech BCPST</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="130" customHeight="130">
       <c r="A18" s="3" t="s">
         <v>91</v>
       </c>
@@ -13302,8 +13346,10 @@
       <c r="F18" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>1188</v>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L’ISIFC (Institut supérieur d’ingénieurs de Franche-Comté), à Besançon, forme des ingénieurs en génie biomédical, avec une triple culture technique, médicale et réglementaire. En 3e année, les options sont la bio-ingénierie, la biomécanique et les microsystèmes, l’e-santé et la microrobotique pour la santé. Les élèves de BCPST y accèdent via le concours Polytech BCPST (13 places) ; 2 places sont ouvertes en TB.</t>
+        </is>
       </c>
       <c r="H18" s="3" t="s">
         <v>557</v>
@@ -13317,8 +13363,10 @@
       <c r="K18" s="3" t="s">
         <v>560</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>1248</v>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Génie biomédical ; Dispositifs médicaux ; Bio-ingénierie ; Biomécanique ; Microsystèmes ; E-santé ; Microrobotique pour la santé ; Réglementation ; Besançon ; Concours Polytech BCPST</t>
+        </is>
       </c>
     </row>
     <row r="19" spans="1:12" ht="39.950000000000003" customHeight="1">
@@ -13359,7 +13407,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="39.950000000000003" customHeight="1">
+    <row r="20" spans="1:12" ht="99" customHeight="99">
       <c r="A20" s="3" t="s">
         <v>144</v>
       </c>
@@ -13378,8 +13426,10 @@
       <c r="F20" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>1189</v>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Polytech Clermont est une école d’ingénieurs du réseau Polytech. Les élèves de BCPST, de PC et de TB peuvent y intégrer la spécialité Génie biologique, centrée sur les biotechnologies durables et les bioprocédés, avec des applications comme le diagnostic, les matériaux biosourcés, la bioénergie et le bioraffinage.</t>
+        </is>
       </c>
       <c r="H20" s="3" t="s">
         <v>518</v>
@@ -13393,11 +13443,13 @@
       <c r="K20" s="3" t="s">
         <v>567</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>1249</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" ht="39.950000000000003" customHeight="1">
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Génie biologique ; Biotechnologies durables ; Bioprocédés ; Matériaux biosourcés ; Bioénergie ; Bioraffinage ; Diagnostic ; Concours Polytech BCPST</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="99" customHeight="99">
       <c r="A21" s="3" t="s">
         <v>85</v>
       </c>
@@ -13416,8 +13468,10 @@
       <c r="F21" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>1190</v>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Polytech Tours est une école d’ingénieurs du réseau Polytech (Université de Tours). Les élèves de BCPST peuvent y intégrer la spécialité Génie de l’aménagement et de l’environnement via le concours Polytech BCPST, avec des enseignements liés à l’aménagement du territoire, à l’environnement et à la gestion de la ville et des réseaux.</t>
+        </is>
       </c>
       <c r="H21" s="3" t="s">
         <v>568</v>
@@ -13431,11 +13485,13 @@
       <c r="K21" s="3" t="s">
         <v>571</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" ht="39.950000000000003" customHeight="1">
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Génie de l’aménagement et de l’environnement ; Aménagement du territoire ; Environnement ; Ville ; Réseaux ; Concours Polytech BCPST ; Tours</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="130" customHeight="130">
       <c r="A22" s="3" t="s">
         <v>119</v>
       </c>
@@ -13454,8 +13510,10 @@
       <c r="F22" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>1191</v>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L’INSA Lyon est une grande école d’ingénieurs publique du groupe INSA, organisée en neuf départements : biosciences, génie civil et urbanisme, génie électrique, génie énergétique et environnement, génie industriel, génie mécanique, informatique, science et génie des matériaux et télécommunications. Les élèves de BCPST peuvent y accéder pour la spécialité biotechnologies et bioinformatique, via le recrutement commun du groupe INSA.</t>
+        </is>
       </c>
       <c r="H22" s="3" t="s">
         <v>540</v>
@@ -13469,11 +13527,13 @@
       <c r="K22" s="3" t="s">
         <v>575</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>1251</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" ht="39.950000000000003" customHeight="1">
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Biosciences ; Biotechnologies et bioinformatique ; Génie civil et urbanisme ; Génie énergétique et environnement ; Génie industriel ; Génie mécanique ; Génie électrique ; Informatique ; Matériaux ; Télécommunications ; Groupe INSA</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="114" customHeight="114">
       <c r="A23" s="3" t="s">
         <v>576</v>
       </c>
@@ -13492,8 +13552,10 @@
       <c r="F23" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="G23" s="3" t="s">
-        <v>1192</v>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L’INSA Rouen Normandie est une école d’ingénieurs publique du groupe INSA, installée à Saint-Étienne-du-Rouvray (avec une antenne au Havre). Elle propose notamment les spécialités génie civil et construction durable, énergétique et propulsion, mécanique, génie mathématique, architecture des systèmes d’information, ainsi que chimie et procédés et gestion des risques.</t>
+        </is>
       </c>
       <c r="H23" s="3" t="s">
         <v>577</v>
@@ -13507,11 +13569,13 @@
       <c r="K23" s="3" t="s">
         <v>580</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>1252</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" ht="39.950000000000003" customHeight="1">
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Génie civil ; Construction durable ; Énergétique et propulsion ; Mécanique ; Génie mathématique ; Architecture des systèmes d’information ; Chimie et procédés ; Gestion des risques ; Groupe INSA</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="130" customHeight="130">
       <c r="A24" s="3" t="s">
         <v>331</v>
       </c>
@@ -13530,8 +13594,10 @@
       <c r="F24" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>1193</v>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L’INSA Toulouse est une grande école d’ingénieurs publique du groupe INSA, avec huit spécialités : génie biologique, génie des procédés et environnement, génie civil, génie mécanique, génie physique, automatique et électronique, génie mathématique et modélisation, informatique et réseaux. Le génie biologique et le génie des procédés et environnement sont les plus proches des profils BCPST (biotechnologies, bioprocédés, environnement).</t>
+        </is>
       </c>
       <c r="H24" s="3" t="s">
         <v>536</v>
@@ -13545,11 +13611,13 @@
       <c r="K24" s="3" t="s">
         <v>583</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>1253</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" ht="39.950000000000003" customHeight="1">
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Génie biologique ; Génie des procédés et environnement ; Biologie des systèmes ; Génie civil ; Génie mécanique ; Génie physique ; Automatique-électronique ; Génie mathématique et modélisation ; Informatique et réseaux ; Groupe INSA</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="99" customHeight="99">
       <c r="A25" s="3" t="s">
         <v>584</v>
       </c>
@@ -13568,8 +13636,10 @@
       <c r="F25" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="G25" s="3" t="s">
-        <v>1194</v>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L’INSA Strasbourg est une école d’ingénieurs et d’architectes du groupe INSA. Elle propose sept spécialités d’ingénieur (génie civil, topographie, génie électrique, génie mécanique, plasturgie, mécatronique, génie climatique et énergétique) et délivre le diplôme d’architecte, ce qui en fait la seule école d’ingénieurs française à le faire.</t>
+        </is>
       </c>
       <c r="H25" s="3" t="s">
         <v>546</v>
@@ -13583,11 +13653,13 @@
       <c r="K25" s="3" t="s">
         <v>587</v>
       </c>
-      <c r="L25" s="3" t="s">
-        <v>1254</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" ht="39.950000000000003" customHeight="1">
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Génie civil ; Topographie ; Génie électrique ; Génie mécanique ; Plasturgie ; Mécatronique ; Génie climatique et énergétique ; Architecture ; Groupe INSA</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="130" customHeight="130">
       <c r="A26" s="3" t="s">
         <v>107</v>
       </c>
@@ -13606,8 +13678,10 @@
       <c r="F26" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="G26" s="3" t="s">
-        <v>1195</v>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ESITech est l’école d’ingénieurs de l’Université de Rouen Normandie (Saint-Étienne-du-Rouvray), liée au groupe INSA. Elle propose deux spécialités : génie biologique (en convention avec l’INSA Rouen, options bioproduction et biotechnologies et produits de santé) et génie physique et santé (dispositifs médicaux, imagerie, biomécanique…). Elle recrute après CPGE sur dossier et épreuves orales, ou via le recrutement commun du groupe INSA.</t>
+        </is>
       </c>
       <c r="H26" s="3" t="s">
         <v>588</v>
@@ -13621,11 +13695,13 @@
       <c r="K26" s="3" t="s">
         <v>591</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>1255</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" ht="39.950000000000003" customHeight="1">
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Génie biologique ; Bioproduction ; Biotechnologies et produits de santé ; Génie physique et santé ; Dispositifs médicaux ; Imagerie médicale ; Biomécanique ; Pharmacie ; Groupe INSA ; Rouen</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="99" customHeight="99">
       <c r="A27" s="3" t="s">
         <v>94</v>
       </c>
@@ -13644,8 +13720,10 @@
       <c r="F27" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>1196</v>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L’Université d’Orléans propose, notamment au sein de son Collegium Sciences et Techniques, des licences et masters scientifiques (sciences de la vie, sciences de la Terre, chimie, physique, mathématiques, informatique). Les étudiants issus de BCPST ou de TB peuvent candidater sur dossier pour poursuivre en licence ou en master.</t>
+        </is>
       </c>
       <c r="H27" s="3" t="s">
         <v>594</v>
@@ -13659,11 +13737,13 @@
       <c r="K27" s="3" t="s">
         <v>597</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>1256</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" ht="39.950000000000003" customHeight="1">
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sciences de la vie ; Sciences de la Terre ; Chimie ; Physique ; Licence ; Master ; Recherche ; Poursuite d’études sur dossier</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="114" customHeight="114">
       <c r="A28" s="3" t="s">
         <v>129</v>
       </c>
@@ -13682,8 +13762,10 @@
       <c r="F28" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="G28" s="3" t="s">
-        <v>1197</v>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Le Mans Université propose, au sein de sa faculté des sciences et techniques, des licences en sciences de la vie, sciences de la Terre, physique-chimie et acoustique et vibrations, ainsi que des masters en acoustique et en chimie. L’université est reconnue pour son pôle d’acoustique. Les étudiants issus de BCPST ou de TB peuvent candidater sur dossier.</t>
+        </is>
       </c>
       <c r="H28" s="3" t="s">
         <v>598</v>
@@ -13697,11 +13779,13 @@
       <c r="K28" s="3" t="s">
         <v>601</v>
       </c>
-      <c r="L28" s="3" t="s">
-        <v>1257</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" ht="39.950000000000003" customHeight="1">
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sciences de la vie ; Sciences de la Terre ; Physique-chimie ; Acoustique et vibrations ; Licence ; Master ; Recherche ; Poursuite d’études sur dossier</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="130" customHeight="130">
       <c r="A29" s="3" t="s">
         <v>319</v>
       </c>
@@ -13720,8 +13804,10 @@
       <c r="F29" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="G29" s="3" t="s">
-        <v>1198</v>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Polytech Nice Sophia, à Sophia Antipolis, est l’école d’ingénieurs de l’Université Côte d’Azur (réseau Polytech). Elle propose notamment le génie biologique (pharmacologie, toxicologie, bio-informatique ; santé, cosmétique, arômes et parfums, environnement) et le génie de l’eau (ressource en eau, inondations, eau potable, eaux usées et pluviales), ainsi que le bâtiment, l’électronique, l’informatique et les mathématiques appliquées.</t>
+        </is>
       </c>
       <c r="H29" s="3" t="s">
         <v>568</v>
@@ -13735,11 +13821,13 @@
       <c r="K29" s="5" t="s">
         <v>604</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>1258</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" ht="39.950000000000003" customHeight="1">
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Génie biologique ; Pharmacologie ; Toxicologie ; Bio-informatique ; Cosmétique ; Arômes et parfums ; Génie de l’eau ; Inondations ; Bâtiment ; Électronique ; Informatique ; Sophia Antipolis</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="114" customHeight="114">
       <c r="A30" s="3" t="s">
         <v>321</v>
       </c>
@@ -13758,8 +13846,10 @@
       <c r="F30" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="G30" s="3" t="s">
-        <v>1199</v>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L’EPISEN (École publique d’ingénieurs de la santé et du numérique), rattachée à l’Université Paris-Est Créteil, propose trois spécialités d’ingénieur à l’interface de la santé et du numérique : génie biomédical et santé, informatique et santé, systèmes d’information. Les élèves de BCPST peuvent y accéder via le concours Polytech BCPST, et l’apprentissage est possible.</t>
+        </is>
       </c>
       <c r="H30" s="6" t="s">
         <v>605</v>
@@ -13773,11 +13863,13 @@
       <c r="K30" s="3" t="s">
         <v>608</v>
       </c>
-      <c r="L30" s="3" t="s">
-        <v>1259</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" ht="39.950000000000003" customHeight="1">
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Santé numérique ; Génie biomédical et santé ; Informatique et santé ; Systèmes d’information ; Apprentissage ; Concours Polytech BCPST ; Créteil</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="130" customHeight="130">
       <c r="A31" s="6" t="s">
         <v>337</v>
       </c>
@@ -13796,8 +13888,10 @@
       <c r="F31" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="G31" s="100" t="s">
-        <v>1200</v>
+      <c r="G31" s="100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L’ESIAB (École supérieure d’ingénieurs en agroalimentaire de Bretagne atlantique), école interne de Bretagne INP et composante de l’Université de Bretagne Occidentale, propose deux spécialités d’ingénieur : agroalimentaire à Quimper (apprentissage possible) et microbiologie et sécurité sanitaire à Brest. Elle forme aux métiers de la production, de la qualité et de l’innovation dans l’industrie agroalimentaire.</t>
+        </is>
       </c>
       <c r="H31" s="6" t="s">
         <v>609</v>
@@ -13811,8 +13905,10 @@
       <c r="K31" s="3" t="s">
         <v>612</v>
       </c>
-      <c r="L31" s="3" t="s">
-        <v>1260</v>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Agroalimentaire ; Microbiologie ; Sécurité sanitaire ; Qualité ; Production ; Innovation ; Industrie agroalimentaire ; Apprentissage ; Quimper ; Brest</t>
+        </is>
       </c>
     </row>
     <row r="32" spans="1:12" ht="39.950000000000003" customHeight="1">
@@ -13853,7 +13949,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="39.950000000000003" customHeight="1">
+    <row r="33" spans="1:12" ht="99" customHeight="99">
       <c r="A33" s="6" t="s">
         <v>350</v>
       </c>
@@ -13872,8 +13968,10 @@
       <c r="F33" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="G33" s="100" t="s">
-        <v>1201</v>
+      <c r="G33" s="100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L’ENS Paris-Saclay (Gif-sur-Yvette) est une école normale supérieure pluridisciplinaire (sciences, ingénierie, sciences sociales). Elle recrute les élèves de BCPST et de TB via le concours ENS (15 places pour la voie BCPST), avec le statut d’élève fonctionnaire. La formation est tournée vers la recherche, jusqu’au master et au doctorat.</t>
+        </is>
       </c>
       <c r="H33" s="6" t="s">
         <v>495</v>
@@ -13887,11 +13985,13 @@
       <c r="K33" s="3" t="s">
         <v>620</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>1261</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" ht="39.950000000000003" customHeight="1">
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Recherche ; Interdisciplinarité ; Biologie ; Master ; Doctorat ; Concours ENS BCPST ; Élèves fonctionnaires ; Gif-sur-Yvette</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" spans="1:12" ht="130" customHeight="130">
       <c r="A34" s="3" t="s">
         <v>209</v>
       </c>
@@ -13910,8 +14010,10 @@
       <c r="F34" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="G34" s="3" t="s">
-        <v>1202</v>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AgroToulouse (Toulouse INP-ENSAT), à Castanet-Tolosan, forme en 3 ans des ingénieurs agronomes (apprentissage possible) dans les domaines de l’agriculture, de l’alimentation et de l’environnement, avec des spécialisations en 3e année (dont l’ingénierie agroalimentaire). L’école délivre aussi le diplôme national d’œnologue. L’admission se fait notamment via le concours Agro-Véto (94 places en BCPST, 8 en TB).</t>
+        </is>
       </c>
       <c r="H34" s="3" t="s">
         <v>536</v>
@@ -13925,11 +14027,13 @@
       <c r="K34" s="3" t="s">
         <v>623</v>
       </c>
-      <c r="L34" s="3" t="s">
-        <v>1262</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" ht="39.950000000000003" customHeight="1">
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Agronomie ; Agroalimentaire ; Environnement ; Œnologie ; Transition agroécologique ; Spécialisations de 3e année ; Apprentissage ; Agreenium ; Groupe INP ; Concours Agro-Véto</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" spans="1:12" ht="130" customHeight="130">
       <c r="A35" s="3" t="s">
         <v>403</v>
       </c>
@@ -13948,8 +14052,10 @@
       <c r="F35" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="G35" s="3" t="s">
-        <v>1203</v>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L’ESBS (École supérieure de biotechnologie de Strasbourg), à Illkirch-Graffenstaden, forme des ingénieurs en biotechnologie, avec des spécialisations en analyse haut-débit, biologie synthétique, et bioproduction et biomédicaments. Elle propose aussi, avec l’ECPM, le diplôme ChemBiotech (chimie et biotechnologie). Elle recrute les élèves de BCPST via le concours Polytech BCPST (8 places), 2 places étant ouvertes en TB.</t>
+        </is>
       </c>
       <c r="H35" s="3" t="s">
         <v>546</v>
@@ -13963,8 +14069,10 @@
       <c r="K35" s="3" t="s">
         <v>626</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>1263</v>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Biotechnologies ; Analyse haut-débit ; Biologie synthétique ; Bioproduction ; Biomédicaments ; ChemBiotech ; Industrie pharmaceutique ; Santé ; Concours Polytech BCPST ; Strasbourg</t>
+        </is>
       </c>
     </row>
     <row r="36" spans="1:12" ht="44.25" customHeight="1">
@@ -14005,7 +14113,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="37" spans="1:12" ht="72" customHeight="1">
+    <row r="37" spans="1:12" ht="99" customHeight="99">
       <c r="A37" s="3" t="s">
         <v>441</v>
       </c>
@@ -14024,8 +14132,10 @@
       <c r="F37" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="G37" s="3" t="s">
-        <v>1204</v>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Les universités toulousaines (notamment l’Université Toulouse III – Paul Sabatier) proposent des licences et masters scientifiques en sciences de la vie, sciences de la Terre, chimie, physique et mathématiques. Les étudiants issus de BCPST ou de TB peuvent candidater sur dossier pour poursuivre en licence ou en master.</t>
+        </is>
       </c>
       <c r="H37" s="3" t="s">
         <v>536</v>
@@ -14039,11 +14149,13 @@
       <c r="K37" s="5" t="s">
         <v>633</v>
       </c>
-      <c r="L37" s="3" t="s">
-        <v>1256</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" ht="29.25" customHeight="1">
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sciences de la vie ; Sciences de la Terre ; Chimie ; Physique ; Licence ; Master ; Recherche ; Poursuite d’études sur dossier</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" spans="1:12" ht="83" customHeight="83">
       <c r="A38" s="3" t="s">
         <v>444</v>
       </c>
@@ -14062,8 +14174,10 @@
       <c r="F38" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="G38" s="3" t="s">
-        <v>1205</v>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L’Université de Rennes propose des licences et masters scientifiques en sciences de la vie, sciences de la Terre et de l’environnement, chimie, physique et mathématiques. Les étudiants issus de BCPST ou de TB peuvent candidater sur dossier pour poursuivre en licence ou en master.</t>
+        </is>
       </c>
       <c r="H38" s="3" t="s">
         <v>514</v>
@@ -14077,11 +14191,13 @@
       <c r="K38" s="3" t="s">
         <v>636</v>
       </c>
-      <c r="L38" s="3" t="s">
-        <v>1264</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" ht="34.5" customHeight="1">
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sciences de la vie ; Sciences de la Terre ; Environnement ; Chimie ; Physique ; Licence ; Master ; Recherche ; Poursuite d’études sur dossier</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" spans="1:12" ht="99" customHeight="99">
       <c r="A39" s="3" t="s">
         <v>446</v>
       </c>
@@ -14100,8 +14216,10 @@
       <c r="F39" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="G39" s="3" t="s">
-        <v>1206</v>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L’UFR Sciences et Techniques de l’Université de Rouen Normandie (Mont-Saint-Aignan) propose des licences et masters scientifiques en sciences de la vie, chimie, physique, mathématiques et informatique. Les étudiants issus de BCPST ou de TB peuvent candidater sur dossier pour poursuivre en licence ou en master.</t>
+        </is>
       </c>
       <c r="H39" s="3" t="s">
         <v>577</v>
@@ -14115,11 +14233,13 @@
       <c r="K39" s="3" t="s">
         <v>638</v>
       </c>
-      <c r="L39" s="3" t="s">
-        <v>1265</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" ht="47.25" customHeight="1">
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sciences de la vie ; Chimie ; Physique ; Mathématiques ; Informatique ; Licence ; Master ; Recherche ; Poursuite d’études sur dossier</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" spans="1:12" ht="99" customHeight="99">
       <c r="A40" s="3" t="s">
         <v>448</v>
       </c>
@@ -14138,8 +14258,10 @@
       <c r="F40" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="G40" s="3" t="s">
-        <v>1207</v>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L’Université d’Évry Paris-Saclay est implantée au cœur du Genopole, biocluster français consacré à la génomique et aux biotechnologies. Elle propose des licences et masters scientifiques, notamment dans les sciences de la vie. Les étudiants issus de BCPST ou de TB peuvent candidater sur dossier.</t>
+        </is>
       </c>
       <c r="H40" s="3" t="s">
         <v>639</v>
@@ -14153,11 +14275,13 @@
       <c r="K40" s="3" t="s">
         <v>642</v>
       </c>
-      <c r="L40" s="3" t="s">
-        <v>1266</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" ht="49.5" customHeight="1">
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sciences de la vie ; Génomique ; Biotechnologies ; Genopole ; Licence ; Master ; Recherche ; Paris-Saclay ; Poursuite d’études sur dossier</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" spans="1:12" ht="99" customHeight="99">
       <c r="A41" s="3" t="s">
         <v>451</v>
       </c>
@@ -14176,8 +14300,10 @@
       <c r="F41" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="G41" s="3" t="s">
-        <v>1208</v>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">La faculté des sciences d’Orsay, composante de l’Université Paris-Saclay, propose des licences et masters scientifiques (sciences de la vie, chimie, physique, mathématiques), adossés à de nombreux laboratoires de recherche. Les étudiants issus de BCPST ou de TB peuvent candidater sur dossier pour poursuivre en licence ou en master.</t>
+        </is>
       </c>
       <c r="H41" s="3" t="s">
         <v>495</v>
@@ -14191,8 +14317,10 @@
       <c r="K41" s="3" t="s">
         <v>645</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>1267</v>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sciences de la vie ; Chimie ; Physique ; Mathématiques ; Licence ; Master ; Recherche ; Paris-Saclay ; Poursuite d’études sur dossier</t>
+        </is>
       </c>
     </row>
     <row r="42" spans="1:12" ht="72" customHeight="1">
@@ -14233,7 +14361,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="43" spans="1:12" ht="72" customHeight="1">
+    <row r="43" spans="1:12" ht="99" customHeight="99">
       <c r="A43" s="10" t="s">
         <v>473</v>
       </c>
@@ -14252,8 +14380,10 @@
       <c r="F43" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="G43" s="100" t="s">
-        <v>1209</v>
+      <c r="G43" s="100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L’ENS de Lyon est une école normale supérieure scientifique et littéraire. Elle recrute les élèves de BCPST via le concours ENS (environ 33 places, statut d’élève fonctionnaire). La formation est tournée vers la recherche (master, doctorat), avec un double cursus ingénieur-chercheur possible avec Centrale Lyon.</t>
+        </is>
       </c>
       <c r="H43" s="10" t="s">
         <v>540</v>
@@ -14267,11 +14397,13 @@
       <c r="K43" s="5" t="s">
         <v>652</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>1268</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" ht="72" customHeight="1">
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Recherche ; Biologie ; Master ; Doctorat ; Double diplôme ; Ingénieur-chercheur ; Concours ENS BCPST ; Élèves fonctionnaires ; Lyon</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" spans="1:12" ht="114" customHeight="114">
       <c r="A44" s="10" t="s">
         <v>653</v>
       </c>
@@ -14290,8 +14422,10 @@
       <c r="F44" s="10" t="s">
         <v>494</v>
       </c>
-      <c r="G44" s="100" t="s">
-        <v>1210</v>
+      <c r="G44" s="100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L’École normale supérieure – PSL (rue d’Ulm, Paris) est une école normale supérieure pluridisciplinaire (sciences, lettres, sciences humaines) adossée à l’Université PSL. Elle recrute les élèves de BCPST via le concours ENS (environ 21 places, statut d’élève fonctionnaire). La formation est tournée vers la recherche, jusqu’au master et au doctorat.</t>
+        </is>
       </c>
       <c r="H44" s="10" t="s">
         <v>495</v>
@@ -14305,11 +14439,13 @@
       <c r="K44" s="5" t="s">
         <v>656</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>1269</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" ht="72" customHeight="1">
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Recherche ; Interdisciplinarité ; Biologie ; Master ; Doctorat ; Concours ENS BCPST ; Élèves fonctionnaires ; PSL ; Paris</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" spans="1:12" ht="99" customHeight="99">
       <c r="A45" s="14" t="s">
         <v>657</v>
       </c>
@@ -14324,8 +14460,10 @@
       <c r="F45" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>1211</v>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CentraleSupélec est une grande école d’ingénieurs généraliste du Groupe des écoles Centrale, sur le plateau de Paris-Saclay, avec des domaines forts en numérique et en énergie. Les élèves de BCPST peuvent y accéder via le concours Agro-Véto, pour un nombre limité de places (campus de Metz).</t>
+        </is>
       </c>
       <c r="H45" s="15" t="s">
         <v>495</v>
@@ -14339,11 +14477,13 @@
       <c r="K45" s="3" t="s">
         <v>661</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>1270</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" ht="72" customHeight="1">
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ingénierie généraliste ; Numérique ; Énergie ; Paris-Saclay ; Campus de Metz ; Concours Agro-Véto ; Groupe Centrale</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" spans="1:12" ht="114" customHeight="114">
       <c r="A46" s="12" t="s">
         <v>662</v>
       </c>
@@ -14362,8 +14502,10 @@
       <c r="F46" s="10" t="s">
         <v>494</v>
       </c>
-      <c r="G46" s="100" t="s">
-        <v>1212</v>
+      <c r="G46" s="100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L’École nationale supérieure de paysage (ENSP), à Versailles et Marseille, délivre le diplôme d’État de paysagiste (DEP), qui confère le grade de master. Le cycle dure 3 ans (apprentissage possible dès la 2e année) et mène au métier de paysagiste concepteur ; une admission en 2e année est possible sur titre avec un bac+3 (dossier et épreuves orales).</t>
+        </is>
       </c>
       <c r="H46" s="10" t="s">
         <v>663</v>
@@ -14377,11 +14519,13 @@
       <c r="K46" s="3" t="s">
         <v>666</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>1271</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" ht="72" customHeight="1">
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paysage ; Paysagiste concepteur ; Projet de paysage ; Diplôme d’État de paysagiste ; Grade de master ; Apprentissage ; Admission sur titre ; Versailles ; Marseille</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" spans="1:12" ht="83" customHeight="83">
       <c r="A47" s="12" t="s">
         <v>667</v>
       </c>
@@ -14396,8 +14540,10 @@
       <c r="F47" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>1213</v>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IMT Mines Albi (Albi-Carmaux) est une école d’ingénieurs généraliste de l’Institut Mines-Télécom, avec des domaines forts en génie des procédés, énergie et matériaux. Elle recrute les élèves de BCPST via le concours G2E (7 places en 2026).</t>
+        </is>
       </c>
       <c r="H47" s="10" t="s">
         <v>668</v>
@@ -14411,11 +14557,13 @@
       <c r="K47" s="3" t="s">
         <v>671</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>1272</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" ht="72" customHeight="1">
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ingénierie généraliste ; Génie des procédés ; Énergie ; Matériaux ; Transitions ; Concours G2E ; Institut Mines-Télécom ; Albi</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" spans="1:12" ht="68" customHeight="68">
       <c r="A48" s="12" t="s">
         <v>672</v>
       </c>
@@ -14430,8 +14578,10 @@
       <c r="F48" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="G48" s="3" t="s">
-        <v>1214</v>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IMT Mines Alès est une école d’ingénieurs généraliste de l’Institut Mines-Télécom, avec des domaines forts en risques, environnement et génie civil. Elle recrute les élèves de BCPST via le concours G2E (6 places en 2026).</t>
+        </is>
       </c>
       <c r="H48" s="10" t="s">
         <v>673</v>
@@ -14445,11 +14595,13 @@
       <c r="K48" s="3" t="s">
         <v>676</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>1273</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" ht="72" customHeight="1">
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ingénierie généraliste ; Risques ; Environnement ; Génie civil ; Concours G2E ; Institut Mines-Télécom ; Alès</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" spans="1:12" ht="83" customHeight="83">
       <c r="A49" s="12" t="s">
         <v>677</v>
       </c>
@@ -14464,8 +14616,10 @@
       <c r="F49" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="G49" s="3" t="s">
-        <v>1215</v>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IMT Nord Europe est une école d’ingénieurs de l’Institut Mines-Télécom, implantée à Douai et à Lille, avec des domaines forts en énergie, environnement et numérique. Elle recrute les élèves de BCPST via le concours G2E (4 places en 2026).</t>
+        </is>
       </c>
       <c r="H49" s="10" t="s">
         <v>678</v>
@@ -14479,11 +14633,13 @@
       <c r="K49" s="3" t="s">
         <v>681</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>1274</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12" ht="51" customHeight="1">
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ingénierie généraliste ; Énergie ; Environnement ; Numérique ; Concours G2E ; Institut Mines-Télécom ; Douai ; Lille</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" spans="1:12" ht="99" customHeight="99">
       <c r="A50" s="12" t="s">
         <v>682</v>
       </c>
@@ -14502,8 +14658,10 @@
       <c r="F50" s="10" t="s">
         <v>494</v>
       </c>
-      <c r="G50" s="3" t="s">
-        <v>1216</v>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Polytech Annecy-Chambéry, école d’ingénieurs de l’Université Savoie Mont Blanc (réseau Polytech), propose cinq spécialités d’ingénieur, dont la spécialité Bâtiment (Bâtiment – Écoconstruction – Énergie) et la mécanique. Les études comprennent environ 39 semaines de stage sur l’ensemble du cursus.</t>
+        </is>
       </c>
       <c r="H50" s="12" t="s">
         <v>683</v>
@@ -14517,11 +14675,13 @@
       <c r="K50" s="3" t="s">
         <v>686</v>
       </c>
-      <c r="L50" s="3" t="s">
-        <v>1275</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12" ht="72" customHeight="1">
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bâtiment ; Écoconstruction ; Énergie ; Environnement ; Mécanique ; Stages ; Annecy ; Chambéry</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" spans="1:12" ht="114" customHeight="114">
       <c r="A51" s="12" t="s">
         <v>687</v>
       </c>
@@ -14540,8 +14700,10 @@
       <c r="F51" s="12" t="s">
         <v>494</v>
       </c>
-      <c r="G51" s="3" t="s">
-        <v>1217</v>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Polytech Sorbonne est l’école d’ingénieurs de Sorbonne Université (réseau Polytech), à Paris. Elle propose notamment les spécialités agroalimentaire, matériaux et sciences de la Terre (aménagement, risques, géo-énergies), accessibles aux élèves de BCPST via le concours Polytech BCPST, ainsi que l’électronique et informatique, la robotique, les mathématiques appliquées et le génie mécanique.</t>
+        </is>
       </c>
       <c r="H51" s="12" t="s">
         <v>495</v>
@@ -14555,11 +14717,13 @@
       <c r="K51" s="3" t="s">
         <v>690</v>
       </c>
-      <c r="L51" s="3" t="s">
-        <v>1276</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12" ht="72" customHeight="1">
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Agroalimentaire ; Matériaux ; Sciences de la Terre ; Aménagement ; Risques ; Géo-énergies ; Robotique ; Électronique et informatique ; Concours Polytech BCPST ; Paris</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" spans="1:12" ht="161" customHeight="161">
       <c r="A52" s="12" t="s">
         <v>691</v>
       </c>
@@ -14578,8 +14742,10 @@
       <c r="F52" s="12" t="s">
         <v>494</v>
       </c>
-      <c r="G52" s="3" t="s">
-        <v>1218</v>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Polytech Orléans est l’école d’ingénieurs de l’Université d’Orléans (réseau Polytech). Elle propose notamment les spécialités génie civil et environnement (parcours constructions durables, géo-environnement et villes durables, travaux publics et aménagement), énergétique, génie physique et systèmes embarqués, matériaux et mécatronique, et génie industriel (site de Chartres). Pour les élèves de BCPST, le concours Polytech BCPST ouvre notamment le génie civil et géo-environnement et le génie industriel pour la cosmétique, la pharmacie et l’agroalimentaire.</t>
+        </is>
       </c>
       <c r="H52" s="12" t="s">
         <v>594</v>
@@ -14593,11 +14759,13 @@
       <c r="K52" s="3" t="s">
         <v>694</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>1277</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12" ht="57.6" customHeight="1">
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Génie civil et environnement ; Constructions durables ; Géo-environnement ; Villes durables ; Travaux publics ; Énergétique ; Matériaux et mécatronique ; Génie industriel ; Cosmétique ; Pharmacie ; Agroalimentaire ; Concours Polytech BCPST</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" spans="1:12" ht="99" customHeight="99">
       <c r="A53" s="12" t="s">
         <v>695</v>
       </c>
@@ -14612,8 +14780,10 @@
       <c r="F53" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="G53" s="100" t="s">
-        <v>1219</v>
+      <c r="G53" s="100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L’ENTPE (École nationale des travaux publics de l’État), à Vaulx-en-Velin près de Lyon, se présente comme l’école de l’aménagement durable des territoires : génie civil, bâtiment, transports, énergie et environnement. Elle recrute les élèves de BCPST via le concours G2E, avec un statut civil ou fonctionnaire.</t>
+        </is>
       </c>
       <c r="H53" s="10" t="s">
         <v>540</v>
@@ -14627,11 +14797,13 @@
       <c r="K53" s="3" t="s">
         <v>698</v>
       </c>
-      <c r="L53" s="3" t="s">
-        <v>1278</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" ht="57.6" customHeight="1">
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aménagement durable des territoires ; Génie civil ; Bâtiment ; Transports ; Énergie ; Environnement ; Concours G2E ; Élèves fonctionnaires ; Vaulx-en-Velin</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" spans="1:12" ht="99" customHeight="99">
       <c r="A54" s="12" t="s">
         <v>699</v>
       </c>
@@ -14646,8 +14818,10 @@
       <c r="F54" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="G54" s="100" t="s">
-        <v>1220</v>
+      <c r="G54" s="100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L’EIVP (École des ingénieurs de la Ville de Paris) forme des ingénieurs en génie urbain : conception et gestion de la ville, infrastructures, eau, génie civil. Elle recrute les élèves de BCPST via le concours G2E (statut civil ou fonctionnaire) et débouche notamment sur des carrières dans les collectivités et les bureaux d’études.</t>
+        </is>
       </c>
       <c r="H54" s="10" t="s">
         <v>495</v>
@@ -14661,11 +14835,13 @@
       <c r="K54" s="3" t="s">
         <v>702</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>1279</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12" ht="72" customHeight="1">
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Génie urbain ; Ville ; Infrastructures ; Eau ; Génie civil ; Collectivités ; Bureaux d’études ; Concours G2E ; Paris</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" spans="1:12" ht="130" customHeight="130">
       <c r="A55" s="12" t="s">
         <v>703</v>
       </c>
@@ -14680,8 +14856,10 @@
       <c r="F55" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="G55" s="3" t="s">
-        <v>1221</v>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L’EOST (École et observatoire des sciences de la Terre), à Strasbourg, est la seule école d’ingénieurs géophysiciens de France. Elle recrute les élèves de BCPST via le concours G2E (13 places en 2026). Les parcours de 3e année comprennent notamment la géophysique appliquée à la géotechnique, à l’eau et à l’environnement, et les géosciences pour la transition énergétique ; les débouchés vont de l’exploration-production à la géotechnique.</t>
+        </is>
       </c>
       <c r="H55" s="10" t="s">
         <v>546</v>
@@ -14695,11 +14873,13 @@
       <c r="K55" s="3" t="s">
         <v>706</v>
       </c>
-      <c r="L55" s="3" t="s">
-        <v>1280</v>
-      </c>
-    </row>
-    <row r="56" spans="1:12" ht="72" customHeight="1">
+      <c r="L55" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Géophysique ; Sciences de la Terre ; Géotechnique ; Eau ; Environnement ; Transition énergétique ; Exploration-production ; Risques naturels ; Concours G2E ; Strasbourg</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" spans="1:12" ht="145" customHeight="145">
       <c r="A56" s="12" t="s">
         <v>250</v>
       </c>
@@ -14714,8 +14894,10 @@
       <c r="F56" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="G56" s="3" t="s">
-        <v>1222</v>
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L’ENSG (École nationale supérieure de géologie), à Vandœuvre-lès-Nancy, est une école d’ingénieurs de l’Université de Lorraine créée en 1908, spécialisée en géosciences. Les parcours de 2e année couvrent les eaux et l’environnement, la géologie des énergies, la géologie numérique et les sciences des données, la géotechnique-génie civil, les matières premières minérales, et les réservoirs et stockages d’énergie. Elle recrute les élèves de BCPST via le concours G2E.</t>
+        </is>
       </c>
       <c r="H56" s="12" t="s">
         <v>507</v>
@@ -14729,11 +14911,13 @@
       <c r="K56" s="3" t="s">
         <v>709</v>
       </c>
-      <c r="L56" s="3" t="s">
-        <v>1281</v>
-      </c>
-    </row>
-    <row r="57" spans="1:12" ht="72" customHeight="1">
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Géologie ; Eaux et environnement ; Géologie des énergies ; Géologie numérique ; Sciences des données ; Géotechnique ; Matières premières minérales ; Stockage d’énergie ; Concours G2E ; Nancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" spans="1:12" ht="68" customHeight="68">
       <c r="A57" s="12" t="s">
         <v>710</v>
       </c>
@@ -14748,8 +14932,10 @@
       <c r="F57" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="G57" s="3" t="s">
-        <v>1223</v>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L’École polytechnique (Palaiseau) est une grande école d’ingénieurs pluridisciplinaire à très forte dimension scientifique. Les élèves de BCPST peuvent l’intégrer via le concours X-BIO (13 places).</t>
+        </is>
       </c>
       <c r="H57" s="10" t="s">
         <v>712</v>
@@ -14763,11 +14949,13 @@
       <c r="K57" s="3" t="s">
         <v>715</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>1282</v>
-      </c>
-    </row>
-    <row r="58" spans="1:12" ht="86.45" customHeight="1">
+      <c r="L57" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ingénierie généraliste ; Sciences fondamentales ; Biologie ; Recherche ; Concours X-BIO ; Palaiseau</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" spans="1:12" ht="130" customHeight="130">
       <c r="A58" s="12" t="s">
         <v>716</v>
       </c>
@@ -14782,8 +14970,10 @@
       <c r="F58" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="G58" s="3" t="s">
-        <v>1224</v>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Centrale Lyon, à Écully, est une école d’ingénieurs généraliste du Groupe Centrale, orientée vers l’industrie. Elle propose de nombreux doubles diplômes : ingénieur-chercheur avec l’ENS de Lyon, ingénieur-médecin, ingénieur-manager (emlyon), architecte-ingénieur (ENSAL), ingénieur-économètre (ENSAE). Elle ouvre des places aux élèves de BCPST via la banque ENS-Ponts-Mines Paris-Écoles Centrale (environ 5 places).</t>
+        </is>
       </c>
       <c r="H58" s="12" t="s">
         <v>718</v>
@@ -14797,11 +14987,13 @@
       <c r="K58" s="5" t="s">
         <v>721</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>1283</v>
-      </c>
-    </row>
-    <row r="59" spans="1:12" ht="72" customHeight="1">
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ingénierie généraliste ; Industrie ; Double diplôme ; Ingénieur-chercheur ; Ingénieur-médecin ; Ingénieur-manager ; Architecte-ingénieur ; Concours BCPST ; Écully</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" spans="1:12" ht="130" customHeight="130">
       <c r="A59" s="12" t="s">
         <v>722</v>
       </c>
@@ -14816,8 +15008,10 @@
       <c r="F59" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="G59" s="100" t="s">
-        <v>1225</v>
+      <c r="G59" s="100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Centrale Nantes est une école d’ingénieurs généraliste du Groupe Centrale, orientée vers l’industrie et le domaine maritime. Elle propose des doubles diplômes (ingénieur-architecte avec l’ENSA Nantes, ingénieur-manager avec Audencia, ingénieur-pharmacien avec Nantes Université) et l’apprentissage. Elle ouvre des places aux élèves de BCPST via la banque ENS-Ponts-Mines Paris-Écoles Centrale (environ 5 places).</t>
+        </is>
       </c>
       <c r="H59" s="10" t="s">
         <v>499</v>
@@ -14831,11 +15025,13 @@
       <c r="K59" s="3" t="s">
         <v>725</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>1284</v>
-      </c>
-    </row>
-    <row r="60" spans="1:12" ht="72" customHeight="1">
+      <c r="L59" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ingénierie généraliste ; Industrie ; Maritime ; Double diplôme ; Ingénieur-architecte ; Ingénieur-pharmacien ; Apprentissage ; Concours BCPST ; Nantes</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" spans="1:12" ht="83" customHeight="83">
       <c r="A60" s="12" t="s">
         <v>726</v>
       </c>
@@ -14850,8 +15046,10 @@
       <c r="F60" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="G60" s="3" t="s">
-        <v>1226</v>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Centrale Méditerranée, à Marseille, est une école d’ingénieurs généraliste du Groupe Centrale, orientée vers l’industrie. Elle ouvre des places aux élèves de BCPST via la banque ENS-Ponts-Mines Paris-Écoles Centrale (environ 5 places).</t>
+        </is>
       </c>
       <c r="H60" s="10" t="s">
         <v>646</v>
@@ -14865,11 +15063,13 @@
       <c r="K60" s="3" t="s">
         <v>729</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>1285</v>
-      </c>
-    </row>
-    <row r="61" spans="1:12" ht="72" customHeight="1">
+      <c r="L60" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ingénierie généraliste ; Industrie ; Concours BCPST ; Marseille ; Groupe Centrale</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" spans="1:12" ht="68" customHeight="68">
       <c r="A61" s="3" t="s">
         <v>730</v>
       </c>
@@ -14884,8 +15084,10 @@
       <c r="F61" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="G61" s="3" t="s">
-        <v>1227</v>
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mines Paris – PSL est une grande école d’ingénieurs généraliste, qui forme les ingénieurs civils des Mines. Les élèves de BCPST peuvent l’intégrer via la banque ENS-Ponts-Mines Paris-Écoles Centrale (environ 4 places).</t>
+        </is>
       </c>
       <c r="H61" s="10" t="s">
         <v>495</v>
@@ -14899,11 +15101,13 @@
       <c r="K61" s="3" t="s">
         <v>734</v>
       </c>
-      <c r="L61" s="3" t="s">
-        <v>1286</v>
-      </c>
-    </row>
-    <row r="62" spans="1:12" ht="72" customHeight="1">
+      <c r="L61" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ingénierie généraliste ; Ingénieur civil des Mines ; PSL ; Concours BCPST ; Paris</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" spans="1:12" ht="99" customHeight="99">
       <c r="A62" s="10" t="s">
         <v>735</v>
       </c>
@@ -14918,8 +15122,10 @@
       <c r="F62" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="G62" s="3" t="s">
-        <v>1228</v>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L’École des Ponts ParisTech (École nationale des ponts et chaussées), à Champs-sur-Marne, forme des ingénieurs généralistes (génie civil, ville, transports, environnement, ingénierie mathématique et informatique, génie industriel). Les élèves de BCPST peuvent l’intégrer via la banque ENS-Ponts-Mines Paris-Écoles Centrale (environ 4 places).</t>
+        </is>
       </c>
       <c r="H62" s="12" t="s">
         <v>736</v>
@@ -14933,11 +15139,13 @@
       <c r="K62" s="3" t="s">
         <v>739</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>1287</v>
-      </c>
-    </row>
-    <row r="63" spans="1:12" ht="48" customHeight="1">
+      <c r="L62" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Génie civil ; Ville ; Transports ; Environnement ; Ingénierie mathématique ; Génie industriel ; Ingénierie généraliste ; Concours BCPST ; Champs-sur-Marne</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" spans="1:12" ht="114" customHeight="114">
       <c r="A63" s="17" t="s">
         <v>740</v>
       </c>
@@ -14950,8 +15158,10 @@
       <c r="F63" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="G63" s="100" t="s">
-        <v>1229</v>
+      <c r="G63" s="100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bordeaux INP est un réseau de grandes écoles d’ingénieurs. Les élèves de BCPST s’orientent notamment vers l’ENSTBB (biotechnologie), l’ENSMAC (ex-ENSCBP : agroalimentaire-génie biologique, chimie-génie physique, accessible via le concours PC BIO) ou l’ENSEGID (géoressources, environnement et ingénierie du développement durable, accessible via le concours G2E).</t>
+        </is>
       </c>
       <c r="H63" s="18" t="s">
         <v>503</v>
@@ -14965,11 +15175,13 @@
       <c r="K63" s="5" t="s">
         <v>744</v>
       </c>
-      <c r="L63" s="3" t="s">
-        <v>1288</v>
-      </c>
-    </row>
-    <row r="64" spans="1:12" ht="42" customHeight="1">
+      <c r="L63" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Réseau d’écoles ; Biotechnologie ; Agroalimentaire ; Génie biologique ; Chimie ; Génie physique ; Géoressources ; Hydrogéologie ; Environnement ; Concours PC BIO ; Concours G2E</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" spans="1:12" ht="68" customHeight="68">
       <c r="A64" s="18" t="s">
         <v>745</v>
       </c>
@@ -14982,8 +15194,10 @@
       <c r="F64" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="G64" s="100" t="s">
-        <v>1230</v>
+      <c r="G64" s="100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chimie ParisTech – PSL (École nationale supérieure de chimie de Paris) est une école d’ingénieurs spécialisée en chimie. Les élèves de BCPST peuvent l’intégrer via le concours PC BIO, qui ouvre un petit nombre de places.</t>
+        </is>
       </c>
       <c r="H64" s="18" t="s">
         <v>495</v>
@@ -14997,11 +15211,13 @@
       <c r="K64" s="3" t="s">
         <v>748</v>
       </c>
-      <c r="L64" s="3" t="s">
-        <v>1289</v>
-      </c>
-    </row>
-    <row r="65" spans="1:13" ht="45" customHeight="1">
+      <c r="L64" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chimie ; Ingénierie chimique ; Concours PC BIO ; PSL ; Paris</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" spans="1:13" ht="83" customHeight="83">
       <c r="A65" s="18" t="s">
         <v>749</v>
       </c>
@@ -15014,8 +15230,10 @@
       <c r="F65" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="G65" s="101" t="s">
-        <v>1231</v>
+      <c r="G65" s="101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L’ENSC Lille (École nationale supérieure de chimie de Lille), école d’ingénieurs spécialisée en chimie, fait partie de Centrale Lille Institut. Les élèves de BCPST peuvent l’intégrer via le concours PC BIO, qui ouvre un petit nombre de places.</t>
+        </is>
       </c>
       <c r="H65" s="18" t="s">
         <v>613</v>
@@ -15029,11 +15247,13 @@
       <c r="K65" s="3" t="s">
         <v>752</v>
       </c>
-      <c r="L65" s="3" t="s">
-        <v>1290</v>
-      </c>
-    </row>
-    <row r="66" spans="1:13" ht="72" customHeight="1">
+      <c r="L65" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chimie ; Ingénierie chimique ; Concours PC BIO ; Centrale Lille Institut ; Lille</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" spans="1:13" ht="68" customHeight="68">
       <c r="A66" s="18" t="s">
         <v>753</v>
       </c>
@@ -15046,8 +15266,10 @@
       <c r="F66" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="G66" s="101" t="s">
-        <v>1232</v>
+      <c r="G66" s="101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L’ENSCM (École nationale supérieure de chimie de Montpellier) est une école d’ingénieurs spécialisée en chimie. Les élèves de BCPST peuvent l’intégrer via le concours PC BIO, qui ouvre un petit nombre de places.</t>
+        </is>
       </c>
       <c r="H66" s="18" t="s">
         <v>527</v>
@@ -15061,11 +15283,13 @@
       <c r="K66" s="5" t="s">
         <v>756</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>1291</v>
-      </c>
-    </row>
-    <row r="67" spans="1:13" ht="72" customHeight="1">
+      <c r="L66" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chimie ; Ingénierie chimique ; Concours PC BIO ; Montpellier</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" spans="1:13" ht="83" customHeight="83">
       <c r="A67" s="18" t="s">
         <v>757</v>
       </c>
@@ -15078,8 +15302,10 @@
       <c r="F67" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="G67" s="101" t="s">
-        <v>1233</v>
+      <c r="G67" s="101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L’ESPCI Paris – PSL est une école d’ingénieurs scientifique, qui allie physique, chimie et biologie avec une forte orientation recherche. Les élèves de BCPST peuvent l’intégrer via le concours PC BIO, qui ouvre un petit nombre de places.</t>
+        </is>
       </c>
       <c r="H67" s="18" t="s">
         <v>495</v>
@@ -15093,11 +15319,13 @@
       <c r="K67" s="3" t="s">
         <v>760</v>
       </c>
-      <c r="L67" s="3" t="s">
-        <v>1292</v>
-      </c>
-    </row>
-    <row r="68" spans="1:13" ht="72" customHeight="1">
+      <c r="L67" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Physique ; Chimie ; Biologie ; Recherche ; Interdisciplinarité ; Concours PC BIO ; PSL ; Paris</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" spans="1:13" ht="83" customHeight="83">
       <c r="A68" s="18" t="s">
         <v>761</v>
       </c>
@@ -15110,8 +15338,10 @@
       <c r="F68" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="G68" s="101" t="s">
-        <v>1234</v>
+      <c r="G68" s="101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L’ENSIC (École nationale supérieure des industries chimiques), à Nancy, est une école d’ingénieurs de Lorraine INP spécialisée dans le génie des procédés et la chimie. Les élèves de BCPST peuvent l’intégrer via le concours PC BIO, qui ouvre un petit nombre de places.</t>
+        </is>
       </c>
       <c r="H68" s="18" t="s">
         <v>762</v>
@@ -15125,11 +15355,13 @@
       <c r="K68" s="3" t="s">
         <v>765</v>
       </c>
-      <c r="L68" s="3" t="s">
-        <v>1293</v>
-      </c>
-    </row>
-    <row r="69" spans="1:13" ht="409.6" customHeight="1">
+      <c r="L68" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Génie des procédés ; Chimie ; Industries chimiques ; Concours PC BIO ; Lorraine INP ; Nancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" spans="1:13" ht="130" customHeight="130">
       <c r="A69" s="28" t="s">
         <v>194</v>
       </c>
@@ -15148,8 +15380,10 @@
       <c r="F69" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="G69" s="3" t="s">
-        <v>1235</v>
+      <c r="G69" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Polytech Nantes est l’école d’ingénieurs de Nantes Université (réseau Polytech), avec des campus à Nantes, Saint-Nazaire et La Roche-sur-Yon. Les élèves de BCPST peuvent y intégrer la spécialité Génie des procédés et bioprocédés (site de Saint-Nazaire, 3 places via le concours Polytech BCPST), avec des options en 3e année : bio-industries, industries chimiques et écotechnologies, management de la qualité, de la sécurité et de l’environnement.</t>
+        </is>
       </c>
       <c r="H69" s="28" t="s">
         <v>499</v>
@@ -15163,8 +15397,10 @@
       <c r="K69" s="3" t="s">
         <v>768</v>
       </c>
-      <c r="L69" s="3" t="s">
-        <v>1294</v>
+      <c r="L69" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Génie des procédés et bioprocédés ; Biotechnologies ; Bio-industries ; Industries chimiques ; Écotechnologies ; Environnement ; Qualité-sécurité-environnement ; Concours Polytech BCPST ; Saint-Nazaire</t>
+        </is>
       </c>
     </row>
     <row r="70" spans="1:13" ht="409.6" customHeight="1">

--- a/anciens_eleves.xlsx
+++ b/anciens_eleves.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bruno\Nextcloud2\Boulot 2026\Site orientation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bruno\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FAE1FAD-F20F-4ADF-AA78-B423738FB848}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7A715BC-7232-4F42-ACD3-D417EFB0B855}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Elèves_BCPST" sheetId="1" r:id="rId1"/>
@@ -22,11 +22,22 @@
     <sheet name="Stats" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3176" uniqueCount="1308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3297" uniqueCount="1351">
   <si>
     <t>Statistiques 2025</t>
   </si>
@@ -3957,6 +3968,135 @@
   </si>
   <si>
     <t xml:space="preserve">VALLERIE </t>
+  </si>
+  <si>
+    <t>BUT</t>
+  </si>
+  <si>
+    <t>Hors carte</t>
+  </si>
+  <si>
+    <t>Faculté (non précisée)</t>
+  </si>
+  <si>
+    <t>Sans nouvelles</t>
+  </si>
+  <si>
+    <t>ALVES</t>
+  </si>
+  <si>
+    <t>Mariana</t>
+  </si>
+  <si>
+    <t>BLIN</t>
+  </si>
+  <si>
+    <t>BRELET</t>
+  </si>
+  <si>
+    <t>Léanne</t>
+  </si>
+  <si>
+    <t>GERVAISE</t>
+  </si>
+  <si>
+    <t>Eden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GONTIER </t>
+  </si>
+  <si>
+    <t>Anaïck</t>
+  </si>
+  <si>
+    <t>PENIN</t>
+  </si>
+  <si>
+    <t>Axelle</t>
+  </si>
+  <si>
+    <t>CARTIER</t>
+  </si>
+  <si>
+    <t>JOURDELAT</t>
+  </si>
+  <si>
+    <t>LATINI</t>
+  </si>
+  <si>
+    <t>PERCHER</t>
+  </si>
+  <si>
+    <t>CHALLIN</t>
+  </si>
+  <si>
+    <t>Margault</t>
+  </si>
+  <si>
+    <t>BAMBIER</t>
+  </si>
+  <si>
+    <t>BOUDIER</t>
+  </si>
+  <si>
+    <t>Véto à l'étranger</t>
+  </si>
+  <si>
+    <t>Alexane</t>
+  </si>
+  <si>
+    <t>TRONIOU</t>
+  </si>
+  <si>
+    <t>PINON</t>
+  </si>
+  <si>
+    <t>FERNANDES</t>
+  </si>
+  <si>
+    <t>HUET</t>
+  </si>
+  <si>
+    <t>DA ROCHA</t>
+  </si>
+  <si>
+    <t>CHAMPIE</t>
+  </si>
+  <si>
+    <t>MARIAT</t>
+  </si>
+  <si>
+    <t>LESOU</t>
+  </si>
+  <si>
+    <t>Paul</t>
+  </si>
+  <si>
+    <t>Wilfried</t>
+  </si>
+  <si>
+    <t>Maëva</t>
+  </si>
+  <si>
+    <t>Eva</t>
+  </si>
+  <si>
+    <t>Clémence</t>
+  </si>
+  <si>
+    <t>AIMARD</t>
+  </si>
+  <si>
+    <t>BAUDRY</t>
+  </si>
+  <si>
+    <t>CABANNE</t>
+  </si>
+  <si>
+    <t>THERIN</t>
+  </si>
+  <si>
+    <t>Victoria</t>
   </si>
 </sst>
 </file>
@@ -4708,6 +4848,10 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4722,10 +4866,6 @@
     <xf numFmtId="0" fontId="32" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -5070,20 +5210,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K196"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <dimension ref="A1:K224"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" customWidth="1"/>
-    <col min="2" max="2" width="14.28515625" customWidth="1"/>
+    <col min="1" max="1" width="27.44140625" customWidth="1"/>
+    <col min="2" max="2" width="14.33203125" customWidth="1"/>
     <col min="3" max="3" width="17" customWidth="1"/>
-    <col min="4" max="4" width="8.5703125" customWidth="1"/>
+    <col min="4" max="4" width="8.5546875" customWidth="1"/>
     <col min="5" max="5" width="9" customWidth="1"/>
-    <col min="6" max="6" width="44.85546875" customWidth="1"/>
+    <col min="6" max="6" width="44.88671875" customWidth="1"/>
     <col min="7" max="7" width="18" customWidth="1"/>
     <col min="8" max="8" width="28" customWidth="1"/>
-    <col min="9" max="9" width="21.42578125" customWidth="1"/>
+    <col min="9" max="9" width="21.44140625" customWidth="1"/>
     <col min="10" max="10" width="56" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="4" customWidth="1"/>
+    <col min="11" max="11" width="14.6640625" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -5117,7 +5257,7 @@
       <c r="J1" s="2" t="s">
         <v>1147</v>
       </c>
-      <c r="K1" s="111" t="s">
+      <c r="K1" s="105" t="s">
         <v>1296</v>
       </c>
     </row>
@@ -7356,7 +7496,7 @@
         <v>262</v>
       </c>
       <c r="B96" s="1" t="str">
-        <f t="shared" ref="B96:B196" si="14">LEFT(A96)</f>
+        <f t="shared" ref="B96:B224" si="14">LEFT(A96)</f>
         <v>P</v>
       </c>
       <c r="C96" s="32" t="s">
@@ -9331,7 +9471,7 @@
       <c r="E181" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="F181" s="112" t="s">
+      <c r="F181" s="106" t="s">
         <v>229</v>
       </c>
       <c r="J181" t="s">
@@ -9358,7 +9498,7 @@
       <c r="E182" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="F182" s="112" t="s">
+      <c r="F182" s="106" t="s">
         <v>695</v>
       </c>
     </row>
@@ -9690,6 +9830,586 @@
       </c>
       <c r="F196" s="88" t="s">
         <v>1001</v>
+      </c>
+    </row>
+    <row r="197" spans="1:11">
+      <c r="A197" s="32" t="s">
+        <v>1312</v>
+      </c>
+      <c r="B197" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>A</v>
+      </c>
+      <c r="C197" s="32" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D197" s="26">
+        <v>2024</v>
+      </c>
+      <c r="E197" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F197" s="3" t="s">
+        <v>1311</v>
+      </c>
+    </row>
+    <row r="198" spans="1:11">
+      <c r="A198" s="32" t="s">
+        <v>1314</v>
+      </c>
+      <c r="B198" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>B</v>
+      </c>
+      <c r="C198" s="32" t="s">
+        <v>1332</v>
+      </c>
+      <c r="D198" s="26">
+        <v>2024</v>
+      </c>
+      <c r="E198" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F198" s="3" t="s">
+        <v>1311</v>
+      </c>
+    </row>
+    <row r="199" spans="1:11">
+      <c r="A199" s="32" t="s">
+        <v>1315</v>
+      </c>
+      <c r="B199" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>B</v>
+      </c>
+      <c r="C199" s="32" t="s">
+        <v>1316</v>
+      </c>
+      <c r="D199" s="26">
+        <v>2024</v>
+      </c>
+      <c r="E199" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F199" s="3" t="s">
+        <v>1311</v>
+      </c>
+    </row>
+    <row r="200" spans="1:11">
+      <c r="A200" s="32" t="s">
+        <v>1317</v>
+      </c>
+      <c r="B200" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>G</v>
+      </c>
+      <c r="C200" s="32" t="s">
+        <v>1318</v>
+      </c>
+      <c r="D200" s="26">
+        <v>2024</v>
+      </c>
+      <c r="E200" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F200" s="3" t="s">
+        <v>1311</v>
+      </c>
+    </row>
+    <row r="201" spans="1:11">
+      <c r="A201" s="32" t="s">
+        <v>1319</v>
+      </c>
+      <c r="B201" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>G</v>
+      </c>
+      <c r="C201" s="32" t="s">
+        <v>1320</v>
+      </c>
+      <c r="D201" s="26">
+        <v>2024</v>
+      </c>
+      <c r="E201" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F201" s="3" t="s">
+        <v>1311</v>
+      </c>
+    </row>
+    <row r="202" spans="1:11">
+      <c r="A202" s="32" t="s">
+        <v>1321</v>
+      </c>
+      <c r="B202" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>P</v>
+      </c>
+      <c r="C202" s="32" t="s">
+        <v>1322</v>
+      </c>
+      <c r="D202" s="26">
+        <v>2024</v>
+      </c>
+      <c r="E202" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F202" s="3" t="s">
+        <v>1311</v>
+      </c>
+    </row>
+    <row r="203" spans="1:11">
+      <c r="A203" s="32" t="s">
+        <v>1323</v>
+      </c>
+      <c r="B203" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>C</v>
+      </c>
+      <c r="C203" s="32" t="s">
+        <v>231</v>
+      </c>
+      <c r="D203" s="26">
+        <v>2023</v>
+      </c>
+      <c r="E203" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F203" s="3" t="s">
+        <v>1311</v>
+      </c>
+    </row>
+    <row r="204" spans="1:11">
+      <c r="A204" s="32" t="s">
+        <v>1324</v>
+      </c>
+      <c r="B204" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>J</v>
+      </c>
+      <c r="C204" s="32"/>
+      <c r="D204" s="26">
+        <v>2023</v>
+      </c>
+      <c r="E204" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F204" s="3" t="s">
+        <v>1311</v>
+      </c>
+    </row>
+    <row r="205" spans="1:11">
+      <c r="A205" s="32" t="s">
+        <v>1325</v>
+      </c>
+      <c r="B205" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>L</v>
+      </c>
+      <c r="C205" s="32" t="s">
+        <v>204</v>
+      </c>
+      <c r="D205" s="26">
+        <v>2023</v>
+      </c>
+      <c r="E205" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F205" s="3" t="s">
+        <v>1311</v>
+      </c>
+    </row>
+    <row r="206" spans="1:11">
+      <c r="A206" s="32" t="s">
+        <v>1326</v>
+      </c>
+      <c r="B206" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>P</v>
+      </c>
+      <c r="D206" s="26">
+        <v>2023</v>
+      </c>
+      <c r="E206" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F206" t="s">
+        <v>1310</v>
+      </c>
+    </row>
+    <row r="207" spans="1:11">
+      <c r="A207" s="32" t="s">
+        <v>1327</v>
+      </c>
+      <c r="B207" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>C</v>
+      </c>
+      <c r="C207" s="32" t="s">
+        <v>450</v>
+      </c>
+      <c r="D207" s="26">
+        <v>2022</v>
+      </c>
+      <c r="E207" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F207" t="s">
+        <v>1311</v>
+      </c>
+    </row>
+    <row r="208" spans="1:11">
+      <c r="A208" s="32" t="s">
+        <v>912</v>
+      </c>
+      <c r="B208" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>G</v>
+      </c>
+      <c r="C208" s="32" t="s">
+        <v>1328</v>
+      </c>
+      <c r="D208" s="26">
+        <v>2022</v>
+      </c>
+      <c r="E208" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F208" t="s">
+        <v>1311</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6">
+      <c r="A209" s="32" t="s">
+        <v>1329</v>
+      </c>
+      <c r="B209" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>B</v>
+      </c>
+      <c r="D209" s="26">
+        <v>2021</v>
+      </c>
+      <c r="E209" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F209" t="s">
+        <v>1311</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6">
+      <c r="A210" s="32" t="s">
+        <v>1330</v>
+      </c>
+      <c r="B210" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>B</v>
+      </c>
+      <c r="C210" s="32" t="s">
+        <v>263</v>
+      </c>
+      <c r="D210" s="26">
+        <v>2021</v>
+      </c>
+      <c r="E210" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F210" t="s">
+        <v>1311</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6">
+      <c r="A211" s="32" t="s">
+        <v>225</v>
+      </c>
+      <c r="B211" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>R</v>
+      </c>
+      <c r="C211" s="32" t="s">
+        <v>226</v>
+      </c>
+      <c r="D211" s="26">
+        <v>2021</v>
+      </c>
+      <c r="E211" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F211" t="s">
+        <v>1311</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6">
+      <c r="A212" s="32" t="s">
+        <v>246</v>
+      </c>
+      <c r="B212" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>E</v>
+      </c>
+      <c r="C212" s="32" t="s">
+        <v>247</v>
+      </c>
+      <c r="D212" s="26">
+        <v>2021</v>
+      </c>
+      <c r="E212" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F212" t="s">
+        <v>1331</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6">
+      <c r="A213" s="32" t="s">
+        <v>1333</v>
+      </c>
+      <c r="B213" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>T</v>
+      </c>
+      <c r="C213" s="32" t="s">
+        <v>1344</v>
+      </c>
+      <c r="D213" s="26">
+        <v>2020</v>
+      </c>
+      <c r="E213" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F213" t="s">
+        <v>1311</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6">
+      <c r="A214" s="32" t="s">
+        <v>1334</v>
+      </c>
+      <c r="B214" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>P</v>
+      </c>
+      <c r="C214" s="32" t="s">
+        <v>1345</v>
+      </c>
+      <c r="D214" s="26">
+        <v>2020</v>
+      </c>
+      <c r="E214" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F214" t="s">
+        <v>1308</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6">
+      <c r="A215" s="32" t="s">
+        <v>1335</v>
+      </c>
+      <c r="B215" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>F</v>
+      </c>
+      <c r="C215" s="32" t="s">
+        <v>1343</v>
+      </c>
+      <c r="D215" s="26">
+        <v>2019</v>
+      </c>
+      <c r="E215" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F215" t="s">
+        <v>1310</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6">
+      <c r="A216" s="32" t="s">
+        <v>1336</v>
+      </c>
+      <c r="B216" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>H</v>
+      </c>
+      <c r="C216" t="s">
+        <v>1342</v>
+      </c>
+      <c r="D216" s="26">
+        <v>2019</v>
+      </c>
+      <c r="E216" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F216" t="s">
+        <v>1310</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6">
+      <c r="A217" s="32" t="s">
+        <v>1337</v>
+      </c>
+      <c r="B217" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>D</v>
+      </c>
+      <c r="C217" t="s">
+        <v>389</v>
+      </c>
+      <c r="D217" s="26">
+        <v>2019</v>
+      </c>
+      <c r="E217" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F217" t="s">
+        <v>1311</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6">
+      <c r="A218" s="32" t="s">
+        <v>1338</v>
+      </c>
+      <c r="B218" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>C</v>
+      </c>
+      <c r="C218" t="s">
+        <v>402</v>
+      </c>
+      <c r="D218" s="26">
+        <v>2019</v>
+      </c>
+      <c r="E218" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F218" t="s">
+        <v>1310</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6">
+      <c r="A219" s="32" t="s">
+        <v>1339</v>
+      </c>
+      <c r="B219" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>M</v>
+      </c>
+      <c r="C219" t="s">
+        <v>1341</v>
+      </c>
+      <c r="D219" s="26">
+        <v>2019</v>
+      </c>
+      <c r="E219" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F219" t="s">
+        <v>1310</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6">
+      <c r="A220" s="32" t="s">
+        <v>1340</v>
+      </c>
+      <c r="B220" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>L</v>
+      </c>
+      <c r="C220" t="s">
+        <v>415</v>
+      </c>
+      <c r="D220" s="26">
+        <v>2019</v>
+      </c>
+      <c r="E220" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F220" t="s">
+        <v>1310</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6">
+      <c r="A221" s="32" t="s">
+        <v>1346</v>
+      </c>
+      <c r="B221" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>A</v>
+      </c>
+      <c r="C221" t="s">
+        <v>454</v>
+      </c>
+      <c r="D221" s="26">
+        <v>2018</v>
+      </c>
+      <c r="E221" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F221" t="s">
+        <v>1310</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6">
+      <c r="A222" s="32" t="s">
+        <v>1347</v>
+      </c>
+      <c r="B222" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>B</v>
+      </c>
+      <c r="C222" t="s">
+        <v>269</v>
+      </c>
+      <c r="D222" s="26">
+        <v>2018</v>
+      </c>
+      <c r="E222" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F222" t="s">
+        <v>1308</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6">
+      <c r="A223" s="32" t="s">
+        <v>1348</v>
+      </c>
+      <c r="B223" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>C</v>
+      </c>
+      <c r="C223" t="s">
+        <v>1098</v>
+      </c>
+      <c r="D223" s="26">
+        <v>2018</v>
+      </c>
+      <c r="E223" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F223" t="s">
+        <v>1310</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6">
+      <c r="A224" s="32" t="s">
+        <v>1349</v>
+      </c>
+      <c r="B224" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>T</v>
+      </c>
+      <c r="C224" t="s">
+        <v>1350</v>
+      </c>
+      <c r="D224" s="26">
+        <v>2018</v>
+      </c>
+      <c r="E224" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F224" t="s">
+        <v>1310</v>
       </c>
     </row>
   </sheetData>
@@ -9719,13 +10439,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:N128"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" customWidth="1"/>
-    <col min="2" max="2" width="16.5703125" customWidth="1"/>
-    <col min="6" max="6" width="42.28515625" customWidth="1"/>
-    <col min="8" max="8" width="32.28515625" customWidth="1"/>
-    <col min="9" max="9" width="96.7109375" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" customWidth="1"/>
+    <col min="2" max="2" width="16.5546875" customWidth="1"/>
+    <col min="6" max="6" width="42.33203125" customWidth="1"/>
+    <col min="8" max="8" width="32.33203125" customWidth="1"/>
+    <col min="9" max="9" width="96.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
@@ -9756,7 +10476,7 @@
       <c r="J1" s="2" t="s">
         <v>1147</v>
       </c>
-      <c r="K1" s="111" t="s">
+      <c r="K1" s="105" t="s">
         <v>1296</v>
       </c>
     </row>
@@ -11389,7 +12109,7 @@
         <f t="shared" ref="B73" si="11">LEFT(A73)</f>
         <v>T</v>
       </c>
-      <c r="C73" s="112" t="s">
+      <c r="C73" s="106" t="s">
         <v>196</v>
       </c>
       <c r="D73" s="1">
@@ -12392,14 +13112,14 @@
       </c>
     </row>
     <row r="119" spans="1:11">
-      <c r="A119" s="112" t="s">
+      <c r="A119" s="106" t="s">
         <v>1307</v>
       </c>
       <c r="B119" s="1" t="str">
         <f t="shared" ref="B119" si="15">LEFT(A119)</f>
         <v>V</v>
       </c>
-      <c r="C119" s="112" t="s">
+      <c r="C119" s="106" t="s">
         <v>138</v>
       </c>
       <c r="D119" s="1">
@@ -12632,21 +13352,21 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:M81"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <dimension ref="A1:M85"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="22.28515625" style="3" customWidth="1"/>
-    <col min="2" max="6" width="11.42578125" style="3" customWidth="1"/>
-    <col min="7" max="7" width="69.140625" style="3" customWidth="1"/>
-    <col min="8" max="8" width="11.42578125" style="3" customWidth="1"/>
-    <col min="9" max="9" width="21.42578125" style="3" customWidth="1"/>
-    <col min="10" max="10" width="42.42578125" style="3" customWidth="1"/>
-    <col min="11" max="11" width="72.28515625" style="3" customWidth="1"/>
-    <col min="12" max="12" width="11.42578125" style="3" customWidth="1"/>
-    <col min="13" max="16384" width="11.42578125" style="3"/>
+    <col min="1" max="1" width="22.33203125" style="3" customWidth="1"/>
+    <col min="2" max="6" width="11.44140625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="69.109375" style="3" customWidth="1"/>
+    <col min="8" max="8" width="11.44140625" style="3" customWidth="1"/>
+    <col min="9" max="9" width="21.44140625" style="3" customWidth="1"/>
+    <col min="10" max="10" width="42.44140625" style="3" customWidth="1"/>
+    <col min="11" max="11" width="72.33203125" style="3" customWidth="1"/>
+    <col min="12" max="12" width="11.44140625" style="3" customWidth="1"/>
+    <col min="13" max="16384" width="11.44140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="39.950000000000003" customHeight="1">
+    <row r="1" spans="1:12" ht="39.9" customHeight="1">
       <c r="A1" s="3" t="s">
         <v>74</v>
       </c>
@@ -12684,7 +13404,7 @@
         <v>925</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="99" customHeight="99">
+    <row r="2" spans="1:12" ht="316.8">
       <c r="A2" s="3" t="s">
         <v>126</v>
       </c>
@@ -12703,10 +13423,8 @@
       <c r="F2" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AgroParisTech est une grande école d’ingénieurs agronomes, membre de l’Université Paris-Saclay. Le cursus ingénieur dure 3 ans (statut étudiant, apprentissage possible, élèves fonctionnaires) et associe sciences du vivant, sciences de l’ingénieur et sciences humaines, économiques et sociales, avec des dominantes d’approfondissement.</t>
-        </is>
+      <c r="G2" s="3" t="s">
+        <v>1177</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>495</v>
@@ -12720,13 +13438,11 @@
       <c r="K2" s="3" t="s">
         <v>498</v>
       </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Agronomie ; Sciences du vivant ; Sciences de l’ingénieur ; Sciences humaines, économiques et sociales ; Alimentation ; Environnement ; Dominantes d’approfondissement ; Apprentissage ; Élèves fonctionnaires ; Paris-Saclay</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" spans="1:12" ht="39.950000000000003" customHeight="1">
+      <c r="L2" s="3" t="s">
+        <v>1236</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="39.9" customHeight="1">
       <c r="A3" s="3" t="s">
         <v>115</v>
       </c>
@@ -12764,7 +13480,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="99" customHeight="99">
+    <row r="4" spans="1:12" ht="144">
       <c r="A4" s="3" t="s">
         <v>37</v>
       </c>
@@ -12783,10 +13499,8 @@
       <c r="F4" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bordeaux Sciences Agro est une école publique d’ingénieurs agronomes, située à Gradignan près de Bordeaux. Le cursus ingénieur dure 3 ans (apprentissage possible) et s’appuie sur le vignoble voisin pour proposer des formations reconnues autour de la vigne et du vin, en plus de l’agronomie, de l’agroalimentaire et de l’agroécologie.</t>
-        </is>
+      <c r="G4" s="3" t="s">
+        <v>1178</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>503</v>
@@ -12800,13 +13514,11 @@
       <c r="K4" s="3" t="s">
         <v>506</v>
       </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Agronomie ; Vigne et vin ; Agroalimentaire ; Agroécologie ; Agreenium ; Apprentissage ; Gradignan</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="39.950000000000003" customHeight="1">
+      <c r="L4" s="3" t="s">
+        <v>1237</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="39.9" customHeight="1">
       <c r="A5" s="3" t="s">
         <v>122</v>
       </c>
@@ -12844,7 +13556,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="39.950000000000003" customHeight="1">
+    <row r="6" spans="1:12" ht="39.9" customHeight="1">
       <c r="A6" s="3" t="s">
         <v>104</v>
       </c>
@@ -12882,7 +13594,7 @@
         <v>921</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="114" customHeight="114">
+    <row r="7" spans="1:12" ht="244.8">
       <c r="A7" s="3" t="s">
         <v>280</v>
       </c>
@@ -12901,10 +13613,8 @@
       <c r="F7" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Le campus de Rennes de l’Institut Agro Rennes-Angers (ex-Agrocampus Ouest) propose les cursus d’ingénieur agronome et d’ingénieur agroalimentaire, avec des spécialisations comme l’agroécologie, l’agroéconomie et les politiques publiques ou le management des entreprises de l’alimentation. L’halieutique (sciences de la mer et du littoral) fait aussi partie de l’offre de formation.</t>
-        </is>
+      <c r="G7" s="3" t="s">
+        <v>1179</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>514</v>
@@ -12918,13 +13628,11 @@
       <c r="K7" s="3" t="s">
         <v>517</v>
       </c>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Agronomie ; Agroalimentaire ; Halieutique ; Mer et littoral ; Agroécologie ; Agroéconomie ; Politiques publiques ; Management des entreprises ; Spécialisations</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="39.950000000000003" customHeight="1">
+      <c r="L7" s="3" t="s">
+        <v>1239</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="39.9" customHeight="1">
       <c r="A8" s="3" t="s">
         <v>112</v>
       </c>
@@ -12962,7 +13670,7 @@
         <v>923</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="39.950000000000003" customHeight="1">
+    <row r="9" spans="1:12" ht="39.9" customHeight="1">
       <c r="A9" s="3" t="s">
         <v>136</v>
       </c>
@@ -13000,7 +13708,7 @@
         <v>918</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="114" customHeight="114">
+    <row r="10" spans="1:12" ht="230.4">
       <c r="A10" s="3" t="s">
         <v>99</v>
       </c>
@@ -13019,10 +13727,8 @@
       <c r="F10" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">L’Institut Agro Montpellier (ex-Montpellier SupAgro) forme des ingénieurs en agronomie, avec un cursus orienté vers l’agronomie et l’agroalimentaire durables, notamment pour les agricultures du Sud (méditerranéennes et tropicales). Il propose de nombreuses options en 3e année, un pôle fort sur la vigne et le vin, ainsi que des doubles diplômes avec des établissements partenaires.</t>
-        </is>
+      <c r="G10" s="3" t="s">
+        <v>1180</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>527</v>
@@ -13036,13 +13742,11 @@
       <c r="K10" s="3" t="s">
         <v>530</v>
       </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Agronomie ; Agroalimentaire ; Agricultures du Sud ; Méditerranée et tropiques ; Vigne et vin ; Systèmes agricoles durables ; Options de 3e année ; Double diplôme</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="99" customHeight="99">
+      <c r="L10" s="3" t="s">
+        <v>1240</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="259.2">
       <c r="A11" s="3" t="s">
         <v>342</v>
       </c>
@@ -13061,10 +13765,8 @@
       <c r="F11" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">L’École nationale vétérinaire d’Alfort, à Maisons-Alfort près de Paris, est l’une des quatre écoles vétérinaires publiques françaises. Elle forme des docteurs vétérinaires en 6 ans et dispose d’un centre hospitalier universitaire vétérinaire, ainsi que d’un site dédié aux équidés en Normandie (Goustranville).</t>
-        </is>
+      <c r="G11" s="3" t="s">
+        <v>1181</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>532</v>
@@ -13078,13 +13780,11 @@
       <c r="K11" s="3" t="s">
         <v>535</v>
       </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Médecine vétérinaire ; Docteur vétérinaire ; Santé animale ; Centre hospitalier universitaire vétérinaire ; Équidés ; Animaux de compagnie ; Maisons-Alfort ; Campus équin Normandie</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="114" customHeight="114">
+      <c r="L11" s="3" t="s">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="273.60000000000002">
       <c r="A12" s="3" t="s">
         <v>367</v>
       </c>
@@ -13103,10 +13803,8 @@
       <c r="F12" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">L’École nationale vétérinaire de Toulouse, membre de l’Université de Toulouse, est l’une des quatre écoles vétérinaires publiques françaises. Elle forme des docteurs vétérinaires en 6 ans, avec un centre hospitalier universitaire vétérinaire (animaux de compagnie, équidés, animaux de production), des formations de spécialisation, un volet santé publique vétérinaire et un stage à l’étranger obligatoire.</t>
-        </is>
+      <c r="G12" s="3" t="s">
+        <v>1182</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>536</v>
@@ -13120,13 +13818,11 @@
       <c r="K12" s="3" t="s">
         <v>539</v>
       </c>
-      <c r="L12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Médecine vétérinaire ; Docteur vétérinaire ; Centre hospitalier universitaire vétérinaire ; Animaux de compagnie ; Équidés ; Animaux de production ; Santé publique vétérinaire ; Spécialisation ; Stage à l’étranger</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" spans="1:12" ht="114" customHeight="114">
+      <c r="L12" s="3" t="s">
+        <v>1242</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="273.60000000000002">
       <c r="A13" s="3" t="s">
         <v>141</v>
       </c>
@@ -13145,10 +13841,8 @@
       <c r="F13" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Le campus vétérinaire de VetAgro Sup se situe à Marcy-l’Étoile, près de Lyon. Il forme des docteurs vétérinaires et s’appuie sur trois centres hospitaliers universitaires vétérinaires (animaux de compagnie, équidés, animaux de production). VetAgro Sup est la seule structure française à former à la fois des vétérinaires, des ingénieurs agronomes et des inspecteurs de santé publique vétérinaire.</t>
-        </is>
+      <c r="G13" s="3" t="s">
+        <v>1183</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>540</v>
@@ -13162,13 +13856,11 @@
       <c r="K13" s="3" t="s">
         <v>542</v>
       </c>
-      <c r="L13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Médecine vétérinaire ; Docteur vétérinaire ; Animaux de compagnie ; Équidés ; Animaux de production ; Centre hospitalier universitaire vétérinaire ; Inspecteur de santé publique vétérinaire ; Marcy-l’Étoile</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" spans="1:12" ht="99" customHeight="99">
+      <c r="L13" s="3" t="s">
+        <v>1243</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="158.4">
       <c r="A14" s="3" t="s">
         <v>255</v>
       </c>
@@ -13187,10 +13879,8 @@
       <c r="F14" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Le site vétérinaire d’Oniris VetAgroBio, à Nantes, forme des docteurs vétérinaires au sein de l’une des quatre écoles vétérinaires publiques françaises, avec une approche « One Health » qui relie santé animale, santé humaine et environnement. L’école propose aussi un cursus d’ingénieur dans le domaine de l’alimentation (voir ONIRIS Nantes).</t>
-        </is>
+      <c r="G14" s="3" t="s">
+        <v>1184</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>499</v>
@@ -13204,13 +13894,11 @@
       <c r="K14" s="3" t="s">
         <v>544</v>
       </c>
-      <c r="L14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Médecine vétérinaire ; Docteur vétérinaire ; One Health ; Santé animale ; Santé publique ; Alimentation ; Nantes</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" spans="1:12" ht="114" customHeight="114">
+      <c r="L14" s="3" t="s">
+        <v>1244</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="288">
       <c r="A15" s="3" t="s">
         <v>229</v>
       </c>
@@ -13226,10 +13914,8 @@
       <c r="F15" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">L’ENGEES (École nationale du génie de l’eau et de l’environnement de Strasbourg) forme en 3 ans des ingénieurs (statut étudiant, apprenti ou fonctionnaire) aux métiers de l’eau et de l’environnement : eau potable, assainissement, ingénierie des cours d’eau et renaturation, gestion des déchets. Les diplômés travaillent notamment en bureaux d’études, en collectivités et dans les entreprises de l’eau.</t>
-        </is>
+      <c r="G15" s="3" t="s">
+        <v>1185</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>546</v>
@@ -13243,13 +13929,11 @@
       <c r="K15" s="3" t="s">
         <v>549</v>
       </c>
-      <c r="L15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Eau potable ; Assainissement ; Cours d’eau ; Renaturation ; Gestion des déchets ; Environnement ; Bureaux d’études ; Collectivités ; Apprentissage ; Élèves fonctionnaires ; Strasbourg</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" spans="1:12" ht="130" customHeight="130">
+      <c r="L15" s="3" t="s">
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="331.2">
       <c r="A16" s="3" t="s">
         <v>88</v>
       </c>
@@ -13262,10 +13946,8 @@
       <c r="F16" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Géodata Paris (ex ENSG-Géomatique) est une école d’ingénieurs spécialisée en géomatique et en sciences de l’information géographique, située à Champs-sur-Marne. Elle recrute les élèves de BCPST via le concours G2E, avec un statut civil ou fonctionnaire. Les enseignements portent sur les données géographiques, la cartographie, la télédétection et leurs applications (environnement, aménagement, agriculture…).</t>
-        </is>
+      <c r="G16" s="3" t="s">
+        <v>1186</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>495</v>
@@ -13279,13 +13961,11 @@
       <c r="K16" s="3" t="s">
         <v>552</v>
       </c>
-      <c r="L16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Géomatique ; Information géographique ; Systèmes d’information géographique ; Télédétection ; Cartographie ; Données spatiales ; Environnement ; Aménagement du territoire ; Concours G2E ; Élèves fonctionnaires</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" spans="1:12" ht="114" customHeight="114">
+      <c r="L16" s="3" t="s">
+        <v>1246</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="230.4">
       <c r="A17" s="3" t="s">
         <v>167</v>
       </c>
@@ -13304,10 +13984,8 @@
       <c r="F17" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">L’ESIR (École supérieure d’ingénieurs de Rennes, Université de Rennes) propose les spécialités informatique, matériaux, systèmes numériques et réseaux (en apprentissage) et technologies de l’information pour la santé. Les élèves de BCPST peuvent y accéder via le concours Polytech BCPST, notamment pour les technologies de l’information pour la santé et les matériaux.</t>
-        </is>
+      <c r="G17" s="3" t="s">
+        <v>1187</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>514</v>
@@ -13321,13 +13999,11 @@
       <c r="K17" s="3" t="s">
         <v>556</v>
       </c>
-      <c r="L17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Informatique ; Matériaux ; Systèmes numériques et réseaux ; Technologies de l’information pour la santé ; Santé numérique ; Apprentissage ; Concours Polytech BCPST</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" spans="1:12" ht="130" customHeight="130">
+      <c r="L17" s="3" t="s">
+        <v>1247</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="273.60000000000002">
       <c r="A18" s="3" t="s">
         <v>91</v>
       </c>
@@ -13346,10 +14022,8 @@
       <c r="F18" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">L’ISIFC (Institut supérieur d’ingénieurs de Franche-Comté), à Besançon, forme des ingénieurs en génie biomédical, avec une triple culture technique, médicale et réglementaire. En 3e année, les options sont la bio-ingénierie, la biomécanique et les microsystèmes, l’e-santé et la microrobotique pour la santé. Les élèves de BCPST y accèdent via le concours Polytech BCPST (13 places) ; 2 places sont ouvertes en TB.</t>
-        </is>
+      <c r="G18" s="3" t="s">
+        <v>1188</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>557</v>
@@ -13363,13 +14037,11 @@
       <c r="K18" s="3" t="s">
         <v>560</v>
       </c>
-      <c r="L18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Génie biomédical ; Dispositifs médicaux ; Bio-ingénierie ; Biomécanique ; Microsystèmes ; E-santé ; Microrobotique pour la santé ; Réglementation ; Besançon ; Concours Polytech BCPST</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" spans="1:12" ht="39.950000000000003" customHeight="1">
+      <c r="L18" s="3" t="s">
+        <v>1248</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="39.9" customHeight="1">
       <c r="A19" s="3" t="s">
         <v>191</v>
       </c>
@@ -13407,7 +14079,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="99" customHeight="99">
+    <row r="20" spans="1:12" ht="201.6">
       <c r="A20" s="3" t="s">
         <v>144</v>
       </c>
@@ -13426,10 +14098,8 @@
       <c r="F20" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Polytech Clermont est une école d’ingénieurs du réseau Polytech. Les élèves de BCPST, de PC et de TB peuvent y intégrer la spécialité Génie biologique, centrée sur les biotechnologies durables et les bioprocédés, avec des applications comme le diagnostic, les matériaux biosourcés, la bioénergie et le bioraffinage.</t>
-        </is>
+      <c r="G20" s="3" t="s">
+        <v>1189</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>518</v>
@@ -13443,13 +14113,11 @@
       <c r="K20" s="3" t="s">
         <v>567</v>
       </c>
-      <c r="L20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Génie biologique ; Biotechnologies durables ; Bioprocédés ; Matériaux biosourcés ; Bioénergie ; Bioraffinage ; Diagnostic ; Concours Polytech BCPST</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" spans="1:12" ht="99" customHeight="99">
+      <c r="L20" s="3" t="s">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="216">
       <c r="A21" s="3" t="s">
         <v>85</v>
       </c>
@@ -13468,10 +14136,8 @@
       <c r="F21" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Polytech Tours est une école d’ingénieurs du réseau Polytech (Université de Tours). Les élèves de BCPST peuvent y intégrer la spécialité Génie de l’aménagement et de l’environnement via le concours Polytech BCPST, avec des enseignements liés à l’aménagement du territoire, à l’environnement et à la gestion de la ville et des réseaux.</t>
-        </is>
+      <c r="G21" s="3" t="s">
+        <v>1190</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>568</v>
@@ -13485,13 +14151,11 @@
       <c r="K21" s="3" t="s">
         <v>571</v>
       </c>
-      <c r="L21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Génie de l’aménagement et de l’environnement ; Aménagement du territoire ; Environnement ; Ville ; Réseaux ; Concours Polytech BCPST ; Tours</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" spans="1:12" ht="130" customHeight="130">
+      <c r="L21" s="3" t="s">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="331.2">
       <c r="A22" s="3" t="s">
         <v>119</v>
       </c>
@@ -13510,10 +14174,8 @@
       <c r="F22" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">L’INSA Lyon est une grande école d’ingénieurs publique du groupe INSA, organisée en neuf départements : biosciences, génie civil et urbanisme, génie électrique, génie énergétique et environnement, génie industriel, génie mécanique, informatique, science et génie des matériaux et télécommunications. Les élèves de BCPST peuvent y accéder pour la spécialité biotechnologies et bioinformatique, via le recrutement commun du groupe INSA.</t>
-        </is>
+      <c r="G22" s="3" t="s">
+        <v>1191</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>540</v>
@@ -13527,13 +14189,11 @@
       <c r="K22" s="3" t="s">
         <v>575</v>
       </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Biosciences ; Biotechnologies et bioinformatique ; Génie civil et urbanisme ; Génie énergétique et environnement ; Génie industriel ; Génie mécanique ; Génie électrique ; Informatique ; Matériaux ; Télécommunications ; Groupe INSA</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" spans="1:12" ht="114" customHeight="114">
+      <c r="L22" s="3" t="s">
+        <v>1251</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="273.60000000000002">
       <c r="A23" s="3" t="s">
         <v>576</v>
       </c>
@@ -13552,10 +14212,8 @@
       <c r="F23" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">L’INSA Rouen Normandie est une école d’ingénieurs publique du groupe INSA, installée à Saint-Étienne-du-Rouvray (avec une antenne au Havre). Elle propose notamment les spécialités génie civil et construction durable, énergétique et propulsion, mécanique, génie mathématique, architecture des systèmes d’information, ainsi que chimie et procédés et gestion des risques.</t>
-        </is>
+      <c r="G23" s="3" t="s">
+        <v>1192</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>577</v>
@@ -13569,13 +14227,11 @@
       <c r="K23" s="3" t="s">
         <v>580</v>
       </c>
-      <c r="L23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Génie civil ; Construction durable ; Énergétique et propulsion ; Mécanique ; Génie mathématique ; Architecture des systèmes d’information ; Chimie et procédés ; Gestion des risques ; Groupe INSA</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" spans="1:12" ht="130" customHeight="130">
+      <c r="L23" s="3" t="s">
+        <v>1252</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="360">
       <c r="A24" s="3" t="s">
         <v>331</v>
       </c>
@@ -13594,10 +14250,8 @@
       <c r="F24" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">L’INSA Toulouse est une grande école d’ingénieurs publique du groupe INSA, avec huit spécialités : génie biologique, génie des procédés et environnement, génie civil, génie mécanique, génie physique, automatique et électronique, génie mathématique et modélisation, informatique et réseaux. Le génie biologique et le génie des procédés et environnement sont les plus proches des profils BCPST (biotechnologies, bioprocédés, environnement).</t>
-        </is>
+      <c r="G24" s="3" t="s">
+        <v>1193</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>536</v>
@@ -13611,13 +14265,11 @@
       <c r="K24" s="3" t="s">
         <v>583</v>
       </c>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Génie biologique ; Génie des procédés et environnement ; Biologie des systèmes ; Génie civil ; Génie mécanique ; Génie physique ; Automatique-électronique ; Génie mathématique et modélisation ; Informatique et réseaux ; Groupe INSA</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" spans="1:12" ht="99" customHeight="99">
+      <c r="L24" s="3" t="s">
+        <v>1253</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="230.4">
       <c r="A25" s="3" t="s">
         <v>584</v>
       </c>
@@ -13636,10 +14288,8 @@
       <c r="F25" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">L’INSA Strasbourg est une école d’ingénieurs et d’architectes du groupe INSA. Elle propose sept spécialités d’ingénieur (génie civil, topographie, génie électrique, génie mécanique, plasturgie, mécatronique, génie climatique et énergétique) et délivre le diplôme d’architecte, ce qui en fait la seule école d’ingénieurs française à le faire.</t>
-        </is>
+      <c r="G25" s="3" t="s">
+        <v>1194</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>546</v>
@@ -13653,13 +14303,11 @@
       <c r="K25" s="3" t="s">
         <v>587</v>
       </c>
-      <c r="L25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Génie civil ; Topographie ; Génie électrique ; Génie mécanique ; Plasturgie ; Mécatronique ; Génie climatique et énergétique ; Architecture ; Groupe INSA</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" spans="1:12" ht="130" customHeight="130">
+      <c r="L25" s="3" t="s">
+        <v>1254</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="288">
       <c r="A26" s="3" t="s">
         <v>107</v>
       </c>
@@ -13678,10 +14326,8 @@
       <c r="F26" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ESITech est l’école d’ingénieurs de l’Université de Rouen Normandie (Saint-Étienne-du-Rouvray), liée au groupe INSA. Elle propose deux spécialités : génie biologique (en convention avec l’INSA Rouen, options bioproduction et biotechnologies et produits de santé) et génie physique et santé (dispositifs médicaux, imagerie, biomécanique…). Elle recrute après CPGE sur dossier et épreuves orales, ou via le recrutement commun du groupe INSA.</t>
-        </is>
+      <c r="G26" s="3" t="s">
+        <v>1195</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>588</v>
@@ -13695,13 +14341,11 @@
       <c r="K26" s="3" t="s">
         <v>591</v>
       </c>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Génie biologique ; Bioproduction ; Biotechnologies et produits de santé ; Génie physique et santé ; Dispositifs médicaux ; Imagerie médicale ; Biomécanique ; Pharmacie ; Groupe INSA ; Rouen</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" spans="1:12" ht="99" customHeight="99">
+      <c r="L26" s="3" t="s">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="172.8">
       <c r="A27" s="3" t="s">
         <v>94</v>
       </c>
@@ -13720,10 +14364,8 @@
       <c r="F27" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">L’Université d’Orléans propose, notamment au sein de son Collegium Sciences et Techniques, des licences et masters scientifiques (sciences de la vie, sciences de la Terre, chimie, physique, mathématiques, informatique). Les étudiants issus de BCPST ou de TB peuvent candidater sur dossier pour poursuivre en licence ou en master.</t>
-        </is>
+      <c r="G27" s="3" t="s">
+        <v>1196</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>594</v>
@@ -13737,13 +14379,11 @@
       <c r="K27" s="3" t="s">
         <v>597</v>
       </c>
-      <c r="L27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sciences de la vie ; Sciences de la Terre ; Chimie ; Physique ; Licence ; Master ; Recherche ; Poursuite d’études sur dossier</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" spans="1:12" ht="114" customHeight="114">
+      <c r="L27" s="3" t="s">
+        <v>1256</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="201.6">
       <c r="A28" s="3" t="s">
         <v>129</v>
       </c>
@@ -13762,10 +14402,8 @@
       <c r="F28" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Le Mans Université propose, au sein de sa faculté des sciences et techniques, des licences en sciences de la vie, sciences de la Terre, physique-chimie et acoustique et vibrations, ainsi que des masters en acoustique et en chimie. L’université est reconnue pour son pôle d’acoustique. Les étudiants issus de BCPST ou de TB peuvent candidater sur dossier.</t>
-        </is>
+      <c r="G28" s="3" t="s">
+        <v>1197</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>598</v>
@@ -13779,13 +14417,11 @@
       <c r="K28" s="3" t="s">
         <v>601</v>
       </c>
-      <c r="L28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sciences de la vie ; Sciences de la Terre ; Physique-chimie ; Acoustique et vibrations ; Licence ; Master ; Recherche ; Poursuite d’études sur dossier</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" spans="1:12" ht="130" customHeight="130">
+      <c r="L28" s="3" t="s">
+        <v>1257</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="288">
       <c r="A29" s="3" t="s">
         <v>319</v>
       </c>
@@ -13804,10 +14440,8 @@
       <c r="F29" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Polytech Nice Sophia, à Sophia Antipolis, est l’école d’ingénieurs de l’Université Côte d’Azur (réseau Polytech). Elle propose notamment le génie biologique (pharmacologie, toxicologie, bio-informatique ; santé, cosmétique, arômes et parfums, environnement) et le génie de l’eau (ressource en eau, inondations, eau potable, eaux usées et pluviales), ainsi que le bâtiment, l’électronique, l’informatique et les mathématiques appliquées.</t>
-        </is>
+      <c r="G29" s="3" t="s">
+        <v>1198</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>568</v>
@@ -13821,13 +14455,11 @@
       <c r="K29" s="5" t="s">
         <v>604</v>
       </c>
-      <c r="L29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Génie biologique ; Pharmacologie ; Toxicologie ; Bio-informatique ; Cosmétique ; Arômes et parfums ; Génie de l’eau ; Inondations ; Bâtiment ; Électronique ; Informatique ; Sophia Antipolis</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" spans="1:12" ht="114" customHeight="114">
+      <c r="L29" s="3" t="s">
+        <v>1258</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="216">
       <c r="A30" s="3" t="s">
         <v>321</v>
       </c>
@@ -13846,10 +14478,8 @@
       <c r="F30" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">L’EPISEN (École publique d’ingénieurs de la santé et du numérique), rattachée à l’Université Paris-Est Créteil, propose trois spécialités d’ingénieur à l’interface de la santé et du numérique : génie biomédical et santé, informatique et santé, systèmes d’information. Les élèves de BCPST peuvent y accéder via le concours Polytech BCPST, et l’apprentissage est possible.</t>
-        </is>
+      <c r="G30" s="3" t="s">
+        <v>1199</v>
       </c>
       <c r="H30" s="6" t="s">
         <v>605</v>
@@ -13863,13 +14493,11 @@
       <c r="K30" s="3" t="s">
         <v>608</v>
       </c>
-      <c r="L30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Santé numérique ; Génie biomédical et santé ; Informatique et santé ; Systèmes d’information ; Apprentissage ; Concours Polytech BCPST ; Créteil</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" spans="1:12" ht="130" customHeight="130">
+      <c r="L30" s="3" t="s">
+        <v>1259</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="201.6">
       <c r="A31" s="6" t="s">
         <v>337</v>
       </c>
@@ -13888,10 +14516,8 @@
       <c r="F31" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="G31" s="100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">L’ESIAB (École supérieure d’ingénieurs en agroalimentaire de Bretagne atlantique), école interne de Bretagne INP et composante de l’Université de Bretagne Occidentale, propose deux spécialités d’ingénieur : agroalimentaire à Quimper (apprentissage possible) et microbiologie et sécurité sanitaire à Brest. Elle forme aux métiers de la production, de la qualité et de l’innovation dans l’industrie agroalimentaire.</t>
-        </is>
+      <c r="G31" s="100" t="s">
+        <v>1200</v>
       </c>
       <c r="H31" s="6" t="s">
         <v>609</v>
@@ -13905,13 +14531,11 @@
       <c r="K31" s="3" t="s">
         <v>612</v>
       </c>
-      <c r="L31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Agroalimentaire ; Microbiologie ; Sécurité sanitaire ; Qualité ; Production ; Innovation ; Industrie agroalimentaire ; Apprentissage ; Quimper ; Brest</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" spans="1:12" ht="39.950000000000003" customHeight="1">
+      <c r="L31" s="3" t="s">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="39.9" customHeight="1">
       <c r="A32" s="6" t="s">
         <v>264</v>
       </c>
@@ -13949,7 +14573,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="99" customHeight="99">
+    <row r="33" spans="1:12" ht="172.8">
       <c r="A33" s="6" t="s">
         <v>350</v>
       </c>
@@ -13968,10 +14592,8 @@
       <c r="F33" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="G33" s="100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">L’ENS Paris-Saclay (Gif-sur-Yvette) est une école normale supérieure pluridisciplinaire (sciences, ingénierie, sciences sociales). Elle recrute les élèves de BCPST et de TB via le concours ENS (15 places pour la voie BCPST), avec le statut d’élève fonctionnaire. La formation est tournée vers la recherche, jusqu’au master et au doctorat.</t>
-        </is>
+      <c r="G33" s="100" t="s">
+        <v>1201</v>
       </c>
       <c r="H33" s="6" t="s">
         <v>495</v>
@@ -13985,13 +14607,11 @@
       <c r="K33" s="3" t="s">
         <v>620</v>
       </c>
-      <c r="L33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Recherche ; Interdisciplinarité ; Biologie ; Master ; Doctorat ; Concours ENS BCPST ; Élèves fonctionnaires ; Gif-sur-Yvette</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" spans="1:12" ht="130" customHeight="130">
+      <c r="L33" s="3" t="s">
+        <v>1261</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" ht="259.2">
       <c r="A34" s="3" t="s">
         <v>209</v>
       </c>
@@ -14010,10 +14630,8 @@
       <c r="F34" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="G34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AgroToulouse (Toulouse INP-ENSAT), à Castanet-Tolosan, forme en 3 ans des ingénieurs agronomes (apprentissage possible) dans les domaines de l’agriculture, de l’alimentation et de l’environnement, avec des spécialisations en 3e année (dont l’ingénierie agroalimentaire). L’école délivre aussi le diplôme national d’œnologue. L’admission se fait notamment via le concours Agro-Véto (94 places en BCPST, 8 en TB).</t>
-        </is>
+      <c r="G34" s="3" t="s">
+        <v>1202</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>536</v>
@@ -14027,13 +14645,11 @@
       <c r="K34" s="3" t="s">
         <v>623</v>
       </c>
-      <c r="L34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Agronomie ; Agroalimentaire ; Environnement ; Œnologie ; Transition agroécologique ; Spécialisations de 3e année ; Apprentissage ; Agreenium ; Groupe INP ; Concours Agro-Véto</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" spans="1:12" ht="130" customHeight="130">
+      <c r="L34" s="3" t="s">
+        <v>1262</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" ht="259.2">
       <c r="A35" s="3" t="s">
         <v>403</v>
       </c>
@@ -14052,10 +14668,8 @@
       <c r="F35" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="G35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">L’ESBS (École supérieure de biotechnologie de Strasbourg), à Illkirch-Graffenstaden, forme des ingénieurs en biotechnologie, avec des spécialisations en analyse haut-débit, biologie synthétique, et bioproduction et biomédicaments. Elle propose aussi, avec l’ECPM, le diplôme ChemBiotech (chimie et biotechnologie). Elle recrute les élèves de BCPST via le concours Polytech BCPST (8 places), 2 places étant ouvertes en TB.</t>
-        </is>
+      <c r="G35" s="3" t="s">
+        <v>1203</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>546</v>
@@ -14069,10 +14683,8 @@
       <c r="K35" s="3" t="s">
         <v>626</v>
       </c>
-      <c r="L35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Biotechnologies ; Analyse haut-débit ; Biologie synthétique ; Bioproduction ; Biomédicaments ; ChemBiotech ; Industrie pharmaceutique ; Santé ; Concours Polytech BCPST ; Strasbourg</t>
-        </is>
+      <c r="L35" s="3" t="s">
+        <v>1263</v>
       </c>
     </row>
     <row r="36" spans="1:12" ht="44.25" customHeight="1">
@@ -14113,7 +14725,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="37" spans="1:12" ht="99" customHeight="99">
+    <row r="37" spans="1:12" ht="172.8">
       <c r="A37" s="3" t="s">
         <v>441</v>
       </c>
@@ -14132,10 +14744,8 @@
       <c r="F37" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="G37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Les universités toulousaines (notamment l’Université Toulouse III – Paul Sabatier) proposent des licences et masters scientifiques en sciences de la vie, sciences de la Terre, chimie, physique et mathématiques. Les étudiants issus de BCPST ou de TB peuvent candidater sur dossier pour poursuivre en licence ou en master.</t>
-        </is>
+      <c r="G37" s="3" t="s">
+        <v>1204</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>536</v>
@@ -14149,13 +14759,11 @@
       <c r="K37" s="5" t="s">
         <v>633</v>
       </c>
-      <c r="L37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sciences de la vie ; Sciences de la Terre ; Chimie ; Physique ; Licence ; Master ; Recherche ; Poursuite d’études sur dossier</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" spans="1:12" ht="83" customHeight="83">
+      <c r="L37" s="3" t="s">
+        <v>1256</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" ht="187.2">
       <c r="A38" s="3" t="s">
         <v>444</v>
       </c>
@@ -14174,10 +14782,8 @@
       <c r="F38" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="G38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">L’Université de Rennes propose des licences et masters scientifiques en sciences de la vie, sciences de la Terre et de l’environnement, chimie, physique et mathématiques. Les étudiants issus de BCPST ou de TB peuvent candidater sur dossier pour poursuivre en licence ou en master.</t>
-        </is>
+      <c r="G38" s="3" t="s">
+        <v>1205</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>514</v>
@@ -14191,13 +14797,11 @@
       <c r="K38" s="3" t="s">
         <v>636</v>
       </c>
-      <c r="L38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sciences de la vie ; Sciences de la Terre ; Environnement ; Chimie ; Physique ; Licence ; Master ; Recherche ; Poursuite d’études sur dossier</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" spans="1:12" ht="99" customHeight="99">
+      <c r="L38" s="3" t="s">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" ht="187.2">
       <c r="A39" s="3" t="s">
         <v>446</v>
       </c>
@@ -14216,10 +14820,8 @@
       <c r="F39" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">L’UFR Sciences et Techniques de l’Université de Rouen Normandie (Mont-Saint-Aignan) propose des licences et masters scientifiques en sciences de la vie, chimie, physique, mathématiques et informatique. Les étudiants issus de BCPST ou de TB peuvent candidater sur dossier pour poursuivre en licence ou en master.</t>
-        </is>
+      <c r="G39" s="3" t="s">
+        <v>1206</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>577</v>
@@ -14233,13 +14835,11 @@
       <c r="K39" s="3" t="s">
         <v>638</v>
       </c>
-      <c r="L39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sciences de la vie ; Chimie ; Physique ; Mathématiques ; Informatique ; Licence ; Master ; Recherche ; Poursuite d’études sur dossier</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" spans="1:12" ht="99" customHeight="99">
+      <c r="L39" s="3" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" ht="187.2">
       <c r="A40" s="3" t="s">
         <v>448</v>
       </c>
@@ -14258,10 +14858,8 @@
       <c r="F40" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="G40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">L’Université d’Évry Paris-Saclay est implantée au cœur du Genopole, biocluster français consacré à la génomique et aux biotechnologies. Elle propose des licences et masters scientifiques, notamment dans les sciences de la vie. Les étudiants issus de BCPST ou de TB peuvent candidater sur dossier.</t>
-        </is>
+      <c r="G40" s="3" t="s">
+        <v>1207</v>
       </c>
       <c r="H40" s="3" t="s">
         <v>639</v>
@@ -14275,13 +14873,11 @@
       <c r="K40" s="3" t="s">
         <v>642</v>
       </c>
-      <c r="L40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sciences de la vie ; Génomique ; Biotechnologies ; Genopole ; Licence ; Master ; Recherche ; Paris-Saclay ; Poursuite d’études sur dossier</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" spans="1:12" ht="99" customHeight="99">
+      <c r="L40" s="3" t="s">
+        <v>1266</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" ht="172.8">
       <c r="A41" s="3" t="s">
         <v>451</v>
       </c>
@@ -14300,10 +14896,8 @@
       <c r="F41" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="G41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">La faculté des sciences d’Orsay, composante de l’Université Paris-Saclay, propose des licences et masters scientifiques (sciences de la vie, chimie, physique, mathématiques), adossés à de nombreux laboratoires de recherche. Les étudiants issus de BCPST ou de TB peuvent candidater sur dossier pour poursuivre en licence ou en master.</t>
-        </is>
+      <c r="G41" s="3" t="s">
+        <v>1208</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>495</v>
@@ -14317,10 +14911,8 @@
       <c r="K41" s="3" t="s">
         <v>645</v>
       </c>
-      <c r="L41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sciences de la vie ; Chimie ; Physique ; Mathématiques ; Licence ; Master ; Recherche ; Paris-Saclay ; Poursuite d’études sur dossier</t>
-        </is>
+      <c r="L41" s="3" t="s">
+        <v>1267</v>
       </c>
     </row>
     <row r="42" spans="1:12" ht="72" customHeight="1">
@@ -14361,7 +14953,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="43" spans="1:12" ht="99" customHeight="99">
+    <row r="43" spans="1:12" ht="187.2">
       <c r="A43" s="10" t="s">
         <v>473</v>
       </c>
@@ -14380,10 +14972,8 @@
       <c r="F43" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="G43" s="100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">L’ENS de Lyon est une école normale supérieure scientifique et littéraire. Elle recrute les élèves de BCPST via le concours ENS (environ 33 places, statut d’élève fonctionnaire). La formation est tournée vers la recherche (master, doctorat), avec un double cursus ingénieur-chercheur possible avec Centrale Lyon.</t>
-        </is>
+      <c r="G43" s="100" t="s">
+        <v>1209</v>
       </c>
       <c r="H43" s="10" t="s">
         <v>540</v>
@@ -14397,13 +14987,11 @@
       <c r="K43" s="5" t="s">
         <v>652</v>
       </c>
-      <c r="L43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Recherche ; Biologie ; Master ; Doctorat ; Double diplôme ; Ingénieur-chercheur ; Concours ENS BCPST ; Élèves fonctionnaires ; Lyon</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" spans="1:12" ht="114" customHeight="114">
+      <c r="L43" s="3" t="s">
+        <v>1268</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" ht="172.8">
       <c r="A44" s="10" t="s">
         <v>653</v>
       </c>
@@ -14422,10 +15010,8 @@
       <c r="F44" s="10" t="s">
         <v>494</v>
       </c>
-      <c r="G44" s="100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">L’École normale supérieure – PSL (rue d’Ulm, Paris) est une école normale supérieure pluridisciplinaire (sciences, lettres, sciences humaines) adossée à l’Université PSL. Elle recrute les élèves de BCPST via le concours ENS (environ 21 places, statut d’élève fonctionnaire). La formation est tournée vers la recherche, jusqu’au master et au doctorat.</t>
-        </is>
+      <c r="G44" s="100" t="s">
+        <v>1210</v>
       </c>
       <c r="H44" s="10" t="s">
         <v>495</v>
@@ -14439,13 +15025,11 @@
       <c r="K44" s="5" t="s">
         <v>656</v>
       </c>
-      <c r="L44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Recherche ; Interdisciplinarité ; Biologie ; Master ; Doctorat ; Concours ENS BCPST ; Élèves fonctionnaires ; PSL ; Paris</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" spans="1:12" ht="99" customHeight="99">
+      <c r="L44" s="3" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" ht="158.4">
       <c r="A45" s="14" t="s">
         <v>657</v>
       </c>
@@ -14460,10 +15044,8 @@
       <c r="F45" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="G45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CentraleSupélec est une grande école d’ingénieurs généraliste du Groupe des écoles Centrale, sur le plateau de Paris-Saclay, avec des domaines forts en numérique et en énergie. Les élèves de BCPST peuvent y accéder via le concours Agro-Véto, pour un nombre limité de places (campus de Metz).</t>
-        </is>
+      <c r="G45" s="3" t="s">
+        <v>1211</v>
       </c>
       <c r="H45" s="15" t="s">
         <v>495</v>
@@ -14477,13 +15059,11 @@
       <c r="K45" s="3" t="s">
         <v>661</v>
       </c>
-      <c r="L45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ingénierie généraliste ; Numérique ; Énergie ; Paris-Saclay ; Campus de Metz ; Concours Agro-Véto ; Groupe Centrale</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" spans="1:12" ht="114" customHeight="114">
+      <c r="L45" s="3" t="s">
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" ht="230.4">
       <c r="A46" s="12" t="s">
         <v>662</v>
       </c>
@@ -14502,10 +15082,8 @@
       <c r="F46" s="10" t="s">
         <v>494</v>
       </c>
-      <c r="G46" s="100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">L’École nationale supérieure de paysage (ENSP), à Versailles et Marseille, délivre le diplôme d’État de paysagiste (DEP), qui confère le grade de master. Le cycle dure 3 ans (apprentissage possible dès la 2e année) et mène au métier de paysagiste concepteur ; une admission en 2e année est possible sur titre avec un bac+3 (dossier et épreuves orales).</t>
-        </is>
+      <c r="G46" s="100" t="s">
+        <v>1212</v>
       </c>
       <c r="H46" s="10" t="s">
         <v>663</v>
@@ -14519,13 +15097,11 @@
       <c r="K46" s="3" t="s">
         <v>666</v>
       </c>
-      <c r="L46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Paysage ; Paysagiste concepteur ; Projet de paysage ; Diplôme d’État de paysagiste ; Grade de master ; Apprentissage ; Admission sur titre ; Versailles ; Marseille</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" spans="1:12" ht="83" customHeight="83">
+      <c r="L46" s="3" t="s">
+        <v>1271</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" ht="172.8">
       <c r="A47" s="12" t="s">
         <v>667</v>
       </c>
@@ -14540,10 +15116,8 @@
       <c r="F47" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="G47" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IMT Mines Albi (Albi-Carmaux) est une école d’ingénieurs généraliste de l’Institut Mines-Télécom, avec des domaines forts en génie des procédés, énergie et matériaux. Elle recrute les élèves de BCPST via le concours G2E (7 places en 2026).</t>
-        </is>
+      <c r="G47" s="3" t="s">
+        <v>1213</v>
       </c>
       <c r="H47" s="10" t="s">
         <v>668</v>
@@ -14557,13 +15131,11 @@
       <c r="K47" s="3" t="s">
         <v>671</v>
       </c>
-      <c r="L47" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ingénierie généraliste ; Génie des procédés ; Énergie ; Matériaux ; Transitions ; Concours G2E ; Institut Mines-Télécom ; Albi</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" spans="1:12" ht="68" customHeight="68">
+      <c r="L47" s="3" t="s">
+        <v>1272</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" ht="158.4">
       <c r="A48" s="12" t="s">
         <v>672</v>
       </c>
@@ -14578,10 +15150,8 @@
       <c r="F48" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="G48" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IMT Mines Alès est une école d’ingénieurs généraliste de l’Institut Mines-Télécom, avec des domaines forts en risques, environnement et génie civil. Elle recrute les élèves de BCPST via le concours G2E (6 places en 2026).</t>
-        </is>
+      <c r="G48" s="3" t="s">
+        <v>1214</v>
       </c>
       <c r="H48" s="10" t="s">
         <v>673</v>
@@ -14595,13 +15165,11 @@
       <c r="K48" s="3" t="s">
         <v>676</v>
       </c>
-      <c r="L48" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ingénierie généraliste ; Risques ; Environnement ; Génie civil ; Concours G2E ; Institut Mines-Télécom ; Alès</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" spans="1:12" ht="83" customHeight="83">
+      <c r="L48" s="3" t="s">
+        <v>1273</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" ht="158.4">
       <c r="A49" s="12" t="s">
         <v>677</v>
       </c>
@@ -14616,10 +15184,8 @@
       <c r="F49" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="G49" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IMT Nord Europe est une école d’ingénieurs de l’Institut Mines-Télécom, implantée à Douai et à Lille, avec des domaines forts en énergie, environnement et numérique. Elle recrute les élèves de BCPST via le concours G2E (4 places en 2026).</t>
-        </is>
+      <c r="G49" s="3" t="s">
+        <v>1215</v>
       </c>
       <c r="H49" s="10" t="s">
         <v>678</v>
@@ -14633,13 +15199,11 @@
       <c r="K49" s="3" t="s">
         <v>681</v>
       </c>
-      <c r="L49" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ingénierie généraliste ; Énergie ; Environnement ; Numérique ; Concours G2E ; Institut Mines-Télécom ; Douai ; Lille</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" spans="1:12" ht="99" customHeight="99">
+      <c r="L49" s="3" t="s">
+        <v>1274</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" ht="144">
       <c r="A50" s="12" t="s">
         <v>682</v>
       </c>
@@ -14658,10 +15222,8 @@
       <c r="F50" s="10" t="s">
         <v>494</v>
       </c>
-      <c r="G50" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Polytech Annecy-Chambéry, école d’ingénieurs de l’Université Savoie Mont Blanc (réseau Polytech), propose cinq spécialités d’ingénieur, dont la spécialité Bâtiment (Bâtiment – Écoconstruction – Énergie) et la mécanique. Les études comprennent environ 39 semaines de stage sur l’ensemble du cursus.</t>
-        </is>
+      <c r="G50" s="3" t="s">
+        <v>1216</v>
       </c>
       <c r="H50" s="12" t="s">
         <v>683</v>
@@ -14675,13 +15237,11 @@
       <c r="K50" s="3" t="s">
         <v>686</v>
       </c>
-      <c r="L50" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bâtiment ; Écoconstruction ; Énergie ; Environnement ; Mécanique ; Stages ; Annecy ; Chambéry</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" spans="1:12" ht="114" customHeight="114">
+      <c r="L50" s="3" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" ht="230.4">
       <c r="A51" s="12" t="s">
         <v>687</v>
       </c>
@@ -14700,10 +15260,8 @@
       <c r="F51" s="12" t="s">
         <v>494</v>
       </c>
-      <c r="G51" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Polytech Sorbonne est l’école d’ingénieurs de Sorbonne Université (réseau Polytech), à Paris. Elle propose notamment les spécialités agroalimentaire, matériaux et sciences de la Terre (aménagement, risques, géo-énergies), accessibles aux élèves de BCPST via le concours Polytech BCPST, ainsi que l’électronique et informatique, la robotique, les mathématiques appliquées et le génie mécanique.</t>
-        </is>
+      <c r="G51" s="3" t="s">
+        <v>1217</v>
       </c>
       <c r="H51" s="12" t="s">
         <v>495</v>
@@ -14717,13 +15275,11 @@
       <c r="K51" s="3" t="s">
         <v>690</v>
       </c>
-      <c r="L51" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Agroalimentaire ; Matériaux ; Sciences de la Terre ; Aménagement ; Risques ; Géo-énergies ; Robotique ; Électronique et informatique ; Concours Polytech BCPST ; Paris</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" spans="1:12" ht="161" customHeight="161">
+      <c r="L51" s="3" t="s">
+        <v>1276</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" ht="360">
       <c r="A52" s="12" t="s">
         <v>691</v>
       </c>
@@ -14742,10 +15298,8 @@
       <c r="F52" s="12" t="s">
         <v>494</v>
       </c>
-      <c r="G52" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Polytech Orléans est l’école d’ingénieurs de l’Université d’Orléans (réseau Polytech). Elle propose notamment les spécialités génie civil et environnement (parcours constructions durables, géo-environnement et villes durables, travaux publics et aménagement), énergétique, génie physique et systèmes embarqués, matériaux et mécatronique, et génie industriel (site de Chartres). Pour les élèves de BCPST, le concours Polytech BCPST ouvre notamment le génie civil et géo-environnement et le génie industriel pour la cosmétique, la pharmacie et l’agroalimentaire.</t>
-        </is>
+      <c r="G52" s="3" t="s">
+        <v>1218</v>
       </c>
       <c r="H52" s="12" t="s">
         <v>594</v>
@@ -14759,13 +15313,11 @@
       <c r="K52" s="3" t="s">
         <v>694</v>
       </c>
-      <c r="L52" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Génie civil et environnement ; Constructions durables ; Géo-environnement ; Villes durables ; Travaux publics ; Énergétique ; Matériaux et mécatronique ; Génie industriel ; Cosmétique ; Pharmacie ; Agroalimentaire ; Concours Polytech BCPST</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" spans="1:12" ht="99" customHeight="99">
+      <c r="L52" s="3" t="s">
+        <v>1277</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" ht="216">
       <c r="A53" s="12" t="s">
         <v>695</v>
       </c>
@@ -14780,10 +15332,8 @@
       <c r="F53" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="G53" s="100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">L’ENTPE (École nationale des travaux publics de l’État), à Vaulx-en-Velin près de Lyon, se présente comme l’école de l’aménagement durable des territoires : génie civil, bâtiment, transports, énergie et environnement. Elle recrute les élèves de BCPST via le concours G2E, avec un statut civil ou fonctionnaire.</t>
-        </is>
+      <c r="G53" s="100" t="s">
+        <v>1219</v>
       </c>
       <c r="H53" s="10" t="s">
         <v>540</v>
@@ -14797,13 +15347,11 @@
       <c r="K53" s="3" t="s">
         <v>698</v>
       </c>
-      <c r="L53" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Aménagement durable des territoires ; Génie civil ; Bâtiment ; Transports ; Énergie ; Environnement ; Concours G2E ; Élèves fonctionnaires ; Vaulx-en-Velin</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" spans="1:12" ht="99" customHeight="99">
+      <c r="L53" s="3" t="s">
+        <v>1278</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" ht="144">
       <c r="A54" s="12" t="s">
         <v>699</v>
       </c>
@@ -14818,10 +15366,8 @@
       <c r="F54" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="G54" s="100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">L’EIVP (École des ingénieurs de la Ville de Paris) forme des ingénieurs en génie urbain : conception et gestion de la ville, infrastructures, eau, génie civil. Elle recrute les élèves de BCPST via le concours G2E (statut civil ou fonctionnaire) et débouche notamment sur des carrières dans les collectivités et les bureaux d’études.</t>
-        </is>
+      <c r="G54" s="100" t="s">
+        <v>1220</v>
       </c>
       <c r="H54" s="10" t="s">
         <v>495</v>
@@ -14835,13 +15381,11 @@
       <c r="K54" s="3" t="s">
         <v>702</v>
       </c>
-      <c r="L54" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Génie urbain ; Ville ; Infrastructures ; Eau ; Génie civil ; Collectivités ; Bureaux d’études ; Concours G2E ; Paris</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" spans="1:12" ht="130" customHeight="130">
+      <c r="L54" s="3" t="s">
+        <v>1279</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" ht="230.4">
       <c r="A55" s="12" t="s">
         <v>703</v>
       </c>
@@ -14856,10 +15400,8 @@
       <c r="F55" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="G55" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">L’EOST (École et observatoire des sciences de la Terre), à Strasbourg, est la seule école d’ingénieurs géophysiciens de France. Elle recrute les élèves de BCPST via le concours G2E (13 places en 2026). Les parcours de 3e année comprennent notamment la géophysique appliquée à la géotechnique, à l’eau et à l’environnement, et les géosciences pour la transition énergétique ; les débouchés vont de l’exploration-production à la géotechnique.</t>
-        </is>
+      <c r="G55" s="3" t="s">
+        <v>1221</v>
       </c>
       <c r="H55" s="10" t="s">
         <v>546</v>
@@ -14873,13 +15415,11 @@
       <c r="K55" s="3" t="s">
         <v>706</v>
       </c>
-      <c r="L55" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Géophysique ; Sciences de la Terre ; Géotechnique ; Eau ; Environnement ; Transition énergétique ; Exploration-production ; Risques naturels ; Concours G2E ; Strasbourg</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" spans="1:12" ht="145" customHeight="145">
+      <c r="L55" s="3" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" ht="259.2">
       <c r="A56" s="12" t="s">
         <v>250</v>
       </c>
@@ -14894,10 +15434,8 @@
       <c r="F56" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="G56" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">L’ENSG (École nationale supérieure de géologie), à Vandœuvre-lès-Nancy, est une école d’ingénieurs de l’Université de Lorraine créée en 1908, spécialisée en géosciences. Les parcours de 2e année couvrent les eaux et l’environnement, la géologie des énergies, la géologie numérique et les sciences des données, la géotechnique-génie civil, les matières premières minérales, et les réservoirs et stockages d’énergie. Elle recrute les élèves de BCPST via le concours G2E.</t>
-        </is>
+      <c r="G56" s="3" t="s">
+        <v>1222</v>
       </c>
       <c r="H56" s="12" t="s">
         <v>507</v>
@@ -14911,13 +15449,11 @@
       <c r="K56" s="3" t="s">
         <v>709</v>
       </c>
-      <c r="L56" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Géologie ; Eaux et environnement ; Géologie des énergies ; Géologie numérique ; Sciences des données ; Géotechnique ; Matières premières minérales ; Stockage d’énergie ; Concours G2E ; Nancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" spans="1:12" ht="68" customHeight="68">
+      <c r="L56" s="3" t="s">
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" ht="129.6">
       <c r="A57" s="12" t="s">
         <v>710</v>
       </c>
@@ -14932,10 +15468,8 @@
       <c r="F57" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="G57" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">L’École polytechnique (Palaiseau) est une grande école d’ingénieurs pluridisciplinaire à très forte dimension scientifique. Les élèves de BCPST peuvent l’intégrer via le concours X-BIO (13 places).</t>
-        </is>
+      <c r="G57" s="3" t="s">
+        <v>1223</v>
       </c>
       <c r="H57" s="10" t="s">
         <v>712</v>
@@ -14949,13 +15483,11 @@
       <c r="K57" s="3" t="s">
         <v>715</v>
       </c>
-      <c r="L57" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ingénierie généraliste ; Sciences fondamentales ; Biologie ; Recherche ; Concours X-BIO ; Palaiseau</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" spans="1:12" ht="130" customHeight="130">
+      <c r="L57" s="3" t="s">
+        <v>1282</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" ht="230.4">
       <c r="A58" s="12" t="s">
         <v>716</v>
       </c>
@@ -14970,10 +15502,8 @@
       <c r="F58" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="G58" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Centrale Lyon, à Écully, est une école d’ingénieurs généraliste du Groupe Centrale, orientée vers l’industrie. Elle propose de nombreux doubles diplômes : ingénieur-chercheur avec l’ENS de Lyon, ingénieur-médecin, ingénieur-manager (emlyon), architecte-ingénieur (ENSAL), ingénieur-économètre (ENSAE). Elle ouvre des places aux élèves de BCPST via la banque ENS-Ponts-Mines Paris-Écoles Centrale (environ 5 places).</t>
-        </is>
+      <c r="G58" s="3" t="s">
+        <v>1224</v>
       </c>
       <c r="H58" s="12" t="s">
         <v>718</v>
@@ -14987,13 +15517,11 @@
       <c r="K58" s="5" t="s">
         <v>721</v>
       </c>
-      <c r="L58" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ingénierie généraliste ; Industrie ; Double diplôme ; Ingénieur-chercheur ; Ingénieur-médecin ; Ingénieur-manager ; Architecte-ingénieur ; Concours BCPST ; Écully</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" spans="1:12" ht="130" customHeight="130">
+      <c r="L58" s="3" t="s">
+        <v>1283</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" ht="216">
       <c r="A59" s="12" t="s">
         <v>722</v>
       </c>
@@ -15008,10 +15536,8 @@
       <c r="F59" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="G59" s="100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Centrale Nantes est une école d’ingénieurs généraliste du Groupe Centrale, orientée vers l’industrie et le domaine maritime. Elle propose des doubles diplômes (ingénieur-architecte avec l’ENSA Nantes, ingénieur-manager avec Audencia, ingénieur-pharmacien avec Nantes Université) et l’apprentissage. Elle ouvre des places aux élèves de BCPST via la banque ENS-Ponts-Mines Paris-Écoles Centrale (environ 5 places).</t>
-        </is>
+      <c r="G59" s="100" t="s">
+        <v>1225</v>
       </c>
       <c r="H59" s="10" t="s">
         <v>499</v>
@@ -15025,13 +15551,11 @@
       <c r="K59" s="3" t="s">
         <v>725</v>
       </c>
-      <c r="L59" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ingénierie généraliste ; Industrie ; Maritime ; Double diplôme ; Ingénieur-architecte ; Ingénieur-pharmacien ; Apprentissage ; Concours BCPST ; Nantes</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" spans="1:12" ht="83" customHeight="83">
+      <c r="L59" s="3" t="s">
+        <v>1284</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" ht="115.2">
       <c r="A60" s="12" t="s">
         <v>726</v>
       </c>
@@ -15046,10 +15570,8 @@
       <c r="F60" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="G60" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Centrale Méditerranée, à Marseille, est une école d’ingénieurs généraliste du Groupe Centrale, orientée vers l’industrie. Elle ouvre des places aux élèves de BCPST via la banque ENS-Ponts-Mines Paris-Écoles Centrale (environ 5 places).</t>
-        </is>
+      <c r="G60" s="3" t="s">
+        <v>1226</v>
       </c>
       <c r="H60" s="10" t="s">
         <v>646</v>
@@ -15063,13 +15585,11 @@
       <c r="K60" s="3" t="s">
         <v>729</v>
       </c>
-      <c r="L60" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ingénierie généraliste ; Industrie ; Concours BCPST ; Marseille ; Groupe Centrale</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" spans="1:12" ht="68" customHeight="68">
+      <c r="L60" s="3" t="s">
+        <v>1285</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" ht="100.8">
       <c r="A61" s="3" t="s">
         <v>730</v>
       </c>
@@ -15084,10 +15604,8 @@
       <c r="F61" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="G61" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mines Paris – PSL est une grande école d’ingénieurs généraliste, qui forme les ingénieurs civils des Mines. Les élèves de BCPST peuvent l’intégrer via la banque ENS-Ponts-Mines Paris-Écoles Centrale (environ 4 places).</t>
-        </is>
+      <c r="G61" s="3" t="s">
+        <v>1227</v>
       </c>
       <c r="H61" s="10" t="s">
         <v>495</v>
@@ -15101,13 +15619,11 @@
       <c r="K61" s="3" t="s">
         <v>734</v>
       </c>
-      <c r="L61" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ingénierie généraliste ; Ingénieur civil des Mines ; PSL ; Concours BCPST ; Paris</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" spans="1:12" ht="99" customHeight="99">
+      <c r="L61" s="3" t="s">
+        <v>1286</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" ht="216">
       <c r="A62" s="10" t="s">
         <v>735</v>
       </c>
@@ -15122,10 +15638,8 @@
       <c r="F62" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="G62" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">L’École des Ponts ParisTech (École nationale des ponts et chaussées), à Champs-sur-Marne, forme des ingénieurs généralistes (génie civil, ville, transports, environnement, ingénierie mathématique et informatique, génie industriel). Les élèves de BCPST peuvent l’intégrer via la banque ENS-Ponts-Mines Paris-Écoles Centrale (environ 4 places).</t>
-        </is>
+      <c r="G62" s="3" t="s">
+        <v>1228</v>
       </c>
       <c r="H62" s="12" t="s">
         <v>736</v>
@@ -15139,13 +15653,11 @@
       <c r="K62" s="3" t="s">
         <v>739</v>
       </c>
-      <c r="L62" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Génie civil ; Ville ; Transports ; Environnement ; Ingénierie mathématique ; Génie industriel ; Ingénierie généraliste ; Concours BCPST ; Champs-sur-Marne</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" spans="1:12" ht="114" customHeight="114">
+      <c r="L62" s="3" t="s">
+        <v>1287</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" ht="288">
       <c r="A63" s="17" t="s">
         <v>740</v>
       </c>
@@ -15158,10 +15670,8 @@
       <c r="F63" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="G63" s="100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bordeaux INP est un réseau de grandes écoles d’ingénieurs. Les élèves de BCPST s’orientent notamment vers l’ENSTBB (biotechnologie), l’ENSMAC (ex-ENSCBP : agroalimentaire-génie biologique, chimie-génie physique, accessible via le concours PC BIO) ou l’ENSEGID (géoressources, environnement et ingénierie du développement durable, accessible via le concours G2E).</t>
-        </is>
+      <c r="G63" s="100" t="s">
+        <v>1229</v>
       </c>
       <c r="H63" s="18" t="s">
         <v>503</v>
@@ -15175,13 +15685,11 @@
       <c r="K63" s="5" t="s">
         <v>744</v>
       </c>
-      <c r="L63" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Réseau d’écoles ; Biotechnologie ; Agroalimentaire ; Génie biologique ; Chimie ; Génie physique ; Géoressources ; Hydrogéologie ; Environnement ; Concours PC BIO ; Concours G2E</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" spans="1:12" ht="68" customHeight="68">
+      <c r="L63" s="3" t="s">
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" ht="86.4">
       <c r="A64" s="18" t="s">
         <v>745</v>
       </c>
@@ -15194,10 +15702,8 @@
       <c r="F64" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="G64" s="100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Chimie ParisTech – PSL (École nationale supérieure de chimie de Paris) est une école d’ingénieurs spécialisée en chimie. Les élèves de BCPST peuvent l’intégrer via le concours PC BIO, qui ouvre un petit nombre de places.</t>
-        </is>
+      <c r="G64" s="100" t="s">
+        <v>1230</v>
       </c>
       <c r="H64" s="18" t="s">
         <v>495</v>
@@ -15211,13 +15717,11 @@
       <c r="K64" s="3" t="s">
         <v>748</v>
       </c>
-      <c r="L64" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Chimie ; Ingénierie chimique ; Concours PC BIO ; PSL ; Paris</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" spans="1:13" ht="83" customHeight="83">
+      <c r="L64" s="3" t="s">
+        <v>1289</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" ht="115.2">
       <c r="A65" s="18" t="s">
         <v>749</v>
       </c>
@@ -15230,10 +15734,8 @@
       <c r="F65" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="G65" s="101" t="inlineStr">
-        <is>
-          <t xml:space="preserve">L’ENSC Lille (École nationale supérieure de chimie de Lille), école d’ingénieurs spécialisée en chimie, fait partie de Centrale Lille Institut. Les élèves de BCPST peuvent l’intégrer via le concours PC BIO, qui ouvre un petit nombre de places.</t>
-        </is>
+      <c r="G65" s="101" t="s">
+        <v>1231</v>
       </c>
       <c r="H65" s="18" t="s">
         <v>613</v>
@@ -15247,13 +15749,11 @@
       <c r="K65" s="3" t="s">
         <v>752</v>
       </c>
-      <c r="L65" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Chimie ; Ingénierie chimique ; Concours PC BIO ; Centrale Lille Institut ; Lille</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" spans="1:13" ht="68" customHeight="68">
+      <c r="L65" s="3" t="s">
+        <v>1290</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" ht="86.4">
       <c r="A66" s="18" t="s">
         <v>753</v>
       </c>
@@ -15266,10 +15766,8 @@
       <c r="F66" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="G66" s="101" t="inlineStr">
-        <is>
-          <t xml:space="preserve">L’ENSCM (École nationale supérieure de chimie de Montpellier) est une école d’ingénieurs spécialisée en chimie. Les élèves de BCPST peuvent l’intégrer via le concours PC BIO, qui ouvre un petit nombre de places.</t>
-        </is>
+      <c r="G66" s="101" t="s">
+        <v>1232</v>
       </c>
       <c r="H66" s="18" t="s">
         <v>527</v>
@@ -15283,13 +15781,11 @@
       <c r="K66" s="5" t="s">
         <v>756</v>
       </c>
-      <c r="L66" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Chimie ; Ingénierie chimique ; Concours PC BIO ; Montpellier</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" spans="1:13" ht="83" customHeight="83">
+      <c r="L66" s="3" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" ht="129.6">
       <c r="A67" s="18" t="s">
         <v>757</v>
       </c>
@@ -15302,10 +15798,8 @@
       <c r="F67" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="G67" s="101" t="inlineStr">
-        <is>
-          <t xml:space="preserve">L’ESPCI Paris – PSL est une école d’ingénieurs scientifique, qui allie physique, chimie et biologie avec une forte orientation recherche. Les élèves de BCPST peuvent l’intégrer via le concours PC BIO, qui ouvre un petit nombre de places.</t>
-        </is>
+      <c r="G67" s="101" t="s">
+        <v>1233</v>
       </c>
       <c r="H67" s="18" t="s">
         <v>495</v>
@@ -15319,13 +15813,11 @@
       <c r="K67" s="3" t="s">
         <v>760</v>
       </c>
-      <c r="L67" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Physique ; Chimie ; Biologie ; Recherche ; Interdisciplinarité ; Concours PC BIO ; PSL ; Paris</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" spans="1:13" ht="83" customHeight="83">
+      <c r="L67" s="3" t="s">
+        <v>1292</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" ht="129.6">
       <c r="A68" s="18" t="s">
         <v>761</v>
       </c>
@@ -15338,10 +15830,8 @@
       <c r="F68" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="G68" s="101" t="inlineStr">
-        <is>
-          <t xml:space="preserve">L’ENSIC (École nationale supérieure des industries chimiques), à Nancy, est une école d’ingénieurs de Lorraine INP spécialisée dans le génie des procédés et la chimie. Les élèves de BCPST peuvent l’intégrer via le concours PC BIO, qui ouvre un petit nombre de places.</t>
-        </is>
+      <c r="G68" s="101" t="s">
+        <v>1234</v>
       </c>
       <c r="H68" s="18" t="s">
         <v>762</v>
@@ -15355,13 +15845,11 @@
       <c r="K68" s="3" t="s">
         <v>765</v>
       </c>
-      <c r="L68" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Génie des procédés ; Chimie ; Industries chimiques ; Concours PC BIO ; Lorraine INP ; Nancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" spans="1:13" ht="130" customHeight="130">
+      <c r="L68" s="3" t="s">
+        <v>1293</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" ht="409.6">
       <c r="A69" s="28" t="s">
         <v>194</v>
       </c>
@@ -15380,10 +15868,8 @@
       <c r="F69" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="G69" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Polytech Nantes est l’école d’ingénieurs de Nantes Université (réseau Polytech), avec des campus à Nantes, Saint-Nazaire et La Roche-sur-Yon. Les élèves de BCPST peuvent y intégrer la spécialité Génie des procédés et bioprocédés (site de Saint-Nazaire, 3 places via le concours Polytech BCPST), avec des options en 3e année : bio-industries, industries chimiques et écotechnologies, management de la qualité, de la sécurité et de l’environnement.</t>
-        </is>
+      <c r="G69" s="3" t="s">
+        <v>1235</v>
       </c>
       <c r="H69" s="28" t="s">
         <v>499</v>
@@ -15397,10 +15883,8 @@
       <c r="K69" s="3" t="s">
         <v>768</v>
       </c>
-      <c r="L69" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Génie des procédés et bioprocédés ; Biotechnologies ; Bio-industries ; Industries chimiques ; Écotechnologies ; Environnement ; Qualité-sécurité-environnement ; Concours Polytech BCPST ; Saint-Nazaire</t>
-        </is>
+      <c r="L69" s="3" t="s">
+        <v>1294</v>
       </c>
     </row>
     <row r="70" spans="1:13" ht="409.6" customHeight="1">
@@ -15444,7 +15928,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="71" spans="1:13" ht="105">
+    <row r="71" spans="1:13" ht="100.8">
       <c r="A71" s="3" t="s">
         <v>892</v>
       </c>
@@ -15482,7 +15966,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="72" spans="1:13" ht="150">
+    <row r="72" spans="1:13" ht="129.6">
       <c r="A72" s="3" t="s">
         <v>900</v>
       </c>
@@ -15520,7 +16004,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="73" spans="1:13" ht="75">
+    <row r="73" spans="1:13" ht="72">
       <c r="A73" s="3" t="s">
         <v>947</v>
       </c>
@@ -15552,7 +16036,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="74" spans="1:13" ht="120">
+    <row r="74" spans="1:13" ht="100.8">
       <c r="A74" s="82" t="s">
         <v>970</v>
       </c>
@@ -15584,7 +16068,7 @@
         <v>974</v>
       </c>
     </row>
-    <row r="75" spans="1:13" ht="135">
+    <row r="75" spans="1:13" ht="129.6">
       <c r="A75" s="84" t="s">
         <v>980</v>
       </c>
@@ -15622,7 +16106,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="76" spans="1:13" ht="150">
+    <row r="76" spans="1:13" ht="129.6">
       <c r="A76" s="86" t="s">
         <v>986</v>
       </c>
@@ -15660,7 +16144,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="77" spans="1:13" ht="360">
+    <row r="77" spans="1:13" ht="331.2">
       <c r="A77" s="89" t="s">
         <v>1001</v>
       </c>
@@ -15698,7 +16182,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="78" spans="1:13" ht="135">
+    <row r="78" spans="1:13" ht="115.2">
       <c r="A78" s="89" t="s">
         <v>1009</v>
       </c>
@@ -15736,7 +16220,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="79" spans="1:13" ht="120">
+    <row r="79" spans="1:13" ht="115.2">
       <c r="A79" s="88" t="s">
         <v>1052</v>
       </c>
@@ -15774,7 +16258,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="80" spans="1:13" ht="120">
+    <row r="80" spans="1:13" ht="100.8">
       <c r="A80" s="89" t="s">
         <v>1080</v>
       </c>
@@ -15806,7 +16290,7 @@
         <v>1084</v>
       </c>
     </row>
-    <row r="81" spans="1:12" ht="150">
+    <row r="81" spans="1:12" ht="129.6">
       <c r="A81" s="89" t="s">
         <v>1138</v>
       </c>
@@ -15842,6 +16326,50 @@
       </c>
       <c r="L81" s="88" t="s">
         <v>1142</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12">
+      <c r="A82" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B82" t="s">
+        <v>1309</v>
+      </c>
+      <c r="C82" t="s">
+        <v>1309</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12">
+      <c r="A83" t="s">
+        <v>1310</v>
+      </c>
+      <c r="B83" t="s">
+        <v>1309</v>
+      </c>
+      <c r="C83" t="s">
+        <v>1309</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12">
+      <c r="A84" t="s">
+        <v>1311</v>
+      </c>
+      <c r="B84" t="s">
+        <v>1309</v>
+      </c>
+      <c r="C84" t="s">
+        <v>1309</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12">
+      <c r="A85" t="s">
+        <v>1331</v>
+      </c>
+      <c r="B85" t="s">
+        <v>1309</v>
+      </c>
+      <c r="C85" t="s">
+        <v>1309</v>
       </c>
     </row>
   </sheetData>
@@ -15902,10 +16430,10 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G18"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
-    <col min="5" max="5" width="23.7109375" customWidth="1"/>
-    <col min="6" max="6" width="24.85546875" customWidth="1"/>
+    <col min="5" max="5" width="23.6640625" customWidth="1"/>
+    <col min="6" max="6" width="24.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -16083,7 +16611,7 @@
       <c r="F13" s="19"/>
       <c r="G13" s="1"/>
     </row>
-    <row r="14" spans="1:7" ht="28.9" customHeight="1">
+    <row r="14" spans="1:7" ht="28.95" customHeight="1">
       <c r="A14" s="24" t="s">
         <v>658</v>
       </c>
@@ -16139,7 +16667,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:Q172"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="37"/>
@@ -16263,80 +16791,80 @@
       </c>
     </row>
     <row r="28" spans="1:17">
-      <c r="A28" s="107" t="s">
+      <c r="A28" s="109" t="s">
         <v>783</v>
       </c>
-      <c r="B28" s="106"/>
-      <c r="C28" s="106"/>
-      <c r="D28" s="106"/>
-      <c r="E28" s="106"/>
-      <c r="F28" s="106"/>
-      <c r="G28" s="106"/>
-      <c r="H28" s="106"/>
-      <c r="I28" s="106"/>
-      <c r="J28" s="106"/>
-      <c r="K28" s="106"/>
-      <c r="L28" s="106"/>
-      <c r="M28" s="106"/>
-      <c r="N28" s="106"/>
-      <c r="O28" s="106"/>
-      <c r="P28" s="106"/>
-      <c r="Q28" s="106"/>
+      <c r="B28" s="108"/>
+      <c r="C28" s="108"/>
+      <c r="D28" s="108"/>
+      <c r="E28" s="108"/>
+      <c r="F28" s="108"/>
+      <c r="G28" s="108"/>
+      <c r="H28" s="108"/>
+      <c r="I28" s="108"/>
+      <c r="J28" s="108"/>
+      <c r="K28" s="108"/>
+      <c r="L28" s="108"/>
+      <c r="M28" s="108"/>
+      <c r="N28" s="108"/>
+      <c r="O28" s="108"/>
+      <c r="P28" s="108"/>
+      <c r="Q28" s="108"/>
     </row>
     <row r="29" spans="1:17">
-      <c r="A29" s="106"/>
-      <c r="B29" s="106"/>
-      <c r="C29" s="106"/>
-      <c r="D29" s="106"/>
-      <c r="E29" s="106"/>
-      <c r="F29" s="106"/>
-      <c r="G29" s="106"/>
-      <c r="H29" s="106"/>
-      <c r="I29" s="106"/>
-      <c r="J29" s="106"/>
-      <c r="K29" s="106"/>
-      <c r="L29" s="106"/>
-      <c r="M29" s="106"/>
-      <c r="N29" s="106"/>
-      <c r="O29" s="106"/>
-      <c r="P29" s="106"/>
-      <c r="Q29" s="106"/>
-    </row>
-    <row r="30" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A30" s="108" t="s">
+      <c r="A29" s="108"/>
+      <c r="B29" s="108"/>
+      <c r="C29" s="108"/>
+      <c r="D29" s="108"/>
+      <c r="E29" s="108"/>
+      <c r="F29" s="108"/>
+      <c r="G29" s="108"/>
+      <c r="H29" s="108"/>
+      <c r="I29" s="108"/>
+      <c r="J29" s="108"/>
+      <c r="K29" s="108"/>
+      <c r="L29" s="108"/>
+      <c r="M29" s="108"/>
+      <c r="N29" s="108"/>
+      <c r="O29" s="108"/>
+      <c r="P29" s="108"/>
+      <c r="Q29" s="108"/>
+    </row>
+    <row r="30" spans="1:17" ht="14.4" customHeight="1">
+      <c r="A30" s="110" t="s">
         <v>20</v>
       </c>
-      <c r="B30" s="105" t="s">
+      <c r="B30" s="107" t="s">
         <v>21</v>
       </c>
-      <c r="C30" s="106"/>
-      <c r="D30" s="106"/>
-      <c r="E30" s="105" t="s">
+      <c r="C30" s="108"/>
+      <c r="D30" s="108"/>
+      <c r="E30" s="107" t="s">
         <v>22</v>
       </c>
-      <c r="F30" s="106"/>
-      <c r="G30" s="106"/>
-      <c r="H30" s="105" t="s">
+      <c r="F30" s="108"/>
+      <c r="G30" s="108"/>
+      <c r="H30" s="107" t="s">
         <v>23</v>
       </c>
-      <c r="I30" s="106"/>
-      <c r="J30" s="106"/>
-      <c r="K30" s="105" t="s">
+      <c r="I30" s="108"/>
+      <c r="J30" s="108"/>
+      <c r="K30" s="107" t="s">
         <v>24</v>
       </c>
-      <c r="L30" s="106"/>
-      <c r="M30" s="106"/>
-      <c r="N30" s="106"/>
-      <c r="O30" s="106"/>
-      <c r="P30" s="105" t="s">
+      <c r="L30" s="108"/>
+      <c r="M30" s="108"/>
+      <c r="N30" s="108"/>
+      <c r="O30" s="108"/>
+      <c r="P30" s="107" t="s">
         <v>25</v>
       </c>
-      <c r="Q30" s="105" t="s">
+      <c r="Q30" s="107" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="31" spans="1:17">
-      <c r="A31" s="106"/>
+      <c r="A31" s="108"/>
       <c r="B31" s="40" t="s">
         <v>27</v>
       </c>
@@ -16379,10 +16907,10 @@
       <c r="O31" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="P31" s="106"/>
-      <c r="Q31" s="106"/>
-    </row>
-    <row r="32" spans="1:17" ht="43.15" customHeight="1">
+      <c r="P31" s="108"/>
+      <c r="Q31" s="108"/>
+    </row>
+    <row r="32" spans="1:17" ht="43.2" customHeight="1">
       <c r="A32" s="40" t="s">
         <v>784</v>
       </c>
@@ -16434,80 +16962,80 @@
       </c>
     </row>
     <row r="33" spans="1:17">
-      <c r="A33" s="107" t="s">
+      <c r="A33" s="109" t="s">
         <v>617</v>
       </c>
-      <c r="B33" s="106"/>
-      <c r="C33" s="106"/>
-      <c r="D33" s="106"/>
-      <c r="E33" s="106"/>
-      <c r="F33" s="106"/>
-      <c r="G33" s="106"/>
-      <c r="H33" s="106"/>
-      <c r="I33" s="106"/>
-      <c r="J33" s="106"/>
-      <c r="K33" s="106"/>
-      <c r="L33" s="106"/>
-      <c r="M33" s="106"/>
-      <c r="N33" s="106"/>
-      <c r="O33" s="106"/>
-      <c r="P33" s="106"/>
-      <c r="Q33" s="106"/>
+      <c r="B33" s="108"/>
+      <c r="C33" s="108"/>
+      <c r="D33" s="108"/>
+      <c r="E33" s="108"/>
+      <c r="F33" s="108"/>
+      <c r="G33" s="108"/>
+      <c r="H33" s="108"/>
+      <c r="I33" s="108"/>
+      <c r="J33" s="108"/>
+      <c r="K33" s="108"/>
+      <c r="L33" s="108"/>
+      <c r="M33" s="108"/>
+      <c r="N33" s="108"/>
+      <c r="O33" s="108"/>
+      <c r="P33" s="108"/>
+      <c r="Q33" s="108"/>
     </row>
     <row r="34" spans="1:17">
-      <c r="A34" s="106"/>
-      <c r="B34" s="106"/>
-      <c r="C34" s="106"/>
-      <c r="D34" s="106"/>
-      <c r="E34" s="106"/>
-      <c r="F34" s="106"/>
-      <c r="G34" s="106"/>
-      <c r="H34" s="106"/>
-      <c r="I34" s="106"/>
-      <c r="J34" s="106"/>
-      <c r="K34" s="106"/>
-      <c r="L34" s="106"/>
-      <c r="M34" s="106"/>
-      <c r="N34" s="106"/>
-      <c r="O34" s="106"/>
-      <c r="P34" s="106"/>
-      <c r="Q34" s="106"/>
-    </row>
-    <row r="35" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A35" s="108" t="s">
+      <c r="A34" s="108"/>
+      <c r="B34" s="108"/>
+      <c r="C34" s="108"/>
+      <c r="D34" s="108"/>
+      <c r="E34" s="108"/>
+      <c r="F34" s="108"/>
+      <c r="G34" s="108"/>
+      <c r="H34" s="108"/>
+      <c r="I34" s="108"/>
+      <c r="J34" s="108"/>
+      <c r="K34" s="108"/>
+      <c r="L34" s="108"/>
+      <c r="M34" s="108"/>
+      <c r="N34" s="108"/>
+      <c r="O34" s="108"/>
+      <c r="P34" s="108"/>
+      <c r="Q34" s="108"/>
+    </row>
+    <row r="35" spans="1:17" ht="14.4" customHeight="1">
+      <c r="A35" s="110" t="s">
         <v>20</v>
       </c>
-      <c r="B35" s="105" t="s">
+      <c r="B35" s="107" t="s">
         <v>21</v>
       </c>
-      <c r="C35" s="106"/>
-      <c r="D35" s="106"/>
-      <c r="E35" s="105" t="s">
+      <c r="C35" s="108"/>
+      <c r="D35" s="108"/>
+      <c r="E35" s="107" t="s">
         <v>22</v>
       </c>
-      <c r="F35" s="106"/>
-      <c r="G35" s="106"/>
-      <c r="H35" s="105" t="s">
+      <c r="F35" s="108"/>
+      <c r="G35" s="108"/>
+      <c r="H35" s="107" t="s">
         <v>23</v>
       </c>
-      <c r="I35" s="106"/>
-      <c r="J35" s="106"/>
-      <c r="K35" s="105" t="s">
+      <c r="I35" s="108"/>
+      <c r="J35" s="108"/>
+      <c r="K35" s="107" t="s">
         <v>24</v>
       </c>
-      <c r="L35" s="106"/>
-      <c r="M35" s="106"/>
-      <c r="N35" s="106"/>
-      <c r="O35" s="106"/>
-      <c r="P35" s="105" t="s">
+      <c r="L35" s="108"/>
+      <c r="M35" s="108"/>
+      <c r="N35" s="108"/>
+      <c r="O35" s="108"/>
+      <c r="P35" s="107" t="s">
         <v>25</v>
       </c>
-      <c r="Q35" s="105" t="s">
+      <c r="Q35" s="107" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="36" spans="1:17">
-      <c r="A36" s="106"/>
+      <c r="A36" s="108"/>
       <c r="B36" s="40" t="s">
         <v>27</v>
       </c>
@@ -16550,8 +17078,8 @@
       <c r="O36" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="P36" s="106"/>
-      <c r="Q36" s="106"/>
+      <c r="P36" s="108"/>
+      <c r="Q36" s="108"/>
     </row>
     <row r="37" spans="1:17">
       <c r="A37" s="40" t="s">
@@ -16604,7 +17132,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="38" spans="1:17" ht="30">
+    <row r="38" spans="1:17">
       <c r="A38" s="40" t="s">
         <v>785</v>
       </c>
@@ -16655,7 +17183,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="28.9" customHeight="1">
+    <row r="39" spans="1:17" ht="28.95" customHeight="1">
       <c r="A39" s="40" t="s">
         <v>68</v>
       </c>
@@ -16772,7 +17300,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="1:17" ht="43.15" customHeight="1">
+    <row r="42" spans="1:17" ht="43.2" customHeight="1">
       <c r="A42" s="43" t="s">
         <v>788</v>
       </c>
@@ -16815,7 +17343,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:17" ht="30">
+    <row r="43" spans="1:17">
       <c r="A43" s="40" t="s">
         <v>789</v>
       </c>
@@ -16848,7 +17376,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="44" spans="1:17" ht="28.9" customHeight="1">
+    <row r="44" spans="1:17" ht="28.95" customHeight="1">
       <c r="A44" s="40" t="s">
         <v>722</v>
       </c>
@@ -16881,7 +17409,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:17" ht="28.9" customHeight="1">
+    <row r="45" spans="1:17" ht="28.95" customHeight="1">
       <c r="A45" s="40" t="s">
         <v>716</v>
       </c>
@@ -16914,7 +17442,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:17" ht="43.15" customHeight="1">
+    <row r="46" spans="1:17" ht="43.2" customHeight="1">
       <c r="A46" s="40" t="s">
         <v>726</v>
       </c>
@@ -16991,80 +17519,80 @@
       </c>
     </row>
     <row r="48" spans="1:17">
-      <c r="A48" s="107" t="s">
+      <c r="A48" s="109" t="s">
         <v>791</v>
       </c>
-      <c r="B48" s="106"/>
-      <c r="C48" s="106"/>
-      <c r="D48" s="106"/>
-      <c r="E48" s="106"/>
-      <c r="F48" s="106"/>
-      <c r="G48" s="106"/>
-      <c r="H48" s="106"/>
-      <c r="I48" s="106"/>
-      <c r="J48" s="106"/>
-      <c r="K48" s="106"/>
-      <c r="L48" s="106"/>
-      <c r="M48" s="106"/>
-      <c r="N48" s="106"/>
-      <c r="O48" s="106"/>
-      <c r="P48" s="106"/>
-      <c r="Q48" s="106"/>
+      <c r="B48" s="108"/>
+      <c r="C48" s="108"/>
+      <c r="D48" s="108"/>
+      <c r="E48" s="108"/>
+      <c r="F48" s="108"/>
+      <c r="G48" s="108"/>
+      <c r="H48" s="108"/>
+      <c r="I48" s="108"/>
+      <c r="J48" s="108"/>
+      <c r="K48" s="108"/>
+      <c r="L48" s="108"/>
+      <c r="M48" s="108"/>
+      <c r="N48" s="108"/>
+      <c r="O48" s="108"/>
+      <c r="P48" s="108"/>
+      <c r="Q48" s="108"/>
     </row>
     <row r="49" spans="1:17">
-      <c r="A49" s="106"/>
-      <c r="B49" s="106"/>
-      <c r="C49" s="106"/>
-      <c r="D49" s="106"/>
-      <c r="E49" s="106"/>
-      <c r="F49" s="106"/>
-      <c r="G49" s="106"/>
-      <c r="H49" s="106"/>
-      <c r="I49" s="106"/>
-      <c r="J49" s="106"/>
-      <c r="K49" s="106"/>
-      <c r="L49" s="106"/>
-      <c r="M49" s="106"/>
-      <c r="N49" s="106"/>
-      <c r="O49" s="106"/>
-      <c r="P49" s="106"/>
-      <c r="Q49" s="106"/>
-    </row>
-    <row r="50" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A50" s="108" t="s">
+      <c r="A49" s="108"/>
+      <c r="B49" s="108"/>
+      <c r="C49" s="108"/>
+      <c r="D49" s="108"/>
+      <c r="E49" s="108"/>
+      <c r="F49" s="108"/>
+      <c r="G49" s="108"/>
+      <c r="H49" s="108"/>
+      <c r="I49" s="108"/>
+      <c r="J49" s="108"/>
+      <c r="K49" s="108"/>
+      <c r="L49" s="108"/>
+      <c r="M49" s="108"/>
+      <c r="N49" s="108"/>
+      <c r="O49" s="108"/>
+      <c r="P49" s="108"/>
+      <c r="Q49" s="108"/>
+    </row>
+    <row r="50" spans="1:17" ht="14.4" customHeight="1">
+      <c r="A50" s="110" t="s">
         <v>20</v>
       </c>
-      <c r="B50" s="105" t="s">
+      <c r="B50" s="107" t="s">
         <v>21</v>
       </c>
-      <c r="C50" s="106"/>
-      <c r="D50" s="106"/>
-      <c r="E50" s="105" t="s">
+      <c r="C50" s="108"/>
+      <c r="D50" s="108"/>
+      <c r="E50" s="107" t="s">
         <v>22</v>
       </c>
-      <c r="F50" s="106"/>
-      <c r="G50" s="106"/>
-      <c r="H50" s="105" t="s">
+      <c r="F50" s="108"/>
+      <c r="G50" s="108"/>
+      <c r="H50" s="107" t="s">
         <v>23</v>
       </c>
-      <c r="I50" s="106"/>
-      <c r="J50" s="106"/>
-      <c r="K50" s="105" t="s">
+      <c r="I50" s="108"/>
+      <c r="J50" s="108"/>
+      <c r="K50" s="107" t="s">
         <v>24</v>
       </c>
-      <c r="L50" s="106"/>
-      <c r="M50" s="106"/>
-      <c r="N50" s="106"/>
-      <c r="O50" s="106"/>
-      <c r="P50" s="105" t="s">
+      <c r="L50" s="108"/>
+      <c r="M50" s="108"/>
+      <c r="N50" s="108"/>
+      <c r="O50" s="108"/>
+      <c r="P50" s="107" t="s">
         <v>25</v>
       </c>
-      <c r="Q50" s="105" t="s">
+      <c r="Q50" s="107" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="51" spans="1:17">
-      <c r="A51" s="106"/>
+      <c r="A51" s="108"/>
       <c r="B51" s="40" t="s">
         <v>27</v>
       </c>
@@ -17107,8 +17635,8 @@
       <c r="O51" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="P51" s="106"/>
-      <c r="Q51" s="106"/>
+      <c r="P51" s="108"/>
+      <c r="Q51" s="108"/>
     </row>
     <row r="52" spans="1:17" ht="57.6" customHeight="1">
       <c r="A52" s="40" t="s">
@@ -17162,80 +17690,80 @@
       </c>
     </row>
     <row r="53" spans="1:17">
-      <c r="A53" s="107" t="s">
+      <c r="A53" s="109" t="s">
         <v>793</v>
       </c>
-      <c r="B53" s="106"/>
-      <c r="C53" s="106"/>
-      <c r="D53" s="106"/>
-      <c r="E53" s="106"/>
-      <c r="F53" s="106"/>
-      <c r="G53" s="106"/>
-      <c r="H53" s="106"/>
-      <c r="I53" s="106"/>
-      <c r="J53" s="106"/>
-      <c r="K53" s="106"/>
-      <c r="L53" s="106"/>
-      <c r="M53" s="106"/>
-      <c r="N53" s="106"/>
-      <c r="O53" s="106"/>
-      <c r="P53" s="106"/>
-      <c r="Q53" s="106"/>
+      <c r="B53" s="108"/>
+      <c r="C53" s="108"/>
+      <c r="D53" s="108"/>
+      <c r="E53" s="108"/>
+      <c r="F53" s="108"/>
+      <c r="G53" s="108"/>
+      <c r="H53" s="108"/>
+      <c r="I53" s="108"/>
+      <c r="J53" s="108"/>
+      <c r="K53" s="108"/>
+      <c r="L53" s="108"/>
+      <c r="M53" s="108"/>
+      <c r="N53" s="108"/>
+      <c r="O53" s="108"/>
+      <c r="P53" s="108"/>
+      <c r="Q53" s="108"/>
     </row>
     <row r="54" spans="1:17">
-      <c r="A54" s="106"/>
-      <c r="B54" s="106"/>
-      <c r="C54" s="106"/>
-      <c r="D54" s="106"/>
-      <c r="E54" s="106"/>
-      <c r="F54" s="106"/>
-      <c r="G54" s="106"/>
-      <c r="H54" s="106"/>
-      <c r="I54" s="106"/>
-      <c r="J54" s="106"/>
-      <c r="K54" s="106"/>
-      <c r="L54" s="106"/>
-      <c r="M54" s="106"/>
-      <c r="N54" s="106"/>
-      <c r="O54" s="106"/>
-      <c r="P54" s="106"/>
-      <c r="Q54" s="106"/>
-    </row>
-    <row r="55" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A55" s="108" t="s">
+      <c r="A54" s="108"/>
+      <c r="B54" s="108"/>
+      <c r="C54" s="108"/>
+      <c r="D54" s="108"/>
+      <c r="E54" s="108"/>
+      <c r="F54" s="108"/>
+      <c r="G54" s="108"/>
+      <c r="H54" s="108"/>
+      <c r="I54" s="108"/>
+      <c r="J54" s="108"/>
+      <c r="K54" s="108"/>
+      <c r="L54" s="108"/>
+      <c r="M54" s="108"/>
+      <c r="N54" s="108"/>
+      <c r="O54" s="108"/>
+      <c r="P54" s="108"/>
+      <c r="Q54" s="108"/>
+    </row>
+    <row r="55" spans="1:17" ht="14.4" customHeight="1">
+      <c r="A55" s="110" t="s">
         <v>20</v>
       </c>
-      <c r="B55" s="105" t="s">
+      <c r="B55" s="107" t="s">
         <v>21</v>
       </c>
-      <c r="C55" s="106"/>
-      <c r="D55" s="106"/>
-      <c r="E55" s="105" t="s">
+      <c r="C55" s="108"/>
+      <c r="D55" s="108"/>
+      <c r="E55" s="107" t="s">
         <v>22</v>
       </c>
-      <c r="F55" s="106"/>
-      <c r="G55" s="106"/>
-      <c r="H55" s="105" t="s">
+      <c r="F55" s="108"/>
+      <c r="G55" s="108"/>
+      <c r="H55" s="107" t="s">
         <v>23</v>
       </c>
-      <c r="I55" s="106"/>
-      <c r="J55" s="106"/>
-      <c r="K55" s="105" t="s">
+      <c r="I55" s="108"/>
+      <c r="J55" s="108"/>
+      <c r="K55" s="107" t="s">
         <v>24</v>
       </c>
-      <c r="L55" s="106"/>
-      <c r="M55" s="106"/>
-      <c r="N55" s="106"/>
-      <c r="O55" s="106"/>
-      <c r="P55" s="105" t="s">
+      <c r="L55" s="108"/>
+      <c r="M55" s="108"/>
+      <c r="N55" s="108"/>
+      <c r="O55" s="108"/>
+      <c r="P55" s="107" t="s">
         <v>25</v>
       </c>
-      <c r="Q55" s="105" t="s">
+      <c r="Q55" s="107" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="56" spans="1:17">
-      <c r="A56" s="106"/>
+      <c r="A56" s="108"/>
       <c r="B56" s="40" t="s">
         <v>27</v>
       </c>
@@ -17278,10 +17806,10 @@
       <c r="O56" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="P56" s="106"/>
-      <c r="Q56" s="106"/>
-    </row>
-    <row r="57" spans="1:17" ht="28.9" customHeight="1">
+      <c r="P56" s="108"/>
+      <c r="Q56" s="108"/>
+    </row>
+    <row r="57" spans="1:17" ht="28.95" customHeight="1">
       <c r="A57" s="40" t="s">
         <v>34</v>
       </c>
@@ -17347,7 +17875,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="43.15" customHeight="1">
+    <row r="59" spans="1:17" ht="43.2" customHeight="1">
       <c r="A59" s="40" t="s">
         <v>37</v>
       </c>
@@ -17380,7 +17908,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="43.15" customHeight="1">
+    <row r="60" spans="1:17" ht="43.2" customHeight="1">
       <c r="A60" s="40" t="s">
         <v>40</v>
       </c>
@@ -17413,7 +17941,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="28.9" customHeight="1">
+    <row r="61" spans="1:17" ht="28.95" customHeight="1">
       <c r="A61" s="40" t="s">
         <v>39</v>
       </c>
@@ -17446,7 +17974,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="100.9" customHeight="1">
+    <row r="62" spans="1:17" ht="100.95" customHeight="1">
       <c r="A62" s="40" t="s">
         <v>36</v>
       </c>
@@ -17512,7 +18040,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="115.15" customHeight="1">
+    <row r="64" spans="1:17" ht="115.2" customHeight="1">
       <c r="A64" s="40" t="s">
         <v>44</v>
       </c>
@@ -17545,7 +18073,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="65" spans="1:17" ht="100.9" customHeight="1">
+    <row r="65" spans="1:17" ht="100.95" customHeight="1">
       <c r="A65" s="40" t="s">
         <v>41</v>
       </c>
@@ -17611,7 +18139,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="67" spans="1:17" ht="115.15" customHeight="1">
+    <row r="67" spans="1:17" ht="115.2" customHeight="1">
       <c r="A67" s="40" t="s">
         <v>31</v>
       </c>
@@ -17743,7 +18271,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="71" spans="1:17" ht="43.15" customHeight="1">
+    <row r="71" spans="1:17" ht="43.2" customHeight="1">
       <c r="A71" s="43" t="s">
         <v>795</v>
       </c>
@@ -17787,80 +18315,80 @@
       </c>
     </row>
     <row r="72" spans="1:17">
-      <c r="A72" s="107" t="s">
+      <c r="A72" s="109" t="s">
         <v>796</v>
       </c>
-      <c r="B72" s="106"/>
-      <c r="C72" s="106"/>
-      <c r="D72" s="106"/>
-      <c r="E72" s="106"/>
-      <c r="F72" s="106"/>
-      <c r="G72" s="106"/>
-      <c r="H72" s="106"/>
-      <c r="I72" s="106"/>
-      <c r="J72" s="106"/>
-      <c r="K72" s="106"/>
-      <c r="L72" s="106"/>
-      <c r="M72" s="106"/>
-      <c r="N72" s="106"/>
-      <c r="O72" s="106"/>
-      <c r="P72" s="106"/>
-      <c r="Q72" s="106"/>
+      <c r="B72" s="108"/>
+      <c r="C72" s="108"/>
+      <c r="D72" s="108"/>
+      <c r="E72" s="108"/>
+      <c r="F72" s="108"/>
+      <c r="G72" s="108"/>
+      <c r="H72" s="108"/>
+      <c r="I72" s="108"/>
+      <c r="J72" s="108"/>
+      <c r="K72" s="108"/>
+      <c r="L72" s="108"/>
+      <c r="M72" s="108"/>
+      <c r="N72" s="108"/>
+      <c r="O72" s="108"/>
+      <c r="P72" s="108"/>
+      <c r="Q72" s="108"/>
     </row>
     <row r="73" spans="1:17">
-      <c r="A73" s="106"/>
-      <c r="B73" s="106"/>
-      <c r="C73" s="106"/>
-      <c r="D73" s="106"/>
-      <c r="E73" s="106"/>
-      <c r="F73" s="106"/>
-      <c r="G73" s="106"/>
-      <c r="H73" s="106"/>
-      <c r="I73" s="106"/>
-      <c r="J73" s="106"/>
-      <c r="K73" s="106"/>
-      <c r="L73" s="106"/>
-      <c r="M73" s="106"/>
-      <c r="N73" s="106"/>
-      <c r="O73" s="106"/>
-      <c r="P73" s="106"/>
-      <c r="Q73" s="106"/>
-    </row>
-    <row r="74" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A74" s="108" t="s">
+      <c r="A73" s="108"/>
+      <c r="B73" s="108"/>
+      <c r="C73" s="108"/>
+      <c r="D73" s="108"/>
+      <c r="E73" s="108"/>
+      <c r="F73" s="108"/>
+      <c r="G73" s="108"/>
+      <c r="H73" s="108"/>
+      <c r="I73" s="108"/>
+      <c r="J73" s="108"/>
+      <c r="K73" s="108"/>
+      <c r="L73" s="108"/>
+      <c r="M73" s="108"/>
+      <c r="N73" s="108"/>
+      <c r="O73" s="108"/>
+      <c r="P73" s="108"/>
+      <c r="Q73" s="108"/>
+    </row>
+    <row r="74" spans="1:17" ht="14.4" customHeight="1">
+      <c r="A74" s="110" t="s">
         <v>20</v>
       </c>
-      <c r="B74" s="105" t="s">
+      <c r="B74" s="107" t="s">
         <v>21</v>
       </c>
-      <c r="C74" s="106"/>
-      <c r="D74" s="106"/>
-      <c r="E74" s="105" t="s">
+      <c r="C74" s="108"/>
+      <c r="D74" s="108"/>
+      <c r="E74" s="107" t="s">
         <v>22</v>
       </c>
-      <c r="F74" s="106"/>
-      <c r="G74" s="106"/>
-      <c r="H74" s="105" t="s">
+      <c r="F74" s="108"/>
+      <c r="G74" s="108"/>
+      <c r="H74" s="107" t="s">
         <v>23</v>
       </c>
-      <c r="I74" s="106"/>
-      <c r="J74" s="106"/>
-      <c r="K74" s="105" t="s">
+      <c r="I74" s="108"/>
+      <c r="J74" s="108"/>
+      <c r="K74" s="107" t="s">
         <v>24</v>
       </c>
-      <c r="L74" s="106"/>
-      <c r="M74" s="106"/>
-      <c r="N74" s="106"/>
-      <c r="O74" s="106"/>
-      <c r="P74" s="105" t="s">
+      <c r="L74" s="108"/>
+      <c r="M74" s="108"/>
+      <c r="N74" s="108"/>
+      <c r="O74" s="108"/>
+      <c r="P74" s="107" t="s">
         <v>25</v>
       </c>
-      <c r="Q74" s="105" t="s">
+      <c r="Q74" s="107" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="75" spans="1:17">
-      <c r="A75" s="106"/>
+      <c r="A75" s="108"/>
       <c r="B75" s="40" t="s">
         <v>27</v>
       </c>
@@ -17903,8 +18431,8 @@
       <c r="O75" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="P75" s="106"/>
-      <c r="Q75" s="106"/>
+      <c r="P75" s="108"/>
+      <c r="Q75" s="108"/>
     </row>
     <row r="76" spans="1:17" ht="57.6" customHeight="1">
       <c r="A76" s="40" t="s">
@@ -17939,7 +18467,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="43.15" customHeight="1">
+    <row r="77" spans="1:17" ht="43.2" customHeight="1">
       <c r="A77" s="40" t="s">
         <v>51</v>
       </c>
@@ -18038,7 +18566,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="28.9" customHeight="1">
+    <row r="80" spans="1:17" ht="28.95" customHeight="1">
       <c r="A80" s="43" t="s">
         <v>797</v>
       </c>
@@ -18082,80 +18610,80 @@
       </c>
     </row>
     <row r="81" spans="1:17">
-      <c r="A81" s="107" t="s">
+      <c r="A81" s="109" t="s">
         <v>798</v>
       </c>
-      <c r="B81" s="106"/>
-      <c r="C81" s="106"/>
-      <c r="D81" s="106"/>
-      <c r="E81" s="106"/>
-      <c r="F81" s="106"/>
-      <c r="G81" s="106"/>
-      <c r="H81" s="106"/>
-      <c r="I81" s="106"/>
-      <c r="J81" s="106"/>
-      <c r="K81" s="106"/>
-      <c r="L81" s="106"/>
-      <c r="M81" s="106"/>
-      <c r="N81" s="106"/>
-      <c r="O81" s="106"/>
-      <c r="P81" s="106"/>
-      <c r="Q81" s="106"/>
+      <c r="B81" s="108"/>
+      <c r="C81" s="108"/>
+      <c r="D81" s="108"/>
+      <c r="E81" s="108"/>
+      <c r="F81" s="108"/>
+      <c r="G81" s="108"/>
+      <c r="H81" s="108"/>
+      <c r="I81" s="108"/>
+      <c r="J81" s="108"/>
+      <c r="K81" s="108"/>
+      <c r="L81" s="108"/>
+      <c r="M81" s="108"/>
+      <c r="N81" s="108"/>
+      <c r="O81" s="108"/>
+      <c r="P81" s="108"/>
+      <c r="Q81" s="108"/>
     </row>
     <row r="82" spans="1:17">
-      <c r="A82" s="106"/>
-      <c r="B82" s="106"/>
-      <c r="C82" s="106"/>
-      <c r="D82" s="106"/>
-      <c r="E82" s="106"/>
-      <c r="F82" s="106"/>
-      <c r="G82" s="106"/>
-      <c r="H82" s="106"/>
-      <c r="I82" s="106"/>
-      <c r="J82" s="106"/>
-      <c r="K82" s="106"/>
-      <c r="L82" s="106"/>
-      <c r="M82" s="106"/>
-      <c r="N82" s="106"/>
-      <c r="O82" s="106"/>
-      <c r="P82" s="106"/>
-      <c r="Q82" s="106"/>
-    </row>
-    <row r="83" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A83" s="108" t="s">
+      <c r="A82" s="108"/>
+      <c r="B82" s="108"/>
+      <c r="C82" s="108"/>
+      <c r="D82" s="108"/>
+      <c r="E82" s="108"/>
+      <c r="F82" s="108"/>
+      <c r="G82" s="108"/>
+      <c r="H82" s="108"/>
+      <c r="I82" s="108"/>
+      <c r="J82" s="108"/>
+      <c r="K82" s="108"/>
+      <c r="L82" s="108"/>
+      <c r="M82" s="108"/>
+      <c r="N82" s="108"/>
+      <c r="O82" s="108"/>
+      <c r="P82" s="108"/>
+      <c r="Q82" s="108"/>
+    </row>
+    <row r="83" spans="1:17" ht="14.4" customHeight="1">
+      <c r="A83" s="110" t="s">
         <v>20</v>
       </c>
-      <c r="B83" s="105" t="s">
+      <c r="B83" s="107" t="s">
         <v>21</v>
       </c>
-      <c r="C83" s="106"/>
-      <c r="D83" s="106"/>
-      <c r="E83" s="105" t="s">
+      <c r="C83" s="108"/>
+      <c r="D83" s="108"/>
+      <c r="E83" s="107" t="s">
         <v>22</v>
       </c>
-      <c r="F83" s="106"/>
-      <c r="G83" s="106"/>
-      <c r="H83" s="105" t="s">
+      <c r="F83" s="108"/>
+      <c r="G83" s="108"/>
+      <c r="H83" s="107" t="s">
         <v>23</v>
       </c>
-      <c r="I83" s="106"/>
-      <c r="J83" s="106"/>
-      <c r="K83" s="105" t="s">
+      <c r="I83" s="108"/>
+      <c r="J83" s="108"/>
+      <c r="K83" s="107" t="s">
         <v>24</v>
       </c>
-      <c r="L83" s="106"/>
-      <c r="M83" s="106"/>
-      <c r="N83" s="106"/>
-      <c r="O83" s="106"/>
-      <c r="P83" s="105" t="s">
+      <c r="L83" s="108"/>
+      <c r="M83" s="108"/>
+      <c r="N83" s="108"/>
+      <c r="O83" s="108"/>
+      <c r="P83" s="107" t="s">
         <v>25</v>
       </c>
-      <c r="Q83" s="105" t="s">
+      <c r="Q83" s="107" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="84" spans="1:17">
-      <c r="A84" s="106"/>
+      <c r="A84" s="108"/>
       <c r="B84" s="40" t="s">
         <v>27</v>
       </c>
@@ -18198,10 +18726,10 @@
       <c r="O84" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="P84" s="106"/>
-      <c r="Q84" s="106"/>
-    </row>
-    <row r="85" spans="1:17" ht="100.9" customHeight="1">
+      <c r="P84" s="108"/>
+      <c r="Q84" s="108"/>
+    </row>
+    <row r="85" spans="1:17" ht="100.95" customHeight="1">
       <c r="A85" s="40" t="s">
         <v>799</v>
       </c>
@@ -18234,7 +18762,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="86" spans="1:17" ht="100.9" customHeight="1">
+    <row r="86" spans="1:17" ht="100.95" customHeight="1">
       <c r="A86" s="40" t="s">
         <v>800</v>
       </c>
@@ -18267,7 +18795,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="87" spans="1:17" ht="28.9" customHeight="1">
+    <row r="87" spans="1:17" ht="28.95" customHeight="1">
       <c r="A87" s="40" t="s">
         <v>745</v>
       </c>
@@ -18333,7 +18861,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="89" spans="1:17" ht="28.9" customHeight="1">
+    <row r="89" spans="1:17" ht="28.95" customHeight="1">
       <c r="A89" s="40" t="s">
         <v>753</v>
       </c>
@@ -18399,7 +18927,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="91" spans="1:17" ht="28.9" customHeight="1">
+    <row r="91" spans="1:17" ht="28.95" customHeight="1">
       <c r="A91" s="40" t="s">
         <v>801</v>
       </c>
@@ -18432,7 +18960,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="92" spans="1:17" ht="28.9" customHeight="1">
+    <row r="92" spans="1:17" ht="28.95" customHeight="1">
       <c r="A92" s="43" t="s">
         <v>802</v>
       </c>
@@ -18476,80 +19004,80 @@
       </c>
     </row>
     <row r="93" spans="1:17">
-      <c r="A93" s="107" t="s">
+      <c r="A93" s="109" t="s">
         <v>803</v>
       </c>
-      <c r="B93" s="106"/>
-      <c r="C93" s="106"/>
-      <c r="D93" s="106"/>
-      <c r="E93" s="106"/>
-      <c r="F93" s="106"/>
-      <c r="G93" s="106"/>
-      <c r="H93" s="106"/>
-      <c r="I93" s="106"/>
-      <c r="J93" s="106"/>
-      <c r="K93" s="106"/>
-      <c r="L93" s="106"/>
-      <c r="M93" s="106"/>
-      <c r="N93" s="106"/>
-      <c r="O93" s="106"/>
-      <c r="P93" s="106"/>
-      <c r="Q93" s="106"/>
+      <c r="B93" s="108"/>
+      <c r="C93" s="108"/>
+      <c r="D93" s="108"/>
+      <c r="E93" s="108"/>
+      <c r="F93" s="108"/>
+      <c r="G93" s="108"/>
+      <c r="H93" s="108"/>
+      <c r="I93" s="108"/>
+      <c r="J93" s="108"/>
+      <c r="K93" s="108"/>
+      <c r="L93" s="108"/>
+      <c r="M93" s="108"/>
+      <c r="N93" s="108"/>
+      <c r="O93" s="108"/>
+      <c r="P93" s="108"/>
+      <c r="Q93" s="108"/>
     </row>
     <row r="94" spans="1:17">
-      <c r="A94" s="106"/>
-      <c r="B94" s="106"/>
-      <c r="C94" s="106"/>
-      <c r="D94" s="106"/>
-      <c r="E94" s="106"/>
-      <c r="F94" s="106"/>
-      <c r="G94" s="106"/>
-      <c r="H94" s="106"/>
-      <c r="I94" s="106"/>
-      <c r="J94" s="106"/>
-      <c r="K94" s="106"/>
-      <c r="L94" s="106"/>
-      <c r="M94" s="106"/>
-      <c r="N94" s="106"/>
-      <c r="O94" s="106"/>
-      <c r="P94" s="106"/>
-      <c r="Q94" s="106"/>
-    </row>
-    <row r="95" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A95" s="108" t="s">
+      <c r="A94" s="108"/>
+      <c r="B94" s="108"/>
+      <c r="C94" s="108"/>
+      <c r="D94" s="108"/>
+      <c r="E94" s="108"/>
+      <c r="F94" s="108"/>
+      <c r="G94" s="108"/>
+      <c r="H94" s="108"/>
+      <c r="I94" s="108"/>
+      <c r="J94" s="108"/>
+      <c r="K94" s="108"/>
+      <c r="L94" s="108"/>
+      <c r="M94" s="108"/>
+      <c r="N94" s="108"/>
+      <c r="O94" s="108"/>
+      <c r="P94" s="108"/>
+      <c r="Q94" s="108"/>
+    </row>
+    <row r="95" spans="1:17" ht="14.4" customHeight="1">
+      <c r="A95" s="110" t="s">
         <v>20</v>
       </c>
-      <c r="B95" s="105" t="s">
+      <c r="B95" s="107" t="s">
         <v>21</v>
       </c>
-      <c r="C95" s="106"/>
-      <c r="D95" s="106"/>
-      <c r="E95" s="105" t="s">
+      <c r="C95" s="108"/>
+      <c r="D95" s="108"/>
+      <c r="E95" s="107" t="s">
         <v>22</v>
       </c>
-      <c r="F95" s="106"/>
-      <c r="G95" s="106"/>
-      <c r="H95" s="105" t="s">
+      <c r="F95" s="108"/>
+      <c r="G95" s="108"/>
+      <c r="H95" s="107" t="s">
         <v>23</v>
       </c>
-      <c r="I95" s="106"/>
-      <c r="J95" s="106"/>
-      <c r="K95" s="105" t="s">
+      <c r="I95" s="108"/>
+      <c r="J95" s="108"/>
+      <c r="K95" s="107" t="s">
         <v>24</v>
       </c>
-      <c r="L95" s="106"/>
-      <c r="M95" s="106"/>
-      <c r="N95" s="106"/>
-      <c r="O95" s="106"/>
-      <c r="P95" s="105" t="s">
+      <c r="L95" s="108"/>
+      <c r="M95" s="108"/>
+      <c r="N95" s="108"/>
+      <c r="O95" s="108"/>
+      <c r="P95" s="107" t="s">
         <v>25</v>
       </c>
-      <c r="Q95" s="105" t="s">
+      <c r="Q95" s="107" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="96" spans="1:17">
-      <c r="A96" s="106"/>
+      <c r="A96" s="108"/>
       <c r="B96" s="40" t="s">
         <v>27</v>
       </c>
@@ -18592,8 +19120,8 @@
       <c r="O96" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="P96" s="106"/>
-      <c r="Q96" s="106"/>
+      <c r="P96" s="108"/>
+      <c r="Q96" s="108"/>
     </row>
     <row r="97" spans="1:17" ht="57.6" customHeight="1">
       <c r="A97" s="40" t="s">
@@ -18694,7 +19222,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="100" spans="1:17" ht="28.9" customHeight="1">
+    <row r="100" spans="1:17" ht="28.95" customHeight="1">
       <c r="A100" s="40" t="s">
         <v>56</v>
       </c>
@@ -18727,7 +19255,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="101" spans="1:17" ht="115.15" customHeight="1">
+    <row r="101" spans="1:17" ht="115.2" customHeight="1">
       <c r="A101" s="40" t="s">
         <v>57</v>
       </c>
@@ -18793,7 +19321,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="28.9" customHeight="1">
+    <row r="103" spans="1:17" ht="28.95" customHeight="1">
       <c r="A103" s="40" t="s">
         <v>806</v>
       </c>
@@ -18826,7 +19354,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="43.15" customHeight="1">
+    <row r="104" spans="1:17" ht="43.2" customHeight="1">
       <c r="A104" s="40" t="s">
         <v>58</v>
       </c>
@@ -18925,7 +19453,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="107" spans="1:17" ht="100.9" customHeight="1">
+    <row r="107" spans="1:17" ht="100.95" customHeight="1">
       <c r="A107" s="40" t="s">
         <v>807</v>
       </c>
@@ -19057,7 +19585,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:17" ht="86.45" customHeight="1">
+    <row r="111" spans="1:17" ht="86.4" customHeight="1">
       <c r="A111" s="40" t="s">
         <v>63</v>
       </c>
@@ -19123,7 +19651,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="113" spans="1:17" ht="86.45" customHeight="1">
+    <row r="113" spans="1:17" ht="86.4" customHeight="1">
       <c r="A113" s="40" t="s">
         <v>809</v>
       </c>
@@ -19189,7 +19717,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="115" spans="1:17" ht="86.45" customHeight="1">
+    <row r="115" spans="1:17" ht="86.4" customHeight="1">
       <c r="A115" s="40" t="s">
         <v>811</v>
       </c>
@@ -19420,7 +19948,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="122" spans="1:17" ht="43.15" customHeight="1">
+    <row r="122" spans="1:17" ht="43.2" customHeight="1">
       <c r="A122" s="40" t="s">
         <v>816</v>
       </c>
@@ -19453,7 +19981,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:17" ht="100.9" customHeight="1">
+    <row r="123" spans="1:17" ht="100.95" customHeight="1">
       <c r="A123" s="40" t="s">
         <v>817</v>
       </c>
@@ -19486,7 +20014,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="124" spans="1:17" ht="100.9" customHeight="1">
+    <row r="124" spans="1:17" ht="100.95" customHeight="1">
       <c r="A124" s="40" t="s">
         <v>818</v>
       </c>
@@ -19519,7 +20047,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="125" spans="1:17" ht="43.15" customHeight="1">
+    <row r="125" spans="1:17" ht="43.2" customHeight="1">
       <c r="A125" s="40" t="s">
         <v>819</v>
       </c>
@@ -19552,7 +20080,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="43.15" customHeight="1">
+    <row r="126" spans="1:17" ht="43.2" customHeight="1">
       <c r="A126" s="43" t="s">
         <v>803</v>
       </c>
@@ -19596,80 +20124,80 @@
       </c>
     </row>
     <row r="127" spans="1:17">
-      <c r="A127" s="107" t="s">
+      <c r="A127" s="109" t="s">
         <v>545</v>
       </c>
-      <c r="B127" s="106"/>
-      <c r="C127" s="106"/>
-      <c r="D127" s="106"/>
-      <c r="E127" s="106"/>
-      <c r="F127" s="106"/>
-      <c r="G127" s="106"/>
-      <c r="H127" s="106"/>
-      <c r="I127" s="106"/>
-      <c r="J127" s="106"/>
-      <c r="K127" s="106"/>
-      <c r="L127" s="106"/>
-      <c r="M127" s="106"/>
-      <c r="N127" s="106"/>
-      <c r="O127" s="106"/>
-      <c r="P127" s="106"/>
-      <c r="Q127" s="106"/>
+      <c r="B127" s="108"/>
+      <c r="C127" s="108"/>
+      <c r="D127" s="108"/>
+      <c r="E127" s="108"/>
+      <c r="F127" s="108"/>
+      <c r="G127" s="108"/>
+      <c r="H127" s="108"/>
+      <c r="I127" s="108"/>
+      <c r="J127" s="108"/>
+      <c r="K127" s="108"/>
+      <c r="L127" s="108"/>
+      <c r="M127" s="108"/>
+      <c r="N127" s="108"/>
+      <c r="O127" s="108"/>
+      <c r="P127" s="108"/>
+      <c r="Q127" s="108"/>
     </row>
     <row r="128" spans="1:17">
-      <c r="A128" s="106"/>
-      <c r="B128" s="106"/>
-      <c r="C128" s="106"/>
-      <c r="D128" s="106"/>
-      <c r="E128" s="106"/>
-      <c r="F128" s="106"/>
-      <c r="G128" s="106"/>
-      <c r="H128" s="106"/>
-      <c r="I128" s="106"/>
-      <c r="J128" s="106"/>
-      <c r="K128" s="106"/>
-      <c r="L128" s="106"/>
-      <c r="M128" s="106"/>
-      <c r="N128" s="106"/>
-      <c r="O128" s="106"/>
-      <c r="P128" s="106"/>
-      <c r="Q128" s="106"/>
-    </row>
-    <row r="129" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A129" s="108" t="s">
+      <c r="A128" s="108"/>
+      <c r="B128" s="108"/>
+      <c r="C128" s="108"/>
+      <c r="D128" s="108"/>
+      <c r="E128" s="108"/>
+      <c r="F128" s="108"/>
+      <c r="G128" s="108"/>
+      <c r="H128" s="108"/>
+      <c r="I128" s="108"/>
+      <c r="J128" s="108"/>
+      <c r="K128" s="108"/>
+      <c r="L128" s="108"/>
+      <c r="M128" s="108"/>
+      <c r="N128" s="108"/>
+      <c r="O128" s="108"/>
+      <c r="P128" s="108"/>
+      <c r="Q128" s="108"/>
+    </row>
+    <row r="129" spans="1:17" ht="14.4" customHeight="1">
+      <c r="A129" s="110" t="s">
         <v>20</v>
       </c>
-      <c r="B129" s="105" t="s">
+      <c r="B129" s="107" t="s">
         <v>21</v>
       </c>
-      <c r="C129" s="106"/>
-      <c r="D129" s="106"/>
-      <c r="E129" s="105" t="s">
+      <c r="C129" s="108"/>
+      <c r="D129" s="108"/>
+      <c r="E129" s="107" t="s">
         <v>22</v>
       </c>
-      <c r="F129" s="106"/>
-      <c r="G129" s="106"/>
-      <c r="H129" s="105" t="s">
+      <c r="F129" s="108"/>
+      <c r="G129" s="108"/>
+      <c r="H129" s="107" t="s">
         <v>23</v>
       </c>
-      <c r="I129" s="106"/>
-      <c r="J129" s="106"/>
-      <c r="K129" s="105" t="s">
+      <c r="I129" s="108"/>
+      <c r="J129" s="108"/>
+      <c r="K129" s="107" t="s">
         <v>24</v>
       </c>
-      <c r="L129" s="106"/>
-      <c r="M129" s="106"/>
-      <c r="N129" s="106"/>
-      <c r="O129" s="106"/>
-      <c r="P129" s="105" t="s">
+      <c r="L129" s="108"/>
+      <c r="M129" s="108"/>
+      <c r="N129" s="108"/>
+      <c r="O129" s="108"/>
+      <c r="P129" s="107" t="s">
         <v>25</v>
       </c>
-      <c r="Q129" s="105" t="s">
+      <c r="Q129" s="107" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="130" spans="1:17">
-      <c r="A130" s="106"/>
+      <c r="A130" s="108"/>
       <c r="B130" s="40" t="s">
         <v>27</v>
       </c>
@@ -19712,10 +20240,10 @@
       <c r="O130" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="P130" s="106"/>
-      <c r="Q130" s="106"/>
-    </row>
-    <row r="131" spans="1:17" ht="43.15" customHeight="1">
+      <c r="P130" s="108"/>
+      <c r="Q130" s="108"/>
+    </row>
+    <row r="131" spans="1:17" ht="43.2" customHeight="1">
       <c r="A131" s="40" t="s">
         <v>820</v>
       </c>
@@ -19817,7 +20345,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="133" spans="1:17" ht="115.15" customHeight="1">
+    <row r="133" spans="1:17" ht="115.2" customHeight="1">
       <c r="A133" s="40" t="s">
         <v>822</v>
       </c>
@@ -19967,7 +20495,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="137" spans="1:17" ht="43.15" customHeight="1">
+    <row r="137" spans="1:17" ht="43.2" customHeight="1">
       <c r="A137" s="43" t="s">
         <v>825</v>
       </c>
@@ -20010,7 +20538,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="138" spans="1:17" ht="30">
+    <row r="138" spans="1:17">
       <c r="A138" s="40" t="s">
         <v>826</v>
       </c>
@@ -20094,7 +20622,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="140" spans="1:17" ht="86.45" customHeight="1">
+    <row r="140" spans="1:17" ht="86.4" customHeight="1">
       <c r="A140" s="40" t="s">
         <v>828</v>
       </c>
@@ -20236,7 +20764,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="144" spans="1:17" ht="43.15" customHeight="1">
+    <row r="144" spans="1:17" ht="43.2" customHeight="1">
       <c r="A144" s="43" t="s">
         <v>832</v>
       </c>
@@ -20312,7 +20840,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="146" spans="1:17" ht="100.9" customHeight="1">
+    <row r="146" spans="1:17" ht="100.95" customHeight="1">
       <c r="A146" s="40" t="s">
         <v>834</v>
       </c>
@@ -20345,7 +20873,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="147" spans="1:17" ht="43.15" customHeight="1">
+    <row r="147" spans="1:17" ht="43.2" customHeight="1">
       <c r="A147" s="43" t="s">
         <v>835</v>
       </c>
@@ -20388,7 +20916,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="148" spans="1:17" ht="28.9" customHeight="1">
+    <row r="148" spans="1:17" ht="28.95" customHeight="1">
       <c r="A148" s="40" t="s">
         <v>836</v>
       </c>
@@ -20472,7 +21000,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="150" spans="1:17" ht="28.9" customHeight="1">
+    <row r="150" spans="1:17" ht="28.95" customHeight="1">
       <c r="A150" s="40" t="s">
         <v>838</v>
       </c>
@@ -20505,7 +21033,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="151" spans="1:17" ht="43.15" customHeight="1">
+    <row r="151" spans="1:17" ht="43.2" customHeight="1">
       <c r="A151" s="43" t="s">
         <v>839</v>
       </c>
@@ -20548,7 +21076,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="152" spans="1:17" ht="43.15" customHeight="1">
+    <row r="152" spans="1:17" ht="43.2" customHeight="1">
       <c r="A152" s="40" t="s">
         <v>840</v>
       </c>
@@ -20599,7 +21127,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="153" spans="1:17" ht="28.9" customHeight="1">
+    <row r="153" spans="1:17" ht="28.95" customHeight="1">
       <c r="A153" s="40" t="s">
         <v>703</v>
       </c>
@@ -20650,7 +21178,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="154" spans="1:17" ht="28.9" customHeight="1">
+    <row r="154" spans="1:17" ht="28.95" customHeight="1">
       <c r="A154" s="40" t="s">
         <v>841</v>
       </c>
@@ -20701,7 +21229,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="155" spans="1:17" ht="28.9" customHeight="1">
+    <row r="155" spans="1:17" ht="28.95" customHeight="1">
       <c r="A155" s="40" t="s">
         <v>667</v>
       </c>
@@ -20734,7 +21262,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="156" spans="1:17" ht="28.9" customHeight="1">
+    <row r="156" spans="1:17" ht="28.95" customHeight="1">
       <c r="A156" s="40" t="s">
         <v>672</v>
       </c>
@@ -20767,7 +21295,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="157" spans="1:17" ht="28.9" customHeight="1">
+    <row r="157" spans="1:17" ht="28.95" customHeight="1">
       <c r="A157" s="40" t="s">
         <v>842</v>
       </c>
@@ -20844,80 +21372,80 @@
       </c>
     </row>
     <row r="159" spans="1:17">
-      <c r="A159" s="107" t="s">
+      <c r="A159" s="109" t="s">
         <v>46</v>
       </c>
-      <c r="B159" s="106"/>
-      <c r="C159" s="106"/>
-      <c r="D159" s="106"/>
-      <c r="E159" s="106"/>
-      <c r="F159" s="106"/>
-      <c r="G159" s="106"/>
-      <c r="H159" s="106"/>
-      <c r="I159" s="106"/>
-      <c r="J159" s="106"/>
-      <c r="K159" s="106"/>
-      <c r="L159" s="106"/>
-      <c r="M159" s="106"/>
-      <c r="N159" s="106"/>
-      <c r="O159" s="106"/>
-      <c r="P159" s="106"/>
-      <c r="Q159" s="106"/>
+      <c r="B159" s="108"/>
+      <c r="C159" s="108"/>
+      <c r="D159" s="108"/>
+      <c r="E159" s="108"/>
+      <c r="F159" s="108"/>
+      <c r="G159" s="108"/>
+      <c r="H159" s="108"/>
+      <c r="I159" s="108"/>
+      <c r="J159" s="108"/>
+      <c r="K159" s="108"/>
+      <c r="L159" s="108"/>
+      <c r="M159" s="108"/>
+      <c r="N159" s="108"/>
+      <c r="O159" s="108"/>
+      <c r="P159" s="108"/>
+      <c r="Q159" s="108"/>
     </row>
     <row r="160" spans="1:17">
-      <c r="A160" s="106"/>
-      <c r="B160" s="106"/>
-      <c r="C160" s="106"/>
-      <c r="D160" s="106"/>
-      <c r="E160" s="106"/>
-      <c r="F160" s="106"/>
-      <c r="G160" s="106"/>
-      <c r="H160" s="106"/>
-      <c r="I160" s="106"/>
-      <c r="J160" s="106"/>
-      <c r="K160" s="106"/>
-      <c r="L160" s="106"/>
-      <c r="M160" s="106"/>
-      <c r="N160" s="106"/>
-      <c r="O160" s="106"/>
-      <c r="P160" s="106"/>
-      <c r="Q160" s="106"/>
-    </row>
-    <row r="161" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A161" s="108" t="s">
+      <c r="A160" s="108"/>
+      <c r="B160" s="108"/>
+      <c r="C160" s="108"/>
+      <c r="D160" s="108"/>
+      <c r="E160" s="108"/>
+      <c r="F160" s="108"/>
+      <c r="G160" s="108"/>
+      <c r="H160" s="108"/>
+      <c r="I160" s="108"/>
+      <c r="J160" s="108"/>
+      <c r="K160" s="108"/>
+      <c r="L160" s="108"/>
+      <c r="M160" s="108"/>
+      <c r="N160" s="108"/>
+      <c r="O160" s="108"/>
+      <c r="P160" s="108"/>
+      <c r="Q160" s="108"/>
+    </row>
+    <row r="161" spans="1:17" ht="14.4" customHeight="1">
+      <c r="A161" s="110" t="s">
         <v>20</v>
       </c>
-      <c r="B161" s="105" t="s">
+      <c r="B161" s="107" t="s">
         <v>21</v>
       </c>
-      <c r="C161" s="106"/>
-      <c r="D161" s="106"/>
-      <c r="E161" s="105" t="s">
+      <c r="C161" s="108"/>
+      <c r="D161" s="108"/>
+      <c r="E161" s="107" t="s">
         <v>22</v>
       </c>
-      <c r="F161" s="106"/>
-      <c r="G161" s="106"/>
-      <c r="H161" s="105" t="s">
+      <c r="F161" s="108"/>
+      <c r="G161" s="108"/>
+      <c r="H161" s="107" t="s">
         <v>23</v>
       </c>
-      <c r="I161" s="106"/>
-      <c r="J161" s="106"/>
-      <c r="K161" s="105" t="s">
+      <c r="I161" s="108"/>
+      <c r="J161" s="108"/>
+      <c r="K161" s="107" t="s">
         <v>24</v>
       </c>
-      <c r="L161" s="106"/>
-      <c r="M161" s="106"/>
-      <c r="N161" s="106"/>
-      <c r="O161" s="106"/>
-      <c r="P161" s="105" t="s">
+      <c r="L161" s="108"/>
+      <c r="M161" s="108"/>
+      <c r="N161" s="108"/>
+      <c r="O161" s="108"/>
+      <c r="P161" s="107" t="s">
         <v>25</v>
       </c>
-      <c r="Q161" s="105" t="s">
+      <c r="Q161" s="107" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="162" spans="1:17">
-      <c r="A162" s="106"/>
+      <c r="A162" s="108"/>
       <c r="B162" s="40" t="s">
         <v>27</v>
       </c>
@@ -20960,10 +21488,10 @@
       <c r="O162" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="P162" s="106"/>
-      <c r="Q162" s="106"/>
-    </row>
-    <row r="163" spans="1:17" ht="28.9" customHeight="1">
+      <c r="P162" s="108"/>
+      <c r="Q162" s="108"/>
+    </row>
+    <row r="163" spans="1:17" ht="28.95" customHeight="1">
       <c r="A163" s="40" t="s">
         <v>46</v>
       </c>
@@ -21015,80 +21543,80 @@
       </c>
     </row>
     <row r="164" spans="1:17">
-      <c r="A164" s="107" t="s">
+      <c r="A164" s="109" t="s">
         <v>69</v>
       </c>
-      <c r="B164" s="106"/>
-      <c r="C164" s="106"/>
-      <c r="D164" s="106"/>
-      <c r="E164" s="106"/>
-      <c r="F164" s="106"/>
-      <c r="G164" s="106"/>
-      <c r="H164" s="106"/>
-      <c r="I164" s="106"/>
-      <c r="J164" s="106"/>
-      <c r="K164" s="106"/>
-      <c r="L164" s="106"/>
-      <c r="M164" s="106"/>
-      <c r="N164" s="106"/>
-      <c r="O164" s="106"/>
-      <c r="P164" s="106"/>
-      <c r="Q164" s="106"/>
+      <c r="B164" s="108"/>
+      <c r="C164" s="108"/>
+      <c r="D164" s="108"/>
+      <c r="E164" s="108"/>
+      <c r="F164" s="108"/>
+      <c r="G164" s="108"/>
+      <c r="H164" s="108"/>
+      <c r="I164" s="108"/>
+      <c r="J164" s="108"/>
+      <c r="K164" s="108"/>
+      <c r="L164" s="108"/>
+      <c r="M164" s="108"/>
+      <c r="N164" s="108"/>
+      <c r="O164" s="108"/>
+      <c r="P164" s="108"/>
+      <c r="Q164" s="108"/>
     </row>
     <row r="165" spans="1:17">
-      <c r="A165" s="106"/>
-      <c r="B165" s="106"/>
-      <c r="C165" s="106"/>
-      <c r="D165" s="106"/>
-      <c r="E165" s="106"/>
-      <c r="F165" s="106"/>
-      <c r="G165" s="106"/>
-      <c r="H165" s="106"/>
-      <c r="I165" s="106"/>
-      <c r="J165" s="106"/>
-      <c r="K165" s="106"/>
-      <c r="L165" s="106"/>
-      <c r="M165" s="106"/>
-      <c r="N165" s="106"/>
-      <c r="O165" s="106"/>
-      <c r="P165" s="106"/>
-      <c r="Q165" s="106"/>
-    </row>
-    <row r="166" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A166" s="108" t="s">
+      <c r="A165" s="108"/>
+      <c r="B165" s="108"/>
+      <c r="C165" s="108"/>
+      <c r="D165" s="108"/>
+      <c r="E165" s="108"/>
+      <c r="F165" s="108"/>
+      <c r="G165" s="108"/>
+      <c r="H165" s="108"/>
+      <c r="I165" s="108"/>
+      <c r="J165" s="108"/>
+      <c r="K165" s="108"/>
+      <c r="L165" s="108"/>
+      <c r="M165" s="108"/>
+      <c r="N165" s="108"/>
+      <c r="O165" s="108"/>
+      <c r="P165" s="108"/>
+      <c r="Q165" s="108"/>
+    </row>
+    <row r="166" spans="1:17" ht="14.4" customHeight="1">
+      <c r="A166" s="110" t="s">
         <v>20</v>
       </c>
-      <c r="B166" s="105" t="s">
+      <c r="B166" s="107" t="s">
         <v>21</v>
       </c>
-      <c r="C166" s="106"/>
-      <c r="D166" s="106"/>
-      <c r="E166" s="105" t="s">
+      <c r="C166" s="108"/>
+      <c r="D166" s="108"/>
+      <c r="E166" s="107" t="s">
         <v>22</v>
       </c>
-      <c r="F166" s="106"/>
-      <c r="G166" s="106"/>
-      <c r="H166" s="105" t="s">
+      <c r="F166" s="108"/>
+      <c r="G166" s="108"/>
+      <c r="H166" s="107" t="s">
         <v>23</v>
       </c>
-      <c r="I166" s="106"/>
-      <c r="J166" s="106"/>
-      <c r="K166" s="105" t="s">
+      <c r="I166" s="108"/>
+      <c r="J166" s="108"/>
+      <c r="K166" s="107" t="s">
         <v>24</v>
       </c>
-      <c r="L166" s="106"/>
-      <c r="M166" s="106"/>
-      <c r="N166" s="106"/>
-      <c r="O166" s="106"/>
-      <c r="P166" s="105" t="s">
+      <c r="L166" s="108"/>
+      <c r="M166" s="108"/>
+      <c r="N166" s="108"/>
+      <c r="O166" s="108"/>
+      <c r="P166" s="107" t="s">
         <v>25</v>
       </c>
-      <c r="Q166" s="105" t="s">
+      <c r="Q166" s="107" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="167" spans="1:17">
-      <c r="A167" s="106"/>
+      <c r="A167" s="108"/>
       <c r="B167" s="40" t="s">
         <v>27</v>
       </c>
@@ -21131,8 +21659,8 @@
       <c r="O167" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="P167" s="106"/>
-      <c r="Q167" s="106"/>
+      <c r="P167" s="108"/>
+      <c r="Q167" s="108"/>
     </row>
     <row r="168" spans="1:17" ht="72" customHeight="1">
       <c r="A168" s="40" t="s">
@@ -21266,7 +21794,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="172" spans="1:17" ht="86.45" customHeight="1">
+    <row r="172" spans="1:17" ht="86.4" customHeight="1">
       <c r="A172" s="43" t="s">
         <v>845</v>
       </c>
@@ -21422,7 +21950,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:Q87"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="37"/>
@@ -21526,80 +22054,80 @@
       </c>
     </row>
     <row r="24" spans="1:17">
-      <c r="A24" s="107" t="s">
+      <c r="A24" s="109" t="s">
         <v>19</v>
       </c>
-      <c r="B24" s="106"/>
-      <c r="C24" s="106"/>
-      <c r="D24" s="106"/>
-      <c r="E24" s="106"/>
-      <c r="F24" s="106"/>
-      <c r="G24" s="106"/>
-      <c r="H24" s="106"/>
-      <c r="I24" s="106"/>
-      <c r="J24" s="106"/>
-      <c r="K24" s="106"/>
-      <c r="L24" s="106"/>
-      <c r="M24" s="106"/>
-      <c r="N24" s="106"/>
-      <c r="O24" s="106"/>
-      <c r="P24" s="106"/>
-      <c r="Q24" s="106"/>
+      <c r="B24" s="108"/>
+      <c r="C24" s="108"/>
+      <c r="D24" s="108"/>
+      <c r="E24" s="108"/>
+      <c r="F24" s="108"/>
+      <c r="G24" s="108"/>
+      <c r="H24" s="108"/>
+      <c r="I24" s="108"/>
+      <c r="J24" s="108"/>
+      <c r="K24" s="108"/>
+      <c r="L24" s="108"/>
+      <c r="M24" s="108"/>
+      <c r="N24" s="108"/>
+      <c r="O24" s="108"/>
+      <c r="P24" s="108"/>
+      <c r="Q24" s="108"/>
     </row>
     <row r="25" spans="1:17">
-      <c r="A25" s="106"/>
-      <c r="B25" s="106"/>
-      <c r="C25" s="106"/>
-      <c r="D25" s="106"/>
-      <c r="E25" s="106"/>
-      <c r="F25" s="106"/>
-      <c r="G25" s="106"/>
-      <c r="H25" s="106"/>
-      <c r="I25" s="106"/>
-      <c r="J25" s="106"/>
-      <c r="K25" s="106"/>
-      <c r="L25" s="106"/>
-      <c r="M25" s="106"/>
-      <c r="N25" s="106"/>
-      <c r="O25" s="106"/>
-      <c r="P25" s="106"/>
-      <c r="Q25" s="106"/>
-    </row>
-    <row r="26" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A26" s="108" t="s">
+      <c r="A25" s="108"/>
+      <c r="B25" s="108"/>
+      <c r="C25" s="108"/>
+      <c r="D25" s="108"/>
+      <c r="E25" s="108"/>
+      <c r="F25" s="108"/>
+      <c r="G25" s="108"/>
+      <c r="H25" s="108"/>
+      <c r="I25" s="108"/>
+      <c r="J25" s="108"/>
+      <c r="K25" s="108"/>
+      <c r="L25" s="108"/>
+      <c r="M25" s="108"/>
+      <c r="N25" s="108"/>
+      <c r="O25" s="108"/>
+      <c r="P25" s="108"/>
+      <c r="Q25" s="108"/>
+    </row>
+    <row r="26" spans="1:17" ht="14.4" customHeight="1">
+      <c r="A26" s="110" t="s">
         <v>20</v>
       </c>
-      <c r="B26" s="105" t="s">
+      <c r="B26" s="107" t="s">
         <v>21</v>
       </c>
-      <c r="C26" s="106"/>
-      <c r="D26" s="106"/>
-      <c r="E26" s="105" t="s">
+      <c r="C26" s="108"/>
+      <c r="D26" s="108"/>
+      <c r="E26" s="107" t="s">
         <v>22</v>
       </c>
-      <c r="F26" s="106"/>
-      <c r="G26" s="106"/>
-      <c r="H26" s="105" t="s">
+      <c r="F26" s="108"/>
+      <c r="G26" s="108"/>
+      <c r="H26" s="107" t="s">
         <v>23</v>
       </c>
-      <c r="I26" s="106"/>
-      <c r="J26" s="106"/>
-      <c r="K26" s="105" t="s">
+      <c r="I26" s="108"/>
+      <c r="J26" s="108"/>
+      <c r="K26" s="107" t="s">
         <v>24</v>
       </c>
-      <c r="L26" s="106"/>
-      <c r="M26" s="106"/>
-      <c r="N26" s="106"/>
-      <c r="O26" s="106"/>
-      <c r="P26" s="105" t="s">
+      <c r="L26" s="108"/>
+      <c r="M26" s="108"/>
+      <c r="N26" s="108"/>
+      <c r="O26" s="108"/>
+      <c r="P26" s="107" t="s">
         <v>25</v>
       </c>
-      <c r="Q26" s="105" t="s">
+      <c r="Q26" s="107" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="27" spans="1:17">
-      <c r="A27" s="106"/>
+      <c r="A27" s="108"/>
       <c r="B27" s="40" t="s">
         <v>27</v>
       </c>
@@ -21642,10 +22170,10 @@
       <c r="O27" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="P27" s="106"/>
-      <c r="Q27" s="106"/>
-    </row>
-    <row r="28" spans="1:17" ht="115.15" customHeight="1">
+      <c r="P27" s="108"/>
+      <c r="Q27" s="108"/>
+    </row>
+    <row r="28" spans="1:17" ht="115.2" customHeight="1">
       <c r="A28" s="40" t="s">
         <v>31</v>
       </c>
@@ -21744,7 +22272,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="28.9" customHeight="1">
+    <row r="31" spans="1:17" ht="28.95" customHeight="1">
       <c r="A31" s="40" t="s">
         <v>34</v>
       </c>
@@ -21810,7 +22338,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:17" ht="100.9" customHeight="1">
+    <row r="33" spans="1:17" ht="100.95" customHeight="1">
       <c r="A33" s="40" t="s">
         <v>36</v>
       </c>
@@ -21843,7 +22371,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="43.15" customHeight="1">
+    <row r="34" spans="1:17" ht="43.2" customHeight="1">
       <c r="A34" s="40" t="s">
         <v>37</v>
       </c>
@@ -21909,7 +22437,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="28.9" customHeight="1">
+    <row r="36" spans="1:17" ht="28.95" customHeight="1">
       <c r="A36" s="40" t="s">
         <v>39</v>
       </c>
@@ -21942,7 +22470,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="37" spans="1:17" ht="43.15" customHeight="1">
+    <row r="37" spans="1:17" ht="43.2" customHeight="1">
       <c r="A37" s="40" t="s">
         <v>40</v>
       </c>
@@ -21975,7 +22503,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="1:17" ht="100.9" customHeight="1">
+    <row r="38" spans="1:17" ht="100.95" customHeight="1">
       <c r="A38" s="40" t="s">
         <v>41</v>
       </c>
@@ -22074,7 +22602,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="1:17" ht="115.15" customHeight="1">
+    <row r="41" spans="1:17" ht="115.2" customHeight="1">
       <c r="A41" s="40" t="s">
         <v>44</v>
       </c>
@@ -22107,7 +22635,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:17" ht="28.9" customHeight="1">
+    <row r="42" spans="1:17" ht="28.95" customHeight="1">
       <c r="A42" s="43" t="s">
         <v>45</v>
       </c>
@@ -22151,80 +22679,80 @@
       </c>
     </row>
     <row r="43" spans="1:17">
-      <c r="A43" s="107" t="s">
+      <c r="A43" s="109" t="s">
         <v>46</v>
       </c>
-      <c r="B43" s="106"/>
-      <c r="C43" s="106"/>
-      <c r="D43" s="106"/>
-      <c r="E43" s="106"/>
-      <c r="F43" s="106"/>
-      <c r="G43" s="106"/>
-      <c r="H43" s="106"/>
-      <c r="I43" s="106"/>
-      <c r="J43" s="106"/>
-      <c r="K43" s="106"/>
-      <c r="L43" s="106"/>
-      <c r="M43" s="106"/>
-      <c r="N43" s="106"/>
-      <c r="O43" s="106"/>
-      <c r="P43" s="106"/>
-      <c r="Q43" s="106"/>
+      <c r="B43" s="108"/>
+      <c r="C43" s="108"/>
+      <c r="D43" s="108"/>
+      <c r="E43" s="108"/>
+      <c r="F43" s="108"/>
+      <c r="G43" s="108"/>
+      <c r="H43" s="108"/>
+      <c r="I43" s="108"/>
+      <c r="J43" s="108"/>
+      <c r="K43" s="108"/>
+      <c r="L43" s="108"/>
+      <c r="M43" s="108"/>
+      <c r="N43" s="108"/>
+      <c r="O43" s="108"/>
+      <c r="P43" s="108"/>
+      <c r="Q43" s="108"/>
     </row>
     <row r="44" spans="1:17">
-      <c r="A44" s="106"/>
-      <c r="B44" s="106"/>
-      <c r="C44" s="106"/>
-      <c r="D44" s="106"/>
-      <c r="E44" s="106"/>
-      <c r="F44" s="106"/>
-      <c r="G44" s="106"/>
-      <c r="H44" s="106"/>
-      <c r="I44" s="106"/>
-      <c r="J44" s="106"/>
-      <c r="K44" s="106"/>
-      <c r="L44" s="106"/>
-      <c r="M44" s="106"/>
-      <c r="N44" s="106"/>
-      <c r="O44" s="106"/>
-      <c r="P44" s="106"/>
-      <c r="Q44" s="106"/>
-    </row>
-    <row r="45" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A45" s="108" t="s">
+      <c r="A44" s="108"/>
+      <c r="B44" s="108"/>
+      <c r="C44" s="108"/>
+      <c r="D44" s="108"/>
+      <c r="E44" s="108"/>
+      <c r="F44" s="108"/>
+      <c r="G44" s="108"/>
+      <c r="H44" s="108"/>
+      <c r="I44" s="108"/>
+      <c r="J44" s="108"/>
+      <c r="K44" s="108"/>
+      <c r="L44" s="108"/>
+      <c r="M44" s="108"/>
+      <c r="N44" s="108"/>
+      <c r="O44" s="108"/>
+      <c r="P44" s="108"/>
+      <c r="Q44" s="108"/>
+    </row>
+    <row r="45" spans="1:17" ht="14.4" customHeight="1">
+      <c r="A45" s="110" t="s">
         <v>20</v>
       </c>
-      <c r="B45" s="105" t="s">
+      <c r="B45" s="107" t="s">
         <v>21</v>
       </c>
-      <c r="C45" s="106"/>
-      <c r="D45" s="106"/>
-      <c r="E45" s="105" t="s">
+      <c r="C45" s="108"/>
+      <c r="D45" s="108"/>
+      <c r="E45" s="107" t="s">
         <v>22</v>
       </c>
-      <c r="F45" s="106"/>
-      <c r="G45" s="106"/>
-      <c r="H45" s="105" t="s">
+      <c r="F45" s="108"/>
+      <c r="G45" s="108"/>
+      <c r="H45" s="107" t="s">
         <v>23</v>
       </c>
-      <c r="I45" s="106"/>
-      <c r="J45" s="106"/>
-      <c r="K45" s="105" t="s">
+      <c r="I45" s="108"/>
+      <c r="J45" s="108"/>
+      <c r="K45" s="107" t="s">
         <v>24</v>
       </c>
-      <c r="L45" s="106"/>
-      <c r="M45" s="106"/>
-      <c r="N45" s="106"/>
-      <c r="O45" s="106"/>
-      <c r="P45" s="105" t="s">
+      <c r="L45" s="108"/>
+      <c r="M45" s="108"/>
+      <c r="N45" s="108"/>
+      <c r="O45" s="108"/>
+      <c r="P45" s="107" t="s">
         <v>25</v>
       </c>
-      <c r="Q45" s="105" t="s">
+      <c r="Q45" s="107" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="46" spans="1:17">
-      <c r="A46" s="106"/>
+      <c r="A46" s="108"/>
       <c r="B46" s="40" t="s">
         <v>27</v>
       </c>
@@ -22267,10 +22795,10 @@
       <c r="O46" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="P46" s="106"/>
-      <c r="Q46" s="106"/>
-    </row>
-    <row r="47" spans="1:17" ht="28.9" customHeight="1">
+      <c r="P46" s="108"/>
+      <c r="Q46" s="108"/>
+    </row>
+    <row r="47" spans="1:17" ht="28.95" customHeight="1">
       <c r="A47" s="40" t="s">
         <v>46</v>
       </c>
@@ -22322,80 +22850,80 @@
       </c>
     </row>
     <row r="48" spans="1:17">
-      <c r="A48" s="107" t="s">
+      <c r="A48" s="109" t="s">
         <v>47</v>
       </c>
-      <c r="B48" s="106"/>
-      <c r="C48" s="106"/>
-      <c r="D48" s="106"/>
-      <c r="E48" s="106"/>
-      <c r="F48" s="106"/>
-      <c r="G48" s="106"/>
-      <c r="H48" s="106"/>
-      <c r="I48" s="106"/>
-      <c r="J48" s="106"/>
-      <c r="K48" s="106"/>
-      <c r="L48" s="106"/>
-      <c r="M48" s="106"/>
-      <c r="N48" s="106"/>
-      <c r="O48" s="106"/>
-      <c r="P48" s="106"/>
-      <c r="Q48" s="106"/>
+      <c r="B48" s="108"/>
+      <c r="C48" s="108"/>
+      <c r="D48" s="108"/>
+      <c r="E48" s="108"/>
+      <c r="F48" s="108"/>
+      <c r="G48" s="108"/>
+      <c r="H48" s="108"/>
+      <c r="I48" s="108"/>
+      <c r="J48" s="108"/>
+      <c r="K48" s="108"/>
+      <c r="L48" s="108"/>
+      <c r="M48" s="108"/>
+      <c r="N48" s="108"/>
+      <c r="O48" s="108"/>
+      <c r="P48" s="108"/>
+      <c r="Q48" s="108"/>
     </row>
     <row r="49" spans="1:17">
-      <c r="A49" s="106"/>
-      <c r="B49" s="106"/>
-      <c r="C49" s="106"/>
-      <c r="D49" s="106"/>
-      <c r="E49" s="106"/>
-      <c r="F49" s="106"/>
-      <c r="G49" s="106"/>
-      <c r="H49" s="106"/>
-      <c r="I49" s="106"/>
-      <c r="J49" s="106"/>
-      <c r="K49" s="106"/>
-      <c r="L49" s="106"/>
-      <c r="M49" s="106"/>
-      <c r="N49" s="106"/>
-      <c r="O49" s="106"/>
-      <c r="P49" s="106"/>
-      <c r="Q49" s="106"/>
-    </row>
-    <row r="50" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A50" s="108" t="s">
+      <c r="A49" s="108"/>
+      <c r="B49" s="108"/>
+      <c r="C49" s="108"/>
+      <c r="D49" s="108"/>
+      <c r="E49" s="108"/>
+      <c r="F49" s="108"/>
+      <c r="G49" s="108"/>
+      <c r="H49" s="108"/>
+      <c r="I49" s="108"/>
+      <c r="J49" s="108"/>
+      <c r="K49" s="108"/>
+      <c r="L49" s="108"/>
+      <c r="M49" s="108"/>
+      <c r="N49" s="108"/>
+      <c r="O49" s="108"/>
+      <c r="P49" s="108"/>
+      <c r="Q49" s="108"/>
+    </row>
+    <row r="50" spans="1:17" ht="14.4" customHeight="1">
+      <c r="A50" s="110" t="s">
         <v>20</v>
       </c>
-      <c r="B50" s="105" t="s">
+      <c r="B50" s="107" t="s">
         <v>21</v>
       </c>
-      <c r="C50" s="106"/>
-      <c r="D50" s="106"/>
-      <c r="E50" s="105" t="s">
+      <c r="C50" s="108"/>
+      <c r="D50" s="108"/>
+      <c r="E50" s="107" t="s">
         <v>22</v>
       </c>
-      <c r="F50" s="106"/>
-      <c r="G50" s="106"/>
-      <c r="H50" s="105" t="s">
+      <c r="F50" s="108"/>
+      <c r="G50" s="108"/>
+      <c r="H50" s="107" t="s">
         <v>23</v>
       </c>
-      <c r="I50" s="106"/>
-      <c r="J50" s="106"/>
-      <c r="K50" s="105" t="s">
+      <c r="I50" s="108"/>
+      <c r="J50" s="108"/>
+      <c r="K50" s="107" t="s">
         <v>24</v>
       </c>
-      <c r="L50" s="106"/>
-      <c r="M50" s="106"/>
-      <c r="N50" s="106"/>
-      <c r="O50" s="106"/>
-      <c r="P50" s="105" t="s">
+      <c r="L50" s="108"/>
+      <c r="M50" s="108"/>
+      <c r="N50" s="108"/>
+      <c r="O50" s="108"/>
+      <c r="P50" s="107" t="s">
         <v>25</v>
       </c>
-      <c r="Q50" s="105" t="s">
+      <c r="Q50" s="107" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="51" spans="1:17">
-      <c r="A51" s="106"/>
+      <c r="A51" s="108"/>
       <c r="B51" s="40" t="s">
         <v>27</v>
       </c>
@@ -22438,8 +22966,8 @@
       <c r="O51" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="P51" s="106"/>
-      <c r="Q51" s="106"/>
+      <c r="P51" s="108"/>
+      <c r="Q51" s="108"/>
     </row>
     <row r="52" spans="1:17" ht="57.6" customHeight="1">
       <c r="A52" s="40" t="s">
@@ -22540,7 +23068,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="1:17" ht="43.15" customHeight="1">
+    <row r="55" spans="1:17" ht="43.2" customHeight="1">
       <c r="A55" s="40" t="s">
         <v>51</v>
       </c>
@@ -22573,7 +23101,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="28.9" customHeight="1">
+    <row r="56" spans="1:17" ht="28.95" customHeight="1">
       <c r="A56" s="43" t="s">
         <v>52</v>
       </c>
@@ -22617,80 +23145,80 @@
       </c>
     </row>
     <row r="57" spans="1:17">
-      <c r="A57" s="107" t="s">
+      <c r="A57" s="109" t="s">
         <v>53</v>
       </c>
-      <c r="B57" s="106"/>
-      <c r="C57" s="106"/>
-      <c r="D57" s="106"/>
-      <c r="E57" s="106"/>
-      <c r="F57" s="106"/>
-      <c r="G57" s="106"/>
-      <c r="H57" s="106"/>
-      <c r="I57" s="106"/>
-      <c r="J57" s="106"/>
-      <c r="K57" s="106"/>
-      <c r="L57" s="106"/>
-      <c r="M57" s="106"/>
-      <c r="N57" s="106"/>
-      <c r="O57" s="106"/>
-      <c r="P57" s="106"/>
-      <c r="Q57" s="106"/>
+      <c r="B57" s="108"/>
+      <c r="C57" s="108"/>
+      <c r="D57" s="108"/>
+      <c r="E57" s="108"/>
+      <c r="F57" s="108"/>
+      <c r="G57" s="108"/>
+      <c r="H57" s="108"/>
+      <c r="I57" s="108"/>
+      <c r="J57" s="108"/>
+      <c r="K57" s="108"/>
+      <c r="L57" s="108"/>
+      <c r="M57" s="108"/>
+      <c r="N57" s="108"/>
+      <c r="O57" s="108"/>
+      <c r="P57" s="108"/>
+      <c r="Q57" s="108"/>
     </row>
     <row r="58" spans="1:17">
-      <c r="A58" s="106"/>
-      <c r="B58" s="106"/>
-      <c r="C58" s="106"/>
-      <c r="D58" s="106"/>
-      <c r="E58" s="106"/>
-      <c r="F58" s="106"/>
-      <c r="G58" s="106"/>
-      <c r="H58" s="106"/>
-      <c r="I58" s="106"/>
-      <c r="J58" s="106"/>
-      <c r="K58" s="106"/>
-      <c r="L58" s="106"/>
-      <c r="M58" s="106"/>
-      <c r="N58" s="106"/>
-      <c r="O58" s="106"/>
-      <c r="P58" s="106"/>
-      <c r="Q58" s="106"/>
-    </row>
-    <row r="59" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A59" s="108" t="s">
+      <c r="A58" s="108"/>
+      <c r="B58" s="108"/>
+      <c r="C58" s="108"/>
+      <c r="D58" s="108"/>
+      <c r="E58" s="108"/>
+      <c r="F58" s="108"/>
+      <c r="G58" s="108"/>
+      <c r="H58" s="108"/>
+      <c r="I58" s="108"/>
+      <c r="J58" s="108"/>
+      <c r="K58" s="108"/>
+      <c r="L58" s="108"/>
+      <c r="M58" s="108"/>
+      <c r="N58" s="108"/>
+      <c r="O58" s="108"/>
+      <c r="P58" s="108"/>
+      <c r="Q58" s="108"/>
+    </row>
+    <row r="59" spans="1:17" ht="14.4" customHeight="1">
+      <c r="A59" s="110" t="s">
         <v>20</v>
       </c>
-      <c r="B59" s="105" t="s">
+      <c r="B59" s="107" t="s">
         <v>21</v>
       </c>
-      <c r="C59" s="106"/>
-      <c r="D59" s="106"/>
-      <c r="E59" s="105" t="s">
+      <c r="C59" s="108"/>
+      <c r="D59" s="108"/>
+      <c r="E59" s="107" t="s">
         <v>22</v>
       </c>
-      <c r="F59" s="106"/>
-      <c r="G59" s="106"/>
-      <c r="H59" s="105" t="s">
+      <c r="F59" s="108"/>
+      <c r="G59" s="108"/>
+      <c r="H59" s="107" t="s">
         <v>23</v>
       </c>
-      <c r="I59" s="106"/>
-      <c r="J59" s="106"/>
-      <c r="K59" s="105" t="s">
+      <c r="I59" s="108"/>
+      <c r="J59" s="108"/>
+      <c r="K59" s="107" t="s">
         <v>24</v>
       </c>
-      <c r="L59" s="106"/>
-      <c r="M59" s="106"/>
-      <c r="N59" s="106"/>
-      <c r="O59" s="106"/>
-      <c r="P59" s="105" t="s">
+      <c r="L59" s="108"/>
+      <c r="M59" s="108"/>
+      <c r="N59" s="108"/>
+      <c r="O59" s="108"/>
+      <c r="P59" s="107" t="s">
         <v>25</v>
       </c>
-      <c r="Q59" s="105" t="s">
+      <c r="Q59" s="107" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="60" spans="1:17">
-      <c r="A60" s="106"/>
+      <c r="A60" s="108"/>
       <c r="B60" s="40" t="s">
         <v>27</v>
       </c>
@@ -22733,8 +23261,8 @@
       <c r="O60" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="P60" s="106"/>
-      <c r="Q60" s="106"/>
+      <c r="P60" s="108"/>
+      <c r="Q60" s="108"/>
     </row>
     <row r="61" spans="1:17" ht="57.6" customHeight="1">
       <c r="A61" s="40" t="s">
@@ -22802,7 +23330,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:17" ht="28.9" customHeight="1">
+    <row r="63" spans="1:17" ht="28.95" customHeight="1">
       <c r="A63" s="40" t="s">
         <v>56</v>
       </c>
@@ -22835,7 +23363,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="115.15" customHeight="1">
+    <row r="64" spans="1:17" ht="115.2" customHeight="1">
       <c r="A64" s="40" t="s">
         <v>57</v>
       </c>
@@ -22868,7 +23396,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:17" ht="43.15" customHeight="1">
+    <row r="65" spans="1:17" ht="43.2" customHeight="1">
       <c r="A65" s="40" t="s">
         <v>58</v>
       </c>
@@ -23033,7 +23561,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:17" ht="86.45" customHeight="1">
+    <row r="70" spans="1:17" ht="86.4" customHeight="1">
       <c r="A70" s="40" t="s">
         <v>63</v>
       </c>
@@ -23165,7 +23693,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="43.15" customHeight="1">
+    <row r="74" spans="1:17" ht="43.2" customHeight="1">
       <c r="A74" s="43" t="s">
         <v>53</v>
       </c>
@@ -23209,80 +23737,80 @@
       </c>
     </row>
     <row r="75" spans="1:17">
-      <c r="A75" s="107" t="s">
+      <c r="A75" s="109" t="s">
         <v>67</v>
       </c>
-      <c r="B75" s="106"/>
-      <c r="C75" s="106"/>
-      <c r="D75" s="106"/>
-      <c r="E75" s="106"/>
-      <c r="F75" s="106"/>
-      <c r="G75" s="106"/>
-      <c r="H75" s="106"/>
-      <c r="I75" s="106"/>
-      <c r="J75" s="106"/>
-      <c r="K75" s="106"/>
-      <c r="L75" s="106"/>
-      <c r="M75" s="106"/>
-      <c r="N75" s="106"/>
-      <c r="O75" s="106"/>
-      <c r="P75" s="106"/>
-      <c r="Q75" s="106"/>
+      <c r="B75" s="108"/>
+      <c r="C75" s="108"/>
+      <c r="D75" s="108"/>
+      <c r="E75" s="108"/>
+      <c r="F75" s="108"/>
+      <c r="G75" s="108"/>
+      <c r="H75" s="108"/>
+      <c r="I75" s="108"/>
+      <c r="J75" s="108"/>
+      <c r="K75" s="108"/>
+      <c r="L75" s="108"/>
+      <c r="M75" s="108"/>
+      <c r="N75" s="108"/>
+      <c r="O75" s="108"/>
+      <c r="P75" s="108"/>
+      <c r="Q75" s="108"/>
     </row>
     <row r="76" spans="1:17">
-      <c r="A76" s="106"/>
-      <c r="B76" s="106"/>
-      <c r="C76" s="106"/>
-      <c r="D76" s="106"/>
-      <c r="E76" s="106"/>
-      <c r="F76" s="106"/>
-      <c r="G76" s="106"/>
-      <c r="H76" s="106"/>
-      <c r="I76" s="106"/>
-      <c r="J76" s="106"/>
-      <c r="K76" s="106"/>
-      <c r="L76" s="106"/>
-      <c r="M76" s="106"/>
-      <c r="N76" s="106"/>
-      <c r="O76" s="106"/>
-      <c r="P76" s="106"/>
-      <c r="Q76" s="106"/>
-    </row>
-    <row r="77" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A77" s="108" t="s">
+      <c r="A76" s="108"/>
+      <c r="B76" s="108"/>
+      <c r="C76" s="108"/>
+      <c r="D76" s="108"/>
+      <c r="E76" s="108"/>
+      <c r="F76" s="108"/>
+      <c r="G76" s="108"/>
+      <c r="H76" s="108"/>
+      <c r="I76" s="108"/>
+      <c r="J76" s="108"/>
+      <c r="K76" s="108"/>
+      <c r="L76" s="108"/>
+      <c r="M76" s="108"/>
+      <c r="N76" s="108"/>
+      <c r="O76" s="108"/>
+      <c r="P76" s="108"/>
+      <c r="Q76" s="108"/>
+    </row>
+    <row r="77" spans="1:17" ht="14.4" customHeight="1">
+      <c r="A77" s="110" t="s">
         <v>20</v>
       </c>
-      <c r="B77" s="105" t="s">
+      <c r="B77" s="107" t="s">
         <v>21</v>
       </c>
-      <c r="C77" s="106"/>
-      <c r="D77" s="106"/>
-      <c r="E77" s="105" t="s">
+      <c r="C77" s="108"/>
+      <c r="D77" s="108"/>
+      <c r="E77" s="107" t="s">
         <v>22</v>
       </c>
-      <c r="F77" s="106"/>
-      <c r="G77" s="106"/>
-      <c r="H77" s="105" t="s">
+      <c r="F77" s="108"/>
+      <c r="G77" s="108"/>
+      <c r="H77" s="107" t="s">
         <v>23</v>
       </c>
-      <c r="I77" s="106"/>
-      <c r="J77" s="106"/>
-      <c r="K77" s="105" t="s">
+      <c r="I77" s="108"/>
+      <c r="J77" s="108"/>
+      <c r="K77" s="107" t="s">
         <v>24</v>
       </c>
-      <c r="L77" s="106"/>
-      <c r="M77" s="106"/>
-      <c r="N77" s="106"/>
-      <c r="O77" s="106"/>
-      <c r="P77" s="105" t="s">
+      <c r="L77" s="108"/>
+      <c r="M77" s="108"/>
+      <c r="N77" s="108"/>
+      <c r="O77" s="108"/>
+      <c r="P77" s="107" t="s">
         <v>25</v>
       </c>
-      <c r="Q77" s="105" t="s">
+      <c r="Q77" s="107" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="78" spans="1:17">
-      <c r="A78" s="106"/>
+      <c r="A78" s="108"/>
       <c r="B78" s="40" t="s">
         <v>27</v>
       </c>
@@ -23325,10 +23853,10 @@
       <c r="O78" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="P78" s="106"/>
-      <c r="Q78" s="106"/>
-    </row>
-    <row r="79" spans="1:17" ht="28.9" customHeight="1">
+      <c r="P78" s="108"/>
+      <c r="Q78" s="108"/>
+    </row>
+    <row r="79" spans="1:17" ht="28.95" customHeight="1">
       <c r="A79" s="40" t="s">
         <v>68</v>
       </c>
@@ -23380,80 +23908,80 @@
       </c>
     </row>
     <row r="80" spans="1:17">
-      <c r="A80" s="107" t="s">
+      <c r="A80" s="109" t="s">
         <v>69</v>
       </c>
-      <c r="B80" s="106"/>
-      <c r="C80" s="106"/>
-      <c r="D80" s="106"/>
-      <c r="E80" s="106"/>
-      <c r="F80" s="106"/>
-      <c r="G80" s="106"/>
-      <c r="H80" s="106"/>
-      <c r="I80" s="106"/>
-      <c r="J80" s="106"/>
-      <c r="K80" s="106"/>
-      <c r="L80" s="106"/>
-      <c r="M80" s="106"/>
-      <c r="N80" s="106"/>
-      <c r="O80" s="106"/>
-      <c r="P80" s="106"/>
-      <c r="Q80" s="106"/>
+      <c r="B80" s="108"/>
+      <c r="C80" s="108"/>
+      <c r="D80" s="108"/>
+      <c r="E80" s="108"/>
+      <c r="F80" s="108"/>
+      <c r="G80" s="108"/>
+      <c r="H80" s="108"/>
+      <c r="I80" s="108"/>
+      <c r="J80" s="108"/>
+      <c r="K80" s="108"/>
+      <c r="L80" s="108"/>
+      <c r="M80" s="108"/>
+      <c r="N80" s="108"/>
+      <c r="O80" s="108"/>
+      <c r="P80" s="108"/>
+      <c r="Q80" s="108"/>
     </row>
     <row r="81" spans="1:17">
-      <c r="A81" s="106"/>
-      <c r="B81" s="106"/>
-      <c r="C81" s="106"/>
-      <c r="D81" s="106"/>
-      <c r="E81" s="106"/>
-      <c r="F81" s="106"/>
-      <c r="G81" s="106"/>
-      <c r="H81" s="106"/>
-      <c r="I81" s="106"/>
-      <c r="J81" s="106"/>
-      <c r="K81" s="106"/>
-      <c r="L81" s="106"/>
-      <c r="M81" s="106"/>
-      <c r="N81" s="106"/>
-      <c r="O81" s="106"/>
-      <c r="P81" s="106"/>
-      <c r="Q81" s="106"/>
-    </row>
-    <row r="82" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A82" s="108" t="s">
+      <c r="A81" s="108"/>
+      <c r="B81" s="108"/>
+      <c r="C81" s="108"/>
+      <c r="D81" s="108"/>
+      <c r="E81" s="108"/>
+      <c r="F81" s="108"/>
+      <c r="G81" s="108"/>
+      <c r="H81" s="108"/>
+      <c r="I81" s="108"/>
+      <c r="J81" s="108"/>
+      <c r="K81" s="108"/>
+      <c r="L81" s="108"/>
+      <c r="M81" s="108"/>
+      <c r="N81" s="108"/>
+      <c r="O81" s="108"/>
+      <c r="P81" s="108"/>
+      <c r="Q81" s="108"/>
+    </row>
+    <row r="82" spans="1:17" ht="14.4" customHeight="1">
+      <c r="A82" s="110" t="s">
         <v>20</v>
       </c>
-      <c r="B82" s="105" t="s">
+      <c r="B82" s="107" t="s">
         <v>21</v>
       </c>
-      <c r="C82" s="106"/>
-      <c r="D82" s="106"/>
-      <c r="E82" s="105" t="s">
+      <c r="C82" s="108"/>
+      <c r="D82" s="108"/>
+      <c r="E82" s="107" t="s">
         <v>22</v>
       </c>
-      <c r="F82" s="106"/>
-      <c r="G82" s="106"/>
-      <c r="H82" s="105" t="s">
+      <c r="F82" s="108"/>
+      <c r="G82" s="108"/>
+      <c r="H82" s="107" t="s">
         <v>23</v>
       </c>
-      <c r="I82" s="106"/>
-      <c r="J82" s="106"/>
-      <c r="K82" s="105" t="s">
+      <c r="I82" s="108"/>
+      <c r="J82" s="108"/>
+      <c r="K82" s="107" t="s">
         <v>24</v>
       </c>
-      <c r="L82" s="106"/>
-      <c r="M82" s="106"/>
-      <c r="N82" s="106"/>
-      <c r="O82" s="106"/>
-      <c r="P82" s="105" t="s">
+      <c r="L82" s="108"/>
+      <c r="M82" s="108"/>
+      <c r="N82" s="108"/>
+      <c r="O82" s="108"/>
+      <c r="P82" s="107" t="s">
         <v>25</v>
       </c>
-      <c r="Q82" s="105" t="s">
+      <c r="Q82" s="107" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="83" spans="1:17">
-      <c r="A83" s="106"/>
+      <c r="A83" s="108"/>
       <c r="B83" s="40" t="s">
         <v>27</v>
       </c>
@@ -23496,8 +24024,8 @@
       <c r="O83" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="P83" s="106"/>
-      <c r="Q83" s="106"/>
+      <c r="P83" s="108"/>
+      <c r="Q83" s="108"/>
     </row>
     <row r="84" spans="1:17" ht="57.6" customHeight="1">
       <c r="A84" s="40" t="s">
@@ -23718,7 +24246,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:G78"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
@@ -23728,18 +24256,18 @@
     <col min="7" max="7" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="22.15" customHeight="1">
-      <c r="A1" s="110" t="s">
+    <row r="1" spans="1:7" ht="22.2" customHeight="1">
+      <c r="A1" s="112" t="s">
         <v>846</v>
       </c>
-      <c r="B1" s="106"/>
-      <c r="C1" s="106"/>
-      <c r="D1" s="106"/>
-      <c r="E1" s="106"/>
-      <c r="F1" s="106"/>
-      <c r="G1" s="106"/>
-    </row>
-    <row r="2" spans="1:7" ht="37.9" customHeight="1">
+      <c r="B1" s="108"/>
+      <c r="C1" s="108"/>
+      <c r="D1" s="108"/>
+      <c r="E1" s="108"/>
+      <c r="F1" s="108"/>
+      <c r="G1" s="108"/>
+    </row>
+    <row r="2" spans="1:7" ht="37.950000000000003" customHeight="1">
       <c r="A2" s="45" t="s">
         <v>847</v>
       </c>
@@ -23762,7 +24290,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="31.9" customHeight="1">
+    <row r="3" spans="1:7" ht="31.95" customHeight="1">
       <c r="A3" s="52" t="s">
         <v>854</v>
       </c>
@@ -23785,7 +24313,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="4" spans="1:7" ht="16.2" customHeight="1">
       <c r="A4" s="46" t="s">
         <v>126</v>
       </c>
@@ -23806,7 +24334,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="5" spans="1:7" ht="16.2" customHeight="1">
       <c r="A5" s="46" t="s">
         <v>37</v>
       </c>
@@ -23827,7 +24355,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="6" spans="1:7" ht="16.2" customHeight="1">
       <c r="A6" s="46" t="s">
         <v>122</v>
       </c>
@@ -23848,7 +24376,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="7" spans="1:7" ht="16.2" customHeight="1">
       <c r="A7" s="46" t="s">
         <v>209</v>
       </c>
@@ -23869,7 +24397,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="8" spans="1:7" ht="16.2" customHeight="1">
       <c r="A8" s="46" t="s">
         <v>662</v>
       </c>
@@ -23890,7 +24418,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="9" spans="1:7" ht="16.2" customHeight="1">
       <c r="A9" s="46" t="s">
         <v>104</v>
       </c>
@@ -23913,7 +24441,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="10" spans="1:7" ht="16.2" customHeight="1">
       <c r="A10" s="46" t="s">
         <v>104</v>
       </c>
@@ -23936,7 +24464,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="11" spans="1:7" ht="16.2" customHeight="1">
       <c r="A11" s="46" t="s">
         <v>104</v>
       </c>
@@ -23959,7 +24487,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="12" spans="1:7" ht="16.2" customHeight="1">
       <c r="A12" s="46" t="s">
         <v>99</v>
       </c>
@@ -23980,7 +24508,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="13" spans="1:7" ht="16.2" customHeight="1">
       <c r="A13" s="46" t="s">
         <v>99</v>
       </c>
@@ -24001,7 +24529,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="14" spans="1:7" ht="16.2" customHeight="1">
       <c r="A14" s="46" t="s">
         <v>280</v>
       </c>
@@ -24022,7 +24550,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="15" spans="1:7" ht="16.2" customHeight="1">
       <c r="A15" s="46" t="s">
         <v>185</v>
       </c>
@@ -24043,7 +24571,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="16" spans="1:7" ht="16.2" customHeight="1">
       <c r="A16" s="46" t="s">
         <v>112</v>
       </c>
@@ -24064,7 +24592,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="17" spans="1:7" ht="16.2" customHeight="1">
       <c r="A17" s="46" t="s">
         <v>115</v>
       </c>
@@ -24085,7 +24613,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="18" spans="1:7" ht="16.2" customHeight="1">
       <c r="A18" s="46" t="s">
         <v>342</v>
       </c>
@@ -24106,7 +24634,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="19" spans="1:7" ht="16.2" customHeight="1">
       <c r="A19" s="46" t="s">
         <v>141</v>
       </c>
@@ -24127,7 +24655,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="20" spans="1:7" ht="16.2" customHeight="1">
       <c r="A20" s="46" t="s">
         <v>255</v>
       </c>
@@ -24148,7 +24676,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="21" spans="1:7" ht="16.2" customHeight="1">
       <c r="A21" s="46" t="s">
         <v>367</v>
       </c>
@@ -24169,7 +24697,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="22" spans="1:7" ht="16.2" customHeight="1">
       <c r="A22" s="46" t="s">
         <v>740</v>
       </c>
@@ -24190,7 +24718,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="23" spans="1:7" ht="16.2" customHeight="1">
       <c r="A23" s="46" t="s">
         <v>749</v>
       </c>
@@ -24211,7 +24739,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="24" spans="1:7" ht="16.2" customHeight="1">
       <c r="A24" s="46" t="s">
         <v>753</v>
       </c>
@@ -24232,7 +24760,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="25" spans="1:7" ht="16.2" customHeight="1">
       <c r="A25" s="46" t="s">
         <v>745</v>
       </c>
@@ -24253,7 +24781,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="26" spans="1:7" ht="16.2" customHeight="1">
       <c r="A26" s="46" t="s">
         <v>757</v>
       </c>
@@ -24274,7 +24802,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="27" spans="1:7" ht="16.2" customHeight="1">
       <c r="A27" s="46" t="s">
         <v>761</v>
       </c>
@@ -24295,7 +24823,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="28" spans="1:7" ht="16.2" customHeight="1">
       <c r="A28" s="48" t="s">
         <v>126</v>
       </c>
@@ -24316,7 +24844,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="29" spans="1:7" ht="16.2" customHeight="1">
       <c r="A29" s="48" t="s">
         <v>280</v>
       </c>
@@ -24337,7 +24865,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="30" spans="1:7" ht="16.2" customHeight="1">
       <c r="A30" s="48" t="s">
         <v>185</v>
       </c>
@@ -24358,7 +24886,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="31" spans="1:7" ht="16.2" customHeight="1">
       <c r="A31" s="48" t="s">
         <v>104</v>
       </c>
@@ -24381,7 +24909,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="32" spans="1:7" ht="16.2" customHeight="1">
       <c r="A32" s="48" t="s">
         <v>104</v>
       </c>
@@ -24402,7 +24930,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="33" spans="1:7" ht="16.2" customHeight="1">
       <c r="A33" s="48" t="s">
         <v>37</v>
       </c>
@@ -24423,7 +24951,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="34" spans="1:7" ht="16.2" customHeight="1">
       <c r="A34" s="48" t="s">
         <v>229</v>
       </c>
@@ -24442,7 +24970,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="35" spans="1:7" ht="16.2" customHeight="1">
       <c r="A35" s="48" t="s">
         <v>122</v>
       </c>
@@ -24463,7 +24991,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="36" spans="1:7" ht="16.2" customHeight="1">
       <c r="A36" s="48" t="s">
         <v>209</v>
       </c>
@@ -24484,7 +25012,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="37" spans="1:7" ht="16.2" customHeight="1">
       <c r="A37" s="48" t="s">
         <v>99</v>
       </c>
@@ -24505,7 +25033,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="38" spans="1:7" ht="16.2" customHeight="1">
       <c r="A38" s="48" t="s">
         <v>99</v>
       </c>
@@ -24526,7 +25054,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="39" spans="1:7" ht="16.2" customHeight="1">
       <c r="A39" s="48" t="s">
         <v>115</v>
       </c>
@@ -24547,7 +25075,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="40" spans="1:7" ht="16.2" customHeight="1">
       <c r="A40" s="48" t="s">
         <v>112</v>
       </c>
@@ -24568,7 +25096,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="41" spans="1:7" ht="16.2" customHeight="1">
       <c r="A41" s="53" t="s">
         <v>342</v>
       </c>
@@ -24589,7 +25117,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="42" spans="1:7" ht="16.2" customHeight="1">
       <c r="A42" s="48" t="s">
         <v>141</v>
       </c>
@@ -24610,7 +25138,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="43" spans="1:7" ht="16.2" customHeight="1">
       <c r="A43" s="48" t="s">
         <v>255</v>
       </c>
@@ -24631,7 +25159,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="44" spans="1:7" ht="16.2" customHeight="1">
       <c r="A44" s="53" t="s">
         <v>367</v>
       </c>
@@ -24652,7 +25180,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="45" spans="1:7" ht="16.2" customHeight="1">
       <c r="A45" s="57" t="s">
         <v>699</v>
       </c>
@@ -24673,7 +25201,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="46" spans="1:7" ht="16.2" customHeight="1">
       <c r="A46" s="50" t="s">
         <v>229</v>
       </c>
@@ -24692,7 +25220,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="47" spans="1:7" ht="16.2" customHeight="1">
       <c r="A47" s="50" t="s">
         <v>88</v>
       </c>
@@ -24711,7 +25239,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="48" spans="1:7" ht="16.2" customHeight="1">
       <c r="A48" s="50" t="s">
         <v>88</v>
       </c>
@@ -24732,7 +25260,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="49" spans="1:7" ht="16.2" customHeight="1">
       <c r="A49" s="50" t="s">
         <v>88</v>
       </c>
@@ -24753,7 +25281,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="50" spans="1:7" ht="16.2" customHeight="1">
       <c r="A50" s="53" t="s">
         <v>695</v>
       </c>
@@ -24774,7 +25302,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="51" spans="1:7" ht="16.2" customHeight="1">
       <c r="A51" s="55" t="s">
         <v>703</v>
       </c>
@@ -24795,7 +25323,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="52" spans="1:7" ht="16.2" customHeight="1">
       <c r="A52" s="50" t="s">
         <v>667</v>
       </c>
@@ -24814,7 +25342,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="53" spans="1:7" ht="16.2" customHeight="1">
       <c r="A53" s="50" t="s">
         <v>672</v>
       </c>
@@ -24833,7 +25361,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="54" spans="1:7" ht="16.2" customHeight="1">
       <c r="A54" s="50" t="s">
         <v>677</v>
       </c>
@@ -24852,7 +25380,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="55" spans="1:7" ht="16.2" customHeight="1">
       <c r="A55" s="53" t="s">
         <v>136</v>
       </c>
@@ -24871,7 +25399,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="56" spans="1:7" ht="16.2" customHeight="1">
       <c r="A56" s="53" t="s">
         <v>136</v>
       </c>
@@ -24890,7 +25418,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="57" spans="1:7" ht="16.2" customHeight="1">
       <c r="A57" s="55" t="s">
         <v>337</v>
       </c>
@@ -24911,7 +25439,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="58" spans="1:7" ht="16.2" customHeight="1">
       <c r="A58" s="55" t="s">
         <v>337</v>
       </c>
@@ -24932,7 +25460,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="59" spans="1:7" ht="16.2" customHeight="1">
       <c r="A59" s="55" t="s">
         <v>167</v>
       </c>
@@ -24953,7 +25481,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="60" spans="1:7" ht="16.2" customHeight="1">
       <c r="A60" s="55" t="s">
         <v>91</v>
       </c>
@@ -24974,7 +25502,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="61" spans="1:7" ht="16.2" customHeight="1">
       <c r="A61" s="55" t="s">
         <v>91</v>
       </c>
@@ -24995,7 +25523,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="62" spans="1:7" ht="16.2" customHeight="1">
       <c r="A62" s="55" t="s">
         <v>191</v>
       </c>
@@ -25016,7 +25544,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="63" spans="1:7" ht="16.2" customHeight="1">
       <c r="A63" s="55" t="s">
         <v>191</v>
       </c>
@@ -25037,7 +25565,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="64" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="64" spans="1:7" ht="16.2" customHeight="1">
       <c r="A64" s="55" t="s">
         <v>144</v>
       </c>
@@ -25058,7 +25586,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="65" spans="1:7" ht="16.2" customHeight="1">
       <c r="A65" s="55" t="s">
         <v>144</v>
       </c>
@@ -25079,7 +25607,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="66" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="66" spans="1:7" ht="16.2" customHeight="1">
       <c r="A66" s="55" t="s">
         <v>85</v>
       </c>
@@ -25100,7 +25628,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="67" spans="1:7" ht="16.2" customHeight="1">
       <c r="A67" s="55" t="s">
         <v>319</v>
       </c>
@@ -25121,7 +25649,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="68" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="68" spans="1:7" ht="16.2" customHeight="1">
       <c r="A68" s="55" t="s">
         <v>319</v>
       </c>
@@ -25142,7 +25670,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="69" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="69" spans="1:7" ht="16.2" customHeight="1">
       <c r="A69" s="55" t="s">
         <v>264</v>
       </c>
@@ -25163,7 +25691,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="70" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="70" spans="1:7" ht="16.2" customHeight="1">
       <c r="A70" s="55" t="s">
         <v>264</v>
       </c>
@@ -25184,7 +25712,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="71" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="71" spans="1:7" ht="16.2" customHeight="1">
       <c r="A71" s="55" t="s">
         <v>425</v>
       </c>
@@ -25205,7 +25733,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="72" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="72" spans="1:7" ht="16.2" customHeight="1">
       <c r="A72" s="55" t="s">
         <v>455</v>
       </c>
@@ -25226,7 +25754,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="73" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="73" spans="1:7" ht="16.2" customHeight="1">
       <c r="A73" s="55" t="s">
         <v>687</v>
       </c>
@@ -25247,7 +25775,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="74" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="74" spans="1:7" ht="16.2" customHeight="1">
       <c r="A74" s="55" t="s">
         <v>691</v>
       </c>
@@ -25268,7 +25796,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="75" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="75" spans="1:7" ht="16.2" customHeight="1">
       <c r="A75" s="55" t="s">
         <v>194</v>
       </c>
@@ -25289,7 +25817,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="76" spans="1:7" ht="16.149999999999999" customHeight="1">
+    <row r="76" spans="1:7" ht="16.2" customHeight="1">
       <c r="A76" s="55" t="s">
         <v>194</v>
       </c>
@@ -25311,15 +25839,15 @@
       </c>
     </row>
     <row r="78" spans="1:7">
-      <c r="A78" s="109" t="s">
+      <c r="A78" s="111" t="s">
         <v>882</v>
       </c>
-      <c r="B78" s="106"/>
-      <c r="C78" s="106"/>
-      <c r="D78" s="106"/>
-      <c r="E78" s="106"/>
-      <c r="F78" s="106"/>
-      <c r="G78" s="106"/>
+      <c r="B78" s="108"/>
+      <c r="C78" s="108"/>
+      <c r="D78" s="108"/>
+      <c r="E78" s="108"/>
+      <c r="F78" s="108"/>
+      <c r="G78" s="108"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/anciens_eleves.xlsx
+++ b/anciens_eleves.xlsx
@@ -5816,7 +5816,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K296"/>
+  <dimension ref="A1:K307"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="27.42578125" customWidth="1"/>
@@ -5832,13 +5832,14 @@
     <col min="11" max="11" width="14.7109375" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1">
       <c r="A1" s="67" t="s">
         <v>74</v>
       </c>
-      <c r="B1" s="34" t="str">
-        <f t="shared" ref="B1:B64" si="0">LEFT(A1)</f>
-        <v>N</v>
+      <c r="B1" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Initiale NOM</t>
+        </is>
       </c>
       <c r="C1" s="2" t="s">
         <v>75</v>
@@ -5868,12 +5869,12 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2">
       <c r="A2" s="93" t="s">
         <v>1096</v>
       </c>
       <c r="B2" s="61" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A2)</f>
         <v>P</v>
       </c>
       <c r="C2" s="93" t="s">
@@ -5892,12 +5893,12 @@
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3">
       <c r="A3" s="93" t="s">
         <v>1094</v>
       </c>
       <c r="B3" s="61" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A3)</f>
         <v>O</v>
       </c>
       <c r="C3" s="93" t="s">
@@ -5916,12 +5917,12 @@
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4">
       <c r="A4" s="81" t="s">
         <v>925</v>
       </c>
       <c r="B4" s="61" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A4)</f>
         <v>T</v>
       </c>
       <c r="C4" s="61" t="s">
@@ -5942,12 +5943,12 @@
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5">
       <c r="A5" s="80" t="s">
         <v>922</v>
       </c>
       <c r="B5" s="61" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A5)</f>
         <v>R</v>
       </c>
       <c r="C5" s="61" t="s">
@@ -5966,12 +5967,12 @@
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6">
       <c r="A6" s="80" t="s">
         <v>882</v>
       </c>
       <c r="B6" s="61" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A6)</f>
         <v>G</v>
       </c>
       <c r="C6" s="61" t="s">
@@ -5993,12 +5994,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7">
       <c r="A7" s="73" t="s">
         <v>877</v>
       </c>
       <c r="B7" s="61" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A7)</f>
         <v>G</v>
       </c>
       <c r="C7" s="61" t="s">
@@ -6017,12 +6018,12 @@
       <c r="H7" s="74"/>
       <c r="I7" s="74"/>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8">
       <c r="A8" s="69" t="s">
         <v>875</v>
       </c>
       <c r="B8" s="61" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A8)</f>
         <v>S</v>
       </c>
       <c r="C8" s="61" t="s">
@@ -6046,12 +6047,14 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
-      <c r="A9" s="69" t="s">
-        <v>327</v>
+    <row r="9">
+      <c r="A9" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THIBAULT</t>
+        </is>
       </c>
       <c r="B9" s="61" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A9)</f>
         <v>T</v>
       </c>
       <c r="C9" s="61" t="s">
@@ -6070,12 +6073,12 @@
       <c r="H9" s="61"/>
       <c r="I9" s="61"/>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10">
       <c r="A10" s="65" t="s">
         <v>867</v>
       </c>
       <c r="B10" s="61" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A10)</f>
         <v>B</v>
       </c>
       <c r="C10" s="61" t="s">
@@ -6094,12 +6097,12 @@
       <c r="H10" s="71"/>
       <c r="I10" s="71"/>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11">
       <c r="A11" s="65" t="s">
         <v>865</v>
       </c>
       <c r="B11" s="61" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A11)</f>
         <v>B</v>
       </c>
       <c r="C11" s="61" t="s">
@@ -6118,12 +6121,12 @@
       <c r="H11" s="61"/>
       <c r="I11" s="61"/>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12">
       <c r="A12" s="65" t="s">
         <v>860</v>
       </c>
       <c r="B12" s="61" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A12)</f>
         <v>K</v>
       </c>
       <c r="C12" s="61" t="s">
@@ -6142,12 +6145,12 @@
       <c r="H12" s="61"/>
       <c r="I12" s="61"/>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13">
       <c r="A13" s="65" t="s">
         <v>858</v>
       </c>
       <c r="B13" s="61" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A13)</f>
         <v>C</v>
       </c>
       <c r="C13" s="61" t="s">
@@ -6169,12 +6172,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14">
       <c r="A14" s="65" t="s">
         <v>856</v>
       </c>
       <c r="B14" s="61" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A14)</f>
         <v>V</v>
       </c>
       <c r="C14" s="61" t="s">
@@ -6198,12 +6201,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15">
       <c r="A15" s="66" t="s">
         <v>854</v>
       </c>
       <c r="B15" s="63" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A15)</f>
         <v>H</v>
       </c>
       <c r="C15" s="61" t="s">
@@ -6225,12 +6228,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16">
       <c r="A16" s="63" t="s">
         <v>82</v>
       </c>
       <c r="B16" s="63" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A16)</f>
         <v>A</v>
       </c>
       <c r="C16" s="63" t="s">
@@ -6249,12 +6252,12 @@
       <c r="H16" s="64"/>
       <c r="I16" s="64"/>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17">
       <c r="A17" s="1" t="s">
         <v>85</v>
       </c>
       <c r="B17" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A17)</f>
         <v>A</v>
       </c>
       <c r="C17" s="1" t="s">
@@ -6272,12 +6275,12 @@
       <c r="G17" s="1"/>
       <c r="H17" s="72"/>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18">
       <c r="A18" s="1" t="s">
         <v>88</v>
       </c>
       <c r="B18" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A18)</f>
         <v>B</v>
       </c>
       <c r="C18" s="1" t="s">
@@ -6294,12 +6297,12 @@
       </c>
       <c r="G18" s="1"/>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19">
       <c r="A19" s="1" t="s">
         <v>91</v>
       </c>
       <c r="B19" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A19)</f>
         <v>C</v>
       </c>
       <c r="C19" s="1" t="s">
@@ -6316,12 +6319,12 @@
       </c>
       <c r="G19" s="1"/>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20">
       <c r="A20" s="1" t="s">
         <v>94</v>
       </c>
       <c r="B20" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A20)</f>
         <v>D</v>
       </c>
       <c r="C20" s="1" t="s">
@@ -6338,12 +6341,12 @@
       </c>
       <c r="G20" s="1"/>
     </row>
-    <row r="21" spans="1:11">
+    <row r="21">
       <c r="A21" s="1" t="s">
         <v>96</v>
       </c>
       <c r="B21" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A21)</f>
         <v>D</v>
       </c>
       <c r="C21" s="1" t="s">
@@ -6360,12 +6363,12 @@
       </c>
       <c r="G21" s="1"/>
     </row>
-    <row r="22" spans="1:11">
+    <row r="22">
       <c r="A22" s="33" t="s">
         <v>99</v>
       </c>
       <c r="B22" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A22)</f>
         <v>F</v>
       </c>
       <c r="C22" s="1" t="s">
@@ -6382,12 +6385,12 @@
       </c>
       <c r="G22" s="1"/>
     </row>
-    <row r="23" spans="1:11">
+    <row r="23">
       <c r="A23" s="33" t="s">
         <v>101</v>
       </c>
       <c r="B23" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A23)</f>
         <v>F</v>
       </c>
       <c r="C23" s="1" t="s">
@@ -6407,12 +6410,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="24" spans="1:11">
+    <row r="24">
       <c r="A24" s="33" t="s">
         <v>104</v>
       </c>
       <c r="B24" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A24)</f>
         <v>G</v>
       </c>
       <c r="C24" s="1" t="s">
@@ -6429,12 +6432,12 @@
       </c>
       <c r="G24" s="1"/>
     </row>
-    <row r="25" spans="1:11">
+    <row r="25">
       <c r="A25" s="33" t="s">
         <v>107</v>
       </c>
       <c r="B25" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A25)</f>
         <v>H</v>
       </c>
       <c r="C25" s="1" t="s">
@@ -6451,12 +6454,12 @@
       </c>
       <c r="G25" s="1"/>
     </row>
-    <row r="26" spans="1:11">
+    <row r="26">
       <c r="A26" s="33" t="s">
         <v>109</v>
       </c>
       <c r="B26" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A26)</f>
         <v>J</v>
       </c>
       <c r="C26" s="1" t="s">
@@ -6473,12 +6476,12 @@
       </c>
       <c r="G26" s="1"/>
     </row>
-    <row r="27" spans="1:11">
+    <row r="27">
       <c r="A27" s="33" t="s">
         <v>112</v>
       </c>
       <c r="B27" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A27)</f>
         <v>L</v>
       </c>
       <c r="C27" s="1" t="s">
@@ -6498,12 +6501,12 @@
         <v>115</v>
       </c>
     </row>
-    <row r="28" spans="1:11">
+    <row r="28">
       <c r="A28" s="33" t="s">
         <v>116</v>
       </c>
       <c r="B28" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A28)</f>
         <v>L</v>
       </c>
       <c r="C28" s="1" t="s">
@@ -6520,12 +6523,12 @@
       </c>
       <c r="G28" s="1"/>
     </row>
-    <row r="29" spans="1:11">
+    <row r="29">
       <c r="A29" s="33" t="s">
         <v>119</v>
       </c>
       <c r="B29" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A29)</f>
         <v>L</v>
       </c>
       <c r="C29" s="1" t="s">
@@ -6542,12 +6545,12 @@
       </c>
       <c r="G29" s="1"/>
     </row>
-    <row r="30" spans="1:11">
+    <row r="30">
       <c r="A30" s="33" t="s">
         <v>122</v>
       </c>
       <c r="B30" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A30)</f>
         <v>M</v>
       </c>
       <c r="C30" s="1" t="s">
@@ -6564,12 +6567,12 @@
       </c>
       <c r="G30" s="1"/>
     </row>
-    <row r="31" spans="1:11">
+    <row r="31">
       <c r="A31" s="33" t="s">
         <v>125</v>
       </c>
       <c r="B31" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A31)</f>
         <v>P</v>
       </c>
       <c r="C31" s="1" t="s">
@@ -6586,12 +6589,12 @@
       </c>
       <c r="G31" s="1"/>
     </row>
-    <row r="32" spans="1:11">
+    <row r="32">
       <c r="A32" s="33" t="s">
         <v>128</v>
       </c>
       <c r="B32" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A32)</f>
         <v>S</v>
       </c>
       <c r="C32" s="1" t="s">
@@ -6608,12 +6611,12 @@
       </c>
       <c r="G32" s="1"/>
     </row>
-    <row r="33" spans="1:11">
+    <row r="33">
       <c r="A33" s="33" t="s">
         <v>130</v>
       </c>
       <c r="B33" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A33)</f>
         <v>V</v>
       </c>
       <c r="C33" s="1" t="s">
@@ -6633,12 +6636,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="34" spans="1:11">
+    <row r="34">
       <c r="A34" s="33" t="s">
         <v>132</v>
       </c>
       <c r="B34" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A34)</f>
         <v>W</v>
       </c>
       <c r="C34" s="1" t="s">
@@ -6655,12 +6658,12 @@
       </c>
       <c r="G34" s="1"/>
     </row>
-    <row r="35" spans="1:11">
+    <row r="35">
       <c r="A35" s="35" t="s">
         <v>135</v>
       </c>
       <c r="B35" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A35)</f>
         <v>B</v>
       </c>
       <c r="C35" s="1" t="s">
@@ -6680,12 +6683,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="36" spans="1:11">
+    <row r="36">
       <c r="A36" s="35" t="s">
         <v>137</v>
       </c>
       <c r="B36" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A36)</f>
         <v>B</v>
       </c>
       <c r="C36" s="1" t="s">
@@ -6705,12 +6708,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="37" spans="1:11">
+    <row r="37">
       <c r="A37" s="35" t="s">
         <v>140</v>
       </c>
       <c r="B37" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A37)</f>
         <v>C</v>
       </c>
       <c r="C37" s="1" t="s">
@@ -6727,12 +6730,12 @@
       </c>
       <c r="G37" s="1"/>
     </row>
-    <row r="38" spans="1:11">
+    <row r="38">
       <c r="A38" s="35" t="s">
         <v>143</v>
       </c>
       <c r="B38" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A38)</f>
         <v>D</v>
       </c>
       <c r="C38" s="1" t="s">
@@ -6754,12 +6757,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="39" spans="1:11">
+    <row r="39">
       <c r="A39" s="35" t="s">
         <v>145</v>
       </c>
       <c r="B39" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A39)</f>
         <v>D</v>
       </c>
       <c r="C39" s="1" t="s">
@@ -6776,12 +6779,12 @@
       </c>
       <c r="G39" s="1"/>
     </row>
-    <row r="40" spans="1:11">
+    <row r="40">
       <c r="A40" s="35" t="s">
         <v>147</v>
       </c>
       <c r="B40" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A40)</f>
         <v>F</v>
       </c>
       <c r="C40" s="1" t="s">
@@ -6801,12 +6804,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="41" spans="1:11">
+    <row r="41">
       <c r="A41" s="35" t="s">
         <v>148</v>
       </c>
       <c r="B41" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A41)</f>
         <v>H</v>
       </c>
       <c r="C41" s="1" t="s">
@@ -6823,12 +6826,12 @@
       </c>
       <c r="G41" s="1"/>
     </row>
-    <row r="42" spans="1:11">
+    <row r="42">
       <c r="A42" s="35" t="s">
         <v>150</v>
       </c>
       <c r="B42" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A42)</f>
         <v>H</v>
       </c>
       <c r="C42" s="1" t="s">
@@ -6845,12 +6848,12 @@
       </c>
       <c r="G42" s="1"/>
     </row>
-    <row r="43" spans="1:11">
+    <row r="43">
       <c r="A43" s="35" t="s">
         <v>152</v>
       </c>
       <c r="B43" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A43)</f>
         <v>J</v>
       </c>
       <c r="C43" s="1" t="s">
@@ -6867,12 +6870,12 @@
       </c>
       <c r="G43" s="1"/>
     </row>
-    <row r="44" spans="1:11">
+    <row r="44">
       <c r="A44" s="35" t="s">
         <v>154</v>
       </c>
       <c r="B44" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A44)</f>
         <v>L</v>
       </c>
       <c r="C44" s="1" t="s">
@@ -6892,12 +6895,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="45" spans="1:11">
+    <row r="45">
       <c r="A45" s="35" t="s">
         <v>156</v>
       </c>
       <c r="B45" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A45)</f>
         <v>N</v>
       </c>
       <c r="C45" s="1" t="s">
@@ -6920,12 +6923,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="46" spans="1:11">
+    <row r="46">
       <c r="A46" s="35" t="s">
         <v>159</v>
       </c>
       <c r="B46" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A46)</f>
         <v>N</v>
       </c>
       <c r="C46" s="1" t="s">
@@ -6942,12 +6945,12 @@
       </c>
       <c r="G46" s="1"/>
     </row>
-    <row r="47" spans="1:11">
+    <row r="47">
       <c r="A47" s="1" t="s">
         <v>1129</v>
       </c>
       <c r="B47" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A47)</f>
         <v>N</v>
       </c>
       <c r="C47" s="1" t="s">
@@ -6964,12 +6967,12 @@
       </c>
       <c r="G47" s="1"/>
     </row>
-    <row r="48" spans="1:11">
+    <row r="48">
       <c r="A48" s="35" t="s">
         <v>162</v>
       </c>
       <c r="B48" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A48)</f>
         <v>P</v>
       </c>
       <c r="C48" s="1" t="s">
@@ -6986,12 +6989,12 @@
       </c>
       <c r="G48" s="1"/>
     </row>
-    <row r="49" spans="1:11">
+    <row r="49">
       <c r="A49" s="35" t="s">
         <v>163</v>
       </c>
       <c r="B49" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A49)</f>
         <v>P</v>
       </c>
       <c r="C49" s="1" t="s">
@@ -7008,12 +7011,12 @@
       </c>
       <c r="G49" s="1"/>
     </row>
-    <row r="50" spans="1:11">
+    <row r="50">
       <c r="A50" s="35" t="s">
         <v>166</v>
       </c>
       <c r="B50" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A50)</f>
         <v>R</v>
       </c>
       <c r="C50" s="1" t="s">
@@ -7033,12 +7036,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="51" spans="1:11">
+    <row r="51">
       <c r="A51" s="114" t="s">
         <v>1540</v>
       </c>
       <c r="B51" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A51)</f>
         <v>S</v>
       </c>
       <c r="C51" s="1" t="s">
@@ -7058,12 +7061,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="52" spans="1:11">
+    <row r="52">
       <c r="A52" s="35" t="s">
         <v>168</v>
       </c>
       <c r="B52" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A52)</f>
         <v>S</v>
       </c>
       <c r="C52" s="1" t="s">
@@ -7080,12 +7083,12 @@
       </c>
       <c r="G52" s="1"/>
     </row>
-    <row r="53" spans="1:11">
+    <row r="53">
       <c r="A53" s="35" t="s">
         <v>170</v>
       </c>
       <c r="B53" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A53)</f>
         <v>T</v>
       </c>
       <c r="C53" s="1" t="s">
@@ -7102,12 +7105,12 @@
       </c>
       <c r="G53" s="1"/>
     </row>
-    <row r="54" spans="1:11">
+    <row r="54">
       <c r="A54" s="114" t="s">
         <v>1538</v>
       </c>
       <c r="B54" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A54)</f>
         <v>B</v>
       </c>
       <c r="C54" s="31" t="s">
@@ -7124,12 +7127,12 @@
       </c>
       <c r="G54" s="32"/>
     </row>
-    <row r="55" spans="1:11">
+    <row r="55">
       <c r="A55" s="35" t="s">
         <v>173</v>
       </c>
       <c r="B55" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A55)</f>
         <v>B</v>
       </c>
       <c r="C55" s="31" t="s">
@@ -7146,12 +7149,12 @@
       </c>
       <c r="G55" s="32"/>
     </row>
-    <row r="56" spans="1:11">
+    <row r="56">
       <c r="A56" s="35" t="s">
         <v>174</v>
       </c>
       <c r="B56" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A56)</f>
         <v>C</v>
       </c>
       <c r="C56" s="31" t="s">
@@ -7170,12 +7173,12 @@
         <v>176</v>
       </c>
     </row>
-    <row r="57" spans="1:11">
+    <row r="57">
       <c r="A57" s="94" t="s">
         <v>1104</v>
       </c>
       <c r="B57" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A57)</f>
         <v>D</v>
       </c>
       <c r="C57" s="31" t="s">
@@ -7197,12 +7200,12 @@
         <v>1130</v>
       </c>
     </row>
-    <row r="58" spans="1:11">
+    <row r="58">
       <c r="A58" s="95" t="s">
         <v>1105</v>
       </c>
       <c r="B58" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A58)</f>
         <v>G</v>
       </c>
       <c r="C58" s="31" t="s">
@@ -7222,12 +7225,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="59" spans="1:11">
+    <row r="59">
       <c r="A59" s="114" t="s">
         <v>1539</v>
       </c>
       <c r="B59" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A59)</f>
         <v>H</v>
       </c>
       <c r="C59" s="31" t="s">
@@ -7244,12 +7247,12 @@
       </c>
       <c r="G59" s="32"/>
     </row>
-    <row r="60" spans="1:11">
+    <row r="60">
       <c r="A60" s="35" t="s">
         <v>181</v>
       </c>
       <c r="B60" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A60)</f>
         <v>J</v>
       </c>
       <c r="C60" s="31" t="s">
@@ -7266,12 +7269,12 @@
       </c>
       <c r="G60" s="32"/>
     </row>
-    <row r="61" spans="1:11">
+    <row r="61">
       <c r="A61" s="35" t="s">
         <v>182</v>
       </c>
       <c r="B61" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A61)</f>
         <v>K</v>
       </c>
       <c r="C61" s="31" t="s">
@@ -7288,12 +7291,12 @@
       </c>
       <c r="G61" s="32"/>
     </row>
-    <row r="62" spans="1:11">
+    <row r="62">
       <c r="A62" s="35" t="s">
         <v>184</v>
       </c>
       <c r="B62" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A62)</f>
         <v>L</v>
       </c>
       <c r="C62" s="31" t="s">
@@ -7313,12 +7316,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="63" spans="1:11">
+    <row r="63">
       <c r="A63" s="35" t="s">
         <v>187</v>
       </c>
       <c r="B63" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A63)</f>
         <v>M</v>
       </c>
       <c r="C63" s="31" t="s">
@@ -7338,12 +7341,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="64" spans="1:11">
+    <row r="64">
       <c r="A64" s="35" t="s">
         <v>190</v>
       </c>
       <c r="B64" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A64)</f>
         <v>M</v>
       </c>
       <c r="C64" s="31" t="s">
@@ -7360,12 +7363,12 @@
       </c>
       <c r="G64" s="32"/>
     </row>
-    <row r="65" spans="1:11">
+    <row r="65">
       <c r="A65" s="35" t="s">
         <v>192</v>
       </c>
       <c r="B65" s="1" t="str">
-        <f t="shared" ref="B65:B128" si="1">LEFT(A65)</f>
+        <f>LEFT(A65)</f>
         <v>M</v>
       </c>
       <c r="C65" s="31" t="s">
@@ -7382,12 +7385,12 @@
       </c>
       <c r="G65" s="32"/>
     </row>
-    <row r="66" spans="1:11">
+    <row r="66">
       <c r="A66" s="35" t="s">
         <v>194</v>
       </c>
       <c r="B66" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A66)</f>
         <v>P</v>
       </c>
       <c r="C66" s="31" t="s">
@@ -7404,12 +7407,12 @@
       </c>
       <c r="G66" s="32"/>
     </row>
-    <row r="67" spans="1:11">
+    <row r="67">
       <c r="A67" s="35" t="s">
         <v>196</v>
       </c>
       <c r="B67" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A67)</f>
         <v>T</v>
       </c>
       <c r="C67" s="31" t="s">
@@ -7426,12 +7429,12 @@
       </c>
       <c r="G67" s="32"/>
     </row>
-    <row r="68" spans="1:11">
+    <row r="68">
       <c r="A68" s="35" t="s">
         <v>198</v>
       </c>
       <c r="B68" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A68)</f>
         <v>T</v>
       </c>
       <c r="C68" s="31" t="s">
@@ -7448,12 +7451,12 @@
       </c>
       <c r="G68" s="32"/>
     </row>
-    <row r="69" spans="1:11">
+    <row r="69">
       <c r="A69" s="35" t="s">
         <v>200</v>
       </c>
       <c r="B69" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A69)</f>
         <v>V</v>
       </c>
       <c r="C69" s="31" t="s">
@@ -7470,12 +7473,12 @@
       </c>
       <c r="G69" s="32"/>
     </row>
-    <row r="70" spans="1:11">
+    <row r="70">
       <c r="A70" s="35" t="s">
         <v>202</v>
       </c>
       <c r="B70" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A70)</f>
         <v>A</v>
       </c>
       <c r="C70" s="32" t="s">
@@ -7495,12 +7498,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="71" spans="1:11">
+    <row r="71">
       <c r="A71" s="35" t="s">
         <v>205</v>
       </c>
       <c r="B71" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A71)</f>
         <v>A</v>
       </c>
       <c r="C71" s="32" t="s">
@@ -7520,12 +7523,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="72" spans="1:11">
+    <row r="72">
       <c r="A72" s="35" t="s">
         <v>207</v>
       </c>
       <c r="B72" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A72)</f>
         <v>B</v>
       </c>
       <c r="C72" s="32" t="s">
@@ -7545,12 +7548,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="73" spans="1:11">
+    <row r="73">
       <c r="A73" s="35" t="s">
         <v>209</v>
       </c>
       <c r="B73" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A73)</f>
         <v>C</v>
       </c>
       <c r="C73" s="32" t="s">
@@ -7567,12 +7570,12 @@
       </c>
       <c r="G73" s="32"/>
     </row>
-    <row r="74" spans="1:11">
+    <row r="74">
       <c r="A74" s="35" t="s">
         <v>211</v>
       </c>
       <c r="B74" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A74)</f>
         <v>D</v>
       </c>
       <c r="C74" s="32" t="s">
@@ -7589,12 +7592,12 @@
       </c>
       <c r="G74" s="32"/>
     </row>
-    <row r="75" spans="1:11">
+    <row r="75">
       <c r="A75" s="35" t="s">
         <v>213</v>
       </c>
       <c r="B75" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A75)</f>
         <v>D</v>
       </c>
       <c r="C75" s="32" t="s">
@@ -7611,12 +7614,12 @@
       </c>
       <c r="G75" s="32"/>
     </row>
-    <row r="76" spans="1:11">
+    <row r="76">
       <c r="A76" s="35" t="s">
         <v>215</v>
       </c>
       <c r="B76" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A76)</f>
         <v>G</v>
       </c>
       <c r="C76" s="32" t="s">
@@ -7635,12 +7638,12 @@
         <v>176</v>
       </c>
     </row>
-    <row r="77" spans="1:11">
+    <row r="77">
       <c r="A77" s="35" t="s">
         <v>217</v>
       </c>
       <c r="B77" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A77)</f>
         <v>G</v>
       </c>
       <c r="C77" s="32" t="s">
@@ -7657,12 +7660,12 @@
       </c>
       <c r="G77" s="26"/>
     </row>
-    <row r="78" spans="1:11">
+    <row r="78">
       <c r="A78" s="35" t="s">
         <v>218</v>
       </c>
       <c r="B78" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A78)</f>
         <v>M</v>
       </c>
       <c r="C78" s="32" t="s">
@@ -7684,12 +7687,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="79" spans="1:11">
+    <row r="79">
       <c r="A79" s="35" t="s">
         <v>220</v>
       </c>
       <c r="B79" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A79)</f>
         <v>R</v>
       </c>
       <c r="C79" s="32" t="s">
@@ -7706,12 +7709,12 @@
       </c>
       <c r="G79" s="32"/>
     </row>
-    <row r="80" spans="1:11">
+    <row r="80">
       <c r="A80" s="35" t="s">
         <v>222</v>
       </c>
       <c r="B80" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A80)</f>
         <v>R</v>
       </c>
       <c r="C80" s="32" t="s">
@@ -7731,12 +7734,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="81" spans="1:11">
+    <row r="81">
       <c r="A81" s="114" t="s">
         <v>1537</v>
       </c>
       <c r="B81" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A81)</f>
         <v>V</v>
       </c>
       <c r="C81" s="32" t="s">
@@ -7753,12 +7756,12 @@
       </c>
       <c r="G81" s="32"/>
     </row>
-    <row r="82" spans="1:11">
+    <row r="82">
       <c r="A82" s="32" t="s">
         <v>226</v>
       </c>
       <c r="B82" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A82)</f>
         <v>A</v>
       </c>
       <c r="C82" s="32" t="s">
@@ -7778,12 +7781,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="83" spans="1:11">
+    <row r="83">
       <c r="A83" s="32" t="s">
         <v>228</v>
       </c>
       <c r="B83" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A83)</f>
         <v>B</v>
       </c>
       <c r="C83" s="32" t="s">
@@ -7803,12 +7806,12 @@
         <v>1107</v>
       </c>
     </row>
-    <row r="84" spans="1:11">
+    <row r="84">
       <c r="A84" s="32" t="s">
         <v>230</v>
       </c>
       <c r="B84" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A84)</f>
         <v>B</v>
       </c>
       <c r="C84" s="32" t="s">
@@ -7828,12 +7831,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="85" spans="1:11">
+    <row r="85">
       <c r="A85" s="32" t="s">
         <v>232</v>
       </c>
       <c r="B85" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A85)</f>
         <v>C</v>
       </c>
       <c r="C85" s="32" t="s">
@@ -7853,12 +7856,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="86" spans="1:11">
+    <row r="86">
       <c r="A86" s="32" t="s">
         <v>234</v>
       </c>
       <c r="B86" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A86)</f>
         <v>C</v>
       </c>
       <c r="C86" s="32" t="s">
@@ -7878,12 +7881,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="87" spans="1:11">
+    <row r="87">
       <c r="A87" s="32" t="s">
         <v>235</v>
       </c>
       <c r="B87" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A87)</f>
         <v>C</v>
       </c>
       <c r="C87" s="32" t="s">
@@ -7906,12 +7909,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="88" spans="1:11">
+    <row r="88">
       <c r="A88" s="32" t="s">
         <v>237</v>
       </c>
       <c r="B88" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A88)</f>
         <v>C</v>
       </c>
       <c r="C88" s="32" t="s">
@@ -7931,12 +7934,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="89" spans="1:11">
+    <row r="89">
       <c r="A89" s="32" t="s">
         <v>239</v>
       </c>
       <c r="B89" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A89)</f>
         <v>E</v>
       </c>
       <c r="C89" s="32" t="s">
@@ -7956,12 +7959,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="90" spans="1:11">
+    <row r="90">
       <c r="A90" s="32" t="s">
         <v>241</v>
       </c>
       <c r="B90" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A90)</f>
         <v>G</v>
       </c>
       <c r="C90" s="32" t="s">
@@ -7978,12 +7981,12 @@
       </c>
       <c r="G90" s="1"/>
     </row>
-    <row r="91" spans="1:11">
+    <row r="91">
       <c r="A91" s="32" t="s">
         <v>244</v>
       </c>
       <c r="B91" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A91)</f>
         <v>J</v>
       </c>
       <c r="C91" s="32" t="s">
@@ -8003,12 +8006,12 @@
         <v>1109</v>
       </c>
     </row>
-    <row r="92" spans="1:11">
+    <row r="92">
       <c r="A92" s="32" t="s">
         <v>246</v>
       </c>
       <c r="B92" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A92)</f>
         <v>L</v>
       </c>
       <c r="C92" s="32" t="s">
@@ -8028,12 +8031,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="93" spans="1:11">
+    <row r="93">
       <c r="A93" s="32" t="s">
         <v>249</v>
       </c>
       <c r="B93" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A93)</f>
         <v>M</v>
       </c>
       <c r="C93" s="32" t="s">
@@ -8053,12 +8056,12 @@
         <v>1110</v>
       </c>
     </row>
-    <row r="94" spans="1:11">
+    <row r="94">
       <c r="A94" s="32" t="s">
         <v>251</v>
       </c>
       <c r="B94" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A94)</f>
         <v>M</v>
       </c>
       <c r="C94" s="32" t="s">
@@ -8078,12 +8081,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="95" spans="1:11">
+    <row r="95">
       <c r="A95" s="32" t="s">
         <v>253</v>
       </c>
       <c r="B95" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A95)</f>
         <v>N</v>
       </c>
       <c r="C95" s="32" t="s">
@@ -8100,12 +8103,12 @@
       </c>
       <c r="G95" s="1"/>
     </row>
-    <row r="96" spans="1:11">
+    <row r="96">
       <c r="A96" s="32" t="s">
         <v>255</v>
       </c>
       <c r="B96" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A96)</f>
         <v>P</v>
       </c>
       <c r="C96" s="32" t="s">
@@ -8125,12 +8128,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="97" spans="1:11">
+    <row r="97">
       <c r="A97" s="32" t="s">
         <v>258</v>
       </c>
       <c r="B97" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A97)</f>
         <v>R</v>
       </c>
       <c r="C97" s="32" t="s">
@@ -8147,12 +8150,12 @@
       </c>
       <c r="G97" s="1"/>
     </row>
-    <row r="98" spans="1:11">
+    <row r="98">
       <c r="A98" s="32" t="s">
         <v>260</v>
       </c>
       <c r="B98" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A98)</f>
         <v>R</v>
       </c>
       <c r="C98" s="32" t="s">
@@ -8169,12 +8172,12 @@
       </c>
       <c r="G98" s="1"/>
     </row>
-    <row r="99" spans="1:11">
+    <row r="99">
       <c r="A99" s="32" t="s">
         <v>261</v>
       </c>
       <c r="B99" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A99)</f>
         <v>B</v>
       </c>
       <c r="C99" s="32" t="s">
@@ -8196,12 +8199,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="100" spans="1:11">
+    <row r="100">
       <c r="A100" s="32" t="s">
         <v>263</v>
       </c>
       <c r="B100" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A100)</f>
         <v>A</v>
       </c>
       <c r="C100" s="32" t="s">
@@ -8220,12 +8223,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="101" spans="1:11">
+    <row r="101">
       <c r="A101" s="32" t="s">
         <v>923</v>
       </c>
       <c r="B101" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A101)</f>
         <v>V</v>
       </c>
       <c r="C101" s="32" t="s">
@@ -8244,12 +8247,12 @@
         <v>1122</v>
       </c>
     </row>
-    <row r="102" spans="1:11">
+    <row r="102">
       <c r="A102" s="32" t="s">
         <v>927</v>
       </c>
       <c r="B102" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A102)</f>
         <v>B</v>
       </c>
       <c r="C102" s="32" t="s">
@@ -8268,12 +8271,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="103" spans="1:11">
+    <row r="103">
       <c r="A103" s="32" t="s">
         <v>928</v>
       </c>
       <c r="B103" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A103)</f>
         <v>B</v>
       </c>
       <c r="C103" s="32" t="s">
@@ -8289,12 +8292,12 @@
         <v>93</v>
       </c>
     </row>
-    <row r="104" spans="1:11">
+    <row r="104">
       <c r="A104" s="32" t="s">
         <v>929</v>
       </c>
       <c r="B104" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A104)</f>
         <v>G</v>
       </c>
       <c r="C104" s="32" t="s">
@@ -8316,12 +8319,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="105" spans="1:11">
+    <row r="105">
       <c r="A105" s="32" t="s">
         <v>931</v>
       </c>
       <c r="B105" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A105)</f>
         <v>G</v>
       </c>
       <c r="C105" s="32" t="s">
@@ -8340,12 +8343,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="106" spans="1:11">
+    <row r="106">
       <c r="A106" s="32" t="s">
         <v>1536</v>
       </c>
       <c r="B106" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A106)</f>
         <v>H</v>
       </c>
       <c r="C106" s="32" t="s">
@@ -8361,12 +8364,12 @@
         <v>933</v>
       </c>
     </row>
-    <row r="107" spans="1:11">
+    <row r="107">
       <c r="A107" s="32" t="s">
         <v>939</v>
       </c>
       <c r="B107" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A107)</f>
         <v>I</v>
       </c>
       <c r="C107" s="32" t="s">
@@ -8382,12 +8385,12 @@
         <v>93</v>
       </c>
     </row>
-    <row r="108" spans="1:11">
+    <row r="108">
       <c r="A108" s="32" t="s">
         <v>941</v>
       </c>
       <c r="B108" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A108)</f>
         <v>L</v>
       </c>
       <c r="C108" s="32" t="s">
@@ -8403,12 +8406,12 @@
         <v>943</v>
       </c>
     </row>
-    <row r="109" spans="1:11">
+    <row r="109">
       <c r="A109" s="32" t="s">
         <v>948</v>
       </c>
       <c r="B109" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A109)</f>
         <v>L</v>
       </c>
       <c r="C109" s="32" t="s">
@@ -8424,12 +8427,12 @@
         <v>949</v>
       </c>
     </row>
-    <row r="110" spans="1:11">
+    <row r="110">
       <c r="A110" s="32" t="s">
         <v>954</v>
       </c>
       <c r="B110" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A110)</f>
         <v>L</v>
       </c>
       <c r="C110" s="32" t="s">
@@ -8451,12 +8454,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="111" spans="1:11">
+    <row r="111">
       <c r="A111" s="32" t="s">
         <v>955</v>
       </c>
       <c r="B111" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A111)</f>
         <v>M</v>
       </c>
       <c r="C111" s="32" t="s">
@@ -8475,12 +8478,12 @@
         <v>1114</v>
       </c>
     </row>
-    <row r="112" spans="1:11">
+    <row r="112">
       <c r="A112" s="32" t="s">
         <v>956</v>
       </c>
       <c r="B112" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A112)</f>
         <v>M</v>
       </c>
       <c r="C112" s="32" t="s">
@@ -8499,12 +8502,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="113" spans="1:11">
+    <row r="113">
       <c r="A113" s="32" t="s">
         <v>957</v>
       </c>
       <c r="B113" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A113)</f>
         <v>N</v>
       </c>
       <c r="C113" s="32" t="s">
@@ -8523,12 +8526,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="114" spans="1:11">
+    <row r="114">
       <c r="A114" s="32" t="s">
         <v>958</v>
       </c>
       <c r="B114" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A114)</f>
         <v>P</v>
       </c>
       <c r="C114" s="32" t="s">
@@ -8547,12 +8550,12 @@
         <v>1115</v>
       </c>
     </row>
-    <row r="115" spans="1:11">
+    <row r="115">
       <c r="A115" s="32" t="s">
         <v>960</v>
       </c>
       <c r="B115" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A115)</f>
         <v>R</v>
       </c>
       <c r="C115" s="32" t="s">
@@ -8574,12 +8577,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="116" spans="1:11">
+    <row r="116">
       <c r="A116" s="32" t="s">
         <v>962</v>
       </c>
       <c r="B116" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A116)</f>
         <v>R</v>
       </c>
       <c r="C116" s="32" t="s">
@@ -8598,12 +8601,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="117" spans="1:11">
+    <row r="117">
       <c r="A117" s="32" t="s">
         <v>971</v>
       </c>
       <c r="B117" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A117)</f>
         <v>T</v>
       </c>
       <c r="C117" s="32" t="s">
@@ -8619,12 +8622,12 @@
         <v>972</v>
       </c>
     </row>
-    <row r="118" spans="1:11">
+    <row r="118">
       <c r="A118" s="32" t="s">
         <v>979</v>
       </c>
       <c r="B118" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A118)</f>
         <v>A</v>
       </c>
       <c r="C118" s="32" t="s">
@@ -8640,12 +8643,12 @@
         <v>933</v>
       </c>
     </row>
-    <row r="119" spans="1:11">
+    <row r="119">
       <c r="A119" s="32" t="s">
         <v>981</v>
       </c>
       <c r="B119" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A119)</f>
         <v>B</v>
       </c>
       <c r="C119" s="32" t="s">
@@ -8664,12 +8667,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="120" spans="1:11">
+    <row r="120">
       <c r="A120" s="32" t="s">
         <v>983</v>
       </c>
       <c r="B120" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A120)</f>
         <v>B</v>
       </c>
       <c r="C120" s="32" t="s">
@@ -8688,12 +8691,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="121" spans="1:11">
+    <row r="121">
       <c r="A121" s="32" t="s">
         <v>984</v>
       </c>
       <c r="B121" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A121)</f>
         <v>B</v>
       </c>
       <c r="C121" s="32" t="s">
@@ -8712,12 +8715,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="122" spans="1:11">
+    <row r="122">
       <c r="A122" s="32" t="s">
         <v>986</v>
       </c>
       <c r="B122" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A122)</f>
         <v>C</v>
       </c>
       <c r="C122" s="32" t="s">
@@ -8739,12 +8742,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="123" spans="1:11">
+    <row r="123">
       <c r="A123" s="32" t="s">
         <v>988</v>
       </c>
       <c r="B123" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A123)</f>
         <v>C</v>
       </c>
       <c r="C123" s="32" t="s">
@@ -8763,12 +8766,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="124" spans="1:11">
+    <row r="124">
       <c r="A124" s="32" t="s">
         <v>989</v>
       </c>
       <c r="B124" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A124)</f>
         <v>D</v>
       </c>
       <c r="C124" s="32" t="s">
@@ -8784,12 +8787,12 @@
         <v>106</v>
       </c>
     </row>
-    <row r="125" spans="1:11">
+    <row r="125">
       <c r="A125" s="32" t="s">
         <v>991</v>
       </c>
       <c r="B125" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A125)</f>
         <v>D</v>
       </c>
       <c r="C125" s="32" t="s">
@@ -8805,12 +8808,12 @@
         <v>37</v>
       </c>
     </row>
-    <row r="126" spans="1:11">
+    <row r="126">
       <c r="A126" s="32" t="s">
         <v>993</v>
       </c>
       <c r="B126" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A126)</f>
         <v>M</v>
       </c>
       <c r="C126" s="32" t="s">
@@ -8829,12 +8832,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="127" spans="1:11">
+    <row r="127">
       <c r="A127" s="32" t="s">
         <v>994</v>
       </c>
       <c r="B127" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A127)</f>
         <v>N</v>
       </c>
       <c r="C127" s="32" t="s">
@@ -8850,12 +8853,12 @@
         <v>426</v>
       </c>
     </row>
-    <row r="128" spans="1:11">
+    <row r="128">
       <c r="A128" s="32" t="s">
         <v>995</v>
       </c>
       <c r="B128" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A128)</f>
         <v>P</v>
       </c>
       <c r="C128" s="32" t="s">
@@ -8871,12 +8874,12 @@
         <v>111</v>
       </c>
     </row>
-    <row r="129" spans="1:11">
+    <row r="129">
       <c r="A129" s="32" t="s">
         <v>996</v>
       </c>
       <c r="B129" s="1" t="str">
-        <f t="shared" ref="B129:B192" si="2">LEFT(A129)</f>
+        <f>LEFT(A129)</f>
         <v>S</v>
       </c>
       <c r="C129" s="32" t="s">
@@ -8892,12 +8895,12 @@
         <v>142</v>
       </c>
     </row>
-    <row r="130" spans="1:11">
+    <row r="130">
       <c r="A130" s="32" t="s">
         <v>997</v>
       </c>
       <c r="B130" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A130)</f>
         <v>S</v>
       </c>
       <c r="C130" s="32" t="s">
@@ -8919,12 +8922,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="131" spans="1:11">
+    <row r="131">
       <c r="A131" s="32" t="s">
         <v>999</v>
       </c>
       <c r="B131" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A131)</f>
         <v>S</v>
       </c>
       <c r="C131" s="32" t="s">
@@ -8949,12 +8952,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="132" spans="1:11">
+    <row r="132">
       <c r="A132" s="32" t="s">
         <v>1308</v>
       </c>
       <c r="B132" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A132)</f>
         <v>B</v>
       </c>
       <c r="C132" s="32" t="s">
@@ -8979,12 +8982,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="133" spans="1:11">
+    <row r="133">
       <c r="A133" s="32" t="s">
         <v>1309</v>
       </c>
       <c r="B133" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A133)</f>
         <v>C</v>
       </c>
       <c r="C133" s="32" t="s">
@@ -9003,12 +9006,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="134" spans="1:11">
+    <row r="134">
       <c r="A134" s="32" t="s">
         <v>1001</v>
       </c>
       <c r="B134" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A134)</f>
         <v>C</v>
       </c>
       <c r="C134" s="32" t="s">
@@ -9027,12 +9030,12 @@
         <v>1119</v>
       </c>
     </row>
-    <row r="135" spans="1:11">
+    <row r="135">
       <c r="A135" s="32" t="s">
         <v>1002</v>
       </c>
       <c r="B135" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A135)</f>
         <v>C</v>
       </c>
       <c r="C135" s="32" t="s">
@@ -9054,12 +9057,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="136" spans="1:11">
+    <row r="136">
       <c r="A136" s="32" t="s">
         <v>1003</v>
       </c>
       <c r="B136" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A136)</f>
         <v>D</v>
       </c>
       <c r="C136" s="32" t="s">
@@ -9075,12 +9078,12 @@
         <v>933</v>
       </c>
     </row>
-    <row r="137" spans="1:11">
+    <row r="137">
       <c r="A137" s="32" t="s">
         <v>1005</v>
       </c>
       <c r="B137" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A137)</f>
         <v>D</v>
       </c>
       <c r="C137" s="32" t="s">
@@ -9096,12 +9099,12 @@
         <v>180</v>
       </c>
     </row>
-    <row r="138" spans="1:11">
+    <row r="138">
       <c r="A138" s="32" t="s">
         <v>1006</v>
       </c>
       <c r="B138" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A138)</f>
         <v>F</v>
       </c>
       <c r="C138" s="32" t="s">
@@ -9120,12 +9123,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="139" spans="1:11">
+    <row r="139">
       <c r="A139" s="32" t="s">
         <v>1007</v>
       </c>
       <c r="B139" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A139)</f>
         <v>H</v>
       </c>
       <c r="C139" s="32" t="s">
@@ -9144,12 +9147,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="140" spans="1:11">
+    <row r="140">
       <c r="A140" s="32" t="s">
         <v>1008</v>
       </c>
       <c r="B140" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A140)</f>
         <v>J</v>
       </c>
       <c r="C140" s="32" t="s">
@@ -9168,12 +9171,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="141" spans="1:11">
+    <row r="141">
       <c r="A141" s="32" t="s">
         <v>1010</v>
       </c>
       <c r="B141" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A141)</f>
         <v>J</v>
       </c>
       <c r="C141" s="32" t="s">
@@ -9192,12 +9195,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="142" spans="1:11">
+    <row r="142">
       <c r="A142" s="32" t="s">
         <v>1011</v>
       </c>
       <c r="B142" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A142)</f>
         <v>L</v>
       </c>
       <c r="C142" s="32" t="s">
@@ -9216,12 +9219,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="143" spans="1:11">
+    <row r="143">
       <c r="A143" s="32" t="s">
         <v>1019</v>
       </c>
       <c r="B143" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A143)</f>
         <v>M</v>
       </c>
       <c r="C143" s="32" t="s">
@@ -9240,12 +9243,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="144" spans="1:11">
+    <row r="144">
       <c r="A144" s="32" t="s">
         <v>1020</v>
       </c>
       <c r="B144" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A144)</f>
         <v>P</v>
       </c>
       <c r="C144" s="32" t="s">
@@ -9261,12 +9264,12 @@
         <v>124</v>
       </c>
     </row>
-    <row r="145" spans="1:11">
+    <row r="145">
       <c r="A145" s="32" t="s">
         <v>1021</v>
       </c>
       <c r="B145" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A145)</f>
         <v>P</v>
       </c>
       <c r="C145" s="32" t="s">
@@ -9291,12 +9294,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="146" spans="1:11">
+    <row r="146">
       <c r="A146" s="32" t="s">
         <v>1257</v>
       </c>
       <c r="B146" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A146)</f>
         <v>P</v>
       </c>
       <c r="C146" s="32" t="s">
@@ -9316,12 +9319,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="147" spans="1:11">
+    <row r="147">
       <c r="A147" s="32" t="s">
         <v>997</v>
       </c>
       <c r="B147" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A147)</f>
         <v>S</v>
       </c>
       <c r="C147" s="32" t="s">
@@ -9337,12 +9340,12 @@
         <v>103</v>
       </c>
     </row>
-    <row r="148" spans="1:11">
+    <row r="148">
       <c r="A148" s="32" t="s">
         <v>1022</v>
       </c>
       <c r="B148" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A148)</f>
         <v>A</v>
       </c>
       <c r="C148" s="32" t="s">
@@ -9361,12 +9364,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="149" spans="1:11">
+    <row r="149">
       <c r="A149" s="32" t="s">
         <v>1023</v>
       </c>
       <c r="B149" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A149)</f>
         <v>B</v>
       </c>
       <c r="C149" s="32" t="s">
@@ -9388,12 +9391,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="150" spans="1:11">
+    <row r="150">
       <c r="A150" s="32" t="s">
         <v>1025</v>
       </c>
       <c r="B150" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A150)</f>
         <v>C</v>
       </c>
       <c r="C150" s="92" t="s">
@@ -9409,12 +9412,12 @@
         <v>103</v>
       </c>
     </row>
-    <row r="151" spans="1:11">
+    <row r="151">
       <c r="A151" s="32" t="s">
         <v>1026</v>
       </c>
       <c r="B151" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A151)</f>
         <v>D</v>
       </c>
       <c r="C151" s="32" t="s">
@@ -9433,12 +9436,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="152" spans="1:11">
+    <row r="152">
       <c r="A152" s="32" t="s">
         <v>1028</v>
       </c>
       <c r="B152" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A152)</f>
         <v>D</v>
       </c>
       <c r="C152" s="32" t="s">
@@ -9457,12 +9460,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="153" spans="1:11">
+    <row r="153">
       <c r="A153" s="32" t="s">
         <v>991</v>
       </c>
       <c r="B153" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A153)</f>
         <v>D</v>
       </c>
       <c r="C153" s="32" t="s">
@@ -9481,12 +9484,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="154" spans="1:11">
+    <row r="154">
       <c r="A154" s="32" t="s">
         <v>1031</v>
       </c>
       <c r="B154" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A154)</f>
         <v>F</v>
       </c>
       <c r="C154" s="32" t="s">
@@ -9505,12 +9508,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="155" spans="1:11">
+    <row r="155">
       <c r="A155" s="32" t="s">
         <v>1032</v>
       </c>
       <c r="B155" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A155)</f>
         <v>F</v>
       </c>
       <c r="C155" s="32" t="s">
@@ -9532,12 +9535,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="156" spans="1:11">
+    <row r="156">
       <c r="A156" s="32" t="s">
         <v>1033</v>
       </c>
       <c r="B156" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A156)</f>
         <v>G</v>
       </c>
       <c r="C156" s="32" t="s">
@@ -9556,12 +9559,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="157" spans="1:11">
+    <row r="157">
       <c r="A157" s="32" t="s">
         <v>1035</v>
       </c>
       <c r="B157" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A157)</f>
         <v>J</v>
       </c>
       <c r="C157" s="32" t="s">
@@ -9577,12 +9580,12 @@
         <v>964</v>
       </c>
     </row>
-    <row r="158" spans="1:11">
+    <row r="158">
       <c r="A158" s="32" t="s">
         <v>1037</v>
       </c>
       <c r="B158" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A158)</f>
         <v>L</v>
       </c>
       <c r="C158" s="32" t="s">
@@ -9601,12 +9604,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="159" spans="1:11">
+    <row r="159">
       <c r="A159" s="32" t="s">
         <v>1038</v>
       </c>
       <c r="B159" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A159)</f>
         <v>M</v>
       </c>
       <c r="C159" s="32" t="s">
@@ -9622,12 +9625,12 @@
         <v>870</v>
       </c>
     </row>
-    <row r="160" spans="1:11">
+    <row r="160">
       <c r="A160" s="32" t="s">
         <v>880</v>
       </c>
       <c r="B160" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A160)</f>
         <v>M</v>
       </c>
       <c r="C160" s="32" t="s">
@@ -9643,12 +9646,12 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="161" spans="1:11">
+    <row r="161">
       <c r="A161" s="32" t="s">
         <v>1046</v>
       </c>
       <c r="B161" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A161)</f>
         <v>M</v>
       </c>
       <c r="C161" s="32" t="s">
@@ -9664,12 +9667,12 @@
         <v>134</v>
       </c>
     </row>
-    <row r="162" spans="1:11">
+    <row r="162">
       <c r="A162" s="32" t="s">
         <v>1048</v>
       </c>
       <c r="B162" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A162)</f>
         <v>M</v>
       </c>
       <c r="C162" s="32" t="s">
@@ -9685,12 +9688,12 @@
         <v>103</v>
       </c>
     </row>
-    <row r="163" spans="1:11">
+    <row r="163">
       <c r="A163" s="32" t="s">
         <v>1049</v>
       </c>
       <c r="B163" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A163)</f>
         <v>P</v>
       </c>
       <c r="C163" s="32" t="s">
@@ -9706,12 +9709,12 @@
         <v>90</v>
       </c>
     </row>
-    <row r="164" spans="1:11">
+    <row r="164">
       <c r="A164" s="32" t="s">
         <v>1051</v>
       </c>
       <c r="B164" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A164)</f>
         <v>S</v>
       </c>
       <c r="C164" s="32" t="s">
@@ -9730,12 +9733,12 @@
         <v>1124</v>
       </c>
     </row>
-    <row r="165" spans="1:11">
+    <row r="165">
       <c r="A165" s="32" t="s">
         <v>1053</v>
       </c>
       <c r="B165" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A165)</f>
         <v>B</v>
       </c>
       <c r="C165" s="32" t="s">
@@ -9754,12 +9757,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="166" spans="1:11">
+    <row r="166">
       <c r="A166" s="32" t="s">
         <v>1054</v>
       </c>
       <c r="B166" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A166)</f>
         <v>C</v>
       </c>
       <c r="C166" s="32" t="s">
@@ -9778,12 +9781,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="167" spans="1:11">
+    <row r="167">
       <c r="A167" s="32" t="s">
         <v>1056</v>
       </c>
       <c r="B167" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A167)</f>
         <v>B</v>
       </c>
       <c r="C167" s="32" t="s">
@@ -9802,12 +9805,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="168" spans="1:11">
+    <row r="168">
       <c r="A168" s="32" t="s">
         <v>1057</v>
       </c>
       <c r="B168" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A168)</f>
         <v>D</v>
       </c>
       <c r="C168" s="32" t="s">
@@ -9823,12 +9826,12 @@
         <v>111</v>
       </c>
     </row>
-    <row r="169" spans="1:11">
+    <row r="169">
       <c r="A169" s="32" t="s">
         <v>1059</v>
       </c>
       <c r="B169" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A169)</f>
         <v>D</v>
       </c>
       <c r="C169" s="32" t="s">
@@ -9844,12 +9847,12 @@
         <v>37</v>
       </c>
     </row>
-    <row r="170" spans="1:11">
+    <row r="170">
       <c r="A170" s="32" t="s">
         <v>1060</v>
       </c>
       <c r="B170" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A170)</f>
         <v>J</v>
       </c>
       <c r="C170" s="32" t="s">
@@ -9865,12 +9868,12 @@
         <v>103</v>
       </c>
     </row>
-    <row r="171" spans="1:11">
+    <row r="171">
       <c r="A171" s="32" t="s">
         <v>1062</v>
       </c>
       <c r="B171" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A171)</f>
         <v>K</v>
       </c>
       <c r="C171" s="32" t="s">
@@ -9889,12 +9892,12 @@
         <v>176</v>
       </c>
     </row>
-    <row r="172" spans="1:11">
+    <row r="172">
       <c r="A172" s="32" t="s">
         <v>1064</v>
       </c>
       <c r="B172" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A172)</f>
         <v>L</v>
       </c>
       <c r="C172" s="32" t="s">
@@ -9910,12 +9913,12 @@
         <v>305</v>
       </c>
     </row>
-    <row r="173" spans="1:11">
+    <row r="173">
       <c r="A173" s="32" t="s">
         <v>1065</v>
       </c>
       <c r="B173" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A173)</f>
         <v>L</v>
       </c>
       <c r="C173" s="32" t="s">
@@ -9934,12 +9937,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="174" spans="1:11">
+    <row r="174">
       <c r="A174" s="32" t="s">
         <v>1067</v>
       </c>
       <c r="B174" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A174)</f>
         <v>P</v>
       </c>
       <c r="C174" s="32" t="s">
@@ -9958,12 +9961,12 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="175" spans="1:11">
+    <row r="175">
       <c r="A175" s="32" t="s">
         <v>1069</v>
       </c>
       <c r="B175" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A175)</f>
         <v>R</v>
       </c>
       <c r="C175" s="32" t="s">
@@ -9979,12 +9982,12 @@
         <v>84</v>
       </c>
     </row>
-    <row r="176" spans="1:11">
+    <row r="176">
       <c r="A176" s="32" t="s">
         <v>1070</v>
       </c>
       <c r="B176" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A176)</f>
         <v>R</v>
       </c>
       <c r="C176" s="32" t="s">
@@ -10003,12 +10006,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="177" spans="1:11">
+    <row r="177">
       <c r="A177" s="32" t="s">
         <v>1072</v>
       </c>
       <c r="B177" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A177)</f>
         <v>R</v>
       </c>
       <c r="C177" s="32" t="s">
@@ -10024,12 +10027,12 @@
         <v>305</v>
       </c>
     </row>
-    <row r="178" spans="1:11">
+    <row r="178">
       <c r="A178" s="32" t="s">
         <v>1074</v>
       </c>
       <c r="B178" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A178)</f>
         <v>S</v>
       </c>
       <c r="C178" s="32" t="s">
@@ -10048,12 +10051,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="179" spans="1:11">
+    <row r="179">
       <c r="A179" s="32" t="s">
         <v>1075</v>
       </c>
       <c r="B179" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A179)</f>
         <v>T</v>
       </c>
       <c r="C179" s="32" t="s">
@@ -10072,12 +10075,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="180" spans="1:11">
+    <row r="180">
       <c r="A180" s="32" t="s">
         <v>1076</v>
       </c>
       <c r="B180" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A180)</f>
         <v>V</v>
       </c>
       <c r="C180" s="32" t="s">
@@ -10096,12 +10099,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="181" spans="1:11">
+    <row r="181">
       <c r="A181" s="32" t="s">
         <v>1262</v>
       </c>
       <c r="B181" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A181)</f>
         <v>S</v>
       </c>
       <c r="C181" s="32" t="s">
@@ -10123,12 +10126,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="182" spans="1:11">
+    <row r="182">
       <c r="A182" s="32" t="s">
         <v>1260</v>
       </c>
       <c r="B182" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A182)</f>
         <v>C</v>
       </c>
       <c r="C182" s="32" t="s">
@@ -10150,12 +10153,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="183" spans="1:11">
+    <row r="183">
       <c r="A183" s="32" t="s">
         <v>1259</v>
       </c>
       <c r="B183" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A183)</f>
         <v>C</v>
       </c>
       <c r="C183" s="32" t="s">
@@ -10174,12 +10177,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="184" spans="1:11">
+    <row r="184">
       <c r="A184" s="32" t="s">
         <v>1258</v>
       </c>
       <c r="B184" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A184)</f>
         <v>B</v>
       </c>
       <c r="C184" s="32" t="s">
@@ -10198,12 +10201,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="185" spans="1:11">
+    <row r="185">
       <c r="A185" s="32" t="s">
         <v>1078</v>
       </c>
       <c r="B185" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A185)</f>
         <v>B</v>
       </c>
       <c r="C185" s="32" t="s">
@@ -10222,12 +10225,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="186" spans="1:11">
+    <row r="186">
       <c r="A186" s="32" t="s">
         <v>1080</v>
       </c>
       <c r="B186" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A186)</f>
         <v>B</v>
       </c>
       <c r="C186" s="32" t="s">
@@ -10249,12 +10252,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="187" spans="1:11">
+    <row r="187">
       <c r="A187" s="32" t="s">
         <v>1081</v>
       </c>
       <c r="B187" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A187)</f>
         <v>B</v>
       </c>
       <c r="C187" s="32" t="s">
@@ -10270,12 +10273,12 @@
         <v>114</v>
       </c>
     </row>
-    <row r="188" spans="1:11">
+    <row r="188">
       <c r="A188" s="32" t="s">
         <v>1082</v>
       </c>
       <c r="B188" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A188)</f>
         <v>D</v>
       </c>
       <c r="C188" s="32" t="s">
@@ -10294,12 +10297,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="189" spans="1:11">
+    <row r="189">
       <c r="A189" s="32" t="s">
         <v>1083</v>
       </c>
       <c r="B189" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A189)</f>
         <v>D</v>
       </c>
       <c r="C189" s="32" t="s">
@@ -10318,12 +10321,12 @@
         <v>1127</v>
       </c>
     </row>
-    <row r="190" spans="1:11">
+    <row r="190">
       <c r="A190" s="32" t="s">
         <v>1085</v>
       </c>
       <c r="B190" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A190)</f>
         <v>D</v>
       </c>
       <c r="C190" s="32" t="s">
@@ -10339,12 +10342,12 @@
         <v>426</v>
       </c>
     </row>
-    <row r="191" spans="1:11">
+    <row r="191">
       <c r="A191" s="32" t="s">
         <v>1086</v>
       </c>
       <c r="B191" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A191)</f>
         <v>H</v>
       </c>
       <c r="C191" s="32" t="s">
@@ -10360,12 +10363,12 @@
         <v>124</v>
       </c>
     </row>
-    <row r="192" spans="1:11">
+    <row r="192">
       <c r="A192" s="32" t="s">
         <v>1088</v>
       </c>
       <c r="B192" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A192)</f>
         <v>J</v>
       </c>
       <c r="C192" s="32" t="s">
@@ -10384,12 +10387,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="193" spans="1:11">
+    <row r="193">
       <c r="A193" s="32" t="s">
         <v>1090</v>
       </c>
       <c r="B193" s="1" t="str">
-        <f t="shared" ref="B193:B256" si="3">LEFT(A193)</f>
+        <f>LEFT(A193)</f>
         <v>M</v>
       </c>
       <c r="C193" s="32" t="s">
@@ -10408,12 +10411,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="194" spans="1:11">
+    <row r="194">
       <c r="A194" s="32" t="s">
         <v>1046</v>
       </c>
       <c r="B194" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A194)</f>
         <v>M</v>
       </c>
       <c r="C194" s="32" t="s">
@@ -10432,12 +10435,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="195" spans="1:11">
+    <row r="195">
       <c r="A195" s="32" t="s">
         <v>1093</v>
       </c>
       <c r="B195" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A195)</f>
         <v>P</v>
       </c>
       <c r="C195" s="32" t="s">
@@ -10459,12 +10462,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="196" spans="1:11">
+    <row r="196">
       <c r="A196" s="32" t="s">
         <v>1535</v>
       </c>
       <c r="B196" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A196)</f>
         <v>V</v>
       </c>
       <c r="C196" s="32" t="s">
@@ -10480,12 +10483,12 @@
         <v>964</v>
       </c>
     </row>
-    <row r="197" spans="1:11">
+    <row r="197">
       <c r="A197" s="32" t="s">
         <v>1270</v>
       </c>
       <c r="B197" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A197)</f>
         <v>A</v>
       </c>
       <c r="C197" s="32" t="s">
@@ -10501,12 +10504,12 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="198" spans="1:11">
+    <row r="198">
       <c r="A198" s="32" t="s">
         <v>1272</v>
       </c>
       <c r="B198" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A198)</f>
         <v>B</v>
       </c>
       <c r="C198" s="32" t="s">
@@ -10522,12 +10525,12 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="199" spans="1:11">
+    <row r="199">
       <c r="A199" s="32" t="s">
         <v>1273</v>
       </c>
       <c r="B199" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A199)</f>
         <v>B</v>
       </c>
       <c r="C199" s="32" t="s">
@@ -10543,12 +10546,12 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="200" spans="1:11">
+    <row r="200">
       <c r="A200" s="32" t="s">
         <v>1275</v>
       </c>
       <c r="B200" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A200)</f>
         <v>G</v>
       </c>
       <c r="C200" s="32" t="s">
@@ -10564,12 +10567,12 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="201" spans="1:11">
+    <row r="201">
       <c r="A201" s="32" t="s">
         <v>1311</v>
       </c>
       <c r="B201" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A201)</f>
         <v>G</v>
       </c>
       <c r="C201" s="32" t="s">
@@ -10588,12 +10591,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="202" spans="1:11">
+    <row r="202">
       <c r="A202" s="32" t="s">
         <v>1278</v>
       </c>
       <c r="B202" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A202)</f>
         <v>P</v>
       </c>
       <c r="C202" s="32" t="s">
@@ -10609,12 +10612,12 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="203" spans="1:11">
+    <row r="203">
       <c r="A203" s="32" t="s">
         <v>1280</v>
       </c>
       <c r="B203" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A203)</f>
         <v>C</v>
       </c>
       <c r="C203" s="32" t="s">
@@ -10630,12 +10633,12 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="204" spans="1:11">
+    <row r="204">
       <c r="A204" s="32" t="s">
         <v>1281</v>
       </c>
       <c r="B204" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A204)</f>
         <v>J</v>
       </c>
       <c r="C204" s="32"/>
@@ -10649,12 +10652,12 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="205" spans="1:11">
+    <row r="205">
       <c r="A205" s="32" t="s">
         <v>1282</v>
       </c>
       <c r="B205" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A205)</f>
         <v>L</v>
       </c>
       <c r="C205" s="32" t="s">
@@ -10673,12 +10676,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="206" spans="1:11">
+    <row r="206">
       <c r="A206" s="32" t="s">
         <v>1283</v>
       </c>
       <c r="B206" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A206)</f>
         <v>P</v>
       </c>
       <c r="D206" s="26">
@@ -10691,12 +10694,12 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="207" spans="1:11">
+    <row r="207">
       <c r="A207" s="32" t="s">
         <v>1284</v>
       </c>
       <c r="B207" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A207)</f>
         <v>C</v>
       </c>
       <c r="C207" s="32" t="s">
@@ -10712,12 +10715,12 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="208" spans="1:11">
+    <row r="208">
       <c r="A208" s="32" t="s">
         <v>882</v>
       </c>
       <c r="B208" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A208)</f>
         <v>G</v>
       </c>
       <c r="C208" s="32" t="s">
@@ -10733,12 +10736,12 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="209" spans="1:11">
+    <row r="209">
       <c r="A209" s="32" t="s">
         <v>1286</v>
       </c>
       <c r="B209" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A209)</f>
         <v>B</v>
       </c>
       <c r="D209" s="26">
@@ -10751,12 +10754,12 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="210" spans="1:11">
+    <row r="210">
       <c r="A210" s="32" t="s">
         <v>1287</v>
       </c>
       <c r="B210" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A210)</f>
         <v>B</v>
       </c>
       <c r="C210" s="32" t="s">
@@ -10775,12 +10778,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="211" spans="1:11">
+    <row r="211">
       <c r="A211" s="32" t="s">
         <v>1290</v>
       </c>
       <c r="B211" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A211)</f>
         <v>T</v>
       </c>
       <c r="C211" s="32" t="s">
@@ -10796,12 +10799,12 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="212" spans="1:11">
+    <row r="212">
       <c r="A212" s="32" t="s">
         <v>1291</v>
       </c>
       <c r="B212" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A212)</f>
         <v>P</v>
       </c>
       <c r="C212" s="32" t="s">
@@ -10817,12 +10820,12 @@
         <v>1266</v>
       </c>
     </row>
-    <row r="213" spans="1:11">
+    <row r="213">
       <c r="A213" s="32" t="s">
         <v>1292</v>
       </c>
       <c r="B213" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A213)</f>
         <v>F</v>
       </c>
       <c r="C213" s="32" t="s">
@@ -10838,12 +10841,12 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="214" spans="1:11">
+    <row r="214">
       <c r="A214" s="32" t="s">
         <v>1293</v>
       </c>
       <c r="B214" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A214)</f>
         <v>H</v>
       </c>
       <c r="C214" t="s">
@@ -10859,12 +10862,12 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="215" spans="1:11">
+    <row r="215">
       <c r="A215" s="32" t="s">
         <v>1294</v>
       </c>
       <c r="B215" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A215)</f>
         <v>D</v>
       </c>
       <c r="C215" t="s">
@@ -10880,12 +10883,12 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="216" spans="1:11">
+    <row r="216">
       <c r="A216" s="32" t="s">
         <v>1295</v>
       </c>
       <c r="B216" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A216)</f>
         <v>C</v>
       </c>
       <c r="C216" t="s">
@@ -10901,12 +10904,12 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="217" spans="1:11">
+    <row r="217">
       <c r="A217" s="32" t="s">
         <v>1296</v>
       </c>
       <c r="B217" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A217)</f>
         <v>M</v>
       </c>
       <c r="C217" t="s">
@@ -10925,12 +10928,12 @@
         <v>176</v>
       </c>
     </row>
-    <row r="218" spans="1:11">
+    <row r="218">
       <c r="A218" s="32" t="s">
         <v>1297</v>
       </c>
       <c r="B218" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A218)</f>
         <v>L</v>
       </c>
       <c r="C218" t="s">
@@ -10946,12 +10949,12 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="219" spans="1:11">
+    <row r="219">
       <c r="A219" s="32" t="s">
         <v>1303</v>
       </c>
       <c r="B219" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A219)</f>
         <v>A</v>
       </c>
       <c r="C219" t="s">
@@ -10967,12 +10970,12 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="220" spans="1:11">
+    <row r="220">
       <c r="A220" s="32" t="s">
         <v>1304</v>
       </c>
       <c r="B220" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A220)</f>
         <v>B</v>
       </c>
       <c r="C220" t="s">
@@ -10988,12 +10991,12 @@
         <v>1266</v>
       </c>
     </row>
-    <row r="221" spans="1:11">
+    <row r="221">
       <c r="A221" s="32" t="s">
         <v>1305</v>
       </c>
       <c r="B221" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A221)</f>
         <v>C</v>
       </c>
       <c r="C221" t="s">
@@ -11009,12 +11012,12 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="222" spans="1:11">
+    <row r="222">
       <c r="A222" s="32" t="s">
         <v>1306</v>
       </c>
       <c r="B222" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A222)</f>
         <v>T</v>
       </c>
       <c r="C222" t="s">
@@ -11030,12 +11033,12 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="223" spans="1:11">
+    <row r="223">
       <c r="A223" s="93" t="s">
         <v>1312</v>
       </c>
       <c r="B223" s="61" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A223)</f>
         <v>B</v>
       </c>
       <c r="D223" s="61">
@@ -11048,12 +11051,12 @@
         <v>443</v>
       </c>
     </row>
-    <row r="224" spans="1:11">
+    <row r="224">
       <c r="A224" s="93" t="s">
         <v>1313</v>
       </c>
       <c r="B224" s="61" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A224)</f>
         <v>G</v>
       </c>
       <c r="D224" s="61">
@@ -11069,12 +11072,12 @@
         <v>176</v>
       </c>
     </row>
-    <row r="225" spans="1:11">
+    <row r="225">
       <c r="A225" s="93" t="s">
         <v>1314</v>
       </c>
       <c r="B225" s="61" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A225)</f>
         <v>C</v>
       </c>
       <c r="D225" s="61">
@@ -11087,12 +11090,12 @@
         <v>933</v>
       </c>
     </row>
-    <row r="226" spans="1:11">
+    <row r="226">
       <c r="A226" s="93" t="s">
         <v>1315</v>
       </c>
       <c r="B226" s="61" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A226)</f>
         <v>B</v>
       </c>
       <c r="D226" s="61">
@@ -11105,12 +11108,12 @@
         <v>1288</v>
       </c>
     </row>
-    <row r="227" spans="1:11">
+    <row r="227">
       <c r="A227" s="93" t="s">
         <v>1316</v>
       </c>
       <c r="B227" s="61" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A227)</f>
         <v>C</v>
       </c>
       <c r="C227" s="93" t="s">
@@ -11126,12 +11129,12 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="228" spans="1:11">
+    <row r="228">
       <c r="A228" s="93" t="s">
         <v>1317</v>
       </c>
       <c r="B228" s="61" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A228)</f>
         <v>C</v>
       </c>
       <c r="C228" s="93" t="s">
@@ -11147,12 +11150,12 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="229" spans="1:11">
+    <row r="229">
       <c r="A229" s="93" t="s">
         <v>1319</v>
       </c>
       <c r="B229" s="61" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A229)</f>
         <v>C</v>
       </c>
       <c r="C229" s="93" t="s">
@@ -11168,12 +11171,12 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="230" spans="1:11">
+    <row r="230">
       <c r="A230" s="93" t="s">
         <v>1321</v>
       </c>
       <c r="B230" s="61" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A230)</f>
         <v>G</v>
       </c>
       <c r="C230" s="93" t="s">
@@ -11189,12 +11192,12 @@
         <v>1266</v>
       </c>
     </row>
-    <row r="231" spans="1:11">
+    <row r="231">
       <c r="A231" s="93" t="s">
         <v>1323</v>
       </c>
       <c r="B231" s="61" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A231)</f>
         <v>L</v>
       </c>
       <c r="C231" s="93" t="s">
@@ -11213,12 +11216,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="232" spans="1:11">
+    <row r="232">
       <c r="A232" s="93" t="s">
         <v>1325</v>
       </c>
       <c r="B232" s="61" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A232)</f>
         <v>C</v>
       </c>
       <c r="C232" s="93" t="s">
@@ -11237,12 +11240,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="233" spans="1:11">
+    <row r="233">
       <c r="A233" s="93" t="s">
         <v>1327</v>
       </c>
       <c r="B233" s="61" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A233)</f>
         <v>G</v>
       </c>
       <c r="C233" s="93" t="s">
@@ -11261,12 +11264,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="234" spans="1:11">
+    <row r="234">
       <c r="A234" s="93" t="s">
         <v>1329</v>
       </c>
       <c r="B234" s="61" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A234)</f>
         <v>M</v>
       </c>
       <c r="C234" s="93" t="s">
@@ -11282,12 +11285,12 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="235" spans="1:11">
+    <row r="235">
       <c r="A235" s="93" t="s">
         <v>1330</v>
       </c>
       <c r="B235" s="61" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A235)</f>
         <v>M</v>
       </c>
       <c r="C235" s="93" t="s">
@@ -11303,12 +11306,12 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="236" spans="1:11">
+    <row r="236">
       <c r="A236" s="93" t="s">
         <v>1332</v>
       </c>
       <c r="B236" s="61" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A236)</f>
         <v>P</v>
       </c>
       <c r="C236" s="93" t="s">
@@ -11324,12 +11327,12 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="237" spans="1:11">
+    <row r="237">
       <c r="A237" s="93" t="s">
         <v>1333</v>
       </c>
       <c r="B237" s="61" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A237)</f>
         <v>A</v>
       </c>
       <c r="D237" s="61">
@@ -11342,12 +11345,12 @@
         <v>378</v>
       </c>
     </row>
-    <row r="238" spans="1:11">
+    <row r="238">
       <c r="A238" s="93" t="s">
         <v>1334</v>
       </c>
       <c r="B238" s="61" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A238)</f>
         <v>B</v>
       </c>
       <c r="C238" s="93" t="s">
@@ -11366,12 +11369,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="239" spans="1:11">
+    <row r="239">
       <c r="A239" s="93" t="s">
         <v>1336</v>
       </c>
       <c r="B239" s="61" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A239)</f>
         <v>B</v>
       </c>
       <c r="C239" s="93" t="s">
@@ -11390,12 +11393,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="240" spans="1:11">
+    <row r="240">
       <c r="A240" s="93" t="s">
         <v>1337</v>
       </c>
       <c r="B240" s="61" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A240)</f>
         <v>B</v>
       </c>
       <c r="C240" s="93" t="s">
@@ -11414,12 +11417,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="241" spans="1:11">
+    <row r="241">
       <c r="A241" s="93" t="s">
         <v>1339</v>
       </c>
       <c r="B241" s="61" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A241)</f>
         <v>F</v>
       </c>
       <c r="D241" s="61">
@@ -11432,12 +11435,12 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="242" spans="1:11">
+    <row r="242">
       <c r="A242" s="93" t="s">
         <v>1340</v>
       </c>
       <c r="B242" s="61" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A242)</f>
         <v>J</v>
       </c>
       <c r="D242" s="61">
@@ -11450,12 +11453,12 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="243" spans="1:11">
+    <row r="243">
       <c r="A243" s="93" t="s">
         <v>1065</v>
       </c>
       <c r="B243" s="61" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A243)</f>
         <v>L</v>
       </c>
       <c r="D243" s="61">
@@ -11468,12 +11471,12 @@
         <v>378</v>
       </c>
     </row>
-    <row r="244" spans="1:11">
+    <row r="244">
       <c r="A244" s="93" t="s">
         <v>1341</v>
       </c>
       <c r="B244" s="61" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A244)</f>
         <v>L</v>
       </c>
       <c r="D244" s="61">
@@ -11486,12 +11489,12 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="245" spans="1:11">
+    <row r="245">
       <c r="A245" s="93" t="s">
         <v>1342</v>
       </c>
       <c r="B245" s="61" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A245)</f>
         <v>P</v>
       </c>
       <c r="C245" s="93" t="s">
@@ -11510,12 +11513,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="246" spans="1:11">
+    <row r="246">
       <c r="A246" s="93" t="s">
         <v>1344</v>
       </c>
       <c r="B246" s="61" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A246)</f>
         <v>P</v>
       </c>
       <c r="C246" s="93" t="s">
@@ -11534,12 +11537,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="247" spans="1:11">
+    <row r="247">
       <c r="A247" s="93" t="s">
         <v>1346</v>
       </c>
       <c r="B247" s="61" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A247)</f>
         <v>T</v>
       </c>
       <c r="D247" s="61">
@@ -11552,12 +11555,12 @@
         <v>106</v>
       </c>
     </row>
-    <row r="248" spans="1:11">
+    <row r="248">
       <c r="A248" s="93" t="s">
         <v>1347</v>
       </c>
       <c r="B248" s="61" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A248)</f>
         <v>A</v>
       </c>
       <c r="C248" s="93" t="s">
@@ -11573,12 +11576,12 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="249" spans="1:11">
+    <row r="249">
       <c r="A249" s="93" t="s">
         <v>1349</v>
       </c>
       <c r="B249" s="61" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A249)</f>
         <v>B</v>
       </c>
       <c r="C249" s="93" t="s">
@@ -11594,12 +11597,12 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="250" spans="1:11">
+    <row r="250">
       <c r="A250" s="93" t="s">
         <v>1351</v>
       </c>
       <c r="B250" s="61" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A250)</f>
         <v>B</v>
       </c>
       <c r="C250" s="93" t="s">
@@ -11615,12 +11618,12 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="251" spans="1:11">
+    <row r="251">
       <c r="A251" s="93" t="s">
         <v>1352</v>
       </c>
       <c r="B251" s="61" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A251)</f>
         <v>D</v>
       </c>
       <c r="C251" s="93" t="s">
@@ -11639,12 +11642,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="252" spans="1:11">
+    <row r="252">
       <c r="A252" s="93" t="s">
         <v>1353</v>
       </c>
       <c r="B252" s="61" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A252)</f>
         <v>D</v>
       </c>
       <c r="C252" s="93" t="s">
@@ -11663,12 +11666,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="253" spans="1:11">
+    <row r="253">
       <c r="A253" s="93" t="s">
         <v>1355</v>
       </c>
       <c r="B253" s="61" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A253)</f>
         <v>F</v>
       </c>
       <c r="C253" s="93" t="s">
@@ -11684,12 +11687,12 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="254" spans="1:11">
+    <row r="254">
       <c r="A254" s="93" t="s">
         <v>1357</v>
       </c>
       <c r="B254" s="61" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A254)</f>
         <v>L</v>
       </c>
       <c r="C254" s="93" t="s">
@@ -11708,12 +11711,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="255" spans="1:11">
+    <row r="255">
       <c r="A255" s="93" t="s">
         <v>1358</v>
       </c>
       <c r="B255" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A255)</f>
         <v>B</v>
       </c>
       <c r="C255" s="93" t="s">
@@ -11729,12 +11732,12 @@
         <v>248</v>
       </c>
     </row>
-    <row r="256" spans="1:11">
+    <row r="256">
       <c r="A256" s="93" t="s">
         <v>1360</v>
       </c>
       <c r="B256" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A256)</f>
         <v>C</v>
       </c>
       <c r="C256" s="93" t="s">
@@ -11750,12 +11753,12 @@
         <v>273</v>
       </c>
     </row>
-    <row r="257" spans="1:11">
+    <row r="257">
       <c r="A257" s="93" t="s">
         <v>1362</v>
       </c>
       <c r="B257" s="1" t="str">
-        <f t="shared" ref="B257:B320" si="4">LEFT(A257)</f>
+        <f>LEFT(A257)</f>
         <v>C</v>
       </c>
       <c r="C257" s="93" t="s">
@@ -11774,12 +11777,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="258" spans="1:11">
+    <row r="258">
       <c r="A258" s="93" t="s">
         <v>1364</v>
       </c>
       <c r="B258" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>LEFT(A258)</f>
         <v>D</v>
       </c>
       <c r="C258" s="93" t="s">
@@ -11795,12 +11798,12 @@
         <v>933</v>
       </c>
     </row>
-    <row r="259" spans="1:11">
+    <row r="259">
       <c r="A259" s="93" t="s">
         <v>1365</v>
       </c>
       <c r="B259" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>LEFT(A259)</f>
         <v>F</v>
       </c>
       <c r="C259" s="93" t="s">
@@ -11816,12 +11819,12 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="260" spans="1:11">
+    <row r="260">
       <c r="A260" s="93" t="s">
         <v>104</v>
       </c>
       <c r="B260" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>LEFT(A260)</f>
         <v>G</v>
       </c>
       <c r="C260" s="93" t="s">
@@ -11840,12 +11843,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="261" spans="1:11">
+    <row r="261">
       <c r="A261" s="93" t="s">
         <v>1367</v>
       </c>
       <c r="B261" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>LEFT(A261)</f>
         <v>G</v>
       </c>
       <c r="C261" s="93" t="s">
@@ -11864,12 +11867,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="262" spans="1:11">
+    <row r="262">
       <c r="A262" s="93" t="s">
         <v>1368</v>
       </c>
       <c r="B262" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>LEFT(A262)</f>
         <v>H</v>
       </c>
       <c r="C262" s="93" t="s">
@@ -11885,12 +11888,12 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="263" spans="1:11">
+    <row r="263">
       <c r="A263" s="93" t="s">
         <v>1370</v>
       </c>
       <c r="B263" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>LEFT(A263)</f>
         <v>L</v>
       </c>
       <c r="C263" s="93" t="s">
@@ -11909,12 +11912,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="264" spans="1:11">
+    <row r="264">
       <c r="A264" s="93" t="s">
         <v>1372</v>
       </c>
       <c r="B264" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>LEFT(A264)</f>
         <v>L</v>
       </c>
       <c r="C264" s="93" t="s">
@@ -11933,12 +11936,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="265" spans="1:11">
+    <row r="265">
       <c r="A265" s="93" t="s">
         <v>1373</v>
       </c>
       <c r="B265" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>LEFT(A265)</f>
         <v>R</v>
       </c>
       <c r="C265" s="93" t="s">
@@ -11957,12 +11960,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="266" spans="1:11">
+    <row r="266">
       <c r="A266" s="93" t="s">
         <v>1374</v>
       </c>
       <c r="B266" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>LEFT(A266)</f>
         <v>S</v>
       </c>
       <c r="C266" s="93" t="s">
@@ -11981,12 +11984,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="267" spans="1:11">
+    <row r="267">
       <c r="A267" s="93" t="s">
         <v>1376</v>
       </c>
       <c r="B267" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>LEFT(A267)</f>
         <v>S</v>
       </c>
       <c r="C267" s="93" t="s">
@@ -12002,12 +12005,12 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="268" spans="1:11">
+    <row r="268">
       <c r="A268" s="93" t="s">
         <v>1378</v>
       </c>
       <c r="B268" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>LEFT(A268)</f>
         <v>A</v>
       </c>
       <c r="C268" s="93" t="s">
@@ -12026,12 +12029,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="269" spans="1:11">
+    <row r="269">
       <c r="A269" s="93" t="s">
         <v>1379</v>
       </c>
       <c r="B269" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>LEFT(A269)</f>
         <v>B</v>
       </c>
       <c r="C269" s="93" t="s">
@@ -12047,12 +12050,12 @@
         <v>103</v>
       </c>
     </row>
-    <row r="270" spans="1:11">
+    <row r="270">
       <c r="A270" s="93" t="s">
         <v>1381</v>
       </c>
       <c r="B270" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>LEFT(A270)</f>
         <v>B</v>
       </c>
       <c r="C270" s="93" t="s">
@@ -12068,12 +12071,12 @@
         <v>273</v>
       </c>
     </row>
-    <row r="271" spans="1:11">
+    <row r="271">
       <c r="A271" s="93" t="s">
         <v>1383</v>
       </c>
       <c r="B271" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>LEFT(A271)</f>
         <v>B</v>
       </c>
       <c r="C271" s="93" t="s">
@@ -12092,12 +12095,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="272" spans="1:11">
+    <row r="272">
       <c r="A272" s="93" t="s">
         <v>1384</v>
       </c>
       <c r="B272" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>LEFT(A272)</f>
         <v>D</v>
       </c>
       <c r="C272" s="93" t="s">
@@ -12116,12 +12119,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="273" spans="1:11">
+    <row r="273">
       <c r="A273" s="93" t="s">
         <v>1386</v>
       </c>
       <c r="B273" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>LEFT(A273)</f>
         <v>D</v>
       </c>
       <c r="C273" s="93" t="s">
@@ -12140,12 +12143,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="274" spans="1:11">
+    <row r="274">
       <c r="A274" s="93" t="s">
         <v>1387</v>
       </c>
       <c r="B274" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>LEFT(A274)</f>
         <v>G</v>
       </c>
       <c r="C274" s="93" t="s">
@@ -12164,12 +12167,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="275" spans="1:11">
+    <row r="275">
       <c r="A275" s="93" t="s">
         <v>1389</v>
       </c>
       <c r="B275" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>LEFT(A275)</f>
         <v>G</v>
       </c>
       <c r="C275" s="93" t="s">
@@ -12185,12 +12188,12 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="276" spans="1:11">
+    <row r="276">
       <c r="A276" s="93" t="s">
         <v>1390</v>
       </c>
       <c r="B276" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>LEFT(A276)</f>
         <v>H</v>
       </c>
       <c r="C276" s="93" t="s">
@@ -12209,12 +12212,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="277" spans="1:11">
+    <row r="277">
       <c r="A277" s="93" t="s">
         <v>1391</v>
       </c>
       <c r="B277" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>LEFT(A277)</f>
         <v>L</v>
       </c>
       <c r="C277" s="93" t="s">
@@ -12230,12 +12233,12 @@
         <v>412</v>
       </c>
     </row>
-    <row r="278" spans="1:11">
+    <row r="278">
       <c r="A278" s="93" t="s">
         <v>1392</v>
       </c>
       <c r="B278" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>LEFT(A278)</f>
         <v>L</v>
       </c>
       <c r="C278" s="93" t="s">
@@ -12254,12 +12257,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="279" spans="1:11">
+    <row r="279">
       <c r="A279" s="93" t="s">
         <v>1090</v>
       </c>
       <c r="B279" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>LEFT(A279)</f>
         <v>M</v>
       </c>
       <c r="C279" s="93" t="s">
@@ -12278,12 +12281,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="280" spans="1:11">
+    <row r="280">
       <c r="A280" s="93" t="s">
         <v>1393</v>
       </c>
       <c r="B280" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>LEFT(A280)</f>
         <v>P</v>
       </c>
       <c r="C280" s="93" t="s">
@@ -12299,12 +12302,12 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="281" spans="1:11">
+    <row r="281">
       <c r="A281" s="93" t="s">
         <v>1395</v>
       </c>
       <c r="B281" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>LEFT(A281)</f>
         <v>P</v>
       </c>
       <c r="C281" s="93" t="s">
@@ -12323,12 +12326,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="282" spans="1:11">
+    <row r="282">
       <c r="A282" s="93" t="s">
         <v>1397</v>
       </c>
       <c r="B282" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>LEFT(A282)</f>
         <v>R</v>
       </c>
       <c r="C282" s="93" t="s">
@@ -12344,12 +12347,12 @@
         <v>1543</v>
       </c>
     </row>
-    <row r="283" spans="1:11">
+    <row r="283">
       <c r="A283" s="93" t="s">
         <v>1398</v>
       </c>
       <c r="B283" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>LEFT(A283)</f>
         <v>V</v>
       </c>
       <c r="C283" s="93" t="s">
@@ -12368,12 +12371,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="284" spans="1:11">
+    <row r="284">
       <c r="A284" s="93" t="s">
         <v>1399</v>
       </c>
       <c r="B284" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>LEFT(A284)</f>
         <v>A</v>
       </c>
       <c r="C284" s="93" t="s">
@@ -12389,12 +12392,12 @@
         <v>224</v>
       </c>
     </row>
-    <row r="285" spans="1:11">
+    <row r="285">
       <c r="A285" s="93" t="s">
         <v>1401</v>
       </c>
       <c r="B285" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>LEFT(A285)</f>
         <v>B</v>
       </c>
       <c r="C285" s="93" t="s">
@@ -12410,12 +12413,12 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="286" spans="1:11">
+    <row r="286">
       <c r="A286" s="93" t="s">
         <v>1403</v>
       </c>
       <c r="B286" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>LEFT(A286)</f>
         <v>B</v>
       </c>
       <c r="C286" s="93" t="s">
@@ -12431,12 +12434,12 @@
         <v>943</v>
       </c>
     </row>
-    <row r="287" spans="1:11">
+    <row r="287">
       <c r="A287" s="93" t="s">
         <v>1404</v>
       </c>
       <c r="B287" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>LEFT(A287)</f>
         <v>D</v>
       </c>
       <c r="C287" s="93" t="s">
@@ -12452,12 +12455,12 @@
         <v>103</v>
       </c>
     </row>
-    <row r="288" spans="1:11">
+    <row r="288">
       <c r="A288" s="93" t="s">
         <v>1405</v>
       </c>
       <c r="B288" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>LEFT(A288)</f>
         <v>F</v>
       </c>
       <c r="C288" s="93" t="s">
@@ -12473,12 +12476,12 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="289" spans="1:6">
+    <row r="289">
       <c r="A289" s="93" t="s">
         <v>1406</v>
       </c>
       <c r="B289" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>LEFT(A289)</f>
         <v>L</v>
       </c>
       <c r="C289" s="93" t="s">
@@ -12494,12 +12497,12 @@
         <v>180</v>
       </c>
     </row>
-    <row r="290" spans="1:6">
+    <row r="290">
       <c r="A290" s="93" t="s">
         <v>1408</v>
       </c>
       <c r="B290" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>LEFT(A290)</f>
         <v>M</v>
       </c>
       <c r="C290" s="93" t="s">
@@ -12515,12 +12518,12 @@
         <v>943</v>
       </c>
     </row>
-    <row r="291" spans="1:6">
+    <row r="291">
       <c r="A291" s="93" t="s">
         <v>1409</v>
       </c>
       <c r="B291" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>LEFT(A291)</f>
         <v>M</v>
       </c>
       <c r="C291" s="93" t="s">
@@ -12536,12 +12539,12 @@
         <v>248</v>
       </c>
     </row>
-    <row r="292" spans="1:6">
+    <row r="292">
       <c r="A292" s="93" t="s">
         <v>1410</v>
       </c>
       <c r="B292" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>LEFT(A292)</f>
         <v>P</v>
       </c>
       <c r="C292" s="93" t="s">
@@ -12557,12 +12560,12 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="293" spans="1:6">
+    <row r="293">
       <c r="A293" s="93" t="s">
         <v>1411</v>
       </c>
       <c r="B293" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>LEFT(A293)</f>
         <v>R</v>
       </c>
       <c r="C293" s="93" t="s">
@@ -12578,12 +12581,12 @@
         <v>1543</v>
       </c>
     </row>
-    <row r="294" spans="1:6">
+    <row r="294">
       <c r="A294" s="93" t="s">
         <v>1413</v>
       </c>
       <c r="B294" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>LEFT(A294)</f>
         <v>S</v>
       </c>
       <c r="C294" s="93" t="s">
@@ -12599,12 +12602,12 @@
         <v>1266</v>
       </c>
     </row>
-    <row r="295" spans="1:6">
+    <row r="295">
       <c r="A295" s="93" t="s">
         <v>1415</v>
       </c>
       <c r="B295" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>LEFT(A295)</f>
         <v>T</v>
       </c>
       <c r="C295" s="93" t="s">
@@ -12620,12 +12623,12 @@
         <v>657</v>
       </c>
     </row>
-    <row r="296" spans="1:6">
+    <row r="296">
       <c r="A296" s="93" t="s">
         <v>1416</v>
       </c>
       <c r="B296" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>LEFT(A296)</f>
         <v>W</v>
       </c>
       <c r="C296" s="93" t="s">
@@ -12639,6 +12642,325 @@
       </c>
       <c r="F296" s="93" t="s">
         <v>426</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BROSSET</t>
+        </is>
+      </c>
+      <c r="B297" s="1" t="str">
+        <f>LEFT(A297)</f>
+        <v>B</v>
+      </c>
+      <c r="C297" s="93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lisa</t>
+        </is>
+      </c>
+      <c r="D297" s="61">
+        <v>2025</v>
+      </c>
+      <c r="E297" s="61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BCPST</t>
+        </is>
+      </c>
+      <c r="F297" s="93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculté (non précisée)</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DUVAL</t>
+        </is>
+      </c>
+      <c r="B298" s="1" t="str">
+        <f>LEFT(A298)</f>
+        <v>D</v>
+      </c>
+      <c r="C298" s="93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alexis</t>
+        </is>
+      </c>
+      <c r="D298" s="61">
+        <v>2025</v>
+      </c>
+      <c r="E298" s="61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BCPST</t>
+        </is>
+      </c>
+      <c r="F298" s="93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GREGOIRE</t>
+        </is>
+      </c>
+      <c r="B299" s="1" t="str">
+        <f>LEFT(A299)</f>
+        <v>G</v>
+      </c>
+      <c r="C299" s="93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Amandine</t>
+        </is>
+      </c>
+      <c r="D299" s="61">
+        <v>2025</v>
+      </c>
+      <c r="E299" s="61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BCPST</t>
+        </is>
+      </c>
+      <c r="F299" s="93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sans nouvelles</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LEMOINE</t>
+        </is>
+      </c>
+      <c r="B300" s="1" t="str">
+        <f>LEFT(A300)</f>
+        <v>L</v>
+      </c>
+      <c r="C300" s="93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aimy</t>
+        </is>
+      </c>
+      <c r="D300" s="61">
+        <v>2025</v>
+      </c>
+      <c r="E300" s="61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BCPST</t>
+        </is>
+      </c>
+      <c r="F300" s="93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Véto à l'étranger</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ROUXELIN</t>
+        </is>
+      </c>
+      <c r="B301" s="1" t="str">
+        <f>LEFT(A301)</f>
+        <v>R</v>
+      </c>
+      <c r="C301" s="93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Camille</t>
+        </is>
+      </c>
+      <c r="D301" s="61">
+        <v>2025</v>
+      </c>
+      <c r="E301" s="61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BCPST</t>
+        </is>
+      </c>
+      <c r="F301" s="93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sans nouvelles</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DISCHLY</t>
+        </is>
+      </c>
+      <c r="B302" s="1" t="str">
+        <f>LEFT(A302)</f>
+        <v>D</v>
+      </c>
+      <c r="C302" s="93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Klara</t>
+        </is>
+      </c>
+      <c r="D302" s="61">
+        <v>2026</v>
+      </c>
+      <c r="E302" s="61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BCPST</t>
+        </is>
+      </c>
+      <c r="F302" s="93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BUT</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JOUANNEAU</t>
+        </is>
+      </c>
+      <c r="B303" s="1" t="str">
+        <f>LEFT(A303)</f>
+        <v>J</v>
+      </c>
+      <c r="C303" s="93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Maxime</t>
+        </is>
+      </c>
+      <c r="D303" s="61">
+        <v>2026</v>
+      </c>
+      <c r="E303" s="61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BCPST</t>
+        </is>
+      </c>
+      <c r="F303" s="93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BUT</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LANGE</t>
+        </is>
+      </c>
+      <c r="B304" s="1" t="str">
+        <f>LEFT(A304)</f>
+        <v>L</v>
+      </c>
+      <c r="C304" s="93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mélina</t>
+        </is>
+      </c>
+      <c r="D304" s="61">
+        <v>2026</v>
+      </c>
+      <c r="E304" s="61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BCPST</t>
+        </is>
+      </c>
+      <c r="F304" s="93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculté d'Orléans</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VAUBRUN</t>
+        </is>
+      </c>
+      <c r="B305" s="1" t="str">
+        <f>LEFT(A305)</f>
+        <v>V</v>
+      </c>
+      <c r="C305" s="93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Virginie</t>
+        </is>
+      </c>
+      <c r="D305" s="61">
+        <v>2026</v>
+      </c>
+      <c r="E305" s="61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BCPST</t>
+        </is>
+      </c>
+      <c r="F305" s="93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sans nouvelles</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MINGOT</t>
+        </is>
+      </c>
+      <c r="B306" s="1" t="str">
+        <f>LEFT(A306)</f>
+        <v>M</v>
+      </c>
+      <c r="C306" s="93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vincent</t>
+        </is>
+      </c>
+      <c r="D306" s="61">
+        <v>2026</v>
+      </c>
+      <c r="E306" s="61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BCPST</t>
+        </is>
+      </c>
+      <c r="F306" s="93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sans nouvelles</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PINTO ROSA</t>
+        </is>
+      </c>
+      <c r="B307" s="1" t="str">
+        <f>LEFT(A307)</f>
+        <v>P</v>
+      </c>
+      <c r="C307" s="93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Inès</t>
+        </is>
+      </c>
+      <c r="D307" s="61">
+        <v>2026</v>
+      </c>
+      <c r="E307" s="61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BCPST</t>
+        </is>
+      </c>
+      <c r="F307" s="93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BUT</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -12677,13 +12999,14 @@
     <col min="9" max="9" width="96.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="B1" s="1" t="str">
-        <f t="shared" ref="B1:B32" si="0">LEFT(A1)</f>
-        <v>N</v>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Initiale NOM</t>
+        </is>
       </c>
       <c r="C1" s="2" t="s">
         <v>75</v>
@@ -12710,12 +13033,12 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2">
       <c r="A2" s="1" t="s">
         <v>1418</v>
       </c>
       <c r="B2" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A2)</f>
         <v>C</v>
       </c>
       <c r="C2" s="61" t="s">
@@ -12733,12 +13056,12 @@
       <c r="H2" s="79"/>
       <c r="I2" s="79"/>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3">
       <c r="A3" s="1" t="s">
         <v>1419</v>
       </c>
       <c r="B3" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A3)</f>
         <v>C</v>
       </c>
       <c r="C3" s="61" t="s">
@@ -12759,12 +13082,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4">
       <c r="A4" s="1" t="s">
         <v>1420</v>
       </c>
       <c r="B4" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A4)</f>
         <v>B</v>
       </c>
       <c r="C4" s="61" t="s">
@@ -12782,12 +13105,12 @@
       <c r="H4" s="79"/>
       <c r="I4" s="79"/>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5">
       <c r="A5" s="1" t="s">
         <v>1421</v>
       </c>
       <c r="B5" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A5)</f>
         <v>M</v>
       </c>
       <c r="C5" s="61" t="s">
@@ -12805,12 +13128,12 @@
       <c r="H5" s="79"/>
       <c r="I5" s="79"/>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6">
       <c r="A6" s="1" t="s">
         <v>1422</v>
       </c>
       <c r="B6" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A6)</f>
         <v>M</v>
       </c>
       <c r="C6" s="61" t="s">
@@ -12828,12 +13151,12 @@
       <c r="H6" s="79"/>
       <c r="I6" s="79"/>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7">
       <c r="A7" s="1" t="s">
         <v>883</v>
       </c>
       <c r="B7" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A7)</f>
         <v>C</v>
       </c>
       <c r="C7" s="61" t="s">
@@ -12851,12 +13174,12 @@
       <c r="H7" s="79"/>
       <c r="I7" s="79"/>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8">
       <c r="A8" s="1" t="s">
         <v>880</v>
       </c>
       <c r="B8" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A8)</f>
         <v>M</v>
       </c>
       <c r="C8" s="61" t="s">
@@ -12874,12 +13197,12 @@
       <c r="H8" s="79"/>
       <c r="I8" s="79"/>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9">
       <c r="A9" s="1" t="s">
         <v>879</v>
       </c>
       <c r="B9" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A9)</f>
         <v>B</v>
       </c>
       <c r="C9" s="61" t="s">
@@ -12897,12 +13220,12 @@
       <c r="H9" s="79"/>
       <c r="I9" s="79"/>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10">
       <c r="A10" s="1" t="s">
         <v>868</v>
       </c>
       <c r="B10" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A10)</f>
         <v>B</v>
       </c>
       <c r="C10" s="61" t="s">
@@ -12920,12 +13243,12 @@
       <c r="H10" s="71"/>
       <c r="I10" s="71"/>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11">
       <c r="A11" s="1" t="s">
         <v>266</v>
       </c>
       <c r="B11" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A11)</f>
         <v>G</v>
       </c>
       <c r="C11" s="61" t="s">
@@ -12943,12 +13266,12 @@
       <c r="H11" s="61"/>
       <c r="I11" s="61"/>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12">
       <c r="A12" s="1" t="s">
         <v>268</v>
       </c>
       <c r="B12" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A12)</f>
         <v>R</v>
       </c>
       <c r="C12" s="61" t="s">
@@ -12969,12 +13292,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13">
       <c r="A13" s="1" t="s">
         <v>270</v>
       </c>
       <c r="B13" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A13)</f>
         <v>B</v>
       </c>
       <c r="C13" s="1" t="s">
@@ -12990,12 +13313,12 @@
         <v>180</v>
       </c>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14">
       <c r="A14" s="1" t="s">
         <v>271</v>
       </c>
       <c r="B14" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A14)</f>
         <v>C</v>
       </c>
       <c r="C14" s="1" t="s">
@@ -13011,12 +13334,12 @@
         <v>273</v>
       </c>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15">
       <c r="A15" s="1" t="s">
         <v>274</v>
       </c>
       <c r="B15" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A15)</f>
         <v>D</v>
       </c>
       <c r="C15" s="1" t="s">
@@ -13038,12 +13361,12 @@
       <c r="M15" s="61"/>
       <c r="N15" s="1"/>
     </row>
-    <row r="16" spans="1:14">
+    <row r="16">
       <c r="A16" s="1" t="s">
         <v>276</v>
       </c>
       <c r="B16" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A16)</f>
         <v>F</v>
       </c>
       <c r="C16" s="1" t="s">
@@ -13059,12 +13382,12 @@
         <v>180</v>
       </c>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17">
       <c r="A17" s="1" t="s">
         <v>278</v>
       </c>
       <c r="B17" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A17)</f>
         <v>S</v>
       </c>
       <c r="C17" s="1" t="s">
@@ -13080,12 +13403,12 @@
         <v>103</v>
       </c>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18">
       <c r="A18" s="1" t="s">
         <v>280</v>
       </c>
       <c r="B18" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A18)</f>
         <v>U</v>
       </c>
       <c r="C18" s="1" t="s">
@@ -13101,12 +13424,12 @@
         <v>90</v>
       </c>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19">
       <c r="A19" s="1" t="s">
         <v>282</v>
       </c>
       <c r="B19" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A19)</f>
         <v>W</v>
       </c>
       <c r="C19" s="1" t="s">
@@ -13122,12 +13445,12 @@
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20">
       <c r="A20" s="1" t="s">
         <v>284</v>
       </c>
       <c r="B20" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A20)</f>
         <v>T</v>
       </c>
       <c r="C20" s="1" t="s">
@@ -13146,12 +13469,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="21" spans="1:11">
+    <row r="21">
       <c r="A21" s="1" t="s">
         <v>1542</v>
       </c>
       <c r="B21" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A21)</f>
         <v>G</v>
       </c>
       <c r="C21" s="1" t="s">
@@ -13170,12 +13493,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="22" spans="1:11">
+    <row r="22">
       <c r="A22" s="1" t="s">
         <v>287</v>
       </c>
       <c r="B22" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A22)</f>
         <v>S</v>
       </c>
       <c r="C22" s="1" t="s">
@@ -13194,12 +13517,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="23" spans="1:11">
+    <row r="23">
       <c r="A23" s="1" t="s">
         <v>1423</v>
       </c>
       <c r="B23" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A23)</f>
         <v>B</v>
       </c>
       <c r="C23" s="1" t="s">
@@ -13215,12 +13538,12 @@
         <v>114</v>
       </c>
     </row>
-    <row r="24" spans="1:11">
+    <row r="24">
       <c r="A24" s="1" t="s">
         <v>1424</v>
       </c>
       <c r="B24" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A24)</f>
         <v>E</v>
       </c>
       <c r="C24" s="1" t="s">
@@ -13236,12 +13559,12 @@
         <v>121</v>
       </c>
     </row>
-    <row r="25" spans="1:11">
+    <row r="25">
       <c r="A25" s="1" t="s">
         <v>291</v>
       </c>
       <c r="B25" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A25)</f>
         <v>G</v>
       </c>
       <c r="C25" s="1" t="s">
@@ -13257,12 +13580,12 @@
         <v>114</v>
       </c>
     </row>
-    <row r="26" spans="1:11">
+    <row r="26">
       <c r="A26" s="1" t="s">
         <v>293</v>
       </c>
       <c r="B26" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A26)</f>
         <v>H</v>
       </c>
       <c r="C26" s="1" t="s">
@@ -13278,12 +13601,12 @@
         <v>114</v>
       </c>
     </row>
-    <row r="27" spans="1:11">
+    <row r="27">
       <c r="A27" s="1" t="s">
         <v>295</v>
       </c>
       <c r="B27" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A27)</f>
         <v>P</v>
       </c>
       <c r="C27" s="1" t="s">
@@ -13299,12 +13622,12 @@
         <v>124</v>
       </c>
     </row>
-    <row r="28" spans="1:11">
+    <row r="28">
       <c r="A28" s="1" t="s">
         <v>297</v>
       </c>
       <c r="B28" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A28)</f>
         <v>R</v>
       </c>
       <c r="C28" s="1" t="s">
@@ -13320,12 +13643,12 @@
         <v>142</v>
       </c>
     </row>
-    <row r="29" spans="1:11">
+    <row r="29">
       <c r="A29" s="1" t="s">
         <v>299</v>
       </c>
       <c r="B29" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A29)</f>
         <v>L</v>
       </c>
       <c r="C29" s="1" t="s">
@@ -13344,12 +13667,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="30" spans="1:11">
+    <row r="30">
       <c r="A30" s="1" t="s">
         <v>1425</v>
       </c>
       <c r="B30" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A30)</f>
         <v>M</v>
       </c>
       <c r="C30" t="s">
@@ -13368,12 +13691,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="31" spans="1:11">
+    <row r="31">
       <c r="A31" s="7" t="s">
         <v>1426</v>
       </c>
       <c r="B31" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A31)</f>
         <v>R</v>
       </c>
       <c r="C31" t="s">
@@ -13392,12 +13715,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="32" spans="1:11">
+    <row r="32">
       <c r="A32" s="1" t="s">
         <v>302</v>
       </c>
       <c r="B32" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A32)</f>
         <v>F</v>
       </c>
       <c r="C32" s="61" t="s">
@@ -13413,12 +13736,12 @@
         <v>111</v>
       </c>
     </row>
-    <row r="33" spans="1:11">
+    <row r="33">
       <c r="A33" s="1" t="s">
         <v>1427</v>
       </c>
       <c r="B33" s="4" t="str">
-        <f t="shared" ref="B33:B64" si="1">LEFT(A33)</f>
+        <f>LEFT(A33)</f>
         <v>G</v>
       </c>
       <c r="C33" t="s">
@@ -13434,12 +13757,12 @@
         <v>121</v>
       </c>
     </row>
-    <row r="34" spans="1:11">
+    <row r="34">
       <c r="A34" s="1" t="s">
         <v>1428</v>
       </c>
       <c r="B34" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A34)</f>
         <v>J</v>
       </c>
       <c r="C34" s="1" t="s">
@@ -13455,12 +13778,12 @@
         <v>248</v>
       </c>
     </row>
-    <row r="35" spans="1:11">
+    <row r="35">
       <c r="A35" s="1" t="s">
         <v>1429</v>
       </c>
       <c r="B35" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A35)</f>
         <v>L</v>
       </c>
       <c r="C35" t="s">
@@ -13476,12 +13799,12 @@
         <v>304</v>
       </c>
     </row>
-    <row r="36" spans="1:11">
+    <row r="36">
       <c r="A36" s="1" t="s">
         <v>1430</v>
       </c>
       <c r="B36" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A36)</f>
         <v>P</v>
       </c>
       <c r="C36" t="s">
@@ -13497,12 +13820,12 @@
         <v>305</v>
       </c>
     </row>
-    <row r="37" spans="1:11">
+    <row r="37">
       <c r="A37" s="7" t="s">
         <v>306</v>
       </c>
       <c r="B37" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A37)</f>
         <v>S</v>
       </c>
       <c r="C37" s="7" t="s">
@@ -13521,12 +13844,12 @@
         <v>918</v>
       </c>
     </row>
-    <row r="38" spans="1:11">
+    <row r="38">
       <c r="A38" s="7" t="s">
         <v>308</v>
       </c>
       <c r="B38" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A38)</f>
         <v>V</v>
       </c>
       <c r="C38" s="7" t="s">
@@ -13542,12 +13865,12 @@
         <v>111</v>
       </c>
     </row>
-    <row r="39" spans="1:11">
+    <row r="39">
       <c r="A39" s="7" t="s">
         <v>310</v>
       </c>
       <c r="B39" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A39)</f>
         <v>B</v>
       </c>
       <c r="C39" s="7" t="s">
@@ -13566,12 +13889,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="40" spans="1:11">
+    <row r="40">
       <c r="A40" s="7" t="s">
         <v>312</v>
       </c>
       <c r="B40" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A40)</f>
         <v>D</v>
       </c>
       <c r="C40" s="7" t="s">
@@ -13590,12 +13913,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="41" spans="1:11">
+    <row r="41">
       <c r="A41" s="7" t="s">
         <v>313</v>
       </c>
       <c r="B41" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A41)</f>
         <v>B</v>
       </c>
       <c r="C41" s="61" t="s">
@@ -13611,12 +13934,12 @@
         <v>314</v>
       </c>
     </row>
-    <row r="42" spans="1:11">
+    <row r="42">
       <c r="A42" s="7" t="s">
         <v>315</v>
       </c>
       <c r="B42" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A42)</f>
         <v>C</v>
       </c>
       <c r="C42" s="7" t="s">
@@ -13632,12 +13955,12 @@
         <v>111</v>
       </c>
     </row>
-    <row r="43" spans="1:11">
+    <row r="43">
       <c r="A43" s="7" t="s">
         <v>317</v>
       </c>
       <c r="B43" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A43)</f>
         <v>C</v>
       </c>
       <c r="C43" s="7" t="s">
@@ -13656,12 +13979,12 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="44" spans="1:11">
+    <row r="44">
       <c r="A44" s="7" t="s">
         <v>319</v>
       </c>
       <c r="B44" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A44)</f>
         <v>F</v>
       </c>
       <c r="C44" s="7" t="s">
@@ -13677,12 +14000,12 @@
         <v>320</v>
       </c>
     </row>
-    <row r="45" spans="1:11">
+    <row r="45">
       <c r="A45" s="7" t="s">
         <v>321</v>
       </c>
       <c r="B45" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A45)</f>
         <v>G</v>
       </c>
       <c r="C45" s="7" t="s">
@@ -13698,12 +14021,12 @@
         <v>180</v>
       </c>
     </row>
-    <row r="46" spans="1:11">
+    <row r="46">
       <c r="A46" s="7" t="s">
         <v>323</v>
       </c>
       <c r="B46" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A46)</f>
         <v>J</v>
       </c>
       <c r="C46" s="7" t="s">
@@ -13719,12 +14042,12 @@
         <v>325</v>
       </c>
     </row>
-    <row r="47" spans="1:11">
+    <row r="47">
       <c r="A47" s="7" t="s">
         <v>326</v>
       </c>
       <c r="B47" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A47)</f>
         <v>L</v>
       </c>
       <c r="C47" s="7" t="s">
@@ -13740,12 +14063,12 @@
         <v>273</v>
       </c>
     </row>
-    <row r="48" spans="1:11">
+    <row r="48">
       <c r="A48" s="7" t="s">
         <v>328</v>
       </c>
       <c r="B48" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A48)</f>
         <v>R</v>
       </c>
       <c r="C48" s="7" t="s">
@@ -13764,12 +14087,12 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="49" spans="1:11">
+    <row r="49">
       <c r="A49" s="7" t="s">
         <v>330</v>
       </c>
       <c r="B49" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A49)</f>
         <v>V</v>
       </c>
       <c r="C49" s="7" t="s">
@@ -13785,12 +14108,12 @@
         <v>257</v>
       </c>
     </row>
-    <row r="50" spans="1:11">
+    <row r="50">
       <c r="A50" t="s">
         <v>331</v>
       </c>
       <c r="B50" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A50)</f>
         <v>W</v>
       </c>
       <c r="C50" s="7" t="s">
@@ -13806,12 +14129,12 @@
         <v>333</v>
       </c>
     </row>
-    <row r="51" spans="1:11">
+    <row r="51">
       <c r="A51" s="7" t="s">
         <v>334</v>
       </c>
       <c r="B51" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A51)</f>
         <v>B</v>
       </c>
       <c r="C51" s="7" t="s">
@@ -13830,12 +14153,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="52" spans="1:11">
+    <row r="52">
       <c r="A52" s="7" t="s">
         <v>336</v>
       </c>
       <c r="B52" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A52)</f>
         <v>M</v>
       </c>
       <c r="C52" s="7" t="s">
@@ -13854,12 +14177,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="53" spans="1:11">
+    <row r="53">
       <c r="A53" s="7" t="s">
         <v>337</v>
       </c>
       <c r="B53" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A53)</f>
         <v>P</v>
       </c>
       <c r="C53" s="7" t="s">
@@ -13878,12 +14201,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="54" spans="1:11">
+    <row r="54">
       <c r="A54" s="7" t="s">
         <v>339</v>
       </c>
       <c r="B54" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A54)</f>
         <v>B</v>
       </c>
       <c r="C54" s="7" t="s">
@@ -13905,12 +14228,12 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="55" spans="1:11">
+    <row r="55">
       <c r="A55" s="7" t="s">
         <v>340</v>
       </c>
       <c r="B55" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A55)</f>
         <v>E</v>
       </c>
       <c r="C55" s="7" t="s">
@@ -13926,12 +14249,12 @@
         <v>224</v>
       </c>
     </row>
-    <row r="56" spans="1:11">
+    <row r="56">
       <c r="A56" s="7" t="s">
         <v>342</v>
       </c>
       <c r="B56" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A56)</f>
         <v>R</v>
       </c>
       <c r="C56" s="7" t="s">
@@ -13956,12 +14279,12 @@
         <v>1134</v>
       </c>
     </row>
-    <row r="57" spans="1:11">
+    <row r="57">
       <c r="A57" s="7" t="s">
         <v>345</v>
       </c>
       <c r="B57" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A57)</f>
         <v>R</v>
       </c>
       <c r="C57" s="7" t="s">
@@ -13977,12 +14300,12 @@
         <v>124</v>
       </c>
     </row>
-    <row r="58" spans="1:11">
+    <row r="58">
       <c r="A58" s="7" t="s">
         <v>278</v>
       </c>
       <c r="B58" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A58)</f>
         <v>S</v>
       </c>
       <c r="C58" s="7" t="s">
@@ -13998,12 +14321,12 @@
         <v>139</v>
       </c>
     </row>
-    <row r="59" spans="1:11">
+    <row r="59">
       <c r="A59" s="7" t="s">
         <v>347</v>
       </c>
       <c r="B59" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A59)</f>
         <v>A</v>
       </c>
       <c r="C59" s="7" t="s">
@@ -14022,12 +14345,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="60" spans="1:11">
+    <row r="60">
       <c r="A60" s="7" t="s">
         <v>348</v>
       </c>
       <c r="B60" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A60)</f>
         <v>B</v>
       </c>
       <c r="C60" s="7" t="s">
@@ -14046,12 +14369,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="61" spans="1:11">
+    <row r="61">
       <c r="A61" s="7" t="s">
         <v>351</v>
       </c>
       <c r="B61" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A61)</f>
         <v>K</v>
       </c>
       <c r="C61" s="7" t="s">
@@ -14070,12 +14393,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="62" spans="1:11">
+    <row r="62">
       <c r="A62" s="7" t="s">
         <v>353</v>
       </c>
       <c r="B62" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A62)</f>
         <v>L</v>
       </c>
       <c r="C62" s="7" t="s">
@@ -14094,12 +14417,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="63" spans="1:11">
+    <row r="63">
       <c r="A63" s="7" t="s">
         <v>355</v>
       </c>
       <c r="B63" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A63)</f>
         <v>L</v>
       </c>
       <c r="C63" s="7" t="s">
@@ -14124,12 +14447,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="64" spans="1:11">
+    <row r="64">
       <c r="A64" s="7" t="s">
         <v>357</v>
       </c>
       <c r="B64" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>LEFT(A64)</f>
         <v>P</v>
       </c>
       <c r="C64" s="7" t="s">
@@ -14148,12 +14471,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="65" spans="1:11">
+    <row r="65">
       <c r="A65" t="s">
         <v>358</v>
       </c>
       <c r="B65" s="1" t="str">
-        <f t="shared" ref="B65:B96" si="2">LEFT(A65)</f>
+        <f>LEFT(A65)</f>
         <v>P</v>
       </c>
       <c r="C65" t="s">
@@ -14169,12 +14492,12 @@
         <v>121</v>
       </c>
     </row>
-    <row r="66" spans="1:11">
+    <row r="66">
       <c r="A66" s="7" t="s">
         <v>360</v>
       </c>
       <c r="B66" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A66)</f>
         <v>A</v>
       </c>
       <c r="C66" s="7" t="s">
@@ -14190,12 +14513,12 @@
         <v>124</v>
       </c>
     </row>
-    <row r="67" spans="1:11">
+    <row r="67">
       <c r="A67" s="7" t="s">
         <v>362</v>
       </c>
       <c r="B67" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A67)</f>
         <v>C</v>
       </c>
       <c r="C67" s="7" t="s">
@@ -14211,12 +14534,12 @@
         <v>121</v>
       </c>
     </row>
-    <row r="68" spans="1:11">
+    <row r="68">
       <c r="A68" s="7" t="s">
         <v>1431</v>
       </c>
       <c r="B68" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A68)</f>
         <v>M</v>
       </c>
       <c r="C68" s="7" t="s">
@@ -14238,12 +14561,12 @@
         <v>919</v>
       </c>
     </row>
-    <row r="69" spans="1:11">
+    <row r="69">
       <c r="A69" s="1" t="s">
         <v>1432</v>
       </c>
       <c r="B69" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A69)</f>
         <v>A</v>
       </c>
       <c r="C69" s="9" t="s">
@@ -14262,12 +14585,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="70" spans="1:11">
+    <row r="70">
       <c r="A70" t="s">
         <v>365</v>
       </c>
       <c r="B70" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A70)</f>
         <v>D</v>
       </c>
       <c r="C70" s="9" t="s">
@@ -14286,12 +14609,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="71" spans="1:11">
+    <row r="71">
       <c r="A71" s="1" t="s">
         <v>1433</v>
       </c>
       <c r="B71" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A71)</f>
         <v>M</v>
       </c>
       <c r="C71" s="9" t="s">
@@ -14310,12 +14633,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="72" spans="1:11">
+    <row r="72">
       <c r="A72" t="s">
         <v>368</v>
       </c>
       <c r="B72" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A72)</f>
         <v>P</v>
       </c>
       <c r="C72" s="9" t="s">
@@ -14334,12 +14657,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="73" spans="1:11">
+    <row r="73">
       <c r="A73" t="s">
         <v>1265</v>
       </c>
       <c r="B73" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A73)</f>
         <v>T</v>
       </c>
       <c r="C73" s="106" t="s">
@@ -14358,12 +14681,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="74" spans="1:11">
+    <row r="74">
       <c r="A74" t="s">
         <v>370</v>
       </c>
       <c r="B74" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A74)</f>
         <v>C</v>
       </c>
       <c r="C74" s="9" t="s">
@@ -14379,12 +14702,12 @@
         <v>204</v>
       </c>
     </row>
-    <row r="75" spans="1:11">
+    <row r="75">
       <c r="A75" t="s">
         <v>372</v>
       </c>
       <c r="B75" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A75)</f>
         <v>C</v>
       </c>
       <c r="C75" s="9" t="s">
@@ -14400,12 +14723,12 @@
         <v>304</v>
       </c>
     </row>
-    <row r="76" spans="1:11">
+    <row r="76">
       <c r="A76" s="1" t="s">
         <v>1434</v>
       </c>
       <c r="B76" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A76)</f>
         <v>L</v>
       </c>
       <c r="C76" s="61" t="s">
@@ -14421,12 +14744,12 @@
         <v>314</v>
       </c>
     </row>
-    <row r="77" spans="1:11">
+    <row r="77">
       <c r="A77" t="s">
         <v>373</v>
       </c>
       <c r="B77" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A77)</f>
         <v>R</v>
       </c>
       <c r="C77" t="s">
@@ -14442,12 +14765,12 @@
         <v>121</v>
       </c>
     </row>
-    <row r="78" spans="1:11">
+    <row r="78">
       <c r="A78" s="1" t="s">
         <v>1436</v>
       </c>
       <c r="B78" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A78)</f>
         <v>R</v>
       </c>
       <c r="C78" s="61" t="s">
@@ -14463,12 +14786,12 @@
         <v>273</v>
       </c>
     </row>
-    <row r="79" spans="1:11">
+    <row r="79">
       <c r="A79" t="s">
         <v>374</v>
       </c>
       <c r="B79" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A79)</f>
         <v>V</v>
       </c>
       <c r="C79" t="s">
@@ -14484,12 +14807,14 @@
         <v>103</v>
       </c>
     </row>
-    <row r="80" spans="1:11">
-      <c r="A80" t="s">
-        <v>1541</v>
+    <row r="80">
+      <c r="A80" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HERTAULT</t>
+        </is>
       </c>
       <c r="B80" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A80)</f>
         <v>H</v>
       </c>
       <c r="C80" t="s">
@@ -14508,12 +14833,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="81" spans="1:11">
+    <row r="81">
       <c r="A81" t="s">
         <v>376</v>
       </c>
       <c r="B81" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A81)</f>
         <v>M</v>
       </c>
       <c r="C81" t="s">
@@ -14529,12 +14854,12 @@
         <v>378</v>
       </c>
     </row>
-    <row r="82" spans="1:11">
+    <row r="82">
       <c r="A82" t="s">
         <v>379</v>
       </c>
       <c r="B82" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A82)</f>
         <v>R</v>
       </c>
       <c r="C82" t="s">
@@ -14550,12 +14875,12 @@
         <v>111</v>
       </c>
     </row>
-    <row r="83" spans="1:11">
+    <row r="83">
       <c r="A83" t="s">
         <v>380</v>
       </c>
       <c r="B83" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A83)</f>
         <v>T</v>
       </c>
       <c r="C83" t="s">
@@ -14571,12 +14896,12 @@
         <v>114</v>
       </c>
     </row>
-    <row r="84" spans="1:11">
+    <row r="84">
       <c r="A84" t="s">
         <v>381</v>
       </c>
       <c r="B84" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A84)</f>
         <v>V</v>
       </c>
       <c r="C84" t="s">
@@ -14592,12 +14917,12 @@
         <v>114</v>
       </c>
     </row>
-    <row r="85" spans="1:11">
+    <row r="85">
       <c r="A85" t="s">
         <v>383</v>
       </c>
       <c r="B85" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A85)</f>
         <v>B</v>
       </c>
       <c r="C85" t="s">
@@ -14616,12 +14941,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="86" spans="1:11">
+    <row r="86">
       <c r="A86" t="s">
         <v>385</v>
       </c>
       <c r="B86" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A86)</f>
         <v>B</v>
       </c>
       <c r="C86" t="s">
@@ -14640,12 +14965,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="87" spans="1:11">
+    <row r="87">
       <c r="A87" t="s">
         <v>386</v>
       </c>
       <c r="B87" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A87)</f>
         <v>D</v>
       </c>
       <c r="C87" s="61" t="s">
@@ -14664,12 +14989,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="88" spans="1:11">
+    <row r="88">
       <c r="A88" t="s">
         <v>387</v>
       </c>
       <c r="B88" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A88)</f>
         <v>G</v>
       </c>
       <c r="C88" t="s">
@@ -14688,12 +15013,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="89" spans="1:11">
+    <row r="89">
       <c r="A89" t="s">
         <v>388</v>
       </c>
       <c r="B89" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A89)</f>
         <v>P</v>
       </c>
       <c r="C89" t="s">
@@ -14712,12 +15037,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="90" spans="1:11">
+    <row r="90">
       <c r="A90" t="s">
         <v>390</v>
       </c>
       <c r="B90" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A90)</f>
         <v>B</v>
       </c>
       <c r="C90" t="s">
@@ -14733,12 +15058,12 @@
         <v>224</v>
       </c>
     </row>
-    <row r="91" spans="1:11">
+    <row r="91">
       <c r="A91" t="s">
         <v>392</v>
       </c>
       <c r="B91" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A91)</f>
         <v>D</v>
       </c>
       <c r="C91" t="s">
@@ -14754,12 +15079,12 @@
         <v>124</v>
       </c>
     </row>
-    <row r="92" spans="1:11">
+    <row r="92">
       <c r="A92" t="s">
         <v>393</v>
       </c>
       <c r="B92" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A92)</f>
         <v>F</v>
       </c>
       <c r="C92" s="61" t="s">
@@ -14775,12 +15100,12 @@
         <v>134</v>
       </c>
     </row>
-    <row r="93" spans="1:11">
+    <row r="93">
       <c r="A93" t="s">
         <v>394</v>
       </c>
       <c r="B93" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A93)</f>
         <v>F</v>
       </c>
       <c r="C93" t="s">
@@ -14796,12 +15121,12 @@
         <v>114</v>
       </c>
     </row>
-    <row r="94" spans="1:11">
+    <row r="94">
       <c r="A94" t="s">
         <v>396</v>
       </c>
       <c r="B94" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A94)</f>
         <v>H</v>
       </c>
       <c r="C94" t="s">
@@ -14817,12 +15142,12 @@
         <v>398</v>
       </c>
     </row>
-    <row r="95" spans="1:11">
+    <row r="95">
       <c r="A95" t="s">
         <v>399</v>
       </c>
       <c r="B95" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A95)</f>
         <v>L</v>
       </c>
       <c r="C95" t="s">
@@ -14838,12 +15163,12 @@
         <v>37</v>
       </c>
     </row>
-    <row r="96" spans="1:11">
+    <row r="96">
       <c r="A96" t="s">
         <v>401</v>
       </c>
       <c r="B96" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f>LEFT(A96)</f>
         <v>V</v>
       </c>
       <c r="C96" t="s">
@@ -14859,12 +15184,12 @@
         <v>121</v>
       </c>
     </row>
-    <row r="97" spans="1:11">
+    <row r="97">
       <c r="A97" t="s">
         <v>402</v>
       </c>
       <c r="B97" s="1" t="str">
-        <f t="shared" ref="B97:B128" si="3">LEFT(A97)</f>
+        <f>LEFT(A97)</f>
         <v>G</v>
       </c>
       <c r="C97" t="s">
@@ -14883,12 +15208,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="98" spans="1:11">
+    <row r="98">
       <c r="A98" t="s">
         <v>404</v>
       </c>
       <c r="B98" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A98)</f>
         <v>B</v>
       </c>
       <c r="C98" t="s">
@@ -14904,12 +15229,12 @@
         <v>124</v>
       </c>
     </row>
-    <row r="99" spans="1:11">
+    <row r="99">
       <c r="A99" t="s">
         <v>405</v>
       </c>
       <c r="B99" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A99)</f>
         <v>C</v>
       </c>
       <c r="C99" t="s">
@@ -14925,12 +15250,12 @@
         <v>180</v>
       </c>
     </row>
-    <row r="100" spans="1:11">
+    <row r="100">
       <c r="A100" t="s">
         <v>406</v>
       </c>
       <c r="B100" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A100)</f>
         <v>F</v>
       </c>
       <c r="C100" t="s">
@@ -14946,12 +15271,12 @@
         <v>224</v>
       </c>
     </row>
-    <row r="101" spans="1:11">
+    <row r="101">
       <c r="A101" t="s">
         <v>407</v>
       </c>
       <c r="B101" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A101)</f>
         <v>P</v>
       </c>
       <c r="C101" t="s">
@@ -14967,12 +15292,12 @@
         <v>273</v>
       </c>
     </row>
-    <row r="102" spans="1:11">
+    <row r="102">
       <c r="A102" t="s">
         <v>409</v>
       </c>
       <c r="B102" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A102)</f>
         <v>R</v>
       </c>
       <c r="C102" t="s">
@@ -14988,12 +15313,12 @@
         <v>121</v>
       </c>
     </row>
-    <row r="103" spans="1:11">
+    <row r="103">
       <c r="A103" s="1" t="s">
         <v>1438</v>
       </c>
       <c r="B103" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A103)</f>
         <v>P</v>
       </c>
       <c r="C103" t="s">
@@ -15009,12 +15334,12 @@
         <v>93</v>
       </c>
     </row>
-    <row r="104" spans="1:11">
+    <row r="104">
       <c r="A104" s="1" t="s">
         <v>1439</v>
       </c>
       <c r="B104" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A104)</f>
         <v>M</v>
       </c>
       <c r="C104" t="s">
@@ -15030,12 +15355,12 @@
         <v>412</v>
       </c>
     </row>
-    <row r="105" spans="1:11">
+    <row r="105">
       <c r="A105" t="s">
         <v>413</v>
       </c>
       <c r="B105" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A105)</f>
         <v>M</v>
       </c>
       <c r="C105" t="s">
@@ -15051,12 +15376,12 @@
         <v>415</v>
       </c>
     </row>
-    <row r="106" spans="1:11">
+    <row r="106">
       <c r="A106" t="s">
         <v>416</v>
       </c>
       <c r="B106" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A106)</f>
         <v>O</v>
       </c>
       <c r="C106" t="s">
@@ -15072,12 +15397,12 @@
         <v>417</v>
       </c>
     </row>
-    <row r="107" spans="1:11">
+    <row r="107">
       <c r="A107" t="s">
         <v>418</v>
       </c>
       <c r="B107" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A107)</f>
         <v>W</v>
       </c>
       <c r="C107" t="s">
@@ -15093,12 +15418,12 @@
         <v>419</v>
       </c>
     </row>
-    <row r="108" spans="1:11">
+    <row r="108">
       <c r="A108" s="9" t="s">
         <v>420</v>
       </c>
       <c r="B108" s="11" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A108)</f>
         <v>D</v>
       </c>
       <c r="C108" s="9" t="s">
@@ -15117,12 +15442,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="109" spans="1:11">
+    <row r="109">
       <c r="A109" s="9" t="s">
         <v>423</v>
       </c>
       <c r="B109" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A109)</f>
         <v>D</v>
       </c>
       <c r="C109" s="9" t="s">
@@ -15141,12 +15466,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="110" spans="1:11">
+    <row r="110">
       <c r="A110" s="9" t="s">
         <v>424</v>
       </c>
       <c r="B110" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A110)</f>
         <v>F</v>
       </c>
       <c r="C110" s="9" t="s">
@@ -15165,12 +15490,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="111" spans="1:11">
+    <row r="111">
       <c r="A111" s="9" t="s">
         <v>427</v>
       </c>
       <c r="B111" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A111)</f>
         <v>G</v>
       </c>
       <c r="C111" s="9" t="s">
@@ -15189,12 +15514,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="112" spans="1:11">
+    <row r="112">
       <c r="A112" s="9" t="s">
         <v>429</v>
       </c>
       <c r="B112" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A112)</f>
         <v>M</v>
       </c>
       <c r="C112" s="9" t="s">
@@ -15213,12 +15538,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="113" spans="1:11">
+    <row r="113">
       <c r="A113" s="9" t="s">
         <v>431</v>
       </c>
       <c r="B113" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A113)</f>
         <v>M</v>
       </c>
       <c r="C113" s="9" t="s">
@@ -15237,12 +15562,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="114" spans="1:11">
+    <row r="114">
       <c r="A114" s="9" t="s">
         <v>432</v>
       </c>
       <c r="B114" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A114)</f>
         <v>P</v>
       </c>
       <c r="C114" s="9" t="s">
@@ -15261,12 +15586,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="115" spans="1:11">
+    <row r="115">
       <c r="A115" s="9" t="s">
         <v>434</v>
       </c>
       <c r="B115" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A115)</f>
         <v>B</v>
       </c>
       <c r="C115" s="9" t="s">
@@ -15282,12 +15607,12 @@
         <v>134</v>
       </c>
     </row>
-    <row r="116" spans="1:11">
+    <row r="116">
       <c r="A116" s="9" t="s">
         <v>436</v>
       </c>
       <c r="B116" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A116)</f>
         <v>C</v>
       </c>
       <c r="C116" s="9" t="s">
@@ -15306,12 +15631,12 @@
         <v>921</v>
       </c>
     </row>
-    <row r="117" spans="1:11">
+    <row r="117">
       <c r="A117" s="9" t="s">
         <v>438</v>
       </c>
       <c r="B117" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A117)</f>
         <v>M</v>
       </c>
       <c r="C117" s="9" t="s">
@@ -15330,12 +15655,12 @@
         <v>921</v>
       </c>
     </row>
-    <row r="118" spans="1:11">
+    <row r="118">
       <c r="A118" s="9" t="s">
         <v>440</v>
       </c>
       <c r="B118" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A118)</f>
         <v>S</v>
       </c>
       <c r="C118" s="9" t="s">
@@ -15351,12 +15676,12 @@
         <v>98</v>
       </c>
     </row>
-    <row r="119" spans="1:11">
+    <row r="119">
       <c r="A119" s="106" t="s">
         <v>1440</v>
       </c>
       <c r="B119" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A119)</f>
         <v>V</v>
       </c>
       <c r="C119" s="106" t="s">
@@ -15375,12 +15700,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="120" spans="1:11">
+    <row r="120">
       <c r="A120" s="9" t="s">
         <v>1441</v>
       </c>
       <c r="B120" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A120)</f>
         <v>V</v>
       </c>
       <c r="C120" s="9" t="s">
@@ -15396,12 +15721,12 @@
         <v>98</v>
       </c>
     </row>
-    <row r="121" spans="1:11">
+    <row r="121">
       <c r="A121" s="9" t="s">
         <v>442</v>
       </c>
       <c r="B121" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A121)</f>
         <v>P</v>
       </c>
       <c r="C121" s="9" t="s">
@@ -15420,12 +15745,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="122" spans="1:11">
+    <row r="122">
       <c r="A122" s="9" t="s">
         <v>444</v>
       </c>
       <c r="B122" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A122)</f>
         <v>P</v>
       </c>
       <c r="C122" s="9" t="s">
@@ -15444,12 +15769,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="123" spans="1:11">
+    <row r="123">
       <c r="A123" s="9" t="s">
         <v>446</v>
       </c>
       <c r="B123" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A123)</f>
         <v>Z</v>
       </c>
       <c r="C123" s="9" t="s">
@@ -15468,12 +15793,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="124" spans="1:11">
+    <row r="124">
       <c r="A124" s="9" t="s">
         <v>448</v>
       </c>
       <c r="B124" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A124)</f>
         <v>B</v>
       </c>
       <c r="C124" s="11" t="s">
@@ -15489,12 +15814,12 @@
         <v>426</v>
       </c>
     </row>
-    <row r="125" spans="1:11">
+    <row r="125">
       <c r="A125" s="9" t="s">
         <v>449</v>
       </c>
       <c r="B125" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A125)</f>
         <v>B</v>
       </c>
       <c r="C125" s="9" t="s">
@@ -15510,12 +15835,12 @@
         <v>103</v>
       </c>
     </row>
-    <row r="126" spans="1:11">
+    <row r="126">
       <c r="A126" t="s">
         <v>450</v>
       </c>
       <c r="B126" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A126)</f>
         <v>D</v>
       </c>
       <c r="C126" s="9" t="s">
@@ -15531,12 +15856,12 @@
         <v>273</v>
       </c>
     </row>
-    <row r="127" spans="1:11">
+    <row r="127">
       <c r="A127" s="9" t="s">
         <v>451</v>
       </c>
       <c r="B127" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A127)</f>
         <v>M</v>
       </c>
       <c r="C127" s="9" t="s">
@@ -15552,12 +15877,12 @@
         <v>273</v>
       </c>
     </row>
-    <row r="128" spans="1:11">
+    <row r="128">
       <c r="A128" s="1" t="s">
         <v>1442</v>
       </c>
       <c r="B128" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f>LEFT(A128)</f>
         <v>B</v>
       </c>
       <c r="C128" s="61" t="s">
@@ -15573,12 +15898,12 @@
         <v>1288</v>
       </c>
     </row>
-    <row r="129" spans="1:11">
+    <row r="129">
       <c r="A129" s="1" t="s">
         <v>137</v>
       </c>
       <c r="B129" s="1" t="str">
-        <f t="shared" ref="B129:B160" si="4">LEFT(A129)</f>
+        <f>LEFT(A129)</f>
         <v>B</v>
       </c>
       <c r="C129" s="61" t="s">
@@ -15594,12 +15919,12 @@
         <v>1288</v>
       </c>
     </row>
-    <row r="130" spans="1:11">
+    <row r="130">
       <c r="A130" s="1" t="s">
         <v>1444</v>
       </c>
       <c r="B130" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>LEFT(A130)</f>
         <v>D</v>
       </c>
       <c r="C130" s="61" t="s">
@@ -15618,12 +15943,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="131" spans="1:11">
+    <row r="131">
       <c r="A131" s="1" t="s">
         <v>1445</v>
       </c>
       <c r="B131" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>LEFT(A131)</f>
         <v>V</v>
       </c>
       <c r="C131" s="61" t="s">
@@ -15642,12 +15967,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="132" spans="1:11">
+    <row r="132">
       <c r="A132" s="1" t="s">
         <v>1446</v>
       </c>
       <c r="B132" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>LEFT(A132)</f>
         <v>D</v>
       </c>
       <c r="C132" s="61" t="s">
@@ -15666,12 +15991,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="133" spans="1:11">
+    <row r="133">
       <c r="A133" s="1" t="s">
         <v>1447</v>
       </c>
       <c r="B133" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>LEFT(A133)</f>
         <v>L</v>
       </c>
       <c r="C133" s="61" t="s">
@@ -15687,12 +16012,12 @@
         <v>320</v>
       </c>
     </row>
-    <row r="134" spans="1:11">
+    <row r="134">
       <c r="A134" s="1" t="s">
         <v>1448</v>
       </c>
       <c r="B134" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>LEFT(A134)</f>
         <v>P</v>
       </c>
       <c r="C134" s="61" t="s">
@@ -15708,12 +16033,12 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="135" spans="1:11">
+    <row r="135">
       <c r="A135" s="1" t="s">
         <v>1450</v>
       </c>
       <c r="B135" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>LEFT(A135)</f>
         <v>C</v>
       </c>
       <c r="C135" s="61" t="s">
@@ -15729,12 +16054,12 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="136" spans="1:11">
+    <row r="136">
       <c r="A136" s="1" t="s">
         <v>104</v>
       </c>
       <c r="B136" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>LEFT(A136)</f>
         <v>G</v>
       </c>
       <c r="C136" s="61" t="s">
@@ -15750,12 +16075,12 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="137" spans="1:11">
+    <row r="137">
       <c r="A137" s="1" t="s">
         <v>1452</v>
       </c>
       <c r="B137" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>LEFT(A137)</f>
         <v>L</v>
       </c>
       <c r="C137" s="61" t="s">
@@ -15771,12 +16096,12 @@
         <v>1288</v>
       </c>
     </row>
-    <row r="138" spans="1:11">
+    <row r="138">
       <c r="A138" s="1" t="s">
         <v>1454</v>
       </c>
       <c r="B138" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>LEFT(A138)</f>
         <v>L</v>
       </c>
       <c r="C138" s="61" t="s">
@@ -15792,12 +16117,12 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="139" spans="1:11">
+    <row r="139">
       <c r="A139" s="1" t="s">
         <v>1455</v>
       </c>
       <c r="B139" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>LEFT(A139)</f>
         <v>L</v>
       </c>
       <c r="C139" s="61" t="s">
@@ -15816,12 +16141,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="140" spans="1:11">
+    <row r="140">
       <c r="A140" s="1" t="s">
         <v>1456</v>
       </c>
       <c r="B140" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>LEFT(A140)</f>
         <v>S</v>
       </c>
       <c r="C140" s="61" t="s">
@@ -15840,12 +16165,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="141" spans="1:11">
+    <row r="141">
       <c r="A141" s="1" t="s">
         <v>1458</v>
       </c>
       <c r="B141" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>LEFT(A141)</f>
         <v>E</v>
       </c>
       <c r="C141" s="61" t="s">
@@ -15861,12 +16186,12 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="142" spans="1:11">
+    <row r="142">
       <c r="A142" s="1" t="s">
         <v>1459</v>
       </c>
       <c r="B142" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>LEFT(A142)</f>
         <v>P</v>
       </c>
       <c r="C142" s="61" t="s">
@@ -15885,12 +16210,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="143" spans="1:11">
+    <row r="143">
       <c r="A143" s="1" t="s">
         <v>1461</v>
       </c>
       <c r="B143" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>LEFT(A143)</f>
         <v>P</v>
       </c>
       <c r="C143" s="61" t="s">
@@ -15906,12 +16231,12 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="144" spans="1:11">
+    <row r="144">
       <c r="A144" s="1" t="s">
         <v>1462</v>
       </c>
       <c r="B144" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>LEFT(A144)</f>
         <v>B</v>
       </c>
       <c r="C144" s="61" t="s">
@@ -15927,12 +16252,12 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="145" spans="1:11">
+    <row r="145">
       <c r="A145" s="1" t="s">
         <v>1464</v>
       </c>
       <c r="B145" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>LEFT(A145)</f>
         <v>K</v>
       </c>
       <c r="C145" s="61" t="s">
@@ -15948,12 +16273,12 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="146" spans="1:11">
+    <row r="146">
       <c r="A146" s="1" t="s">
         <v>1466</v>
       </c>
       <c r="B146" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>LEFT(A146)</f>
         <v>L</v>
       </c>
       <c r="C146" s="61" t="s">
@@ -15972,12 +16297,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="147" spans="1:11">
+    <row r="147">
       <c r="A147" s="1" t="s">
         <v>1468</v>
       </c>
       <c r="B147" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>LEFT(A147)</f>
         <v>P</v>
       </c>
       <c r="C147" s="61" t="s">
@@ -15996,12 +16321,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="148" spans="1:11">
+    <row r="148">
       <c r="A148" s="1" t="s">
         <v>1470</v>
       </c>
       <c r="B148" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>LEFT(A148)</f>
         <v>R</v>
       </c>
       <c r="C148" s="61" t="s">
@@ -16017,12 +16342,12 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="149" spans="1:11">
+    <row r="149">
       <c r="A149" s="1" t="s">
         <v>1472</v>
       </c>
       <c r="B149" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>LEFT(A149)</f>
         <v>S</v>
       </c>
       <c r="C149" s="61" t="s">
@@ -16038,12 +16363,12 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="150" spans="1:11">
+    <row r="150">
       <c r="A150" s="1" t="s">
         <v>1474</v>
       </c>
       <c r="B150" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>LEFT(A150)</f>
         <v>C</v>
       </c>
       <c r="C150" s="61" t="s">
@@ -16062,12 +16387,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="151" spans="1:11">
+    <row r="151">
       <c r="A151" s="1" t="s">
         <v>1476</v>
       </c>
       <c r="B151" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>LEFT(A151)</f>
         <v>E</v>
       </c>
       <c r="C151" s="61" t="s">
@@ -16086,12 +16411,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="152" spans="1:11">
+    <row r="152">
       <c r="A152" s="1" t="s">
         <v>1477</v>
       </c>
       <c r="B152" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>LEFT(A152)</f>
         <v>L</v>
       </c>
       <c r="C152" s="61" t="s">
@@ -16107,12 +16432,12 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="153" spans="1:11">
+    <row r="153">
       <c r="A153" s="1" t="s">
         <v>1479</v>
       </c>
       <c r="B153" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>LEFT(A153)</f>
         <v>P</v>
       </c>
       <c r="C153" s="61" t="s">
@@ -16128,12 +16453,12 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="154" spans="1:11">
+    <row r="154">
       <c r="A154" s="1" t="s">
         <v>1481</v>
       </c>
       <c r="B154" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>LEFT(A154)</f>
         <v>T</v>
       </c>
       <c r="C154" s="61" t="s">
@@ -16152,12 +16477,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="155" spans="1:11">
+    <row r="155">
       <c r="A155" s="1" t="s">
         <v>1482</v>
       </c>
       <c r="B155" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>LEFT(A155)</f>
         <v>V</v>
       </c>
       <c r="C155" s="61" t="s">
@@ -16176,12 +16501,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="156" spans="1:11">
+    <row r="156">
       <c r="A156" s="1" t="s">
         <v>1484</v>
       </c>
       <c r="B156" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>LEFT(A156)</f>
         <v>C</v>
       </c>
       <c r="C156" s="61" t="s">
@@ -16197,12 +16522,12 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="157" spans="1:11">
+    <row r="157">
       <c r="A157" s="1" t="s">
         <v>1485</v>
       </c>
       <c r="B157" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>LEFT(A157)</f>
         <v>G</v>
       </c>
       <c r="C157" s="61" t="s">
@@ -16218,12 +16543,12 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="158" spans="1:11">
+    <row r="158">
       <c r="A158" s="1" t="s">
         <v>1486</v>
       </c>
       <c r="B158" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>LEFT(A158)</f>
         <v>G</v>
       </c>
       <c r="C158" s="61" t="s">
@@ -16239,12 +16564,12 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="159" spans="1:11">
+    <row r="159">
       <c r="A159" s="1" t="s">
         <v>1487</v>
       </c>
       <c r="B159" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>LEFT(A159)</f>
         <v>K</v>
       </c>
       <c r="C159" s="61" t="s">
@@ -16260,12 +16585,12 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="160" spans="1:11">
+    <row r="160">
       <c r="A160" s="1" t="s">
         <v>1489</v>
       </c>
       <c r="B160" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>LEFT(A160)</f>
         <v>L</v>
       </c>
       <c r="C160" s="61" t="s">
@@ -16284,12 +16609,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="161" spans="1:6">
+    <row r="161">
       <c r="A161" s="1" t="s">
         <v>1490</v>
       </c>
       <c r="B161" s="1" t="str">
-        <f t="shared" ref="B161:B192" si="5">LEFT(A161)</f>
+        <f>LEFT(A161)</f>
         <v>M</v>
       </c>
       <c r="C161" s="61" t="s">
@@ -16305,12 +16630,12 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="162" spans="1:6">
+    <row r="162">
       <c r="A162" s="1" t="s">
         <v>1046</v>
       </c>
       <c r="B162" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f>LEFT(A162)</f>
         <v>M</v>
       </c>
       <c r="C162" s="61" t="s">
@@ -16326,12 +16651,12 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="163" spans="1:6">
+    <row r="163">
       <c r="A163" s="1" t="s">
         <v>1491</v>
       </c>
       <c r="B163" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f>LEFT(A163)</f>
         <v>M</v>
       </c>
       <c r="C163" s="61" t="s">
@@ -16347,12 +16672,12 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="164" spans="1:6">
+    <row r="164">
       <c r="A164" s="1" t="s">
         <v>1493</v>
       </c>
       <c r="B164" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f>LEFT(A164)</f>
         <v>P</v>
       </c>
       <c r="C164" s="61" t="s">
@@ -16368,12 +16693,12 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="165" spans="1:6">
+    <row r="165">
       <c r="A165" s="1" t="s">
         <v>1479</v>
       </c>
       <c r="B165" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f>LEFT(A165)</f>
         <v>P</v>
       </c>
       <c r="C165" s="61" t="s">
@@ -16389,12 +16714,12 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="166" spans="1:6">
+    <row r="166">
       <c r="A166" s="1" t="s">
         <v>1496</v>
       </c>
       <c r="B166" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f>LEFT(A166)</f>
         <v>B</v>
       </c>
       <c r="C166" s="61" t="s">
@@ -16410,12 +16735,12 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="167" spans="1:6">
+    <row r="167">
       <c r="A167" s="1" t="s">
         <v>1497</v>
       </c>
       <c r="B167" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f>LEFT(A167)</f>
         <v>L</v>
       </c>
       <c r="C167" s="61" t="s">
@@ -16431,12 +16756,12 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="168" spans="1:6">
+    <row r="168">
       <c r="A168" s="1" t="s">
         <v>1498</v>
       </c>
       <c r="B168" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f>LEFT(A168)</f>
         <v>M</v>
       </c>
       <c r="C168" s="61" t="s">
@@ -16452,12 +16777,12 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="169" spans="1:6">
+    <row r="169">
       <c r="A169" s="1" t="s">
         <v>1500</v>
       </c>
       <c r="B169" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f>LEFT(A169)</f>
         <v>R</v>
       </c>
       <c r="C169" s="61" t="s">
@@ -16473,12 +16798,12 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="170" spans="1:6">
+    <row r="170">
       <c r="A170" s="1" t="s">
         <v>1502</v>
       </c>
       <c r="B170" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f>LEFT(A170)</f>
         <v>T</v>
       </c>
       <c r="C170" s="61" t="s">
@@ -16494,12 +16819,12 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="171" spans="1:6">
+    <row r="171">
       <c r="A171" s="1" t="s">
         <v>1503</v>
       </c>
       <c r="B171" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f>LEFT(A171)</f>
         <v>D</v>
       </c>
       <c r="C171" s="61" t="s">
@@ -16515,12 +16840,12 @@
         <v>106</v>
       </c>
     </row>
-    <row r="172" spans="1:6">
+    <row r="172">
       <c r="A172" s="1" t="s">
         <v>1504</v>
       </c>
       <c r="B172" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f>LEFT(A172)</f>
         <v>G</v>
       </c>
       <c r="C172" s="61" t="s">
@@ -16536,12 +16861,12 @@
         <v>933</v>
       </c>
     </row>
-    <row r="173" spans="1:6">
+    <row r="173">
       <c r="A173" s="1" t="s">
         <v>1506</v>
       </c>
       <c r="B173" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f>LEFT(A173)</f>
         <v>P</v>
       </c>
       <c r="C173" s="61" t="s">
@@ -16557,12 +16882,12 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="174" spans="1:6">
+    <row r="174">
       <c r="A174" s="1" t="s">
         <v>1507</v>
       </c>
       <c r="B174" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f>LEFT(A174)</f>
         <v>W</v>
       </c>
       <c r="C174" s="61" t="s">
@@ -16578,12 +16903,12 @@
         <v>1266</v>
       </c>
     </row>
-    <row r="175" spans="1:6">
+    <row r="175">
       <c r="A175" s="1" t="s">
         <v>1508</v>
       </c>
       <c r="B175" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f>LEFT(A175)</f>
         <v>C</v>
       </c>
       <c r="C175" s="61" t="s">
@@ -16599,12 +16924,12 @@
         <v>933</v>
       </c>
     </row>
-    <row r="176" spans="1:6">
+    <row r="176">
       <c r="A176" s="1" t="s">
         <v>1510</v>
       </c>
       <c r="B176" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f>LEFT(A176)</f>
         <v>D</v>
       </c>
       <c r="C176" s="61" t="s">
@@ -16620,12 +16945,12 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="177" spans="1:11">
+    <row r="177">
       <c r="A177" s="1" t="s">
         <v>1511</v>
       </c>
       <c r="B177" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f>LEFT(A177)</f>
         <v>D</v>
       </c>
       <c r="C177" s="61" t="s">
@@ -16644,12 +16969,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="178" spans="1:11">
+    <row r="178">
       <c r="A178" s="1" t="s">
         <v>1512</v>
       </c>
       <c r="B178" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f>LEFT(A178)</f>
         <v>K</v>
       </c>
       <c r="C178" s="61" t="s">
@@ -16665,12 +16990,12 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="179" spans="1:11">
+    <row r="179">
       <c r="A179" s="1" t="s">
         <v>1513</v>
       </c>
       <c r="B179" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f>LEFT(A179)</f>
         <v>R</v>
       </c>
       <c r="C179" s="61" t="s">
@@ -16686,12 +17011,12 @@
         <v>93</v>
       </c>
     </row>
-    <row r="180" spans="1:11">
+    <row r="180">
       <c r="A180" s="1" t="s">
         <v>1515</v>
       </c>
       <c r="B180" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f>LEFT(A180)</f>
         <v>T</v>
       </c>
       <c r="C180" s="61" t="s">
@@ -16707,12 +17032,12 @@
         <v>419</v>
       </c>
     </row>
-    <row r="181" spans="1:11">
+    <row r="181">
       <c r="A181" s="1" t="s">
         <v>1517</v>
       </c>
       <c r="B181" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f>LEFT(A181)</f>
         <v>B</v>
       </c>
       <c r="C181" s="61" t="s">
@@ -16728,12 +17053,12 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="182" spans="1:11">
+    <row r="182">
       <c r="A182" s="1" t="s">
         <v>1518</v>
       </c>
       <c r="B182" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f>LEFT(A182)</f>
         <v>C</v>
       </c>
       <c r="C182" s="61" t="s">
@@ -16749,12 +17074,12 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="183" spans="1:11">
+    <row r="183">
       <c r="A183" s="1" t="s">
         <v>1520</v>
       </c>
       <c r="B183" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f>LEFT(A183)</f>
         <v>H</v>
       </c>
       <c r="C183" s="61" t="s">
@@ -16770,12 +17095,12 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="184" spans="1:11">
+    <row r="184">
       <c r="A184" s="1" t="s">
         <v>1522</v>
       </c>
       <c r="B184" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f>LEFT(A184)</f>
         <v>K</v>
       </c>
       <c r="C184" s="61" t="s">
@@ -16791,12 +17116,12 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="185" spans="1:11">
+    <row r="185">
       <c r="A185" s="1" t="s">
         <v>1523</v>
       </c>
       <c r="B185" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f>LEFT(A185)</f>
         <v>P</v>
       </c>
       <c r="C185" s="61" t="s">
@@ -16812,12 +17137,12 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="186" spans="1:11">
+    <row r="186">
       <c r="A186" s="1" t="s">
         <v>393</v>
       </c>
       <c r="B186" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f>LEFT(A186)</f>
         <v>F</v>
       </c>
       <c r="C186" s="61" t="s">
@@ -16833,12 +17158,12 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="187" spans="1:11">
+    <row r="187">
       <c r="A187" s="1" t="s">
         <v>1526</v>
       </c>
       <c r="B187" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f>LEFT(A187)</f>
         <v>B</v>
       </c>
       <c r="C187" s="61" t="s">
@@ -16854,12 +17179,12 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="188" spans="1:11">
+    <row r="188">
       <c r="A188" s="1" t="s">
         <v>1528</v>
       </c>
       <c r="B188" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f>LEFT(A188)</f>
         <v>L</v>
       </c>
       <c r="C188" s="61" t="s">
@@ -16878,12 +17203,12 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="189" spans="1:11">
+    <row r="189">
       <c r="A189" s="1" t="s">
         <v>1530</v>
       </c>
       <c r="B189" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f>LEFT(A189)</f>
         <v>B</v>
       </c>
       <c r="C189" s="61" t="s">
@@ -16899,12 +17224,12 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="190" spans="1:11">
+    <row r="190">
       <c r="A190" s="1" t="s">
         <v>1532</v>
       </c>
       <c r="B190" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f>LEFT(A190)</f>
         <v>D</v>
       </c>
       <c r="C190" s="61" t="s">
@@ -16920,12 +17245,12 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="191" spans="1:11">
+    <row r="191">
       <c r="A191" s="1" t="s">
         <v>1513</v>
       </c>
       <c r="B191" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f>LEFT(A191)</f>
         <v>R</v>
       </c>
       <c r="C191" s="61" t="s">

--- a/anciens_eleves.xlsx
+++ b/anciens_eleves.xlsx
@@ -5816,7 +5816,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K307"/>
+  <dimension ref="A1:K313"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="27.42578125" customWidth="1"/>
@@ -12669,7 +12669,7 @@
       </c>
       <c r="F297" s="93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Faculté (non précisée)</t>
+          <t xml:space="preserve">UPPA</t>
         </is>
       </c>
     </row>
@@ -12727,7 +12727,7 @@
       </c>
       <c r="F299" s="93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sans nouvelles</t>
+          <t xml:space="preserve">Sup'Véto</t>
         </is>
       </c>
     </row>
@@ -12930,7 +12930,7 @@
       </c>
       <c r="F306" s="93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sans nouvelles</t>
+          <t xml:space="preserve">IFSI</t>
         </is>
       </c>
     </row>
@@ -12960,6 +12960,180 @@
       <c r="F307" s="93" t="inlineStr">
         <is>
           <t xml:space="preserve">BUT</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BELIN</t>
+        </is>
+      </c>
+      <c r="B308" s="1" t="str">
+        <f>LEFT(A308)</f>
+        <v>B</v>
+      </c>
+      <c r="C308" s="93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Axel</t>
+        </is>
+      </c>
+      <c r="D308" s="61">
+        <v>2026</v>
+      </c>
+      <c r="E308" s="61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BCPST</t>
+        </is>
+      </c>
+      <c r="F308" s="93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5/2</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DECOUDUN</t>
+        </is>
+      </c>
+      <c r="B309" s="1" t="str">
+        <f>LEFT(A309)</f>
+        <v>D</v>
+      </c>
+      <c r="C309" s="93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mélanie</t>
+        </is>
+      </c>
+      <c r="D309" s="61">
+        <v>2026</v>
+      </c>
+      <c r="E309" s="61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BCPST</t>
+        </is>
+      </c>
+      <c r="F309" s="93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5/2</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JUIN</t>
+        </is>
+      </c>
+      <c r="B310" s="1" t="str">
+        <f>LEFT(A310)</f>
+        <v>J</v>
+      </c>
+      <c r="C310" s="93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Océane</t>
+        </is>
+      </c>
+      <c r="D310" s="61">
+        <v>2026</v>
+      </c>
+      <c r="E310" s="61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BCPST</t>
+        </is>
+      </c>
+      <c r="F310" s="93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5/2</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KINIUK</t>
+        </is>
+      </c>
+      <c r="B311" s="1" t="str">
+        <f>LEFT(A311)</f>
+        <v>K</v>
+      </c>
+      <c r="C311" s="93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alexandre</t>
+        </is>
+      </c>
+      <c r="D311" s="61">
+        <v>2026</v>
+      </c>
+      <c r="E311" s="61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BCPST</t>
+        </is>
+      </c>
+      <c r="F311" s="93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5/2</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PHILIPPE</t>
+        </is>
+      </c>
+      <c r="B312" s="1" t="str">
+        <f>LEFT(A312)</f>
+        <v>P</v>
+      </c>
+      <c r="C312" s="93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Thomas</t>
+        </is>
+      </c>
+      <c r="D312" s="61">
+        <v>2026</v>
+      </c>
+      <c r="E312" s="61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BCPST</t>
+        </is>
+      </c>
+      <c r="F312" s="93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5/2</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PRENCHÈRE</t>
+        </is>
+      </c>
+      <c r="B313" s="1" t="str">
+        <f>LEFT(A313)</f>
+        <v>P</v>
+      </c>
+      <c r="C313" s="93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kelvin</t>
+        </is>
+      </c>
+      <c r="D313" s="61">
+        <v>2026</v>
+      </c>
+      <c r="E313" s="61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BCPST</t>
+        </is>
+      </c>
+      <c r="F313" s="93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5/2</t>
         </is>
       </c>
     </row>
@@ -17300,7 +17474,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:M87"/>
+  <dimension ref="A1:M91"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22.28515625" style="3" customWidth="1"/>
@@ -17314,7 +17488,7 @@
     <col min="13" max="16384" width="11.42578125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="39.950000000000003" customHeight="1">
+    <row r="1" ht="39.950000000000003" customHeight="1">
       <c r="A1" s="3" t="s">
         <v>74</v>
       </c>
@@ -17352,7 +17526,7 @@
         <v>895</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="345">
+    <row r="2" ht="345">
       <c r="A2" s="3" t="s">
         <v>124</v>
       </c>
@@ -17390,7 +17564,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="39.950000000000003" customHeight="1">
+    <row r="3" ht="39.950000000000003" customHeight="1">
       <c r="A3" s="3" t="s">
         <v>114</v>
       </c>
@@ -17428,7 +17602,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="180">
+    <row r="4" ht="180">
       <c r="A4" s="3" t="s">
         <v>37</v>
       </c>
@@ -17466,7 +17640,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="39.950000000000003" customHeight="1">
+    <row r="5" ht="39.950000000000003" customHeight="1">
       <c r="A5" s="3" t="s">
         <v>121</v>
       </c>
@@ -17504,7 +17678,7 @@
         <v>1197</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="39.950000000000003" customHeight="1">
+    <row r="6" ht="39.950000000000003" customHeight="1">
       <c r="A6" s="3" t="s">
         <v>103</v>
       </c>
@@ -17542,7 +17716,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="285">
+    <row r="7" ht="285">
       <c r="A7" s="3" t="s">
         <v>273</v>
       </c>
@@ -17580,7 +17754,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="39.950000000000003" customHeight="1">
+    <row r="8" ht="39.950000000000003" customHeight="1">
       <c r="A8" s="3" t="s">
         <v>111</v>
       </c>
@@ -17618,7 +17792,7 @@
         <v>893</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="39.950000000000003" customHeight="1">
+    <row r="9" ht="39.950000000000003" customHeight="1">
       <c r="A9" s="3" t="s">
         <v>134</v>
       </c>
@@ -17656,7 +17830,7 @@
         <v>888</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="270">
+    <row r="10" ht="270">
       <c r="A10" s="3" t="s">
         <v>98</v>
       </c>
@@ -17694,7 +17868,7 @@
         <v>1199</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="300">
+    <row r="11" ht="300">
       <c r="A11" s="3" t="s">
         <v>325</v>
       </c>
@@ -17732,7 +17906,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="345">
+    <row r="12" ht="345">
       <c r="A12" s="3" t="s">
         <v>350</v>
       </c>
@@ -17770,7 +17944,7 @@
         <v>1201</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="330">
+    <row r="13" ht="330">
       <c r="A13" s="3" t="s">
         <v>139</v>
       </c>
@@ -17808,7 +17982,7 @@
         <v>1202</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="180">
+    <row r="14" ht="180">
       <c r="A14" s="3" t="s">
         <v>248</v>
       </c>
@@ -17846,7 +18020,7 @@
         <v>1203</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="315">
+    <row r="15" ht="315">
       <c r="A15" s="3" t="s">
         <v>224</v>
       </c>
@@ -17881,7 +18055,7 @@
         <v>1204</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="375">
+    <row r="16" ht="375">
       <c r="A16" s="3" t="s">
         <v>87</v>
       </c>
@@ -17913,7 +18087,7 @@
         <v>1205</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="300">
+    <row r="17" ht="300">
       <c r="A17" s="3" t="s">
         <v>165</v>
       </c>
@@ -17951,7 +18125,7 @@
         <v>1206</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="300">
+    <row r="18" ht="300">
       <c r="A18" s="3" t="s">
         <v>90</v>
       </c>
@@ -17989,7 +18163,7 @@
         <v>1207</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="39.950000000000003" customHeight="1">
+    <row r="19" ht="39.950000000000003" customHeight="1">
       <c r="A19" s="3" t="s">
         <v>186</v>
       </c>
@@ -18027,7 +18201,7 @@
         <v>897</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="285">
+    <row r="20" ht="285">
       <c r="A20" s="3" t="s">
         <v>142</v>
       </c>
@@ -18065,7 +18239,7 @@
         <v>1208</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="225">
+    <row r="21" ht="225">
       <c r="A21" s="3" t="s">
         <v>84</v>
       </c>
@@ -18103,7 +18277,7 @@
         <v>1209</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="405">
+    <row r="22" ht="405">
       <c r="A22" s="3" t="s">
         <v>118</v>
       </c>
@@ -18141,7 +18315,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="315">
+    <row r="23" ht="315">
       <c r="A23" s="3" t="s">
         <v>546</v>
       </c>
@@ -18179,7 +18353,7 @@
         <v>1211</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="405">
+    <row r="24" ht="405">
       <c r="A24" s="3" t="s">
         <v>314</v>
       </c>
@@ -18217,7 +18391,7 @@
         <v>1212</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="255">
+    <row r="25" ht="255">
       <c r="A25" s="3" t="s">
         <v>554</v>
       </c>
@@ -18255,7 +18429,7 @@
         <v>1213</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="330">
+    <row r="26" ht="330">
       <c r="A26" s="3" t="s">
         <v>106</v>
       </c>
@@ -18293,7 +18467,7 @@
         <v>1214</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="180">
+    <row r="27" ht="180">
       <c r="A27" s="3" t="s">
         <v>93</v>
       </c>
@@ -18331,7 +18505,7 @@
         <v>1215</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="225">
+    <row r="28" ht="225">
       <c r="A28" s="3" t="s">
         <v>127</v>
       </c>
@@ -18369,7 +18543,7 @@
         <v>1216</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="330">
+    <row r="29" ht="330">
       <c r="A29" s="3" t="s">
         <v>304</v>
       </c>
@@ -18407,7 +18581,7 @@
         <v>1217</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="240">
+    <row r="30" ht="240">
       <c r="A30" s="3" t="s">
         <v>305</v>
       </c>
@@ -18445,7 +18619,7 @@
         <v>1218</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="255">
+    <row r="31" ht="255">
       <c r="A31" s="6" t="s">
         <v>320</v>
       </c>
@@ -18483,7 +18657,7 @@
         <v>1219</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="39.950000000000003" customHeight="1">
+    <row r="32" ht="39.950000000000003" customHeight="1">
       <c r="A32" s="6" t="s">
         <v>257</v>
       </c>
@@ -18521,7 +18695,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="180">
+    <row r="33" ht="180">
       <c r="A33" s="6" t="s">
         <v>333</v>
       </c>
@@ -18559,7 +18733,7 @@
         <v>1220</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="300">
+    <row r="34" ht="300">
       <c r="A34" s="3" t="s">
         <v>204</v>
       </c>
@@ -18597,7 +18771,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="315">
+    <row r="35" ht="315">
       <c r="A35" s="3" t="s">
         <v>378</v>
       </c>
@@ -18635,7 +18809,7 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="44.25" customHeight="1">
+    <row r="36" ht="44.25" customHeight="1">
       <c r="A36" s="3" t="s">
         <v>398</v>
       </c>
@@ -18673,7 +18847,7 @@
         <v>898</v>
       </c>
     </row>
-    <row r="37" spans="1:12" ht="180">
+    <row r="37" ht="180">
       <c r="A37" s="3" t="s">
         <v>412</v>
       </c>
@@ -18711,7 +18885,7 @@
         <v>1215</v>
       </c>
     </row>
-    <row r="38" spans="1:12" ht="210">
+    <row r="38" ht="210">
       <c r="A38" s="3" t="s">
         <v>415</v>
       </c>
@@ -18749,7 +18923,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="39" spans="1:12" ht="195">
+    <row r="39" ht="195">
       <c r="A39" s="3" t="s">
         <v>417</v>
       </c>
@@ -18787,7 +18961,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="40" spans="1:12" ht="210">
+    <row r="40" ht="210">
       <c r="A40" s="3" t="s">
         <v>419</v>
       </c>
@@ -18825,7 +18999,7 @@
         <v>1225</v>
       </c>
     </row>
-    <row r="41" spans="1:12" ht="195">
+    <row r="41" ht="195">
       <c r="A41" s="3" t="s">
         <v>422</v>
       </c>
@@ -18863,7 +19037,7 @@
         <v>1226</v>
       </c>
     </row>
-    <row r="42" spans="1:12" ht="72" customHeight="1">
+    <row r="42" ht="72" customHeight="1">
       <c r="A42" s="10" t="s">
         <v>426</v>
       </c>
@@ -18901,7 +19075,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="43" spans="1:12" ht="195">
+    <row r="43" ht="195">
       <c r="A43" s="10" t="s">
         <v>443</v>
       </c>
@@ -18939,7 +19113,7 @@
         <v>1227</v>
       </c>
     </row>
-    <row r="44" spans="1:12" ht="180">
+    <row r="44" ht="180">
       <c r="A44" s="10" t="s">
         <v>623</v>
       </c>
@@ -18977,7 +19151,7 @@
         <v>1228</v>
       </c>
     </row>
-    <row r="45" spans="1:12" ht="180">
+    <row r="45" ht="180">
       <c r="A45" s="14" t="s">
         <v>627</v>
       </c>
@@ -19011,7 +19185,7 @@
         <v>1229</v>
       </c>
     </row>
-    <row r="46" spans="1:12" ht="240">
+    <row r="46" ht="240">
       <c r="A46" s="12" t="s">
         <v>632</v>
       </c>
@@ -19049,7 +19223,7 @@
         <v>1230</v>
       </c>
     </row>
-    <row r="47" spans="1:12" ht="195">
+    <row r="47" ht="195">
       <c r="A47" s="12" t="s">
         <v>637</v>
       </c>
@@ -19083,7 +19257,7 @@
         <v>1231</v>
       </c>
     </row>
-    <row r="48" spans="1:12" ht="180">
+    <row r="48" ht="180">
       <c r="A48" s="12" t="s">
         <v>642</v>
       </c>
@@ -19117,7 +19291,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="49" spans="1:12" ht="180">
+    <row r="49" ht="180">
       <c r="A49" s="12" t="s">
         <v>647</v>
       </c>
@@ -19151,7 +19325,7 @@
         <v>1233</v>
       </c>
     </row>
-    <row r="50" spans="1:12" ht="150">
+    <row r="50" ht="150">
       <c r="A50" s="12" t="s">
         <v>652</v>
       </c>
@@ -19189,7 +19363,7 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="51" spans="1:12" ht="285">
+    <row r="51" ht="285">
       <c r="A51" s="12" t="s">
         <v>657</v>
       </c>
@@ -19227,7 +19401,7 @@
         <v>1235</v>
       </c>
     </row>
-    <row r="52" spans="1:12" ht="409.5">
+    <row r="52" ht="409.5">
       <c r="A52" s="12" t="s">
         <v>661</v>
       </c>
@@ -19265,7 +19439,7 @@
         <v>1236</v>
       </c>
     </row>
-    <row r="53" spans="1:12" ht="225">
+    <row r="53" ht="225">
       <c r="A53" s="12" t="s">
         <v>665</v>
       </c>
@@ -19299,7 +19473,7 @@
         <v>1237</v>
       </c>
     </row>
-    <row r="54" spans="1:12" ht="165">
+    <row r="54" ht="165">
       <c r="A54" s="12" t="s">
         <v>669</v>
       </c>
@@ -19333,7 +19507,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="55" spans="1:12" ht="270">
+    <row r="55" ht="270">
       <c r="A55" s="12" t="s">
         <v>673</v>
       </c>
@@ -19367,7 +19541,7 @@
         <v>1239</v>
       </c>
     </row>
-    <row r="56" spans="1:12" ht="315">
+    <row r="56" ht="315">
       <c r="A56" s="12" t="s">
         <v>243</v>
       </c>
@@ -19401,7 +19575,7 @@
         <v>1240</v>
       </c>
     </row>
-    <row r="57" spans="1:12" ht="150">
+    <row r="57" ht="150">
       <c r="A57" s="12" t="s">
         <v>680</v>
       </c>
@@ -19435,7 +19609,7 @@
         <v>1241</v>
       </c>
     </row>
-    <row r="58" spans="1:12" ht="240">
+    <row r="58" ht="240">
       <c r="A58" s="12" t="s">
         <v>686</v>
       </c>
@@ -19469,7 +19643,7 @@
         <v>1242</v>
       </c>
     </row>
-    <row r="59" spans="1:12" ht="240">
+    <row r="59" ht="240">
       <c r="A59" s="12" t="s">
         <v>692</v>
       </c>
@@ -19503,7 +19677,7 @@
         <v>1243</v>
       </c>
     </row>
-    <row r="60" spans="1:12" ht="120">
+    <row r="60" ht="120">
       <c r="A60" s="12" t="s">
         <v>696</v>
       </c>
@@ -19537,7 +19711,7 @@
         <v>1244</v>
       </c>
     </row>
-    <row r="61" spans="1:12" ht="120">
+    <row r="61" ht="120">
       <c r="A61" s="3" t="s">
         <v>700</v>
       </c>
@@ -19571,7 +19745,7 @@
         <v>1245</v>
       </c>
     </row>
-    <row r="62" spans="1:12" ht="225">
+    <row r="62" ht="225">
       <c r="A62" s="10" t="s">
         <v>705</v>
       </c>
@@ -19605,7 +19779,7 @@
         <v>1246</v>
       </c>
     </row>
-    <row r="63" spans="1:12" ht="315">
+    <row r="63" ht="315">
       <c r="A63" s="17" t="s">
         <v>710</v>
       </c>
@@ -19637,7 +19811,7 @@
         <v>1247</v>
       </c>
     </row>
-    <row r="64" spans="1:12" ht="90">
+    <row r="64" ht="90">
       <c r="A64" s="18" t="s">
         <v>715</v>
       </c>
@@ -19669,7 +19843,7 @@
         <v>1248</v>
       </c>
     </row>
-    <row r="65" spans="1:13" ht="135">
+    <row r="65" ht="135">
       <c r="A65" s="18" t="s">
         <v>719</v>
       </c>
@@ -19701,7 +19875,7 @@
         <v>1249</v>
       </c>
     </row>
-    <row r="66" spans="1:13" ht="105">
+    <row r="66" ht="105">
       <c r="A66" s="18" t="s">
         <v>723</v>
       </c>
@@ -19733,7 +19907,7 @@
         <v>1250</v>
       </c>
     </row>
-    <row r="67" spans="1:13" ht="135">
+    <row r="67" ht="135">
       <c r="A67" s="18" t="s">
         <v>727</v>
       </c>
@@ -19765,7 +19939,7 @@
         <v>1251</v>
       </c>
     </row>
-    <row r="68" spans="1:13" ht="135">
+    <row r="68" ht="135">
       <c r="A68" s="18" t="s">
         <v>731</v>
       </c>
@@ -19797,7 +19971,7 @@
         <v>1252</v>
       </c>
     </row>
-    <row r="69" spans="1:13" ht="409.5">
+    <row r="69" ht="409.5">
       <c r="A69" s="28" t="s">
         <v>189</v>
       </c>
@@ -19835,7 +20009,7 @@
         <v>1253</v>
       </c>
     </row>
-    <row r="70" spans="1:13" ht="409.6" customHeight="1">
+    <row r="70" ht="409.6" customHeight="1">
       <c r="A70" s="116" t="s">
         <v>180</v>
       </c>
@@ -19876,7 +20050,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="71" spans="1:13" ht="105">
+    <row r="71" ht="105">
       <c r="A71" s="3" t="s">
         <v>862</v>
       </c>
@@ -19914,7 +20088,7 @@
         <v>903</v>
       </c>
     </row>
-    <row r="72" spans="1:13" ht="150">
+    <row r="72" ht="150">
       <c r="A72" s="3" t="s">
         <v>870</v>
       </c>
@@ -19952,7 +20126,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="73" spans="1:13" ht="75">
+    <row r="73" ht="75">
       <c r="A73" s="3" t="s">
         <v>911</v>
       </c>
@@ -19984,7 +20158,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="74" spans="1:13" ht="120">
+    <row r="74" ht="120">
       <c r="A74" s="82" t="s">
         <v>933</v>
       </c>
@@ -20016,7 +20190,7 @@
         <v>937</v>
       </c>
     </row>
-    <row r="75" spans="1:13" ht="135">
+    <row r="75" ht="135">
       <c r="A75" s="84" t="s">
         <v>943</v>
       </c>
@@ -20054,7 +20228,7 @@
         <v>1254</v>
       </c>
     </row>
-    <row r="76" spans="1:13" ht="150">
+    <row r="76" ht="150">
       <c r="A76" s="86" t="s">
         <v>949</v>
       </c>
@@ -20092,7 +20266,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="77" spans="1:13" ht="360">
+    <row r="77" ht="360">
       <c r="A77" s="89" t="s">
         <v>964</v>
       </c>
@@ -20130,7 +20304,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="78" spans="1:13" ht="135">
+    <row r="78" ht="135">
       <c r="A78" s="89" t="s">
         <v>972</v>
       </c>
@@ -20168,7 +20342,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="79" spans="1:13" ht="120">
+    <row r="79" ht="120">
       <c r="A79" s="88" t="s">
         <v>1013</v>
       </c>
@@ -20206,7 +20380,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="80" spans="1:13" ht="120">
+    <row r="80" ht="120">
       <c r="A80" s="89" t="s">
         <v>1040</v>
       </c>
@@ -20238,7 +20412,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="81" spans="1:12" ht="150">
+    <row r="81" ht="150">
       <c r="A81" s="89" t="s">
         <v>1097</v>
       </c>
@@ -20276,7 +20450,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="82" spans="1:12">
+    <row r="82">
       <c r="A82" t="s">
         <v>1266</v>
       </c>
@@ -20287,7 +20461,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="83" spans="1:12">
+    <row r="83">
       <c r="A83" t="s">
         <v>1268</v>
       </c>
@@ -20298,7 +20472,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="84" spans="1:12">
+    <row r="84">
       <c r="A84" t="s">
         <v>1269</v>
       </c>
@@ -20309,7 +20483,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="85" spans="1:12">
+    <row r="85">
       <c r="A85" t="s">
         <v>1288</v>
       </c>
@@ -20320,7 +20494,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="86" spans="1:12" ht="105">
+    <row r="86" ht="105">
       <c r="A86" t="s">
         <v>1543</v>
       </c>
@@ -20354,7 +20528,7 @@
         <v>1547</v>
       </c>
     </row>
-    <row r="87" spans="1:12">
+    <row r="87">
       <c r="A87" t="s">
         <v>1549</v>
       </c>
@@ -20363,6 +20537,115 @@
       </c>
       <c r="C87" t="s">
         <v>1267</v>
+      </c>
+    </row>
+    <row r="88" ht="360">
+      <c r="A88" s="89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UPPA</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fac</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fac</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aucune</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aucune</t>
+        </is>
+      </c>
+      <c r="F88" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TB + BCPST</t>
+        </is>
+      </c>
+      <c r="G88" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L’Université de Pau et des Pays de l’Adour (UPPA) propose, au sein de son collège Sciences et technologies pour l’énergie et l’environnement, des licences en sciences de la vie, sciences de la Terre et physique-chimie sur ses campus de Pau et d’Anglet. À Anglet, la licence de sciences de la vie propose un parcours « biologie des organismes » ; à Pau, la L3 propose les parcours biologie générale et sciences de la Terre, et biologie cellulaire et moléculaire.</t>
+        </is>
+      </c>
+      <c r="H88" s="89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Anglet</t>
+        </is>
+      </c>
+      <c r="I88" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.univ-pau.fr</t>
+        </is>
+      </c>
+      <c r="J88" s="85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[43.4749, -1.5120]</t>
+        </is>
+      </c>
+      <c r="K88" s="36"/>
+      <c r="L88" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sciences de la vie ; Biologie des organismes ; Sciences de la Terre ; Physique-chimie ; Licence ; Master ; Pau ; Anglet ; Poursuite d’études sur dossier</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sup'Véto</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hors carte</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hors carte</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IFSI</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hors carte</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hors carte</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5/2</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hors carte</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hors carte</t>
+        </is>
       </c>
     </row>
   </sheetData>
